--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="98">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,60 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>CONMEBOL Copa Libertadores</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>00:35:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Nautico PE</t>
+  </si>
+  <si>
+    <t>Univ Catolica (Chile)</t>
+  </si>
+  <si>
+    <t>Tolima</t>
+  </si>
+  <si>
+    <t>Goias</t>
+  </si>
+  <si>
+    <t>Atletico Madrid</t>
+  </si>
+  <si>
+    <t>Ceara SC Fortaleza</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Independiente (Ecu)</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>Malaga</t>
+  </si>
+  <si>
+    <t>2026-08-17 00:56:53</t>
   </si>
 </sst>
 </file>
@@ -585,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -830,6 +884,1216 @@
         <v>79</v>
       </c>
     </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2">
+        <v>2.28</v>
+      </c>
+      <c r="G2">
+        <v>2.3</v>
+      </c>
+      <c r="H2">
+        <v>3.85</v>
+      </c>
+      <c r="I2">
+        <v>3.9</v>
+      </c>
+      <c r="J2">
+        <v>3.3</v>
+      </c>
+      <c r="K2">
+        <v>3.35</v>
+      </c>
+      <c r="L2">
+        <v>1.42</v>
+      </c>
+      <c r="M2">
+        <v>1.09</v>
+      </c>
+      <c r="N2">
+        <v>3.3</v>
+      </c>
+      <c r="O2">
+        <v>1.37</v>
+      </c>
+      <c r="P2">
+        <v>1.71</v>
+      </c>
+      <c r="Q2">
+        <v>2.16</v>
+      </c>
+      <c r="R2">
+        <v>1.26</v>
+      </c>
+      <c r="S2">
+        <v>3.9</v>
+      </c>
+      <c r="T2">
+        <v>1.8</v>
+      </c>
+      <c r="U2">
+        <v>1.89</v>
+      </c>
+      <c r="V2">
+        <v>1.34</v>
+      </c>
+      <c r="W2">
+        <v>1.77</v>
+      </c>
+      <c r="X2">
+        <v>13.5</v>
+      </c>
+      <c r="Y2">
+        <v>13</v>
+      </c>
+      <c r="Z2">
+        <v>28</v>
+      </c>
+      <c r="AA2">
+        <v>90</v>
+      </c>
+      <c r="AB2">
+        <v>10</v>
+      </c>
+      <c r="AC2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD2">
+        <v>16.5</v>
+      </c>
+      <c r="AE2">
+        <v>60</v>
+      </c>
+      <c r="AF2">
+        <v>14.5</v>
+      </c>
+      <c r="AG2">
+        <v>11.5</v>
+      </c>
+      <c r="AH2">
+        <v>22</v>
+      </c>
+      <c r="AI2">
+        <v>75</v>
+      </c>
+      <c r="AJ2">
+        <v>36</v>
+      </c>
+      <c r="AK2">
+        <v>29</v>
+      </c>
+      <c r="AL2">
+        <v>48</v>
+      </c>
+      <c r="AM2">
+        <v>140</v>
+      </c>
+      <c r="AN2">
+        <v>24</v>
+      </c>
+      <c r="AO2">
+        <v>70</v>
+      </c>
+      <c r="AP2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ2">
+        <v>10.5</v>
+      </c>
+      <c r="AR2">
+        <v>19</v>
+      </c>
+      <c r="AS2">
+        <v>6.2</v>
+      </c>
+      <c r="AT2">
+        <v>7.6</v>
+      </c>
+      <c r="AU2">
+        <v>6.4</v>
+      </c>
+      <c r="AV2">
+        <v>13</v>
+      </c>
+      <c r="AW2">
+        <v>36</v>
+      </c>
+      <c r="AX2">
+        <v>11.5</v>
+      </c>
+      <c r="AY2">
+        <v>9.4</v>
+      </c>
+      <c r="AZ2">
+        <v>16</v>
+      </c>
+      <c r="BA2">
+        <v>6</v>
+      </c>
+      <c r="BB2">
+        <v>5.6</v>
+      </c>
+      <c r="BC2">
+        <v>5.4</v>
+      </c>
+      <c r="BD2">
+        <v>5.8</v>
+      </c>
+      <c r="BE2">
+        <v>6.4</v>
+      </c>
+      <c r="BF2">
+        <v>19</v>
+      </c>
+      <c r="BG2">
+        <v>6</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.04</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.04</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.04</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.04</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.04</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.04</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.04</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.04</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.04</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.04</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3">
+        <v>2.66</v>
+      </c>
+      <c r="G3">
+        <v>2.9</v>
+      </c>
+      <c r="H3">
+        <v>2.96</v>
+      </c>
+      <c r="I3">
+        <v>3.4</v>
+      </c>
+      <c r="J3">
+        <v>2.98</v>
+      </c>
+      <c r="K3">
+        <v>3.25</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>2.3</v>
+      </c>
+      <c r="O3">
+        <v>1.47</v>
+      </c>
+      <c r="P3">
+        <v>1.43</v>
+      </c>
+      <c r="Q3">
+        <v>2.46</v>
+      </c>
+      <c r="R3">
+        <v>1.17</v>
+      </c>
+      <c r="S3">
+        <v>4.5</v>
+      </c>
+      <c r="T3">
+        <v>1.11</v>
+      </c>
+      <c r="U3">
+        <v>1.11</v>
+      </c>
+      <c r="V3">
+        <v>1.42</v>
+      </c>
+      <c r="W3">
+        <v>1.53</v>
+      </c>
+      <c r="X3">
+        <v>10.5</v>
+      </c>
+      <c r="Y3">
+        <v>11</v>
+      </c>
+      <c r="Z3">
+        <v>23</v>
+      </c>
+      <c r="AA3">
+        <v>70</v>
+      </c>
+      <c r="AB3">
+        <v>10</v>
+      </c>
+      <c r="AC3">
+        <v>8.4</v>
+      </c>
+      <c r="AD3">
+        <v>17</v>
+      </c>
+      <c r="AE3">
+        <v>55</v>
+      </c>
+      <c r="AF3">
+        <v>20</v>
+      </c>
+      <c r="AG3">
+        <v>16</v>
+      </c>
+      <c r="AH3">
+        <v>26</v>
+      </c>
+      <c r="AI3">
+        <v>80</v>
+      </c>
+      <c r="AJ3">
+        <v>55</v>
+      </c>
+      <c r="AK3">
+        <v>46</v>
+      </c>
+      <c r="AL3">
+        <v>75</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>55</v>
+      </c>
+      <c r="AO3">
+        <v>65</v>
+      </c>
+      <c r="AP3">
+        <v>3.25</v>
+      </c>
+      <c r="AQ3">
+        <v>7.8</v>
+      </c>
+      <c r="AR3">
+        <v>14.5</v>
+      </c>
+      <c r="AS3">
+        <v>4.4</v>
+      </c>
+      <c r="AT3">
+        <v>7.4</v>
+      </c>
+      <c r="AU3">
+        <v>5.9</v>
+      </c>
+      <c r="AV3">
+        <v>10.5</v>
+      </c>
+      <c r="AW3">
+        <v>4.3</v>
+      </c>
+      <c r="AX3">
+        <v>13</v>
+      </c>
+      <c r="AY3">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3">
+        <v>17.5</v>
+      </c>
+      <c r="BA3">
+        <v>4.4</v>
+      </c>
+      <c r="BB3">
+        <v>4.3</v>
+      </c>
+      <c r="BC3">
+        <v>4.3</v>
+      </c>
+      <c r="BD3">
+        <v>4.4</v>
+      </c>
+      <c r="BE3">
+        <v>4.7</v>
+      </c>
+      <c r="BF3">
+        <v>4.3</v>
+      </c>
+      <c r="BG3">
+        <v>4.4</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.04</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.04</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.04</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.04</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.04</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.04</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.04</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.04</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.04</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.04</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4">
+        <v>2.98</v>
+      </c>
+      <c r="G4">
+        <v>3.45</v>
+      </c>
+      <c r="H4">
+        <v>2.54</v>
+      </c>
+      <c r="I4">
+        <v>2.78</v>
+      </c>
+      <c r="J4">
+        <v>3.05</v>
+      </c>
+      <c r="K4">
+        <v>3.4</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.1</v>
+      </c>
+      <c r="N4">
+        <v>2.98</v>
+      </c>
+      <c r="O4">
+        <v>1.44</v>
+      </c>
+      <c r="P4">
+        <v>1.67</v>
+      </c>
+      <c r="Q4">
+        <v>2.32</v>
+      </c>
+      <c r="R4">
+        <v>1.25</v>
+      </c>
+      <c r="S4">
+        <v>4.4</v>
+      </c>
+      <c r="T4">
+        <v>1.87</v>
+      </c>
+      <c r="U4">
+        <v>1.93</v>
+      </c>
+      <c r="V4">
+        <v>1.56</v>
+      </c>
+      <c r="W4">
+        <v>1.4</v>
+      </c>
+      <c r="X4">
+        <v>11</v>
+      </c>
+      <c r="Y4">
+        <v>9.6</v>
+      </c>
+      <c r="Z4">
+        <v>17.5</v>
+      </c>
+      <c r="AA4">
+        <v>44</v>
+      </c>
+      <c r="AB4">
+        <v>11</v>
+      </c>
+      <c r="AC4">
+        <v>7.6</v>
+      </c>
+      <c r="AD4">
+        <v>13</v>
+      </c>
+      <c r="AE4">
+        <v>36</v>
+      </c>
+      <c r="AF4">
+        <v>22</v>
+      </c>
+      <c r="AG4">
+        <v>15</v>
+      </c>
+      <c r="AH4">
+        <v>21</v>
+      </c>
+      <c r="AI4">
+        <v>55</v>
+      </c>
+      <c r="AJ4">
+        <v>65</v>
+      </c>
+      <c r="AK4">
+        <v>46</v>
+      </c>
+      <c r="AL4">
+        <v>65</v>
+      </c>
+      <c r="AM4">
+        <v>150</v>
+      </c>
+      <c r="AN4">
+        <v>50</v>
+      </c>
+      <c r="AO4">
+        <v>36</v>
+      </c>
+      <c r="AP4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ4">
+        <v>7.8</v>
+      </c>
+      <c r="AR4">
+        <v>13.5</v>
+      </c>
+      <c r="AS4">
+        <v>7.2</v>
+      </c>
+      <c r="AT4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU4">
+        <v>6.2</v>
+      </c>
+      <c r="AV4">
+        <v>10.5</v>
+      </c>
+      <c r="AW4">
+        <v>7</v>
+      </c>
+      <c r="AX4">
+        <v>17.5</v>
+      </c>
+      <c r="AY4">
+        <v>11.5</v>
+      </c>
+      <c r="AZ4">
+        <v>17</v>
+      </c>
+      <c r="BA4">
+        <v>7.6</v>
+      </c>
+      <c r="BB4">
+        <v>7.6</v>
+      </c>
+      <c r="BC4">
+        <v>7.4</v>
+      </c>
+      <c r="BD4">
+        <v>7.6</v>
+      </c>
+      <c r="BE4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF4">
+        <v>7.4</v>
+      </c>
+      <c r="BG4">
+        <v>7</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.04</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.04</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.04</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.04</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.04</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.04</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.04</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.04</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.04</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.04</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5">
+        <v>2.38</v>
+      </c>
+      <c r="G5">
+        <v>2.58</v>
+      </c>
+      <c r="H5">
+        <v>3.55</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3.05</v>
+      </c>
+      <c r="K5">
+        <v>3.35</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>2.2</v>
+      </c>
+      <c r="O5">
+        <v>1.47</v>
+      </c>
+      <c r="P5">
+        <v>1.38</v>
+      </c>
+      <c r="Q5">
+        <v>2.66</v>
+      </c>
+      <c r="R5">
+        <v>1.17</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
+        <v>1.81</v>
+      </c>
+      <c r="U5">
+        <v>1.53</v>
+      </c>
+      <c r="V5">
+        <v>1.33</v>
+      </c>
+      <c r="W5">
+        <v>1.64</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>13</v>
+      </c>
+      <c r="Z5">
+        <v>34</v>
+      </c>
+      <c r="AA5">
+        <v>100</v>
+      </c>
+      <c r="AB5">
+        <v>10</v>
+      </c>
+      <c r="AC5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD5">
+        <v>23</v>
+      </c>
+      <c r="AE5">
+        <v>90</v>
+      </c>
+      <c r="AF5">
+        <v>20</v>
+      </c>
+      <c r="AG5">
+        <v>18</v>
+      </c>
+      <c r="AH5">
+        <v>950</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>55</v>
+      </c>
+      <c r="AK5">
+        <v>50</v>
+      </c>
+      <c r="AL5">
+        <v>95</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>60</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>2.34</v>
+      </c>
+      <c r="AQ5">
+        <v>6.2</v>
+      </c>
+      <c r="AR5">
+        <v>15</v>
+      </c>
+      <c r="AS5">
+        <v>2.28</v>
+      </c>
+      <c r="AT5">
+        <v>4.9</v>
+      </c>
+      <c r="AU5">
+        <v>4.7</v>
+      </c>
+      <c r="AV5">
+        <v>10.5</v>
+      </c>
+      <c r="AW5">
+        <v>2.28</v>
+      </c>
+      <c r="AX5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ5">
+        <v>15</v>
+      </c>
+      <c r="BA5">
+        <v>2.34</v>
+      </c>
+      <c r="BB5">
+        <v>2.24</v>
+      </c>
+      <c r="BC5">
+        <v>23</v>
+      </c>
+      <c r="BD5">
+        <v>2.28</v>
+      </c>
+      <c r="BE5">
+        <v>2.34</v>
+      </c>
+      <c r="BF5">
+        <v>2.26</v>
+      </c>
+      <c r="BG5">
+        <v>2.34</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.71</v>
+      </c>
+      <c r="BJ5">
+        <v>16</v>
+      </c>
+      <c r="BK5">
+        <v>1.55</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.71</v>
+      </c>
+      <c r="BN5">
+        <v>6.8</v>
+      </c>
+      <c r="BO5">
+        <v>3.55</v>
+      </c>
+      <c r="BP5">
+        <v>30</v>
+      </c>
+      <c r="BQ5">
+        <v>1.62</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.67</v>
+      </c>
+      <c r="BT5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU5">
+        <v>4.4</v>
+      </c>
+      <c r="BV5">
+        <v>50</v>
+      </c>
+      <c r="BW5">
+        <v>1.66</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.68</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.68</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6">
+        <v>1.33</v>
+      </c>
+      <c r="G6">
+        <v>1.35</v>
+      </c>
+      <c r="H6">
+        <v>11.5</v>
+      </c>
+      <c r="I6">
+        <v>13</v>
+      </c>
+      <c r="J6">
+        <v>5.8</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>1.28</v>
+      </c>
+      <c r="M6">
+        <v>1.05</v>
+      </c>
+      <c r="N6">
+        <v>4.5</v>
+      </c>
+      <c r="O6">
+        <v>1.27</v>
+      </c>
+      <c r="P6">
+        <v>2.2</v>
+      </c>
+      <c r="Q6">
+        <v>1.77</v>
+      </c>
+      <c r="R6">
+        <v>1.47</v>
+      </c>
+      <c r="S6">
+        <v>2.94</v>
+      </c>
+      <c r="T6">
+        <v>2.28</v>
+      </c>
+      <c r="U6">
+        <v>1.73</v>
+      </c>
+      <c r="V6">
+        <v>1.08</v>
+      </c>
+      <c r="W6">
+        <v>3.9</v>
+      </c>
+      <c r="X6">
+        <v>19</v>
+      </c>
+      <c r="Y6">
+        <v>36</v>
+      </c>
+      <c r="Z6">
+        <v>130</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>8.4</v>
+      </c>
+      <c r="AC6">
+        <v>13.5</v>
+      </c>
+      <c r="AD6">
+        <v>48</v>
+      </c>
+      <c r="AE6">
+        <v>260</v>
+      </c>
+      <c r="AF6">
+        <v>7.6</v>
+      </c>
+      <c r="AG6">
+        <v>10.5</v>
+      </c>
+      <c r="AH6">
+        <v>38</v>
+      </c>
+      <c r="AI6">
+        <v>190</v>
+      </c>
+      <c r="AJ6">
+        <v>10</v>
+      </c>
+      <c r="AK6">
+        <v>15</v>
+      </c>
+      <c r="AL6">
+        <v>46</v>
+      </c>
+      <c r="AM6">
+        <v>250</v>
+      </c>
+      <c r="AN6">
+        <v>5.5</v>
+      </c>
+      <c r="AO6">
+        <v>460</v>
+      </c>
+      <c r="AP6">
+        <v>16.5</v>
+      </c>
+      <c r="AQ6">
+        <v>20</v>
+      </c>
+      <c r="AR6">
+        <v>38</v>
+      </c>
+      <c r="AS6">
+        <v>17.5</v>
+      </c>
+      <c r="AT6">
+        <v>7.6</v>
+      </c>
+      <c r="AU6">
+        <v>12</v>
+      </c>
+      <c r="AV6">
+        <v>34</v>
+      </c>
+      <c r="AW6">
+        <v>48</v>
+      </c>
+      <c r="AX6">
+        <v>6.8</v>
+      </c>
+      <c r="AY6">
+        <v>10</v>
+      </c>
+      <c r="AZ6">
+        <v>23</v>
+      </c>
+      <c r="BA6">
+        <v>46</v>
+      </c>
+      <c r="BB6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC6">
+        <v>13</v>
+      </c>
+      <c r="BD6">
+        <v>29</v>
+      </c>
+      <c r="BE6">
+        <v>50</v>
+      </c>
+      <c r="BF6">
+        <v>5.2</v>
+      </c>
+      <c r="BG6">
+        <v>95</v>
+      </c>
+      <c r="BH6">
+        <v>4.1</v>
+      </c>
+      <c r="BI6">
+        <v>3.05</v>
+      </c>
+      <c r="BJ6">
+        <v>14</v>
+      </c>
+      <c r="BK6">
+        <v>5.9</v>
+      </c>
+      <c r="BL6">
+        <v>210</v>
+      </c>
+      <c r="BM6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN6">
+        <v>3.75</v>
+      </c>
+      <c r="BO6">
+        <v>2.86</v>
+      </c>
+      <c r="BP6">
+        <v>7.8</v>
+      </c>
+      <c r="BQ6">
+        <v>5.6</v>
+      </c>
+      <c r="BR6">
+        <v>28</v>
+      </c>
+      <c r="BS6">
+        <v>7.4</v>
+      </c>
+      <c r="BT6">
+        <v>16</v>
+      </c>
+      <c r="BU6">
+        <v>6.2</v>
+      </c>
+      <c r="BV6">
+        <v>130</v>
+      </c>
+      <c r="BW6">
+        <v>9.4</v>
+      </c>
+      <c r="BX6">
+        <v>120</v>
+      </c>
+      <c r="BY6">
+        <v>9.4</v>
+      </c>
+      <c r="BZ6">
+        <v>13.5</v>
+      </c>
+      <c r="CA6">
+        <v>5.8</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -307,7 +307,7 @@
     <t>Malaga</t>
   </si>
   <si>
-    <t>2026-08-17 00:56:53</t>
+    <t>2026-08-17 03:05:56</t>
   </si>
 </sst>
 </file>
@@ -901,16 +901,16 @@
         <v>92</v>
       </c>
       <c r="F2">
+        <v>2.22</v>
+      </c>
+      <c r="G2">
         <v>2.28</v>
-      </c>
-      <c r="G2">
-        <v>2.3</v>
       </c>
       <c r="H2">
         <v>3.85</v>
       </c>
       <c r="I2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>3.3</v>
@@ -919,7 +919,7 @@
         <v>3.35</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M2">
         <v>1.09</v>
@@ -934,31 +934,31 @@
         <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
         <v>1.26</v>
       </c>
       <c r="S2">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
         <v>1.8</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X2">
         <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
         <v>28</v>
@@ -967,13 +967,13 @@
         <v>90</v>
       </c>
       <c r="AB2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE2">
         <v>60</v>
@@ -985,7 +985,7 @@
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI2">
         <v>75</v>
@@ -997,19 +997,19 @@
         <v>29</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO2">
         <v>70</v>
       </c>
       <c r="AP2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
         <v>10.5</v>
@@ -1018,7 +1018,7 @@
         <v>19</v>
       </c>
       <c r="AS2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT2">
         <v>7.6</v>
@@ -1027,7 +1027,7 @@
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW2">
         <v>36</v>
@@ -1039,88 +1039,88 @@
         <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB2">
+        <v>5.9</v>
+      </c>
+      <c r="BC2">
+        <v>19.5</v>
+      </c>
+      <c r="BD2">
+        <v>34</v>
+      </c>
+      <c r="BE2">
+        <v>6.8</v>
+      </c>
+      <c r="BF2">
+        <v>18</v>
+      </c>
+      <c r="BG2">
+        <v>6.4</v>
+      </c>
+      <c r="BH2">
+        <v>3.5</v>
+      </c>
+      <c r="BI2">
+        <v>2.62</v>
+      </c>
+      <c r="BJ2">
+        <v>11.5</v>
+      </c>
+      <c r="BK2">
+        <v>3.95</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>5.8</v>
+      </c>
+      <c r="BN2">
         <v>5.6</v>
       </c>
-      <c r="BC2">
+      <c r="BO2">
+        <v>4</v>
+      </c>
+      <c r="BP2">
+        <v>20</v>
+      </c>
+      <c r="BQ2">
+        <v>4.6</v>
+      </c>
+      <c r="BR2">
+        <v>40</v>
+      </c>
+      <c r="BS2">
+        <v>5.3</v>
+      </c>
+      <c r="BT2">
+        <v>7.6</v>
+      </c>
+      <c r="BU2">
         <v>5.4</v>
       </c>
-      <c r="BD2">
-        <v>5.8</v>
-      </c>
-      <c r="BE2">
-        <v>6.4</v>
-      </c>
-      <c r="BF2">
-        <v>19</v>
-      </c>
-      <c r="BG2">
-        <v>6</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.04</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>1.04</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.04</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>1.04</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>1.04</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.04</v>
-      </c>
-      <c r="BT2">
-        <v>1000</v>
-      </c>
-      <c r="BU2">
-        <v>1.04</v>
-      </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB2" t="s">
         <v>97</v>
@@ -1143,16 +1143,16 @@
         <v>93</v>
       </c>
       <c r="F3">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G3">
         <v>2.9</v>
       </c>
       <c r="H3">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I3">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
         <v>2.98</v>
@@ -1164,43 +1164,43 @@
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="P3">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.53</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3">
         <v>23</v>
@@ -1209,25 +1209,25 @@
         <v>70</v>
       </c>
       <c r="AB3">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AC3">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AE3">
         <v>55</v>
       </c>
       <c r="AF3">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI3">
         <v>80</v>
@@ -1242,7 +1242,7 @@
         <v>75</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN3">
         <v>55</v>
@@ -1251,118 +1251,118 @@
         <v>65</v>
       </c>
       <c r="AP3">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS3">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
+        <v>32</v>
+      </c>
+      <c r="AX3">
+        <v>15</v>
+      </c>
+      <c r="AY3">
+        <v>11.5</v>
+      </c>
+      <c r="AZ3">
+        <v>18</v>
+      </c>
+      <c r="BA3">
+        <v>11.5</v>
+      </c>
+      <c r="BB3">
+        <v>32</v>
+      </c>
+      <c r="BC3">
+        <v>29</v>
+      </c>
+      <c r="BD3">
+        <v>42</v>
+      </c>
+      <c r="BE3">
+        <v>13</v>
+      </c>
+      <c r="BF3">
+        <v>27</v>
+      </c>
+      <c r="BG3">
+        <v>40</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.73</v>
+      </c>
+      <c r="BJ3">
+        <v>15</v>
+      </c>
+      <c r="BK3">
+        <v>1.55</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.73</v>
+      </c>
+      <c r="BN3">
+        <v>7.6</v>
+      </c>
+      <c r="BO3">
+        <v>3.9</v>
+      </c>
+      <c r="BP3">
+        <v>34</v>
+      </c>
+      <c r="BQ3">
+        <v>1.65</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.69</v>
+      </c>
+      <c r="BT3">
+        <v>8</v>
+      </c>
+      <c r="BU3">
         <v>4.3</v>
       </c>
-      <c r="AX3">
-        <v>13</v>
-      </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
-        <v>17.5</v>
-      </c>
-      <c r="BA3">
-        <v>4.4</v>
-      </c>
-      <c r="BB3">
-        <v>4.3</v>
-      </c>
-      <c r="BC3">
-        <v>4.3</v>
-      </c>
-      <c r="BD3">
-        <v>4.4</v>
-      </c>
-      <c r="BE3">
-        <v>4.7</v>
-      </c>
-      <c r="BF3">
-        <v>4.3</v>
-      </c>
-      <c r="BG3">
-        <v>4.4</v>
-      </c>
-      <c r="BH3">
-        <v>1000</v>
-      </c>
-      <c r="BI3">
-        <v>1.04</v>
-      </c>
-      <c r="BJ3">
-        <v>1000</v>
-      </c>
-      <c r="BK3">
-        <v>1.04</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>1.04</v>
-      </c>
-      <c r="BN3">
-        <v>1000</v>
-      </c>
-      <c r="BO3">
-        <v>1.04</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>1.04</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>1.04</v>
-      </c>
-      <c r="BT3">
-        <v>1000</v>
-      </c>
-      <c r="BU3">
-        <v>1.04</v>
-      </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="CB3" t="s">
         <v>97</v>
@@ -1388,7 +1388,7 @@
         <v>2.98</v>
       </c>
       <c r="G4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
         <v>2.54</v>
@@ -1427,7 +1427,7 @@
         <v>4.4</v>
       </c>
       <c r="T4">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U4">
         <v>1.93</v>
@@ -1436,7 +1436,7 @@
         <v>1.56</v>
       </c>
       <c r="W4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X4">
         <v>11</v>
@@ -1475,10 +1475,10 @@
         <v>55</v>
       </c>
       <c r="AJ4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL4">
         <v>65</v>
@@ -1502,7 +1502,7 @@
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT4">
         <v>8.800000000000001</v>
@@ -1514,7 +1514,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX4">
         <v>17.5</v>
@@ -1529,22 +1529,22 @@
         <v>7.6</v>
       </c>
       <c r="BB4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC4">
         <v>7.4</v>
       </c>
       <c r="BD4">
+        <v>7.8</v>
+      </c>
+      <c r="BE4">
+        <v>8.4</v>
+      </c>
+      <c r="BF4">
         <v>7.6</v>
       </c>
-      <c r="BE4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF4">
-        <v>7.4</v>
-      </c>
       <c r="BG4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1630,10 +1630,10 @@
         <v>2.38</v>
       </c>
       <c r="G5">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H5">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I5">
         <v>4</v>
@@ -1645,19 +1645,19 @@
         <v>3.35</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="O5">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P5">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="Q5">
         <v>2.66</v>
@@ -1678,7 +1678,7 @@
         <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1729,7 +1729,7 @@
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO5">
         <v>1000</v>
@@ -1738,13 +1738,13 @@
         <v>2.34</v>
       </c>
       <c r="AQ5">
-        <v>6.2</v>
+        <v>1.99</v>
       </c>
       <c r="AR5">
         <v>15</v>
       </c>
       <c r="AS5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AT5">
         <v>4.9</v>
@@ -1765,19 +1765,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>2.2</v>
       </c>
       <c r="BA5">
         <v>2.34</v>
       </c>
       <c r="BB5">
+        <v>2.26</v>
+      </c>
+      <c r="BC5">
         <v>2.24</v>
       </c>
-      <c r="BC5">
-        <v>23</v>
-      </c>
       <c r="BD5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BE5">
         <v>2.34</v>
@@ -1789,64 +1789,64 @@
         <v>2.34</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI5">
-        <v>1.71</v>
+        <v>2.44</v>
       </c>
       <c r="BJ5">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.71</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="BO5">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BP5">
         <v>30</v>
       </c>
       <c r="BQ5">
-        <v>1.62</v>
+        <v>7.4</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS5">
-        <v>1.67</v>
+        <v>9</v>
       </c>
       <c r="BT5">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BU5">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV5">
         <v>50</v>
       </c>
       <c r="BW5">
-        <v>1.66</v>
+        <v>8.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.68</v>
+        <v>9.4</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.68</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="s">
         <v>97</v>
@@ -1872,28 +1872,28 @@
         <v>1.33</v>
       </c>
       <c r="G6">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H6">
         <v>11.5</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K6">
         <v>6</v>
       </c>
       <c r="L6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O6">
         <v>1.27</v>
@@ -1908,10 +1908,10 @@
         <v>1.47</v>
       </c>
       <c r="S6">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="T6">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U6">
         <v>1.73</v>
@@ -1923,10 +1923,10 @@
         <v>3.9</v>
       </c>
       <c r="X6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z6">
         <v>130</v>
@@ -1935,7 +1935,7 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6">
         <v>13.5</v>
@@ -1986,7 +1986,7 @@
         <v>38</v>
       </c>
       <c r="AS6">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT6">
         <v>7.6</v>
@@ -2019,7 +2019,7 @@
         <v>13</v>
       </c>
       <c r="BD6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE6">
         <v>50</v>
@@ -2031,7 +2031,7 @@
         <v>95</v>
       </c>
       <c r="BH6">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BI6">
         <v>3.05</v>
@@ -2040,16 +2040,16 @@
         <v>14</v>
       </c>
       <c r="BK6">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BL6">
         <v>210</v>
       </c>
       <c r="BM6">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BO6">
         <v>2.86</v>
@@ -2058,37 +2058,37 @@
         <v>7.8</v>
       </c>
       <c r="BQ6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR6">
         <v>28</v>
       </c>
       <c r="BS6">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6">
         <v>16</v>
       </c>
       <c r="BU6">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BV6">
         <v>130</v>
       </c>
       <c r="BW6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX6">
         <v>120</v>
       </c>
       <c r="BY6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
         <v>13.5</v>
       </c>
       <c r="CA6">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="s">
         <v>97</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
+    <t>Chinese Super League</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
@@ -274,6 +277,9 @@
     <t>00:35:00</t>
   </si>
   <si>
+    <t>11:35:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -289,6 +295,9 @@
     <t>Goias</t>
   </si>
   <si>
+    <t>Shanghai Port FC</t>
+  </si>
+  <si>
     <t>Atletico Madrid</t>
   </si>
   <si>
@@ -304,10 +313,13 @@
     <t>Juventude</t>
   </si>
   <si>
+    <t>Dalian Yingbo</t>
+  </si>
+  <si>
     <t>Malaga</t>
   </si>
   <si>
-    <t>2026-08-17 03:05:56</t>
+    <t>2026-08-17 05:14:50</t>
   </si>
 </sst>
 </file>
@@ -639,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -889,28 +901,28 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
         <v>2.28</v>
       </c>
       <c r="H2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J2">
         <v>3.3</v>
@@ -919,37 +931,37 @@
         <v>3.35</v>
       </c>
       <c r="L2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="U2">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
         <v>1.78</v>
@@ -958,7 +970,7 @@
         <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Z2">
         <v>28</v>
@@ -967,25 +979,25 @@
         <v>90</v>
       </c>
       <c r="AB2">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
         <v>60</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI2">
         <v>75</v>
@@ -997,25 +1009,25 @@
         <v>29</v>
       </c>
       <c r="AL2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO2">
         <v>70</v>
       </c>
       <c r="AP2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ2">
         <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS2">
         <v>6.6</v>
@@ -1027,10 +1039,10 @@
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>36</v>
+        <v>6.4</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1039,91 +1051,91 @@
         <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>6.2</v>
       </c>
       <c r="BE2">
         <v>6.8</v>
       </c>
       <c r="BF2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG2">
         <v>6.4</v>
       </c>
       <c r="BH2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP2">
         <v>20</v>
       </c>
       <c r="BQ2">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BR2">
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BT2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW2">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BX2">
         <v>55</v>
       </c>
       <c r="BY2">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BZ2">
         <v>38</v>
       </c>
       <c r="CA2">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1131,25 +1143,25 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F3">
         <v>2.7</v>
       </c>
       <c r="G3">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>3.25</v>
@@ -1158,37 +1170,37 @@
         <v>2.98</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M3">
         <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O3">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P3">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q3">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T3">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
         <v>1.44</v>
@@ -1197,10 +1209,10 @@
         <v>1.53</v>
       </c>
       <c r="X3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
         <v>23</v>
@@ -1209,67 +1221,67 @@
         <v>70</v>
       </c>
       <c r="AB3">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3">
         <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE3">
         <v>55</v>
       </c>
       <c r="AF3">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AG3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI3">
         <v>80</v>
       </c>
       <c r="AJ3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL3">
         <v>75</v>
       </c>
       <c r="AM3">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN3">
         <v>55</v>
       </c>
       <c r="AO3">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP3">
         <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR3">
         <v>17</v>
       </c>
       <c r="AS3">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="AT3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
         <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW3">
         <v>32</v>
@@ -1278,13 +1290,13 @@
         <v>15</v>
       </c>
       <c r="AY3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
         <v>18</v>
       </c>
       <c r="BA3">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="BB3">
         <v>32</v>
@@ -1293,10 +1305,10 @@
         <v>29</v>
       </c>
       <c r="BD3">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="BE3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BF3">
         <v>27</v>
@@ -1305,67 +1317,67 @@
         <v>40</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BI3">
-        <v>1.73</v>
+        <v>2.36</v>
       </c>
       <c r="BJ3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BK3">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.73</v>
+        <v>15.5</v>
       </c>
       <c r="BN3">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="BP3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.65</v>
+        <v>10</v>
       </c>
       <c r="BR3">
+        <v>65</v>
+      </c>
+      <c r="BS3">
+        <v>12</v>
+      </c>
+      <c r="BT3">
+        <v>6</v>
+      </c>
+      <c r="BU3">
+        <v>5.3</v>
+      </c>
+      <c r="BV3">
         <v>1000</v>
       </c>
-      <c r="BS3">
-        <v>1.69</v>
-      </c>
-      <c r="BT3">
-        <v>8</v>
-      </c>
-      <c r="BU3">
-        <v>4.3</v>
-      </c>
-      <c r="BV3">
-        <v>40</v>
-      </c>
       <c r="BW3">
-        <v>1.66</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.69</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.69</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1373,28 +1385,28 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F4">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H4">
         <v>2.54</v>
       </c>
       <c r="I4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J4">
         <v>3.05</v>
@@ -1403,13 +1415,13 @@
         <v>3.4</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O4">
         <v>1.44</v>
@@ -1433,31 +1445,31 @@
         <v>1.93</v>
       </c>
       <c r="V4">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
         <v>1.42</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y4">
         <v>9.6</v>
       </c>
       <c r="Z4">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AA4">
         <v>44</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
         <v>36</v>
@@ -1466,19 +1478,19 @@
         <v>22</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI4">
         <v>55</v>
       </c>
       <c r="AJ4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AK4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL4">
         <v>65</v>
@@ -1487,7 +1499,7 @@
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AO4">
         <v>36</v>
@@ -1499,13 +1511,13 @@
         <v>7.8</v>
       </c>
       <c r="AR4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS4">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU4">
         <v>6.2</v>
@@ -1514,7 +1526,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX4">
         <v>17.5</v>
@@ -1523,91 +1535,91 @@
         <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BB4">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BC4">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BD4">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE4">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF4">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BG4">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1615,76 +1627,76 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F5">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="H5">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="J5">
         <v>3.05</v>
       </c>
       <c r="K5">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="L5">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="P5">
         <v>1.48</v>
       </c>
       <c r="Q5">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="R5">
         <v>1.17</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="T5">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="U5">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z5">
         <v>34</v>
@@ -1693,10 +1705,10 @@
         <v>100</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AC5">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
         <v>23</v>
@@ -1705,19 +1717,19 @@
         <v>90</v>
       </c>
       <c r="AF5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AG5">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AH5">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK5">
         <v>50</v>
@@ -1726,73 +1738,73 @@
         <v>95</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP5">
-        <v>2.34</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5">
-        <v>1.99</v>
+        <v>8.4</v>
       </c>
       <c r="AR5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AS5">
-        <v>2.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AU5">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>2.28</v>
+        <v>8.6</v>
       </c>
       <c r="AX5">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AY5">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
-        <v>2.2</v>
+        <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>2.34</v>
+        <v>9</v>
       </c>
       <c r="BB5">
-        <v>2.26</v>
+        <v>29</v>
       </c>
       <c r="BC5">
-        <v>2.24</v>
+        <v>29</v>
       </c>
       <c r="BD5">
-        <v>2.3</v>
+        <v>8.6</v>
       </c>
       <c r="BE5">
-        <v>2.34</v>
+        <v>9.4</v>
       </c>
       <c r="BF5">
-        <v>2.26</v>
+        <v>32</v>
       </c>
       <c r="BG5">
-        <v>2.34</v>
+        <v>9</v>
       </c>
       <c r="BH5">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BI5">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="BJ5">
         <v>11.5</v>
@@ -1804,28 +1816,28 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BN5">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BO5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP5">
         <v>30</v>
       </c>
       <c r="BQ5">
+        <v>5.5</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>6.4</v>
+      </c>
+      <c r="BT5">
         <v>7.4</v>
-      </c>
-      <c r="BR5">
-        <v>65</v>
-      </c>
-      <c r="BS5">
-        <v>9</v>
-      </c>
-      <c r="BT5">
-        <v>6.6</v>
       </c>
       <c r="BU5">
         <v>5.8</v>
@@ -1834,22 +1846,22 @@
         <v>50</v>
       </c>
       <c r="BW5">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1857,241 +1869,483 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6">
+        <v>1.65</v>
+      </c>
+      <c r="G6">
+        <v>1.85</v>
+      </c>
+      <c r="H6">
+        <v>4.3</v>
+      </c>
+      <c r="I6">
+        <v>6.6</v>
+      </c>
+      <c r="J6">
+        <v>4.2</v>
+      </c>
+      <c r="K6">
+        <v>6.2</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>2.56</v>
+      </c>
+      <c r="Q6">
+        <v>1.46</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
         <v>83</v>
       </c>
-      <c r="C6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6">
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7">
         <v>1.33</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>1.34</v>
       </c>
-      <c r="H6">
-        <v>11.5</v>
-      </c>
-      <c r="I6">
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
         <v>12.5</v>
       </c>
-      <c r="J6">
+      <c r="J7">
         <v>5.9</v>
       </c>
-      <c r="K6">
+      <c r="K7">
+        <v>6.2</v>
+      </c>
+      <c r="L7">
+        <v>1.28</v>
+      </c>
+      <c r="M7">
+        <v>1.05</v>
+      </c>
+      <c r="N7">
+        <v>4.4</v>
+      </c>
+      <c r="O7">
+        <v>1.27</v>
+      </c>
+      <c r="P7">
+        <v>2.2</v>
+      </c>
+      <c r="Q7">
+        <v>1.77</v>
+      </c>
+      <c r="R7">
+        <v>1.46</v>
+      </c>
+      <c r="S7">
+        <v>2.98</v>
+      </c>
+      <c r="T7">
+        <v>2.28</v>
+      </c>
+      <c r="U7">
+        <v>1.72</v>
+      </c>
+      <c r="V7">
+        <v>1.08</v>
+      </c>
+      <c r="W7">
+        <v>3.95</v>
+      </c>
+      <c r="X7">
+        <v>18.5</v>
+      </c>
+      <c r="Y7">
+        <v>34</v>
+      </c>
+      <c r="Z7">
+        <v>130</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC7">
+        <v>13.5</v>
+      </c>
+      <c r="AD7">
+        <v>48</v>
+      </c>
+      <c r="AE7">
+        <v>270</v>
+      </c>
+      <c r="AF7">
+        <v>7.6</v>
+      </c>
+      <c r="AG7">
+        <v>10.5</v>
+      </c>
+      <c r="AH7">
+        <v>38</v>
+      </c>
+      <c r="AI7">
+        <v>200</v>
+      </c>
+      <c r="AJ7">
+        <v>10</v>
+      </c>
+      <c r="AK7">
+        <v>15</v>
+      </c>
+      <c r="AL7">
+        <v>46</v>
+      </c>
+      <c r="AM7">
+        <v>240</v>
+      </c>
+      <c r="AN7">
+        <v>5.5</v>
+      </c>
+      <c r="AO7">
+        <v>480</v>
+      </c>
+      <c r="AP7">
+        <v>16.5</v>
+      </c>
+      <c r="AQ7">
+        <v>20</v>
+      </c>
+      <c r="AR7">
+        <v>38</v>
+      </c>
+      <c r="AS7">
+        <v>18.5</v>
+      </c>
+      <c r="AT7">
+        <v>7.6</v>
+      </c>
+      <c r="AU7">
+        <v>12</v>
+      </c>
+      <c r="AV7">
+        <v>34</v>
+      </c>
+      <c r="AW7">
+        <v>48</v>
+      </c>
+      <c r="AX7">
+        <v>6.8</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>23</v>
+      </c>
+      <c r="BA7">
+        <v>46</v>
+      </c>
+      <c r="BB7">
+        <v>9</v>
+      </c>
+      <c r="BC7">
+        <v>13</v>
+      </c>
+      <c r="BD7">
+        <v>32</v>
+      </c>
+      <c r="BE7">
+        <v>50</v>
+      </c>
+      <c r="BF7">
+        <v>5.2</v>
+      </c>
+      <c r="BG7">
+        <v>95</v>
+      </c>
+      <c r="BH7">
+        <v>4</v>
+      </c>
+      <c r="BI7">
+        <v>3.05</v>
+      </c>
+      <c r="BJ7">
+        <v>14</v>
+      </c>
+      <c r="BK7">
+        <v>6.2</v>
+      </c>
+      <c r="BL7">
+        <v>220</v>
+      </c>
+      <c r="BM7">
+        <v>10.5</v>
+      </c>
+      <c r="BN7">
+        <v>3.7</v>
+      </c>
+      <c r="BO7">
+        <v>2.84</v>
+      </c>
+      <c r="BP7">
+        <v>7.8</v>
+      </c>
+      <c r="BQ7">
+        <v>5.6</v>
+      </c>
+      <c r="BR7">
+        <v>28</v>
+      </c>
+      <c r="BS7">
+        <v>7.8</v>
+      </c>
+      <c r="BT7">
+        <v>16.5</v>
+      </c>
+      <c r="BU7">
+        <v>6.6</v>
+      </c>
+      <c r="BV7">
+        <v>140</v>
+      </c>
+      <c r="BW7">
+        <v>10</v>
+      </c>
+      <c r="BX7">
+        <v>120</v>
+      </c>
+      <c r="BY7">
+        <v>10</v>
+      </c>
+      <c r="BZ7">
+        <v>13.5</v>
+      </c>
+      <c r="CA7">
         <v>6</v>
       </c>
-      <c r="L6">
-        <v>1.29</v>
-      </c>
-      <c r="M6">
-        <v>1.05</v>
-      </c>
-      <c r="N6">
-        <v>4.4</v>
-      </c>
-      <c r="O6">
-        <v>1.27</v>
-      </c>
-      <c r="P6">
-        <v>2.2</v>
-      </c>
-      <c r="Q6">
-        <v>1.77</v>
-      </c>
-      <c r="R6">
-        <v>1.47</v>
-      </c>
-      <c r="S6">
-        <v>2.98</v>
-      </c>
-      <c r="T6">
-        <v>2.32</v>
-      </c>
-      <c r="U6">
-        <v>1.73</v>
-      </c>
-      <c r="V6">
-        <v>1.08</v>
-      </c>
-      <c r="W6">
-        <v>3.9</v>
-      </c>
-      <c r="X6">
-        <v>18.5</v>
-      </c>
-      <c r="Y6">
-        <v>34</v>
-      </c>
-      <c r="Z6">
-        <v>130</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC6">
-        <v>13.5</v>
-      </c>
-      <c r="AD6">
-        <v>48</v>
-      </c>
-      <c r="AE6">
-        <v>260</v>
-      </c>
-      <c r="AF6">
-        <v>7.6</v>
-      </c>
-      <c r="AG6">
-        <v>10.5</v>
-      </c>
-      <c r="AH6">
-        <v>38</v>
-      </c>
-      <c r="AI6">
-        <v>190</v>
-      </c>
-      <c r="AJ6">
-        <v>10</v>
-      </c>
-      <c r="AK6">
-        <v>15</v>
-      </c>
-      <c r="AL6">
-        <v>46</v>
-      </c>
-      <c r="AM6">
-        <v>250</v>
-      </c>
-      <c r="AN6">
-        <v>5.5</v>
-      </c>
-      <c r="AO6">
-        <v>460</v>
-      </c>
-      <c r="AP6">
-        <v>16.5</v>
-      </c>
-      <c r="AQ6">
-        <v>20</v>
-      </c>
-      <c r="AR6">
-        <v>38</v>
-      </c>
-      <c r="AS6">
-        <v>18.5</v>
-      </c>
-      <c r="AT6">
-        <v>7.6</v>
-      </c>
-      <c r="AU6">
-        <v>12</v>
-      </c>
-      <c r="AV6">
-        <v>34</v>
-      </c>
-      <c r="AW6">
-        <v>48</v>
-      </c>
-      <c r="AX6">
-        <v>6.8</v>
-      </c>
-      <c r="AY6">
-        <v>10</v>
-      </c>
-      <c r="AZ6">
-        <v>23</v>
-      </c>
-      <c r="BA6">
-        <v>46</v>
-      </c>
-      <c r="BB6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC6">
-        <v>13</v>
-      </c>
-      <c r="BD6">
-        <v>32</v>
-      </c>
-      <c r="BE6">
-        <v>50</v>
-      </c>
-      <c r="BF6">
-        <v>5.2</v>
-      </c>
-      <c r="BG6">
-        <v>95</v>
-      </c>
-      <c r="BH6">
-        <v>3.95</v>
-      </c>
-      <c r="BI6">
-        <v>3.05</v>
-      </c>
-      <c r="BJ6">
-        <v>14</v>
-      </c>
-      <c r="BK6">
-        <v>6.4</v>
-      </c>
-      <c r="BL6">
-        <v>210</v>
-      </c>
-      <c r="BM6">
-        <v>11</v>
-      </c>
-      <c r="BN6">
-        <v>3.7</v>
-      </c>
-      <c r="BO6">
-        <v>2.86</v>
-      </c>
-      <c r="BP6">
-        <v>7.8</v>
-      </c>
-      <c r="BQ6">
-        <v>5.7</v>
-      </c>
-      <c r="BR6">
-        <v>28</v>
-      </c>
-      <c r="BS6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT6">
-        <v>16</v>
-      </c>
-      <c r="BU6">
-        <v>6.8</v>
-      </c>
-      <c r="BV6">
-        <v>130</v>
-      </c>
-      <c r="BW6">
-        <v>10.5</v>
-      </c>
-      <c r="BX6">
-        <v>120</v>
-      </c>
-      <c r="BY6">
-        <v>10.5</v>
-      </c>
-      <c r="BZ6">
-        <v>13.5</v>
-      </c>
-      <c r="CA6">
-        <v>6.2</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>97</v>
+      <c r="CB7" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -319,7 +319,7 @@
     <t>Malaga</t>
   </si>
   <si>
-    <t>2026-08-17 05:14:50</t>
+    <t>2026-08-17 07:24:14</t>
   </si>
 </sst>
 </file>
@@ -916,16 +916,16 @@
         <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I2">
         <v>3.95</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
         <v>3.35</v>
@@ -937,13 +937,13 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -952,7 +952,7 @@
         <v>1.27</v>
       </c>
       <c r="S2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T2">
         <v>1.86</v>
@@ -961,7 +961,7 @@
         <v>1.96</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
         <v>1.78</v>
@@ -985,7 +985,7 @@
         <v>8</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE2">
         <v>60</v>
@@ -994,7 +994,7 @@
         <v>16</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>20</v>
@@ -1030,10 +1030,10 @@
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1042,7 +1042,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1063,25 +1063,25 @@
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF2">
         <v>19</v>
       </c>
       <c r="BG2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
         <v>8</v>
@@ -1093,7 +1093,7 @@
         <v>6.2</v>
       </c>
       <c r="BN2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
         <v>3.95</v>
@@ -1114,7 +1114,7 @@
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV2">
         <v>38</v>
@@ -1126,10 +1126,10 @@
         <v>55</v>
       </c>
       <c r="BY2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="CA2">
         <v>5.6</v>
@@ -1167,10 +1167,10 @@
         <v>3.25</v>
       </c>
       <c r="J3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
         <v>1.49</v>
@@ -1179,7 +1179,7 @@
         <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O3">
         <v>1.54</v>
@@ -1191,10 +1191,10 @@
         <v>2.62</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T3">
         <v>2.1</v>
@@ -1227,7 +1227,7 @@
         <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE3">
         <v>55</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH3">
         <v>26</v>
@@ -1263,7 +1263,7 @@
         <v>80</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ3">
         <v>7.8</v>
@@ -1293,10 +1293,10 @@
         <v>12</v>
       </c>
       <c r="AZ3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB3">
         <v>32</v>
@@ -1305,10 +1305,10 @@
         <v>29</v>
       </c>
       <c r="BD3">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BE3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF3">
         <v>27</v>
@@ -1397,16 +1397,16 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
         <v>2.54</v>
       </c>
       <c r="I4">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J4">
         <v>3.05</v>
@@ -1421,7 +1421,7 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O4">
         <v>1.44</v>
@@ -1439,13 +1439,13 @@
         <v>4.4</v>
       </c>
       <c r="T4">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U4">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W4">
         <v>1.42</v>
@@ -1457,19 +1457,19 @@
         <v>9.6</v>
       </c>
       <c r="Z4">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AA4">
         <v>44</v>
       </c>
       <c r="AB4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC4">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE4">
         <v>36</v>
@@ -1478,19 +1478,19 @@
         <v>22</v>
       </c>
       <c r="AG4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4">
         <v>55</v>
       </c>
       <c r="AJ4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL4">
         <v>65</v>
@@ -1499,7 +1499,7 @@
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AO4">
         <v>36</v>
@@ -1511,13 +1511,13 @@
         <v>7.8</v>
       </c>
       <c r="AR4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AT4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4">
         <v>6.2</v>
@@ -1526,7 +1526,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>5.7</v>
+        <v>25</v>
       </c>
       <c r="AX4">
         <v>17.5</v>
@@ -1535,28 +1535,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA4">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB4">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="BC4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BF4">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="BG4">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH4">
         <v>3.1</v>
@@ -1639,7 +1639,7 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G5">
         <v>2.54</v>
@@ -1663,19 +1663,19 @@
         <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O5">
         <v>1.58</v>
       </c>
       <c r="P5">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q5">
         <v>2.76</v>
       </c>
       <c r="R5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
         <v>5.9</v>
@@ -1687,7 +1687,7 @@
         <v>1.75</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W5">
         <v>1.65</v>
@@ -1696,7 +1696,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z5">
         <v>34</v>
@@ -1756,7 +1756,7 @@
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT5">
         <v>6.6</v>
@@ -1768,7 +1768,7 @@
         <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5">
         <v>12.5</v>
@@ -1789,10 +1789,10 @@
         <v>29</v>
       </c>
       <c r="BD5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF5">
         <v>32</v>
@@ -1881,22 +1881,22 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="G6">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I6">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="J6">
         <v>4.2</v>
       </c>
       <c r="K6">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2129,16 +2129,16 @@
         <v>1.34</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J7">
         <v>5.9</v>
       </c>
       <c r="K7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>1.28</v>
@@ -2156,16 +2156,16 @@
         <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S7">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U7">
         <v>1.72</v>
@@ -2174,13 +2174,13 @@
         <v>1.08</v>
       </c>
       <c r="W7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="X7">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z7">
         <v>130</v>
@@ -2189,7 +2189,7 @@
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>13.5</v>
@@ -2201,10 +2201,10 @@
         <v>270</v>
       </c>
       <c r="AF7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH7">
         <v>38</v>
@@ -2213,34 +2213,34 @@
         <v>200</v>
       </c>
       <c r="AJ7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK7">
         <v>15</v>
       </c>
       <c r="AL7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM7">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AN7">
         <v>5.5</v>
       </c>
       <c r="AO7">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="AP7">
         <v>16.5</v>
       </c>
       <c r="AQ7">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AR7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS7">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AT7">
         <v>7.6</v>
@@ -2249,10 +2249,10 @@
         <v>12</v>
       </c>
       <c r="AV7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AW7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX7">
         <v>6.8</v>
@@ -2261,25 +2261,25 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BA7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB7">
         <v>9</v>
       </c>
       <c r="BC7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BE7">
         <v>50</v>
       </c>
       <c r="BF7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BG7">
         <v>95</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -319,7 +319,7 @@
     <t>Malaga</t>
   </si>
   <si>
-    <t>2026-08-17 07:24:14</t>
+    <t>2026-08-17 09:33:37</t>
   </si>
 </sst>
 </file>
@@ -916,7 +916,7 @@
         <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H2">
         <v>3.85</v>
@@ -925,7 +925,7 @@
         <v>3.95</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K2">
         <v>3.35</v>
@@ -937,13 +937,13 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -952,7 +952,7 @@
         <v>1.27</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
         <v>1.86</v>
@@ -982,7 +982,7 @@
         <v>9</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
         <v>17</v>
@@ -1021,7 +1021,7 @@
         <v>70</v>
       </c>
       <c r="AP2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2">
         <v>10.5</v>
@@ -1030,7 +1030,7 @@
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT2">
         <v>7.4</v>
@@ -1054,10 +1054,10 @@
         <v>16</v>
       </c>
       <c r="BA2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC2">
         <v>21</v>
@@ -1066,13 +1066,13 @@
         <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF2">
         <v>19</v>
       </c>
       <c r="BG2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
@@ -1081,16 +1081,16 @@
         <v>2.58</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
@@ -1102,37 +1102,37 @@
         <v>20</v>
       </c>
       <c r="BQ2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR2">
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
         <v>38</v>
       </c>
       <c r="BW2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX2">
         <v>55</v>
       </c>
       <c r="BY2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BZ2">
         <v>40</v>
       </c>
       <c r="CA2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB2" t="s">
         <v>101</v>
@@ -1158,7 +1158,7 @@
         <v>2.7</v>
       </c>
       <c r="G3">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -1206,7 +1206,7 @@
         <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X3">
         <v>9.199999999999999</v>
@@ -1272,7 +1272,7 @@
         <v>17</v>
       </c>
       <c r="AS3">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
@@ -1296,7 +1296,7 @@
         <v>19</v>
       </c>
       <c r="BA3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB3">
         <v>32</v>
@@ -1308,7 +1308,7 @@
         <v>42</v>
       </c>
       <c r="BE3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF3">
         <v>27</v>
@@ -1326,7 +1326,7 @@
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1338,7 +1338,7 @@
         <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
         <v>1000</v>
@@ -1347,7 +1347,7 @@
         <v>10</v>
       </c>
       <c r="BR3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
         <v>12</v>
@@ -1356,7 +1356,7 @@
         <v>6</v>
       </c>
       <c r="BU3">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1403,28 +1403,28 @@
         <v>3.4</v>
       </c>
       <c r="H4">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="I4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
         <v>1.67</v>
@@ -1439,7 +1439,7 @@
         <v>4.4</v>
       </c>
       <c r="T4">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="U4">
         <v>1.94</v>
@@ -1526,7 +1526,7 @@
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="AX4">
         <v>17.5</v>
@@ -1535,7 +1535,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
         <v>7.2</v>
@@ -1559,7 +1559,7 @@
         <v>6.8</v>
       </c>
       <c r="BH4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI4">
         <v>2.48</v>
@@ -1568,13 +1568,13 @@
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN4">
         <v>6.4</v>
@@ -1586,13 +1586,13 @@
         <v>29</v>
       </c>
       <c r="BQ4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR4">
         <v>46</v>
       </c>
       <c r="BS4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT4">
         <v>5.6</v>
@@ -1604,19 +1604,19 @@
         <v>23</v>
       </c>
       <c r="BW4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>42</v>
       </c>
       <c r="BY4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="CA4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="s">
         <v>101</v>
@@ -1663,19 +1663,19 @@
         <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
         <v>1.58</v>
       </c>
       <c r="P5">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Q5">
         <v>2.76</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S5">
         <v>5.9</v>
@@ -1795,70 +1795,70 @@
         <v>9.6</v>
       </c>
       <c r="BF5">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5">
         <v>9</v>
       </c>
       <c r="BH5">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BI5">
         <v>2.22</v>
       </c>
       <c r="BJ5">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BN5">
         <v>5.8</v>
       </c>
       <c r="BO5">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BQ5">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BT5">
         <v>7.4</v>
       </c>
       <c r="BU5">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV5">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BW5">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB5" t="s">
         <v>101</v>
@@ -1881,226 +1881,226 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="G6">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="H6">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="I6">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="J6">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="K6">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P6">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="Q6">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>101</v>
@@ -2156,7 +2156,7 @@
         <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R7">
         <v>1.47</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -319,7 +319,7 @@
     <t>Malaga</t>
   </si>
   <si>
-    <t>2026-08-17 09:33:37</t>
+    <t>2026-08-17 11:42:58</t>
   </si>
 </sst>
 </file>
@@ -916,7 +916,7 @@
         <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
         <v>3.85</v>
@@ -946,7 +946,7 @@
         <v>1.72</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R2">
         <v>1.27</v>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI2">
         <v>75</v>
@@ -1030,7 +1030,7 @@
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT2">
         <v>7.4</v>
@@ -1042,7 +1042,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1054,10 +1054,10 @@
         <v>16</v>
       </c>
       <c r="BA2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BC2">
         <v>21</v>
@@ -1066,13 +1066,13 @@
         <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF2">
         <v>19</v>
       </c>
       <c r="BG2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
@@ -1158,7 +1158,7 @@
         <v>2.7</v>
       </c>
       <c r="G3">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -1170,13 +1170,13 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
         <v>1.49</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
         <v>2.64</v>
@@ -1206,7 +1206,7 @@
         <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X3">
         <v>9.199999999999999</v>
@@ -1215,7 +1215,7 @@
         <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AA3">
         <v>70</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
         <v>26</v>
@@ -1272,49 +1272,49 @@
         <v>17</v>
       </c>
       <c r="AS3">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
         <v>32</v>
       </c>
       <c r="AX3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BB3">
         <v>32</v>
       </c>
       <c r="BC3">
-        <v>29</v>
+        <v>6.4</v>
       </c>
       <c r="BD3">
         <v>42</v>
       </c>
       <c r="BE3">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BF3">
         <v>27</v>
       </c>
       <c r="BG3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH3">
         <v>2.76</v>
@@ -1400,19 +1400,19 @@
         <v>3.05</v>
       </c>
       <c r="G4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H4">
         <v>2.6</v>
       </c>
       <c r="I4">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J4">
         <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L4">
         <v>1.44</v>
@@ -1430,7 +1430,7 @@
         <v>1.67</v>
       </c>
       <c r="Q4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R4">
         <v>1.25</v>
@@ -1448,7 +1448,7 @@
         <v>1.56</v>
       </c>
       <c r="W4">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X4">
         <v>12</v>
@@ -1610,10 +1610,10 @@
         <v>42</v>
       </c>
       <c r="BY4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA4">
         <v>8.4</v>
@@ -1639,7 +1639,7 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G5">
         <v>2.54</v>
@@ -1660,10 +1660,10 @@
         <v>1.6</v>
       </c>
       <c r="M5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O5">
         <v>1.58</v>
@@ -1672,91 +1672,91 @@
         <v>1.48</v>
       </c>
       <c r="Q5">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="R5">
         <v>1.17</v>
       </c>
       <c r="S5">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="T5">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="U5">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="V5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
         <v>1.65</v>
       </c>
       <c r="X5">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="Z5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA5">
         <v>100</v>
       </c>
       <c r="AB5">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AD5">
         <v>23</v>
       </c>
       <c r="AE5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF5">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AH5">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AI5">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK5">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
         <v>95</v>
       </c>
       <c r="AM5">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO5">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>7.2</v>
+        <v>2.16</v>
       </c>
       <c r="AQ5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR5">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AS5">
-        <v>9</v>
+        <v>2.1</v>
       </c>
       <c r="AT5">
         <v>6.6</v>
@@ -1768,7 +1768,7 @@
         <v>14.5</v>
       </c>
       <c r="AW5">
-        <v>8.800000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="AX5">
         <v>12.5</v>
@@ -1777,28 +1777,28 @@
         <v>11</v>
       </c>
       <c r="AZ5">
-        <v>18.5</v>
+        <v>2.02</v>
       </c>
       <c r="BA5">
-        <v>9</v>
+        <v>2.16</v>
       </c>
       <c r="BB5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BC5">
-        <v>29</v>
+        <v>2.16</v>
       </c>
       <c r="BD5">
-        <v>8.800000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="BE5">
-        <v>9.6</v>
+        <v>2.16</v>
       </c>
       <c r="BF5">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BG5">
-        <v>9</v>
+        <v>2.16</v>
       </c>
       <c r="BH5">
         <v>2.9</v>
@@ -1881,226 +1881,226 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="G6">
-        <v>1.59</v>
+        <v>1000</v>
       </c>
       <c r="H6">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I6">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="P6">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="Q6">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R6">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="S6">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="V6">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL6">
         <v>1000</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="CB6" t="s">
         <v>101</v>
@@ -2135,7 +2135,7 @@
         <v>13</v>
       </c>
       <c r="J7">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -2162,13 +2162,13 @@
         <v>1.47</v>
       </c>
       <c r="S7">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T7">
         <v>2.3</v>
       </c>
       <c r="U7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V7">
         <v>1.08</v>
@@ -2192,13 +2192,13 @@
         <v>8</v>
       </c>
       <c r="AC7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD7">
         <v>48</v>
       </c>
       <c r="AE7">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AF7">
         <v>7.4</v>
@@ -2222,13 +2222,13 @@
         <v>48</v>
       </c>
       <c r="AM7">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AO7">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="AP7">
         <v>16.5</v>
@@ -2267,7 +2267,7 @@
         <v>48</v>
       </c>
       <c r="BB7">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC7">
         <v>13.5</v>
@@ -2279,7 +2279,7 @@
         <v>50</v>
       </c>
       <c r="BF7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG7">
         <v>95</v>
@@ -2294,7 +2294,7 @@
         <v>14</v>
       </c>
       <c r="BK7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL7">
         <v>220</v>
@@ -2306,7 +2306,7 @@
         <v>3.7</v>
       </c>
       <c r="BO7">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BP7">
         <v>7.8</v>
@@ -2321,10 +2321,10 @@
         <v>7.8</v>
       </c>
       <c r="BT7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BU7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV7">
         <v>140</v>
@@ -2339,7 +2339,7 @@
         <v>10</v>
       </c>
       <c r="BZ7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CA7">
         <v>6</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -319,7 +319,7 @@
     <t>Malaga</t>
   </si>
   <si>
-    <t>2026-08-17 11:42:58</t>
+    <t>2026-08-17 13:52:13</t>
   </si>
 </sst>
 </file>
@@ -913,10 +913,10 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H2">
         <v>3.85</v>
@@ -928,7 +928,7 @@
         <v>3.2</v>
       </c>
       <c r="K2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
         <v>1.45</v>
@@ -943,7 +943,7 @@
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
         <v>2.12</v>
@@ -964,7 +964,7 @@
         <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X2">
         <v>13.5</v>
@@ -1173,13 +1173,13 @@
         <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O3">
         <v>1.54</v>
@@ -1209,13 +1209,13 @@
         <v>1.53</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
         <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AA3">
         <v>70</v>
@@ -1242,7 +1242,7 @@
         <v>26</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
         <v>60</v>
@@ -1272,10 +1272,10 @@
         <v>17</v>
       </c>
       <c r="AS3">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
@@ -1296,34 +1296,34 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB3">
         <v>32</v>
       </c>
       <c r="BC3">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD3">
         <v>42</v>
       </c>
       <c r="BE3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BF3">
         <v>27</v>
       </c>
       <c r="BG3">
-        <v>42</v>
+        <v>5.7</v>
       </c>
       <c r="BH3">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BI3">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
         <v>8.6</v>
@@ -1350,7 +1350,7 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT3">
         <v>6</v>
@@ -1368,13 +1368,13 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
         <v>101</v>
@@ -1400,7 +1400,7 @@
         <v>3.05</v>
       </c>
       <c r="G4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H4">
         <v>2.6</v>
@@ -1409,7 +1409,7 @@
         <v>2.78</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
         <v>3.3</v>
@@ -1421,13 +1421,13 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
         <v>2.34</v>
@@ -1448,7 +1448,7 @@
         <v>1.56</v>
       </c>
       <c r="W4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X4">
         <v>12</v>
@@ -1639,7 +1639,7 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G5">
         <v>2.54</v>
@@ -1648,22 +1648,22 @@
         <v>3.55</v>
       </c>
       <c r="I5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J5">
         <v>3.05</v>
       </c>
       <c r="K5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L5">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="M5">
         <v>1.13</v>
       </c>
       <c r="N5">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
         <v>1.58</v>
@@ -1672,31 +1672,31 @@
         <v>1.48</v>
       </c>
       <c r="Q5">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="R5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="T5">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="U5">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W5">
         <v>1.65</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y5">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z5">
         <v>32</v>
@@ -1705,49 +1705,49 @@
         <v>100</v>
       </c>
       <c r="AB5">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AC5">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE5">
         <v>85</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG5">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AH5">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL5">
         <v>95</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP5">
-        <v>2.16</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5">
         <v>8.6</v>
@@ -1756,7 +1756,7 @@
         <v>16.5</v>
       </c>
       <c r="AS5">
-        <v>2.1</v>
+        <v>9</v>
       </c>
       <c r="AT5">
         <v>6.6</v>
@@ -1765,40 +1765,40 @@
         <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>2.1</v>
+        <v>40</v>
       </c>
       <c r="AX5">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY5">
         <v>11</v>
       </c>
       <c r="AZ5">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="BA5">
-        <v>2.16</v>
+        <v>9</v>
       </c>
       <c r="BB5">
         <v>26</v>
       </c>
       <c r="BC5">
-        <v>2.16</v>
+        <v>7.8</v>
       </c>
       <c r="BD5">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5">
-        <v>2.16</v>
+        <v>9.4</v>
       </c>
       <c r="BF5">
         <v>27</v>
       </c>
       <c r="BG5">
-        <v>2.16</v>
+        <v>9</v>
       </c>
       <c r="BH5">
         <v>2.9</v>
@@ -1810,7 +1810,7 @@
         <v>13.5</v>
       </c>
       <c r="BK5">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1881,31 +1881,31 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>1.67</v>
       </c>
       <c r="H6">
+        <v>5.4</v>
+      </c>
+      <c r="I6">
+        <v>7.6</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
         <v>5.1</v>
       </c>
-      <c r="I6">
-        <v>6.6</v>
-      </c>
-      <c r="J6">
-        <v>3.95</v>
-      </c>
-      <c r="K6">
-        <v>5.6</v>
-      </c>
       <c r="L6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O6">
         <v>1.16</v>
@@ -1914,154 +1914,154 @@
         <v>2.56</v>
       </c>
       <c r="Q6">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="R6">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U6">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V6">
         <v>1.17</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="X6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z6">
+        <v>60</v>
+      </c>
+      <c r="AA6">
+        <v>140</v>
+      </c>
+      <c r="AB6">
+        <v>14.5</v>
+      </c>
+      <c r="AC6">
+        <v>12</v>
+      </c>
+      <c r="AD6">
+        <v>25</v>
+      </c>
+      <c r="AE6">
         <v>70</v>
-      </c>
-      <c r="AA6">
-        <v>170</v>
-      </c>
-      <c r="AB6">
-        <v>15.5</v>
-      </c>
-      <c r="AC6">
-        <v>14.5</v>
-      </c>
-      <c r="AD6">
-        <v>29</v>
-      </c>
-      <c r="AE6">
-        <v>80</v>
       </c>
       <c r="AF6">
         <v>14</v>
       </c>
       <c r="AG6">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI6">
         <v>70</v>
       </c>
       <c r="AJ6">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM6">
         <v>85</v>
       </c>
       <c r="AN6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AO6">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP6">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="AQ6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="AR6">
-        <v>4.2</v>
+        <v>38</v>
       </c>
       <c r="AS6">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV6">
-        <v>3.9</v>
+        <v>17.5</v>
       </c>
       <c r="AW6">
-        <v>4.2</v>
+        <v>48</v>
       </c>
       <c r="AX6">
         <v>10</v>
       </c>
       <c r="AY6">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6">
-        <v>3.75</v>
+        <v>15.5</v>
       </c>
       <c r="BA6">
-        <v>4.2</v>
+        <v>40</v>
       </c>
       <c r="BB6">
+        <v>13.5</v>
+      </c>
+      <c r="BC6">
         <v>12.5</v>
-      </c>
-      <c r="BC6">
-        <v>12</v>
       </c>
       <c r="BD6">
         <v>21</v>
       </c>
       <c r="BE6">
-        <v>4.2</v>
+        <v>48</v>
       </c>
       <c r="BF6">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="BG6">
-        <v>4.2</v>
+        <v>30</v>
       </c>
       <c r="BH6">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BI6">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ6">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BN6">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BO6">
         <v>3.75</v>
@@ -2070,37 +2070,37 @@
         <v>10.5</v>
       </c>
       <c r="BQ6">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BR6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS6">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BT6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU6">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="BZ6">
         <v>12.5</v>
       </c>
       <c r="CA6">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="CB6" t="s">
         <v>101</v>
@@ -2129,16 +2129,16 @@
         <v>1.34</v>
       </c>
       <c r="H7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I7">
         <v>13</v>
       </c>
       <c r="J7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L7">
         <v>1.28</v>
@@ -2156,7 +2156,7 @@
         <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R7">
         <v>1.47</v>
@@ -2174,7 +2174,7 @@
         <v>1.08</v>
       </c>
       <c r="W7">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="X7">
         <v>17.5</v>
@@ -2252,7 +2252,7 @@
         <v>36</v>
       </c>
       <c r="AW7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX7">
         <v>6.8</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Chinese Super League</t>
   </si>
   <si>
+    <t>South African Premier Division</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
@@ -280,6 +283,9 @@
     <t>11:35:00</t>
   </si>
   <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -298,6 +304,9 @@
     <t>Shanghai Port FC</t>
   </si>
   <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
     <t>Atletico Madrid</t>
   </si>
   <si>
@@ -316,10 +325,13 @@
     <t>Dalian Yingbo</t>
   </si>
   <si>
+    <t>Marumo Gallants FC</t>
+  </si>
+  <si>
     <t>Malaga</t>
   </si>
   <si>
-    <t>2026-08-17 13:52:13</t>
+    <t>2026-08-17 16:01:02</t>
   </si>
 </sst>
 </file>
@@ -651,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -901,31 +913,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
         <v>3.3</v>
@@ -964,10 +976,10 @@
         <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y2">
         <v>13</v>
@@ -979,7 +991,7 @@
         <v>90</v>
       </c>
       <c r="AB2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
@@ -991,7 +1003,7 @@
         <v>60</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG2">
         <v>12</v>
@@ -1030,7 +1042,7 @@
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT2">
         <v>7.4</v>
@@ -1042,7 +1054,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1054,25 +1066,25 @@
         <v>16</v>
       </c>
       <c r="BA2">
+        <v>7.4</v>
+      </c>
+      <c r="BB2">
         <v>6.6</v>
-      </c>
-      <c r="BB2">
-        <v>6</v>
       </c>
       <c r="BC2">
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF2">
         <v>19</v>
       </c>
       <c r="BG2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
@@ -1135,7 +1147,7 @@
         <v>5.7</v>
       </c>
       <c r="CB2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1143,16 +1155,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F3">
         <v>2.7</v>
@@ -1182,7 +1194,7 @@
         <v>2.66</v>
       </c>
       <c r="O3">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P3">
         <v>1.54</v>
@@ -1194,7 +1206,7 @@
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T3">
         <v>2.1</v>
@@ -1209,10 +1221,10 @@
         <v>1.53</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z3">
         <v>23</v>
@@ -1251,7 +1263,7 @@
         <v>48</v>
       </c>
       <c r="AL3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM3">
         <v>200</v>
@@ -1272,7 +1284,7 @@
         <v>17</v>
       </c>
       <c r="AS3">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1296,25 +1308,25 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BB3">
         <v>32</v>
       </c>
       <c r="BC3">
-        <v>5.5</v>
+        <v>34</v>
       </c>
       <c r="BD3">
         <v>42</v>
       </c>
       <c r="BE3">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF3">
         <v>27</v>
       </c>
       <c r="BG3">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH3">
         <v>2.68</v>
@@ -1377,7 +1389,7 @@
         <v>12.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1385,31 +1397,31 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>3.05</v>
       </c>
       <c r="G4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H4">
         <v>2.6</v>
       </c>
       <c r="I4">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
         <v>3.3</v>
@@ -1421,7 +1433,7 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O4">
         <v>1.45</v>
@@ -1430,31 +1442,31 @@
         <v>1.68</v>
       </c>
       <c r="Q4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T4">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U4">
         <v>1.94</v>
       </c>
       <c r="V4">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X4">
         <v>12</v>
       </c>
       <c r="Y4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z4">
         <v>17.5</v>
@@ -1463,7 +1475,7 @@
         <v>44</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
@@ -1478,7 +1490,7 @@
         <v>22</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
         <v>21</v>
@@ -1514,19 +1526,19 @@
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="AT4">
         <v>8.800000000000001</v>
       </c>
       <c r="AU4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX4">
         <v>17.5</v>
@@ -1538,25 +1550,25 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC4">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF4">
         <v>36</v>
       </c>
       <c r="BG4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH4">
         <v>3.05</v>
@@ -1619,7 +1631,7 @@
         <v>8.4</v>
       </c>
       <c r="CB4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1627,16 +1639,16 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F5">
         <v>2.44</v>
@@ -1693,7 +1705,7 @@
         <v>1.65</v>
       </c>
       <c r="X5">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5">
         <v>9.800000000000001</v>
@@ -1756,7 +1768,7 @@
         <v>16.5</v>
       </c>
       <c r="AS5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT5">
         <v>6.6</v>
@@ -1777,28 +1789,28 @@
         <v>11</v>
       </c>
       <c r="AZ5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BA5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB5">
         <v>26</v>
       </c>
       <c r="BC5">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BD5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE5">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF5">
         <v>27</v>
       </c>
       <c r="BG5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH5">
         <v>2.9</v>
@@ -1861,7 +1873,7 @@
         <v>5.7</v>
       </c>
       <c r="CB5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1869,184 +1881,184 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F6">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="G6">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="H6">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="K6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O6">
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
         <v>1.47</v>
       </c>
       <c r="R6">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="S6">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T6">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U6">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W6">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="X6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA6">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="AB6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE6">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AF6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
         <v>19.5</v>
       </c>
       <c r="AI6">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ6">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL6">
         <v>28</v>
       </c>
       <c r="AM6">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AN6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP6">
-        <v>21</v>
+        <v>5.7</v>
       </c>
       <c r="AQ6">
         <v>24</v>
       </c>
       <c r="AR6">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AS6">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV6">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW6">
-        <v>48</v>
+        <v>6.4</v>
       </c>
       <c r="AX6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6">
         <v>8.6</v>
       </c>
       <c r="AZ6">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BA6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BB6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF6">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="BG6">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BH6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BI6">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
@@ -2058,13 +2070,13 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BN6">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BO6">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BP6">
         <v>10.5</v>
@@ -2073,16 +2085,16 @@
         <v>4.1</v>
       </c>
       <c r="BR6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS6">
         <v>5.2</v>
       </c>
       <c r="BT6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2097,13 +2109,13 @@
         <v>5.9</v>
       </c>
       <c r="BZ6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2111,241 +2123,483 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7">
+        <v>1.05</v>
+      </c>
+      <c r="G7">
+        <v>990</v>
+      </c>
+      <c r="H7">
+        <v>1.1</v>
+      </c>
+      <c r="I7">
+        <v>990</v>
+      </c>
+      <c r="J7">
+        <v>3.55</v>
+      </c>
+      <c r="K7">
+        <v>950</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>1.26</v>
+      </c>
+      <c r="O7">
+        <v>1.2</v>
+      </c>
+      <c r="P7">
+        <v>1.25</v>
+      </c>
+      <c r="Q7">
+        <v>1.2</v>
+      </c>
+      <c r="R7">
+        <v>1.13</v>
+      </c>
+      <c r="S7">
+        <v>1.2</v>
+      </c>
+      <c r="T7">
+        <v>1.11</v>
+      </c>
+      <c r="U7">
+        <v>1.11</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.27</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7">
+        <v>1.01</v>
+      </c>
+      <c r="AR7">
+        <v>1.01</v>
+      </c>
+      <c r="AS7">
+        <v>1.01</v>
+      </c>
+      <c r="AT7">
+        <v>1.01</v>
+      </c>
+      <c r="AU7">
+        <v>1.01</v>
+      </c>
+      <c r="AV7">
+        <v>1.01</v>
+      </c>
+      <c r="AW7">
+        <v>1.01</v>
+      </c>
+      <c r="AX7">
+        <v>1.01</v>
+      </c>
+      <c r="AY7">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7">
+        <v>1.01</v>
+      </c>
+      <c r="BA7">
+        <v>1.01</v>
+      </c>
+      <c r="BB7">
+        <v>1.01</v>
+      </c>
+      <c r="BC7">
+        <v>1.01</v>
+      </c>
+      <c r="BD7">
+        <v>1.01</v>
+      </c>
+      <c r="BE7">
+        <v>1.01</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.04</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.04</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.04</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.04</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.04</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.04</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.04</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.04</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.04</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.04</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
         <v>84</v>
       </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7">
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8">
+        <v>1.32</v>
+      </c>
+      <c r="G8">
         <v>1.33</v>
       </c>
-      <c r="G7">
-        <v>1.34</v>
-      </c>
-      <c r="H7">
+      <c r="H8">
+        <v>13</v>
+      </c>
+      <c r="I8">
+        <v>13.5</v>
+      </c>
+      <c r="J8">
+        <v>5.9</v>
+      </c>
+      <c r="K8">
+        <v>6</v>
+      </c>
+      <c r="L8">
+        <v>1.28</v>
+      </c>
+      <c r="M8">
+        <v>1.05</v>
+      </c>
+      <c r="N8">
+        <v>4.4</v>
+      </c>
+      <c r="O8">
+        <v>1.27</v>
+      </c>
+      <c r="P8">
+        <v>2.2</v>
+      </c>
+      <c r="Q8">
+        <v>1.76</v>
+      </c>
+      <c r="R8">
+        <v>1.47</v>
+      </c>
+      <c r="S8">
+        <v>2.94</v>
+      </c>
+      <c r="T8">
+        <v>2.28</v>
+      </c>
+      <c r="U8">
+        <v>1.72</v>
+      </c>
+      <c r="V8">
+        <v>1.08</v>
+      </c>
+      <c r="W8">
+        <v>4</v>
+      </c>
+      <c r="X8">
+        <v>17.5</v>
+      </c>
+      <c r="Y8">
+        <v>34</v>
+      </c>
+      <c r="Z8">
+        <v>130</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>8</v>
+      </c>
+      <c r="AC8">
+        <v>13</v>
+      </c>
+      <c r="AD8">
+        <v>48</v>
+      </c>
+      <c r="AE8">
+        <v>260</v>
+      </c>
+      <c r="AF8">
+        <v>7.4</v>
+      </c>
+      <c r="AG8">
+        <v>11</v>
+      </c>
+      <c r="AH8">
+        <v>38</v>
+      </c>
+      <c r="AI8">
+        <v>200</v>
+      </c>
+      <c r="AJ8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK8">
+        <v>15</v>
+      </c>
+      <c r="AL8">
+        <v>48</v>
+      </c>
+      <c r="AM8">
+        <v>250</v>
+      </c>
+      <c r="AN8">
+        <v>5.6</v>
+      </c>
+      <c r="AO8">
+        <v>470</v>
+      </c>
+      <c r="AP8">
+        <v>16.5</v>
+      </c>
+      <c r="AQ8">
+        <v>27</v>
+      </c>
+      <c r="AR8">
+        <v>40</v>
+      </c>
+      <c r="AS8">
+        <v>21</v>
+      </c>
+      <c r="AT8">
+        <v>7.6</v>
+      </c>
+      <c r="AU8">
         <v>12</v>
       </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>5.9</v>
-      </c>
-      <c r="K7">
-        <v>6.2</v>
-      </c>
-      <c r="L7">
-        <v>1.28</v>
-      </c>
-      <c r="M7">
-        <v>1.05</v>
-      </c>
-      <c r="N7">
-        <v>4.4</v>
-      </c>
-      <c r="O7">
-        <v>1.27</v>
-      </c>
-      <c r="P7">
-        <v>2.2</v>
-      </c>
-      <c r="Q7">
-        <v>1.76</v>
-      </c>
-      <c r="R7">
-        <v>1.47</v>
-      </c>
-      <c r="S7">
-        <v>2.94</v>
-      </c>
-      <c r="T7">
-        <v>2.3</v>
-      </c>
-      <c r="U7">
-        <v>1.73</v>
-      </c>
-      <c r="V7">
-        <v>1.08</v>
-      </c>
-      <c r="W7">
-        <v>3.95</v>
-      </c>
-      <c r="X7">
-        <v>17.5</v>
-      </c>
-      <c r="Y7">
+      <c r="AV8">
         <v>36</v>
       </c>
-      <c r="Z7">
-        <v>130</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>8</v>
-      </c>
-      <c r="AC7">
-        <v>13</v>
-      </c>
-      <c r="AD7">
+      <c r="AW8">
         <v>48</v>
       </c>
-      <c r="AE7">
-        <v>260</v>
-      </c>
-      <c r="AF7">
-        <v>7.4</v>
-      </c>
-      <c r="AG7">
-        <v>11</v>
-      </c>
-      <c r="AH7">
-        <v>38</v>
-      </c>
-      <c r="AI7">
-        <v>200</v>
-      </c>
-      <c r="AJ7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK7">
-        <v>15</v>
-      </c>
-      <c r="AL7">
+      <c r="AX8">
+        <v>6.8</v>
+      </c>
+      <c r="AY8">
+        <v>10</v>
+      </c>
+      <c r="AZ8">
+        <v>30</v>
+      </c>
+      <c r="BA8">
         <v>48</v>
       </c>
-      <c r="AM7">
-        <v>250</v>
-      </c>
-      <c r="AN7">
+      <c r="BB8">
+        <v>9</v>
+      </c>
+      <c r="BC8">
+        <v>13.5</v>
+      </c>
+      <c r="BD8">
+        <v>40</v>
+      </c>
+      <c r="BE8">
+        <v>50</v>
+      </c>
+      <c r="BF8">
+        <v>5.2</v>
+      </c>
+      <c r="BG8">
+        <v>95</v>
+      </c>
+      <c r="BH8">
+        <v>4</v>
+      </c>
+      <c r="BI8">
+        <v>3.05</v>
+      </c>
+      <c r="BJ8">
+        <v>14</v>
+      </c>
+      <c r="BK8">
+        <v>6</v>
+      </c>
+      <c r="BL8">
+        <v>220</v>
+      </c>
+      <c r="BM8">
+        <v>10.5</v>
+      </c>
+      <c r="BN8">
+        <v>3.7</v>
+      </c>
+      <c r="BO8">
+        <v>2.86</v>
+      </c>
+      <c r="BP8">
+        <v>7.8</v>
+      </c>
+      <c r="BQ8">
         <v>5.6</v>
       </c>
-      <c r="AO7">
-        <v>470</v>
-      </c>
-      <c r="AP7">
-        <v>16.5</v>
-      </c>
-      <c r="AQ7">
-        <v>27</v>
-      </c>
-      <c r="AR7">
-        <v>40</v>
-      </c>
-      <c r="AS7">
-        <v>21</v>
-      </c>
-      <c r="AT7">
-        <v>7.6</v>
-      </c>
-      <c r="AU7">
-        <v>12</v>
-      </c>
-      <c r="AV7">
-        <v>36</v>
-      </c>
-      <c r="AW7">
-        <v>48</v>
-      </c>
-      <c r="AX7">
-        <v>6.8</v>
-      </c>
-      <c r="AY7">
+      <c r="BR8">
+        <v>28</v>
+      </c>
+      <c r="BS8">
+        <v>7.8</v>
+      </c>
+      <c r="BT8">
+        <v>16</v>
+      </c>
+      <c r="BU8">
+        <v>6.4</v>
+      </c>
+      <c r="BV8">
+        <v>140</v>
+      </c>
+      <c r="BW8">
         <v>10</v>
       </c>
-      <c r="AZ7">
-        <v>30</v>
-      </c>
-      <c r="BA7">
-        <v>48</v>
-      </c>
-      <c r="BB7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC7">
-        <v>13.5</v>
-      </c>
-      <c r="BD7">
-        <v>40</v>
-      </c>
-      <c r="BE7">
-        <v>50</v>
-      </c>
-      <c r="BF7">
-        <v>5.2</v>
-      </c>
-      <c r="BG7">
-        <v>95</v>
-      </c>
-      <c r="BH7">
-        <v>4</v>
-      </c>
-      <c r="BI7">
-        <v>3.05</v>
-      </c>
-      <c r="BJ7">
+      <c r="BX8">
+        <v>120</v>
+      </c>
+      <c r="BY8">
+        <v>10</v>
+      </c>
+      <c r="BZ8">
         <v>14</v>
       </c>
-      <c r="BK7">
+      <c r="CA8">
         <v>6</v>
       </c>
-      <c r="BL7">
-        <v>220</v>
-      </c>
-      <c r="BM7">
-        <v>10.5</v>
-      </c>
-      <c r="BN7">
-        <v>3.7</v>
-      </c>
-      <c r="BO7">
-        <v>2.86</v>
-      </c>
-      <c r="BP7">
-        <v>7.8</v>
-      </c>
-      <c r="BQ7">
-        <v>5.6</v>
-      </c>
-      <c r="BR7">
-        <v>28</v>
-      </c>
-      <c r="BS7">
-        <v>7.8</v>
-      </c>
-      <c r="BT7">
-        <v>16</v>
-      </c>
-      <c r="BU7">
-        <v>6.4</v>
-      </c>
-      <c r="BV7">
-        <v>140</v>
-      </c>
-      <c r="BW7">
-        <v>10</v>
-      </c>
-      <c r="BX7">
-        <v>120</v>
-      </c>
-      <c r="BY7">
-        <v>10</v>
-      </c>
-      <c r="BZ7">
-        <v>14</v>
-      </c>
-      <c r="CA7">
-        <v>6</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>101</v>
+      <c r="CB8" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -331,7 +331,7 @@
     <t>Malaga</t>
   </si>
   <si>
-    <t>2026-08-17 16:01:02</t>
+    <t>2026-08-17 18:08:56</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1096,7 @@
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1108,7 +1108,7 @@
         <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
         <v>20</v>
@@ -1167,7 +1167,7 @@
         <v>99</v>
       </c>
       <c r="F3">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G3">
         <v>2.88</v>
@@ -1176,7 +1176,7 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -1197,7 +1197,7 @@
         <v>1.55</v>
       </c>
       <c r="P3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
         <v>2.62</v>
@@ -1215,7 +1215,7 @@
         <v>1.8</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
         <v>1.53</v>
@@ -1242,7 +1242,7 @@
         <v>17</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF3">
         <v>20</v>
@@ -1254,13 +1254,13 @@
         <v>26</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL3">
         <v>65</v>
@@ -1284,7 +1284,7 @@
         <v>17</v>
       </c>
       <c r="AS3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1308,7 +1308,7 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB3">
         <v>32</v>
@@ -1320,13 +1320,13 @@
         <v>42</v>
       </c>
       <c r="BE3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF3">
         <v>27</v>
       </c>
       <c r="BG3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH3">
         <v>2.68</v>
@@ -1350,7 +1350,7 @@
         <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP3">
         <v>1000</v>
@@ -1368,7 +1368,7 @@
         <v>6</v>
       </c>
       <c r="BU3">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1418,7 +1418,7 @@
         <v>2.6</v>
       </c>
       <c r="I4">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J4">
         <v>3.2</v>
@@ -1439,10 +1439,10 @@
         <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1451,13 +1451,13 @@
         <v>4.6</v>
       </c>
       <c r="T4">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W4">
         <v>1.45</v>
@@ -1893,55 +1893,55 @@
         <v>102</v>
       </c>
       <c r="F6">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="G6">
         <v>1.56</v>
       </c>
       <c r="H6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R6">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="S6">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T6">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="U6">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="V6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W6">
         <v>2.78</v>
@@ -1959,7 +1959,7 @@
         <v>210</v>
       </c>
       <c r="AB6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC6">
         <v>12.5</v>
@@ -1971,37 +1971,37 @@
         <v>85</v>
       </c>
       <c r="AF6">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI6">
         <v>80</v>
       </c>
       <c r="AJ6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM6">
         <v>100</v>
       </c>
       <c r="AN6">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AO6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP6">
-        <v>5.7</v>
+        <v>23</v>
       </c>
       <c r="AQ6">
         <v>24</v>
@@ -2010,25 +2010,25 @@
         <v>44</v>
       </c>
       <c r="AS6">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AT6">
         <v>10</v>
       </c>
       <c r="AU6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV6">
         <v>19.5</v>
       </c>
       <c r="AW6">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX6">
         <v>9.800000000000001</v>
       </c>
       <c r="AY6">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
         <v>14</v>
@@ -2037,10 +2037,10 @@
         <v>50</v>
       </c>
       <c r="BB6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD6">
         <v>20</v>
@@ -2052,67 +2052,67 @@
         <v>4.8</v>
       </c>
       <c r="BG6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH6">
+        <v>5</v>
+      </c>
+      <c r="BI6">
+        <v>3.85</v>
+      </c>
+      <c r="BJ6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK6">
+        <v>4.9</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN6">
+        <v>4.8</v>
+      </c>
+      <c r="BO6">
+        <v>3.7</v>
+      </c>
+      <c r="BP6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ6">
+        <v>4.9</v>
+      </c>
+      <c r="BR6">
+        <v>20</v>
+      </c>
+      <c r="BS6">
+        <v>6.6</v>
+      </c>
+      <c r="BT6">
+        <v>10.5</v>
+      </c>
+      <c r="BU6">
         <v>5.1</v>
       </c>
-      <c r="BI6">
-        <v>3.75</v>
-      </c>
-      <c r="BJ6">
-        <v>10.5</v>
-      </c>
-      <c r="BK6">
-        <v>4.1</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>6.2</v>
-      </c>
-      <c r="BN6">
-        <v>4.9</v>
-      </c>
-      <c r="BO6">
-        <v>3.65</v>
-      </c>
-      <c r="BP6">
-        <v>10.5</v>
-      </c>
-      <c r="BQ6">
-        <v>4.1</v>
-      </c>
-      <c r="BR6">
-        <v>22</v>
-      </c>
-      <c r="BS6">
-        <v>5.2</v>
-      </c>
-      <c r="BT6">
-        <v>11</v>
-      </c>
-      <c r="BU6">
-        <v>4.2</v>
-      </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BZ6">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="CA6">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB6" t="s">
         <v>105</v>
@@ -2135,19 +2135,19 @@
         <v>103</v>
       </c>
       <c r="F7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="G7">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>1.57</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2159,13 +2159,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O7">
         <v>1.2</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q7">
         <v>1.2</v>
@@ -2183,10 +2183,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2377,10 +2377,10 @@
         <v>104</v>
       </c>
       <c r="F8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H8">
         <v>13</v>
@@ -2389,13 +2389,13 @@
         <v>13.5</v>
       </c>
       <c r="J8">
+        <v>5.8</v>
+      </c>
+      <c r="K8">
         <v>5.9</v>
       </c>
-      <c r="K8">
-        <v>6</v>
-      </c>
       <c r="L8">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M8">
         <v>1.05</v>
@@ -2416,10 +2416,10 @@
         <v>1.47</v>
       </c>
       <c r="S8">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U8">
         <v>1.72</v>
@@ -2434,13 +2434,13 @@
         <v>17.5</v>
       </c>
       <c r="Y8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z8">
         <v>130</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>680</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -2452,16 +2452,16 @@
         <v>48</v>
       </c>
       <c r="AE8">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AF8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG8">
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI8">
         <v>200</v>
@@ -2473,40 +2473,40 @@
         <v>15</v>
       </c>
       <c r="AL8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM8">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN8">
         <v>5.6</v>
       </c>
       <c r="AO8">
-        <v>470</v>
+        <v>380</v>
       </c>
       <c r="AP8">
         <v>16.5</v>
       </c>
       <c r="AQ8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AR8">
         <v>40</v>
       </c>
       <c r="AS8">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AT8">
         <v>7.6</v>
       </c>
       <c r="AU8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV8">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AW8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX8">
         <v>6.8</v>
@@ -2515,13 +2515,13 @@
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA8">
         <v>48</v>
       </c>
       <c r="BB8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC8">
         <v>13.5</v>
@@ -2533,70 +2533,70 @@
         <v>50</v>
       </c>
       <c r="BF8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG8">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BH8">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BI8">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8">
         <v>14</v>
       </c>
       <c r="BK8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BL8">
         <v>220</v>
       </c>
       <c r="BM8">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN8">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BO8">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="BP8">
         <v>7.8</v>
       </c>
       <c r="BQ8">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR8">
         <v>28</v>
       </c>
       <c r="BS8">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BT8">
         <v>16</v>
       </c>
       <c r="BU8">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BV8">
         <v>140</v>
       </c>
       <c r="BW8">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BX8">
         <v>120</v>
       </c>
       <c r="BY8">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BZ8">
         <v>14</v>
       </c>
       <c r="CA8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="s">
         <v>105</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -331,7 +331,7 @@
     <t>Malaga</t>
   </si>
   <si>
-    <t>2026-08-17 18:08:56</t>
+    <t>2026-08-17 20:16:10</t>
   </si>
 </sst>
 </file>
@@ -925,7 +925,7 @@
         <v>98</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
         <v>2.3</v>
@@ -934,7 +934,7 @@
         <v>3.9</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J2">
         <v>3.25</v>
@@ -952,13 +952,13 @@
         <v>3.15</v>
       </c>
       <c r="O2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
         <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
         <v>1.27</v>
@@ -1027,7 +1027,7 @@
         <v>140</v>
       </c>
       <c r="AN2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO2">
         <v>70</v>
@@ -1054,7 +1054,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1066,7 +1066,7 @@
         <v>16</v>
       </c>
       <c r="BA2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB2">
         <v>6.6</v>
@@ -1075,10 +1075,10 @@
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF2">
         <v>19</v>
@@ -1167,22 +1167,22 @@
         <v>99</v>
       </c>
       <c r="F3">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="G3">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
         <v>1.51</v>
@@ -1191,22 +1191,22 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O3">
         <v>1.55</v>
       </c>
       <c r="P3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q3">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="R3">
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T3">
         <v>2.1</v>
@@ -1215,7 +1215,7 @@
         <v>1.8</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W3">
         <v>1.53</v>
@@ -1269,7 +1269,7 @@
         <v>200</v>
       </c>
       <c r="AN3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO3">
         <v>80</v>
@@ -1284,7 +1284,7 @@
         <v>17</v>
       </c>
       <c r="AS3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1308,7 +1308,7 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB3">
         <v>32</v>
@@ -1320,13 +1320,13 @@
         <v>42</v>
       </c>
       <c r="BE3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF3">
         <v>27</v>
       </c>
       <c r="BG3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH3">
         <v>2.68</v>
@@ -1421,7 +1421,7 @@
         <v>2.7</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
         <v>3.3</v>
@@ -1433,16 +1433,16 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1451,7 +1451,7 @@
         <v>4.6</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U4">
         <v>1.93</v>
@@ -1469,7 +1469,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA4">
         <v>44</v>
@@ -1505,7 +1505,7 @@
         <v>44</v>
       </c>
       <c r="AL4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM4">
         <v>150</v>
@@ -1526,13 +1526,13 @@
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="AT4">
         <v>8.800000000000001</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
         <v>10.5</v>
@@ -1550,22 +1550,22 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC4">
+        <v>34</v>
+      </c>
+      <c r="BD4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE4">
+        <v>9</v>
+      </c>
+      <c r="BF4">
         <v>8</v>
-      </c>
-      <c r="BC4">
-        <v>7.6</v>
-      </c>
-      <c r="BD4">
-        <v>8</v>
-      </c>
-      <c r="BE4">
-        <v>8.6</v>
-      </c>
-      <c r="BF4">
-        <v>36</v>
       </c>
       <c r="BG4">
         <v>7.4</v>
@@ -1672,7 +1672,7 @@
         <v>1.63</v>
       </c>
       <c r="M5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N5">
         <v>2.5</v>
@@ -1723,7 +1723,7 @@
         <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE5">
         <v>85</v>
@@ -1789,7 +1789,7 @@
         <v>11</v>
       </c>
       <c r="AZ5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA5">
         <v>10</v>
@@ -1893,22 +1893,22 @@
         <v>102</v>
       </c>
       <c r="F6">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G6">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L6">
         <v>1.22</v>
@@ -1923,28 +1923,28 @@
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q6">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R6">
         <v>1.69</v>
       </c>
       <c r="S6">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T6">
         <v>1.63</v>
       </c>
       <c r="U6">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V6">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="X6">
         <v>30</v>
@@ -1953,7 +1953,7 @@
         <v>34</v>
       </c>
       <c r="Z6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA6">
         <v>210</v>
@@ -1962,7 +1962,7 @@
         <v>13.5</v>
       </c>
       <c r="AC6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD6">
         <v>26</v>
@@ -1980,7 +1980,7 @@
         <v>18.5</v>
       </c>
       <c r="AI6">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ6">
         <v>16</v>
@@ -2001,7 +2001,7 @@
         <v>60</v>
       </c>
       <c r="AP6">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ6">
         <v>24</v>
@@ -2022,7 +2022,7 @@
         <v>19.5</v>
       </c>
       <c r="AW6">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX6">
         <v>9.800000000000001</v>
@@ -2135,19 +2135,19 @@
         <v>103</v>
       </c>
       <c r="F7">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G7">
-        <v>110</v>
+        <v>3.05</v>
       </c>
       <c r="H7">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2159,13 +2159,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O7">
         <v>1.2</v>
       </c>
       <c r="P7">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q7">
         <v>1.2</v>
@@ -2183,10 +2183,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W7">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2377,10 +2377,10 @@
         <v>104</v>
       </c>
       <c r="F8">
+        <v>1.32</v>
+      </c>
+      <c r="G8">
         <v>1.33</v>
-      </c>
-      <c r="G8">
-        <v>1.34</v>
       </c>
       <c r="H8">
         <v>13</v>
@@ -2389,19 +2389,19 @@
         <v>13.5</v>
       </c>
       <c r="J8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M8">
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O8">
         <v>1.27</v>
@@ -2410,13 +2410,13 @@
         <v>2.2</v>
       </c>
       <c r="Q8">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R8">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T8">
         <v>2.3</v>
@@ -2434,13 +2434,13 @@
         <v>17.5</v>
       </c>
       <c r="Y8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z8">
         <v>130</v>
       </c>
       <c r="AA8">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -2452,10 +2452,10 @@
         <v>48</v>
       </c>
       <c r="AE8">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AF8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AG8">
         <v>11</v>
@@ -2467,7 +2467,7 @@
         <v>200</v>
       </c>
       <c r="AJ8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AK8">
         <v>15</v>
@@ -2479,10 +2479,10 @@
         <v>240</v>
       </c>
       <c r="AN8">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO8">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AP8">
         <v>16.5</v>
@@ -2503,13 +2503,13 @@
         <v>12.5</v>
       </c>
       <c r="AV8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AW8">
         <v>50</v>
       </c>
       <c r="AX8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY8">
         <v>10</v>
@@ -2521,7 +2521,7 @@
         <v>48</v>
       </c>
       <c r="BB8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC8">
         <v>13.5</v>
@@ -2548,13 +2548,13 @@
         <v>14</v>
       </c>
       <c r="BK8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="BM8">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN8">
         <v>3.55</v>
@@ -2563,7 +2563,7 @@
         <v>3.3</v>
       </c>
       <c r="BP8">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BQ8">
         <v>6.6</v>
@@ -2572,31 +2572,31 @@
         <v>28</v>
       </c>
       <c r="BS8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT8">
         <v>16</v>
       </c>
       <c r="BU8">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BV8">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BW8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX8">
         <v>120</v>
       </c>
       <c r="BY8">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BZ8">
         <v>14</v>
       </c>
       <c r="CA8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="s">
         <v>105</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -331,7 +331,7 @@
     <t>Malaga</t>
   </si>
   <si>
-    <t>2026-08-17 20:16:10</t>
+    <t>2026-08-17 22:23:24</t>
   </si>
 </sst>
 </file>
@@ -925,7 +925,7 @@
         <v>98</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
         <v>2.3</v>
@@ -934,103 +934,103 @@
         <v>3.9</v>
       </c>
       <c r="I2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J2">
+        <v>3.2</v>
+      </c>
+      <c r="K2">
         <v>3.25</v>
       </c>
-      <c r="K2">
-        <v>3.3</v>
-      </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M2">
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
         <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="U2">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="V2">
         <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X2">
         <v>13</v>
       </c>
       <c r="Y2">
+        <v>14.5</v>
+      </c>
+      <c r="Z2">
+        <v>32</v>
+      </c>
+      <c r="AA2">
+        <v>95</v>
+      </c>
+      <c r="AB2">
+        <v>9.6</v>
+      </c>
+      <c r="AC2">
+        <v>8.6</v>
+      </c>
+      <c r="AD2">
+        <v>19</v>
+      </c>
+      <c r="AE2">
+        <v>65</v>
+      </c>
+      <c r="AF2">
+        <v>15.5</v>
+      </c>
+      <c r="AG2">
         <v>13</v>
       </c>
-      <c r="Z2">
-        <v>28</v>
-      </c>
-      <c r="AA2">
-        <v>90</v>
-      </c>
-      <c r="AB2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC2">
-        <v>7.8</v>
-      </c>
-      <c r="AD2">
-        <v>17</v>
-      </c>
-      <c r="AE2">
-        <v>60</v>
-      </c>
-      <c r="AF2">
-        <v>14</v>
-      </c>
-      <c r="AG2">
-        <v>12</v>
-      </c>
       <c r="AH2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ2">
         <v>36</v>
       </c>
       <c r="AK2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AO2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP2">
         <v>9.6</v>
@@ -1039,112 +1039,112 @@
         <v>10.5</v>
       </c>
       <c r="AR2">
+        <v>4.4</v>
+      </c>
+      <c r="AS2">
+        <v>4.9</v>
+      </c>
+      <c r="AT2">
+        <v>7</v>
+      </c>
+      <c r="AU2">
+        <v>6.2</v>
+      </c>
+      <c r="AV2">
+        <v>14</v>
+      </c>
+      <c r="AW2">
+        <v>4.7</v>
+      </c>
+      <c r="AX2">
+        <v>11</v>
+      </c>
+      <c r="AY2">
+        <v>9.6</v>
+      </c>
+      <c r="AZ2">
+        <v>16.5</v>
+      </c>
+      <c r="BA2">
+        <v>4.8</v>
+      </c>
+      <c r="BB2">
+        <v>4.5</v>
+      </c>
+      <c r="BC2">
+        <v>4.4</v>
+      </c>
+      <c r="BD2">
+        <v>4.7</v>
+      </c>
+      <c r="BE2">
+        <v>4.9</v>
+      </c>
+      <c r="BF2">
+        <v>18.5</v>
+      </c>
+      <c r="BG2">
+        <v>4.8</v>
+      </c>
+      <c r="BH2">
+        <v>3.4</v>
+      </c>
+      <c r="BI2">
+        <v>2.56</v>
+      </c>
+      <c r="BJ2">
+        <v>12</v>
+      </c>
+      <c r="BK2">
+        <v>3.95</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>5.7</v>
+      </c>
+      <c r="BN2">
+        <v>5.6</v>
+      </c>
+      <c r="BO2">
+        <v>3.95</v>
+      </c>
+      <c r="BP2">
         <v>21</v>
       </c>
-      <c r="AS2">
-        <v>7.4</v>
-      </c>
-      <c r="AT2">
-        <v>7.4</v>
-      </c>
-      <c r="AU2">
-        <v>6.4</v>
-      </c>
-      <c r="AV2">
-        <v>12</v>
-      </c>
-      <c r="AW2">
-        <v>7</v>
-      </c>
-      <c r="AX2">
-        <v>11.5</v>
-      </c>
-      <c r="AY2">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2">
-        <v>16</v>
-      </c>
-      <c r="BA2">
-        <v>7.2</v>
-      </c>
-      <c r="BB2">
-        <v>6.6</v>
-      </c>
-      <c r="BC2">
-        <v>21</v>
-      </c>
-      <c r="BD2">
-        <v>6.8</v>
-      </c>
-      <c r="BE2">
-        <v>7.6</v>
-      </c>
-      <c r="BF2">
-        <v>19</v>
-      </c>
-      <c r="BG2">
-        <v>7.2</v>
-      </c>
-      <c r="BH2">
-        <v>3.45</v>
-      </c>
-      <c r="BI2">
-        <v>2.58</v>
-      </c>
-      <c r="BJ2">
-        <v>11.5</v>
-      </c>
-      <c r="BK2">
-        <v>8</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>6.4</v>
-      </c>
-      <c r="BN2">
-        <v>5.1</v>
-      </c>
-      <c r="BO2">
-        <v>4.3</v>
-      </c>
-      <c r="BP2">
-        <v>20</v>
-      </c>
       <c r="BQ2">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BR2">
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV2">
         <v>38</v>
       </c>
       <c r="BW2">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BX2">
         <v>55</v>
       </c>
       <c r="BY2">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BZ2">
         <v>40</v>
       </c>
       <c r="CA2">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1170,10 +1170,10 @@
         <v>2.8</v>
       </c>
       <c r="G3">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>3.15</v>
@@ -1188,40 +1188,40 @@
         <v>1.51</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P3">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
         <v>1.53</v>
       </c>
       <c r="X3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y3">
         <v>10</v>
@@ -1242,7 +1242,7 @@
         <v>17</v>
       </c>
       <c r="AE3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>20</v>
@@ -1251,40 +1251,40 @@
         <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI3">
         <v>80</v>
       </c>
       <c r="AJ3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK3">
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AM3">
         <v>200</v>
       </c>
       <c r="AN3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AO3">
         <v>80</v>
       </c>
       <c r="AP3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR3">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1293,40 +1293,40 @@
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW3">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="AX3">
         <v>14.5</v>
       </c>
       <c r="AY3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="BA3">
         <v>7.4</v>
       </c>
       <c r="BB3">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="BC3">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BD3">
-        <v>42</v>
+        <v>7.2</v>
       </c>
       <c r="BE3">
         <v>7.8</v>
       </c>
       <c r="BF3">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="BG3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH3">
         <v>2.68</v>
@@ -1338,13 +1338,13 @@
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN3">
         <v>5.6</v>
@@ -1356,16 +1356,16 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU3">
         <v>5.3</v>
@@ -1374,19 +1374,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
+        <v>13.5</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
         <v>13</v>
-      </c>
-      <c r="BZ3">
-        <v>1000</v>
-      </c>
-      <c r="CA3">
-        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
         <v>105</v>
@@ -1409,178 +1409,178 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H4">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="I4">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="J4">
+        <v>3.15</v>
+      </c>
+      <c r="K4">
         <v>3.25</v>
       </c>
-      <c r="K4">
-        <v>3.3</v>
-      </c>
       <c r="L4">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="Q4">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="T4">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="W4">
         <v>1.45</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA4">
+        <v>48</v>
+      </c>
+      <c r="AB4">
+        <v>10</v>
+      </c>
+      <c r="AC4">
+        <v>6.8</v>
+      </c>
+      <c r="AD4">
+        <v>13.5</v>
+      </c>
+      <c r="AE4">
+        <v>40</v>
+      </c>
+      <c r="AF4">
+        <v>19.5</v>
+      </c>
+      <c r="AG4">
+        <v>15.5</v>
+      </c>
+      <c r="AH4">
+        <v>23</v>
+      </c>
+      <c r="AI4">
+        <v>65</v>
+      </c>
+      <c r="AJ4">
+        <v>65</v>
+      </c>
+      <c r="AK4">
+        <v>48</v>
+      </c>
+      <c r="AL4">
+        <v>75</v>
+      </c>
+      <c r="AM4">
+        <v>170</v>
+      </c>
+      <c r="AN4">
+        <v>60</v>
+      </c>
+      <c r="AO4">
         <v>44</v>
       </c>
-      <c r="AB4">
-        <v>10.5</v>
-      </c>
-      <c r="AC4">
-        <v>7.6</v>
-      </c>
-      <c r="AD4">
-        <v>13</v>
-      </c>
-      <c r="AE4">
-        <v>36</v>
-      </c>
-      <c r="AF4">
-        <v>22</v>
-      </c>
-      <c r="AG4">
-        <v>14.5</v>
-      </c>
-      <c r="AH4">
-        <v>21</v>
-      </c>
-      <c r="AI4">
-        <v>55</v>
-      </c>
-      <c r="AJ4">
-        <v>60</v>
-      </c>
-      <c r="AK4">
-        <v>44</v>
-      </c>
-      <c r="AL4">
-        <v>60</v>
-      </c>
-      <c r="AM4">
-        <v>150</v>
-      </c>
-      <c r="AN4">
-        <v>50</v>
-      </c>
-      <c r="AO4">
-        <v>36</v>
-      </c>
       <c r="AP4">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR4">
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT4">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX4">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA4">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BB4">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC4">
+        <v>40</v>
+      </c>
+      <c r="BD4">
+        <v>60</v>
+      </c>
+      <c r="BE4">
+        <v>10</v>
+      </c>
+      <c r="BF4">
+        <v>46</v>
+      </c>
+      <c r="BG4">
         <v>34</v>
       </c>
-      <c r="BD4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE4">
-        <v>9</v>
-      </c>
-      <c r="BF4">
-        <v>8</v>
-      </c>
-      <c r="BG4">
-        <v>7.4</v>
-      </c>
       <c r="BH4">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="BI4">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1595,40 +1595,40 @@
         <v>4.8</v>
       </c>
       <c r="BP4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BQ4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BS4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU4">
         <v>4.3</v>
       </c>
       <c r="BV4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX4">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BY4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="CA4">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="s">
         <v>105</v>
@@ -1657,16 +1657,16 @@
         <v>2.54</v>
       </c>
       <c r="H5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I5">
         <v>3.8</v>
       </c>
       <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
         <v>3.05</v>
-      </c>
-      <c r="K5">
-        <v>3.1</v>
       </c>
       <c r="L5">
         <v>1.63</v>
@@ -1678,10 +1678,10 @@
         <v>2.5</v>
       </c>
       <c r="O5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P5">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q5">
         <v>2.76</v>
@@ -1690,7 +1690,7 @@
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T5">
         <v>2.16</v>
@@ -1702,7 +1702,7 @@
         <v>1.35</v>
       </c>
       <c r="W5">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X5">
         <v>8.199999999999999</v>
@@ -1813,7 +1813,7 @@
         <v>10</v>
       </c>
       <c r="BH5">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI5">
         <v>2.22</v>
@@ -1849,10 +1849,10 @@
         <v>5.6</v>
       </c>
       <c r="BT5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
         <v>42</v>
@@ -1893,208 +1893,208 @@
         <v>102</v>
       </c>
       <c r="F6">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="G6">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="H6">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="K6">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L6">
         <v>1.22</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O6">
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q6">
         <v>1.5</v>
       </c>
       <c r="R6">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="S6">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="T6">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U6">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W6">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="X6">
         <v>30</v>
       </c>
       <c r="Y6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA6">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
         <v>13.5</v>
       </c>
       <c r="AC6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE6">
         <v>85</v>
       </c>
       <c r="AF6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG6">
         <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL6">
         <v>27</v>
       </c>
       <c r="AM6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN6">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AO6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AQ6">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AR6">
         <v>44</v>
       </c>
       <c r="AS6">
+        <v>46</v>
+      </c>
+      <c r="AT6">
+        <v>11.5</v>
+      </c>
+      <c r="AU6">
+        <v>10.5</v>
+      </c>
+      <c r="AV6">
+        <v>22</v>
+      </c>
+      <c r="AW6">
+        <v>32</v>
+      </c>
+      <c r="AX6">
         <v>10</v>
       </c>
-      <c r="AT6">
-        <v>10</v>
-      </c>
-      <c r="AU6">
-        <v>10</v>
-      </c>
-      <c r="AV6">
-        <v>19.5</v>
-      </c>
-      <c r="AW6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX6">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AY6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA6">
         <v>50</v>
       </c>
       <c r="BB6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC6">
         <v>12.5</v>
       </c>
       <c r="BD6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE6">
         <v>50</v>
       </c>
       <c r="BF6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG6">
         <v>40</v>
       </c>
       <c r="BH6">
+        <v>5.1</v>
+      </c>
+      <c r="BI6">
+        <v>3.95</v>
+      </c>
+      <c r="BJ6">
+        <v>10.5</v>
+      </c>
+      <c r="BK6">
         <v>5</v>
       </c>
-      <c r="BI6">
-        <v>3.85</v>
-      </c>
-      <c r="BJ6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK6">
-        <v>4.9</v>
-      </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO6">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BP6">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BQ6">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BR6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BS6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2109,10 +2109,10 @@
         <v>8</v>
       </c>
       <c r="BZ6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CA6">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="CB6" t="s">
         <v>105</v>
@@ -2138,16 +2138,16 @@
         <v>1.09</v>
       </c>
       <c r="G7">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="H7">
-        <v>1.63</v>
+        <v>1.1</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2183,10 +2183,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2404,7 +2404,7 @@
         <v>4.5</v>
       </c>
       <c r="O8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
         <v>2.2</v>
@@ -2506,7 +2506,7 @@
         <v>38</v>
       </c>
       <c r="AW8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX8">
         <v>7</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="146">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,15 @@
     <t>Spanish La Liga</t>
   </si>
   <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Canadian Premier League</t>
+  </si>
+  <si>
+    <t>US MLS</t>
+  </si>
+  <si>
     <t>2026-08-19</t>
   </si>
   <si>
@@ -289,6 +298,21 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Nautico PE</t>
   </si>
   <si>
@@ -310,6 +334,54 @@
     <t>Atletico Madrid</t>
   </si>
   <si>
+    <t>Aguilas Doradas</t>
+  </si>
+  <si>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
+    <t>Cerro Porteno</t>
+  </si>
+  <si>
+    <t>Avai</t>
+  </si>
+  <si>
+    <t>Fortaleza EC</t>
+  </si>
+  <si>
+    <t>Atletico Ottawa</t>
+  </si>
+  <si>
+    <t>Forge</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Cuiaba</t>
+  </si>
+  <si>
+    <t>Toronto FC</t>
+  </si>
+  <si>
+    <t>New York Red Bulls</t>
+  </si>
+  <si>
+    <t>DC Utd</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Columbus</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
     <t>Ceara SC Fortaleza</t>
   </si>
   <si>
@@ -331,7 +403,55 @@
     <t>Malaga</t>
   </si>
   <si>
-    <t>2026-08-17 22:23:24</t>
+    <t>Llaneros FC</t>
+  </si>
+  <si>
+    <t>CA Platense</t>
+  </si>
+  <si>
+    <t>SE Palmeiras</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>Sao Bernardo</t>
+  </si>
+  <si>
+    <t>Vancouver FC</t>
+  </si>
+  <si>
+    <t>FC Supra du Quebec</t>
+  </si>
+  <si>
+    <t>Inter Miami CF</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>Operario PR</t>
+  </si>
+  <si>
+    <t>Charlotte FC</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>CF Montreal</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>2026-08-18 00:31:35</t>
   </si>
 </sst>
 </file>
@@ -663,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -913,16 +1033,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F2">
         <v>2.26</v>
@@ -958,7 +1078,7 @@
         <v>1.67</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="R2">
         <v>1.25</v>
@@ -967,10 +1087,10 @@
         <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="U2">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="V2">
         <v>1.33</v>
@@ -1045,10 +1165,10 @@
         <v>4.9</v>
       </c>
       <c r="AT2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
         <v>14</v>
@@ -1147,7 +1267,7 @@
         <v>5.1</v>
       </c>
       <c r="CB2" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1155,16 +1275,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="F3">
         <v>2.8</v>
@@ -1188,16 +1308,16 @@
         <v>1.51</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
         <v>1.56</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q3">
         <v>2.7</v>
@@ -1206,7 +1326,7 @@
         <v>1.19</v>
       </c>
       <c r="S3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T3">
         <v>2.14</v>
@@ -1221,7 +1341,7 @@
         <v>1.53</v>
       </c>
       <c r="X3">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="Y3">
         <v>10</v>
@@ -1284,7 +1404,7 @@
         <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1296,7 +1416,7 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX3">
         <v>14.5</v>
@@ -1305,28 +1425,28 @@
         <v>12</v>
       </c>
       <c r="AZ3">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB3">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BC3">
         <v>24</v>
       </c>
       <c r="BD3">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BG3">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BH3">
         <v>2.68</v>
@@ -1389,7 +1509,7 @@
         <v>13</v>
       </c>
       <c r="CB3" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1397,28 +1517,28 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="F4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G4">
         <v>3.25</v>
       </c>
       <c r="H4">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="I4">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J4">
         <v>3.15</v>
@@ -1427,22 +1547,22 @@
         <v>3.25</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="O4">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="P4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q4">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R4">
         <v>1.2</v>
@@ -1457,28 +1577,28 @@
         <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA4">
         <v>48</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD4">
         <v>13.5</v>
@@ -1490,10 +1610,10 @@
         <v>19.5</v>
       </c>
       <c r="AG4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI4">
         <v>65</v>
@@ -1505,7 +1625,7 @@
         <v>48</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM4">
         <v>170</v>
@@ -1526,7 +1646,7 @@
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT4">
         <v>8.199999999999999</v>
@@ -1538,7 +1658,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="AX4">
         <v>16.5</v>
@@ -1547,22 +1667,22 @@
         <v>13</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB4">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="BC4">
         <v>40</v>
       </c>
       <c r="BD4">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF4">
         <v>46</v>
@@ -1571,7 +1691,7 @@
         <v>34</v>
       </c>
       <c r="BH4">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI4">
         <v>2.38</v>
@@ -1580,13 +1700,13 @@
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
         <v>6.4</v>
@@ -1598,13 +1718,13 @@
         <v>30</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4">
         <v>50</v>
       </c>
       <c r="BS4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4">
         <v>5.7</v>
@@ -1616,22 +1736,22 @@
         <v>24</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ4">
         <v>46</v>
       </c>
       <c r="CA4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1639,16 +1759,16 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="F5">
         <v>2.44</v>
@@ -1657,7 +1777,7 @@
         <v>2.54</v>
       </c>
       <c r="H5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I5">
         <v>3.8</v>
@@ -1666,13 +1786,13 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L5">
         <v>1.63</v>
       </c>
       <c r="M5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N5">
         <v>2.5</v>
@@ -1681,13 +1801,13 @@
         <v>1.59</v>
       </c>
       <c r="P5">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q5">
         <v>2.76</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S5">
         <v>5.9</v>
@@ -1873,7 +1993,7 @@
         <v>5.7</v>
       </c>
       <c r="CB5" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1881,16 +2001,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="F6">
         <v>1.49</v>
@@ -1908,34 +2028,34 @@
         <v>4.9</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L6">
         <v>1.22</v>
       </c>
       <c r="M6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O6">
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q6">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R6">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S6">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="T6">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U6">
         <v>2.4</v>
@@ -1944,7 +2064,7 @@
         <v>1.16</v>
       </c>
       <c r="W6">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="X6">
         <v>30</v>
@@ -1998,7 +2118,7 @@
         <v>5.1</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP6">
         <v>20</v>
@@ -2022,7 +2142,7 @@
         <v>22</v>
       </c>
       <c r="AW6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX6">
         <v>10</v>
@@ -2052,7 +2172,7 @@
         <v>4.7</v>
       </c>
       <c r="BG6">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BH6">
         <v>5.1</v>
@@ -2115,7 +2235,7 @@
         <v>5.1</v>
       </c>
       <c r="CB6" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2123,31 +2243,31 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="F7">
         <v>1.09</v>
       </c>
       <c r="G7">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2183,10 +2303,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W7">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2357,7 +2477,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2365,16 +2485,16 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="F8">
         <v>1.32</v>
@@ -2491,7 +2611,7 @@
         <v>30</v>
       </c>
       <c r="AR8">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AS8">
         <v>55</v>
@@ -2599,7 +2719,3879 @@
         <v>7.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>105</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9">
+        <v>1.98</v>
+      </c>
+      <c r="G9">
+        <v>2.12</v>
+      </c>
+      <c r="H9">
+        <v>3.95</v>
+      </c>
+      <c r="I9">
+        <v>4.7</v>
+      </c>
+      <c r="J9">
+        <v>3.35</v>
+      </c>
+      <c r="K9">
+        <v>3.7</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.09</v>
+      </c>
+      <c r="N9">
+        <v>3.05</v>
+      </c>
+      <c r="O9">
+        <v>1.39</v>
+      </c>
+      <c r="P9">
+        <v>1.71</v>
+      </c>
+      <c r="Q9">
+        <v>2.08</v>
+      </c>
+      <c r="R9">
+        <v>1.28</v>
+      </c>
+      <c r="S9">
+        <v>3.55</v>
+      </c>
+      <c r="T9">
+        <v>1.9</v>
+      </c>
+      <c r="U9">
+        <v>1.94</v>
+      </c>
+      <c r="V9">
+        <v>1.27</v>
+      </c>
+      <c r="W9">
+        <v>1.89</v>
+      </c>
+      <c r="X9">
+        <v>14</v>
+      </c>
+      <c r="Y9">
+        <v>14</v>
+      </c>
+      <c r="Z9">
+        <v>38</v>
+      </c>
+      <c r="AA9">
+        <v>120</v>
+      </c>
+      <c r="AB9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC9">
+        <v>8</v>
+      </c>
+      <c r="AD9">
+        <v>18.5</v>
+      </c>
+      <c r="AE9">
+        <v>85</v>
+      </c>
+      <c r="AF9">
+        <v>12.5</v>
+      </c>
+      <c r="AG9">
+        <v>11</v>
+      </c>
+      <c r="AH9">
+        <v>21</v>
+      </c>
+      <c r="AI9">
+        <v>95</v>
+      </c>
+      <c r="AJ9">
+        <v>29</v>
+      </c>
+      <c r="AK9">
+        <v>32</v>
+      </c>
+      <c r="AL9">
+        <v>50</v>
+      </c>
+      <c r="AM9">
+        <v>150</v>
+      </c>
+      <c r="AN9">
+        <v>19</v>
+      </c>
+      <c r="AO9">
+        <v>100</v>
+      </c>
+      <c r="AP9">
+        <v>5.7</v>
+      </c>
+      <c r="AQ9">
+        <v>5.7</v>
+      </c>
+      <c r="AR9">
+        <v>7.4</v>
+      </c>
+      <c r="AS9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT9">
+        <v>6.2</v>
+      </c>
+      <c r="AU9">
+        <v>6.2</v>
+      </c>
+      <c r="AV9">
+        <v>6.2</v>
+      </c>
+      <c r="AW9">
+        <v>8.4</v>
+      </c>
+      <c r="AX9">
+        <v>5.4</v>
+      </c>
+      <c r="AY9">
+        <v>5.1</v>
+      </c>
+      <c r="AZ9">
+        <v>6.6</v>
+      </c>
+      <c r="BA9">
+        <v>8.6</v>
+      </c>
+      <c r="BB9">
+        <v>6.8</v>
+      </c>
+      <c r="BC9">
+        <v>6.8</v>
+      </c>
+      <c r="BD9">
+        <v>8</v>
+      </c>
+      <c r="BE9">
+        <v>9</v>
+      </c>
+      <c r="BF9">
+        <v>6.4</v>
+      </c>
+      <c r="BG9">
+        <v>8.6</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.04</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.04</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.04</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.04</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.04</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.04</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.04</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.04</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.04</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.04</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>2.4</v>
+      </c>
+      <c r="G10">
+        <v>2.56</v>
+      </c>
+      <c r="H10">
+        <v>3.5</v>
+      </c>
+      <c r="I10">
+        <v>3.85</v>
+      </c>
+      <c r="J10">
+        <v>3.05</v>
+      </c>
+      <c r="K10">
+        <v>3.25</v>
+      </c>
+      <c r="L10">
+        <v>1.47</v>
+      </c>
+      <c r="M10">
+        <v>1.12</v>
+      </c>
+      <c r="N10">
+        <v>2.5</v>
+      </c>
+      <c r="O10">
+        <v>1.49</v>
+      </c>
+      <c r="P10">
+        <v>1.48</v>
+      </c>
+      <c r="Q10">
+        <v>2.6</v>
+      </c>
+      <c r="R10">
+        <v>1.2</v>
+      </c>
+      <c r="S10">
+        <v>5.4</v>
+      </c>
+      <c r="T10">
+        <v>2.1</v>
+      </c>
+      <c r="U10">
+        <v>1.63</v>
+      </c>
+      <c r="V10">
+        <v>1.35</v>
+      </c>
+      <c r="W10">
+        <v>1.64</v>
+      </c>
+      <c r="X10">
+        <v>10.5</v>
+      </c>
+      <c r="Y10">
+        <v>10.5</v>
+      </c>
+      <c r="Z10">
+        <v>30</v>
+      </c>
+      <c r="AA10">
+        <v>110</v>
+      </c>
+      <c r="AB10">
+        <v>7.6</v>
+      </c>
+      <c r="AC10">
+        <v>7.6</v>
+      </c>
+      <c r="AD10">
+        <v>17.5</v>
+      </c>
+      <c r="AE10">
+        <v>75</v>
+      </c>
+      <c r="AF10">
+        <v>14.5</v>
+      </c>
+      <c r="AG10">
+        <v>13</v>
+      </c>
+      <c r="AH10">
+        <v>25</v>
+      </c>
+      <c r="AI10">
+        <v>110</v>
+      </c>
+      <c r="AJ10">
+        <v>44</v>
+      </c>
+      <c r="AK10">
+        <v>42</v>
+      </c>
+      <c r="AL10">
+        <v>80</v>
+      </c>
+      <c r="AM10">
+        <v>240</v>
+      </c>
+      <c r="AN10">
+        <v>44</v>
+      </c>
+      <c r="AO10">
+        <v>110</v>
+      </c>
+      <c r="AP10">
+        <v>7.4</v>
+      </c>
+      <c r="AQ10">
+        <v>8.6</v>
+      </c>
+      <c r="AR10">
+        <v>21</v>
+      </c>
+      <c r="AS10">
+        <v>7</v>
+      </c>
+      <c r="AT10">
+        <v>6.2</v>
+      </c>
+      <c r="AU10">
+        <v>6.2</v>
+      </c>
+      <c r="AV10">
+        <v>14</v>
+      </c>
+      <c r="AW10">
+        <v>6.8</v>
+      </c>
+      <c r="AX10">
+        <v>11.5</v>
+      </c>
+      <c r="AY10">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10">
+        <v>20</v>
+      </c>
+      <c r="BA10">
+        <v>7</v>
+      </c>
+      <c r="BB10">
+        <v>6.2</v>
+      </c>
+      <c r="BC10">
+        <v>6.2</v>
+      </c>
+      <c r="BD10">
+        <v>6.8</v>
+      </c>
+      <c r="BE10">
+        <v>7.2</v>
+      </c>
+      <c r="BF10">
+        <v>27</v>
+      </c>
+      <c r="BG10">
+        <v>7</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.66</v>
+      </c>
+      <c r="BJ10">
+        <v>17</v>
+      </c>
+      <c r="BK10">
+        <v>1.51</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.66</v>
+      </c>
+      <c r="BN10">
+        <v>7</v>
+      </c>
+      <c r="BO10">
+        <v>3.35</v>
+      </c>
+      <c r="BP10">
+        <v>30</v>
+      </c>
+      <c r="BQ10">
+        <v>1.57</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.62</v>
+      </c>
+      <c r="BT10">
+        <v>9.6</v>
+      </c>
+      <c r="BU10">
+        <v>4.4</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.61</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.63</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.62</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F11">
+        <v>5.4</v>
+      </c>
+      <c r="G11">
+        <v>6.4</v>
+      </c>
+      <c r="H11">
+        <v>1.78</v>
+      </c>
+      <c r="I11">
+        <v>1.85</v>
+      </c>
+      <c r="J11">
+        <v>3.4</v>
+      </c>
+      <c r="K11">
+        <v>3.6</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.11</v>
+      </c>
+      <c r="N11">
+        <v>2.62</v>
+      </c>
+      <c r="O11">
+        <v>1.48</v>
+      </c>
+      <c r="P11">
+        <v>1.56</v>
+      </c>
+      <c r="Q11">
+        <v>2.44</v>
+      </c>
+      <c r="R11">
+        <v>1.23</v>
+      </c>
+      <c r="S11">
+        <v>5</v>
+      </c>
+      <c r="T11">
+        <v>2.2</v>
+      </c>
+      <c r="U11">
+        <v>1.61</v>
+      </c>
+      <c r="V11">
+        <v>2.16</v>
+      </c>
+      <c r="W11">
+        <v>1.19</v>
+      </c>
+      <c r="X11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y11">
+        <v>6.6</v>
+      </c>
+      <c r="Z11">
+        <v>9.6</v>
+      </c>
+      <c r="AA11">
+        <v>21</v>
+      </c>
+      <c r="AB11">
+        <v>14.5</v>
+      </c>
+      <c r="AC11">
+        <v>8.4</v>
+      </c>
+      <c r="AD11">
+        <v>11.5</v>
+      </c>
+      <c r="AE11">
+        <v>25</v>
+      </c>
+      <c r="AF11">
+        <v>55</v>
+      </c>
+      <c r="AG11">
+        <v>25</v>
+      </c>
+      <c r="AH11">
+        <v>28</v>
+      </c>
+      <c r="AI11">
+        <v>70</v>
+      </c>
+      <c r="AJ11">
+        <v>230</v>
+      </c>
+      <c r="AK11">
+        <v>140</v>
+      </c>
+      <c r="AL11">
+        <v>150</v>
+      </c>
+      <c r="AM11">
+        <v>270</v>
+      </c>
+      <c r="AN11">
+        <v>230</v>
+      </c>
+      <c r="AO11">
+        <v>19.5</v>
+      </c>
+      <c r="AP11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ11">
+        <v>5.7</v>
+      </c>
+      <c r="AR11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS11">
+        <v>17</v>
+      </c>
+      <c r="AT11">
+        <v>12.5</v>
+      </c>
+      <c r="AU11">
+        <v>7.2</v>
+      </c>
+      <c r="AV11">
+        <v>9.4</v>
+      </c>
+      <c r="AW11">
+        <v>21</v>
+      </c>
+      <c r="AX11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY11">
+        <v>20</v>
+      </c>
+      <c r="AZ11">
+        <v>7.6</v>
+      </c>
+      <c r="BA11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB11">
+        <v>10</v>
+      </c>
+      <c r="BC11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE11">
+        <v>10</v>
+      </c>
+      <c r="BF11">
+        <v>10</v>
+      </c>
+      <c r="BG11">
+        <v>14.5</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>1.04</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.04</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>1.04</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.04</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.04</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>1.04</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.04</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.04</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12">
+        <v>2.92</v>
+      </c>
+      <c r="G12">
+        <v>3.1</v>
+      </c>
+      <c r="H12">
+        <v>2.74</v>
+      </c>
+      <c r="I12">
+        <v>2.96</v>
+      </c>
+      <c r="J12">
+        <v>3.1</v>
+      </c>
+      <c r="K12">
+        <v>3.3</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>1.1</v>
+      </c>
+      <c r="O12">
+        <v>1.02</v>
+      </c>
+      <c r="P12">
+        <v>1.59</v>
+      </c>
+      <c r="Q12">
+        <v>2.22</v>
+      </c>
+      <c r="R12">
+        <v>1.22</v>
+      </c>
+      <c r="S12">
+        <v>3.65</v>
+      </c>
+      <c r="T12">
+        <v>1.11</v>
+      </c>
+      <c r="U12">
+        <v>1.11</v>
+      </c>
+      <c r="V12">
+        <v>1.51</v>
+      </c>
+      <c r="W12">
+        <v>1.47</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12">
+        <v>1.01</v>
+      </c>
+      <c r="AR12">
+        <v>1.01</v>
+      </c>
+      <c r="AS12">
+        <v>1.01</v>
+      </c>
+      <c r="AT12">
+        <v>1.01</v>
+      </c>
+      <c r="AU12">
+        <v>1.01</v>
+      </c>
+      <c r="AV12">
+        <v>1.01</v>
+      </c>
+      <c r="AW12">
+        <v>1.01</v>
+      </c>
+      <c r="AX12">
+        <v>1.01</v>
+      </c>
+      <c r="AY12">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12">
+        <v>1.01</v>
+      </c>
+      <c r="BA12">
+        <v>1.01</v>
+      </c>
+      <c r="BB12">
+        <v>1.01</v>
+      </c>
+      <c r="BC12">
+        <v>1.01</v>
+      </c>
+      <c r="BD12">
+        <v>1.01</v>
+      </c>
+      <c r="BE12">
+        <v>1.01</v>
+      </c>
+      <c r="BF12">
+        <v>1.01</v>
+      </c>
+      <c r="BG12">
+        <v>1.01</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.04</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.04</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.04</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.04</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.04</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.04</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.04</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.04</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.04</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.04</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F13">
+        <v>1.62</v>
+      </c>
+      <c r="G13">
+        <v>1.73</v>
+      </c>
+      <c r="H13">
+        <v>6.2</v>
+      </c>
+      <c r="I13">
+        <v>9.4</v>
+      </c>
+      <c r="J13">
+        <v>3.15</v>
+      </c>
+      <c r="K13">
+        <v>4.5</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>2.7</v>
+      </c>
+      <c r="O13">
+        <v>1.02</v>
+      </c>
+      <c r="P13">
+        <v>1.73</v>
+      </c>
+      <c r="Q13">
+        <v>1.41</v>
+      </c>
+      <c r="R13">
+        <v>1.15</v>
+      </c>
+      <c r="S13">
+        <v>3.75</v>
+      </c>
+      <c r="T13">
+        <v>2.06</v>
+      </c>
+      <c r="U13">
+        <v>1.71</v>
+      </c>
+      <c r="V13">
+        <v>1.12</v>
+      </c>
+      <c r="W13">
+        <v>2.36</v>
+      </c>
+      <c r="X13">
+        <v>14.5</v>
+      </c>
+      <c r="Y13">
+        <v>24</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>13</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>26</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>16.5</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.28</v>
+      </c>
+      <c r="AQ13">
+        <v>1.33</v>
+      </c>
+      <c r="AR13">
+        <v>1.41</v>
+      </c>
+      <c r="AS13">
+        <v>1.41</v>
+      </c>
+      <c r="AT13">
+        <v>1.4</v>
+      </c>
+      <c r="AU13">
+        <v>1.4</v>
+      </c>
+      <c r="AV13">
+        <v>19</v>
+      </c>
+      <c r="AW13">
+        <v>1.41</v>
+      </c>
+      <c r="AX13">
+        <v>1.41</v>
+      </c>
+      <c r="AY13">
+        <v>1.27</v>
+      </c>
+      <c r="AZ13">
+        <v>1.4</v>
+      </c>
+      <c r="BA13">
+        <v>1.41</v>
+      </c>
+      <c r="BB13">
+        <v>1.41</v>
+      </c>
+      <c r="BC13">
+        <v>1.33</v>
+      </c>
+      <c r="BD13">
+        <v>1.41</v>
+      </c>
+      <c r="BE13">
+        <v>1.41</v>
+      </c>
+      <c r="BF13">
+        <v>1.29</v>
+      </c>
+      <c r="BG13">
+        <v>1.41</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.04</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.04</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.04</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.04</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.04</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.04</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.04</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14">
+        <v>1.15</v>
+      </c>
+      <c r="G14">
+        <v>990</v>
+      </c>
+      <c r="H14">
+        <v>1.04</v>
+      </c>
+      <c r="I14">
+        <v>990</v>
+      </c>
+      <c r="J14">
+        <v>1.09</v>
+      </c>
+      <c r="K14">
+        <v>950</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>1.26</v>
+      </c>
+      <c r="O14">
+        <v>1.18</v>
+      </c>
+      <c r="P14">
+        <v>1.25</v>
+      </c>
+      <c r="Q14">
+        <v>1.18</v>
+      </c>
+      <c r="R14">
+        <v>1.08</v>
+      </c>
+      <c r="S14">
+        <v>1.18</v>
+      </c>
+      <c r="T14">
+        <v>1.11</v>
+      </c>
+      <c r="U14">
+        <v>1.11</v>
+      </c>
+      <c r="V14">
+        <v>1.06</v>
+      </c>
+      <c r="W14">
+        <v>1.33</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.04</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.04</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.04</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.04</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.04</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.04</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.04</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.04</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.04</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.04</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15">
+        <v>1.54</v>
+      </c>
+      <c r="G15">
+        <v>1.98</v>
+      </c>
+      <c r="H15">
+        <v>4.1</v>
+      </c>
+      <c r="I15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J15">
+        <v>3.8</v>
+      </c>
+      <c r="K15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L15">
+        <v>1.27</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>2.68</v>
+      </c>
+      <c r="O15">
+        <v>1.25</v>
+      </c>
+      <c r="P15">
+        <v>1.83</v>
+      </c>
+      <c r="Q15">
+        <v>1.64</v>
+      </c>
+      <c r="R15">
+        <v>1.31</v>
+      </c>
+      <c r="S15">
+        <v>2.58</v>
+      </c>
+      <c r="T15">
+        <v>1.11</v>
+      </c>
+      <c r="U15">
+        <v>1.11</v>
+      </c>
+      <c r="V15">
+        <v>1.14</v>
+      </c>
+      <c r="W15">
+        <v>2.02</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15">
+        <v>1.01</v>
+      </c>
+      <c r="AR15">
+        <v>1.01</v>
+      </c>
+      <c r="AS15">
+        <v>1.01</v>
+      </c>
+      <c r="AT15">
+        <v>1.01</v>
+      </c>
+      <c r="AU15">
+        <v>1.01</v>
+      </c>
+      <c r="AV15">
+        <v>1.01</v>
+      </c>
+      <c r="AW15">
+        <v>1.01</v>
+      </c>
+      <c r="AX15">
+        <v>1.01</v>
+      </c>
+      <c r="AY15">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15">
+        <v>1.01</v>
+      </c>
+      <c r="BA15">
+        <v>1.01</v>
+      </c>
+      <c r="BB15">
+        <v>1.01</v>
+      </c>
+      <c r="BC15">
+        <v>1.01</v>
+      </c>
+      <c r="BD15">
+        <v>1.01</v>
+      </c>
+      <c r="BE15">
+        <v>1.01</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.04</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.04</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.04</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.04</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.04</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.04</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.04</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.04</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.04</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16">
+        <v>2.46</v>
+      </c>
+      <c r="G16">
+        <v>2.54</v>
+      </c>
+      <c r="H16">
+        <v>2.66</v>
+      </c>
+      <c r="I16">
+        <v>2.76</v>
+      </c>
+      <c r="J16">
+        <v>4.1</v>
+      </c>
+      <c r="K16">
+        <v>4.4</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.02</v>
+      </c>
+      <c r="N16">
+        <v>6.8</v>
+      </c>
+      <c r="O16">
+        <v>1.15</v>
+      </c>
+      <c r="P16">
+        <v>3.05</v>
+      </c>
+      <c r="Q16">
+        <v>1.44</v>
+      </c>
+      <c r="R16">
+        <v>1.81</v>
+      </c>
+      <c r="S16">
+        <v>2.1</v>
+      </c>
+      <c r="T16">
+        <v>1.44</v>
+      </c>
+      <c r="U16">
+        <v>3.05</v>
+      </c>
+      <c r="V16">
+        <v>1.57</v>
+      </c>
+      <c r="W16">
+        <v>1.64</v>
+      </c>
+      <c r="X16">
+        <v>36</v>
+      </c>
+      <c r="Y16">
+        <v>22</v>
+      </c>
+      <c r="Z16">
+        <v>26</v>
+      </c>
+      <c r="AA16">
+        <v>44</v>
+      </c>
+      <c r="AB16">
+        <v>21</v>
+      </c>
+      <c r="AC16">
+        <v>11.5</v>
+      </c>
+      <c r="AD16">
+        <v>15.5</v>
+      </c>
+      <c r="AE16">
+        <v>26</v>
+      </c>
+      <c r="AF16">
+        <v>24</v>
+      </c>
+      <c r="AG16">
+        <v>13.5</v>
+      </c>
+      <c r="AH16">
+        <v>14.5</v>
+      </c>
+      <c r="AI16">
+        <v>28</v>
+      </c>
+      <c r="AJ16">
+        <v>38</v>
+      </c>
+      <c r="AK16">
+        <v>23</v>
+      </c>
+      <c r="AL16">
+        <v>27</v>
+      </c>
+      <c r="AM16">
+        <v>50</v>
+      </c>
+      <c r="AN16">
+        <v>11</v>
+      </c>
+      <c r="AO16">
+        <v>13</v>
+      </c>
+      <c r="AP16">
+        <v>22</v>
+      </c>
+      <c r="AQ16">
+        <v>17.5</v>
+      </c>
+      <c r="AR16">
+        <v>21</v>
+      </c>
+      <c r="AS16">
+        <v>25</v>
+      </c>
+      <c r="AT16">
+        <v>17.5</v>
+      </c>
+      <c r="AU16">
+        <v>9.6</v>
+      </c>
+      <c r="AV16">
+        <v>11.5</v>
+      </c>
+      <c r="AW16">
+        <v>20</v>
+      </c>
+      <c r="AX16">
+        <v>19.5</v>
+      </c>
+      <c r="AY16">
+        <v>11</v>
+      </c>
+      <c r="AZ16">
+        <v>12.5</v>
+      </c>
+      <c r="BA16">
+        <v>17.5</v>
+      </c>
+      <c r="BB16">
+        <v>23</v>
+      </c>
+      <c r="BC16">
+        <v>19.5</v>
+      </c>
+      <c r="BD16">
+        <v>21</v>
+      </c>
+      <c r="BE16">
+        <v>24</v>
+      </c>
+      <c r="BF16">
+        <v>9.6</v>
+      </c>
+      <c r="BG16">
+        <v>11</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>2.06</v>
+      </c>
+      <c r="BJ16">
+        <v>11.5</v>
+      </c>
+      <c r="BK16">
+        <v>5.1</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>2.02</v>
+      </c>
+      <c r="BN16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO16">
+        <v>4.1</v>
+      </c>
+      <c r="BP16">
+        <v>23</v>
+      </c>
+      <c r="BQ16">
+        <v>1.9</v>
+      </c>
+      <c r="BR16">
+        <v>30</v>
+      </c>
+      <c r="BS16">
+        <v>1.94</v>
+      </c>
+      <c r="BT16">
+        <v>9.6</v>
+      </c>
+      <c r="BU16">
+        <v>4.3</v>
+      </c>
+      <c r="BV16">
+        <v>26</v>
+      </c>
+      <c r="BW16">
+        <v>1.92</v>
+      </c>
+      <c r="BX16">
+        <v>32</v>
+      </c>
+      <c r="BY16">
+        <v>1.94</v>
+      </c>
+      <c r="BZ16">
+        <v>18.5</v>
+      </c>
+      <c r="CA16">
+        <v>1.86</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17">
+        <v>1.38</v>
+      </c>
+      <c r="G17">
+        <v>1.42</v>
+      </c>
+      <c r="H17">
+        <v>10.5</v>
+      </c>
+      <c r="I17">
+        <v>13.5</v>
+      </c>
+      <c r="J17">
+        <v>4.7</v>
+      </c>
+      <c r="K17">
+        <v>5.3</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>3.4</v>
+      </c>
+      <c r="O17">
+        <v>1.31</v>
+      </c>
+      <c r="P17">
+        <v>1.86</v>
+      </c>
+      <c r="Q17">
+        <v>1.97</v>
+      </c>
+      <c r="R17">
+        <v>1.28</v>
+      </c>
+      <c r="S17">
+        <v>3.2</v>
+      </c>
+      <c r="T17">
+        <v>2.08</v>
+      </c>
+      <c r="U17">
+        <v>1.56</v>
+      </c>
+      <c r="V17">
+        <v>1.08</v>
+      </c>
+      <c r="W17">
+        <v>3.3</v>
+      </c>
+      <c r="X17">
+        <v>20</v>
+      </c>
+      <c r="Y17">
+        <v>950</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>9.6</v>
+      </c>
+      <c r="AC17">
+        <v>12</v>
+      </c>
+      <c r="AD17">
+        <v>950</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>10</v>
+      </c>
+      <c r="AG17">
+        <v>15.5</v>
+      </c>
+      <c r="AH17">
+        <v>950</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>16</v>
+      </c>
+      <c r="AK17">
+        <v>25</v>
+      </c>
+      <c r="AL17">
+        <v>70</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>10.5</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>2.66</v>
+      </c>
+      <c r="AQ17">
+        <v>2.86</v>
+      </c>
+      <c r="AR17">
+        <v>3.05</v>
+      </c>
+      <c r="AS17">
+        <v>3.05</v>
+      </c>
+      <c r="AT17">
+        <v>2.32</v>
+      </c>
+      <c r="AU17">
+        <v>2.44</v>
+      </c>
+      <c r="AV17">
+        <v>2.94</v>
+      </c>
+      <c r="AW17">
+        <v>3.05</v>
+      </c>
+      <c r="AX17">
+        <v>2.36</v>
+      </c>
+      <c r="AY17">
+        <v>2.56</v>
+      </c>
+      <c r="AZ17">
+        <v>2.9</v>
+      </c>
+      <c r="BA17">
+        <v>3.05</v>
+      </c>
+      <c r="BB17">
+        <v>2.58</v>
+      </c>
+      <c r="BC17">
+        <v>2.74</v>
+      </c>
+      <c r="BD17">
+        <v>2.96</v>
+      </c>
+      <c r="BE17">
+        <v>3.05</v>
+      </c>
+      <c r="BF17">
+        <v>4.9</v>
+      </c>
+      <c r="BG17">
+        <v>3.05</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.04</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.04</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.04</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.04</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.04</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.04</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.04</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.04</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.04</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.04</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18">
+        <v>2.22</v>
+      </c>
+      <c r="G18">
+        <v>2.38</v>
+      </c>
+      <c r="H18">
+        <v>3.9</v>
+      </c>
+      <c r="I18">
+        <v>4.4</v>
+      </c>
+      <c r="J18">
+        <v>3.05</v>
+      </c>
+      <c r="K18">
+        <v>3.25</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>2.46</v>
+      </c>
+      <c r="O18">
+        <v>1.54</v>
+      </c>
+      <c r="P18">
+        <v>1.48</v>
+      </c>
+      <c r="Q18">
+        <v>2.74</v>
+      </c>
+      <c r="R18">
+        <v>1.13</v>
+      </c>
+      <c r="S18">
+        <v>5.7</v>
+      </c>
+      <c r="T18">
+        <v>2.14</v>
+      </c>
+      <c r="U18">
+        <v>1.68</v>
+      </c>
+      <c r="V18">
+        <v>1.3</v>
+      </c>
+      <c r="W18">
+        <v>1.72</v>
+      </c>
+      <c r="X18">
+        <v>8.6</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>7</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.17</v>
+      </c>
+      <c r="AQ18">
+        <v>1.35</v>
+      </c>
+      <c r="AR18">
+        <v>1.35</v>
+      </c>
+      <c r="AS18">
+        <v>1.35</v>
+      </c>
+      <c r="AT18">
+        <v>1.13</v>
+      </c>
+      <c r="AU18">
+        <v>1.35</v>
+      </c>
+      <c r="AV18">
+        <v>1.35</v>
+      </c>
+      <c r="AW18">
+        <v>1.35</v>
+      </c>
+      <c r="AX18">
+        <v>1.35</v>
+      </c>
+      <c r="AY18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ18">
+        <v>1.35</v>
+      </c>
+      <c r="BA18">
+        <v>1.35</v>
+      </c>
+      <c r="BB18">
+        <v>1.35</v>
+      </c>
+      <c r="BC18">
+        <v>1.35</v>
+      </c>
+      <c r="BD18">
+        <v>1.35</v>
+      </c>
+      <c r="BE18">
+        <v>1.35</v>
+      </c>
+      <c r="BF18">
+        <v>1.35</v>
+      </c>
+      <c r="BG18">
+        <v>1.35</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>2.12</v>
+      </c>
+      <c r="BJ18">
+        <v>17</v>
+      </c>
+      <c r="BK18">
+        <v>1.51</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.65</v>
+      </c>
+      <c r="BN18">
+        <v>6.8</v>
+      </c>
+      <c r="BO18">
+        <v>3.3</v>
+      </c>
+      <c r="BP18">
+        <v>30</v>
+      </c>
+      <c r="BQ18">
+        <v>1.57</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.62</v>
+      </c>
+      <c r="BT18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU18">
+        <v>4.5</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.61</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.63</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.62</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19">
+        <v>2.28</v>
+      </c>
+      <c r="G19">
+        <v>2.4</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <v>3.25</v>
+      </c>
+      <c r="J19">
+        <v>3.8</v>
+      </c>
+      <c r="K19">
+        <v>4.2</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.05</v>
+      </c>
+      <c r="N19">
+        <v>4.6</v>
+      </c>
+      <c r="O19">
+        <v>1.23</v>
+      </c>
+      <c r="P19">
+        <v>2.3</v>
+      </c>
+      <c r="Q19">
+        <v>1.7</v>
+      </c>
+      <c r="R19">
+        <v>1.51</v>
+      </c>
+      <c r="S19">
+        <v>2.74</v>
+      </c>
+      <c r="T19">
+        <v>1.62</v>
+      </c>
+      <c r="U19">
+        <v>2.42</v>
+      </c>
+      <c r="V19">
+        <v>1.45</v>
+      </c>
+      <c r="W19">
+        <v>1.72</v>
+      </c>
+      <c r="X19">
+        <v>24</v>
+      </c>
+      <c r="Y19">
+        <v>16</v>
+      </c>
+      <c r="Z19">
+        <v>27</v>
+      </c>
+      <c r="AA19">
+        <v>55</v>
+      </c>
+      <c r="AB19">
+        <v>13</v>
+      </c>
+      <c r="AC19">
+        <v>10</v>
+      </c>
+      <c r="AD19">
+        <v>16</v>
+      </c>
+      <c r="AE19">
+        <v>36</v>
+      </c>
+      <c r="AF19">
+        <v>17</v>
+      </c>
+      <c r="AG19">
+        <v>13</v>
+      </c>
+      <c r="AH19">
+        <v>16</v>
+      </c>
+      <c r="AI19">
+        <v>44</v>
+      </c>
+      <c r="AJ19">
+        <v>36</v>
+      </c>
+      <c r="AK19">
+        <v>26</v>
+      </c>
+      <c r="AL19">
+        <v>36</v>
+      </c>
+      <c r="AM19">
+        <v>80</v>
+      </c>
+      <c r="AN19">
+        <v>16.5</v>
+      </c>
+      <c r="AO19">
+        <v>24</v>
+      </c>
+      <c r="AP19">
+        <v>18</v>
+      </c>
+      <c r="AQ19">
+        <v>13.5</v>
+      </c>
+      <c r="AR19">
+        <v>21</v>
+      </c>
+      <c r="AS19">
+        <v>28</v>
+      </c>
+      <c r="AT19">
+        <v>11.5</v>
+      </c>
+      <c r="AU19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV19">
+        <v>12</v>
+      </c>
+      <c r="AW19">
+        <v>19.5</v>
+      </c>
+      <c r="AX19">
+        <v>15</v>
+      </c>
+      <c r="AY19">
+        <v>10</v>
+      </c>
+      <c r="AZ19">
+        <v>14</v>
+      </c>
+      <c r="BA19">
+        <v>23</v>
+      </c>
+      <c r="BB19">
+        <v>20</v>
+      </c>
+      <c r="BC19">
+        <v>20</v>
+      </c>
+      <c r="BD19">
+        <v>20</v>
+      </c>
+      <c r="BE19">
+        <v>32</v>
+      </c>
+      <c r="BF19">
+        <v>12.5</v>
+      </c>
+      <c r="BG19">
+        <v>20</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.9</v>
+      </c>
+      <c r="BJ19">
+        <v>12.5</v>
+      </c>
+      <c r="BK19">
+        <v>5.4</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.91</v>
+      </c>
+      <c r="BN19">
+        <v>7.8</v>
+      </c>
+      <c r="BO19">
+        <v>3.6</v>
+      </c>
+      <c r="BP19">
+        <v>23</v>
+      </c>
+      <c r="BQ19">
+        <v>1.76</v>
+      </c>
+      <c r="BR19">
+        <v>38</v>
+      </c>
+      <c r="BS19">
+        <v>1.82</v>
+      </c>
+      <c r="BT19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU19">
+        <v>4.3</v>
+      </c>
+      <c r="BV19">
+        <v>32</v>
+      </c>
+      <c r="BW19">
+        <v>1.8</v>
+      </c>
+      <c r="BX19">
+        <v>46</v>
+      </c>
+      <c r="BY19">
+        <v>1.83</v>
+      </c>
+      <c r="BZ19">
+        <v>28</v>
+      </c>
+      <c r="CA19">
+        <v>1.79</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20">
+        <v>2.96</v>
+      </c>
+      <c r="G20">
+        <v>3.05</v>
+      </c>
+      <c r="H20">
+        <v>2.34</v>
+      </c>
+      <c r="I20">
+        <v>2.42</v>
+      </c>
+      <c r="J20">
+        <v>4</v>
+      </c>
+      <c r="K20">
+        <v>4.3</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.02</v>
+      </c>
+      <c r="N20">
+        <v>5.6</v>
+      </c>
+      <c r="O20">
+        <v>1.19</v>
+      </c>
+      <c r="P20">
+        <v>2.58</v>
+      </c>
+      <c r="Q20">
+        <v>1.58</v>
+      </c>
+      <c r="R20">
+        <v>1.64</v>
+      </c>
+      <c r="S20">
+        <v>2.42</v>
+      </c>
+      <c r="T20">
+        <v>1.53</v>
+      </c>
+      <c r="U20">
+        <v>2.66</v>
+      </c>
+      <c r="V20">
+        <v>1.71</v>
+      </c>
+      <c r="W20">
+        <v>1.48</v>
+      </c>
+      <c r="X20">
+        <v>30</v>
+      </c>
+      <c r="Y20">
+        <v>18</v>
+      </c>
+      <c r="Z20">
+        <v>22</v>
+      </c>
+      <c r="AA20">
+        <v>34</v>
+      </c>
+      <c r="AB20">
+        <v>23</v>
+      </c>
+      <c r="AC20">
+        <v>10.5</v>
+      </c>
+      <c r="AD20">
+        <v>12</v>
+      </c>
+      <c r="AE20">
+        <v>26</v>
+      </c>
+      <c r="AF20">
+        <v>29</v>
+      </c>
+      <c r="AG20">
+        <v>14</v>
+      </c>
+      <c r="AH20">
+        <v>15</v>
+      </c>
+      <c r="AI20">
+        <v>30</v>
+      </c>
+      <c r="AJ20">
+        <v>60</v>
+      </c>
+      <c r="AK20">
+        <v>29</v>
+      </c>
+      <c r="AL20">
+        <v>38</v>
+      </c>
+      <c r="AM20">
+        <v>260</v>
+      </c>
+      <c r="AN20">
+        <v>18.5</v>
+      </c>
+      <c r="AO20">
+        <v>14</v>
+      </c>
+      <c r="AP20">
+        <v>18</v>
+      </c>
+      <c r="AQ20">
+        <v>13.5</v>
+      </c>
+      <c r="AR20">
+        <v>14</v>
+      </c>
+      <c r="AS20">
+        <v>21</v>
+      </c>
+      <c r="AT20">
+        <v>15.5</v>
+      </c>
+      <c r="AU20">
+        <v>8.6</v>
+      </c>
+      <c r="AV20">
+        <v>10.5</v>
+      </c>
+      <c r="AW20">
+        <v>18.5</v>
+      </c>
+      <c r="AX20">
+        <v>20</v>
+      </c>
+      <c r="AY20">
+        <v>11.5</v>
+      </c>
+      <c r="AZ20">
+        <v>13</v>
+      </c>
+      <c r="BA20">
+        <v>18.5</v>
+      </c>
+      <c r="BB20">
+        <v>26</v>
+      </c>
+      <c r="BC20">
+        <v>18</v>
+      </c>
+      <c r="BD20">
+        <v>20</v>
+      </c>
+      <c r="BE20">
+        <v>28</v>
+      </c>
+      <c r="BF20">
+        <v>15</v>
+      </c>
+      <c r="BG20">
+        <v>11</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.04</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.04</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.04</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.04</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.04</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.04</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.04</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.04</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.04</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.04</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21">
+        <v>2.22</v>
+      </c>
+      <c r="G21">
+        <v>2.32</v>
+      </c>
+      <c r="H21">
+        <v>3.25</v>
+      </c>
+      <c r="I21">
+        <v>3.5</v>
+      </c>
+      <c r="J21">
+        <v>3.7</v>
+      </c>
+      <c r="K21">
+        <v>3.85</v>
+      </c>
+      <c r="L21">
+        <v>1.3</v>
+      </c>
+      <c r="M21">
+        <v>1.06</v>
+      </c>
+      <c r="N21">
+        <v>4.1</v>
+      </c>
+      <c r="O21">
+        <v>1.28</v>
+      </c>
+      <c r="P21">
+        <v>2.08</v>
+      </c>
+      <c r="Q21">
+        <v>1.83</v>
+      </c>
+      <c r="R21">
+        <v>1.43</v>
+      </c>
+      <c r="S21">
+        <v>3.1</v>
+      </c>
+      <c r="T21">
+        <v>1.69</v>
+      </c>
+      <c r="U21">
+        <v>2.32</v>
+      </c>
+      <c r="V21">
+        <v>1.4</v>
+      </c>
+      <c r="W21">
+        <v>1.76</v>
+      </c>
+      <c r="X21">
+        <v>20</v>
+      </c>
+      <c r="Y21">
+        <v>15</v>
+      </c>
+      <c r="Z21">
+        <v>30</v>
+      </c>
+      <c r="AA21">
+        <v>610</v>
+      </c>
+      <c r="AB21">
+        <v>12</v>
+      </c>
+      <c r="AC21">
+        <v>8.6</v>
+      </c>
+      <c r="AD21">
+        <v>15</v>
+      </c>
+      <c r="AE21">
+        <v>44</v>
+      </c>
+      <c r="AF21">
+        <v>17.5</v>
+      </c>
+      <c r="AG21">
+        <v>12</v>
+      </c>
+      <c r="AH21">
+        <v>16.5</v>
+      </c>
+      <c r="AI21">
+        <v>55</v>
+      </c>
+      <c r="AJ21">
+        <v>38</v>
+      </c>
+      <c r="AK21">
+        <v>27</v>
+      </c>
+      <c r="AL21">
+        <v>40</v>
+      </c>
+      <c r="AM21">
+        <v>95</v>
+      </c>
+      <c r="AN21">
+        <v>19.5</v>
+      </c>
+      <c r="AO21">
+        <v>55</v>
+      </c>
+      <c r="AP21">
+        <v>13.5</v>
+      </c>
+      <c r="AQ21">
+        <v>12.5</v>
+      </c>
+      <c r="AR21">
+        <v>21</v>
+      </c>
+      <c r="AS21">
+        <v>29</v>
+      </c>
+      <c r="AT21">
+        <v>10</v>
+      </c>
+      <c r="AU21">
+        <v>7.8</v>
+      </c>
+      <c r="AV21">
+        <v>12.5</v>
+      </c>
+      <c r="AW21">
+        <v>22</v>
+      </c>
+      <c r="AX21">
+        <v>13.5</v>
+      </c>
+      <c r="AY21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ21">
+        <v>13</v>
+      </c>
+      <c r="BA21">
+        <v>25</v>
+      </c>
+      <c r="BB21">
+        <v>21</v>
+      </c>
+      <c r="BC21">
+        <v>15.5</v>
+      </c>
+      <c r="BD21">
+        <v>21</v>
+      </c>
+      <c r="BE21">
+        <v>34</v>
+      </c>
+      <c r="BF21">
+        <v>14.5</v>
+      </c>
+      <c r="BG21">
+        <v>21</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.04</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>1.04</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.04</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>1.04</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>1.04</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.04</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>1.04</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>1.04</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.04</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>1.04</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E22" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22">
+        <v>2.92</v>
+      </c>
+      <c r="G22">
+        <v>3.05</v>
+      </c>
+      <c r="H22">
+        <v>2.28</v>
+      </c>
+      <c r="I22">
+        <v>2.36</v>
+      </c>
+      <c r="J22">
+        <v>4.1</v>
+      </c>
+      <c r="K22">
+        <v>4.4</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.02</v>
+      </c>
+      <c r="N22">
+        <v>7.6</v>
+      </c>
+      <c r="O22">
+        <v>1.13</v>
+      </c>
+      <c r="P22">
+        <v>3.15</v>
+      </c>
+      <c r="Q22">
+        <v>1.42</v>
+      </c>
+      <c r="R22">
+        <v>1.89</v>
+      </c>
+      <c r="S22">
+        <v>2.02</v>
+      </c>
+      <c r="T22">
+        <v>1.42</v>
+      </c>
+      <c r="U22">
+        <v>3.2</v>
+      </c>
+      <c r="V22">
+        <v>1.73</v>
+      </c>
+      <c r="W22">
+        <v>1.49</v>
+      </c>
+      <c r="X22">
+        <v>36</v>
+      </c>
+      <c r="Y22">
+        <v>21</v>
+      </c>
+      <c r="Z22">
+        <v>22</v>
+      </c>
+      <c r="AA22">
+        <v>36</v>
+      </c>
+      <c r="AB22">
+        <v>25</v>
+      </c>
+      <c r="AC22">
+        <v>11.5</v>
+      </c>
+      <c r="AD22">
+        <v>12.5</v>
+      </c>
+      <c r="AE22">
+        <v>20</v>
+      </c>
+      <c r="AF22">
+        <v>44</v>
+      </c>
+      <c r="AG22">
+        <v>14.5</v>
+      </c>
+      <c r="AH22">
+        <v>13.5</v>
+      </c>
+      <c r="AI22">
+        <v>32</v>
+      </c>
+      <c r="AJ22">
+        <v>60</v>
+      </c>
+      <c r="AK22">
+        <v>27</v>
+      </c>
+      <c r="AL22">
+        <v>42</v>
+      </c>
+      <c r="AM22">
+        <v>46</v>
+      </c>
+      <c r="AN22">
+        <v>13.5</v>
+      </c>
+      <c r="AO22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AP22">
+        <v>30</v>
+      </c>
+      <c r="AQ22">
+        <v>18.5</v>
+      </c>
+      <c r="AR22">
+        <v>19.5</v>
+      </c>
+      <c r="AS22">
+        <v>30</v>
+      </c>
+      <c r="AT22">
+        <v>21</v>
+      </c>
+      <c r="AU22">
+        <v>10</v>
+      </c>
+      <c r="AV22">
+        <v>11</v>
+      </c>
+      <c r="AW22">
+        <v>18</v>
+      </c>
+      <c r="AX22">
+        <v>25</v>
+      </c>
+      <c r="AY22">
+        <v>11.5</v>
+      </c>
+      <c r="AZ22">
+        <v>12.5</v>
+      </c>
+      <c r="BA22">
+        <v>21</v>
+      </c>
+      <c r="BB22">
+        <v>42</v>
+      </c>
+      <c r="BC22">
+        <v>23</v>
+      </c>
+      <c r="BD22">
+        <v>24</v>
+      </c>
+      <c r="BE22">
+        <v>36</v>
+      </c>
+      <c r="BF22">
+        <v>12</v>
+      </c>
+      <c r="BG22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.04</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>1.04</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.04</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>1.04</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>1.04</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.04</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>1.04</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.04</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.04</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.04</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" t="s">
+        <v>143</v>
+      </c>
+      <c r="F23">
+        <v>1.67</v>
+      </c>
+      <c r="G23">
+        <v>1.69</v>
+      </c>
+      <c r="H23">
+        <v>5.1</v>
+      </c>
+      <c r="I23">
+        <v>5.5</v>
+      </c>
+      <c r="J23">
+        <v>4.5</v>
+      </c>
+      <c r="K23">
+        <v>4.7</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.02</v>
+      </c>
+      <c r="N23">
+        <v>5.6</v>
+      </c>
+      <c r="O23">
+        <v>1.19</v>
+      </c>
+      <c r="P23">
+        <v>2.52</v>
+      </c>
+      <c r="Q23">
+        <v>1.59</v>
+      </c>
+      <c r="R23">
+        <v>1.62</v>
+      </c>
+      <c r="S23">
+        <v>2.44</v>
+      </c>
+      <c r="T23">
+        <v>1.66</v>
+      </c>
+      <c r="U23">
+        <v>2.34</v>
+      </c>
+      <c r="V23">
+        <v>1.22</v>
+      </c>
+      <c r="W23">
+        <v>2.44</v>
+      </c>
+      <c r="X23">
+        <v>25</v>
+      </c>
+      <c r="Y23">
+        <v>26</v>
+      </c>
+      <c r="Z23">
+        <v>48</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>12.5</v>
+      </c>
+      <c r="AC23">
+        <v>10.5</v>
+      </c>
+      <c r="AD23">
+        <v>22</v>
+      </c>
+      <c r="AE23">
+        <v>65</v>
+      </c>
+      <c r="AF23">
+        <v>12.5</v>
+      </c>
+      <c r="AG23">
+        <v>10.5</v>
+      </c>
+      <c r="AH23">
+        <v>19</v>
+      </c>
+      <c r="AI23">
+        <v>60</v>
+      </c>
+      <c r="AJ23">
+        <v>18</v>
+      </c>
+      <c r="AK23">
+        <v>15.5</v>
+      </c>
+      <c r="AL23">
+        <v>29</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>7</v>
+      </c>
+      <c r="AO23">
+        <v>55</v>
+      </c>
+      <c r="AP23">
+        <v>21</v>
+      </c>
+      <c r="AQ23">
+        <v>20</v>
+      </c>
+      <c r="AR23">
+        <v>26</v>
+      </c>
+      <c r="AS23">
+        <v>42</v>
+      </c>
+      <c r="AT23">
+        <v>11</v>
+      </c>
+      <c r="AU23">
+        <v>9.6</v>
+      </c>
+      <c r="AV23">
+        <v>18</v>
+      </c>
+      <c r="AW23">
+        <v>29</v>
+      </c>
+      <c r="AX23">
+        <v>10.5</v>
+      </c>
+      <c r="AY23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ23">
+        <v>15.5</v>
+      </c>
+      <c r="BA23">
+        <v>28</v>
+      </c>
+      <c r="BB23">
+        <v>15</v>
+      </c>
+      <c r="BC23">
+        <v>13.5</v>
+      </c>
+      <c r="BD23">
+        <v>18</v>
+      </c>
+      <c r="BE23">
+        <v>34</v>
+      </c>
+      <c r="BF23">
+        <v>6.4</v>
+      </c>
+      <c r="BG23">
+        <v>27</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.04</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.04</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.04</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.04</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.04</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.04</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.04</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.04</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.04</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.04</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24">
+        <v>2.02</v>
+      </c>
+      <c r="G24">
+        <v>2.08</v>
+      </c>
+      <c r="H24">
+        <v>3.45</v>
+      </c>
+      <c r="I24">
+        <v>3.65</v>
+      </c>
+      <c r="J24">
+        <v>4.1</v>
+      </c>
+      <c r="K24">
+        <v>4.4</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.03</v>
+      </c>
+      <c r="N24">
+        <v>6.4</v>
+      </c>
+      <c r="O24">
+        <v>1.16</v>
+      </c>
+      <c r="P24">
+        <v>2.82</v>
+      </c>
+      <c r="Q24">
+        <v>1.51</v>
+      </c>
+      <c r="R24">
+        <v>1.75</v>
+      </c>
+      <c r="S24">
+        <v>2.22</v>
+      </c>
+      <c r="T24">
+        <v>1.49</v>
+      </c>
+      <c r="U24">
+        <v>2.82</v>
+      </c>
+      <c r="V24">
+        <v>1.37</v>
+      </c>
+      <c r="W24">
+        <v>1.92</v>
+      </c>
+      <c r="X24">
+        <v>29</v>
+      </c>
+      <c r="Y24">
+        <v>23</v>
+      </c>
+      <c r="Z24">
+        <v>32</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>16</v>
+      </c>
+      <c r="AC24">
+        <v>10.5</v>
+      </c>
+      <c r="AD24">
+        <v>16</v>
+      </c>
+      <c r="AE24">
+        <v>34</v>
+      </c>
+      <c r="AF24">
+        <v>17.5</v>
+      </c>
+      <c r="AG24">
+        <v>11.5</v>
+      </c>
+      <c r="AH24">
+        <v>14.5</v>
+      </c>
+      <c r="AI24">
+        <v>34</v>
+      </c>
+      <c r="AJ24">
+        <v>28</v>
+      </c>
+      <c r="AK24">
+        <v>18</v>
+      </c>
+      <c r="AL24">
+        <v>24</v>
+      </c>
+      <c r="AM24">
+        <v>180</v>
+      </c>
+      <c r="AN24">
+        <v>8.6</v>
+      </c>
+      <c r="AO24">
+        <v>21</v>
+      </c>
+      <c r="AP24">
+        <v>20</v>
+      </c>
+      <c r="AQ24">
+        <v>19.5</v>
+      </c>
+      <c r="AR24">
+        <v>22</v>
+      </c>
+      <c r="AS24">
+        <v>42</v>
+      </c>
+      <c r="AT24">
+        <v>14</v>
+      </c>
+      <c r="AU24">
+        <v>9.4</v>
+      </c>
+      <c r="AV24">
+        <v>13.5</v>
+      </c>
+      <c r="AW24">
+        <v>21</v>
+      </c>
+      <c r="AX24">
+        <v>15</v>
+      </c>
+      <c r="AY24">
+        <v>10</v>
+      </c>
+      <c r="AZ24">
+        <v>12.5</v>
+      </c>
+      <c r="BA24">
+        <v>21</v>
+      </c>
+      <c r="BB24">
+        <v>18</v>
+      </c>
+      <c r="BC24">
+        <v>16</v>
+      </c>
+      <c r="BD24">
+        <v>21</v>
+      </c>
+      <c r="BE24">
+        <v>34</v>
+      </c>
+      <c r="BF24">
+        <v>7.8</v>
+      </c>
+      <c r="BG24">
+        <v>18</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>3.25</v>
+      </c>
+      <c r="BJ24">
+        <v>12.5</v>
+      </c>
+      <c r="BK24">
+        <v>5.3</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>2</v>
+      </c>
+      <c r="BN24">
+        <v>7.8</v>
+      </c>
+      <c r="BO24">
+        <v>3.6</v>
+      </c>
+      <c r="BP24">
+        <v>18.5</v>
+      </c>
+      <c r="BQ24">
+        <v>1.84</v>
+      </c>
+      <c r="BR24">
+        <v>29</v>
+      </c>
+      <c r="BS24">
+        <v>1.9</v>
+      </c>
+      <c r="BT24">
+        <v>10.5</v>
+      </c>
+      <c r="BU24">
+        <v>4.8</v>
+      </c>
+      <c r="BV24">
+        <v>34</v>
+      </c>
+      <c r="BW24">
+        <v>1.92</v>
+      </c>
+      <c r="BX24">
+        <v>40</v>
+      </c>
+      <c r="BY24">
+        <v>1.94</v>
+      </c>
+      <c r="BZ24">
+        <v>19</v>
+      </c>
+      <c r="CA24">
+        <v>1.84</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -451,7 +451,7 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-18 00:31:35</t>
+    <t>2026-08-18 02:39:46</t>
   </si>
 </sst>
 </file>
@@ -1045,10 +1045,10 @@
         <v>122</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H2">
         <v>3.9</v>
@@ -1057,52 +1057,52 @@
         <v>4</v>
       </c>
       <c r="J2">
+        <v>3.15</v>
+      </c>
+      <c r="K2">
         <v>3.2</v>
       </c>
-      <c r="K2">
-        <v>3.25</v>
-      </c>
       <c r="L2">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="P2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="U2">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="V2">
         <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z2">
         <v>32</v>
@@ -1111,10 +1111,10 @@
         <v>95</v>
       </c>
       <c r="AB2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
         <v>19</v>
@@ -1123,13 +1123,13 @@
         <v>65</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG2">
         <v>13</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2">
         <v>80</v>
@@ -1147,124 +1147,124 @@
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO2">
         <v>75</v>
       </c>
       <c r="AP2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS2">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV2">
         <v>14</v>
       </c>
       <c r="AW2">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
         <v>16.5</v>
       </c>
       <c r="BA2">
+        <v>5.2</v>
+      </c>
+      <c r="BB2">
         <v>4.8</v>
       </c>
-      <c r="BB2">
-        <v>4.5</v>
-      </c>
       <c r="BC2">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD2">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE2">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG2">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BI2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BN2">
         <v>5.6</v>
       </c>
       <c r="BO2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP2">
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS2">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV2">
         <v>38</v>
       </c>
       <c r="BW2">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BX2">
         <v>55</v>
       </c>
       <c r="BY2">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BZ2">
         <v>40</v>
       </c>
       <c r="CA2">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="CB2" t="s">
         <v>145</v>
@@ -1287,10 +1287,10 @@
         <v>123</v>
       </c>
       <c r="F3">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -1305,31 +1305,31 @@
         <v>3.15</v>
       </c>
       <c r="L3">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="M3">
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="O3">
         <v>1.56</v>
       </c>
       <c r="P3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
         <v>2.7</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U3">
         <v>1.79</v>
@@ -1362,7 +1362,7 @@
         <v>17</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF3">
         <v>20</v>
@@ -1395,7 +1395,7 @@
         <v>80</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ3">
         <v>7.6</v>
@@ -1407,13 +1407,13 @@
         <v>6.4</v>
       </c>
       <c r="AT3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW3">
         <v>6.2</v>
@@ -1425,37 +1425,37 @@
         <v>12</v>
       </c>
       <c r="AZ3">
-        <v>5.5</v>
+        <v>21</v>
       </c>
       <c r="BA3">
         <v>6.6</v>
       </c>
       <c r="BB3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC3">
         <v>24</v>
       </c>
       <c r="BD3">
+        <v>6.6</v>
+      </c>
+      <c r="BE3">
+        <v>7</v>
+      </c>
+      <c r="BF3">
         <v>6.4</v>
-      </c>
-      <c r="BE3">
-        <v>6.8</v>
-      </c>
-      <c r="BF3">
-        <v>6.2</v>
       </c>
       <c r="BG3">
         <v>6.4</v>
       </c>
       <c r="BH3">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BI3">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK3">
         <v>7</v>
@@ -1464,7 +1464,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN3">
         <v>5.6</v>
@@ -1476,13 +1476,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT3">
         <v>5.9</v>
@@ -1494,19 +1494,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CB3" t="s">
         <v>145</v>
@@ -1529,13 +1529,13 @@
         <v>124</v>
       </c>
       <c r="F4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G4">
         <v>3.25</v>
       </c>
       <c r="H4">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I4">
         <v>2.74</v>
@@ -1547,34 +1547,34 @@
         <v>3.25</v>
       </c>
       <c r="L4">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O4">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P4">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q4">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="R4">
         <v>1.2</v>
       </c>
       <c r="S4">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V4">
         <v>1.57</v>
@@ -1583,7 +1583,7 @@
         <v>1.44</v>
       </c>
       <c r="X4">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4">
         <v>8.6</v>
@@ -1595,7 +1595,7 @@
         <v>48</v>
       </c>
       <c r="AB4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -1607,7 +1607,7 @@
         <v>40</v>
       </c>
       <c r="AF4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
@@ -1616,7 +1616,7 @@
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ4">
         <v>65</v>
@@ -1625,10 +1625,10 @@
         <v>48</v>
       </c>
       <c r="AL4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM4">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AN4">
         <v>60</v>
@@ -1637,7 +1637,7 @@
         <v>44</v>
       </c>
       <c r="AP4">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4">
         <v>7.4</v>
@@ -1646,7 +1646,7 @@
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT4">
         <v>8.199999999999999</v>
@@ -1655,10 +1655,10 @@
         <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW4">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="AX4">
         <v>16.5</v>
@@ -1670,28 +1670,28 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB4">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="BC4">
         <v>40</v>
       </c>
       <c r="BD4">
+        <v>12.5</v>
+      </c>
+      <c r="BE4">
+        <v>14</v>
+      </c>
+      <c r="BF4">
         <v>12</v>
       </c>
-      <c r="BE4">
+      <c r="BG4">
         <v>11.5</v>
       </c>
-      <c r="BF4">
-        <v>46</v>
-      </c>
-      <c r="BG4">
-        <v>34</v>
-      </c>
       <c r="BH4">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BI4">
         <v>2.38</v>
@@ -1700,13 +1700,13 @@
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN4">
         <v>6.4</v>
@@ -1718,16 +1718,16 @@
         <v>30</v>
       </c>
       <c r="BQ4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
         <v>50</v>
       </c>
       <c r="BS4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU4">
         <v>4.3</v>
@@ -1736,19 +1736,19 @@
         <v>24</v>
       </c>
       <c r="BW4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="CA4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
         <v>145</v>
@@ -1774,88 +1774,88 @@
         <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="H5">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="I5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
       <c r="K5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O5">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="P5">
         <v>1.49</v>
       </c>
       <c r="Q5">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="R5">
         <v>1.17</v>
       </c>
       <c r="S5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="T5">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V5">
         <v>1.35</v>
       </c>
       <c r="W5">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="X5">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>9.800000000000001</v>
       </c>
       <c r="Z5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA5">
         <v>100</v>
       </c>
       <c r="AB5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF5">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AH5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI5">
         <v>110</v>
@@ -1864,79 +1864,79 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL5">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM5">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN5">
         <v>50</v>
       </c>
       <c r="AO5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP5">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5">
         <v>8.6</v>
       </c>
       <c r="AR5">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AT5">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
         <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AW5">
-        <v>40</v>
+        <v>7.2</v>
       </c>
       <c r="AX5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY5">
         <v>11</v>
       </c>
       <c r="AZ5">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BB5">
+        <v>27</v>
+      </c>
+      <c r="BC5">
         <v>26</v>
       </c>
-      <c r="BC5">
-        <v>32</v>
-      </c>
       <c r="BD5">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BE5">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BF5">
-        <v>27</v>
+        <v>6.8</v>
       </c>
       <c r="BG5">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BH5">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BI5">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5">
         <v>13.5</v>
@@ -1948,7 +1948,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BN5">
         <v>5.8</v>
@@ -1957,16 +1957,16 @@
         <v>4.1</v>
       </c>
       <c r="BP5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BT5">
         <v>7.6</v>
@@ -1975,22 +1975,22 @@
         <v>5.2</v>
       </c>
       <c r="BV5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW5">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="s">
         <v>145</v>
@@ -2016,7 +2016,7 @@
         <v>1.49</v>
       </c>
       <c r="G6">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H6">
         <v>6.8</v>
@@ -2025,10 +2025,10 @@
         <v>7.6</v>
       </c>
       <c r="J6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L6">
         <v>1.22</v>
@@ -2037,7 +2037,7 @@
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O6">
         <v>1.16</v>
@@ -2049,10 +2049,10 @@
         <v>1.48</v>
       </c>
       <c r="R6">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S6">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T6">
         <v>1.67</v>
@@ -2061,10 +2061,10 @@
         <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W6">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="X6">
         <v>30</v>
@@ -2115,13 +2115,13 @@
         <v>95</v>
       </c>
       <c r="AN6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO6">
         <v>65</v>
       </c>
       <c r="AP6">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AQ6">
         <v>30</v>
@@ -2136,7 +2136,7 @@
         <v>11.5</v>
       </c>
       <c r="AU6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV6">
         <v>22</v>
@@ -2172,7 +2172,7 @@
         <v>4.7</v>
       </c>
       <c r="BG6">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BH6">
         <v>5.1</v>
@@ -2181,7 +2181,7 @@
         <v>3.95</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK6">
         <v>5</v>
@@ -2190,7 +2190,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN6">
         <v>4.7</v>
@@ -2202,37 +2202,37 @@
         <v>9</v>
       </c>
       <c r="BQ6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR6">
         <v>19.5</v>
       </c>
       <c r="BS6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT6">
         <v>11.5</v>
       </c>
       <c r="BU6">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6">
         <v>11</v>
       </c>
       <c r="CA6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB6" t="s">
         <v>145</v>
@@ -2255,19 +2255,19 @@
         <v>127</v>
       </c>
       <c r="F7">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
         <v>2.28</v>
       </c>
       <c r="H7">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2306,7 +2306,7 @@
         <v>1.05</v>
       </c>
       <c r="W7">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2503,10 +2503,10 @@
         <v>1.33</v>
       </c>
       <c r="H8">
+        <v>12.5</v>
+      </c>
+      <c r="I8">
         <v>13</v>
-      </c>
-      <c r="I8">
-        <v>13.5</v>
       </c>
       <c r="J8">
         <v>5.9</v>
@@ -2527,7 +2527,7 @@
         <v>1.26</v>
       </c>
       <c r="P8">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q8">
         <v>1.79</v>
@@ -2566,13 +2566,13 @@
         <v>8</v>
       </c>
       <c r="AC8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AE8">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AF8">
         <v>7.4</v>
@@ -2584,7 +2584,7 @@
         <v>36</v>
       </c>
       <c r="AI8">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AJ8">
         <v>9.6</v>
@@ -2605,7 +2605,7 @@
         <v>370</v>
       </c>
       <c r="AP8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ8">
         <v>30</v>
@@ -2635,7 +2635,7 @@
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BA8">
         <v>48</v>
@@ -2647,7 +2647,7 @@
         <v>13.5</v>
       </c>
       <c r="BD8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE8">
         <v>50</v>
@@ -2668,13 +2668,13 @@
         <v>14</v>
       </c>
       <c r="BK8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL8">
         <v>210</v>
       </c>
       <c r="BM8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN8">
         <v>3.55</v>
@@ -2692,28 +2692,28 @@
         <v>28</v>
       </c>
       <c r="BS8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT8">
         <v>16</v>
       </c>
       <c r="BU8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV8">
         <v>130</v>
       </c>
       <c r="BW8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BX8">
         <v>120</v>
       </c>
       <c r="BY8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA8">
         <v>7.4</v>
@@ -2999,34 +2999,34 @@
         <v>3.25</v>
       </c>
       <c r="L10">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
         <v>1.12</v>
       </c>
       <c r="N10">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O10">
         <v>1.49</v>
       </c>
       <c r="P10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
       </c>
       <c r="R10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
         <v>5.4</v>
       </c>
       <c r="T10">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V10">
         <v>1.35</v>
@@ -3044,7 +3044,7 @@
         <v>30</v>
       </c>
       <c r="AA10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB10">
         <v>7.6</v>
@@ -3068,7 +3068,7 @@
         <v>25</v>
       </c>
       <c r="AI10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ10">
         <v>44</v>
@@ -3080,7 +3080,7 @@
         <v>80</v>
       </c>
       <c r="AM10">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN10">
         <v>44</v>
@@ -3098,7 +3098,7 @@
         <v>21</v>
       </c>
       <c r="AS10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT10">
         <v>6.2</v>
@@ -3110,7 +3110,7 @@
         <v>14</v>
       </c>
       <c r="AW10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX10">
         <v>11.5</v>
@@ -3122,25 +3122,25 @@
         <v>20</v>
       </c>
       <c r="BA10">
+        <v>7.2</v>
+      </c>
+      <c r="BB10">
+        <v>6.6</v>
+      </c>
+      <c r="BC10">
+        <v>6.4</v>
+      </c>
+      <c r="BD10">
         <v>7</v>
       </c>
-      <c r="BB10">
-        <v>6.2</v>
-      </c>
-      <c r="BC10">
-        <v>6.2</v>
-      </c>
-      <c r="BD10">
-        <v>6.8</v>
-      </c>
       <c r="BE10">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF10">
         <v>27</v>
       </c>
       <c r="BG10">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3164,7 +3164,7 @@
         <v>7</v>
       </c>
       <c r="BO10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP10">
         <v>30</v>
@@ -3200,7 +3200,7 @@
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CB10" t="s">
         <v>145</v>
@@ -3223,13 +3223,13 @@
         <v>131</v>
       </c>
       <c r="F11">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="G11">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="H11">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="I11">
         <v>1.85</v>
@@ -3241,7 +3241,7 @@
         <v>3.6</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M11">
         <v>1.11</v>
@@ -3256,7 +3256,7 @@
         <v>1.56</v>
       </c>
       <c r="Q11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R11">
         <v>1.23</v>
@@ -3265,16 +3265,16 @@
         <v>5</v>
       </c>
       <c r="T11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U11">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V11">
         <v>2.16</v>
       </c>
       <c r="W11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X11">
         <v>9.800000000000001</v>
@@ -3283,7 +3283,7 @@
         <v>6.6</v>
       </c>
       <c r="Z11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AA11">
         <v>21</v>
@@ -3295,16 +3295,16 @@
         <v>8.4</v>
       </c>
       <c r="AD11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE11">
         <v>25</v>
       </c>
       <c r="AF11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH11">
         <v>28</v>
@@ -3313,22 +3313,22 @@
         <v>70</v>
       </c>
       <c r="AJ11">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AK11">
+        <v>130</v>
+      </c>
+      <c r="AL11">
         <v>140</v>
       </c>
-      <c r="AL11">
-        <v>150</v>
-      </c>
       <c r="AM11">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN11">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AO11">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AP11">
         <v>8.199999999999999</v>
@@ -3343,7 +3343,7 @@
         <v>17</v>
       </c>
       <c r="AT11">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU11">
         <v>7.2</v>
@@ -3355,94 +3355,94 @@
         <v>21</v>
       </c>
       <c r="AX11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY11">
         <v>20</v>
       </c>
       <c r="AZ11">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB11">
         <v>10</v>
       </c>
       <c r="BC11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BD11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF11">
         <v>10</v>
       </c>
       <c r="BG11">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB11" t="s">
         <v>145</v>
@@ -3465,16 +3465,16 @@
         <v>132</v>
       </c>
       <c r="F12">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="G12">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="I12">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J12">
         <v>3.1</v>
@@ -3498,7 +3498,7 @@
         <v>1.59</v>
       </c>
       <c r="Q12">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R12">
         <v>1.22</v>
@@ -3513,10 +3513,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3710,16 +3710,16 @@
         <v>1.62</v>
       </c>
       <c r="G13">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H13">
         <v>6.2</v>
       </c>
       <c r="I13">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="K13">
         <v>4.5</v>
@@ -3740,7 +3740,7 @@
         <v>1.73</v>
       </c>
       <c r="Q13">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="R13">
         <v>1.15</v>
@@ -3749,16 +3749,16 @@
         <v>3.75</v>
       </c>
       <c r="T13">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
         <v>1.71</v>
       </c>
       <c r="V13">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W13">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X13">
         <v>14.5</v>
@@ -3949,19 +3949,19 @@
         <v>134</v>
       </c>
       <c r="F14">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G14">
         <v>990</v>
       </c>
       <c r="H14">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="I14">
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -3979,7 +3979,7 @@
         <v>1.18</v>
       </c>
       <c r="P14">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q14">
         <v>1.18</v>
@@ -4000,7 +4000,7 @@
         <v>1.06</v>
       </c>
       <c r="W14">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4194,10 +4194,10 @@
         <v>1.54</v>
       </c>
       <c r="G15">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H15">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I15">
         <v>8.199999999999999</v>
@@ -4206,7 +4206,7 @@
         <v>3.8</v>
       </c>
       <c r="K15">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L15">
         <v>1.27</v>
@@ -4433,46 +4433,46 @@
         <v>136</v>
       </c>
       <c r="F16">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G16">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H16">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I16">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J16">
         <v>4.1</v>
       </c>
       <c r="K16">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>1.15</v>
       </c>
       <c r="P16">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q16">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R16">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S16">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="T16">
         <v>1.44</v>
@@ -4487,7 +4487,7 @@
         <v>1.64</v>
       </c>
       <c r="X16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y16">
         <v>22</v>
@@ -4541,7 +4541,7 @@
         <v>13</v>
       </c>
       <c r="AP16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ16">
         <v>17.5</v>
@@ -4592,13 +4592,13 @@
         <v>9.6</v>
       </c>
       <c r="BG16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BJ16">
         <v>11.5</v>
@@ -4610,7 +4610,7 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BN16">
         <v>8.800000000000001</v>
@@ -4622,16 +4622,16 @@
         <v>23</v>
       </c>
       <c r="BQ16">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BR16">
         <v>30</v>
       </c>
       <c r="BS16">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BT16">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU16">
         <v>4.3</v>
@@ -4640,19 +4640,19 @@
         <v>26</v>
       </c>
       <c r="BW16">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BX16">
         <v>32</v>
       </c>
       <c r="BY16">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="BZ16">
         <v>18.5</v>
       </c>
       <c r="CA16">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CB16" t="s">
         <v>145</v>
@@ -4684,13 +4684,13 @@
         <v>10.5</v>
       </c>
       <c r="I17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J17">
         <v>4.7</v>
       </c>
       <c r="K17">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4705,16 +4705,16 @@
         <v>1.31</v>
       </c>
       <c r="P17">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q17">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="R17">
         <v>1.28</v>
       </c>
       <c r="S17">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T17">
         <v>2.08</v>
@@ -4726,7 +4726,7 @@
         <v>1.08</v>
       </c>
       <c r="W17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X17">
         <v>20</v>
@@ -4917,16 +4917,16 @@
         <v>138</v>
       </c>
       <c r="F18">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G18">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I18">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J18">
         <v>3.05</v>
@@ -4941,7 +4941,7 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="O18">
         <v>1.54</v>
@@ -4953,7 +4953,7 @@
         <v>2.74</v>
       </c>
       <c r="R18">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="S18">
         <v>5.7</v>
@@ -4968,7 +4968,7 @@
         <v>1.3</v>
       </c>
       <c r="W18">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="X18">
         <v>8.6</v>
@@ -5082,7 +5082,7 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="BJ18">
         <v>17</v>
@@ -5159,58 +5159,58 @@
         <v>139</v>
       </c>
       <c r="F19">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G19">
         <v>2.4</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J19">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K19">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M19">
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O19">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P19">
         <v>2.3</v>
       </c>
       <c r="Q19">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R19">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S19">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="T19">
         <v>1.62</v>
       </c>
       <c r="U19">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V19">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W19">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X19">
         <v>24</v>
@@ -5228,7 +5228,7 @@
         <v>13</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD19">
         <v>16</v>
@@ -5240,13 +5240,13 @@
         <v>17</v>
       </c>
       <c r="AG19">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH19">
         <v>16</v>
       </c>
       <c r="AI19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ19">
         <v>36</v>
@@ -5258,7 +5258,7 @@
         <v>36</v>
       </c>
       <c r="AM19">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN19">
         <v>16.5</v>
@@ -5276,13 +5276,13 @@
         <v>21</v>
       </c>
       <c r="AS19">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU19">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV19">
         <v>12</v>
@@ -5294,22 +5294,22 @@
         <v>15</v>
       </c>
       <c r="AY19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19">
         <v>14</v>
       </c>
       <c r="BA19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC19">
         <v>20</v>
       </c>
       <c r="BD19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE19">
         <v>32</v>
@@ -5330,13 +5330,13 @@
         <v>12.5</v>
       </c>
       <c r="BK19">
-        <v>5.4</v>
+        <v>1.65</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="BN19">
         <v>7.8</v>
@@ -5354,7 +5354,7 @@
         <v>38</v>
       </c>
       <c r="BS19">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="BT19">
         <v>9.199999999999999</v>
@@ -5375,7 +5375,7 @@
         <v>1.83</v>
       </c>
       <c r="BZ19">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA19">
         <v>1.79</v>
@@ -5416,22 +5416,22 @@
         <v>4</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M20">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N20">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O20">
         <v>1.19</v>
       </c>
       <c r="P20">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q20">
         <v>1.58</v>
@@ -5440,7 +5440,7 @@
         <v>1.64</v>
       </c>
       <c r="S20">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T20">
         <v>1.53</v>
@@ -5479,7 +5479,7 @@
         <v>26</v>
       </c>
       <c r="AF20">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG20">
         <v>14</v>
@@ -5494,7 +5494,7 @@
         <v>60</v>
       </c>
       <c r="AK20">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AL20">
         <v>38</v>
@@ -5643,16 +5643,16 @@
         <v>141</v>
       </c>
       <c r="F21">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G21">
         <v>2.32</v>
       </c>
       <c r="H21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I21">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J21">
         <v>3.7</v>
@@ -5661,28 +5661,28 @@
         <v>3.85</v>
       </c>
       <c r="L21">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M21">
         <v>1.06</v>
       </c>
       <c r="N21">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O21">
         <v>1.28</v>
       </c>
       <c r="P21">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q21">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R21">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S21">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T21">
         <v>1.69</v>
@@ -5691,7 +5691,7 @@
         <v>2.32</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
         <v>1.76</v>
@@ -5706,16 +5706,16 @@
         <v>30</v>
       </c>
       <c r="AA21">
-        <v>610</v>
+        <v>520</v>
       </c>
       <c r="AB21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC21">
         <v>8.6</v>
       </c>
       <c r="AD21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE21">
         <v>44</v>
@@ -5751,7 +5751,7 @@
         <v>55</v>
       </c>
       <c r="AP21">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ21">
         <v>12.5</v>
@@ -5766,7 +5766,7 @@
         <v>10</v>
       </c>
       <c r="AU21">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV21">
         <v>12.5</v>
@@ -5802,7 +5802,7 @@
         <v>14.5</v>
       </c>
       <c r="BG21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5885,7 +5885,7 @@
         <v>142</v>
       </c>
       <c r="F22">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G22">
         <v>3.05</v>
@@ -5894,16 +5894,16 @@
         <v>2.28</v>
       </c>
       <c r="I22">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K22">
         <v>4.4</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M22">
         <v>1.02</v>
@@ -5915,13 +5915,13 @@
         <v>1.13</v>
       </c>
       <c r="P22">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R22">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S22">
         <v>2.02</v>
@@ -5933,7 +5933,7 @@
         <v>3.2</v>
       </c>
       <c r="V22">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W22">
         <v>1.49</v>
@@ -5987,10 +5987,10 @@
         <v>46</v>
       </c>
       <c r="AN22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO22">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AP22">
         <v>30</v>
@@ -6005,7 +6005,7 @@
         <v>30</v>
       </c>
       <c r="AT22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU22">
         <v>10</v>
@@ -6017,7 +6017,7 @@
         <v>18</v>
       </c>
       <c r="AX22">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY22">
         <v>11.5</v>
@@ -6032,7 +6032,7 @@
         <v>42</v>
       </c>
       <c r="BC22">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="BD22">
         <v>24</v>
@@ -6133,7 +6133,7 @@
         <v>1.69</v>
       </c>
       <c r="H23">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I23">
         <v>5.5</v>
@@ -6145,19 +6145,19 @@
         <v>4.7</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N23">
         <v>5.6</v>
       </c>
       <c r="O23">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P23">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q23">
         <v>1.59</v>
@@ -6166,7 +6166,7 @@
         <v>1.62</v>
       </c>
       <c r="S23">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T23">
         <v>1.66</v>
@@ -6238,7 +6238,7 @@
         <v>21</v>
       </c>
       <c r="AQ23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR23">
         <v>26</v>
@@ -6372,13 +6372,13 @@
         <v>2.02</v>
       </c>
       <c r="G24">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H24">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I24">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J24">
         <v>4.1</v>
@@ -6387,7 +6387,7 @@
         <v>4.4</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M24">
         <v>1.03</v>
@@ -6396,31 +6396,31 @@
         <v>6.4</v>
       </c>
       <c r="O24">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P24">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="Q24">
         <v>1.51</v>
       </c>
       <c r="R24">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S24">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T24">
         <v>1.49</v>
       </c>
       <c r="U24">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="V24">
         <v>1.37</v>
       </c>
       <c r="W24">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X24">
         <v>29</v>
@@ -6432,7 +6432,7 @@
         <v>32</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB24">
         <v>16</v>
@@ -6468,7 +6468,7 @@
         <v>24</v>
       </c>
       <c r="AM24">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN24">
         <v>8.6</v>
@@ -6510,7 +6510,7 @@
         <v>12.5</v>
       </c>
       <c r="BA24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB24">
         <v>18</v>
@@ -6528,7 +6528,7 @@
         <v>7.8</v>
       </c>
       <c r="BG24">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BN24">
         <v>7.8</v>
@@ -6555,13 +6555,13 @@
         <v>3.6</v>
       </c>
       <c r="BP24">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ24">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BR24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS24">
         <v>1.9</v>
@@ -6576,19 +6576,19 @@
         <v>34</v>
       </c>
       <c r="BW24">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="BX24">
         <v>40</v>
       </c>
       <c r="BY24">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="BZ24">
         <v>19</v>
       </c>
       <c r="CA24">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CB24" t="s">
         <v>145</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="148">
   <si>
     <t>League</t>
   </si>
@@ -355,6 +355,9 @@
     <t>Forge</t>
   </si>
   <si>
+    <t>Cucuta Deportivo</t>
+  </si>
+  <si>
     <t>Philadelphia</t>
   </si>
   <si>
@@ -424,6 +427,9 @@
     <t>FC Supra du Quebec</t>
   </si>
   <si>
+    <t>Internacional de Bogotá</t>
+  </si>
+  <si>
     <t>Inter Miami CF</t>
   </si>
   <si>
@@ -451,7 +457,7 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-18 02:39:46</t>
+    <t>2026-08-18 04:47:25</t>
   </si>
 </sst>
 </file>
@@ -783,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1042,7 +1048,7 @@
         <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F2">
         <v>2.28</v>
@@ -1060,25 +1066,25 @@
         <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
         <v>1.5</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R2">
         <v>1.26</v>
@@ -1090,7 +1096,7 @@
         <v>1.91</v>
       </c>
       <c r="U2">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V2">
         <v>1.33</v>
@@ -1099,7 +1105,7 @@
         <v>1.75</v>
       </c>
       <c r="X2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y2">
         <v>14</v>
@@ -1108,13 +1114,13 @@
         <v>32</v>
       </c>
       <c r="AA2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB2">
         <v>9.4</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
         <v>19</v>
@@ -1123,46 +1129,46 @@
         <v>65</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI2">
         <v>80</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK2">
+        <v>34</v>
+      </c>
+      <c r="AL2">
+        <v>60</v>
+      </c>
+      <c r="AM2">
+        <v>160</v>
+      </c>
+      <c r="AN2">
         <v>32</v>
       </c>
-      <c r="AL2">
-        <v>55</v>
-      </c>
-      <c r="AM2">
-        <v>150</v>
-      </c>
-      <c r="AN2">
-        <v>29</v>
-      </c>
       <c r="AO2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
         <v>10</v>
       </c>
       <c r="AR2">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AS2">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT2">
         <v>7</v>
@@ -1174,40 +1180,40 @@
         <v>14</v>
       </c>
       <c r="AW2">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2">
         <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB2">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BC2">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BD2">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BE2">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF2">
         <v>20</v>
       </c>
       <c r="BG2">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI2">
         <v>2.54</v>
@@ -1222,7 +1228,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BN2">
         <v>5.6</v>
@@ -1234,13 +1240,13 @@
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR2">
         <v>42</v>
       </c>
       <c r="BS2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
@@ -1252,22 +1258,22 @@
         <v>38</v>
       </c>
       <c r="BW2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX2">
         <v>55</v>
       </c>
       <c r="BY2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BZ2">
         <v>40</v>
       </c>
       <c r="CA2">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="CB2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1284,19 +1290,19 @@
         <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F3">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="G3">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="I3">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="J3">
         <v>3.05</v>
@@ -1311,34 +1317,34 @@
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q3">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X3">
         <v>10</v>
@@ -1371,13 +1377,13 @@
         <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI3">
         <v>80</v>
       </c>
       <c r="AJ3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK3">
         <v>55</v>
@@ -1401,7 +1407,7 @@
         <v>7.6</v>
       </c>
       <c r="AR3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS3">
         <v>6.4</v>
@@ -1413,7 +1419,7 @@
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
         <v>6.2</v>
@@ -1425,7 +1431,7 @@
         <v>12</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
         <v>6.6</v>
@@ -1446,28 +1452,28 @@
         <v>6.4</v>
       </c>
       <c r="BG3">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="BH3">
         <v>2.72</v>
       </c>
       <c r="BI3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ3">
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO3">
         <v>5</v>
@@ -1476,19 +1482,19 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT3">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BU3">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1500,16 +1506,16 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1526,7 +1532,7 @@
         <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F4">
         <v>3.1</v>
@@ -1547,31 +1553,31 @@
         <v>3.25</v>
       </c>
       <c r="L4">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M4">
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O4">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P4">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q4">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S4">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
         <v>1.83</v>
@@ -1583,7 +1589,7 @@
         <v>1.44</v>
       </c>
       <c r="X4">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y4">
         <v>8.6</v>
@@ -1601,7 +1607,7 @@
         <v>7</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE4">
         <v>40</v>
@@ -1616,7 +1622,7 @@
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ4">
         <v>65</v>
@@ -1625,10 +1631,10 @@
         <v>48</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM4">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN4">
         <v>60</v>
@@ -1637,7 +1643,7 @@
         <v>44</v>
       </c>
       <c r="AP4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4">
         <v>7.4</v>
@@ -1646,7 +1652,7 @@
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT4">
         <v>8.199999999999999</v>
@@ -1658,7 +1664,7 @@
         <v>12</v>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX4">
         <v>16.5</v>
@@ -1670,28 +1676,28 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB4">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BC4">
         <v>40</v>
       </c>
       <c r="BD4">
-        <v>12.5</v>
+        <v>46</v>
       </c>
       <c r="BE4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BF4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI4">
         <v>2.38</v>
@@ -1700,25 +1706,25 @@
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN4">
         <v>6.4</v>
       </c>
       <c r="BO4">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BP4">
         <v>30</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR4">
         <v>50</v>
@@ -1730,28 +1736,28 @@
         <v>5.6</v>
       </c>
       <c r="BU4">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV4">
         <v>24</v>
       </c>
       <c r="BW4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="CA4">
         <v>10</v>
       </c>
       <c r="CB4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1768,16 +1774,16 @@
         <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G5">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I5">
         <v>3.85</v>
@@ -1792,19 +1798,19 @@
         <v>1.64</v>
       </c>
       <c r="M5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N5">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="P5">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q5">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R5">
         <v>1.17</v>
@@ -1813,19 +1819,19 @@
         <v>6.2</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U5">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V5">
         <v>1.35</v>
       </c>
       <c r="W5">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y5">
         <v>9.800000000000001</v>
@@ -1852,7 +1858,7 @@
         <v>14</v>
       </c>
       <c r="AG5">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="AH5">
         <v>29</v>
@@ -1876,7 +1882,7 @@
         <v>50</v>
       </c>
       <c r="AO5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP5">
         <v>6.2</v>
@@ -1888,10 +1894,10 @@
         <v>21</v>
       </c>
       <c r="AS5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU5">
         <v>6.2</v>
@@ -1933,7 +1939,7 @@
         <v>7.4</v>
       </c>
       <c r="BH5">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI5">
         <v>2.24</v>
@@ -1948,7 +1954,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN5">
         <v>5.8</v>
@@ -1960,40 +1966,40 @@
         <v>25</v>
       </c>
       <c r="BQ5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BT5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU5">
         <v>5.2</v>
       </c>
       <c r="BV5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2010,7 +2016,7 @@
         <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F6">
         <v>1.49</v>
@@ -2037,7 +2043,7 @@
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O6">
         <v>1.16</v>
@@ -2052,13 +2058,13 @@
         <v>1.77</v>
       </c>
       <c r="S6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T6">
         <v>1.67</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V6">
         <v>1.15</v>
@@ -2121,7 +2127,7 @@
         <v>65</v>
       </c>
       <c r="AP6">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AQ6">
         <v>30</v>
@@ -2142,13 +2148,13 @@
         <v>22</v>
       </c>
       <c r="AW6">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AX6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6">
         <v>17</v>
@@ -2169,7 +2175,7 @@
         <v>50</v>
       </c>
       <c r="BF6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG6">
         <v>40</v>
@@ -2181,7 +2187,7 @@
         <v>3.95</v>
       </c>
       <c r="BJ6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
         <v>5</v>
@@ -2190,7 +2196,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN6">
         <v>4.7</v>
@@ -2202,40 +2208,40 @@
         <v>9</v>
       </c>
       <c r="BQ6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR6">
         <v>19.5</v>
       </c>
       <c r="BS6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT6">
         <v>11.5</v>
       </c>
       <c r="BU6">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ6">
         <v>11</v>
       </c>
       <c r="CA6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="CB6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2252,16 +2258,16 @@
         <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F7">
         <v>1.04</v>
       </c>
       <c r="G7">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I7">
         <v>990</v>
@@ -2303,10 +2309,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W7">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2477,7 +2483,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2494,7 +2500,7 @@
         <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F8">
         <v>1.32</v>
@@ -2503,7 +2509,7 @@
         <v>1.33</v>
       </c>
       <c r="H8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I8">
         <v>13</v>
@@ -2512,7 +2518,7 @@
         <v>5.9</v>
       </c>
       <c r="K8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L8">
         <v>1.36</v>
@@ -2527,7 +2533,7 @@
         <v>1.26</v>
       </c>
       <c r="P8">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q8">
         <v>1.79</v>
@@ -2569,7 +2575,7 @@
         <v>13.5</v>
       </c>
       <c r="AD8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AE8">
         <v>250</v>
@@ -2584,7 +2590,7 @@
         <v>36</v>
       </c>
       <c r="AI8">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AJ8">
         <v>9.6</v>
@@ -2605,13 +2611,13 @@
         <v>370</v>
       </c>
       <c r="AP8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8">
         <v>30</v>
       </c>
       <c r="AR8">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AS8">
         <v>55</v>
@@ -2635,7 +2641,7 @@
         <v>10</v>
       </c>
       <c r="AZ8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA8">
         <v>48</v>
@@ -2644,10 +2650,10 @@
         <v>9</v>
       </c>
       <c r="BC8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE8">
         <v>50</v>
@@ -2674,7 +2680,7 @@
         <v>210</v>
       </c>
       <c r="BM8">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="BN8">
         <v>3.55</v>
@@ -2704,13 +2710,13 @@
         <v>130</v>
       </c>
       <c r="BW8">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="BX8">
         <v>120</v>
       </c>
       <c r="BY8">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BZ8">
         <v>13.5</v>
@@ -2719,7 +2725,7 @@
         <v>7.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2736,16 +2742,16 @@
         <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F9">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G9">
         <v>2.12</v>
       </c>
       <c r="H9">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I9">
         <v>4.7</v>
@@ -2754,7 +2760,7 @@
         <v>3.35</v>
       </c>
       <c r="K9">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2763,22 +2769,22 @@
         <v>1.09</v>
       </c>
       <c r="N9">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O9">
         <v>1.39</v>
       </c>
       <c r="P9">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q9">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R9">
         <v>1.28</v>
       </c>
       <c r="S9">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T9">
         <v>1.9</v>
@@ -2850,7 +2856,7 @@
         <v>5.7</v>
       </c>
       <c r="AQ9">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="AR9">
         <v>7.4</v>
@@ -2859,43 +2865,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV9">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AW9">
         <v>8.4</v>
       </c>
       <c r="AX9">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY9">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA9">
         <v>8.6</v>
       </c>
       <c r="BB9">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BC9">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BD9">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9">
         <v>9</v>
       </c>
       <c r="BF9">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BG9">
         <v>8.6</v>
@@ -2961,7 +2967,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2978,7 +2984,7 @@
         <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F10">
         <v>2.4</v>
@@ -3005,16 +3011,16 @@
         <v>1.12</v>
       </c>
       <c r="N10">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O10">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="P10">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q10">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R10">
         <v>1.18</v>
@@ -3023,7 +3029,7 @@
         <v>5.4</v>
       </c>
       <c r="T10">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
         <v>1.64</v>
@@ -3170,7 +3176,7 @@
         <v>30</v>
       </c>
       <c r="BQ10">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BR10">
         <v>1000</v>
@@ -3203,7 +3209,7 @@
         <v>1.63</v>
       </c>
       <c r="CB10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3220,7 +3226,7 @@
         <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F11">
         <v>5.2</v>
@@ -3229,10 +3235,10 @@
         <v>5.9</v>
       </c>
       <c r="H11">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I11">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="J11">
         <v>3.4</v>
@@ -3247,7 +3253,7 @@
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O11">
         <v>1.48</v>
@@ -3259,19 +3265,19 @@
         <v>2.46</v>
       </c>
       <c r="R11">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S11">
         <v>5</v>
       </c>
       <c r="T11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U11">
         <v>1.62</v>
       </c>
       <c r="V11">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W11">
         <v>1.2</v>
@@ -3328,10 +3334,10 @@
         <v>220</v>
       </c>
       <c r="AO11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11">
         <v>5.7</v>
@@ -3355,7 +3361,7 @@
         <v>21</v>
       </c>
       <c r="AX11">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY11">
         <v>20</v>
@@ -3364,10 +3370,10 @@
         <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC11">
         <v>10</v>
@@ -3379,7 +3385,7 @@
         <v>10.5</v>
       </c>
       <c r="BF11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG11">
         <v>17</v>
@@ -3445,7 +3451,7 @@
         <v>5.3</v>
       </c>
       <c r="CB11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3462,169 +3468,169 @@
         <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F12">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I12">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J12">
         <v>3.1</v>
       </c>
       <c r="K12">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="O12">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="P12">
         <v>1.59</v>
       </c>
       <c r="Q12">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R12">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S12">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W12">
         <v>1.5</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3687,7 +3693,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3704,169 +3710,169 @@
         <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F13">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="G13">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H13">
         <v>6.2</v>
       </c>
       <c r="I13">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K13">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N13">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="O13">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="P13">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q13">
-        <v>1.59</v>
+        <v>2.12</v>
       </c>
       <c r="R13">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="S13">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U13">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="V13">
         <v>1.15</v>
       </c>
       <c r="W13">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X13">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y13">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG13">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK13">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN13">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP13">
-        <v>1.28</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>15.5</v>
       </c>
       <c r="AR13">
-        <v>1.41</v>
+        <v>6</v>
       </c>
       <c r="AS13">
-        <v>1.41</v>
+        <v>6.4</v>
       </c>
       <c r="AT13">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="AU13">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV13">
-        <v>19</v>
+        <v>5.3</v>
       </c>
       <c r="AW13">
-        <v>1.41</v>
+        <v>6.2</v>
       </c>
       <c r="AX13">
-        <v>1.41</v>
+        <v>7.6</v>
       </c>
       <c r="AY13">
-        <v>1.27</v>
+        <v>9</v>
       </c>
       <c r="AZ13">
-        <v>1.4</v>
+        <v>21</v>
       </c>
       <c r="BA13">
-        <v>1.41</v>
+        <v>6.2</v>
       </c>
       <c r="BB13">
-        <v>1.41</v>
+        <v>14</v>
       </c>
       <c r="BC13">
-        <v>1.33</v>
+        <v>17.5</v>
       </c>
       <c r="BD13">
-        <v>1.41</v>
+        <v>5.9</v>
       </c>
       <c r="BE13">
-        <v>1.41</v>
+        <v>6.4</v>
       </c>
       <c r="BF13">
-        <v>1.29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG13">
-        <v>1.41</v>
+        <v>6.4</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3929,7 +3935,7 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3946,25 +3952,25 @@
         <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F14">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="G14">
-        <v>990</v>
+        <v>2.94</v>
       </c>
       <c r="H14">
-        <v>1.41</v>
+        <v>2.58</v>
       </c>
       <c r="I14">
-        <v>990</v>
+        <v>2.96</v>
       </c>
       <c r="J14">
-        <v>1.59</v>
+        <v>3.1</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -3973,13 +3979,13 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="O14">
         <v>1.18</v>
       </c>
       <c r="P14">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="Q14">
         <v>1.18</v>
@@ -3997,10 +4003,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.06</v>
+        <v>1.51</v>
       </c>
       <c r="W14">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4171,7 +4177,7 @@
         <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4188,7 +4194,7 @@
         <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F15">
         <v>1.54</v>
@@ -4413,254 +4419,254 @@
         <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
         <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
         <v>113</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F16">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="G16">
-        <v>2.56</v>
+        <v>110</v>
       </c>
       <c r="H16">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="I16">
-        <v>2.74</v>
+        <v>110</v>
       </c>
       <c r="J16">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="K16">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L16">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>7</v>
+        <v>1.09</v>
       </c>
       <c r="O16">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="P16">
-        <v>3</v>
+        <v>1.09</v>
       </c>
       <c r="Q16">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="R16">
-        <v>1.82</v>
+        <v>1.08</v>
       </c>
       <c r="S16">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="T16">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="W16">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
         <v>88</v>
@@ -4672,232 +4678,232 @@
         <v>114</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F17">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="G17">
-        <v>1.42</v>
+        <v>2.58</v>
       </c>
       <c r="H17">
-        <v>10.5</v>
+        <v>2.66</v>
       </c>
       <c r="I17">
-        <v>13</v>
+        <v>2.72</v>
       </c>
       <c r="J17">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K17">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="P17">
-        <v>1.89</v>
+        <v>3</v>
       </c>
       <c r="Q17">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="R17">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="S17">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="T17">
+        <v>1.44</v>
+      </c>
+      <c r="U17">
+        <v>3.05</v>
+      </c>
+      <c r="V17">
+        <v>1.58</v>
+      </c>
+      <c r="W17">
+        <v>1.64</v>
+      </c>
+      <c r="X17">
+        <v>34</v>
+      </c>
+      <c r="Y17">
+        <v>22</v>
+      </c>
+      <c r="Z17">
+        <v>26</v>
+      </c>
+      <c r="AA17">
+        <v>44</v>
+      </c>
+      <c r="AB17">
+        <v>21</v>
+      </c>
+      <c r="AC17">
+        <v>11.5</v>
+      </c>
+      <c r="AD17">
+        <v>15.5</v>
+      </c>
+      <c r="AE17">
+        <v>25</v>
+      </c>
+      <c r="AF17">
+        <v>24</v>
+      </c>
+      <c r="AG17">
+        <v>13.5</v>
+      </c>
+      <c r="AH17">
+        <v>14.5</v>
+      </c>
+      <c r="AI17">
+        <v>28</v>
+      </c>
+      <c r="AJ17">
+        <v>38</v>
+      </c>
+      <c r="AK17">
+        <v>23</v>
+      </c>
+      <c r="AL17">
+        <v>27</v>
+      </c>
+      <c r="AM17">
+        <v>46</v>
+      </c>
+      <c r="AN17">
+        <v>11</v>
+      </c>
+      <c r="AO17">
+        <v>12.5</v>
+      </c>
+      <c r="AP17">
+        <v>21</v>
+      </c>
+      <c r="AQ17">
+        <v>17.5</v>
+      </c>
+      <c r="AR17">
+        <v>21</v>
+      </c>
+      <c r="AS17">
+        <v>25</v>
+      </c>
+      <c r="AT17">
+        <v>17.5</v>
+      </c>
+      <c r="AU17">
+        <v>9.6</v>
+      </c>
+      <c r="AV17">
+        <v>11.5</v>
+      </c>
+      <c r="AW17">
+        <v>20</v>
+      </c>
+      <c r="AX17">
+        <v>19.5</v>
+      </c>
+      <c r="AY17">
+        <v>11</v>
+      </c>
+      <c r="AZ17">
+        <v>12.5</v>
+      </c>
+      <c r="BA17">
+        <v>17.5</v>
+      </c>
+      <c r="BB17">
+        <v>23</v>
+      </c>
+      <c r="BC17">
+        <v>19.5</v>
+      </c>
+      <c r="BD17">
+        <v>21</v>
+      </c>
+      <c r="BE17">
+        <v>24</v>
+      </c>
+      <c r="BF17">
+        <v>9.6</v>
+      </c>
+      <c r="BG17">
+        <v>11</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
         <v>2.08</v>
       </c>
-      <c r="U17">
-        <v>1.56</v>
-      </c>
-      <c r="V17">
-        <v>1.08</v>
-      </c>
-      <c r="W17">
-        <v>3.25</v>
-      </c>
-      <c r="X17">
-        <v>20</v>
-      </c>
-      <c r="Y17">
-        <v>950</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>9.6</v>
-      </c>
-      <c r="AC17">
-        <v>12</v>
-      </c>
-      <c r="AD17">
-        <v>950</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>10</v>
-      </c>
-      <c r="AG17">
-        <v>15.5</v>
-      </c>
-      <c r="AH17">
-        <v>950</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>16</v>
-      </c>
-      <c r="AK17">
-        <v>25</v>
-      </c>
-      <c r="AL17">
-        <v>70</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>10.5</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>2.66</v>
-      </c>
-      <c r="AQ17">
-        <v>2.86</v>
-      </c>
-      <c r="AR17">
-        <v>3.05</v>
-      </c>
-      <c r="AS17">
-        <v>3.05</v>
-      </c>
-      <c r="AT17">
-        <v>2.32</v>
-      </c>
-      <c r="AU17">
-        <v>2.44</v>
-      </c>
-      <c r="AV17">
-        <v>2.94</v>
-      </c>
-      <c r="AW17">
-        <v>3.05</v>
-      </c>
-      <c r="AX17">
-        <v>2.36</v>
-      </c>
-      <c r="AY17">
-        <v>2.56</v>
-      </c>
-      <c r="AZ17">
-        <v>2.9</v>
-      </c>
-      <c r="BA17">
-        <v>3.05</v>
-      </c>
-      <c r="BB17">
-        <v>2.58</v>
-      </c>
-      <c r="BC17">
-        <v>2.74</v>
-      </c>
-      <c r="BD17">
-        <v>2.96</v>
-      </c>
-      <c r="BE17">
-        <v>3.05</v>
-      </c>
-      <c r="BF17">
-        <v>4.9</v>
-      </c>
-      <c r="BG17">
-        <v>3.05</v>
-      </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
-        <v>1.04</v>
-      </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK17">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO17">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ17">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS17">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU17">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA17">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="CB17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4914,237 +4920,237 @@
         <v>115</v>
       </c>
       <c r="E18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F18">
-        <v>2.24</v>
+        <v>1.38</v>
       </c>
       <c r="G18">
-        <v>2.32</v>
+        <v>1.42</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I18">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="J18">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="K18">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N18">
-        <v>2.56</v>
+        <v>3.6</v>
       </c>
       <c r="O18">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="P18">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="Q18">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="R18">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="S18">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="T18">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="U18">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V18">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="W18">
-        <v>1.75</v>
+        <v>3.35</v>
       </c>
       <c r="X18">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA18">
         <v>1000</v>
       </c>
       <c r="AB18">
+        <v>7.4</v>
+      </c>
+      <c r="AC18">
+        <v>11.5</v>
+      </c>
+      <c r="AD18">
+        <v>44</v>
+      </c>
+      <c r="AE18">
+        <v>270</v>
+      </c>
+      <c r="AF18">
+        <v>7.8</v>
+      </c>
+      <c r="AG18">
+        <v>11</v>
+      </c>
+      <c r="AH18">
+        <v>34</v>
+      </c>
+      <c r="AI18">
+        <v>220</v>
+      </c>
+      <c r="AJ18">
+        <v>12</v>
+      </c>
+      <c r="AK18">
+        <v>17.5</v>
+      </c>
+      <c r="AL18">
+        <v>50</v>
+      </c>
+      <c r="AM18">
+        <v>270</v>
+      </c>
+      <c r="AN18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO18">
+        <v>470</v>
+      </c>
+      <c r="AP18">
+        <v>13</v>
+      </c>
+      <c r="AQ18">
         <v>7</v>
       </c>
-      <c r="AC18">
-        <v>1000</v>
-      </c>
-      <c r="AD18">
-        <v>1000</v>
-      </c>
-      <c r="AE18">
-        <v>1000</v>
-      </c>
-      <c r="AF18">
-        <v>1000</v>
-      </c>
-      <c r="AG18">
-        <v>1000</v>
-      </c>
-      <c r="AH18">
-        <v>1000</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>1000</v>
-      </c>
-      <c r="AK18">
-        <v>1000</v>
-      </c>
-      <c r="AL18">
-        <v>1000</v>
-      </c>
-      <c r="AM18">
-        <v>1000</v>
-      </c>
-      <c r="AN18">
-        <v>1000</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
-        <v>1.17</v>
-      </c>
-      <c r="AQ18">
-        <v>1.35</v>
-      </c>
       <c r="AR18">
-        <v>1.35</v>
+        <v>8.4</v>
       </c>
       <c r="AS18">
-        <v>1.35</v>
+        <v>9</v>
       </c>
       <c r="AT18">
-        <v>1.13</v>
+        <v>6</v>
       </c>
       <c r="AU18">
-        <v>1.35</v>
+        <v>9.6</v>
       </c>
       <c r="AV18">
-        <v>1.35</v>
+        <v>7.6</v>
       </c>
       <c r="AW18">
-        <v>1.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX18">
-        <v>1.35</v>
+        <v>6.4</v>
       </c>
       <c r="AY18">
+        <v>9</v>
+      </c>
+      <c r="AZ18">
+        <v>7.2</v>
+      </c>
+      <c r="BA18">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ18">
-        <v>1.35</v>
-      </c>
-      <c r="BA18">
-        <v>1.35</v>
-      </c>
       <c r="BB18">
-        <v>1.35</v>
+        <v>9.6</v>
       </c>
       <c r="BC18">
-        <v>1.35</v>
+        <v>14</v>
       </c>
       <c r="BD18">
-        <v>1.35</v>
+        <v>7.6</v>
       </c>
       <c r="BE18">
-        <v>1.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18">
-        <v>1.35</v>
+        <v>6.4</v>
       </c>
       <c r="BG18">
-        <v>1.35</v>
+        <v>9</v>
       </c>
       <c r="BH18">
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
         <v>88</v>
@@ -5156,232 +5162,232 @@
         <v>116</v>
       </c>
       <c r="E19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F19">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G19">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H19">
+        <v>4.1</v>
+      </c>
+      <c r="I19">
+        <v>4.3</v>
+      </c>
+      <c r="J19">
         <v>3.05</v>
       </c>
-      <c r="I19">
-        <v>3.2</v>
-      </c>
-      <c r="J19">
-        <v>3.75</v>
-      </c>
       <c r="K19">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="L19">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>4.9</v>
+        <v>2.56</v>
       </c>
       <c r="O19">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="P19">
-        <v>2.3</v>
+        <v>1.51</v>
       </c>
       <c r="Q19">
-        <v>1.71</v>
+        <v>2.74</v>
       </c>
       <c r="R19">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="S19">
-        <v>2.82</v>
+        <v>5.7</v>
       </c>
       <c r="T19">
+        <v>2.14</v>
+      </c>
+      <c r="U19">
+        <v>1.68</v>
+      </c>
+      <c r="V19">
+        <v>1.3</v>
+      </c>
+      <c r="W19">
+        <v>1.76</v>
+      </c>
+      <c r="X19">
+        <v>8.6</v>
+      </c>
+      <c r="Y19">
+        <v>13</v>
+      </c>
+      <c r="Z19">
+        <v>34</v>
+      </c>
+      <c r="AA19">
+        <v>120</v>
+      </c>
+      <c r="AB19">
+        <v>6.8</v>
+      </c>
+      <c r="AC19">
+        <v>9</v>
+      </c>
+      <c r="AD19">
+        <v>23</v>
+      </c>
+      <c r="AE19">
+        <v>90</v>
+      </c>
+      <c r="AF19">
+        <v>15</v>
+      </c>
+      <c r="AG19">
+        <v>14</v>
+      </c>
+      <c r="AH19">
+        <v>32</v>
+      </c>
+      <c r="AI19">
+        <v>130</v>
+      </c>
+      <c r="AJ19">
+        <v>40</v>
+      </c>
+      <c r="AK19">
+        <v>40</v>
+      </c>
+      <c r="AL19">
+        <v>80</v>
+      </c>
+      <c r="AM19">
+        <v>280</v>
+      </c>
+      <c r="AN19">
+        <v>42</v>
+      </c>
+      <c r="AO19">
+        <v>140</v>
+      </c>
+      <c r="AP19">
+        <v>7.2</v>
+      </c>
+      <c r="AQ19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR19">
+        <v>4.7</v>
+      </c>
+      <c r="AS19">
+        <v>5.2</v>
+      </c>
+      <c r="AT19">
+        <v>5.9</v>
+      </c>
+      <c r="AU19">
+        <v>6.4</v>
+      </c>
+      <c r="AV19">
+        <v>16</v>
+      </c>
+      <c r="AW19">
+        <v>5.1</v>
+      </c>
+      <c r="AX19">
+        <v>10</v>
+      </c>
+      <c r="AY19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ19">
+        <v>4.6</v>
+      </c>
+      <c r="BA19">
+        <v>5.2</v>
+      </c>
+      <c r="BB19">
+        <v>4.8</v>
+      </c>
+      <c r="BC19">
+        <v>4.8</v>
+      </c>
+      <c r="BD19">
+        <v>5.1</v>
+      </c>
+      <c r="BE19">
+        <v>5.3</v>
+      </c>
+      <c r="BF19">
+        <v>4.8</v>
+      </c>
+      <c r="BG19">
+        <v>5.2</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.65</v>
+      </c>
+      <c r="BJ19">
+        <v>17</v>
+      </c>
+      <c r="BK19">
+        <v>1.51</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.65</v>
+      </c>
+      <c r="BN19">
+        <v>6.8</v>
+      </c>
+      <c r="BO19">
+        <v>3.3</v>
+      </c>
+      <c r="BP19">
+        <v>30</v>
+      </c>
+      <c r="BQ19">
+        <v>1.57</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
         <v>1.62</v>
       </c>
-      <c r="U19">
-        <v>2.44</v>
-      </c>
-      <c r="V19">
-        <v>1.46</v>
-      </c>
-      <c r="W19">
-        <v>1.71</v>
-      </c>
-      <c r="X19">
-        <v>24</v>
-      </c>
-      <c r="Y19">
-        <v>16</v>
-      </c>
-      <c r="Z19">
-        <v>27</v>
-      </c>
-      <c r="AA19">
-        <v>55</v>
-      </c>
-      <c r="AB19">
-        <v>13</v>
-      </c>
-      <c r="AC19">
-        <v>9.6</v>
-      </c>
-      <c r="AD19">
-        <v>16</v>
-      </c>
-      <c r="AE19">
-        <v>36</v>
-      </c>
-      <c r="AF19">
-        <v>17</v>
-      </c>
-      <c r="AG19">
-        <v>13.5</v>
-      </c>
-      <c r="AH19">
-        <v>16</v>
-      </c>
-      <c r="AI19">
-        <v>42</v>
-      </c>
-      <c r="AJ19">
-        <v>36</v>
-      </c>
-      <c r="AK19">
-        <v>26</v>
-      </c>
-      <c r="AL19">
-        <v>36</v>
-      </c>
-      <c r="AM19">
-        <v>75</v>
-      </c>
-      <c r="AN19">
-        <v>16.5</v>
-      </c>
-      <c r="AO19">
-        <v>24</v>
-      </c>
-      <c r="AP19">
-        <v>18</v>
-      </c>
-      <c r="AQ19">
-        <v>13.5</v>
-      </c>
-      <c r="AR19">
-        <v>21</v>
-      </c>
-      <c r="AS19">
-        <v>27</v>
-      </c>
-      <c r="AT19">
-        <v>12</v>
-      </c>
-      <c r="AU19">
-        <v>8</v>
-      </c>
-      <c r="AV19">
-        <v>12</v>
-      </c>
-      <c r="AW19">
-        <v>19.5</v>
-      </c>
-      <c r="AX19">
-        <v>15</v>
-      </c>
-      <c r="AY19">
-        <v>10.5</v>
-      </c>
-      <c r="AZ19">
-        <v>14</v>
-      </c>
-      <c r="BA19">
-        <v>22</v>
-      </c>
-      <c r="BB19">
-        <v>21</v>
-      </c>
-      <c r="BC19">
-        <v>20</v>
-      </c>
-      <c r="BD19">
-        <v>21</v>
-      </c>
-      <c r="BE19">
-        <v>32</v>
-      </c>
-      <c r="BF19">
-        <v>12.5</v>
-      </c>
-      <c r="BG19">
-        <v>20</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.9</v>
-      </c>
-      <c r="BJ19">
-        <v>12.5</v>
-      </c>
-      <c r="BK19">
-        <v>1.65</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.9</v>
-      </c>
-      <c r="BN19">
-        <v>7.8</v>
-      </c>
-      <c r="BO19">
-        <v>3.6</v>
-      </c>
-      <c r="BP19">
-        <v>23</v>
-      </c>
-      <c r="BQ19">
-        <v>1.76</v>
-      </c>
-      <c r="BR19">
-        <v>38</v>
-      </c>
-      <c r="BS19">
-        <v>1.81</v>
-      </c>
       <c r="BT19">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU19">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="BX19">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="BZ19">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="CB19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5398,232 +5404,232 @@
         <v>117</v>
       </c>
       <c r="E20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F20">
-        <v>2.96</v>
+        <v>2.34</v>
       </c>
       <c r="G20">
+        <v>2.4</v>
+      </c>
+      <c r="H20">
         <v>3.05</v>
       </c>
-      <c r="H20">
-        <v>2.34</v>
-      </c>
       <c r="I20">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="J20">
+        <v>3.75</v>
+      </c>
+      <c r="K20">
         <v>4</v>
       </c>
-      <c r="K20">
-        <v>4.2</v>
-      </c>
       <c r="L20">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="O20">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="P20">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q20">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="R20">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="S20">
-        <v>2.46</v>
+        <v>2.82</v>
       </c>
       <c r="T20">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="U20">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
+        <v>1.46</v>
+      </c>
+      <c r="W20">
         <v>1.71</v>
       </c>
-      <c r="W20">
-        <v>1.48</v>
-      </c>
       <c r="X20">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Y20">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z20">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AA20">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AB20">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AC20">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD20">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE20">
+        <v>36</v>
+      </c>
+      <c r="AF20">
+        <v>17</v>
+      </c>
+      <c r="AG20">
+        <v>13.5</v>
+      </c>
+      <c r="AH20">
+        <v>16</v>
+      </c>
+      <c r="AI20">
+        <v>42</v>
+      </c>
+      <c r="AJ20">
+        <v>36</v>
+      </c>
+      <c r="AK20">
         <v>26</v>
       </c>
-      <c r="AF20">
-        <v>26</v>
-      </c>
-      <c r="AG20">
-        <v>14</v>
-      </c>
-      <c r="AH20">
-        <v>15</v>
-      </c>
-      <c r="AI20">
-        <v>30</v>
-      </c>
-      <c r="AJ20">
-        <v>60</v>
-      </c>
-      <c r="AK20">
-        <v>34</v>
-      </c>
       <c r="AL20">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM20">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO20">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AP20">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ20">
         <v>13.5</v>
       </c>
       <c r="AR20">
+        <v>21</v>
+      </c>
+      <c r="AS20">
+        <v>27</v>
+      </c>
+      <c r="AT20">
+        <v>11.5</v>
+      </c>
+      <c r="AU20">
+        <v>8</v>
+      </c>
+      <c r="AV20">
+        <v>12</v>
+      </c>
+      <c r="AW20">
+        <v>19.5</v>
+      </c>
+      <c r="AX20">
+        <v>15</v>
+      </c>
+      <c r="AY20">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20">
         <v>14</v>
       </c>
-      <c r="AS20">
+      <c r="BA20">
+        <v>22</v>
+      </c>
+      <c r="BB20">
         <v>21</v>
       </c>
-      <c r="AT20">
-        <v>15.5</v>
-      </c>
-      <c r="AU20">
-        <v>8.6</v>
-      </c>
-      <c r="AV20">
-        <v>10.5</v>
-      </c>
-      <c r="AW20">
-        <v>18.5</v>
-      </c>
-      <c r="AX20">
+      <c r="BC20">
         <v>20</v>
       </c>
-      <c r="AY20">
-        <v>11.5</v>
-      </c>
-      <c r="AZ20">
-        <v>13</v>
-      </c>
-      <c r="BA20">
-        <v>18.5</v>
-      </c>
-      <c r="BB20">
-        <v>26</v>
-      </c>
-      <c r="BC20">
-        <v>18</v>
-      </c>
       <c r="BD20">
+        <v>21</v>
+      </c>
+      <c r="BE20">
+        <v>32</v>
+      </c>
+      <c r="BF20">
+        <v>12.5</v>
+      </c>
+      <c r="BG20">
         <v>20</v>
       </c>
-      <c r="BE20">
-        <v>28</v>
-      </c>
-      <c r="BF20">
-        <v>15</v>
-      </c>
-      <c r="BG20">
-        <v>11</v>
-      </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK20">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO20">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="CB20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5640,232 +5646,232 @@
         <v>118</v>
       </c>
       <c r="E21" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F21">
-        <v>2.26</v>
+        <v>2.96</v>
       </c>
       <c r="G21">
+        <v>3.1</v>
+      </c>
+      <c r="H21">
         <v>2.32</v>
       </c>
-      <c r="H21">
-        <v>3.3</v>
-      </c>
       <c r="I21">
-        <v>3.45</v>
+        <v>2.4</v>
       </c>
       <c r="J21">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K21">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="L21">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="M21">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N21">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="O21">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="P21">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="Q21">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="R21">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="S21">
-        <v>3.15</v>
+        <v>2.46</v>
       </c>
       <c r="T21">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="U21">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="W21">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="X21">
+        <v>30</v>
+      </c>
+      <c r="Y21">
+        <v>18</v>
+      </c>
+      <c r="Z21">
+        <v>22</v>
+      </c>
+      <c r="AA21">
+        <v>34</v>
+      </c>
+      <c r="AB21">
+        <v>23</v>
+      </c>
+      <c r="AC21">
+        <v>10.5</v>
+      </c>
+      <c r="AD21">
+        <v>12</v>
+      </c>
+      <c r="AE21">
+        <v>26</v>
+      </c>
+      <c r="AF21">
+        <v>26</v>
+      </c>
+      <c r="AG21">
+        <v>14</v>
+      </c>
+      <c r="AH21">
+        <v>15.5</v>
+      </c>
+      <c r="AI21">
+        <v>30</v>
+      </c>
+      <c r="AJ21">
+        <v>60</v>
+      </c>
+      <c r="AK21">
+        <v>34</v>
+      </c>
+      <c r="AL21">
+        <v>38</v>
+      </c>
+      <c r="AM21">
+        <v>270</v>
+      </c>
+      <c r="AN21">
+        <v>21</v>
+      </c>
+      <c r="AO21">
+        <v>14</v>
+      </c>
+      <c r="AP21">
+        <v>18</v>
+      </c>
+      <c r="AQ21">
+        <v>13.5</v>
+      </c>
+      <c r="AR21">
+        <v>14</v>
+      </c>
+      <c r="AS21">
+        <v>21</v>
+      </c>
+      <c r="AT21">
+        <v>15.5</v>
+      </c>
+      <c r="AU21">
+        <v>8.6</v>
+      </c>
+      <c r="AV21">
+        <v>10.5</v>
+      </c>
+      <c r="AW21">
+        <v>18.5</v>
+      </c>
+      <c r="AX21">
         <v>20</v>
       </c>
-      <c r="Y21">
-        <v>15</v>
-      </c>
-      <c r="Z21">
-        <v>30</v>
-      </c>
-      <c r="AA21">
-        <v>520</v>
-      </c>
-      <c r="AB21">
-        <v>12.5</v>
-      </c>
-      <c r="AC21">
-        <v>8.6</v>
-      </c>
-      <c r="AD21">
-        <v>14.5</v>
-      </c>
-      <c r="AE21">
-        <v>44</v>
-      </c>
-      <c r="AF21">
-        <v>17.5</v>
-      </c>
-      <c r="AG21">
+      <c r="AY21">
         <v>12</v>
-      </c>
-      <c r="AH21">
-        <v>16.5</v>
-      </c>
-      <c r="AI21">
-        <v>55</v>
-      </c>
-      <c r="AJ21">
-        <v>38</v>
-      </c>
-      <c r="AK21">
-        <v>27</v>
-      </c>
-      <c r="AL21">
-        <v>40</v>
-      </c>
-      <c r="AM21">
-        <v>95</v>
-      </c>
-      <c r="AN21">
-        <v>19.5</v>
-      </c>
-      <c r="AO21">
-        <v>55</v>
-      </c>
-      <c r="AP21">
-        <v>15</v>
-      </c>
-      <c r="AQ21">
-        <v>12.5</v>
-      </c>
-      <c r="AR21">
-        <v>21</v>
-      </c>
-      <c r="AS21">
-        <v>29</v>
-      </c>
-      <c r="AT21">
-        <v>10</v>
-      </c>
-      <c r="AU21">
-        <v>7.6</v>
-      </c>
-      <c r="AV21">
-        <v>12.5</v>
-      </c>
-      <c r="AW21">
-        <v>22</v>
-      </c>
-      <c r="AX21">
-        <v>13.5</v>
-      </c>
-      <c r="AY21">
-        <v>8.800000000000001</v>
       </c>
       <c r="AZ21">
         <v>13</v>
       </c>
       <c r="BA21">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="BB21">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BC21">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD21">
         <v>21</v>
       </c>
       <c r="BE21">
+        <v>28</v>
+      </c>
+      <c r="BF21">
+        <v>15</v>
+      </c>
+      <c r="BG21">
+        <v>11</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.99</v>
+      </c>
+      <c r="BJ21">
+        <v>12.5</v>
+      </c>
+      <c r="BK21">
+        <v>5.3</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.96</v>
+      </c>
+      <c r="BN21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO21">
+        <v>4.3</v>
+      </c>
+      <c r="BP21">
+        <v>30</v>
+      </c>
+      <c r="BQ21">
+        <v>1.87</v>
+      </c>
+      <c r="BR21">
+        <v>38</v>
+      </c>
+      <c r="BS21">
+        <v>1.9</v>
+      </c>
+      <c r="BT21">
+        <v>8</v>
+      </c>
+      <c r="BU21">
+        <v>3.8</v>
+      </c>
+      <c r="BV21">
+        <v>23</v>
+      </c>
+      <c r="BW21">
+        <v>1.84</v>
+      </c>
+      <c r="BX21">
         <v>34</v>
       </c>
-      <c r="BF21">
-        <v>14.5</v>
-      </c>
-      <c r="BG21">
-        <v>20</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>1.04</v>
-      </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
-      <c r="BK21">
-        <v>1.04</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>1.04</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>1.04</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>1.04</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>1.04</v>
-      </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
-      <c r="BU21">
-        <v>1.04</v>
-      </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
-      <c r="BW21">
-        <v>1.04</v>
-      </c>
-      <c r="BX21">
-        <v>1000</v>
-      </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="CB21" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5882,232 +5888,232 @@
         <v>119</v>
       </c>
       <c r="E22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F22">
-        <v>2.96</v>
+        <v>2.26</v>
       </c>
       <c r="G22">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="H22">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="I22">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="J22">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K22">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L22">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="M22">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N22">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="O22">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="P22">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q22">
+        <v>1.84</v>
+      </c>
+      <c r="R22">
+        <v>1.43</v>
+      </c>
+      <c r="S22">
+        <v>3.15</v>
+      </c>
+      <c r="T22">
+        <v>1.69</v>
+      </c>
+      <c r="U22">
+        <v>2.32</v>
+      </c>
+      <c r="V22">
         <v>1.41</v>
       </c>
-      <c r="R22">
-        <v>1.91</v>
-      </c>
-      <c r="S22">
-        <v>2.02</v>
-      </c>
-      <c r="T22">
-        <v>1.42</v>
-      </c>
-      <c r="U22">
-        <v>3.2</v>
-      </c>
-      <c r="V22">
-        <v>1.74</v>
-      </c>
       <c r="W22">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="X22">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="Y22">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Z22">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AA22">
-        <v>36</v>
+        <v>520</v>
       </c>
       <c r="AB22">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="AC22">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD22">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE22">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AF22">
-        <v>44</v>
+        <v>17.5</v>
       </c>
       <c r="AG22">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH22">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI22">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AJ22">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AK22">
         <v>27</v>
       </c>
       <c r="AL22">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM22">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AN22">
+        <v>19.5</v>
+      </c>
+      <c r="AO22">
+        <v>55</v>
+      </c>
+      <c r="AP22">
+        <v>15</v>
+      </c>
+      <c r="AQ22">
+        <v>12.5</v>
+      </c>
+      <c r="AR22">
+        <v>21</v>
+      </c>
+      <c r="AS22">
+        <v>29</v>
+      </c>
+      <c r="AT22">
+        <v>10</v>
+      </c>
+      <c r="AU22">
+        <v>7.6</v>
+      </c>
+      <c r="AV22">
+        <v>12.5</v>
+      </c>
+      <c r="AW22">
+        <v>22</v>
+      </c>
+      <c r="AX22">
+        <v>13.5</v>
+      </c>
+      <c r="AY22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ22">
         <v>13</v>
       </c>
-      <c r="AO22">
-        <v>9</v>
-      </c>
-      <c r="AP22">
-        <v>30</v>
-      </c>
-      <c r="AQ22">
-        <v>18.5</v>
-      </c>
-      <c r="AR22">
-        <v>19.5</v>
-      </c>
-      <c r="AS22">
-        <v>30</v>
-      </c>
-      <c r="AT22">
-        <v>22</v>
-      </c>
-      <c r="AU22">
-        <v>10</v>
-      </c>
-      <c r="AV22">
-        <v>11</v>
-      </c>
-      <c r="AW22">
-        <v>18</v>
-      </c>
-      <c r="AX22">
-        <v>26</v>
-      </c>
-      <c r="AY22">
-        <v>11.5</v>
-      </c>
-      <c r="AZ22">
-        <v>12.5</v>
-      </c>
       <c r="BA22">
+        <v>25</v>
+      </c>
+      <c r="BB22">
         <v>21</v>
       </c>
-      <c r="BB22">
-        <v>42</v>
-      </c>
       <c r="BC22">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD22">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE22">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF22">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BG22">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BH22">
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK22">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO22">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ22">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS22">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU22">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW22">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY22">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA22">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="CB22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6124,169 +6130,169 @@
         <v>120</v>
       </c>
       <c r="E23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F23">
-        <v>1.67</v>
+        <v>2.96</v>
       </c>
       <c r="G23">
-        <v>1.69</v>
+        <v>3.05</v>
       </c>
       <c r="H23">
-        <v>5.2</v>
+        <v>2.28</v>
       </c>
       <c r="I23">
-        <v>5.5</v>
+        <v>2.36</v>
       </c>
       <c r="J23">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K23">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L23">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="M23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N23">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="O23">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="P23">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="Q23">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="R23">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="S23">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="T23">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="U23">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="V23">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="W23">
-        <v>2.44</v>
+        <v>1.49</v>
       </c>
       <c r="X23">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="Y23">
+        <v>21</v>
+      </c>
+      <c r="Z23">
+        <v>22</v>
+      </c>
+      <c r="AA23">
+        <v>36</v>
+      </c>
+      <c r="AB23">
+        <v>34</v>
+      </c>
+      <c r="AC23">
+        <v>11.5</v>
+      </c>
+      <c r="AD23">
+        <v>12.5</v>
+      </c>
+      <c r="AE23">
+        <v>20</v>
+      </c>
+      <c r="AF23">
+        <v>30</v>
+      </c>
+      <c r="AG23">
+        <v>14.5</v>
+      </c>
+      <c r="AH23">
+        <v>13.5</v>
+      </c>
+      <c r="AI23">
+        <v>32</v>
+      </c>
+      <c r="AJ23">
+        <v>60</v>
+      </c>
+      <c r="AK23">
+        <v>27</v>
+      </c>
+      <c r="AL23">
+        <v>42</v>
+      </c>
+      <c r="AM23">
+        <v>46</v>
+      </c>
+      <c r="AN23">
+        <v>13</v>
+      </c>
+      <c r="AO23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AP23">
+        <v>30</v>
+      </c>
+      <c r="AQ23">
+        <v>18.5</v>
+      </c>
+      <c r="AR23">
+        <v>15</v>
+      </c>
+      <c r="AS23">
+        <v>21</v>
+      </c>
+      <c r="AT23">
+        <v>22</v>
+      </c>
+      <c r="AU23">
+        <v>10</v>
+      </c>
+      <c r="AV23">
+        <v>11</v>
+      </c>
+      <c r="AW23">
+        <v>18</v>
+      </c>
+      <c r="AX23">
         <v>26</v>
       </c>
-      <c r="Z23">
-        <v>48</v>
-      </c>
-      <c r="AA23">
-        <v>1000</v>
-      </c>
-      <c r="AB23">
+      <c r="AY23">
         <v>12.5</v>
       </c>
-      <c r="AC23">
-        <v>10.5</v>
-      </c>
-      <c r="AD23">
-        <v>22</v>
-      </c>
-      <c r="AE23">
-        <v>65</v>
-      </c>
-      <c r="AF23">
+      <c r="AZ23">
         <v>12.5</v>
       </c>
-      <c r="AG23">
-        <v>10.5</v>
-      </c>
-      <c r="AH23">
-        <v>19</v>
-      </c>
-      <c r="AI23">
-        <v>60</v>
-      </c>
-      <c r="AJ23">
-        <v>18</v>
-      </c>
-      <c r="AK23">
-        <v>15.5</v>
-      </c>
-      <c r="AL23">
-        <v>29</v>
-      </c>
-      <c r="AM23">
-        <v>1000</v>
-      </c>
-      <c r="AN23">
-        <v>7</v>
-      </c>
-      <c r="AO23">
-        <v>55</v>
-      </c>
-      <c r="AP23">
+      <c r="BA23">
         <v>21</v>
       </c>
-      <c r="AQ23">
-        <v>21</v>
-      </c>
-      <c r="AR23">
-        <v>26</v>
-      </c>
-      <c r="AS23">
+      <c r="BB23">
         <v>42</v>
       </c>
-      <c r="AT23">
-        <v>11</v>
-      </c>
-      <c r="AU23">
-        <v>9.6</v>
-      </c>
-      <c r="AV23">
-        <v>18</v>
-      </c>
-      <c r="AW23">
-        <v>29</v>
-      </c>
-      <c r="AX23">
-        <v>10.5</v>
-      </c>
-      <c r="AY23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ23">
-        <v>15.5</v>
-      </c>
-      <c r="BA23">
-        <v>28</v>
-      </c>
-      <c r="BB23">
-        <v>15</v>
-      </c>
       <c r="BC23">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD23">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BE23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF23">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BG23">
-        <v>27</v>
+        <v>8.4</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6349,7 +6355,7 @@
         <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6366,232 +6372,474 @@
         <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F24">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="G24">
-        <v>2.06</v>
+        <v>1.69</v>
       </c>
       <c r="H24">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="I24">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="J24">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K24">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L24">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M24">
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="O24">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P24">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="Q24">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="R24">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="S24">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="T24">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="U24">
-        <v>2.86</v>
+        <v>2.34</v>
       </c>
       <c r="V24">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="W24">
-        <v>1.94</v>
+        <v>2.44</v>
       </c>
       <c r="X24">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y24">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Z24">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AA24">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AC24">
         <v>10.5</v>
       </c>
       <c r="AD24">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE24">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AF24">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG24">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AI24">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AJ24">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AK24">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL24">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AM24">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AO24">
+        <v>55</v>
+      </c>
+      <c r="AP24">
         <v>21</v>
       </c>
-      <c r="AP24">
+      <c r="AQ24">
         <v>20</v>
       </c>
-      <c r="AQ24">
-        <v>19.5</v>
-      </c>
       <c r="AR24">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AS24">
         <v>42</v>
       </c>
       <c r="AT24">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AU24">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV24">
+        <v>18</v>
+      </c>
+      <c r="AW24">
+        <v>29</v>
+      </c>
+      <c r="AX24">
+        <v>10.5</v>
+      </c>
+      <c r="AY24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24">
+        <v>15.5</v>
+      </c>
+      <c r="BA24">
+        <v>28</v>
+      </c>
+      <c r="BB24">
+        <v>15</v>
+      </c>
+      <c r="BC24">
         <v>13.5</v>
       </c>
-      <c r="AW24">
-        <v>21</v>
-      </c>
-      <c r="AX24">
-        <v>15</v>
-      </c>
-      <c r="AY24">
-        <v>10</v>
-      </c>
-      <c r="AZ24">
-        <v>12.5</v>
-      </c>
-      <c r="BA24">
-        <v>22</v>
-      </c>
-      <c r="BB24">
+      <c r="BD24">
         <v>18</v>
-      </c>
-      <c r="BC24">
-        <v>16</v>
-      </c>
-      <c r="BD24">
-        <v>21</v>
       </c>
       <c r="BE24">
         <v>34</v>
       </c>
       <c r="BF24">
+        <v>6.2</v>
+      </c>
+      <c r="BG24">
+        <v>27</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.04</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.04</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.04</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.04</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.04</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.04</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.04</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.04</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.04</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>1.04</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25">
+        <v>2.02</v>
+      </c>
+      <c r="G25">
+        <v>2.06</v>
+      </c>
+      <c r="H25">
+        <v>3.5</v>
+      </c>
+      <c r="I25">
+        <v>3.7</v>
+      </c>
+      <c r="J25">
+        <v>4.2</v>
+      </c>
+      <c r="K25">
+        <v>4.4</v>
+      </c>
+      <c r="L25">
+        <v>1.25</v>
+      </c>
+      <c r="M25">
+        <v>1.03</v>
+      </c>
+      <c r="N25">
+        <v>6.4</v>
+      </c>
+      <c r="O25">
+        <v>1.17</v>
+      </c>
+      <c r="P25">
+        <v>2.88</v>
+      </c>
+      <c r="Q25">
+        <v>1.5</v>
+      </c>
+      <c r="R25">
+        <v>1.76</v>
+      </c>
+      <c r="S25">
+        <v>2.24</v>
+      </c>
+      <c r="T25">
+        <v>1.49</v>
+      </c>
+      <c r="U25">
+        <v>2.86</v>
+      </c>
+      <c r="V25">
+        <v>1.37</v>
+      </c>
+      <c r="W25">
+        <v>1.94</v>
+      </c>
+      <c r="X25">
+        <v>29</v>
+      </c>
+      <c r="Y25">
+        <v>23</v>
+      </c>
+      <c r="Z25">
+        <v>32</v>
+      </c>
+      <c r="AA25">
+        <v>80</v>
+      </c>
+      <c r="AB25">
+        <v>16</v>
+      </c>
+      <c r="AC25">
+        <v>10.5</v>
+      </c>
+      <c r="AD25">
+        <v>16</v>
+      </c>
+      <c r="AE25">
+        <v>34</v>
+      </c>
+      <c r="AF25">
+        <v>17.5</v>
+      </c>
+      <c r="AG25">
+        <v>11.5</v>
+      </c>
+      <c r="AH25">
+        <v>14.5</v>
+      </c>
+      <c r="AI25">
+        <v>34</v>
+      </c>
+      <c r="AJ25">
+        <v>28</v>
+      </c>
+      <c r="AK25">
+        <v>18</v>
+      </c>
+      <c r="AL25">
+        <v>24</v>
+      </c>
+      <c r="AM25">
+        <v>190</v>
+      </c>
+      <c r="AN25">
+        <v>8.6</v>
+      </c>
+      <c r="AO25">
+        <v>21</v>
+      </c>
+      <c r="AP25">
+        <v>20</v>
+      </c>
+      <c r="AQ25">
+        <v>19.5</v>
+      </c>
+      <c r="AR25">
+        <v>22</v>
+      </c>
+      <c r="AS25">
+        <v>42</v>
+      </c>
+      <c r="AT25">
+        <v>14</v>
+      </c>
+      <c r="AU25">
+        <v>9.4</v>
+      </c>
+      <c r="AV25">
+        <v>13.5</v>
+      </c>
+      <c r="AW25">
+        <v>21</v>
+      </c>
+      <c r="AX25">
+        <v>15</v>
+      </c>
+      <c r="AY25">
+        <v>10</v>
+      </c>
+      <c r="AZ25">
+        <v>12.5</v>
+      </c>
+      <c r="BA25">
+        <v>22</v>
+      </c>
+      <c r="BB25">
+        <v>18</v>
+      </c>
+      <c r="BC25">
+        <v>16</v>
+      </c>
+      <c r="BD25">
+        <v>21</v>
+      </c>
+      <c r="BE25">
+        <v>34</v>
+      </c>
+      <c r="BF25">
         <v>7.8</v>
       </c>
-      <c r="BG24">
+      <c r="BG25">
         <v>18.5</v>
       </c>
-      <c r="BH24">
-        <v>1000</v>
-      </c>
-      <c r="BI24">
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
         <v>3.25</v>
       </c>
-      <c r="BJ24">
+      <c r="BJ25">
         <v>12.5</v>
       </c>
-      <c r="BK24">
+      <c r="BK25">
         <v>5.3</v>
       </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
         <v>1.99</v>
       </c>
-      <c r="BN24">
+      <c r="BN25">
         <v>7.8</v>
       </c>
-      <c r="BO24">
+      <c r="BO25">
         <v>3.6</v>
       </c>
-      <c r="BP24">
+      <c r="BP25">
         <v>19</v>
       </c>
-      <c r="BQ24">
+      <c r="BQ25">
         <v>1.83</v>
       </c>
-      <c r="BR24">
+      <c r="BR25">
         <v>30</v>
       </c>
-      <c r="BS24">
+      <c r="BS25">
         <v>1.9</v>
       </c>
-      <c r="BT24">
+      <c r="BT25">
         <v>10.5</v>
       </c>
-      <c r="BU24">
+      <c r="BU25">
         <v>4.8</v>
       </c>
-      <c r="BV24">
+      <c r="BV25">
         <v>34</v>
       </c>
-      <c r="BW24">
+      <c r="BW25">
         <v>1.91</v>
       </c>
-      <c r="BX24">
+      <c r="BX25">
         <v>40</v>
       </c>
-      <c r="BY24">
+      <c r="BY25">
         <v>1.93</v>
       </c>
-      <c r="BZ24">
+      <c r="BZ25">
         <v>19</v>
       </c>
-      <c r="CA24">
+      <c r="CA25">
         <v>1.83</v>
       </c>
-      <c r="CB24" t="s">
-        <v>145</v>
+      <c r="CB25" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -457,7 +457,7 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-18 04:47:25</t>
+    <t>2026-08-18 06:55:43</t>
   </si>
 </sst>
 </file>
@@ -1051,226 +1051,226 @@
         <v>123</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
         <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
         <v>1.5</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P2">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q2">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T2">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="U2">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X2">
+        <v>11</v>
+      </c>
+      <c r="Y2">
         <v>12.5</v>
       </c>
-      <c r="Y2">
-        <v>14</v>
-      </c>
       <c r="Z2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
         <v>23</v>
       </c>
       <c r="AI2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AK2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM2">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AO2">
         <v>80</v>
       </c>
       <c r="AP2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR2">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="AS2">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AT2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>4.7</v>
+        <v>46</v>
       </c>
       <c r="AX2">
+        <v>12</v>
+      </c>
+      <c r="AY2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ2">
+        <v>17</v>
+      </c>
+      <c r="BA2">
+        <v>55</v>
+      </c>
+      <c r="BB2">
+        <v>26</v>
+      </c>
+      <c r="BC2">
+        <v>24</v>
+      </c>
+      <c r="BD2">
+        <v>40</v>
+      </c>
+      <c r="BE2">
         <v>11.5</v>
       </c>
-      <c r="AY2">
-        <v>9.6</v>
-      </c>
-      <c r="AZ2">
-        <v>16.5</v>
-      </c>
-      <c r="BA2">
-        <v>4.7</v>
-      </c>
-      <c r="BB2">
-        <v>4.4</v>
-      </c>
-      <c r="BC2">
-        <v>4.4</v>
-      </c>
-      <c r="BD2">
-        <v>4.6</v>
-      </c>
-      <c r="BE2">
-        <v>4.9</v>
-      </c>
       <c r="BF2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG2">
-        <v>4.7</v>
+        <v>55</v>
       </c>
       <c r="BH2">
         <v>3.3</v>
       </c>
       <c r="BI2">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BR2">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX2">
         <v>55</v>
       </c>
       <c r="BY2">
+        <v>5.7</v>
+      </c>
+      <c r="BZ2">
+        <v>42</v>
+      </c>
+      <c r="CA2">
         <v>5.6</v>
-      </c>
-      <c r="BZ2">
-        <v>40</v>
-      </c>
-      <c r="CA2">
-        <v>5.3</v>
       </c>
       <c r="CB2" t="s">
         <v>147</v>
@@ -1293,37 +1293,37 @@
         <v>124</v>
       </c>
       <c r="F3">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G3">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H3">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="I3">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="J3">
         <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L3">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O3">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q3">
         <v>2.66</v>
@@ -1338,67 +1338,67 @@
         <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V3">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="X3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AB3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
         <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
         <v>55</v>
       </c>
       <c r="AF3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
         <v>24</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AL3">
         <v>85</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN3">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AO3">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AP3">
         <v>8</v>
@@ -1407,73 +1407,73 @@
         <v>7.6</v>
       </c>
       <c r="AR3">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="AX3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ3">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>6.6</v>
+        <v>50</v>
       </c>
       <c r="BB3">
-        <v>6.4</v>
+        <v>46</v>
       </c>
       <c r="BC3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="BD3">
-        <v>6.6</v>
+        <v>46</v>
       </c>
       <c r="BE3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BF3">
-        <v>6.4</v>
+        <v>44</v>
       </c>
       <c r="BG3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH3">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="BI3">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3">
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="BN3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO3">
         <v>5</v>
@@ -1482,37 +1482,37 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BT3">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU3">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB3" t="s">
         <v>147</v>
@@ -1535,16 +1535,16 @@
         <v>125</v>
       </c>
       <c r="F4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G4">
         <v>3.25</v>
       </c>
       <c r="H4">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I4">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J4">
         <v>3.15</v>
@@ -1553,37 +1553,37 @@
         <v>3.25</v>
       </c>
       <c r="L4">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M4">
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P4">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="R4">
         <v>1.21</v>
       </c>
       <c r="S4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W4">
         <v>1.44</v>
@@ -1592,13 +1592,13 @@
         <v>9.6</v>
       </c>
       <c r="Y4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA4">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB4">
         <v>9.6</v>
@@ -1610,10 +1610,10 @@
         <v>13</v>
       </c>
       <c r="AE4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
@@ -1640,19 +1640,19 @@
         <v>60</v>
       </c>
       <c r="AO4">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP4">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AR4">
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AT4">
         <v>8.199999999999999</v>
@@ -1661,19 +1661,19 @@
         <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW4">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="AX4">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AY4">
         <v>13</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA4">
         <v>50</v>
@@ -1688,19 +1688,19 @@
         <v>46</v>
       </c>
       <c r="BE4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG4">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BH4">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="BI4">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="BJ4">
         <v>11</v>
@@ -1712,7 +1712,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BN4">
         <v>6.4</v>
@@ -1724,37 +1724,37 @@
         <v>30</v>
       </c>
       <c r="BQ4">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BR4">
         <v>50</v>
       </c>
       <c r="BS4">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU4">
         <v>4.7</v>
       </c>
       <c r="BV4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW4">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="CB4" t="s">
         <v>147</v>
@@ -1783,7 +1783,7 @@
         <v>2.5</v>
       </c>
       <c r="H5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I5">
         <v>3.85</v>
@@ -1810,7 +1810,7 @@
         <v>1.48</v>
       </c>
       <c r="Q5">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R5">
         <v>1.17</v>
@@ -1834,7 +1834,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Y5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z5">
         <v>34</v>
@@ -1888,16 +1888,16 @@
         <v>6.2</v>
       </c>
       <c r="AQ5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR5">
         <v>21</v>
       </c>
       <c r="AS5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
         <v>6.2</v>
@@ -1906,7 +1906,7 @@
         <v>15</v>
       </c>
       <c r="AW5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX5">
         <v>12</v>
@@ -1918,7 +1918,7 @@
         <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB5">
         <v>27</v>
@@ -1927,16 +1927,16 @@
         <v>26</v>
       </c>
       <c r="BD5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE5">
+        <v>8</v>
+      </c>
+      <c r="BF5">
+        <v>7</v>
+      </c>
+      <c r="BG5">
         <v>7.6</v>
-      </c>
-      <c r="BF5">
-        <v>6.8</v>
-      </c>
-      <c r="BG5">
-        <v>7.4</v>
       </c>
       <c r="BH5">
         <v>2.82</v>
@@ -1945,7 +1945,7 @@
         <v>2.24</v>
       </c>
       <c r="BJ5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK5">
         <v>9.199999999999999</v>
@@ -1954,7 +1954,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN5">
         <v>5.8</v>
@@ -1972,7 +1972,7 @@
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT5">
         <v>7.4</v>
@@ -1984,13 +1984,13 @@
         <v>42</v>
       </c>
       <c r="BW5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
@@ -2064,10 +2064,10 @@
         <v>1.67</v>
       </c>
       <c r="U6">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W6">
         <v>2.92</v>
@@ -2088,10 +2088,10 @@
         <v>13.5</v>
       </c>
       <c r="AC6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE6">
         <v>85</v>
@@ -2124,7 +2124,7 @@
         <v>5</v>
       </c>
       <c r="AO6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP6">
         <v>20</v>
@@ -2264,10 +2264,10 @@
         <v>1.04</v>
       </c>
       <c r="G7">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="H7">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I7">
         <v>990</v>
@@ -2291,7 +2291,7 @@
         <v>1.2</v>
       </c>
       <c r="P7">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
         <v>1.2</v>
@@ -2300,7 +2300,7 @@
         <v>1.13</v>
       </c>
       <c r="S7">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2312,7 +2312,7 @@
         <v>1.06</v>
       </c>
       <c r="W7">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2503,25 +2503,25 @@
         <v>129</v>
       </c>
       <c r="F8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H8">
         <v>12</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J8">
+        <v>5.8</v>
+      </c>
+      <c r="K8">
         <v>5.9</v>
       </c>
-      <c r="K8">
-        <v>6.2</v>
-      </c>
       <c r="L8">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M8">
         <v>1.05</v>
@@ -2536,13 +2536,13 @@
         <v>2.2</v>
       </c>
       <c r="Q8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R8">
         <v>1.46</v>
       </c>
       <c r="S8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T8">
         <v>2.3</v>
@@ -2554,19 +2554,19 @@
         <v>1.08</v>
       </c>
       <c r="W8">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="X8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z8">
         <v>130</v>
       </c>
       <c r="AA8">
-        <v>670</v>
+        <v>620</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -2584,7 +2584,7 @@
         <v>7.4</v>
       </c>
       <c r="AG8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH8">
         <v>36</v>
@@ -2608,7 +2608,7 @@
         <v>5.5</v>
       </c>
       <c r="AO8">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AP8">
         <v>16.5</v>
@@ -2617,7 +2617,7 @@
         <v>30</v>
       </c>
       <c r="AR8">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AS8">
         <v>55</v>
@@ -2629,7 +2629,7 @@
         <v>12.5</v>
       </c>
       <c r="AV8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AW8">
         <v>48</v>
@@ -2644,13 +2644,13 @@
         <v>32</v>
       </c>
       <c r="BA8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD8">
         <v>40</v>
@@ -2662,7 +2662,7 @@
         <v>5.3</v>
       </c>
       <c r="BG8">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="BH8">
         <v>3.85</v>
@@ -2775,10 +2775,10 @@
         <v>1.39</v>
       </c>
       <c r="P9">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R9">
         <v>1.28</v>
@@ -2787,7 +2787,7 @@
         <v>4</v>
       </c>
       <c r="T9">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U9">
         <v>1.94</v>
@@ -2796,7 +2796,7 @@
         <v>1.27</v>
       </c>
       <c r="W9">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X9">
         <v>14</v>
@@ -2823,7 +2823,7 @@
         <v>85</v>
       </c>
       <c r="AF9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG9">
         <v>11</v>
@@ -2847,22 +2847,22 @@
         <v>150</v>
       </c>
       <c r="AN9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AO9">
         <v>100</v>
       </c>
       <c r="AP9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ9">
         <v>12</v>
       </c>
       <c r="AR9">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS9">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT9">
         <v>7</v>
@@ -2874,7 +2874,7 @@
         <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX9">
         <v>10.5</v>
@@ -2886,7 +2886,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB9">
         <v>21</v>
@@ -2898,13 +2898,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF9">
         <v>16</v>
       </c>
       <c r="BG9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2987,40 +2987,40 @@
         <v>131</v>
       </c>
       <c r="F10">
+        <v>2.3</v>
+      </c>
+      <c r="G10">
         <v>2.4</v>
       </c>
-      <c r="G10">
-        <v>2.56</v>
-      </c>
       <c r="H10">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I10">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="J10">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N10">
         <v>2.56</v>
       </c>
       <c r="O10">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P10">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q10">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="R10">
         <v>1.18</v>
@@ -3029,16 +3029,16 @@
         <v>5.4</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U10">
         <v>1.64</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="X10">
         <v>10.5</v>
@@ -3053,10 +3053,10 @@
         <v>100</v>
       </c>
       <c r="AB10">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AC10">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10">
         <v>17.5</v>
@@ -3065,13 +3065,13 @@
         <v>75</v>
       </c>
       <c r="AF10">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH10">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AI10">
         <v>100</v>
@@ -3095,7 +3095,7 @@
         <v>110</v>
       </c>
       <c r="AP10">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ10">
         <v>8.6</v>
@@ -3104,55 +3104,55 @@
         <v>21</v>
       </c>
       <c r="AS10">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU10">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV10">
         <v>14</v>
       </c>
       <c r="AW10">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX10">
         <v>11.5</v>
       </c>
       <c r="AY10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ10">
         <v>20</v>
       </c>
       <c r="BA10">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB10">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC10">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="BD10">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE10">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10">
         <v>27</v>
       </c>
       <c r="BG10">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BJ10">
         <v>17</v>
@@ -3164,28 +3164,28 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BN10">
         <v>7</v>
       </c>
       <c r="BO10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP10">
         <v>30</v>
       </c>
       <c r="BQ10">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="BT10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU10">
         <v>4.4</v>
@@ -3200,13 +3200,13 @@
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CB10" t="s">
         <v>147</v>
@@ -3247,19 +3247,19 @@
         <v>3.6</v>
       </c>
       <c r="L11">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M11">
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O11">
         <v>1.48</v>
       </c>
       <c r="P11">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
         <v>2.46</v>
@@ -3343,10 +3343,10 @@
         <v>5.7</v>
       </c>
       <c r="AR11">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT11">
         <v>11.5</v>
@@ -3361,7 +3361,7 @@
         <v>21</v>
       </c>
       <c r="AX11">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="AY11">
         <v>20</v>
@@ -3471,7 +3471,7 @@
         <v>133</v>
       </c>
       <c r="F12">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -3480,13 +3480,13 @@
         <v>2.82</v>
       </c>
       <c r="I12">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J12">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K12">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3495,25 +3495,25 @@
         <v>1.09</v>
       </c>
       <c r="N12">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="P12">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="Q12">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S12">
         <v>4.1</v>
       </c>
       <c r="T12">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="U12">
         <v>1.98</v>
@@ -3531,16 +3531,16 @@
         <v>12</v>
       </c>
       <c r="Z12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB12">
         <v>12</v>
       </c>
       <c r="AC12">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD12">
         <v>16</v>
@@ -3552,7 +3552,7 @@
         <v>23</v>
       </c>
       <c r="AG12">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH12">
         <v>23</v>
@@ -3561,7 +3561,7 @@
         <v>65</v>
       </c>
       <c r="AJ12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK12">
         <v>46</v>
@@ -3576,121 +3576,121 @@
         <v>48</v>
       </c>
       <c r="AO12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR12">
+        <v>4.4</v>
+      </c>
+      <c r="AS12">
+        <v>5.2</v>
+      </c>
+      <c r="AT12">
         <v>8.6</v>
-      </c>
-      <c r="AR12">
-        <v>15.5</v>
-      </c>
-      <c r="AS12">
-        <v>4</v>
-      </c>
-      <c r="AT12">
-        <v>8.800000000000001</v>
       </c>
       <c r="AU12">
         <v>6.4</v>
       </c>
       <c r="AV12">
+        <v>11.5</v>
+      </c>
+      <c r="AW12">
+        <v>5</v>
+      </c>
+      <c r="AX12">
+        <v>16</v>
+      </c>
+      <c r="AY12">
         <v>11</v>
-      </c>
-      <c r="AW12">
-        <v>3.95</v>
-      </c>
-      <c r="AX12">
-        <v>16.5</v>
-      </c>
-      <c r="AY12">
-        <v>11.5</v>
       </c>
       <c r="AZ12">
         <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BB12">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BC12">
+        <v>5</v>
+      </c>
+      <c r="BD12">
+        <v>5.2</v>
+      </c>
+      <c r="BE12">
+        <v>5.5</v>
+      </c>
+      <c r="BF12">
+        <v>5.1</v>
+      </c>
+      <c r="BG12">
+        <v>5</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.74</v>
+      </c>
+      <c r="BJ12">
+        <v>14.5</v>
+      </c>
+      <c r="BK12">
+        <v>1.56</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.74</v>
+      </c>
+      <c r="BN12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO12">
         <v>3.95</v>
       </c>
-      <c r="BD12">
-        <v>4</v>
-      </c>
-      <c r="BE12">
-        <v>4.2</v>
-      </c>
-      <c r="BF12">
-        <v>3.95</v>
-      </c>
-      <c r="BG12">
-        <v>3.95</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.04</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.04</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.04</v>
-      </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="CB12" t="s">
         <v>147</v>
@@ -3731,7 +3731,7 @@
         <v>4</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M13">
         <v>1.09</v>
@@ -3743,13 +3743,13 @@
         <v>1.34</v>
       </c>
       <c r="P13">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q13">
         <v>2.12</v>
       </c>
       <c r="R13">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S13">
         <v>4.1</v>
@@ -3818,7 +3818,7 @@
         <v>13.5</v>
       </c>
       <c r="AO13">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AP13">
         <v>10</v>
@@ -3875,64 +3875,64 @@
         <v>6.4</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB13" t="s">
         <v>147</v>
@@ -3958,7 +3958,7 @@
         <v>2.4</v>
       </c>
       <c r="G14">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="H14">
         <v>2.58</v>
@@ -3967,7 +3967,7 @@
         <v>2.96</v>
       </c>
       <c r="J14">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="K14">
         <v>4.4</v>
@@ -3979,22 +3979,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.44</v>
+        <v>2.56</v>
       </c>
       <c r="O14">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P14">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="Q14">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="R14">
-        <v>1.08</v>
+        <v>1.46</v>
       </c>
       <c r="S14">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -4006,7 +4006,7 @@
         <v>1.51</v>
       </c>
       <c r="W14">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4197,22 +4197,22 @@
         <v>136</v>
       </c>
       <c r="F15">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G15">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="H15">
         <v>4.3</v>
       </c>
       <c r="I15">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J15">
-        <v>3.8</v>
+        <v>1.09</v>
       </c>
       <c r="K15">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L15">
         <v>1.27</v>
@@ -4221,7 +4221,7 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="O15">
         <v>1.25</v>
@@ -4230,7 +4230,7 @@
         <v>1.83</v>
       </c>
       <c r="Q15">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R15">
         <v>1.31</v>
@@ -4245,10 +4245,10 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W15">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4445,7 +4445,7 @@
         <v>110</v>
       </c>
       <c r="H16">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I16">
         <v>110</v>
@@ -4463,22 +4463,22 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="O16">
         <v>1.42</v>
       </c>
       <c r="P16">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
         <v>1.42</v>
       </c>
       <c r="R16">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S16">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4490,7 +4490,7 @@
         <v>1.01</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4681,22 +4681,22 @@
         <v>138</v>
       </c>
       <c r="F17">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G17">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H17">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I17">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="J17">
         <v>4.1</v>
       </c>
       <c r="K17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.24</v>
@@ -4723,13 +4723,13 @@
         <v>2.14</v>
       </c>
       <c r="T17">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U17">
         <v>3.05</v>
       </c>
       <c r="V17">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W17">
         <v>1.64</v>
@@ -4738,10 +4738,10 @@
         <v>34</v>
       </c>
       <c r="Y17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z17">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AA17">
         <v>44</v>
@@ -4753,7 +4753,7 @@
         <v>11.5</v>
       </c>
       <c r="AD17">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE17">
         <v>25</v>
@@ -4768,7 +4768,7 @@
         <v>14.5</v>
       </c>
       <c r="AI17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ17">
         <v>38</v>
@@ -4786,10 +4786,10 @@
         <v>11</v>
       </c>
       <c r="AO17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AP17">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AQ17">
         <v>17.5</v>
@@ -4846,7 +4846,7 @@
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BJ17">
         <v>11.5</v>
@@ -4858,7 +4858,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BN17">
         <v>8.800000000000001</v>
@@ -4870,16 +4870,16 @@
         <v>23</v>
       </c>
       <c r="BQ17">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="BR17">
         <v>30</v>
       </c>
       <c r="BS17">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="BT17">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BU17">
         <v>4.3</v>
@@ -4888,19 +4888,19 @@
         <v>26</v>
       </c>
       <c r="BW17">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="BX17">
         <v>32</v>
       </c>
       <c r="BY17">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="BZ17">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA17">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CB17" t="s">
         <v>147</v>
@@ -4953,10 +4953,10 @@
         <v>1.32</v>
       </c>
       <c r="P18">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q18">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R18">
         <v>1.34</v>
@@ -4989,7 +4989,7 @@
         <v>1000</v>
       </c>
       <c r="AB18">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC18">
         <v>11.5</v>
@@ -5034,13 +5034,13 @@
         <v>13</v>
       </c>
       <c r="AQ18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR18">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS18">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT18">
         <v>6</v>
@@ -5049,10 +5049,10 @@
         <v>9.6</v>
       </c>
       <c r="AV18">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW18">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX18">
         <v>6.4</v>
@@ -5061,10 +5061,10 @@
         <v>9</v>
       </c>
       <c r="AZ18">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BA18">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB18">
         <v>9.6</v>
@@ -5073,16 +5073,16 @@
         <v>14</v>
       </c>
       <c r="BD18">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="BE18">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF18">
         <v>6.4</v>
       </c>
       <c r="BG18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5294,7 +5294,7 @@
         <v>16</v>
       </c>
       <c r="AW19">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX19">
         <v>10</v>
@@ -5303,7 +5303,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA19">
         <v>5.2</v>
@@ -5318,13 +5318,13 @@
         <v>5.1</v>
       </c>
       <c r="BE19">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF19">
         <v>4.8</v>
       </c>
       <c r="BG19">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5422,7 +5422,7 @@
         <v>3.75</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L20">
         <v>1.33</v>
@@ -5667,7 +5667,7 @@
         <v>4.2</v>
       </c>
       <c r="L21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M21">
         <v>1.03</v>
@@ -5679,13 +5679,13 @@
         <v>1.19</v>
       </c>
       <c r="P21">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q21">
         <v>1.58</v>
       </c>
       <c r="R21">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S21">
         <v>2.46</v>
@@ -5805,70 +5805,70 @@
         <v>28</v>
       </c>
       <c r="BF21">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG21">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI21">
-        <v>1.99</v>
+        <v>3.45</v>
       </c>
       <c r="BJ21">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK21">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.96</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN21">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BO21">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BP21">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BQ21">
-        <v>1.87</v>
+        <v>6.8</v>
       </c>
       <c r="BR21">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BS21">
-        <v>1.9</v>
+        <v>7.2</v>
       </c>
       <c r="BT21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BU21">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV21">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BW21">
-        <v>1.84</v>
+        <v>6</v>
       </c>
       <c r="BX21">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BY21">
-        <v>1.89</v>
+        <v>7</v>
       </c>
       <c r="BZ21">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="CA21">
-        <v>1.84</v>
+        <v>6.2</v>
       </c>
       <c r="CB21" t="s">
         <v>147</v>
@@ -5927,7 +5927,7 @@
         <v>1.84</v>
       </c>
       <c r="R22">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S22">
         <v>3.15</v>
@@ -5942,7 +5942,7 @@
         <v>1.41</v>
       </c>
       <c r="W22">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X22">
         <v>20</v>
@@ -6133,7 +6133,7 @@
         <v>144</v>
       </c>
       <c r="F23">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G23">
         <v>3.05</v>
@@ -6145,7 +6145,7 @@
         <v>2.36</v>
       </c>
       <c r="J23">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K23">
         <v>4.4</v>
@@ -6163,10 +6163,10 @@
         <v>1.13</v>
       </c>
       <c r="P23">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R23">
         <v>1.91</v>
@@ -6181,10 +6181,10 @@
         <v>3.2</v>
       </c>
       <c r="V23">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W23">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X23">
         <v>34</v>
@@ -6199,7 +6199,7 @@
         <v>36</v>
       </c>
       <c r="AB23">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AC23">
         <v>11.5</v>
@@ -6247,10 +6247,10 @@
         <v>18.5</v>
       </c>
       <c r="AR23">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AS23">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AT23">
         <v>22</v>
@@ -6280,7 +6280,7 @@
         <v>42</v>
       </c>
       <c r="BC23">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD23">
         <v>24</v>
@@ -6298,61 +6298,61 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="CB23" t="s">
         <v>147</v>
@@ -6396,7 +6396,7 @@
         <v>1.29</v>
       </c>
       <c r="M24">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N24">
         <v>5.6</v>
@@ -6405,10 +6405,10 @@
         <v>1.2</v>
       </c>
       <c r="P24">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q24">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R24">
         <v>1.62</v>
@@ -6420,7 +6420,7 @@
         <v>1.66</v>
       </c>
       <c r="U24">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V24">
         <v>1.22</v>
@@ -6459,7 +6459,7 @@
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI24">
         <v>60</v>
@@ -6471,7 +6471,7 @@
         <v>15.5</v>
       </c>
       <c r="AL24">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM24">
         <v>1000</v>
@@ -6486,19 +6486,19 @@
         <v>21</v>
       </c>
       <c r="AQ24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR24">
         <v>26</v>
       </c>
       <c r="AS24">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT24">
         <v>10.5</v>
       </c>
       <c r="AU24">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV24">
         <v>18</v>
@@ -6528,10 +6528,10 @@
         <v>18</v>
       </c>
       <c r="BE24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF24">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG24">
         <v>27</v>
@@ -6540,61 +6540,61 @@
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK24">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO24">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ24">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS24">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA24">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="CB24" t="s">
         <v>147</v>
@@ -6626,7 +6626,7 @@
         <v>3.5</v>
       </c>
       <c r="I25">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J25">
         <v>4.2</v>
@@ -6650,13 +6650,13 @@
         <v>2.88</v>
       </c>
       <c r="Q25">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R25">
         <v>1.76</v>
       </c>
       <c r="S25">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T25">
         <v>1.49</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="164">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Chinese Super League</t>
   </si>
   <si>
+    <t>Serbian First League</t>
+  </si>
+  <si>
     <t>South African Premier Division</t>
   </si>
   <si>
@@ -292,9 +295,18 @@
     <t>11:35:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
     <t>17:30:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -328,27 +340,45 @@
     <t>Shanghai Port FC</t>
   </si>
   <si>
+    <t>FK Vrsac</t>
+  </si>
+  <si>
+    <t>FK Bor 1919</t>
+  </si>
+  <si>
+    <t>FK Javor Ivanjica</t>
+  </si>
+  <si>
+    <t>FK Teleoptik Zemun</t>
+  </si>
+  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
+    <t>Metalac Gornji Milanovac</t>
+  </si>
+  <si>
+    <t>FK Backa Topola</t>
+  </si>
+  <si>
     <t>Atletico Madrid</t>
   </si>
   <si>
     <t>Aguilas Doradas</t>
   </si>
   <si>
+    <t>Cerro Porteno</t>
+  </si>
+  <si>
     <t>Coquimbo Unido</t>
   </si>
   <si>
-    <t>Cerro Porteno</t>
+    <t>Fortaleza EC</t>
   </si>
   <si>
     <t>Avai</t>
   </si>
   <si>
-    <t>Fortaleza EC</t>
-  </si>
-  <si>
     <t>Atletico Ottawa</t>
   </si>
   <si>
@@ -358,30 +388,30 @@
     <t>Cucuta Deportivo</t>
   </si>
   <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Cuiaba</t>
+  </si>
+  <si>
+    <t>Toronto FC</t>
+  </si>
+  <si>
+    <t>New York Red Bulls</t>
+  </si>
+  <si>
+    <t>DC Utd</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Columbus</t>
+  </si>
+  <si>
     <t>Philadelphia</t>
   </si>
   <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>Cuiaba</t>
-  </si>
-  <si>
-    <t>Toronto FC</t>
-  </si>
-  <si>
-    <t>New York Red Bulls</t>
-  </si>
-  <si>
-    <t>DC Utd</t>
-  </si>
-  <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
-    <t>Columbus</t>
-  </si>
-  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
@@ -400,27 +430,45 @@
     <t>Dalian Yingbo</t>
   </si>
   <si>
+    <t>FK Dubocica</t>
+  </si>
+  <si>
+    <t>Vozdovac</t>
+  </si>
+  <si>
+    <t>FK Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>FK Napredak</t>
+  </si>
+  <si>
     <t>Marumo Gallants FC</t>
   </si>
   <si>
+    <t>Fk Smederevo</t>
+  </si>
+  <si>
+    <t>FK Spartak</t>
+  </si>
+  <si>
     <t>Malaga</t>
   </si>
   <si>
     <t>Llaneros FC</t>
   </si>
   <si>
+    <t>SE Palmeiras</t>
+  </si>
+  <si>
     <t>CA Platense</t>
   </si>
   <si>
-    <t>SE Palmeiras</t>
+    <t>Sao Bernardo</t>
   </si>
   <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>Sao Bernardo</t>
-  </si>
-  <si>
     <t>Vancouver FC</t>
   </si>
   <si>
@@ -430,34 +478,34 @@
     <t>Internacional de Bogotá</t>
   </si>
   <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>Operario PR</t>
+  </si>
+  <si>
+    <t>Charlotte FC</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>CF Montreal</t>
+  </si>
+  <si>
     <t>Inter Miami CF</t>
   </si>
   <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
-    <t>Operario PR</t>
-  </si>
-  <si>
-    <t>Charlotte FC</t>
-  </si>
-  <si>
-    <t>Nashville SC</t>
-  </si>
-  <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
-    <t>CF Montreal</t>
-  </si>
-  <si>
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-18 06:55:43</t>
+    <t>2026-08-18 09:04:10</t>
   </si>
 </sst>
 </file>
@@ -789,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1039,16 +1087,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F2">
         <v>2.26</v>
@@ -1057,7 +1105,7 @@
         <v>2.3</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I2">
         <v>4.1</v>
@@ -1069,31 +1117,31 @@
         <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U2">
         <v>1.97</v>
@@ -1117,7 +1165,7 @@
         <v>90</v>
       </c>
       <c r="AB2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC2">
         <v>7.2</v>
@@ -1156,13 +1204,13 @@
         <v>25</v>
       </c>
       <c r="AO2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
         <v>23</v>
@@ -1180,7 +1228,7 @@
         <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX2">
         <v>12</v>
@@ -1192,7 +1240,7 @@
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BB2">
         <v>26</v>
@@ -1201,7 +1249,7 @@
         <v>24</v>
       </c>
       <c r="BD2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE2">
         <v>11.5</v>
@@ -1213,7 +1261,7 @@
         <v>55</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI2">
         <v>2.5</v>
@@ -1231,7 +1279,7 @@
         <v>6.2</v>
       </c>
       <c r="BN2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO2">
         <v>4.2</v>
@@ -1240,7 +1288,7 @@
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1258,13 +1306,13 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BX2">
         <v>55</v>
       </c>
       <c r="BY2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BZ2">
         <v>42</v>
@@ -1273,7 +1321,7 @@
         <v>5.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1281,151 +1329,151 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F3">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="G3">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="H3">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="I3">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="J3">
         <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
         <v>1.58</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="O3">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q3">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U3">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z3">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AA3">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AB3">
         <v>9.6</v>
       </c>
       <c r="AC3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AF3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG3">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH3">
         <v>24</v>
       </c>
       <c r="AI3">
+        <v>80</v>
+      </c>
+      <c r="AJ3">
         <v>70</v>
       </c>
-      <c r="AJ3">
+      <c r="AK3">
         <v>55</v>
       </c>
-      <c r="AK3">
-        <v>46</v>
-      </c>
       <c r="AL3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM3">
         <v>180</v>
       </c>
       <c r="AN3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AO3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR3">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AS3">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AX3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY3">
         <v>13</v>
@@ -1434,31 +1482,31 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="BB3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BC3">
         <v>40</v>
       </c>
       <c r="BD3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE3">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BF3">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="BG3">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="BH3">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI3">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BJ3">
         <v>11</v>
@@ -1470,52 +1518,52 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BN3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BO3">
         <v>5</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ3">
         <v>11.5</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS3">
         <v>14</v>
       </c>
       <c r="BT3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BU3">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA3">
         <v>13.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1523,16 +1571,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F4">
         <v>3.15</v>
@@ -1544,19 +1592,19 @@
         <v>2.62</v>
       </c>
       <c r="I4">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L4">
         <v>1.54</v>
       </c>
       <c r="M4">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
         <v>2.88</v>
@@ -1565,10 +1613,10 @@
         <v>1.5</v>
       </c>
       <c r="P4">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q4">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R4">
         <v>1.21</v>
@@ -1583,7 +1631,7 @@
         <v>1.86</v>
       </c>
       <c r="V4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W4">
         <v>1.44</v>
@@ -1592,7 +1640,7 @@
         <v>9.6</v>
       </c>
       <c r="Y4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z4">
         <v>15</v>
@@ -1601,19 +1649,19 @@
         <v>42</v>
       </c>
       <c r="AB4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4">
         <v>7</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE4">
         <v>38</v>
       </c>
       <c r="AF4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
@@ -1622,7 +1670,7 @@
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ4">
         <v>65</v>
@@ -1646,7 +1694,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AR4">
         <v>13.5</v>
@@ -1673,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA4">
         <v>50</v>
@@ -1688,19 +1736,19 @@
         <v>46</v>
       </c>
       <c r="BE4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF4">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BG4">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BH4">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BI4">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4">
         <v>11</v>
@@ -1712,10 +1760,10 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BN4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO4">
         <v>5.2</v>
@@ -1724,16 +1772,16 @@
         <v>30</v>
       </c>
       <c r="BQ4">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR4">
         <v>50</v>
       </c>
       <c r="BS4">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU4">
         <v>4.7</v>
@@ -1742,22 +1790,22 @@
         <v>23</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CA4">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1765,28 +1813,28 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F5">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G5">
         <v>2.5</v>
       </c>
       <c r="H5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -1801,7 +1849,7 @@
         <v>1.15</v>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O5">
         <v>1.63</v>
@@ -1810,7 +1858,7 @@
         <v>1.48</v>
       </c>
       <c r="Q5">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R5">
         <v>1.17</v>
@@ -1819,10 +1867,10 @@
         <v>6.2</v>
       </c>
       <c r="T5">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U5">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V5">
         <v>1.35</v>
@@ -1840,7 +1888,7 @@
         <v>34</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB5">
         <v>8</v>
@@ -1852,7 +1900,7 @@
         <v>20</v>
       </c>
       <c r="AE5">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF5">
         <v>14</v>
@@ -1861,40 +1909,40 @@
         <v>13</v>
       </c>
       <c r="AH5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI5">
         <v>110</v>
       </c>
       <c r="AJ5">
+        <v>48</v>
+      </c>
+      <c r="AK5">
         <v>46</v>
       </c>
-      <c r="AK5">
-        <v>44</v>
-      </c>
       <c r="AL5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AM5">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO5">
         <v>110</v>
       </c>
       <c r="AP5">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR5">
         <v>21</v>
       </c>
       <c r="AS5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT5">
         <v>6.2</v>
@@ -1906,7 +1954,7 @@
         <v>15</v>
       </c>
       <c r="AW5">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="AX5">
         <v>12</v>
@@ -1915,10 +1963,10 @@
         <v>11</v>
       </c>
       <c r="AZ5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB5">
         <v>27</v>
@@ -1927,16 +1975,16 @@
         <v>26</v>
       </c>
       <c r="BD5">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BE5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF5">
+        <v>12.5</v>
+      </c>
+      <c r="BG5">
         <v>8</v>
-      </c>
-      <c r="BF5">
-        <v>7</v>
-      </c>
-      <c r="BG5">
-        <v>7.6</v>
       </c>
       <c r="BH5">
         <v>2.82</v>
@@ -1999,7 +2047,7 @@
         <v>6.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2007,22 +2055,22 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F6">
         <v>1.49</v>
       </c>
       <c r="G6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H6">
         <v>6.8</v>
@@ -2034,7 +2082,7 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L6">
         <v>1.22</v>
@@ -2052,7 +2100,7 @@
         <v>2.82</v>
       </c>
       <c r="Q6">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R6">
         <v>1.77</v>
@@ -2064,16 +2112,16 @@
         <v>1.67</v>
       </c>
       <c r="U6">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W6">
         <v>2.92</v>
       </c>
       <c r="X6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y6">
         <v>38</v>
@@ -2091,7 +2139,7 @@
         <v>12</v>
       </c>
       <c r="AD6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE6">
         <v>85</v>
@@ -2103,7 +2151,7 @@
         <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI6">
         <v>1000</v>
@@ -2121,13 +2169,13 @@
         <v>95</v>
       </c>
       <c r="AN6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AO6">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ6">
         <v>30</v>
@@ -2154,7 +2202,7 @@
         <v>10.5</v>
       </c>
       <c r="AY6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
         <v>17</v>
@@ -2175,7 +2223,7 @@
         <v>50</v>
       </c>
       <c r="BF6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG6">
         <v>40</v>
@@ -2187,7 +2235,7 @@
         <v>3.95</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK6">
         <v>5</v>
@@ -2196,7 +2244,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN6">
         <v>4.7</v>
@@ -2205,43 +2253,43 @@
         <v>3.6</v>
       </c>
       <c r="BP6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ6">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR6">
         <v>19.5</v>
       </c>
       <c r="BS6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT6">
         <v>11.5</v>
       </c>
       <c r="BU6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6">
         <v>11</v>
       </c>
       <c r="CA6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2249,34 +2297,34 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G7">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="I7">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2285,34 +2333,34 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="O7">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="Q7">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="R7">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="S7">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2426,1758 +2474,1758 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F8">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="G8">
-        <v>1.34</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="I8">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="K8">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="L8">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>4.5</v>
+        <v>1.07</v>
       </c>
       <c r="O8">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>2.2</v>
+        <v>1.07</v>
       </c>
       <c r="Q8">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
-        <v>1.46</v>
+        <v>1.07</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>620</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F9">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="G9">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="K9">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
         <v>1.09</v>
       </c>
-      <c r="N9">
-        <v>3.15</v>
-      </c>
       <c r="O9">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.76</v>
+        <v>1.08</v>
       </c>
       <c r="Q9">
-        <v>2.14</v>
+        <v>1.35</v>
       </c>
       <c r="R9">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="S9">
-        <v>4</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="F10">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="G10">
-        <v>2.4</v>
+        <v>1000</v>
       </c>
       <c r="H10">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="K10">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.09</v>
+      </c>
+      <c r="O10">
+        <v>1.01</v>
+      </c>
+      <c r="P10">
+        <v>1.08</v>
+      </c>
+      <c r="Q10">
+        <v>1.32</v>
+      </c>
+      <c r="R10">
+        <v>1.07</v>
+      </c>
+      <c r="S10">
+        <v>1.32</v>
+      </c>
+      <c r="T10">
         <v>1.11</v>
       </c>
-      <c r="N10">
-        <v>2.56</v>
-      </c>
-      <c r="O10">
-        <v>1.56</v>
-      </c>
-      <c r="P10">
-        <v>1.55</v>
-      </c>
-      <c r="Q10">
-        <v>2.68</v>
-      </c>
-      <c r="R10">
-        <v>1.18</v>
-      </c>
-      <c r="S10">
-        <v>5.4</v>
-      </c>
-      <c r="T10">
-        <v>2.18</v>
-      </c>
       <c r="U10">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
         <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F11">
-        <v>5.2</v>
+        <v>1.21</v>
       </c>
       <c r="G11">
-        <v>5.9</v>
+        <v>1.25</v>
       </c>
       <c r="H11">
-        <v>1.81</v>
+        <v>14</v>
       </c>
       <c r="I11">
-        <v>1.89</v>
+        <v>23</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <v>1.2</v>
+      </c>
+      <c r="P11">
+        <v>2.36</v>
+      </c>
+      <c r="Q11">
+        <v>1.57</v>
+      </c>
+      <c r="R11">
         <v>1.54</v>
       </c>
-      <c r="M11">
-        <v>1.11</v>
-      </c>
-      <c r="N11">
-        <v>2.72</v>
-      </c>
-      <c r="O11">
-        <v>1.48</v>
-      </c>
-      <c r="P11">
-        <v>1.59</v>
-      </c>
-      <c r="Q11">
-        <v>2.46</v>
-      </c>
-      <c r="R11">
-        <v>1.22</v>
-      </c>
       <c r="S11">
+        <v>2.38</v>
+      </c>
+      <c r="T11">
+        <v>2.26</v>
+      </c>
+      <c r="U11">
+        <v>1.61</v>
+      </c>
+      <c r="V11">
+        <v>1.04</v>
+      </c>
+      <c r="W11">
+        <v>4.7</v>
+      </c>
+      <c r="X11">
+        <v>30</v>
+      </c>
+      <c r="Y11">
+        <v>950</v>
+      </c>
+      <c r="Z11">
+        <v>220</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>11</v>
+      </c>
+      <c r="AC11">
+        <v>20</v>
+      </c>
+      <c r="AD11">
+        <v>950</v>
+      </c>
+      <c r="AE11">
+        <v>420</v>
+      </c>
+      <c r="AF11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG11">
+        <v>14.5</v>
+      </c>
+      <c r="AH11">
+        <v>50</v>
+      </c>
+      <c r="AI11">
+        <v>290</v>
+      </c>
+      <c r="AJ11">
+        <v>10.5</v>
+      </c>
+      <c r="AK11">
+        <v>18</v>
+      </c>
+      <c r="AL11">
+        <v>60</v>
+      </c>
+      <c r="AM11">
+        <v>300</v>
+      </c>
+      <c r="AN11">
         <v>5</v>
       </c>
-      <c r="T11">
-        <v>2.2</v>
-      </c>
-      <c r="U11">
-        <v>1.62</v>
-      </c>
-      <c r="V11">
-        <v>2.12</v>
-      </c>
-      <c r="W11">
-        <v>1.2</v>
-      </c>
-      <c r="X11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y11">
-        <v>6.6</v>
-      </c>
-      <c r="Z11">
-        <v>10</v>
-      </c>
-      <c r="AA11">
-        <v>21</v>
-      </c>
-      <c r="AB11">
-        <v>14.5</v>
-      </c>
-      <c r="AC11">
-        <v>8.4</v>
-      </c>
-      <c r="AD11">
-        <v>11</v>
-      </c>
-      <c r="AE11">
-        <v>25</v>
-      </c>
-      <c r="AF11">
-        <v>50</v>
-      </c>
-      <c r="AG11">
-        <v>23</v>
-      </c>
-      <c r="AH11">
-        <v>28</v>
-      </c>
-      <c r="AI11">
-        <v>70</v>
-      </c>
-      <c r="AJ11">
-        <v>210</v>
-      </c>
-      <c r="AK11">
-        <v>130</v>
-      </c>
-      <c r="AL11">
-        <v>140</v>
-      </c>
-      <c r="AM11">
-        <v>260</v>
-      </c>
-      <c r="AN11">
-        <v>220</v>
-      </c>
       <c r="AO11">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="AQ11">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="AR11">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="AS11">
-        <v>18</v>
+        <v>4.7</v>
       </c>
       <c r="AT11">
-        <v>11.5</v>
+        <v>3.3</v>
       </c>
       <c r="AU11">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="AV11">
-        <v>9.4</v>
+        <v>4.4</v>
       </c>
       <c r="AW11">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="AX11">
-        <v>36</v>
+        <v>3.05</v>
       </c>
       <c r="AY11">
-        <v>20</v>
+        <v>3.55</v>
       </c>
       <c r="AZ11">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA11">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="BB11">
-        <v>10.5</v>
+        <v>3.25</v>
       </c>
       <c r="BC11">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="BD11">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="BE11">
-        <v>10.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF11">
-        <v>10.5</v>
+        <v>2.42</v>
       </c>
       <c r="BG11">
-        <v>17</v>
+        <v>4.7</v>
       </c>
       <c r="BH11">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F12">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="I12">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="K12">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>1.07</v>
       </c>
       <c r="O12">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="P12">
-        <v>1.7</v>
+        <v>1.07</v>
       </c>
       <c r="Q12">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R12">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="S12">
-        <v>4.1</v>
+        <v>1.48</v>
       </c>
       <c r="T12">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F13">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="G13">
-        <v>1.73</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="I13">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L13">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.15</v>
+        <v>1.1</v>
       </c>
       <c r="O13">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.71</v>
+        <v>1.08</v>
       </c>
       <c r="Q13">
-        <v>2.12</v>
+        <v>1.32</v>
       </c>
       <c r="R13">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="S13">
-        <v>4.1</v>
+        <v>1.32</v>
       </c>
       <c r="T13">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
         <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F14">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="G14">
-        <v>2.72</v>
+        <v>1.37</v>
       </c>
       <c r="H14">
-        <v>2.58</v>
+        <v>11</v>
       </c>
       <c r="I14">
-        <v>2.96</v>
+        <v>12</v>
       </c>
       <c r="J14">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="K14">
+        <v>5.7</v>
+      </c>
+      <c r="L14">
+        <v>1.37</v>
+      </c>
+      <c r="M14">
+        <v>1.06</v>
+      </c>
+      <c r="N14">
         <v>4.4</v>
       </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
-      <c r="M14">
-        <v>1.01</v>
-      </c>
-      <c r="N14">
-        <v>2.56</v>
-      </c>
       <c r="O14">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="P14">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q14">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S14">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V14">
-        <v>1.51</v>
+        <v>1.09</v>
       </c>
       <c r="W14">
-        <v>1.58</v>
+        <v>3.7</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>140</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>36</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>26</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>26</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB14" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4185,178 +4233,178 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F15">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="G15">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="H15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I15">
+        <v>4.7</v>
+      </c>
+      <c r="J15">
+        <v>3.35</v>
+      </c>
+      <c r="K15">
+        <v>3.8</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.09</v>
+      </c>
+      <c r="N15">
+        <v>3.15</v>
+      </c>
+      <c r="O15">
+        <v>1.39</v>
+      </c>
+      <c r="P15">
+        <v>1.76</v>
+      </c>
+      <c r="Q15">
+        <v>2.14</v>
+      </c>
+      <c r="R15">
+        <v>1.28</v>
+      </c>
+      <c r="S15">
+        <v>4</v>
+      </c>
+      <c r="T15">
+        <v>1.92</v>
+      </c>
+      <c r="U15">
+        <v>1.94</v>
+      </c>
+      <c r="V15">
+        <v>1.27</v>
+      </c>
+      <c r="W15">
+        <v>1.9</v>
+      </c>
+      <c r="X15">
+        <v>13.5</v>
+      </c>
+      <c r="Y15">
+        <v>14</v>
+      </c>
+      <c r="Z15">
+        <v>38</v>
+      </c>
+      <c r="AA15">
+        <v>120</v>
+      </c>
+      <c r="AB15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC15">
+        <v>8</v>
+      </c>
+      <c r="AD15">
+        <v>18.5</v>
+      </c>
+      <c r="AE15">
+        <v>85</v>
+      </c>
+      <c r="AF15">
+        <v>12</v>
+      </c>
+      <c r="AG15">
+        <v>11</v>
+      </c>
+      <c r="AH15">
+        <v>21</v>
+      </c>
+      <c r="AI15">
+        <v>95</v>
+      </c>
+      <c r="AJ15">
+        <v>29</v>
+      </c>
+      <c r="AK15">
+        <v>32</v>
+      </c>
+      <c r="AL15">
+        <v>50</v>
+      </c>
+      <c r="AM15">
+        <v>150</v>
+      </c>
+      <c r="AN15">
+        <v>25</v>
+      </c>
+      <c r="AO15">
+        <v>100</v>
+      </c>
+      <c r="AP15">
+        <v>5.8</v>
+      </c>
+      <c r="AQ15">
+        <v>12</v>
+      </c>
+      <c r="AR15">
+        <v>7.8</v>
+      </c>
+      <c r="AS15">
+        <v>9.4</v>
+      </c>
+      <c r="AT15">
+        <v>7</v>
+      </c>
+      <c r="AU15">
+        <v>7</v>
+      </c>
+      <c r="AV15">
+        <v>15.5</v>
+      </c>
+      <c r="AW15">
+        <v>9</v>
+      </c>
+      <c r="AX15">
+        <v>10.5</v>
+      </c>
+      <c r="AY15">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB15">
+        <v>21</v>
+      </c>
+      <c r="BC15">
+        <v>20</v>
+      </c>
+      <c r="BD15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE15">
         <v>9.6</v>
       </c>
-      <c r="J15">
-        <v>1.09</v>
-      </c>
-      <c r="K15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L15">
-        <v>1.27</v>
-      </c>
-      <c r="M15">
-        <v>1.01</v>
-      </c>
-      <c r="N15">
-        <v>2.64</v>
-      </c>
-      <c r="O15">
-        <v>1.25</v>
-      </c>
-      <c r="P15">
-        <v>1.83</v>
-      </c>
-      <c r="Q15">
-        <v>1.61</v>
-      </c>
-      <c r="R15">
-        <v>1.31</v>
-      </c>
-      <c r="S15">
-        <v>2.58</v>
-      </c>
-      <c r="T15">
-        <v>1.11</v>
-      </c>
-      <c r="U15">
-        <v>1.11</v>
-      </c>
-      <c r="V15">
-        <v>1.15</v>
-      </c>
-      <c r="W15">
-        <v>2</v>
-      </c>
-      <c r="X15">
-        <v>1000</v>
-      </c>
-      <c r="Y15">
-        <v>1000</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>1000</v>
-      </c>
-      <c r="AC15">
-        <v>1000</v>
-      </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15">
-        <v>1.01</v>
-      </c>
-      <c r="AR15">
-        <v>1.01</v>
-      </c>
-      <c r="AS15">
-        <v>1.01</v>
-      </c>
-      <c r="AT15">
-        <v>1.01</v>
-      </c>
-      <c r="AU15">
-        <v>1.01</v>
-      </c>
-      <c r="AV15">
-        <v>1.01</v>
-      </c>
-      <c r="AW15">
-        <v>1.01</v>
-      </c>
-      <c r="AX15">
-        <v>1.01</v>
-      </c>
-      <c r="AY15">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15">
-        <v>1.01</v>
-      </c>
-      <c r="BA15">
-        <v>1.01</v>
-      </c>
-      <c r="BB15">
-        <v>1.01</v>
-      </c>
-      <c r="BC15">
-        <v>1.01</v>
-      </c>
-      <c r="BD15">
-        <v>1.01</v>
-      </c>
-      <c r="BE15">
-        <v>1.01</v>
-      </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4419,491 +4467,491 @@
         <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F16">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="G16">
-        <v>110</v>
+        <v>5.9</v>
       </c>
       <c r="H16">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="I16">
-        <v>110</v>
+        <v>1.89</v>
       </c>
       <c r="J16">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N16">
-        <v>1.26</v>
+        <v>2.66</v>
       </c>
       <c r="O16">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q16">
-        <v>1.42</v>
+        <v>2.48</v>
       </c>
       <c r="R16">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="S16">
-        <v>1.44</v>
+        <v>5</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V16">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="W16">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="CB16" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F17">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="G17">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="H17">
+        <v>3.6</v>
+      </c>
+      <c r="I17">
+        <v>3.85</v>
+      </c>
+      <c r="J17">
+        <v>3.15</v>
+      </c>
+      <c r="K17">
+        <v>3.2</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.11</v>
+      </c>
+      <c r="N17">
+        <v>2.58</v>
+      </c>
+      <c r="O17">
+        <v>1.56</v>
+      </c>
+      <c r="P17">
+        <v>1.55</v>
+      </c>
+      <c r="Q17">
         <v>2.68</v>
       </c>
-      <c r="I17">
-        <v>2.76</v>
-      </c>
-      <c r="J17">
-        <v>4.1</v>
-      </c>
-      <c r="K17">
-        <v>4.3</v>
-      </c>
-      <c r="L17">
-        <v>1.24</v>
-      </c>
-      <c r="M17">
-        <v>1.03</v>
-      </c>
-      <c r="N17">
-        <v>7</v>
-      </c>
-      <c r="O17">
-        <v>1.15</v>
-      </c>
-      <c r="P17">
-        <v>3</v>
-      </c>
-      <c r="Q17">
-        <v>1.46</v>
-      </c>
       <c r="R17">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="S17">
-        <v>2.14</v>
+        <v>5.4</v>
       </c>
       <c r="T17">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="U17">
-        <v>3.05</v>
+        <v>1.64</v>
       </c>
       <c r="V17">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="X17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y17">
+        <v>10.5</v>
+      </c>
+      <c r="Z17">
+        <v>25</v>
+      </c>
+      <c r="AA17">
+        <v>85</v>
+      </c>
+      <c r="AB17">
+        <v>7.2</v>
+      </c>
+      <c r="AC17">
+        <v>8</v>
+      </c>
+      <c r="AD17">
+        <v>17</v>
+      </c>
+      <c r="AE17">
+        <v>65</v>
+      </c>
+      <c r="AF17">
+        <v>13.5</v>
+      </c>
+      <c r="AG17">
+        <v>12</v>
+      </c>
+      <c r="AH17">
+        <v>27</v>
+      </c>
+      <c r="AI17">
+        <v>95</v>
+      </c>
+      <c r="AJ17">
+        <v>36</v>
+      </c>
+      <c r="AK17">
         <v>34</v>
       </c>
-      <c r="Y17">
-        <v>21</v>
-      </c>
-      <c r="Z17">
-        <v>34</v>
-      </c>
-      <c r="AA17">
-        <v>44</v>
-      </c>
-      <c r="AB17">
-        <v>21</v>
-      </c>
-      <c r="AC17">
-        <v>11.5</v>
-      </c>
-      <c r="AD17">
-        <v>15</v>
-      </c>
-      <c r="AE17">
-        <v>25</v>
-      </c>
-      <c r="AF17">
-        <v>24</v>
-      </c>
-      <c r="AG17">
-        <v>13.5</v>
-      </c>
-      <c r="AH17">
-        <v>14.5</v>
-      </c>
-      <c r="AI17">
-        <v>27</v>
-      </c>
-      <c r="AJ17">
+      <c r="AL17">
+        <v>65</v>
+      </c>
+      <c r="AM17">
+        <v>220</v>
+      </c>
+      <c r="AN17">
         <v>38</v>
       </c>
-      <c r="AK17">
-        <v>23</v>
-      </c>
-      <c r="AL17">
-        <v>27</v>
-      </c>
-      <c r="AM17">
-        <v>46</v>
-      </c>
-      <c r="AN17">
-        <v>11</v>
-      </c>
       <c r="AO17">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="AP17">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="AQ17">
-        <v>17.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17">
         <v>21</v>
       </c>
       <c r="AS17">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AT17">
-        <v>17.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU17">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV17">
+        <v>14.5</v>
+      </c>
+      <c r="AW17">
+        <v>50</v>
+      </c>
+      <c r="AX17">
         <v>11.5</v>
       </c>
-      <c r="AW17">
-        <v>20</v>
-      </c>
-      <c r="AX17">
-        <v>19.5</v>
-      </c>
       <c r="AY17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="BA17">
-        <v>17.5</v>
+        <v>60</v>
       </c>
       <c r="BB17">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BC17">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="BD17">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="BE17">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="BF17">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BG17">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="BH17">
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="BJ17">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="BK17">
-        <v>5.1</v>
+        <v>1.51</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="BN17">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BO17">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="BP17">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BQ17">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="BR17">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="BT17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV17">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="BX17">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="BZ17">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="CB17" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4911,241 +4959,241 @@
         <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F18">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="G18">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="H18">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="I18">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="K18">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M18">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N18">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="O18">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P18">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="Q18">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="R18">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="S18">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="T18">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="U18">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="V18">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="W18">
-        <v>3.35</v>
+        <v>2.36</v>
       </c>
       <c r="X18">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y18">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="Z18">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB18">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD18">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AE18">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="AF18">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG18">
         <v>11</v>
       </c>
       <c r="AH18">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AI18">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="AJ18">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AK18">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AL18">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM18">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="AN18">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AO18">
-        <v>470</v>
+        <v>240</v>
       </c>
       <c r="AP18">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ18">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="AR18">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AS18">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AT18">
         <v>6</v>
       </c>
       <c r="AU18">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV18">
+        <v>6.4</v>
+      </c>
+      <c r="AW18">
         <v>7.8</v>
       </c>
-      <c r="AW18">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AX18">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY18">
         <v>9</v>
       </c>
       <c r="AZ18">
+        <v>21</v>
+      </c>
+      <c r="BA18">
+        <v>7.8</v>
+      </c>
+      <c r="BB18">
+        <v>14</v>
+      </c>
+      <c r="BC18">
+        <v>17.5</v>
+      </c>
+      <c r="BD18">
+        <v>7.2</v>
+      </c>
+      <c r="BE18">
+        <v>8</v>
+      </c>
+      <c r="BF18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG18">
+        <v>8</v>
+      </c>
+      <c r="BH18">
+        <v>3.8</v>
+      </c>
+      <c r="BI18">
+        <v>2.64</v>
+      </c>
+      <c r="BJ18">
+        <v>12</v>
+      </c>
+      <c r="BK18">
+        <v>8.4</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>7.4</v>
+      </c>
+      <c r="BN18">
+        <v>4</v>
+      </c>
+      <c r="BO18">
+        <v>3.4</v>
+      </c>
+      <c r="BP18">
+        <v>12</v>
+      </c>
+      <c r="BQ18">
+        <v>4.7</v>
+      </c>
+      <c r="BR18">
+        <v>36</v>
+      </c>
+      <c r="BS18">
+        <v>6.2</v>
+      </c>
+      <c r="BT18">
+        <v>10.5</v>
+      </c>
+      <c r="BU18">
+        <v>4.4</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>6.8</v>
+      </c>
+      <c r="BX18">
+        <v>90</v>
+      </c>
+      <c r="BY18">
+        <v>7</v>
+      </c>
+      <c r="BZ18">
         <v>27</v>
       </c>
-      <c r="BA18">
-        <v>9</v>
-      </c>
-      <c r="BB18">
-        <v>9.6</v>
-      </c>
-      <c r="BC18">
-        <v>14</v>
-      </c>
-      <c r="BD18">
-        <v>40</v>
-      </c>
-      <c r="BE18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF18">
-        <v>6.4</v>
-      </c>
-      <c r="BG18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.04</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.04</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>1.04</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>1.04</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>1.04</v>
-      </c>
-      <c r="BT18">
-        <v>1000</v>
-      </c>
-      <c r="BU18">
-        <v>1.04</v>
-      </c>
-      <c r="BV18">
-        <v>1000</v>
-      </c>
-      <c r="BW18">
-        <v>1.04</v>
-      </c>
-      <c r="BX18">
-        <v>1000</v>
-      </c>
-      <c r="BY18">
-        <v>1.04</v>
-      </c>
-      <c r="BZ18">
-        <v>1000</v>
-      </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB18" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5153,241 +5201,241 @@
         <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F19">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="G19">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="H19">
+        <v>2.82</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19">
+        <v>3.1</v>
+      </c>
+      <c r="K19">
+        <v>3.3</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.09</v>
+      </c>
+      <c r="N19">
+        <v>3.05</v>
+      </c>
+      <c r="O19">
+        <v>1.41</v>
+      </c>
+      <c r="P19">
+        <v>1.7</v>
+      </c>
+      <c r="Q19">
+        <v>2.24</v>
+      </c>
+      <c r="R19">
+        <v>1.26</v>
+      </c>
+      <c r="S19">
         <v>4.1</v>
       </c>
-      <c r="I19">
-        <v>4.3</v>
-      </c>
-      <c r="J19">
-        <v>3.05</v>
-      </c>
-      <c r="K19">
-        <v>3.15</v>
-      </c>
-      <c r="L19">
-        <v>1.01</v>
-      </c>
-      <c r="M19">
-        <v>1.01</v>
-      </c>
-      <c r="N19">
-        <v>2.56</v>
-      </c>
-      <c r="O19">
-        <v>1.57</v>
-      </c>
-      <c r="P19">
+      <c r="T19">
+        <v>1.89</v>
+      </c>
+      <c r="U19">
+        <v>1.98</v>
+      </c>
+      <c r="V19">
+        <v>1.5</v>
+      </c>
+      <c r="W19">
         <v>1.51</v>
       </c>
-      <c r="Q19">
-        <v>2.74</v>
-      </c>
-      <c r="R19">
-        <v>1.17</v>
-      </c>
-      <c r="S19">
-        <v>5.7</v>
-      </c>
-      <c r="T19">
-        <v>2.14</v>
-      </c>
-      <c r="U19">
-        <v>1.68</v>
-      </c>
-      <c r="V19">
-        <v>1.3</v>
-      </c>
-      <c r="W19">
-        <v>1.76</v>
-      </c>
       <c r="X19">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="Y19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z19">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AA19">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AB19">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD19">
+        <v>16</v>
+      </c>
+      <c r="AE19">
+        <v>44</v>
+      </c>
+      <c r="AF19">
         <v>23</v>
-      </c>
-      <c r="AE19">
-        <v>90</v>
-      </c>
-      <c r="AF19">
-        <v>15</v>
       </c>
       <c r="AG19">
         <v>14</v>
       </c>
       <c r="AH19">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AI19">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AJ19">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AK19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AL19">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AM19">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="AN19">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AO19">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="AP19">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AQ19">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR19">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AS19">
         <v>5.2</v>
       </c>
       <c r="AT19">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AU19">
         <v>6.4</v>
       </c>
       <c r="AV19">
+        <v>11.5</v>
+      </c>
+      <c r="AW19">
+        <v>5</v>
+      </c>
+      <c r="AX19">
         <v>16</v>
       </c>
-      <c r="AW19">
-        <v>5.2</v>
-      </c>
-      <c r="AX19">
-        <v>10</v>
-      </c>
       <c r="AY19">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ19">
-        <v>4.7</v>
+        <v>16.5</v>
       </c>
       <c r="BA19">
         <v>5.2</v>
       </c>
       <c r="BB19">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BC19">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD19">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE19">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF19">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BG19">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BH19">
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="BJ19">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BK19">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="BN19">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO19">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="BP19">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BQ19">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="BT19">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BU19">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW19">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="CB19" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5395,241 +5443,241 @@
         <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F20">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G20">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="H20">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="I20">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="J20">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K20">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="L20">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>4.9</v>
+        <v>2.56</v>
       </c>
       <c r="O20">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="Q20">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
       <c r="R20">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="S20">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="T20">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W20">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="X20">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
         <v>1000</v>
       </c>
       <c r="AN20">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5637,1113 +5685,1113 @@
         <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F21">
-        <v>2.96</v>
+        <v>1.54</v>
       </c>
       <c r="G21">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="H21">
-        <v>2.32</v>
+        <v>4.1</v>
       </c>
       <c r="I21">
-        <v>2.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>1.09</v>
       </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L21">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>5.8</v>
+        <v>2.64</v>
       </c>
       <c r="O21">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="P21">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="Q21">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R21">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="S21">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="T21">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="U21">
-        <v>2.66</v>
+        <v>1.11</v>
       </c>
       <c r="V21">
-        <v>1.72</v>
+        <v>1.15</v>
       </c>
       <c r="W21">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="X21">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="F22">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="G22">
-        <v>2.32</v>
+        <v>600</v>
       </c>
       <c r="H22">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="I22">
-        <v>3.45</v>
+        <v>990</v>
       </c>
       <c r="J22">
-        <v>3.7</v>
+        <v>1.09</v>
       </c>
       <c r="K22">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L22">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>4.3</v>
+        <v>1.28</v>
       </c>
       <c r="O22">
+        <v>1.42</v>
+      </c>
+      <c r="P22">
         <v>1.28</v>
       </c>
-      <c r="P22">
-        <v>2.12</v>
-      </c>
       <c r="Q22">
-        <v>1.84</v>
+        <v>1.42</v>
       </c>
       <c r="R22">
+        <v>1.13</v>
+      </c>
+      <c r="S22">
         <v>1.44</v>
       </c>
-      <c r="S22">
-        <v>3.15</v>
-      </c>
       <c r="T22">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="U22">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="W22">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="X22">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV22">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>1.39</v>
       </c>
       <c r="G23">
-        <v>3.05</v>
+        <v>1.42</v>
       </c>
       <c r="H23">
+        <v>11</v>
+      </c>
+      <c r="I23">
+        <v>12.5</v>
+      </c>
+      <c r="J23">
+        <v>4.7</v>
+      </c>
+      <c r="K23">
+        <v>5.2</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.06</v>
+      </c>
+      <c r="N23">
+        <v>3.6</v>
+      </c>
+      <c r="O23">
+        <v>1.32</v>
+      </c>
+      <c r="P23">
+        <v>1.9</v>
+      </c>
+      <c r="Q23">
+        <v>1.96</v>
+      </c>
+      <c r="R23">
+        <v>1.34</v>
+      </c>
+      <c r="S23">
+        <v>3.4</v>
+      </c>
+      <c r="T23">
         <v>2.28</v>
       </c>
-      <c r="I23">
-        <v>2.36</v>
-      </c>
-      <c r="J23">
-        <v>4.1</v>
-      </c>
-      <c r="K23">
-        <v>4.4</v>
-      </c>
-      <c r="L23">
-        <v>1.22</v>
-      </c>
-      <c r="M23">
-        <v>1.02</v>
-      </c>
-      <c r="N23">
-        <v>7.6</v>
-      </c>
-      <c r="O23">
-        <v>1.13</v>
-      </c>
-      <c r="P23">
-        <v>3.2</v>
-      </c>
-      <c r="Q23">
-        <v>1.44</v>
-      </c>
-      <c r="R23">
-        <v>1.91</v>
-      </c>
-      <c r="S23">
-        <v>2.02</v>
-      </c>
-      <c r="T23">
-        <v>1.41</v>
-      </c>
       <c r="U23">
-        <v>3.2</v>
+        <v>1.66</v>
       </c>
       <c r="V23">
-        <v>1.75</v>
+        <v>1.08</v>
       </c>
       <c r="W23">
-        <v>1.48</v>
+        <v>3.35</v>
       </c>
       <c r="X23">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="Y23">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Z23">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="AA23">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>24</v>
+        <v>7.2</v>
       </c>
       <c r="AC23">
         <v>11.5</v>
       </c>
       <c r="AD23">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="AE23">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="AF23">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="AG23">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AH23">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="AI23">
-        <v>32</v>
+        <v>220</v>
       </c>
       <c r="AJ23">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="AK23">
+        <v>17.5</v>
+      </c>
+      <c r="AL23">
+        <v>50</v>
+      </c>
+      <c r="AM23">
+        <v>270</v>
+      </c>
+      <c r="AN23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO23">
+        <v>470</v>
+      </c>
+      <c r="AP23">
+        <v>13</v>
+      </c>
+      <c r="AQ23">
+        <v>7.2</v>
+      </c>
+      <c r="AR23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS23">
+        <v>9.4</v>
+      </c>
+      <c r="AT23">
+        <v>6</v>
+      </c>
+      <c r="AU23">
+        <v>9.6</v>
+      </c>
+      <c r="AV23">
+        <v>7.8</v>
+      </c>
+      <c r="AW23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX23">
+        <v>6.4</v>
+      </c>
+      <c r="AY23">
+        <v>9</v>
+      </c>
+      <c r="AZ23">
         <v>27</v>
       </c>
-      <c r="AL23">
-        <v>42</v>
-      </c>
-      <c r="AM23">
-        <v>46</v>
-      </c>
-      <c r="AN23">
-        <v>13</v>
-      </c>
-      <c r="AO23">
+      <c r="BA23">
+        <v>9</v>
+      </c>
+      <c r="BB23">
+        <v>9.6</v>
+      </c>
+      <c r="BC23">
+        <v>14</v>
+      </c>
+      <c r="BD23">
+        <v>40</v>
+      </c>
+      <c r="BE23">
         <v>9.199999999999999</v>
       </c>
-      <c r="AP23">
-        <v>30</v>
-      </c>
-      <c r="AQ23">
-        <v>18.5</v>
-      </c>
-      <c r="AR23">
-        <v>19.5</v>
-      </c>
-      <c r="AS23">
-        <v>30</v>
-      </c>
-      <c r="AT23">
-        <v>22</v>
-      </c>
-      <c r="AU23">
-        <v>10</v>
-      </c>
-      <c r="AV23">
-        <v>11</v>
-      </c>
-      <c r="AW23">
-        <v>18</v>
-      </c>
-      <c r="AX23">
-        <v>26</v>
-      </c>
-      <c r="AY23">
-        <v>12.5</v>
-      </c>
-      <c r="AZ23">
-        <v>12.5</v>
-      </c>
-      <c r="BA23">
-        <v>21</v>
-      </c>
-      <c r="BB23">
-        <v>42</v>
-      </c>
-      <c r="BC23">
-        <v>18</v>
-      </c>
-      <c r="BD23">
-        <v>24</v>
-      </c>
-      <c r="BE23">
-        <v>36</v>
-      </c>
       <c r="BF23">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="BG23">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.97</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.88</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E24" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="F24">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="G24">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="H24">
+        <v>4</v>
+      </c>
+      <c r="I24">
+        <v>4.3</v>
+      </c>
+      <c r="J24">
+        <v>3.05</v>
+      </c>
+      <c r="K24">
+        <v>3.2</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.13</v>
+      </c>
+      <c r="N24">
+        <v>2.56</v>
+      </c>
+      <c r="O24">
+        <v>1.57</v>
+      </c>
+      <c r="P24">
+        <v>1.48</v>
+      </c>
+      <c r="Q24">
+        <v>2.74</v>
+      </c>
+      <c r="R24">
+        <v>1.17</v>
+      </c>
+      <c r="S24">
+        <v>5.7</v>
+      </c>
+      <c r="T24">
+        <v>2.16</v>
+      </c>
+      <c r="U24">
+        <v>1.7</v>
+      </c>
+      <c r="V24">
+        <v>1.3</v>
+      </c>
+      <c r="W24">
+        <v>1.76</v>
+      </c>
+      <c r="X24">
+        <v>8.6</v>
+      </c>
+      <c r="Y24">
+        <v>13</v>
+      </c>
+      <c r="Z24">
+        <v>34</v>
+      </c>
+      <c r="AA24">
+        <v>120</v>
+      </c>
+      <c r="AB24">
+        <v>6.8</v>
+      </c>
+      <c r="AC24">
+        <v>9</v>
+      </c>
+      <c r="AD24">
+        <v>23</v>
+      </c>
+      <c r="AE24">
+        <v>90</v>
+      </c>
+      <c r="AF24">
+        <v>15</v>
+      </c>
+      <c r="AG24">
+        <v>14</v>
+      </c>
+      <c r="AH24">
+        <v>32</v>
+      </c>
+      <c r="AI24">
+        <v>130</v>
+      </c>
+      <c r="AJ24">
+        <v>40</v>
+      </c>
+      <c r="AK24">
+        <v>40</v>
+      </c>
+      <c r="AL24">
+        <v>80</v>
+      </c>
+      <c r="AM24">
+        <v>280</v>
+      </c>
+      <c r="AN24">
+        <v>42</v>
+      </c>
+      <c r="AO24">
+        <v>140</v>
+      </c>
+      <c r="AP24">
+        <v>7.2</v>
+      </c>
+      <c r="AQ24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR24">
+        <v>4.7</v>
+      </c>
+      <c r="AS24">
+        <v>5.2</v>
+      </c>
+      <c r="AT24">
+        <v>5.9</v>
+      </c>
+      <c r="AU24">
+        <v>6.4</v>
+      </c>
+      <c r="AV24">
+        <v>16</v>
+      </c>
+      <c r="AW24">
+        <v>5.2</v>
+      </c>
+      <c r="AX24">
+        <v>10</v>
+      </c>
+      <c r="AY24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ24">
+        <v>4.7</v>
+      </c>
+      <c r="BA24">
+        <v>5.2</v>
+      </c>
+      <c r="BB24">
+        <v>27</v>
+      </c>
+      <c r="BC24">
+        <v>27</v>
+      </c>
+      <c r="BD24">
+        <v>5.1</v>
+      </c>
+      <c r="BE24">
         <v>5.4</v>
       </c>
-      <c r="I24">
-        <v>5.5</v>
-      </c>
-      <c r="J24">
-        <v>4.4</v>
-      </c>
-      <c r="K24">
-        <v>4.7</v>
-      </c>
-      <c r="L24">
-        <v>1.29</v>
-      </c>
-      <c r="M24">
-        <v>1.04</v>
-      </c>
-      <c r="N24">
-        <v>5.6</v>
-      </c>
-      <c r="O24">
-        <v>1.2</v>
-      </c>
-      <c r="P24">
-        <v>2.58</v>
-      </c>
-      <c r="Q24">
-        <v>1.6</v>
-      </c>
-      <c r="R24">
-        <v>1.62</v>
-      </c>
-      <c r="S24">
-        <v>2.5</v>
-      </c>
-      <c r="T24">
-        <v>1.66</v>
-      </c>
-      <c r="U24">
-        <v>2.36</v>
-      </c>
-      <c r="V24">
-        <v>1.22</v>
-      </c>
-      <c r="W24">
-        <v>2.44</v>
-      </c>
-      <c r="X24">
-        <v>25</v>
-      </c>
-      <c r="Y24">
-        <v>26</v>
-      </c>
-      <c r="Z24">
-        <v>48</v>
-      </c>
-      <c r="AA24">
-        <v>1000</v>
-      </c>
-      <c r="AB24">
-        <v>12.5</v>
-      </c>
-      <c r="AC24">
-        <v>10.5</v>
-      </c>
-      <c r="AD24">
-        <v>22</v>
-      </c>
-      <c r="AE24">
-        <v>65</v>
-      </c>
-      <c r="AF24">
-        <v>12.5</v>
-      </c>
-      <c r="AG24">
-        <v>10.5</v>
-      </c>
-      <c r="AH24">
-        <v>18</v>
-      </c>
-      <c r="AI24">
-        <v>60</v>
-      </c>
-      <c r="AJ24">
-        <v>18</v>
-      </c>
-      <c r="AK24">
-        <v>15.5</v>
-      </c>
-      <c r="AL24">
-        <v>28</v>
-      </c>
-      <c r="AM24">
-        <v>1000</v>
-      </c>
-      <c r="AN24">
-        <v>7</v>
-      </c>
-      <c r="AO24">
-        <v>55</v>
-      </c>
-      <c r="AP24">
-        <v>21</v>
-      </c>
-      <c r="AQ24">
-        <v>21</v>
-      </c>
-      <c r="AR24">
-        <v>26</v>
-      </c>
-      <c r="AS24">
-        <v>40</v>
-      </c>
-      <c r="AT24">
-        <v>10.5</v>
-      </c>
-      <c r="AU24">
-        <v>9.4</v>
-      </c>
-      <c r="AV24">
-        <v>18</v>
-      </c>
-      <c r="AW24">
+      <c r="BF24">
         <v>29</v>
       </c>
-      <c r="AX24">
-        <v>10.5</v>
-      </c>
-      <c r="AY24">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ24">
-        <v>15.5</v>
-      </c>
-      <c r="BA24">
-        <v>28</v>
-      </c>
-      <c r="BB24">
-        <v>15</v>
-      </c>
-      <c r="BC24">
-        <v>13.5</v>
-      </c>
-      <c r="BD24">
-        <v>18</v>
-      </c>
-      <c r="BE24">
-        <v>32</v>
-      </c>
-      <c r="BF24">
-        <v>6.4</v>
-      </c>
       <c r="BG24">
-        <v>27</v>
+        <v>5.3</v>
       </c>
       <c r="BH24">
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="BJ24">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BK24">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="BN24">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BO24">
         <v>3.3</v>
       </c>
       <c r="BP24">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="BQ24">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="BR24">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="BT24">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU24">
-        <v>1.78</v>
+        <v>4.5</v>
       </c>
       <c r="BV24">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="BZ24">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="CB24" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E25" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F25">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="G25">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="H25">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="I25">
+        <v>3.2</v>
+      </c>
+      <c r="J25">
         <v>3.75</v>
       </c>
-      <c r="J25">
-        <v>4.2</v>
-      </c>
       <c r="K25">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L25">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="M25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N25">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="O25">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="P25">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="Q25">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="R25">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="S25">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="T25">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="U25">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="V25">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W25">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="X25">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Y25">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Z25">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA25">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB25">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AC25">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD25">
         <v>16</v>
       </c>
       <c r="AE25">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF25">
         <v>17.5</v>
       </c>
       <c r="AG25">
+        <v>13</v>
+      </c>
+      <c r="AH25">
+        <v>16</v>
+      </c>
+      <c r="AI25">
+        <v>44</v>
+      </c>
+      <c r="AJ25">
+        <v>36</v>
+      </c>
+      <c r="AK25">
+        <v>26</v>
+      </c>
+      <c r="AL25">
+        <v>36</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>16.5</v>
+      </c>
+      <c r="AO25">
+        <v>23</v>
+      </c>
+      <c r="AP25">
+        <v>17.5</v>
+      </c>
+      <c r="AQ25">
+        <v>14</v>
+      </c>
+      <c r="AR25">
+        <v>20</v>
+      </c>
+      <c r="AS25">
+        <v>34</v>
+      </c>
+      <c r="AT25">
         <v>11.5</v>
       </c>
-      <c r="AH25">
-        <v>14.5</v>
-      </c>
-      <c r="AI25">
-        <v>34</v>
-      </c>
-      <c r="AJ25">
-        <v>28</v>
-      </c>
-      <c r="AK25">
-        <v>18</v>
-      </c>
-      <c r="AL25">
-        <v>24</v>
-      </c>
-      <c r="AM25">
-        <v>190</v>
-      </c>
-      <c r="AN25">
-        <v>8.6</v>
-      </c>
-      <c r="AO25">
-        <v>21</v>
-      </c>
-      <c r="AP25">
-        <v>20</v>
-      </c>
-      <c r="AQ25">
-        <v>19.5</v>
-      </c>
-      <c r="AR25">
-        <v>22</v>
-      </c>
-      <c r="AS25">
-        <v>42</v>
-      </c>
-      <c r="AT25">
-        <v>14</v>
-      </c>
       <c r="AU25">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AV25">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AW25">
         <v>21</v>
@@ -6755,91 +6803,1543 @@
         <v>10</v>
       </c>
       <c r="AZ25">
+        <v>14</v>
+      </c>
+      <c r="BA25">
+        <v>25</v>
+      </c>
+      <c r="BB25">
+        <v>20</v>
+      </c>
+      <c r="BC25">
+        <v>20</v>
+      </c>
+      <c r="BD25">
+        <v>20</v>
+      </c>
+      <c r="BE25">
+        <v>36</v>
+      </c>
+      <c r="BF25">
         <v>12.5</v>
       </c>
-      <c r="BA25">
+      <c r="BG25">
+        <v>20</v>
+      </c>
+      <c r="BH25">
+        <v>4.7</v>
+      </c>
+      <c r="BI25">
+        <v>3.15</v>
+      </c>
+      <c r="BJ25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK25">
+        <v>4.5</v>
+      </c>
+      <c r="BL25">
+        <v>110</v>
+      </c>
+      <c r="BM25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN25">
+        <v>5.6</v>
+      </c>
+      <c r="BO25">
+        <v>4.9</v>
+      </c>
+      <c r="BP25">
+        <v>16.5</v>
+      </c>
+      <c r="BQ25">
+        <v>6</v>
+      </c>
+      <c r="BR25">
+        <v>26</v>
+      </c>
+      <c r="BS25">
+        <v>7</v>
+      </c>
+      <c r="BT25">
+        <v>6.6</v>
+      </c>
+      <c r="BU25">
+        <v>5.7</v>
+      </c>
+      <c r="BV25">
         <v>22</v>
       </c>
-      <c r="BB25">
-        <v>18</v>
-      </c>
-      <c r="BC25">
-        <v>16</v>
-      </c>
-      <c r="BD25">
-        <v>21</v>
-      </c>
-      <c r="BE25">
-        <v>34</v>
-      </c>
-      <c r="BF25">
-        <v>7.8</v>
-      </c>
-      <c r="BG25">
-        <v>18.5</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>3.25</v>
-      </c>
-      <c r="BJ25">
-        <v>12.5</v>
-      </c>
-      <c r="BK25">
-        <v>5.3</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>1.99</v>
-      </c>
-      <c r="BN25">
-        <v>7.8</v>
-      </c>
-      <c r="BO25">
-        <v>3.6</v>
-      </c>
-      <c r="BP25">
-        <v>19</v>
-      </c>
-      <c r="BQ25">
-        <v>1.83</v>
-      </c>
-      <c r="BR25">
+      <c r="BW25">
+        <v>6.6</v>
+      </c>
+      <c r="BX25">
         <v>30</v>
       </c>
-      <c r="BS25">
-        <v>1.9</v>
-      </c>
-      <c r="BT25">
-        <v>10.5</v>
-      </c>
-      <c r="BU25">
-        <v>4.8</v>
-      </c>
-      <c r="BV25">
-        <v>34</v>
-      </c>
-      <c r="BW25">
-        <v>1.91</v>
-      </c>
-      <c r="BX25">
-        <v>40</v>
-      </c>
       <c r="BY25">
-        <v>1.93</v>
+        <v>7.2</v>
       </c>
       <c r="BZ25">
         <v>19</v>
       </c>
       <c r="CA25">
+        <v>6.2</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" t="s">
+        <v>157</v>
+      </c>
+      <c r="F26">
+        <v>2.96</v>
+      </c>
+      <c r="G26">
+        <v>3.05</v>
+      </c>
+      <c r="H26">
+        <v>2.34</v>
+      </c>
+      <c r="I26">
+        <v>2.42</v>
+      </c>
+      <c r="J26">
+        <v>3.95</v>
+      </c>
+      <c r="K26">
+        <v>4.2</v>
+      </c>
+      <c r="L26">
+        <v>1.29</v>
+      </c>
+      <c r="M26">
+        <v>1.04</v>
+      </c>
+      <c r="N26">
+        <v>5.8</v>
+      </c>
+      <c r="O26">
+        <v>1.19</v>
+      </c>
+      <c r="P26">
+        <v>2.6</v>
+      </c>
+      <c r="Q26">
+        <v>1.59</v>
+      </c>
+      <c r="R26">
+        <v>1.64</v>
+      </c>
+      <c r="S26">
+        <v>2.48</v>
+      </c>
+      <c r="T26">
+        <v>1.54</v>
+      </c>
+      <c r="U26">
+        <v>2.66</v>
+      </c>
+      <c r="V26">
+        <v>1.7</v>
+      </c>
+      <c r="W26">
+        <v>1.48</v>
+      </c>
+      <c r="X26">
+        <v>27</v>
+      </c>
+      <c r="Y26">
+        <v>18</v>
+      </c>
+      <c r="Z26">
+        <v>19.5</v>
+      </c>
+      <c r="AA26">
+        <v>34</v>
+      </c>
+      <c r="AB26">
+        <v>23</v>
+      </c>
+      <c r="AC26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD26">
+        <v>12</v>
+      </c>
+      <c r="AE26">
+        <v>26</v>
+      </c>
+      <c r="AF26">
+        <v>26</v>
+      </c>
+      <c r="AG26">
+        <v>14</v>
+      </c>
+      <c r="AH26">
+        <v>15</v>
+      </c>
+      <c r="AI26">
+        <v>30</v>
+      </c>
+      <c r="AJ26">
+        <v>160</v>
+      </c>
+      <c r="AK26">
+        <v>34</v>
+      </c>
+      <c r="AL26">
+        <v>38</v>
+      </c>
+      <c r="AM26">
+        <v>260</v>
+      </c>
+      <c r="AN26">
+        <v>18.5</v>
+      </c>
+      <c r="AO26">
+        <v>14</v>
+      </c>
+      <c r="AP26">
+        <v>18</v>
+      </c>
+      <c r="AQ26">
+        <v>13.5</v>
+      </c>
+      <c r="AR26">
+        <v>14</v>
+      </c>
+      <c r="AS26">
+        <v>21</v>
+      </c>
+      <c r="AT26">
+        <v>15.5</v>
+      </c>
+      <c r="AU26">
+        <v>8.6</v>
+      </c>
+      <c r="AV26">
+        <v>10.5</v>
+      </c>
+      <c r="AW26">
+        <v>18.5</v>
+      </c>
+      <c r="AX26">
+        <v>20</v>
+      </c>
+      <c r="AY26">
+        <v>12</v>
+      </c>
+      <c r="AZ26">
+        <v>13</v>
+      </c>
+      <c r="BA26">
+        <v>19</v>
+      </c>
+      <c r="BB26">
+        <v>26</v>
+      </c>
+      <c r="BC26">
+        <v>18.5</v>
+      </c>
+      <c r="BD26">
+        <v>22</v>
+      </c>
+      <c r="BE26">
+        <v>30</v>
+      </c>
+      <c r="BF26">
+        <v>15.5</v>
+      </c>
+      <c r="BG26">
+        <v>11</v>
+      </c>
+      <c r="BH26">
+        <v>4.6</v>
+      </c>
+      <c r="BI26">
+        <v>3.45</v>
+      </c>
+      <c r="BJ26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK26">
+        <v>4.6</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>8.6</v>
+      </c>
+      <c r="BN26">
+        <v>7</v>
+      </c>
+      <c r="BO26">
+        <v>5.7</v>
+      </c>
+      <c r="BP26">
+        <v>22</v>
+      </c>
+      <c r="BQ26">
+        <v>6.6</v>
+      </c>
+      <c r="BR26">
+        <v>28</v>
+      </c>
+      <c r="BS26">
+        <v>7.2</v>
+      </c>
+      <c r="BT26">
+        <v>6</v>
+      </c>
+      <c r="BU26">
+        <v>4.9</v>
+      </c>
+      <c r="BV26">
+        <v>16.5</v>
+      </c>
+      <c r="BW26">
+        <v>6</v>
+      </c>
+      <c r="BX26">
+        <v>24</v>
+      </c>
+      <c r="BY26">
+        <v>6.8</v>
+      </c>
+      <c r="BZ26">
+        <v>16.5</v>
+      </c>
+      <c r="CA26">
+        <v>6</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27">
+        <v>2.26</v>
+      </c>
+      <c r="G27">
+        <v>2.32</v>
+      </c>
+      <c r="H27">
+        <v>3.3</v>
+      </c>
+      <c r="I27">
+        <v>3.45</v>
+      </c>
+      <c r="J27">
+        <v>3.7</v>
+      </c>
+      <c r="K27">
+        <v>3.85</v>
+      </c>
+      <c r="L27">
+        <v>1.36</v>
+      </c>
+      <c r="M27">
+        <v>1.06</v>
+      </c>
+      <c r="N27">
+        <v>4.4</v>
+      </c>
+      <c r="O27">
+        <v>1.27</v>
+      </c>
+      <c r="P27">
+        <v>2.18</v>
+      </c>
+      <c r="Q27">
+        <v>1.81</v>
+      </c>
+      <c r="R27">
+        <v>1.46</v>
+      </c>
+      <c r="S27">
+        <v>3.05</v>
+      </c>
+      <c r="T27">
+        <v>1.67</v>
+      </c>
+      <c r="U27">
+        <v>2.36</v>
+      </c>
+      <c r="V27">
+        <v>1.41</v>
+      </c>
+      <c r="W27">
+        <v>1.75</v>
+      </c>
+      <c r="X27">
+        <v>20</v>
+      </c>
+      <c r="Y27">
+        <v>15.5</v>
+      </c>
+      <c r="Z27">
+        <v>30</v>
+      </c>
+      <c r="AA27">
+        <v>470</v>
+      </c>
+      <c r="AB27">
+        <v>13</v>
+      </c>
+      <c r="AC27">
+        <v>8.6</v>
+      </c>
+      <c r="AD27">
+        <v>14.5</v>
+      </c>
+      <c r="AE27">
+        <v>44</v>
+      </c>
+      <c r="AF27">
+        <v>15.5</v>
+      </c>
+      <c r="AG27">
+        <v>12</v>
+      </c>
+      <c r="AH27">
+        <v>21</v>
+      </c>
+      <c r="AI27">
+        <v>55</v>
+      </c>
+      <c r="AJ27">
+        <v>38</v>
+      </c>
+      <c r="AK27">
+        <v>27</v>
+      </c>
+      <c r="AL27">
+        <v>40</v>
+      </c>
+      <c r="AM27">
+        <v>95</v>
+      </c>
+      <c r="AN27">
+        <v>19.5</v>
+      </c>
+      <c r="AO27">
+        <v>50</v>
+      </c>
+      <c r="AP27">
+        <v>15.5</v>
+      </c>
+      <c r="AQ27">
+        <v>13</v>
+      </c>
+      <c r="AR27">
+        <v>21</v>
+      </c>
+      <c r="AS27">
+        <v>40</v>
+      </c>
+      <c r="AT27">
+        <v>10</v>
+      </c>
+      <c r="AU27">
+        <v>7.6</v>
+      </c>
+      <c r="AV27">
+        <v>12.5</v>
+      </c>
+      <c r="AW27">
+        <v>22</v>
+      </c>
+      <c r="AX27">
+        <v>13.5</v>
+      </c>
+      <c r="AY27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ27">
+        <v>12.5</v>
+      </c>
+      <c r="BA27">
+        <v>25</v>
+      </c>
+      <c r="BB27">
+        <v>21</v>
+      </c>
+      <c r="BC27">
+        <v>16</v>
+      </c>
+      <c r="BD27">
+        <v>23</v>
+      </c>
+      <c r="BE27">
+        <v>38</v>
+      </c>
+      <c r="BF27">
+        <v>14.5</v>
+      </c>
+      <c r="BG27">
+        <v>19.5</v>
+      </c>
+      <c r="BH27">
+        <v>4.4</v>
+      </c>
+      <c r="BI27">
+        <v>2.98</v>
+      </c>
+      <c r="BJ27">
+        <v>9</v>
+      </c>
+      <c r="BK27">
+        <v>5.8</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>6</v>
+      </c>
+      <c r="BN27">
+        <v>6.4</v>
+      </c>
+      <c r="BO27">
+        <v>4.7</v>
+      </c>
+      <c r="BP27">
+        <v>16</v>
+      </c>
+      <c r="BQ27">
+        <v>4.5</v>
+      </c>
+      <c r="BR27">
+        <v>40</v>
+      </c>
+      <c r="BS27">
+        <v>5.1</v>
+      </c>
+      <c r="BT27">
+        <v>8</v>
+      </c>
+      <c r="BU27">
+        <v>4.4</v>
+      </c>
+      <c r="BV27">
+        <v>38</v>
+      </c>
+      <c r="BW27">
+        <v>5</v>
+      </c>
+      <c r="BX27">
+        <v>50</v>
+      </c>
+      <c r="BY27">
+        <v>5.3</v>
+      </c>
+      <c r="BZ27">
+        <v>22</v>
+      </c>
+      <c r="CA27">
+        <v>4.9</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28">
+        <v>2.96</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28">
+        <v>2.32</v>
+      </c>
+      <c r="I28">
+        <v>2.36</v>
+      </c>
+      <c r="J28">
+        <v>4.1</v>
+      </c>
+      <c r="K28">
+        <v>4.3</v>
+      </c>
+      <c r="L28">
+        <v>1.22</v>
+      </c>
+      <c r="M28">
+        <v>1.02</v>
+      </c>
+      <c r="N28">
+        <v>7.6</v>
+      </c>
+      <c r="O28">
+        <v>1.13</v>
+      </c>
+      <c r="P28">
+        <v>3.25</v>
+      </c>
+      <c r="Q28">
+        <v>1.42</v>
+      </c>
+      <c r="R28">
+        <v>1.9</v>
+      </c>
+      <c r="S28">
+        <v>2.04</v>
+      </c>
+      <c r="T28">
+        <v>1.41</v>
+      </c>
+      <c r="U28">
+        <v>3.25</v>
+      </c>
+      <c r="V28">
+        <v>1.73</v>
+      </c>
+      <c r="W28">
+        <v>1.5</v>
+      </c>
+      <c r="X28">
+        <v>34</v>
+      </c>
+      <c r="Y28">
+        <v>21</v>
+      </c>
+      <c r="Z28">
+        <v>22</v>
+      </c>
+      <c r="AA28">
+        <v>36</v>
+      </c>
+      <c r="AB28">
+        <v>26</v>
+      </c>
+      <c r="AC28">
+        <v>11</v>
+      </c>
+      <c r="AD28">
+        <v>12.5</v>
+      </c>
+      <c r="AE28">
+        <v>21</v>
+      </c>
+      <c r="AF28">
+        <v>29</v>
+      </c>
+      <c r="AG28">
+        <v>14</v>
+      </c>
+      <c r="AH28">
+        <v>13.5</v>
+      </c>
+      <c r="AI28">
+        <v>25</v>
+      </c>
+      <c r="AJ28">
+        <v>60</v>
+      </c>
+      <c r="AK28">
+        <v>27</v>
+      </c>
+      <c r="AL28">
+        <v>42</v>
+      </c>
+      <c r="AM28">
+        <v>46</v>
+      </c>
+      <c r="AN28">
+        <v>13</v>
+      </c>
+      <c r="AO28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AP28">
+        <v>30</v>
+      </c>
+      <c r="AQ28">
+        <v>18.5</v>
+      </c>
+      <c r="AR28">
+        <v>20</v>
+      </c>
+      <c r="AS28">
+        <v>23</v>
+      </c>
+      <c r="AT28">
+        <v>22</v>
+      </c>
+      <c r="AU28">
+        <v>10</v>
+      </c>
+      <c r="AV28">
+        <v>11</v>
+      </c>
+      <c r="AW28">
+        <v>18</v>
+      </c>
+      <c r="AX28">
+        <v>26</v>
+      </c>
+      <c r="AY28">
+        <v>12.5</v>
+      </c>
+      <c r="AZ28">
+        <v>12.5</v>
+      </c>
+      <c r="BA28">
+        <v>21</v>
+      </c>
+      <c r="BB28">
+        <v>40</v>
+      </c>
+      <c r="BC28">
+        <v>23</v>
+      </c>
+      <c r="BD28">
+        <v>24</v>
+      </c>
+      <c r="BE28">
+        <v>36</v>
+      </c>
+      <c r="BF28">
+        <v>12</v>
+      </c>
+      <c r="BG28">
+        <v>8.4</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>2.1</v>
+      </c>
+      <c r="BJ28">
+        <v>11.5</v>
+      </c>
+      <c r="BK28">
+        <v>5.1</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>2.04</v>
+      </c>
+      <c r="BN28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BO28">
+        <v>4.7</v>
+      </c>
+      <c r="BP28">
+        <v>26</v>
+      </c>
+      <c r="BQ28">
+        <v>1.95</v>
+      </c>
+      <c r="BR28">
+        <v>32</v>
+      </c>
+      <c r="BS28">
+        <v>1.98</v>
+      </c>
+      <c r="BT28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU28">
+        <v>4.3</v>
+      </c>
+      <c r="BV28">
+        <v>21</v>
+      </c>
+      <c r="BW28">
+        <v>1.92</v>
+      </c>
+      <c r="BX28">
+        <v>29</v>
+      </c>
+      <c r="BY28">
+        <v>1.97</v>
+      </c>
+      <c r="BZ28">
+        <v>17</v>
+      </c>
+      <c r="CA28">
+        <v>1.88</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29">
+        <v>1.69</v>
+      </c>
+      <c r="G29">
+        <v>1.73</v>
+      </c>
+      <c r="H29">
+        <v>5.1</v>
+      </c>
+      <c r="I29">
+        <v>5.3</v>
+      </c>
+      <c r="J29">
+        <v>4.3</v>
+      </c>
+      <c r="K29">
+        <v>4.6</v>
+      </c>
+      <c r="L29">
+        <v>1.29</v>
+      </c>
+      <c r="M29">
+        <v>1.04</v>
+      </c>
+      <c r="N29">
+        <v>5.5</v>
+      </c>
+      <c r="O29">
+        <v>1.2</v>
+      </c>
+      <c r="P29">
+        <v>2.56</v>
+      </c>
+      <c r="Q29">
+        <v>1.6</v>
+      </c>
+      <c r="R29">
+        <v>1.62</v>
+      </c>
+      <c r="S29">
+        <v>2.52</v>
+      </c>
+      <c r="T29">
+        <v>1.64</v>
+      </c>
+      <c r="U29">
+        <v>2.42</v>
+      </c>
+      <c r="V29">
+        <v>1.23</v>
+      </c>
+      <c r="W29">
+        <v>2.38</v>
+      </c>
+      <c r="X29">
+        <v>25</v>
+      </c>
+      <c r="Y29">
+        <v>25</v>
+      </c>
+      <c r="Z29">
+        <v>44</v>
+      </c>
+      <c r="AA29">
+        <v>1000</v>
+      </c>
+      <c r="AB29">
+        <v>12.5</v>
+      </c>
+      <c r="AC29">
+        <v>10.5</v>
+      </c>
+      <c r="AD29">
+        <v>21</v>
+      </c>
+      <c r="AE29">
+        <v>60</v>
+      </c>
+      <c r="AF29">
+        <v>13.5</v>
+      </c>
+      <c r="AG29">
+        <v>10.5</v>
+      </c>
+      <c r="AH29">
+        <v>17.5</v>
+      </c>
+      <c r="AI29">
+        <v>55</v>
+      </c>
+      <c r="AJ29">
+        <v>19</v>
+      </c>
+      <c r="AK29">
+        <v>17</v>
+      </c>
+      <c r="AL29">
+        <v>28</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>7.4</v>
+      </c>
+      <c r="AO29">
+        <v>48</v>
+      </c>
+      <c r="AP29">
+        <v>21</v>
+      </c>
+      <c r="AQ29">
+        <v>20</v>
+      </c>
+      <c r="AR29">
+        <v>25</v>
+      </c>
+      <c r="AS29">
+        <v>55</v>
+      </c>
+      <c r="AT29">
+        <v>10.5</v>
+      </c>
+      <c r="AU29">
+        <v>9.4</v>
+      </c>
+      <c r="AV29">
+        <v>16.5</v>
+      </c>
+      <c r="AW29">
+        <v>32</v>
+      </c>
+      <c r="AX29">
+        <v>11</v>
+      </c>
+      <c r="AY29">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ29">
+        <v>14.5</v>
+      </c>
+      <c r="BA29">
+        <v>30</v>
+      </c>
+      <c r="BB29">
+        <v>16</v>
+      </c>
+      <c r="BC29">
+        <v>14.5</v>
+      </c>
+      <c r="BD29">
+        <v>18.5</v>
+      </c>
+      <c r="BE29">
+        <v>36</v>
+      </c>
+      <c r="BF29">
+        <v>6.6</v>
+      </c>
+      <c r="BG29">
+        <v>27</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>2.06</v>
+      </c>
+      <c r="BJ29">
+        <v>12.5</v>
+      </c>
+      <c r="BK29">
+        <v>1.77</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>2.06</v>
+      </c>
+      <c r="BN29">
+        <v>6.2</v>
+      </c>
+      <c r="BO29">
+        <v>3.3</v>
+      </c>
+      <c r="BP29">
+        <v>15</v>
+      </c>
+      <c r="BQ29">
+        <v>1.81</v>
+      </c>
+      <c r="BR29">
+        <v>29</v>
+      </c>
+      <c r="BS29">
+        <v>1.93</v>
+      </c>
+      <c r="BT29">
+        <v>12.5</v>
+      </c>
+      <c r="BU29">
+        <v>1.77</v>
+      </c>
+      <c r="BV29">
+        <v>50</v>
+      </c>
+      <c r="BW29">
+        <v>1.98</v>
+      </c>
+      <c r="BX29">
+        <v>50</v>
+      </c>
+      <c r="BY29">
+        <v>1.98</v>
+      </c>
+      <c r="BZ29">
+        <v>19</v>
+      </c>
+      <c r="CA29">
+        <v>1.86</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" t="s">
+        <v>161</v>
+      </c>
+      <c r="F30">
+        <v>2.52</v>
+      </c>
+      <c r="G30">
+        <v>2.56</v>
+      </c>
+      <c r="H30">
+        <v>2.66</v>
+      </c>
+      <c r="I30">
+        <v>2.7</v>
+      </c>
+      <c r="J30">
+        <v>4.1</v>
+      </c>
+      <c r="K30">
+        <v>4.3</v>
+      </c>
+      <c r="L30">
+        <v>1.23</v>
+      </c>
+      <c r="M30">
+        <v>1.03</v>
+      </c>
+      <c r="N30">
+        <v>7.2</v>
+      </c>
+      <c r="O30">
+        <v>1.14</v>
+      </c>
+      <c r="P30">
+        <v>3.15</v>
+      </c>
+      <c r="Q30">
+        <v>1.45</v>
+      </c>
+      <c r="R30">
+        <v>1.86</v>
+      </c>
+      <c r="S30">
+        <v>2.12</v>
+      </c>
+      <c r="T30">
+        <v>1.43</v>
+      </c>
+      <c r="U30">
+        <v>3.1</v>
+      </c>
+      <c r="V30">
+        <v>1.58</v>
+      </c>
+      <c r="W30">
+        <v>1.64</v>
+      </c>
+      <c r="X30">
+        <v>34</v>
+      </c>
+      <c r="Y30">
+        <v>21</v>
+      </c>
+      <c r="Z30">
+        <v>32</v>
+      </c>
+      <c r="AA30">
+        <v>44</v>
+      </c>
+      <c r="AB30">
+        <v>21</v>
+      </c>
+      <c r="AC30">
+        <v>11.5</v>
+      </c>
+      <c r="AD30">
+        <v>14</v>
+      </c>
+      <c r="AE30">
+        <v>25</v>
+      </c>
+      <c r="AF30">
+        <v>24</v>
+      </c>
+      <c r="AG30">
+        <v>13</v>
+      </c>
+      <c r="AH30">
+        <v>14.5</v>
+      </c>
+      <c r="AI30">
+        <v>27</v>
+      </c>
+      <c r="AJ30">
+        <v>38</v>
+      </c>
+      <c r="AK30">
+        <v>23</v>
+      </c>
+      <c r="AL30">
+        <v>26</v>
+      </c>
+      <c r="AM30">
+        <v>42</v>
+      </c>
+      <c r="AN30">
+        <v>11</v>
+      </c>
+      <c r="AO30">
+        <v>12.5</v>
+      </c>
+      <c r="AP30">
+        <v>22</v>
+      </c>
+      <c r="AQ30">
+        <v>17.5</v>
+      </c>
+      <c r="AR30">
+        <v>21</v>
+      </c>
+      <c r="AS30">
+        <v>26</v>
+      </c>
+      <c r="AT30">
+        <v>17.5</v>
+      </c>
+      <c r="AU30">
+        <v>10</v>
+      </c>
+      <c r="AV30">
+        <v>11.5</v>
+      </c>
+      <c r="AW30">
+        <v>20</v>
+      </c>
+      <c r="AX30">
+        <v>19.5</v>
+      </c>
+      <c r="AY30">
+        <v>11.5</v>
+      </c>
+      <c r="AZ30">
+        <v>12.5</v>
+      </c>
+      <c r="BA30">
+        <v>18.5</v>
+      </c>
+      <c r="BB30">
+        <v>23</v>
+      </c>
+      <c r="BC30">
+        <v>19.5</v>
+      </c>
+      <c r="BD30">
+        <v>21</v>
+      </c>
+      <c r="BE30">
+        <v>30</v>
+      </c>
+      <c r="BF30">
+        <v>9.6</v>
+      </c>
+      <c r="BG30">
+        <v>11</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
+        <v>2.08</v>
+      </c>
+      <c r="BJ30">
+        <v>11.5</v>
+      </c>
+      <c r="BK30">
+        <v>5.1</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>2.04</v>
+      </c>
+      <c r="BN30">
+        <v>9</v>
+      </c>
+      <c r="BO30">
+        <v>4.3</v>
+      </c>
+      <c r="BP30">
+        <v>23</v>
+      </c>
+      <c r="BQ30">
+        <v>1.91</v>
+      </c>
+      <c r="BR30">
+        <v>30</v>
+      </c>
+      <c r="BS30">
+        <v>1.95</v>
+      </c>
+      <c r="BT30">
+        <v>9.6</v>
+      </c>
+      <c r="BU30">
+        <v>4.3</v>
+      </c>
+      <c r="BV30">
+        <v>25</v>
+      </c>
+      <c r="BW30">
+        <v>1.93</v>
+      </c>
+      <c r="BX30">
+        <v>30</v>
+      </c>
+      <c r="BY30">
+        <v>1.95</v>
+      </c>
+      <c r="BZ30">
+        <v>17.5</v>
+      </c>
+      <c r="CA30">
+        <v>1.86</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" t="s">
+        <v>102</v>
+      </c>
+      <c r="D31" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" t="s">
+        <v>162</v>
+      </c>
+      <c r="F31">
+        <v>2.02</v>
+      </c>
+      <c r="G31">
+        <v>2.06</v>
+      </c>
+      <c r="H31">
+        <v>3.5</v>
+      </c>
+      <c r="I31">
+        <v>3.65</v>
+      </c>
+      <c r="J31">
+        <v>4.2</v>
+      </c>
+      <c r="K31">
+        <v>4.4</v>
+      </c>
+      <c r="L31">
+        <v>1.25</v>
+      </c>
+      <c r="M31">
+        <v>1.03</v>
+      </c>
+      <c r="N31">
+        <v>6.4</v>
+      </c>
+      <c r="O31">
+        <v>1.17</v>
+      </c>
+      <c r="P31">
+        <v>2.88</v>
+      </c>
+      <c r="Q31">
+        <v>1.5</v>
+      </c>
+      <c r="R31">
+        <v>1.76</v>
+      </c>
+      <c r="S31">
+        <v>2.24</v>
+      </c>
+      <c r="T31">
+        <v>1.5</v>
+      </c>
+      <c r="U31">
+        <v>2.86</v>
+      </c>
+      <c r="V31">
+        <v>1.37</v>
+      </c>
+      <c r="W31">
+        <v>1.93</v>
+      </c>
+      <c r="X31">
+        <v>55</v>
+      </c>
+      <c r="Y31">
+        <v>23</v>
+      </c>
+      <c r="Z31">
+        <v>32</v>
+      </c>
+      <c r="AA31">
+        <v>80</v>
+      </c>
+      <c r="AB31">
+        <v>16</v>
+      </c>
+      <c r="AC31">
+        <v>10.5</v>
+      </c>
+      <c r="AD31">
+        <v>16</v>
+      </c>
+      <c r="AE31">
+        <v>34</v>
+      </c>
+      <c r="AF31">
+        <v>17.5</v>
+      </c>
+      <c r="AG31">
+        <v>11.5</v>
+      </c>
+      <c r="AH31">
+        <v>15</v>
+      </c>
+      <c r="AI31">
+        <v>34</v>
+      </c>
+      <c r="AJ31">
+        <v>27</v>
+      </c>
+      <c r="AK31">
+        <v>18</v>
+      </c>
+      <c r="AL31">
+        <v>24</v>
+      </c>
+      <c r="AM31">
+        <v>190</v>
+      </c>
+      <c r="AN31">
+        <v>8.6</v>
+      </c>
+      <c r="AO31">
+        <v>21</v>
+      </c>
+      <c r="AP31">
+        <v>21</v>
+      </c>
+      <c r="AQ31">
+        <v>19.5</v>
+      </c>
+      <c r="AR31">
+        <v>22</v>
+      </c>
+      <c r="AS31">
+        <v>42</v>
+      </c>
+      <c r="AT31">
+        <v>14</v>
+      </c>
+      <c r="AU31">
+        <v>9.4</v>
+      </c>
+      <c r="AV31">
+        <v>13.5</v>
+      </c>
+      <c r="AW31">
+        <v>23</v>
+      </c>
+      <c r="AX31">
+        <v>15</v>
+      </c>
+      <c r="AY31">
+        <v>10</v>
+      </c>
+      <c r="AZ31">
+        <v>13</v>
+      </c>
+      <c r="BA31">
+        <v>22</v>
+      </c>
+      <c r="BB31">
+        <v>18.5</v>
+      </c>
+      <c r="BC31">
+        <v>16</v>
+      </c>
+      <c r="BD31">
+        <v>21</v>
+      </c>
+      <c r="BE31">
+        <v>34</v>
+      </c>
+      <c r="BF31">
+        <v>7.8</v>
+      </c>
+      <c r="BG31">
+        <v>18.5</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>3.25</v>
+      </c>
+      <c r="BJ31">
+        <v>12.5</v>
+      </c>
+      <c r="BK31">
+        <v>5.3</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.99</v>
+      </c>
+      <c r="BN31">
+        <v>7.8</v>
+      </c>
+      <c r="BO31">
+        <v>3.6</v>
+      </c>
+      <c r="BP31">
+        <v>19</v>
+      </c>
+      <c r="BQ31">
         <v>1.83</v>
       </c>
-      <c r="CB25" t="s">
-        <v>147</v>
+      <c r="BR31">
+        <v>30</v>
+      </c>
+      <c r="BS31">
+        <v>1.9</v>
+      </c>
+      <c r="BT31">
+        <v>10.5</v>
+      </c>
+      <c r="BU31">
+        <v>4.8</v>
+      </c>
+      <c r="BV31">
+        <v>34</v>
+      </c>
+      <c r="BW31">
+        <v>1.91</v>
+      </c>
+      <c r="BX31">
+        <v>40</v>
+      </c>
+      <c r="BY31">
+        <v>1.93</v>
+      </c>
+      <c r="BZ31">
+        <v>19</v>
+      </c>
+      <c r="CA31">
+        <v>1.83</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="168">
   <si>
     <t>League</t>
   </si>
@@ -340,6 +340,9 @@
     <t>Shanghai Port FC</t>
   </si>
   <si>
+    <t>FK Graficar</t>
+  </si>
+  <si>
     <t>FK Vrsac</t>
   </si>
   <si>
@@ -355,6 +358,9 @@
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
+    <t>FK Borac Cacak</t>
+  </si>
+  <si>
     <t>Metalac Gornji Milanovac</t>
   </si>
   <si>
@@ -367,12 +373,12 @@
     <t>Aguilas Doradas</t>
   </si>
   <si>
+    <t>Coquimbo Unido</t>
+  </si>
+  <si>
     <t>Cerro Porteno</t>
   </si>
   <si>
-    <t>Coquimbo Unido</t>
-  </si>
-  <si>
     <t>Fortaleza EC</t>
   </si>
   <si>
@@ -430,6 +436,9 @@
     <t>Dalian Yingbo</t>
   </si>
   <si>
+    <t>FK Loznica</t>
+  </si>
+  <si>
     <t>FK Dubocica</t>
   </si>
   <si>
@@ -445,6 +454,9 @@
     <t>Marumo Gallants FC</t>
   </si>
   <si>
+    <t>FK Proleter Zrenjanin</t>
+  </si>
+  <si>
     <t>Fk Smederevo</t>
   </si>
   <si>
@@ -457,12 +469,12 @@
     <t>Llaneros FC</t>
   </si>
   <si>
+    <t>CA Platense</t>
+  </si>
+  <si>
     <t>SE Palmeiras</t>
   </si>
   <si>
-    <t>CA Platense</t>
-  </si>
-  <si>
     <t>Sao Bernardo</t>
   </si>
   <si>
@@ -505,7 +517,7 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-18 09:04:10</t>
+    <t>2026-08-18 11:12:28</t>
   </si>
 </sst>
 </file>
@@ -837,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB31"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1096,25 +1108,25 @@
         <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
         <v>1.51</v>
@@ -1126,31 +1138,31 @@
         <v>3.15</v>
       </c>
       <c r="O2">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Q2">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
         <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T2">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="U2">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X2">
         <v>11</v>
@@ -1165,16 +1177,16 @@
         <v>90</v>
       </c>
       <c r="AB2">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD2">
         <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF2">
         <v>13</v>
@@ -1183,28 +1195,28 @@
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI2">
         <v>75</v>
       </c>
       <c r="AJ2">
+        <v>38</v>
+      </c>
+      <c r="AK2">
         <v>29</v>
       </c>
-      <c r="AK2">
-        <v>28</v>
-      </c>
       <c r="AL2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN2">
         <v>25</v>
       </c>
       <c r="AO2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP2">
         <v>9.199999999999999</v>
@@ -1216,7 +1228,7 @@
         <v>23</v>
       </c>
       <c r="AS2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT2">
         <v>7.6</v>
@@ -1234,16 +1246,16 @@
         <v>12</v>
       </c>
       <c r="AY2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BC2">
         <v>24</v>
@@ -1252,7 +1264,7 @@
         <v>42</v>
       </c>
       <c r="BE2">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF2">
         <v>21</v>
@@ -1282,13 +1294,13 @@
         <v>5.6</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP2">
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1300,7 +1312,7 @@
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BV2">
         <v>1000</v>
@@ -1309,7 +1321,7 @@
         <v>5.5</v>
       </c>
       <c r="BX2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
         <v>5.8</v>
@@ -1321,7 +1333,7 @@
         <v>5.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1338,61 +1350,61 @@
         <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F3">
         <v>3.4</v>
       </c>
       <c r="G3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H3">
         <v>2.58</v>
       </c>
       <c r="I3">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J3">
         <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L3">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M3">
         <v>1.13</v>
       </c>
       <c r="N3">
+        <v>2.68</v>
+      </c>
+      <c r="O3">
+        <v>1.56</v>
+      </c>
+      <c r="P3">
+        <v>1.56</v>
+      </c>
+      <c r="Q3">
         <v>2.72</v>
-      </c>
-      <c r="O3">
-        <v>1.55</v>
-      </c>
-      <c r="P3">
-        <v>1.57</v>
-      </c>
-      <c r="Q3">
-        <v>2.7</v>
       </c>
       <c r="R3">
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X3">
         <v>9.199999999999999</v>
@@ -1407,7 +1419,7 @@
         <v>40</v>
       </c>
       <c r="AB3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3">
         <v>7</v>
@@ -1422,13 +1434,13 @@
         <v>21</v>
       </c>
       <c r="AG3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH3">
         <v>24</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
         <v>70</v>
@@ -1437,13 +1449,13 @@
         <v>55</v>
       </c>
       <c r="AL3">
+        <v>100</v>
+      </c>
+      <c r="AM3">
+        <v>210</v>
+      </c>
+      <c r="AN3">
         <v>80</v>
-      </c>
-      <c r="AM3">
-        <v>180</v>
-      </c>
-      <c r="AN3">
-        <v>70</v>
       </c>
       <c r="AO3">
         <v>42</v>
@@ -1473,16 +1485,16 @@
         <v>32</v>
       </c>
       <c r="AX3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AY3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3">
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BB3">
         <v>55</v>
@@ -1491,22 +1503,22 @@
         <v>40</v>
       </c>
       <c r="BD3">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BE3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF3">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="BG3">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BH3">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BI3">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3">
         <v>11</v>
@@ -1518,25 +1530,25 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>17</v>
+        <v>2.38</v>
       </c>
       <c r="BN3">
         <v>6.2</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BP3">
         <v>38</v>
       </c>
       <c r="BQ3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR3">
         <v>65</v>
       </c>
       <c r="BS3">
-        <v>14</v>
+        <v>2.3</v>
       </c>
       <c r="BT3">
         <v>5.2</v>
@@ -1548,22 +1560,22 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13</v>
+        <v>2.28</v>
       </c>
       <c r="BZ3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>13.5</v>
+        <v>2.28</v>
       </c>
       <c r="CB3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1580,31 +1592,31 @@
         <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F4">
+        <v>3.25</v>
+      </c>
+      <c r="G4">
+        <v>3.4</v>
+      </c>
+      <c r="H4">
+        <v>2.56</v>
+      </c>
+      <c r="I4">
+        <v>2.62</v>
+      </c>
+      <c r="J4">
         <v>3.15</v>
       </c>
-      <c r="G4">
-        <v>3.25</v>
-      </c>
-      <c r="H4">
-        <v>2.62</v>
-      </c>
-      <c r="I4">
-        <v>2.68</v>
-      </c>
-      <c r="J4">
+      <c r="K4">
         <v>3.2</v>
       </c>
-      <c r="K4">
-        <v>3.3</v>
-      </c>
       <c r="L4">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N4">
         <v>2.88</v>
@@ -1613,7 +1625,7 @@
         <v>1.5</v>
       </c>
       <c r="P4">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
         <v>2.58</v>
@@ -1628,19 +1640,19 @@
         <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W4">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X4">
         <v>9.6</v>
       </c>
       <c r="Y4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z4">
         <v>15</v>
@@ -1649,25 +1661,25 @@
         <v>42</v>
       </c>
       <c r="AB4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC4">
         <v>7</v>
       </c>
       <c r="AD4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE4">
         <v>38</v>
       </c>
       <c r="AF4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI4">
         <v>60</v>
@@ -1676,34 +1688,34 @@
         <v>65</v>
       </c>
       <c r="AK4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL4">
         <v>70</v>
       </c>
       <c r="AM4">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AN4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO4">
         <v>40</v>
       </c>
       <c r="AP4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4">
         <v>7.6</v>
       </c>
       <c r="AR4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT4">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU4">
         <v>6.2</v>
@@ -1712,40 +1724,40 @@
         <v>11</v>
       </c>
       <c r="AW4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY4">
         <v>13</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA4">
         <v>50</v>
       </c>
       <c r="BB4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC4">
         <v>40</v>
       </c>
       <c r="BD4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BE4">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BF4">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="BG4">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BH4">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BI4">
         <v>2.5</v>
@@ -1760,7 +1772,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN4">
         <v>6.2</v>
@@ -1772,13 +1784,13 @@
         <v>30</v>
       </c>
       <c r="BQ4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR4">
         <v>50</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT4">
         <v>5.3</v>
@@ -1790,22 +1802,22 @@
         <v>23</v>
       </c>
       <c r="BW4">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>44</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1822,22 +1834,22 @@
         <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F5">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="G5">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="H5">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="I5">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K5">
         <v>3.05</v>
@@ -1852,10 +1864,10 @@
         <v>2.54</v>
       </c>
       <c r="O5">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q5">
         <v>2.96</v>
@@ -1870,121 +1882,121 @@
         <v>2.28</v>
       </c>
       <c r="U5">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V5">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="X5">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="Y5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AA5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE5">
         <v>75</v>
       </c>
       <c r="AF5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ5">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AK5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL5">
         <v>80</v>
       </c>
       <c r="AM5">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AN5">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AO5">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AP5">
         <v>7</v>
       </c>
       <c r="AQ5">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>55</v>
       </c>
       <c r="AT5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV5">
+        <v>16</v>
+      </c>
+      <c r="AW5">
+        <v>46</v>
+      </c>
+      <c r="AX5">
+        <v>11.5</v>
+      </c>
+      <c r="AY5">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5">
+        <v>24</v>
+      </c>
+      <c r="BA5">
+        <v>60</v>
+      </c>
+      <c r="BB5">
+        <v>30</v>
+      </c>
+      <c r="BC5">
+        <v>32</v>
+      </c>
+      <c r="BD5">
+        <v>48</v>
+      </c>
+      <c r="BE5">
+        <v>16</v>
+      </c>
+      <c r="BF5">
+        <v>34</v>
+      </c>
+      <c r="BG5">
         <v>15</v>
-      </c>
-      <c r="AW5">
-        <v>42</v>
-      </c>
-      <c r="AX5">
-        <v>12</v>
-      </c>
-      <c r="AY5">
-        <v>11</v>
-      </c>
-      <c r="AZ5">
-        <v>19</v>
-      </c>
-      <c r="BA5">
-        <v>8</v>
-      </c>
-      <c r="BB5">
-        <v>27</v>
-      </c>
-      <c r="BC5">
-        <v>26</v>
-      </c>
-      <c r="BD5">
-        <v>42</v>
-      </c>
-      <c r="BE5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF5">
-        <v>12.5</v>
-      </c>
-      <c r="BG5">
-        <v>8</v>
       </c>
       <c r="BH5">
         <v>2.82</v>
@@ -1993,7 +2005,7 @@
         <v>2.24</v>
       </c>
       <c r="BJ5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BK5">
         <v>9.199999999999999</v>
@@ -2002,52 +2014,52 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP5">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BQ5">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS5">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BT5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV5">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BW5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY5">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA5">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2064,22 +2076,22 @@
         <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F6">
         <v>1.49</v>
       </c>
       <c r="G6">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H6">
         <v>6.8</v>
       </c>
       <c r="I6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
         <v>5.3</v>
@@ -2097,7 +2109,7 @@
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q6">
         <v>1.49</v>
@@ -2106,7 +2118,7 @@
         <v>1.77</v>
       </c>
       <c r="S6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T6">
         <v>1.67</v>
@@ -2115,10 +2127,10 @@
         <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W6">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X6">
         <v>32</v>
@@ -2196,7 +2208,7 @@
         <v>22</v>
       </c>
       <c r="AW6">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AX6">
         <v>10.5</v>
@@ -2289,7 +2301,7 @@
         <v>5.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2306,25 +2318,25 @@
         <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F7">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H7">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2333,34 +2345,34 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="P7">
         <v>1.07</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R7">
         <v>1.07</v>
       </c>
       <c r="S7">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
         <v>1.01</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2417,52 +2429,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2531,7 +2543,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2542,31 +2554,31 @@
         <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
         <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F8">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H8">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2575,34 +2587,34 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="R8">
         <v>1.07</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2716,64 +2728,64 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2790,25 +2802,25 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2817,31 +2829,31 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
         <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q9">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="R9">
         <v>1.07</v>
       </c>
       <c r="S9">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9">
         <v>1.01</v>
@@ -2958,64 +2970,64 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3032,25 +3044,25 @@
         <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3059,22 +3071,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
+        <v>1.1</v>
+      </c>
+      <c r="O10">
+        <v>1.01</v>
+      </c>
+      <c r="P10">
         <v>1.09</v>
       </c>
-      <c r="O10">
-        <v>1.01</v>
-      </c>
-      <c r="P10">
-        <v>1.08</v>
-      </c>
       <c r="Q10">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="R10">
         <v>1.07</v>
       </c>
       <c r="S10">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3083,10 +3095,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3200,99 +3212,99 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
         <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
         <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F11">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="G11">
-        <v>1.25</v>
+        <v>990</v>
       </c>
       <c r="H11">
-        <v>14</v>
+        <v>1.02</v>
       </c>
       <c r="I11">
-        <v>23</v>
+        <v>990</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="K11">
-        <v>8</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3301,142 +3313,142 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="O11">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="P11">
-        <v>2.36</v>
+        <v>1.09</v>
       </c>
       <c r="Q11">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="R11">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="S11">
-        <v>2.38</v>
+        <v>1.32</v>
       </c>
       <c r="T11">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
         <v>1000</v>
       </c>
       <c r="AB11">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3499,249 +3511,249 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
         <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F12">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>1.26</v>
       </c>
       <c r="H12">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="J12">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="K12">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M12">
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.07</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="P12">
-        <v>1.07</v>
+        <v>2.38</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R12">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="S12">
-        <v>1.48</v>
+        <v>2.48</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="CB12" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3752,31 +3764,31 @@
         <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
         <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3785,22 +3797,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="O13">
         <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q13">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="R13">
         <v>1.07</v>
       </c>
       <c r="S13">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3983,428 +3995,428 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
         <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
         <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F14">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="G14">
-        <v>1.37</v>
+        <v>990</v>
       </c>
       <c r="H14">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="I14">
-        <v>12</v>
+        <v>990</v>
       </c>
       <c r="J14">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="K14">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="L14">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="O14">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="P14">
-        <v>2.14</v>
+        <v>1.07</v>
       </c>
       <c r="Q14">
-        <v>1.85</v>
+        <v>1.02</v>
       </c>
       <c r="R14">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="S14">
-        <v>3.15</v>
+        <v>1.48</v>
       </c>
       <c r="T14">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W14">
-        <v>3.7</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>570</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>140</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>36</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>26</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>26</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
         <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
         <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F15">
-        <v>1.98</v>
+        <v>1.02</v>
       </c>
       <c r="G15">
-        <v>2.12</v>
+        <v>990</v>
       </c>
       <c r="H15">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="I15">
-        <v>4.7</v>
+        <v>990</v>
       </c>
       <c r="J15">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="K15">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
-        <v>3.15</v>
+        <v>1.11</v>
       </c>
       <c r="O15">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="P15">
-        <v>1.76</v>
+        <v>1.07</v>
       </c>
       <c r="Q15">
-        <v>2.14</v>
+        <v>1.27</v>
       </c>
       <c r="R15">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="S15">
-        <v>4</v>
+        <v>1.27</v>
       </c>
       <c r="T15">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="U15">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W15">
-        <v>1.9</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4467,1464 +4479,1464 @@
         <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
         <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
         <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F16">
-        <v>5.2</v>
+        <v>1.35</v>
       </c>
       <c r="G16">
-        <v>5.9</v>
+        <v>1.37</v>
       </c>
       <c r="H16">
-        <v>1.81</v>
+        <v>11.5</v>
       </c>
       <c r="I16">
-        <v>1.89</v>
+        <v>12</v>
       </c>
       <c r="J16">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="K16">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="L16">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="M16">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N16">
-        <v>2.66</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="P16">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="Q16">
-        <v>2.48</v>
+        <v>1.85</v>
       </c>
       <c r="R16">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="S16">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="T16">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U16">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="V16">
-        <v>2.12</v>
+        <v>1.09</v>
       </c>
       <c r="W16">
-        <v>1.2</v>
+        <v>3.75</v>
       </c>
       <c r="X16">
+        <v>17</v>
+      </c>
+      <c r="Y16">
+        <v>34</v>
+      </c>
+      <c r="Z16">
+        <v>110</v>
+      </c>
+      <c r="AA16">
+        <v>570</v>
+      </c>
+      <c r="AB16">
+        <v>8</v>
+      </c>
+      <c r="AC16">
+        <v>12.5</v>
+      </c>
+      <c r="AD16">
+        <v>42</v>
+      </c>
+      <c r="AE16">
+        <v>240</v>
+      </c>
+      <c r="AF16">
+        <v>7.2</v>
+      </c>
+      <c r="AG16">
+        <v>10.5</v>
+      </c>
+      <c r="AH16">
+        <v>36</v>
+      </c>
+      <c r="AI16">
+        <v>190</v>
+      </c>
+      <c r="AJ16">
+        <v>10</v>
+      </c>
+      <c r="AK16">
+        <v>15</v>
+      </c>
+      <c r="AL16">
+        <v>46</v>
+      </c>
+      <c r="AM16">
+        <v>240</v>
+      </c>
+      <c r="AN16">
+        <v>5.8</v>
+      </c>
+      <c r="AO16">
+        <v>400</v>
+      </c>
+      <c r="AP16">
+        <v>16</v>
+      </c>
+      <c r="AQ16">
+        <v>27</v>
+      </c>
+      <c r="AR16">
+        <v>42</v>
+      </c>
+      <c r="AS16">
+        <v>140</v>
+      </c>
+      <c r="AT16">
+        <v>7.6</v>
+      </c>
+      <c r="AU16">
+        <v>11.5</v>
+      </c>
+      <c r="AV16">
+        <v>38</v>
+      </c>
+      <c r="AW16">
+        <v>48</v>
+      </c>
+      <c r="AX16">
+        <v>7</v>
+      </c>
+      <c r="AY16">
+        <v>10</v>
+      </c>
+      <c r="AZ16">
+        <v>30</v>
+      </c>
+      <c r="BA16">
+        <v>46</v>
+      </c>
+      <c r="BB16">
         <v>9.800000000000001</v>
       </c>
-      <c r="Y16">
-        <v>6.6</v>
-      </c>
-      <c r="Z16">
-        <v>10</v>
-      </c>
-      <c r="AA16">
-        <v>21</v>
-      </c>
-      <c r="AB16">
+      <c r="BC16">
         <v>14</v>
       </c>
-      <c r="AC16">
-        <v>8.4</v>
-      </c>
-      <c r="AD16">
-        <v>11</v>
-      </c>
-      <c r="AE16">
-        <v>25</v>
-      </c>
-      <c r="AF16">
+      <c r="BD16">
+        <v>40</v>
+      </c>
+      <c r="BE16">
         <v>50</v>
       </c>
-      <c r="AG16">
-        <v>23</v>
-      </c>
-      <c r="AH16">
-        <v>28</v>
-      </c>
-      <c r="AI16">
-        <v>70</v>
-      </c>
-      <c r="AJ16">
-        <v>210</v>
-      </c>
-      <c r="AK16">
-        <v>130</v>
-      </c>
-      <c r="AL16">
-        <v>140</v>
-      </c>
-      <c r="AM16">
-        <v>260</v>
-      </c>
-      <c r="AN16">
-        <v>220</v>
-      </c>
-      <c r="AO16">
-        <v>20</v>
-      </c>
-      <c r="AP16">
-        <v>8.4</v>
-      </c>
-      <c r="AQ16">
-        <v>5.7</v>
-      </c>
-      <c r="AR16">
-        <v>8.6</v>
-      </c>
-      <c r="AS16">
-        <v>18</v>
-      </c>
-      <c r="AT16">
-        <v>11.5</v>
-      </c>
-      <c r="AU16">
-        <v>7.2</v>
-      </c>
-      <c r="AV16">
-        <v>9.4</v>
-      </c>
-      <c r="AW16">
-        <v>21</v>
-      </c>
-      <c r="AX16">
-        <v>36</v>
-      </c>
-      <c r="AY16">
-        <v>20</v>
-      </c>
-      <c r="AZ16">
-        <v>19.5</v>
-      </c>
-      <c r="BA16">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB16">
-        <v>11</v>
-      </c>
-      <c r="BC16">
-        <v>10.5</v>
-      </c>
-      <c r="BD16">
-        <v>10.5</v>
-      </c>
-      <c r="BE16">
-        <v>11</v>
-      </c>
       <c r="BF16">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="BG16">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="BH16">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="BI16">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="BJ16">
         <v>14</v>
       </c>
       <c r="BK16">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM16">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="BN16">
+        <v>3.55</v>
+      </c>
+      <c r="BO16">
+        <v>3.3</v>
+      </c>
+      <c r="BP16">
+        <v>7.4</v>
+      </c>
+      <c r="BQ16">
+        <v>6.6</v>
+      </c>
+      <c r="BR16">
+        <v>28</v>
+      </c>
+      <c r="BS16">
         <v>10.5</v>
       </c>
-      <c r="BO16">
-        <v>3.85</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>5.6</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>5.7</v>
-      </c>
       <c r="BT16">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="BU16">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV16">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="BW16">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="BX16">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="BY16">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="BZ16">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="CA16">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="CB16" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
         <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
         <v>118</v>
       </c>
       <c r="E17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F17">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="G17">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="H17">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I17">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="J17">
+        <v>3.35</v>
+      </c>
+      <c r="K17">
+        <v>3.8</v>
+      </c>
+      <c r="L17">
+        <v>1.4</v>
+      </c>
+      <c r="M17">
+        <v>1.09</v>
+      </c>
+      <c r="N17">
         <v>3.15</v>
       </c>
-      <c r="K17">
-        <v>3.2</v>
-      </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
-        <v>1.11</v>
-      </c>
-      <c r="N17">
-        <v>2.58</v>
-      </c>
       <c r="O17">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="P17">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="Q17">
-        <v>2.68</v>
+        <v>2.14</v>
       </c>
       <c r="R17">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="S17">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="T17">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="U17">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W17">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="X17">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="Y17">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Z17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AA17">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AB17">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC17">
         <v>8</v>
       </c>
       <c r="AD17">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE17">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF17">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH17">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AI17">
         <v>95</v>
       </c>
       <c r="AJ17">
+        <v>29</v>
+      </c>
+      <c r="AK17">
+        <v>32</v>
+      </c>
+      <c r="AL17">
+        <v>50</v>
+      </c>
+      <c r="AM17">
+        <v>150</v>
+      </c>
+      <c r="AN17">
+        <v>25</v>
+      </c>
+      <c r="AO17">
+        <v>100</v>
+      </c>
+      <c r="AP17">
+        <v>5.8</v>
+      </c>
+      <c r="AQ17">
+        <v>12</v>
+      </c>
+      <c r="AR17">
+        <v>7.8</v>
+      </c>
+      <c r="AS17">
+        <v>9.4</v>
+      </c>
+      <c r="AT17">
+        <v>7</v>
+      </c>
+      <c r="AU17">
+        <v>7</v>
+      </c>
+      <c r="AV17">
+        <v>15.5</v>
+      </c>
+      <c r="AW17">
+        <v>9</v>
+      </c>
+      <c r="AX17">
+        <v>10.5</v>
+      </c>
+      <c r="AY17">
+        <v>9.4</v>
+      </c>
+      <c r="AZ17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB17">
+        <v>21</v>
+      </c>
+      <c r="BC17">
+        <v>20</v>
+      </c>
+      <c r="BD17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE17">
+        <v>9.6</v>
+      </c>
+      <c r="BF17">
+        <v>16</v>
+      </c>
+      <c r="BG17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH17">
+        <v>3.5</v>
+      </c>
+      <c r="BI17">
+        <v>2.6</v>
+      </c>
+      <c r="BJ17">
+        <v>12</v>
+      </c>
+      <c r="BK17">
+        <v>3.95</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>5.7</v>
+      </c>
+      <c r="BN17">
+        <v>5.2</v>
+      </c>
+      <c r="BO17">
+        <v>3.7</v>
+      </c>
+      <c r="BP17">
+        <v>17.5</v>
+      </c>
+      <c r="BQ17">
+        <v>4.4</v>
+      </c>
+      <c r="BR17">
+        <v>38</v>
+      </c>
+      <c r="BS17">
+        <v>5.1</v>
+      </c>
+      <c r="BT17">
+        <v>8.6</v>
+      </c>
+      <c r="BU17">
+        <v>3.5</v>
+      </c>
+      <c r="BV17">
+        <v>46</v>
+      </c>
+      <c r="BW17">
+        <v>5.2</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>5.4</v>
+      </c>
+      <c r="BZ17">
         <v>36</v>
       </c>
-      <c r="AK17">
-        <v>34</v>
-      </c>
-      <c r="AL17">
-        <v>65</v>
-      </c>
-      <c r="AM17">
-        <v>220</v>
-      </c>
-      <c r="AN17">
-        <v>38</v>
-      </c>
-      <c r="AO17">
-        <v>95</v>
-      </c>
-      <c r="AP17">
-        <v>8</v>
-      </c>
-      <c r="AQ17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR17">
-        <v>21</v>
-      </c>
-      <c r="AS17">
-        <v>60</v>
-      </c>
-      <c r="AT17">
-        <v>6.4</v>
-      </c>
-      <c r="AU17">
-        <v>6.8</v>
-      </c>
-      <c r="AV17">
-        <v>14.5</v>
-      </c>
-      <c r="AW17">
-        <v>50</v>
-      </c>
-      <c r="AX17">
-        <v>11.5</v>
-      </c>
-      <c r="AY17">
-        <v>10.5</v>
-      </c>
-      <c r="AZ17">
-        <v>22</v>
-      </c>
-      <c r="BA17">
-        <v>60</v>
-      </c>
-      <c r="BB17">
-        <v>29</v>
-      </c>
-      <c r="BC17">
-        <v>29</v>
-      </c>
-      <c r="BD17">
-        <v>50</v>
-      </c>
-      <c r="BE17">
-        <v>10.5</v>
-      </c>
-      <c r="BF17">
-        <v>29</v>
-      </c>
-      <c r="BG17">
-        <v>55</v>
-      </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
-        <v>1.65</v>
-      </c>
-      <c r="BJ17">
-        <v>17</v>
-      </c>
-      <c r="BK17">
-        <v>1.51</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.65</v>
-      </c>
-      <c r="BN17">
-        <v>7</v>
-      </c>
-      <c r="BO17">
-        <v>3.45</v>
-      </c>
-      <c r="BP17">
-        <v>30</v>
-      </c>
-      <c r="BQ17">
-        <v>1.57</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>1.61</v>
-      </c>
-      <c r="BT17">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU17">
-        <v>4.4</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>1.61</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>1.62</v>
-      </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
       <c r="CA17">
-        <v>1.62</v>
+        <v>5.1</v>
       </c>
       <c r="CB17" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
         <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
         <v>119</v>
       </c>
       <c r="E18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F18">
-        <v>1.64</v>
+        <v>2.38</v>
       </c>
       <c r="G18">
-        <v>1.73</v>
+        <v>2.46</v>
       </c>
       <c r="H18">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="I18">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="J18">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="K18">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="L18">
+        <v>1.49</v>
+      </c>
+      <c r="M18">
+        <v>1.11</v>
+      </c>
+      <c r="N18">
+        <v>2.54</v>
+      </c>
+      <c r="O18">
+        <v>1.57</v>
+      </c>
+      <c r="P18">
+        <v>1.53</v>
+      </c>
+      <c r="Q18">
+        <v>2.68</v>
+      </c>
+      <c r="R18">
+        <v>1.18</v>
+      </c>
+      <c r="S18">
+        <v>5.6</v>
+      </c>
+      <c r="T18">
+        <v>2.18</v>
+      </c>
+      <c r="U18">
+        <v>1.71</v>
+      </c>
+      <c r="V18">
         <v>1.37</v>
       </c>
-      <c r="M18">
-        <v>1.09</v>
-      </c>
-      <c r="N18">
-        <v>3.15</v>
-      </c>
-      <c r="O18">
-        <v>1.34</v>
-      </c>
-      <c r="P18">
-        <v>1.71</v>
-      </c>
-      <c r="Q18">
-        <v>2.12</v>
-      </c>
-      <c r="R18">
-        <v>1.26</v>
-      </c>
-      <c r="S18">
-        <v>4.1</v>
-      </c>
-      <c r="T18">
-        <v>2.1</v>
-      </c>
-      <c r="U18">
-        <v>1.76</v>
-      </c>
-      <c r="V18">
-        <v>1.16</v>
-      </c>
       <c r="W18">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="X18">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y18">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z18">
+        <v>25</v>
+      </c>
+      <c r="AA18">
+        <v>85</v>
+      </c>
+      <c r="AB18">
+        <v>7.2</v>
+      </c>
+      <c r="AC18">
+        <v>8</v>
+      </c>
+      <c r="AD18">
+        <v>17</v>
+      </c>
+      <c r="AE18">
         <v>65</v>
       </c>
-      <c r="AA18">
-        <v>260</v>
-      </c>
-      <c r="AB18">
-        <v>7</v>
-      </c>
-      <c r="AC18">
-        <v>9.6</v>
-      </c>
-      <c r="AD18">
-        <v>28</v>
-      </c>
-      <c r="AE18">
-        <v>140</v>
-      </c>
       <c r="AF18">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AG18">
+        <v>12</v>
+      </c>
+      <c r="AH18">
+        <v>27</v>
+      </c>
+      <c r="AI18">
+        <v>95</v>
+      </c>
+      <c r="AJ18">
+        <v>36</v>
+      </c>
+      <c r="AK18">
+        <v>36</v>
+      </c>
+      <c r="AL18">
+        <v>70</v>
+      </c>
+      <c r="AM18">
+        <v>220</v>
+      </c>
+      <c r="AN18">
+        <v>38</v>
+      </c>
+      <c r="AO18">
+        <v>95</v>
+      </c>
+      <c r="AP18">
+        <v>8</v>
+      </c>
+      <c r="AQ18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR18">
+        <v>20</v>
+      </c>
+      <c r="AS18">
+        <v>10.5</v>
+      </c>
+      <c r="AT18">
+        <v>6.4</v>
+      </c>
+      <c r="AU18">
+        <v>6.8</v>
+      </c>
+      <c r="AV18">
+        <v>14.5</v>
+      </c>
+      <c r="AW18">
+        <v>50</v>
+      </c>
+      <c r="AX18">
+        <v>11.5</v>
+      </c>
+      <c r="AY18">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18">
+        <v>22</v>
+      </c>
+      <c r="BA18">
+        <v>60</v>
+      </c>
+      <c r="BB18">
+        <v>29</v>
+      </c>
+      <c r="BC18">
+        <v>29</v>
+      </c>
+      <c r="BD18">
+        <v>50</v>
+      </c>
+      <c r="BE18">
         <v>11</v>
       </c>
-      <c r="AH18">
-        <v>26</v>
-      </c>
-      <c r="AI18">
-        <v>140</v>
-      </c>
-      <c r="AJ18">
-        <v>17.5</v>
-      </c>
-      <c r="AK18">
-        <v>21</v>
-      </c>
-      <c r="AL18">
+      <c r="BF18">
+        <v>29</v>
+      </c>
+      <c r="BG18">
         <v>55</v>
       </c>
-      <c r="AM18">
-        <v>210</v>
-      </c>
-      <c r="AN18">
-        <v>13.5</v>
-      </c>
-      <c r="AO18">
-        <v>240</v>
-      </c>
-      <c r="AP18">
-        <v>10</v>
-      </c>
-      <c r="AQ18">
-        <v>15.5</v>
-      </c>
-      <c r="AR18">
-        <v>7.4</v>
-      </c>
-      <c r="AS18">
-        <v>8</v>
-      </c>
-      <c r="AT18">
-        <v>6</v>
-      </c>
-      <c r="AU18">
-        <v>7.6</v>
-      </c>
-      <c r="AV18">
-        <v>6.4</v>
-      </c>
-      <c r="AW18">
-        <v>7.8</v>
-      </c>
-      <c r="AX18">
-        <v>7.6</v>
-      </c>
-      <c r="AY18">
-        <v>9</v>
-      </c>
-      <c r="AZ18">
-        <v>21</v>
-      </c>
-      <c r="BA18">
-        <v>7.8</v>
-      </c>
-      <c r="BB18">
-        <v>14</v>
-      </c>
-      <c r="BC18">
-        <v>17.5</v>
-      </c>
-      <c r="BD18">
-        <v>7.2</v>
-      </c>
-      <c r="BE18">
-        <v>8</v>
-      </c>
-      <c r="BF18">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG18">
-        <v>8</v>
-      </c>
       <c r="BH18">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="BI18">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="BJ18">
         <v>12</v>
       </c>
       <c r="BK18">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BN18">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BO18">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP18">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BQ18">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BR18">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BS18">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BT18">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BU18">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW18">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX18">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BZ18">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="CA18">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="CB18" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
         <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
         <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F19">
-        <v>2.76</v>
+        <v>5.2</v>
       </c>
       <c r="G19">
-        <v>2.96</v>
+        <v>5.9</v>
       </c>
       <c r="H19">
-        <v>2.82</v>
+        <v>1.83</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>1.89</v>
       </c>
       <c r="J19">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K19">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M19">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N19">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="O19">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="P19">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q19">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="R19">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S19">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="U19">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="W19">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="X19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y19">
+        <v>6.6</v>
+      </c>
+      <c r="Z19">
+        <v>10</v>
+      </c>
+      <c r="AA19">
+        <v>21</v>
+      </c>
+      <c r="AB19">
+        <v>14</v>
+      </c>
+      <c r="AC19">
+        <v>8.4</v>
+      </c>
+      <c r="AD19">
+        <v>11</v>
+      </c>
+      <c r="AE19">
+        <v>25</v>
+      </c>
+      <c r="AF19">
+        <v>50</v>
+      </c>
+      <c r="AG19">
+        <v>23</v>
+      </c>
+      <c r="AH19">
+        <v>28</v>
+      </c>
+      <c r="AI19">
+        <v>70</v>
+      </c>
+      <c r="AJ19">
+        <v>210</v>
+      </c>
+      <c r="AK19">
+        <v>130</v>
+      </c>
+      <c r="AL19">
+        <v>140</v>
+      </c>
+      <c r="AM19">
+        <v>260</v>
+      </c>
+      <c r="AN19">
+        <v>220</v>
+      </c>
+      <c r="AO19">
+        <v>20</v>
+      </c>
+      <c r="AP19">
+        <v>8.6</v>
+      </c>
+      <c r="AQ19">
+        <v>5.7</v>
+      </c>
+      <c r="AR19">
+        <v>8.6</v>
+      </c>
+      <c r="AS19">
+        <v>18</v>
+      </c>
+      <c r="AT19">
+        <v>11.5</v>
+      </c>
+      <c r="AU19">
+        <v>7.2</v>
+      </c>
+      <c r="AV19">
+        <v>9.4</v>
+      </c>
+      <c r="AW19">
+        <v>21</v>
+      </c>
+      <c r="AX19">
+        <v>36</v>
+      </c>
+      <c r="AY19">
+        <v>20</v>
+      </c>
+      <c r="AZ19">
+        <v>23</v>
+      </c>
+      <c r="BA19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB19">
+        <v>11</v>
+      </c>
+      <c r="BC19">
+        <v>10.5</v>
+      </c>
+      <c r="BD19">
+        <v>10.5</v>
+      </c>
+      <c r="BE19">
+        <v>11</v>
+      </c>
+      <c r="BF19">
+        <v>11</v>
+      </c>
+      <c r="BG19">
+        <v>17</v>
+      </c>
+      <c r="BH19">
+        <v>3.15</v>
+      </c>
+      <c r="BI19">
+        <v>2.38</v>
+      </c>
+      <c r="BJ19">
         <v>13.5</v>
       </c>
-      <c r="Y19">
-        <v>12</v>
-      </c>
-      <c r="Z19">
-        <v>23</v>
-      </c>
-      <c r="AA19">
-        <v>60</v>
-      </c>
-      <c r="AB19">
-        <v>12</v>
-      </c>
-      <c r="AC19">
-        <v>7.8</v>
-      </c>
-      <c r="AD19">
-        <v>16</v>
-      </c>
-      <c r="AE19">
-        <v>44</v>
-      </c>
-      <c r="AF19">
-        <v>23</v>
-      </c>
-      <c r="AG19">
-        <v>14</v>
-      </c>
-      <c r="AH19">
-        <v>23</v>
-      </c>
-      <c r="AI19">
+      <c r="BK19">
+        <v>5.4</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN19">
+        <v>9</v>
+      </c>
+      <c r="BO19">
+        <v>7</v>
+      </c>
+      <c r="BP19">
         <v>65</v>
       </c>
-      <c r="AJ19">
-        <v>60</v>
-      </c>
-      <c r="AK19">
-        <v>44</v>
-      </c>
-      <c r="AL19">
-        <v>65</v>
-      </c>
-      <c r="AM19">
-        <v>150</v>
-      </c>
-      <c r="AN19">
-        <v>46</v>
-      </c>
-      <c r="AO19">
-        <v>44</v>
-      </c>
-      <c r="AP19">
-        <v>9.6</v>
-      </c>
-      <c r="AQ19">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR19">
-        <v>4.4</v>
-      </c>
-      <c r="AS19">
-        <v>5.2</v>
-      </c>
-      <c r="AT19">
-        <v>8.6</v>
-      </c>
-      <c r="AU19">
-        <v>6.4</v>
-      </c>
-      <c r="AV19">
-        <v>11.5</v>
-      </c>
-      <c r="AW19">
-        <v>5</v>
-      </c>
-      <c r="AX19">
-        <v>16</v>
-      </c>
-      <c r="AY19">
-        <v>11</v>
-      </c>
-      <c r="AZ19">
-        <v>16.5</v>
-      </c>
-      <c r="BA19">
-        <v>5.2</v>
-      </c>
-      <c r="BB19">
-        <v>5.2</v>
-      </c>
-      <c r="BC19">
-        <v>5</v>
-      </c>
-      <c r="BD19">
-        <v>5.2</v>
-      </c>
-      <c r="BE19">
-        <v>5.5</v>
-      </c>
-      <c r="BF19">
-        <v>5</v>
-      </c>
-      <c r="BG19">
-        <v>5</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.74</v>
-      </c>
-      <c r="BJ19">
-        <v>14.5</v>
-      </c>
-      <c r="BK19">
-        <v>1.56</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.74</v>
-      </c>
-      <c r="BN19">
+      <c r="BQ19">
+        <v>8</v>
+      </c>
+      <c r="BR19">
+        <v>85</v>
+      </c>
+      <c r="BS19">
         <v>8.199999999999999</v>
       </c>
-      <c r="BO19">
-        <v>3.95</v>
-      </c>
-      <c r="BP19">
-        <v>36</v>
-      </c>
-      <c r="BQ19">
-        <v>1.66</v>
-      </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
-        <v>1.69</v>
-      </c>
       <c r="BT19">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="BU19">
         <v>3.7</v>
       </c>
       <c r="BV19">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="BW19">
-        <v>1.66</v>
+        <v>5.6</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY19">
-        <v>1.69</v>
+        <v>7.4</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA19">
-        <v>1.69</v>
+        <v>7.2</v>
       </c>
       <c r="CB19" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
         <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
         <v>121</v>
       </c>
       <c r="E20" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F20">
+        <v>1.63</v>
+      </c>
+      <c r="G20">
+        <v>1.7</v>
+      </c>
+      <c r="H20">
+        <v>6.2</v>
+      </c>
+      <c r="I20">
+        <v>7.8</v>
+      </c>
+      <c r="J20">
+        <v>3.7</v>
+      </c>
+      <c r="K20">
+        <v>4.1</v>
+      </c>
+      <c r="L20">
+        <v>1.36</v>
+      </c>
+      <c r="M20">
+        <v>1.09</v>
+      </c>
+      <c r="N20">
+        <v>3.15</v>
+      </c>
+      <c r="O20">
+        <v>1.34</v>
+      </c>
+      <c r="P20">
+        <v>1.71</v>
+      </c>
+      <c r="Q20">
+        <v>2.12</v>
+      </c>
+      <c r="R20">
+        <v>1.26</v>
+      </c>
+      <c r="S20">
+        <v>4.1</v>
+      </c>
+      <c r="T20">
+        <v>2.1</v>
+      </c>
+      <c r="U20">
+        <v>1.76</v>
+      </c>
+      <c r="V20">
+        <v>1.15</v>
+      </c>
+      <c r="W20">
         <v>2.4</v>
       </c>
-      <c r="G20">
-        <v>2.72</v>
-      </c>
-      <c r="H20">
-        <v>2.58</v>
-      </c>
-      <c r="I20">
-        <v>2.96</v>
-      </c>
-      <c r="J20">
+      <c r="X20">
+        <v>13</v>
+      </c>
+      <c r="Y20">
+        <v>19.5</v>
+      </c>
+      <c r="Z20">
+        <v>65</v>
+      </c>
+      <c r="AA20">
+        <v>260</v>
+      </c>
+      <c r="AB20">
+        <v>7</v>
+      </c>
+      <c r="AC20">
+        <v>11</v>
+      </c>
+      <c r="AD20">
+        <v>28</v>
+      </c>
+      <c r="AE20">
+        <v>140</v>
+      </c>
+      <c r="AF20">
+        <v>9.4</v>
+      </c>
+      <c r="AG20">
+        <v>11</v>
+      </c>
+      <c r="AH20">
+        <v>26</v>
+      </c>
+      <c r="AI20">
+        <v>140</v>
+      </c>
+      <c r="AJ20">
+        <v>17.5</v>
+      </c>
+      <c r="AK20">
+        <v>21</v>
+      </c>
+      <c r="AL20">
+        <v>55</v>
+      </c>
+      <c r="AM20">
+        <v>210</v>
+      </c>
+      <c r="AN20">
+        <v>13.5</v>
+      </c>
+      <c r="AO20">
+        <v>240</v>
+      </c>
+      <c r="AP20">
+        <v>10</v>
+      </c>
+      <c r="AQ20">
+        <v>15.5</v>
+      </c>
+      <c r="AR20">
+        <v>7</v>
+      </c>
+      <c r="AS20">
+        <v>7.6</v>
+      </c>
+      <c r="AT20">
+        <v>6</v>
+      </c>
+      <c r="AU20">
+        <v>7.6</v>
+      </c>
+      <c r="AV20">
+        <v>6</v>
+      </c>
+      <c r="AW20">
+        <v>7.4</v>
+      </c>
+      <c r="AX20">
+        <v>7.6</v>
+      </c>
+      <c r="AY20">
+        <v>9</v>
+      </c>
+      <c r="AZ20">
+        <v>21</v>
+      </c>
+      <c r="BA20">
+        <v>7.4</v>
+      </c>
+      <c r="BB20">
+        <v>14</v>
+      </c>
+      <c r="BC20">
+        <v>17.5</v>
+      </c>
+      <c r="BD20">
+        <v>6.8</v>
+      </c>
+      <c r="BE20">
+        <v>7.4</v>
+      </c>
+      <c r="BF20">
+        <v>10.5</v>
+      </c>
+      <c r="BG20">
+        <v>7.6</v>
+      </c>
+      <c r="BH20">
         <v>3.8</v>
       </c>
-      <c r="K20">
+      <c r="BI20">
+        <v>2.64</v>
+      </c>
+      <c r="BJ20">
+        <v>12</v>
+      </c>
+      <c r="BK20">
+        <v>8.4</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>7.4</v>
+      </c>
+      <c r="BN20">
+        <v>4</v>
+      </c>
+      <c r="BO20">
+        <v>3.4</v>
+      </c>
+      <c r="BP20">
+        <v>12</v>
+      </c>
+      <c r="BQ20">
+        <v>4.7</v>
+      </c>
+      <c r="BR20">
+        <v>36</v>
+      </c>
+      <c r="BS20">
+        <v>6.2</v>
+      </c>
+      <c r="BT20">
+        <v>10.5</v>
+      </c>
+      <c r="BU20">
         <v>4.4</v>
       </c>
-      <c r="L20">
-        <v>1.01</v>
-      </c>
-      <c r="M20">
-        <v>1.01</v>
-      </c>
-      <c r="N20">
-        <v>2.56</v>
-      </c>
-      <c r="O20">
-        <v>1.18</v>
-      </c>
-      <c r="P20">
-        <v>2.16</v>
-      </c>
-      <c r="Q20">
-        <v>1.46</v>
-      </c>
-      <c r="R20">
-        <v>1.46</v>
-      </c>
-      <c r="S20">
-        <v>2.2</v>
-      </c>
-      <c r="T20">
-        <v>1.11</v>
-      </c>
-      <c r="U20">
-        <v>1.11</v>
-      </c>
-      <c r="V20">
-        <v>1.51</v>
-      </c>
-      <c r="W20">
-        <v>1.58</v>
-      </c>
-      <c r="X20">
-        <v>1000</v>
-      </c>
-      <c r="Y20">
-        <v>1000</v>
-      </c>
-      <c r="Z20">
-        <v>1000</v>
-      </c>
-      <c r="AA20">
-        <v>1000</v>
-      </c>
-      <c r="AB20">
-        <v>1000</v>
-      </c>
-      <c r="AC20">
-        <v>1000</v>
-      </c>
-      <c r="AD20">
-        <v>1000</v>
-      </c>
-      <c r="AE20">
-        <v>1000</v>
-      </c>
-      <c r="AF20">
-        <v>1000</v>
-      </c>
-      <c r="AG20">
-        <v>1000</v>
-      </c>
-      <c r="AH20">
-        <v>1000</v>
-      </c>
-      <c r="AI20">
-        <v>1000</v>
-      </c>
-      <c r="AJ20">
-        <v>1000</v>
-      </c>
-      <c r="AK20">
-        <v>1000</v>
-      </c>
-      <c r="AL20">
-        <v>1000</v>
-      </c>
-      <c r="AM20">
-        <v>1000</v>
-      </c>
-      <c r="AN20">
-        <v>1000</v>
-      </c>
-      <c r="AO20">
-        <v>1000</v>
-      </c>
-      <c r="AP20">
-        <v>1.01</v>
-      </c>
-      <c r="AQ20">
-        <v>1.01</v>
-      </c>
-      <c r="AR20">
-        <v>1.01</v>
-      </c>
-      <c r="AS20">
-        <v>1.01</v>
-      </c>
-      <c r="AT20">
-        <v>1.01</v>
-      </c>
-      <c r="AU20">
-        <v>1.01</v>
-      </c>
-      <c r="AV20">
-        <v>1.01</v>
-      </c>
-      <c r="AW20">
-        <v>1.01</v>
-      </c>
-      <c r="AX20">
-        <v>1.01</v>
-      </c>
-      <c r="AY20">
-        <v>1.01</v>
-      </c>
-      <c r="AZ20">
-        <v>1.01</v>
-      </c>
-      <c r="BA20">
-        <v>1.01</v>
-      </c>
-      <c r="BB20">
-        <v>1.01</v>
-      </c>
-      <c r="BC20">
-        <v>1.01</v>
-      </c>
-      <c r="BD20">
-        <v>1.01</v>
-      </c>
-      <c r="BE20">
-        <v>1.01</v>
-      </c>
-      <c r="BF20">
-        <v>1.01</v>
-      </c>
-      <c r="BG20">
-        <v>1.01</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.04</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.04</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.04</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.04</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>1.04</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>1.04</v>
-      </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
-        <v>1.04</v>
-      </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB20" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
         <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
         <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F21">
-        <v>1.54</v>
+        <v>2.76</v>
       </c>
       <c r="G21">
-        <v>1.9</v>
+        <v>2.96</v>
       </c>
       <c r="H21">
-        <v>4.1</v>
+        <v>2.82</v>
       </c>
       <c r="I21">
-        <v>9.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="J21">
+        <v>3.2</v>
+      </c>
+      <c r="K21">
+        <v>3.3</v>
+      </c>
+      <c r="L21">
+        <v>1.4</v>
+      </c>
+      <c r="M21">
         <v>1.09</v>
       </c>
-      <c r="K21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L21">
-        <v>1.27</v>
-      </c>
-      <c r="M21">
-        <v>1.01</v>
-      </c>
       <c r="N21">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="O21">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="P21">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="Q21">
-        <v>1.61</v>
+        <v>2.22</v>
       </c>
       <c r="R21">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S21">
-        <v>2.58</v>
+        <v>4.2</v>
       </c>
       <c r="T21">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U21">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V21">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>2.1</v>
+        <v>1.51</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP21">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW21">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX21">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA21">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB21">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC21">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD21">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK21">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO21">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ21">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS21">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB21" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
         <v>89</v>
@@ -5936,721 +5948,721 @@
         <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F22">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G22">
-        <v>600</v>
+        <v>2.72</v>
       </c>
       <c r="H22">
-        <v>1.09</v>
+        <v>2.58</v>
       </c>
       <c r="I22">
-        <v>990</v>
+        <v>2.92</v>
       </c>
       <c r="J22">
-        <v>1.09</v>
+        <v>3.8</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M22">
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.28</v>
+        <v>5.1</v>
       </c>
       <c r="O22">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="P22">
-        <v>1.28</v>
+        <v>2.38</v>
       </c>
       <c r="Q22">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="R22">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="S22">
-        <v>1.44</v>
+        <v>2.48</v>
       </c>
       <c r="T22">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U22">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V22">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W22">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI22">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK22">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO22">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ22">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU22">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW22">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA22">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB22" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
         <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
         <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F23">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="G23">
-        <v>1.42</v>
+        <v>1.82</v>
       </c>
       <c r="H23">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="I23">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="J23">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="K23">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M23">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N23">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O23">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="P23">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q23">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="R23">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S23">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="T23">
-        <v>2.28</v>
+        <v>1.76</v>
       </c>
       <c r="U23">
-        <v>1.66</v>
+        <v>2.08</v>
       </c>
       <c r="V23">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="W23">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="X23">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Y23">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Z23">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB23">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AC23">
         <v>11.5</v>
       </c>
       <c r="AD23">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AE23">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AF23">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="AG23">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH23">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AI23">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="AJ23">
+        <v>22</v>
+      </c>
+      <c r="AK23">
+        <v>22</v>
+      </c>
+      <c r="AL23">
+        <v>40</v>
+      </c>
+      <c r="AM23">
+        <v>120</v>
+      </c>
+      <c r="AN23">
         <v>12</v>
       </c>
-      <c r="AK23">
-        <v>17.5</v>
-      </c>
-      <c r="AL23">
-        <v>50</v>
-      </c>
-      <c r="AM23">
-        <v>270</v>
-      </c>
-      <c r="AN23">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AO23">
-        <v>470</v>
+        <v>85</v>
       </c>
       <c r="AP23">
         <v>13</v>
       </c>
       <c r="AQ23">
+        <v>14</v>
+      </c>
+      <c r="AR23">
+        <v>1.01</v>
+      </c>
+      <c r="AS23">
+        <v>1.01</v>
+      </c>
+      <c r="AT23">
         <v>7.2</v>
       </c>
-      <c r="AR23">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS23">
-        <v>9.4</v>
-      </c>
-      <c r="AT23">
+      <c r="AU23">
+        <v>7</v>
+      </c>
+      <c r="AV23">
+        <v>14.5</v>
+      </c>
+      <c r="AW23">
+        <v>1.01</v>
+      </c>
+      <c r="AX23">
+        <v>8.4</v>
+      </c>
+      <c r="AY23">
+        <v>7.6</v>
+      </c>
+      <c r="AZ23">
+        <v>14</v>
+      </c>
+      <c r="BA23">
+        <v>1.01</v>
+      </c>
+      <c r="BB23">
+        <v>13</v>
+      </c>
+      <c r="BC23">
+        <v>13</v>
+      </c>
+      <c r="BD23">
+        <v>1.03</v>
+      </c>
+      <c r="BE23">
+        <v>1.01</v>
+      </c>
+      <c r="BF23">
+        <v>7.2</v>
+      </c>
+      <c r="BG23">
+        <v>1.01</v>
+      </c>
+      <c r="BH23">
+        <v>3.85</v>
+      </c>
+      <c r="BI23">
+        <v>2.98</v>
+      </c>
+      <c r="BJ23">
+        <v>10</v>
+      </c>
+      <c r="BK23">
+        <v>5.6</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>11.5</v>
+      </c>
+      <c r="BN23">
+        <v>4.5</v>
+      </c>
+      <c r="BO23">
+        <v>3.45</v>
+      </c>
+      <c r="BP23">
+        <v>11.5</v>
+      </c>
+      <c r="BQ23">
         <v>6</v>
       </c>
-      <c r="AU23">
-        <v>9.6</v>
-      </c>
-      <c r="AV23">
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>8.6</v>
+      </c>
+      <c r="BT23">
+        <v>9</v>
+      </c>
+      <c r="BU23">
+        <v>5.3</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>10</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>10</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
         <v>7.8</v>
       </c>
-      <c r="AW23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX23">
-        <v>6.4</v>
-      </c>
-      <c r="AY23">
-        <v>9</v>
-      </c>
-      <c r="AZ23">
-        <v>27</v>
-      </c>
-      <c r="BA23">
-        <v>9</v>
-      </c>
-      <c r="BB23">
-        <v>9.6</v>
-      </c>
-      <c r="BC23">
-        <v>14</v>
-      </c>
-      <c r="BD23">
-        <v>40</v>
-      </c>
-      <c r="BE23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF23">
-        <v>6.4</v>
-      </c>
-      <c r="BG23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH23">
-        <v>1000</v>
-      </c>
-      <c r="BI23">
-        <v>1.04</v>
-      </c>
-      <c r="BJ23">
-        <v>1000</v>
-      </c>
-      <c r="BK23">
-        <v>1.04</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>1.04</v>
-      </c>
-      <c r="BN23">
-        <v>1000</v>
-      </c>
-      <c r="BO23">
-        <v>1.04</v>
-      </c>
-      <c r="BP23">
-        <v>1000</v>
-      </c>
-      <c r="BQ23">
-        <v>1.04</v>
-      </c>
-      <c r="BR23">
-        <v>1000</v>
-      </c>
-      <c r="BS23">
-        <v>1.04</v>
-      </c>
-      <c r="BT23">
-        <v>1000</v>
-      </c>
-      <c r="BU23">
-        <v>1.04</v>
-      </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
-      <c r="BW23">
-        <v>1.04</v>
-      </c>
-      <c r="BX23">
-        <v>1000</v>
-      </c>
-      <c r="BY23">
-        <v>1.04</v>
-      </c>
-      <c r="BZ23">
-        <v>1000</v>
-      </c>
-      <c r="CA23">
-        <v>1.04</v>
-      </c>
       <c r="CB23" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
         <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
         <v>125</v>
       </c>
       <c r="E24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F24">
-        <v>2.28</v>
+        <v>1.21</v>
       </c>
       <c r="G24">
-        <v>2.3</v>
+        <v>600</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>2.26</v>
       </c>
       <c r="I24">
-        <v>4.3</v>
+        <v>990</v>
       </c>
       <c r="J24">
-        <v>3.05</v>
+        <v>1.74</v>
       </c>
       <c r="K24">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="L24">
         <v>1.01</v>
       </c>
       <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>1.3</v>
+      </c>
+      <c r="O24">
+        <v>1.42</v>
+      </c>
+      <c r="P24">
+        <v>1.3</v>
+      </c>
+      <c r="Q24">
+        <v>1.42</v>
+      </c>
+      <c r="R24">
         <v>1.13</v>
       </c>
-      <c r="N24">
-        <v>2.56</v>
-      </c>
-      <c r="O24">
-        <v>1.57</v>
-      </c>
-      <c r="P24">
-        <v>1.48</v>
-      </c>
-      <c r="Q24">
-        <v>2.74</v>
-      </c>
-      <c r="R24">
-        <v>1.17</v>
-      </c>
       <c r="S24">
-        <v>5.7</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U24">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W24">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="X24">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP24">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
         <v>89</v>
@@ -6662,237 +6674,237 @@
         <v>126</v>
       </c>
       <c r="E25" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F25">
-        <v>2.32</v>
+        <v>1.39</v>
       </c>
       <c r="G25">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="H25">
-        <v>3.05</v>
+        <v>11</v>
       </c>
       <c r="I25">
-        <v>3.2</v>
+        <v>12.5</v>
       </c>
       <c r="J25">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="K25">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="L25">
         <v>1.33</v>
       </c>
       <c r="M25">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N25">
+        <v>3.6</v>
+      </c>
+      <c r="O25">
+        <v>1.33</v>
+      </c>
+      <c r="P25">
+        <v>1.9</v>
+      </c>
+      <c r="Q25">
+        <v>1.96</v>
+      </c>
+      <c r="R25">
+        <v>1.35</v>
+      </c>
+      <c r="S25">
+        <v>3.45</v>
+      </c>
+      <c r="T25">
+        <v>2.28</v>
+      </c>
+      <c r="U25">
+        <v>1.66</v>
+      </c>
+      <c r="V25">
+        <v>1.08</v>
+      </c>
+      <c r="W25">
+        <v>3.35</v>
+      </c>
+      <c r="X25">
+        <v>16</v>
+      </c>
+      <c r="Y25">
+        <v>32</v>
+      </c>
+      <c r="Z25">
+        <v>130</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>7.2</v>
+      </c>
+      <c r="AC25">
+        <v>11.5</v>
+      </c>
+      <c r="AD25">
+        <v>44</v>
+      </c>
+      <c r="AE25">
+        <v>270</v>
+      </c>
+      <c r="AF25">
+        <v>7.8</v>
+      </c>
+      <c r="AG25">
+        <v>11</v>
+      </c>
+      <c r="AH25">
+        <v>34</v>
+      </c>
+      <c r="AI25">
+        <v>220</v>
+      </c>
+      <c r="AJ25">
+        <v>12</v>
+      </c>
+      <c r="AK25">
+        <v>17.5</v>
+      </c>
+      <c r="AL25">
+        <v>50</v>
+      </c>
+      <c r="AM25">
+        <v>270</v>
+      </c>
+      <c r="AN25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO25">
+        <v>470</v>
+      </c>
+      <c r="AP25">
+        <v>13</v>
+      </c>
+      <c r="AQ25">
+        <v>7.2</v>
+      </c>
+      <c r="AR25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS25">
+        <v>9.4</v>
+      </c>
+      <c r="AT25">
+        <v>6</v>
+      </c>
+      <c r="AU25">
+        <v>9.6</v>
+      </c>
+      <c r="AV25">
+        <v>7.8</v>
+      </c>
+      <c r="AW25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX25">
+        <v>6.4</v>
+      </c>
+      <c r="AY25">
+        <v>9</v>
+      </c>
+      <c r="AZ25">
+        <v>27</v>
+      </c>
+      <c r="BA25">
+        <v>9</v>
+      </c>
+      <c r="BB25">
+        <v>9.6</v>
+      </c>
+      <c r="BC25">
+        <v>14</v>
+      </c>
+      <c r="BD25">
+        <v>40</v>
+      </c>
+      <c r="BE25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF25">
+        <v>6.4</v>
+      </c>
+      <c r="BG25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH25">
+        <v>3.6</v>
+      </c>
+      <c r="BI25">
+        <v>2.78</v>
+      </c>
+      <c r="BJ25">
+        <v>14</v>
+      </c>
+      <c r="BK25">
+        <v>6</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>10.5</v>
+      </c>
+      <c r="BN25">
+        <v>3.7</v>
+      </c>
+      <c r="BO25">
+        <v>2.86</v>
+      </c>
+      <c r="BP25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ25">
         <v>4.9</v>
       </c>
-      <c r="O25">
-        <v>1.23</v>
-      </c>
-      <c r="P25">
-        <v>2.32</v>
-      </c>
-      <c r="Q25">
-        <v>1.72</v>
-      </c>
-      <c r="R25">
-        <v>1.52</v>
-      </c>
-      <c r="S25">
-        <v>2.8</v>
-      </c>
-      <c r="T25">
-        <v>1.61</v>
-      </c>
-      <c r="U25">
-        <v>2.44</v>
-      </c>
-      <c r="V25">
-        <v>1.45</v>
-      </c>
-      <c r="W25">
-        <v>1.72</v>
-      </c>
-      <c r="X25">
-        <v>24</v>
-      </c>
-      <c r="Y25">
-        <v>16</v>
-      </c>
-      <c r="Z25">
-        <v>27</v>
-      </c>
-      <c r="AA25">
-        <v>70</v>
-      </c>
-      <c r="AB25">
-        <v>13</v>
-      </c>
-      <c r="AC25">
-        <v>9.6</v>
-      </c>
-      <c r="AD25">
-        <v>16</v>
-      </c>
-      <c r="AE25">
-        <v>36</v>
-      </c>
-      <c r="AF25">
-        <v>17.5</v>
-      </c>
-      <c r="AG25">
-        <v>13</v>
-      </c>
-      <c r="AH25">
-        <v>16</v>
-      </c>
-      <c r="AI25">
-        <v>44</v>
-      </c>
-      <c r="AJ25">
-        <v>36</v>
-      </c>
-      <c r="AK25">
-        <v>26</v>
-      </c>
-      <c r="AL25">
-        <v>36</v>
-      </c>
-      <c r="AM25">
-        <v>1000</v>
-      </c>
-      <c r="AN25">
-        <v>16.5</v>
-      </c>
-      <c r="AO25">
-        <v>23</v>
-      </c>
-      <c r="AP25">
-        <v>17.5</v>
-      </c>
-      <c r="AQ25">
-        <v>14</v>
-      </c>
-      <c r="AR25">
-        <v>20</v>
-      </c>
-      <c r="AS25">
-        <v>34</v>
-      </c>
-      <c r="AT25">
-        <v>11.5</v>
-      </c>
-      <c r="AU25">
-        <v>8</v>
-      </c>
-      <c r="AV25">
-        <v>12</v>
-      </c>
-      <c r="AW25">
-        <v>21</v>
-      </c>
-      <c r="AX25">
-        <v>15</v>
-      </c>
-      <c r="AY25">
+      <c r="BR25">
+        <v>32</v>
+      </c>
+      <c r="BS25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT25">
+        <v>14.5</v>
+      </c>
+      <c r="BU25">
+        <v>6.2</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
         <v>10</v>
       </c>
-      <c r="AZ25">
-        <v>14</v>
-      </c>
-      <c r="BA25">
-        <v>25</v>
-      </c>
-      <c r="BB25">
-        <v>20</v>
-      </c>
-      <c r="BC25">
-        <v>20</v>
-      </c>
-      <c r="BD25">
-        <v>20</v>
-      </c>
-      <c r="BE25">
-        <v>36</v>
-      </c>
-      <c r="BF25">
-        <v>12.5</v>
-      </c>
-      <c r="BG25">
-        <v>20</v>
-      </c>
-      <c r="BH25">
-        <v>4.7</v>
-      </c>
-      <c r="BI25">
-        <v>3.15</v>
-      </c>
-      <c r="BJ25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK25">
-        <v>4.5</v>
-      </c>
-      <c r="BL25">
-        <v>110</v>
-      </c>
-      <c r="BM25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN25">
-        <v>5.6</v>
-      </c>
-      <c r="BO25">
-        <v>4.9</v>
-      </c>
-      <c r="BP25">
-        <v>16.5</v>
-      </c>
-      <c r="BQ25">
-        <v>6</v>
-      </c>
-      <c r="BR25">
-        <v>26</v>
-      </c>
-      <c r="BS25">
-        <v>7</v>
-      </c>
-      <c r="BT25">
-        <v>6.6</v>
-      </c>
-      <c r="BU25">
-        <v>5.7</v>
-      </c>
-      <c r="BV25">
-        <v>22</v>
-      </c>
-      <c r="BW25">
-        <v>6.6</v>
-      </c>
       <c r="BX25">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BZ25">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CA25">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB25" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
@@ -6904,232 +6916,232 @@
         <v>127</v>
       </c>
       <c r="E26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F26">
-        <v>2.96</v>
+        <v>2.22</v>
       </c>
       <c r="G26">
+        <v>2.26</v>
+      </c>
+      <c r="H26">
+        <v>4.2</v>
+      </c>
+      <c r="I26">
+        <v>4.3</v>
+      </c>
+      <c r="J26">
         <v>3.05</v>
       </c>
-      <c r="H26">
-        <v>2.34</v>
-      </c>
-      <c r="I26">
-        <v>2.42</v>
-      </c>
-      <c r="J26">
-        <v>3.95</v>
-      </c>
       <c r="K26">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="L26">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="M26">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="N26">
+        <v>2.52</v>
+      </c>
+      <c r="O26">
+        <v>1.58</v>
+      </c>
+      <c r="P26">
+        <v>1.51</v>
+      </c>
+      <c r="Q26">
+        <v>2.74</v>
+      </c>
+      <c r="R26">
+        <v>1.18</v>
+      </c>
+      <c r="S26">
         <v>5.8</v>
       </c>
-      <c r="O26">
-        <v>1.19</v>
-      </c>
-      <c r="P26">
-        <v>2.6</v>
-      </c>
-      <c r="Q26">
-        <v>1.59</v>
-      </c>
-      <c r="R26">
-        <v>1.64</v>
-      </c>
-      <c r="S26">
-        <v>2.48</v>
-      </c>
       <c r="T26">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="U26">
-        <v>2.66</v>
+        <v>1.7</v>
       </c>
       <c r="V26">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="X26">
-        <v>27</v>
+        <v>8.6</v>
       </c>
       <c r="Y26">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Z26">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="AA26">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="AB26">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="AC26">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD26">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE26">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="AF26">
-        <v>26</v>
+        <v>13.5</v>
       </c>
       <c r="AG26">
         <v>14</v>
       </c>
       <c r="AH26">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="AI26">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="AJ26">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="AK26">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL26">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AM26">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AN26">
-        <v>18.5</v>
+        <v>42</v>
       </c>
       <c r="AO26">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="AP26">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="AQ26">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR26">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="AS26">
-        <v>21</v>
+        <v>5.9</v>
       </c>
       <c r="AT26">
-        <v>15.5</v>
+        <v>5.9</v>
       </c>
       <c r="AU26">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV26">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AW26">
-        <v>18.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX26">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AY26">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ26">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="BA26">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="BB26">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC26">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="BD26">
-        <v>22</v>
+        <v>5.8</v>
       </c>
       <c r="BE26">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="BF26">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="BG26">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BH26">
-        <v>4.6</v>
+        <v>2.68</v>
       </c>
       <c r="BI26">
-        <v>3.45</v>
+        <v>2.14</v>
       </c>
       <c r="BJ26">
+        <v>12.5</v>
+      </c>
+      <c r="BK26">
         <v>8.800000000000001</v>
       </c>
-      <c r="BK26">
-        <v>4.6</v>
-      </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BN26">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BO26">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP26">
         <v>22</v>
       </c>
       <c r="BQ26">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR26">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="BS26">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT26">
+        <v>7.4</v>
+      </c>
+      <c r="BU26">
         <v>6</v>
       </c>
-      <c r="BU26">
-        <v>4.9</v>
-      </c>
       <c r="BV26">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BX26">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BZ26">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB26" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7146,232 +7158,232 @@
         <v>128</v>
       </c>
       <c r="E27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F27">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="G27">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="H27">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="I27">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J27">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K27">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L27">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M27">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N27">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O27">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P27">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q27">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="R27">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S27">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="T27">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="U27">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="V27">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="X27">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y27">
         <v>15.5</v>
       </c>
       <c r="Z27">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA27">
-        <v>470</v>
+        <v>70</v>
       </c>
       <c r="AB27">
         <v>13</v>
       </c>
       <c r="AC27">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AE27">
+        <v>36</v>
+      </c>
+      <c r="AF27">
+        <v>17</v>
+      </c>
+      <c r="AG27">
+        <v>13.5</v>
+      </c>
+      <c r="AH27">
+        <v>16</v>
+      </c>
+      <c r="AI27">
         <v>44</v>
       </c>
-      <c r="AF27">
-        <v>15.5</v>
-      </c>
-      <c r="AG27">
+      <c r="AJ27">
+        <v>36</v>
+      </c>
+      <c r="AK27">
+        <v>24</v>
+      </c>
+      <c r="AL27">
+        <v>36</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>16.5</v>
+      </c>
+      <c r="AO27">
+        <v>23</v>
+      </c>
+      <c r="AP27">
+        <v>17</v>
+      </c>
+      <c r="AQ27">
+        <v>13.5</v>
+      </c>
+      <c r="AR27">
+        <v>20</v>
+      </c>
+      <c r="AS27">
+        <v>29</v>
+      </c>
+      <c r="AT27">
+        <v>11.5</v>
+      </c>
+      <c r="AU27">
+        <v>8</v>
+      </c>
+      <c r="AV27">
         <v>12</v>
-      </c>
-      <c r="AH27">
-        <v>21</v>
-      </c>
-      <c r="AI27">
-        <v>55</v>
-      </c>
-      <c r="AJ27">
-        <v>38</v>
-      </c>
-      <c r="AK27">
-        <v>27</v>
-      </c>
-      <c r="AL27">
-        <v>40</v>
-      </c>
-      <c r="AM27">
-        <v>95</v>
-      </c>
-      <c r="AN27">
-        <v>19.5</v>
-      </c>
-      <c r="AO27">
-        <v>50</v>
-      </c>
-      <c r="AP27">
-        <v>15.5</v>
-      </c>
-      <c r="AQ27">
-        <v>13</v>
-      </c>
-      <c r="AR27">
-        <v>21</v>
-      </c>
-      <c r="AS27">
-        <v>40</v>
-      </c>
-      <c r="AT27">
-        <v>10</v>
-      </c>
-      <c r="AU27">
-        <v>7.6</v>
-      </c>
-      <c r="AV27">
-        <v>12.5</v>
       </c>
       <c r="AW27">
         <v>22</v>
       </c>
       <c r="AX27">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY27">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ27">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA27">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BB27">
+        <v>20</v>
+      </c>
+      <c r="BC27">
+        <v>20</v>
+      </c>
+      <c r="BD27">
         <v>21</v>
       </c>
-      <c r="BC27">
-        <v>16</v>
-      </c>
-      <c r="BD27">
-        <v>23</v>
-      </c>
       <c r="BE27">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BF27">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG27">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH27">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BI27">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="BJ27">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BK27">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL27">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM27">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BN27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO27">
+        <v>4.9</v>
+      </c>
+      <c r="BP27">
+        <v>16.5</v>
+      </c>
+      <c r="BQ27">
+        <v>4.3</v>
+      </c>
+      <c r="BR27">
+        <v>26</v>
+      </c>
+      <c r="BS27">
         <v>4.7</v>
       </c>
-      <c r="BP27">
-        <v>16</v>
-      </c>
-      <c r="BQ27">
+      <c r="BT27">
+        <v>7.8</v>
+      </c>
+      <c r="BU27">
+        <v>4.9</v>
+      </c>
+      <c r="BV27">
+        <v>22</v>
+      </c>
+      <c r="BW27">
+        <v>4.6</v>
+      </c>
+      <c r="BX27">
+        <v>30</v>
+      </c>
+      <c r="BY27">
+        <v>4.9</v>
+      </c>
+      <c r="BZ27">
+        <v>20</v>
+      </c>
+      <c r="CA27">
         <v>4.5</v>
       </c>
-      <c r="BR27">
-        <v>40</v>
-      </c>
-      <c r="BS27">
-        <v>5.1</v>
-      </c>
-      <c r="BT27">
-        <v>8</v>
-      </c>
-      <c r="BU27">
-        <v>4.4</v>
-      </c>
-      <c r="BV27">
-        <v>38</v>
-      </c>
-      <c r="BW27">
-        <v>5</v>
-      </c>
-      <c r="BX27">
-        <v>50</v>
-      </c>
-      <c r="BY27">
-        <v>5.3</v>
-      </c>
-      <c r="BZ27">
-        <v>22</v>
-      </c>
-      <c r="CA27">
-        <v>4.9</v>
-      </c>
       <c r="CB27" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7388,232 +7400,232 @@
         <v>129</v>
       </c>
       <c r="E28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F28">
         <v>2.96</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H28">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I28">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J28">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K28">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L28">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="M28">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N28">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="O28">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="P28">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q28">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="R28">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="S28">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="T28">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="U28">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="V28">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W28">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X28">
+        <v>27</v>
+      </c>
+      <c r="Y28">
+        <v>16.5</v>
+      </c>
+      <c r="Z28">
+        <v>19</v>
+      </c>
+      <c r="AA28">
         <v>34</v>
       </c>
-      <c r="Y28">
-        <v>21</v>
-      </c>
-      <c r="Z28">
-        <v>22</v>
-      </c>
-      <c r="AA28">
-        <v>36</v>
-      </c>
       <c r="AB28">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AC28">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD28">
         <v>12.5</v>
       </c>
       <c r="AE28">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AF28">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG28">
         <v>14</v>
       </c>
       <c r="AH28">
+        <v>15</v>
+      </c>
+      <c r="AI28">
+        <v>30</v>
+      </c>
+      <c r="AJ28">
+        <v>160</v>
+      </c>
+      <c r="AK28">
+        <v>34</v>
+      </c>
+      <c r="AL28">
+        <v>38</v>
+      </c>
+      <c r="AM28">
+        <v>260</v>
+      </c>
+      <c r="AN28">
+        <v>18.5</v>
+      </c>
+      <c r="AO28">
+        <v>14</v>
+      </c>
+      <c r="AP28">
+        <v>18</v>
+      </c>
+      <c r="AQ28">
         <v>13.5</v>
       </c>
-      <c r="AI28">
-        <v>25</v>
-      </c>
-      <c r="AJ28">
-        <v>60</v>
-      </c>
-      <c r="AK28">
-        <v>27</v>
-      </c>
-      <c r="AL28">
-        <v>42</v>
-      </c>
-      <c r="AM28">
-        <v>46</v>
-      </c>
-      <c r="AN28">
+      <c r="AR28">
+        <v>16</v>
+      </c>
+      <c r="AS28">
+        <v>21</v>
+      </c>
+      <c r="AT28">
+        <v>15.5</v>
+      </c>
+      <c r="AU28">
+        <v>8.6</v>
+      </c>
+      <c r="AV28">
+        <v>10.5</v>
+      </c>
+      <c r="AW28">
+        <v>18.5</v>
+      </c>
+      <c r="AX28">
+        <v>20</v>
+      </c>
+      <c r="AY28">
+        <v>12</v>
+      </c>
+      <c r="AZ28">
         <v>13</v>
       </c>
-      <c r="AO28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AP28">
+      <c r="BA28">
+        <v>18.5</v>
+      </c>
+      <c r="BB28">
+        <v>26</v>
+      </c>
+      <c r="BC28">
+        <v>19</v>
+      </c>
+      <c r="BD28">
+        <v>22</v>
+      </c>
+      <c r="BE28">
         <v>30</v>
       </c>
-      <c r="AQ28">
-        <v>18.5</v>
-      </c>
-      <c r="AR28">
-        <v>20</v>
-      </c>
-      <c r="AS28">
-        <v>23</v>
-      </c>
-      <c r="AT28">
+      <c r="BF28">
+        <v>15.5</v>
+      </c>
+      <c r="BG28">
+        <v>11</v>
+      </c>
+      <c r="BH28">
+        <v>4.6</v>
+      </c>
+      <c r="BI28">
+        <v>3.45</v>
+      </c>
+      <c r="BJ28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK28">
+        <v>4.6</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN28">
+        <v>7</v>
+      </c>
+      <c r="BO28">
+        <v>5.7</v>
+      </c>
+      <c r="BP28">
         <v>22</v>
       </c>
-      <c r="AU28">
-        <v>10</v>
-      </c>
-      <c r="AV28">
-        <v>11</v>
-      </c>
-      <c r="AW28">
-        <v>18</v>
-      </c>
-      <c r="AX28">
-        <v>26</v>
-      </c>
-      <c r="AY28">
-        <v>12.5</v>
-      </c>
-      <c r="AZ28">
-        <v>12.5</v>
-      </c>
-      <c r="BA28">
-        <v>21</v>
-      </c>
-      <c r="BB28">
-        <v>40</v>
-      </c>
-      <c r="BC28">
-        <v>23</v>
-      </c>
-      <c r="BD28">
+      <c r="BQ28">
+        <v>6.8</v>
+      </c>
+      <c r="BR28">
+        <v>28</v>
+      </c>
+      <c r="BS28">
+        <v>7.2</v>
+      </c>
+      <c r="BT28">
+        <v>6</v>
+      </c>
+      <c r="BU28">
+        <v>4.9</v>
+      </c>
+      <c r="BV28">
+        <v>16</v>
+      </c>
+      <c r="BW28">
+        <v>6</v>
+      </c>
+      <c r="BX28">
         <v>24</v>
       </c>
-      <c r="BE28">
-        <v>36</v>
-      </c>
-      <c r="BF28">
-        <v>12</v>
-      </c>
-      <c r="BG28">
-        <v>8.4</v>
-      </c>
-      <c r="BH28">
-        <v>1000</v>
-      </c>
-      <c r="BI28">
-        <v>2.1</v>
-      </c>
-      <c r="BJ28">
-        <v>11.5</v>
-      </c>
-      <c r="BK28">
-        <v>5.1</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>2.04</v>
-      </c>
-      <c r="BN28">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BO28">
-        <v>4.7</v>
-      </c>
-      <c r="BP28">
-        <v>26</v>
-      </c>
-      <c r="BQ28">
-        <v>1.95</v>
-      </c>
-      <c r="BR28">
-        <v>32</v>
-      </c>
-      <c r="BS28">
-        <v>1.98</v>
-      </c>
-      <c r="BT28">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU28">
-        <v>4.3</v>
-      </c>
-      <c r="BV28">
-        <v>21</v>
-      </c>
-      <c r="BW28">
-        <v>1.92</v>
-      </c>
-      <c r="BX28">
-        <v>29</v>
-      </c>
       <c r="BY28">
-        <v>1.97</v>
+        <v>7</v>
       </c>
       <c r="BZ28">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA28">
-        <v>1.88</v>
+        <v>6.2</v>
       </c>
       <c r="CB28" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7630,232 +7642,232 @@
         <v>130</v>
       </c>
       <c r="E29" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F29">
-        <v>1.69</v>
+        <v>2.26</v>
       </c>
       <c r="G29">
-        <v>1.73</v>
+        <v>2.32</v>
       </c>
       <c r="H29">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="I29">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="J29">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="K29">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="L29">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M29">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N29">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="O29">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="P29">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="Q29">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="R29">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="S29">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="T29">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U29">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="W29">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="X29">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Y29">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="Z29">
+        <v>30</v>
+      </c>
+      <c r="AA29">
+        <v>470</v>
+      </c>
+      <c r="AB29">
+        <v>12</v>
+      </c>
+      <c r="AC29">
+        <v>8.6</v>
+      </c>
+      <c r="AD29">
+        <v>14.5</v>
+      </c>
+      <c r="AE29">
         <v>44</v>
       </c>
-      <c r="AA29">
-        <v>1000</v>
-      </c>
-      <c r="AB29">
-        <v>12.5</v>
-      </c>
-      <c r="AC29">
-        <v>10.5</v>
-      </c>
-      <c r="AD29">
-        <v>21</v>
-      </c>
-      <c r="AE29">
-        <v>60</v>
-      </c>
       <c r="AF29">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH29">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI29">
         <v>55</v>
       </c>
       <c r="AJ29">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="AK29">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AL29">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN29">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="AO29">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP29">
+        <v>15.5</v>
+      </c>
+      <c r="AQ29">
+        <v>13</v>
+      </c>
+      <c r="AR29">
         <v>21</v>
       </c>
-      <c r="AQ29">
-        <v>20</v>
-      </c>
-      <c r="AR29">
+      <c r="AS29">
+        <v>29</v>
+      </c>
+      <c r="AT29">
+        <v>10</v>
+      </c>
+      <c r="AU29">
+        <v>7.6</v>
+      </c>
+      <c r="AV29">
+        <v>12.5</v>
+      </c>
+      <c r="AW29">
+        <v>24</v>
+      </c>
+      <c r="AX29">
+        <v>13.5</v>
+      </c>
+      <c r="AY29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ29">
+        <v>13.5</v>
+      </c>
+      <c r="BA29">
         <v>25</v>
       </c>
-      <c r="AS29">
-        <v>55</v>
-      </c>
-      <c r="AT29">
-        <v>10.5</v>
-      </c>
-      <c r="AU29">
-        <v>9.4</v>
-      </c>
-      <c r="AV29">
-        <v>16.5</v>
-      </c>
-      <c r="AW29">
-        <v>32</v>
-      </c>
-      <c r="AX29">
+      <c r="BB29">
+        <v>21</v>
+      </c>
+      <c r="BC29">
+        <v>15.5</v>
+      </c>
+      <c r="BD29">
+        <v>21</v>
+      </c>
+      <c r="BE29">
+        <v>38</v>
+      </c>
+      <c r="BF29">
+        <v>14</v>
+      </c>
+      <c r="BG29">
+        <v>19.5</v>
+      </c>
+      <c r="BH29">
+        <v>4.4</v>
+      </c>
+      <c r="BI29">
+        <v>3</v>
+      </c>
+      <c r="BJ29">
         <v>11</v>
       </c>
-      <c r="AY29">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ29">
-        <v>14.5</v>
-      </c>
-      <c r="BA29">
+      <c r="BK29">
+        <v>5.8</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>6.6</v>
+      </c>
+      <c r="BN29">
+        <v>5.3</v>
+      </c>
+      <c r="BO29">
+        <v>4.7</v>
+      </c>
+      <c r="BP29">
+        <v>16</v>
+      </c>
+      <c r="BQ29">
+        <v>4.9</v>
+      </c>
+      <c r="BR29">
+        <v>40</v>
+      </c>
+      <c r="BS29">
+        <v>5.6</v>
+      </c>
+      <c r="BT29">
+        <v>6.8</v>
+      </c>
+      <c r="BU29">
+        <v>5.2</v>
+      </c>
+      <c r="BV29">
         <v>30</v>
       </c>
-      <c r="BB29">
-        <v>16</v>
-      </c>
-      <c r="BC29">
-        <v>14.5</v>
-      </c>
-      <c r="BD29">
-        <v>18.5</v>
-      </c>
-      <c r="BE29">
-        <v>36</v>
-      </c>
-      <c r="BF29">
-        <v>6.6</v>
-      </c>
-      <c r="BG29">
-        <v>27</v>
-      </c>
-      <c r="BH29">
-        <v>1000</v>
-      </c>
-      <c r="BI29">
-        <v>2.06</v>
-      </c>
-      <c r="BJ29">
-        <v>12.5</v>
-      </c>
-      <c r="BK29">
-        <v>1.77</v>
-      </c>
-      <c r="BL29">
-        <v>1000</v>
-      </c>
-      <c r="BM29">
-        <v>2.06</v>
-      </c>
-      <c r="BN29">
-        <v>6.2</v>
-      </c>
-      <c r="BO29">
-        <v>3.3</v>
-      </c>
-      <c r="BP29">
-        <v>15</v>
-      </c>
-      <c r="BQ29">
-        <v>1.81</v>
-      </c>
-      <c r="BR29">
-        <v>29</v>
-      </c>
-      <c r="BS29">
-        <v>1.93</v>
-      </c>
-      <c r="BT29">
-        <v>12.5</v>
-      </c>
-      <c r="BU29">
-        <v>1.77</v>
-      </c>
-      <c r="BV29">
-        <v>50</v>
-      </c>
       <c r="BW29">
-        <v>1.98</v>
+        <v>5.7</v>
       </c>
       <c r="BX29">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY29">
-        <v>1.98</v>
+        <v>6</v>
       </c>
       <c r="BZ29">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="CA29">
-        <v>1.86</v>
+        <v>5.5</v>
       </c>
       <c r="CB29" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7872,19 +7884,19 @@
         <v>131</v>
       </c>
       <c r="E30" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F30">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="G30">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="H30">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="I30">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J30">
         <v>4.1</v>
@@ -7896,37 +7908,37 @@
         <v>1.23</v>
       </c>
       <c r="M30">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N30">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O30">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P30">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q30">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="R30">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="S30">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="T30">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="U30">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V30">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="W30">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="X30">
         <v>34</v>
@@ -7935,169 +7947,169 @@
         <v>21</v>
       </c>
       <c r="Z30">
+        <v>23</v>
+      </c>
+      <c r="AA30">
+        <v>36</v>
+      </c>
+      <c r="AB30">
+        <v>34</v>
+      </c>
+      <c r="AC30">
+        <v>11</v>
+      </c>
+      <c r="AD30">
+        <v>12.5</v>
+      </c>
+      <c r="AE30">
+        <v>21</v>
+      </c>
+      <c r="AF30">
+        <v>29</v>
+      </c>
+      <c r="AG30">
+        <v>14</v>
+      </c>
+      <c r="AH30">
+        <v>13.5</v>
+      </c>
+      <c r="AI30">
+        <v>23</v>
+      </c>
+      <c r="AJ30">
+        <v>55</v>
+      </c>
+      <c r="AK30">
+        <v>27</v>
+      </c>
+      <c r="AL30">
+        <v>29</v>
+      </c>
+      <c r="AM30">
+        <v>46</v>
+      </c>
+      <c r="AN30">
+        <v>13</v>
+      </c>
+      <c r="AO30">
+        <v>9.4</v>
+      </c>
+      <c r="AP30">
+        <v>30</v>
+      </c>
+      <c r="AQ30">
+        <v>18.5</v>
+      </c>
+      <c r="AR30">
+        <v>15.5</v>
+      </c>
+      <c r="AS30">
         <v>32</v>
       </c>
-      <c r="AA30">
-        <v>44</v>
-      </c>
-      <c r="AB30">
-        <v>21</v>
-      </c>
-      <c r="AC30">
-        <v>11.5</v>
-      </c>
-      <c r="AD30">
-        <v>14</v>
-      </c>
-      <c r="AE30">
-        <v>25</v>
-      </c>
-      <c r="AF30">
-        <v>24</v>
-      </c>
-      <c r="AG30">
-        <v>13</v>
-      </c>
-      <c r="AH30">
-        <v>14.5</v>
-      </c>
-      <c r="AI30">
-        <v>27</v>
-      </c>
-      <c r="AJ30">
-        <v>38</v>
-      </c>
-      <c r="AK30">
-        <v>23</v>
-      </c>
-      <c r="AL30">
-        <v>26</v>
-      </c>
-      <c r="AM30">
-        <v>42</v>
-      </c>
-      <c r="AN30">
-        <v>11</v>
-      </c>
-      <c r="AO30">
-        <v>12.5</v>
-      </c>
-      <c r="AP30">
+      <c r="AT30">
         <v>22</v>
-      </c>
-      <c r="AQ30">
-        <v>17.5</v>
-      </c>
-      <c r="AR30">
-        <v>21</v>
-      </c>
-      <c r="AS30">
-        <v>26</v>
-      </c>
-      <c r="AT30">
-        <v>17.5</v>
       </c>
       <c r="AU30">
         <v>10</v>
       </c>
       <c r="AV30">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW30">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX30">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AY30">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ30">
         <v>12.5</v>
       </c>
       <c r="BA30">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BB30">
+        <v>42</v>
+      </c>
+      <c r="BC30">
         <v>23</v>
       </c>
-      <c r="BC30">
-        <v>19.5</v>
-      </c>
       <c r="BD30">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE30">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BF30">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG30">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BH30">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI30">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="BJ30">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK30">
         <v>5.1</v>
       </c>
       <c r="BL30">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM30">
-        <v>2.04</v>
+        <v>11</v>
       </c>
       <c r="BN30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BO30">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BP30">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BQ30">
-        <v>1.91</v>
+        <v>7.8</v>
       </c>
       <c r="BR30">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BS30">
-        <v>1.95</v>
+        <v>8.4</v>
       </c>
       <c r="BT30">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU30">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV30">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="BW30">
-        <v>1.93</v>
+        <v>7.2</v>
       </c>
       <c r="BX30">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY30">
-        <v>1.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ30">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="CA30">
-        <v>1.86</v>
+        <v>6.2</v>
       </c>
       <c r="CB30" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8114,232 +8126,716 @@
         <v>132</v>
       </c>
       <c r="E31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F31">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="G31">
-        <v>2.06</v>
+        <v>1.74</v>
       </c>
       <c r="H31">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="I31">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="J31">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K31">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L31">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M31">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N31">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="O31">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P31">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="Q31">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="R31">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="S31">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="T31">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="U31">
-        <v>2.86</v>
+        <v>2.42</v>
       </c>
       <c r="V31">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="W31">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="X31">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="Y31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z31">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AA31">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AC31">
         <v>10.5</v>
       </c>
       <c r="AD31">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE31">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AF31">
+        <v>13.5</v>
+      </c>
+      <c r="AG31">
+        <v>10.5</v>
+      </c>
+      <c r="AH31">
         <v>17.5</v>
       </c>
-      <c r="AG31">
-        <v>11.5</v>
-      </c>
-      <c r="AH31">
-        <v>15</v>
-      </c>
       <c r="AI31">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AJ31">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AK31">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AM31">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN31">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO31">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="AP31">
         <v>21</v>
       </c>
       <c r="AQ31">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR31">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AS31">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT31">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AU31">
         <v>9.4</v>
       </c>
       <c r="AV31">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW31">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AX31">
+        <v>11</v>
+      </c>
+      <c r="AY31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ31">
         <v>15</v>
       </c>
-      <c r="AY31">
-        <v>10</v>
-      </c>
-      <c r="AZ31">
-        <v>13</v>
-      </c>
       <c r="BA31">
+        <v>27</v>
+      </c>
+      <c r="BB31">
+        <v>16</v>
+      </c>
+      <c r="BC31">
+        <v>14.5</v>
+      </c>
+      <c r="BD31">
+        <v>18</v>
+      </c>
+      <c r="BE31">
+        <v>36</v>
+      </c>
+      <c r="BF31">
+        <v>6.6</v>
+      </c>
+      <c r="BG31">
+        <v>26</v>
+      </c>
+      <c r="BH31">
+        <v>4.5</v>
+      </c>
+      <c r="BI31">
+        <v>3.5</v>
+      </c>
+      <c r="BJ31">
+        <v>9.6</v>
+      </c>
+      <c r="BK31">
+        <v>4.9</v>
+      </c>
+      <c r="BL31">
+        <v>90</v>
+      </c>
+      <c r="BM31">
+        <v>9</v>
+      </c>
+      <c r="BN31">
+        <v>4.9</v>
+      </c>
+      <c r="BO31">
+        <v>3.75</v>
+      </c>
+      <c r="BP31">
+        <v>11.5</v>
+      </c>
+      <c r="BQ31">
+        <v>5.3</v>
+      </c>
+      <c r="BR31">
         <v>22</v>
       </c>
-      <c r="BB31">
-        <v>18.5</v>
-      </c>
-      <c r="BC31">
-        <v>16</v>
-      </c>
-      <c r="BD31">
-        <v>21</v>
-      </c>
-      <c r="BE31">
-        <v>34</v>
-      </c>
-      <c r="BF31">
-        <v>7.8</v>
-      </c>
-      <c r="BG31">
-        <v>18.5</v>
-      </c>
-      <c r="BH31">
-        <v>1000</v>
-      </c>
-      <c r="BI31">
-        <v>3.25</v>
-      </c>
-      <c r="BJ31">
-        <v>12.5</v>
-      </c>
-      <c r="BK31">
-        <v>5.3</v>
-      </c>
-      <c r="BL31">
-        <v>1000</v>
-      </c>
-      <c r="BM31">
-        <v>1.99</v>
-      </c>
-      <c r="BN31">
-        <v>7.8</v>
-      </c>
-      <c r="BO31">
-        <v>3.6</v>
-      </c>
-      <c r="BP31">
-        <v>19</v>
-      </c>
-      <c r="BQ31">
-        <v>1.83</v>
-      </c>
-      <c r="BR31">
-        <v>30</v>
-      </c>
       <c r="BS31">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="BT31">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU31">
         <v>4.8</v>
       </c>
       <c r="BV31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW31">
-        <v>1.91</v>
+        <v>7.8</v>
       </c>
       <c r="BX31">
         <v>40</v>
       </c>
       <c r="BY31">
+        <v>8</v>
+      </c>
+      <c r="BZ31">
+        <v>15</v>
+      </c>
+      <c r="CA31">
+        <v>6</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" t="s">
+        <v>133</v>
+      </c>
+      <c r="E32" t="s">
+        <v>165</v>
+      </c>
+      <c r="F32">
+        <v>2.52</v>
+      </c>
+      <c r="G32">
+        <v>2.56</v>
+      </c>
+      <c r="H32">
+        <v>2.66</v>
+      </c>
+      <c r="I32">
+        <v>2.72</v>
+      </c>
+      <c r="J32">
+        <v>4.1</v>
+      </c>
+      <c r="K32">
+        <v>4.3</v>
+      </c>
+      <c r="L32">
+        <v>1.23</v>
+      </c>
+      <c r="M32">
+        <v>1.02</v>
+      </c>
+      <c r="N32">
+        <v>7.2</v>
+      </c>
+      <c r="O32">
+        <v>1.14</v>
+      </c>
+      <c r="P32">
+        <v>3.1</v>
+      </c>
+      <c r="Q32">
+        <v>1.45</v>
+      </c>
+      <c r="R32">
+        <v>1.86</v>
+      </c>
+      <c r="S32">
+        <v>2.1</v>
+      </c>
+      <c r="T32">
+        <v>1.43</v>
+      </c>
+      <c r="U32">
+        <v>3.15</v>
+      </c>
+      <c r="V32">
+        <v>1.58</v>
+      </c>
+      <c r="W32">
+        <v>1.64</v>
+      </c>
+      <c r="X32">
+        <v>34</v>
+      </c>
+      <c r="Y32">
+        <v>21</v>
+      </c>
+      <c r="Z32">
+        <v>27</v>
+      </c>
+      <c r="AA32">
+        <v>44</v>
+      </c>
+      <c r="AB32">
+        <v>21</v>
+      </c>
+      <c r="AC32">
+        <v>11.5</v>
+      </c>
+      <c r="AD32">
+        <v>13.5</v>
+      </c>
+      <c r="AE32">
+        <v>25</v>
+      </c>
+      <c r="AF32">
+        <v>24</v>
+      </c>
+      <c r="AG32">
+        <v>13</v>
+      </c>
+      <c r="AH32">
+        <v>14.5</v>
+      </c>
+      <c r="AI32">
+        <v>27</v>
+      </c>
+      <c r="AJ32">
+        <v>38</v>
+      </c>
+      <c r="AK32">
+        <v>23</v>
+      </c>
+      <c r="AL32">
+        <v>26</v>
+      </c>
+      <c r="AM32">
+        <v>42</v>
+      </c>
+      <c r="AN32">
+        <v>11</v>
+      </c>
+      <c r="AO32">
+        <v>12.5</v>
+      </c>
+      <c r="AP32">
+        <v>22</v>
+      </c>
+      <c r="AQ32">
+        <v>18.5</v>
+      </c>
+      <c r="AR32">
+        <v>21</v>
+      </c>
+      <c r="AS32">
+        <v>34</v>
+      </c>
+      <c r="AT32">
+        <v>18</v>
+      </c>
+      <c r="AU32">
+        <v>10</v>
+      </c>
+      <c r="AV32">
+        <v>11.5</v>
+      </c>
+      <c r="AW32">
+        <v>20</v>
+      </c>
+      <c r="AX32">
+        <v>19.5</v>
+      </c>
+      <c r="AY32">
+        <v>11.5</v>
+      </c>
+      <c r="AZ32">
+        <v>12.5</v>
+      </c>
+      <c r="BA32">
+        <v>18</v>
+      </c>
+      <c r="BB32">
+        <v>23</v>
+      </c>
+      <c r="BC32">
+        <v>19.5</v>
+      </c>
+      <c r="BD32">
+        <v>21</v>
+      </c>
+      <c r="BE32">
+        <v>28</v>
+      </c>
+      <c r="BF32">
+        <v>9.6</v>
+      </c>
+      <c r="BG32">
+        <v>11</v>
+      </c>
+      <c r="BH32">
+        <v>6.2</v>
+      </c>
+      <c r="BI32">
+        <v>4</v>
+      </c>
+      <c r="BJ32">
+        <v>8.6</v>
+      </c>
+      <c r="BK32">
+        <v>6</v>
+      </c>
+      <c r="BL32">
+        <v>60</v>
+      </c>
+      <c r="BM32">
+        <v>5.7</v>
+      </c>
+      <c r="BN32">
+        <v>6.6</v>
+      </c>
+      <c r="BO32">
+        <v>4.8</v>
+      </c>
+      <c r="BP32">
+        <v>16.5</v>
+      </c>
+      <c r="BQ32">
+        <v>4.5</v>
+      </c>
+      <c r="BR32">
+        <v>22</v>
+      </c>
+      <c r="BS32">
+        <v>4.9</v>
+      </c>
+      <c r="BT32">
+        <v>8</v>
+      </c>
+      <c r="BU32">
+        <v>5.7</v>
+      </c>
+      <c r="BV32">
+        <v>21</v>
+      </c>
+      <c r="BW32">
+        <v>4.8</v>
+      </c>
+      <c r="BX32">
+        <v>26</v>
+      </c>
+      <c r="BY32">
+        <v>5.1</v>
+      </c>
+      <c r="BZ32">
+        <v>12.5</v>
+      </c>
+      <c r="CA32">
+        <v>4.2</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33">
+        <v>2.04</v>
+      </c>
+      <c r="G33">
+        <v>2.08</v>
+      </c>
+      <c r="H33">
+        <v>3.5</v>
+      </c>
+      <c r="I33">
+        <v>3.65</v>
+      </c>
+      <c r="J33">
+        <v>4.2</v>
+      </c>
+      <c r="K33">
+        <v>4.4</v>
+      </c>
+      <c r="L33">
+        <v>1.26</v>
+      </c>
+      <c r="M33">
+        <v>1.03</v>
+      </c>
+      <c r="N33">
+        <v>6.4</v>
+      </c>
+      <c r="O33">
+        <v>1.16</v>
+      </c>
+      <c r="P33">
+        <v>2.88</v>
+      </c>
+      <c r="Q33">
+        <v>1.5</v>
+      </c>
+      <c r="R33">
+        <v>1.75</v>
+      </c>
+      <c r="S33">
+        <v>2.24</v>
+      </c>
+      <c r="T33">
+        <v>1.5</v>
+      </c>
+      <c r="U33">
+        <v>2.86</v>
+      </c>
+      <c r="V33">
+        <v>1.37</v>
+      </c>
+      <c r="W33">
         <v>1.93</v>
       </c>
-      <c r="BZ31">
-        <v>19</v>
-      </c>
-      <c r="CA31">
-        <v>1.83</v>
-      </c>
-      <c r="CB31" t="s">
-        <v>163</v>
+      <c r="X33">
+        <v>55</v>
+      </c>
+      <c r="Y33">
+        <v>23</v>
+      </c>
+      <c r="Z33">
+        <v>32</v>
+      </c>
+      <c r="AA33">
+        <v>1000</v>
+      </c>
+      <c r="AB33">
+        <v>16</v>
+      </c>
+      <c r="AC33">
+        <v>10.5</v>
+      </c>
+      <c r="AD33">
+        <v>16</v>
+      </c>
+      <c r="AE33">
+        <v>34</v>
+      </c>
+      <c r="AF33">
+        <v>17.5</v>
+      </c>
+      <c r="AG33">
+        <v>11.5</v>
+      </c>
+      <c r="AH33">
+        <v>15</v>
+      </c>
+      <c r="AI33">
+        <v>34</v>
+      </c>
+      <c r="AJ33">
+        <v>27</v>
+      </c>
+      <c r="AK33">
+        <v>18</v>
+      </c>
+      <c r="AL33">
+        <v>24</v>
+      </c>
+      <c r="AM33">
+        <v>190</v>
+      </c>
+      <c r="AN33">
+        <v>8.4</v>
+      </c>
+      <c r="AO33">
+        <v>20</v>
+      </c>
+      <c r="AP33">
+        <v>23</v>
+      </c>
+      <c r="AQ33">
+        <v>19.5</v>
+      </c>
+      <c r="AR33">
+        <v>22</v>
+      </c>
+      <c r="AS33">
+        <v>42</v>
+      </c>
+      <c r="AT33">
+        <v>14</v>
+      </c>
+      <c r="AU33">
+        <v>9.6</v>
+      </c>
+      <c r="AV33">
+        <v>13.5</v>
+      </c>
+      <c r="AW33">
+        <v>21</v>
+      </c>
+      <c r="AX33">
+        <v>15</v>
+      </c>
+      <c r="AY33">
+        <v>10</v>
+      </c>
+      <c r="AZ33">
+        <v>13</v>
+      </c>
+      <c r="BA33">
+        <v>21</v>
+      </c>
+      <c r="BB33">
+        <v>18.5</v>
+      </c>
+      <c r="BC33">
+        <v>16</v>
+      </c>
+      <c r="BD33">
+        <v>21</v>
+      </c>
+      <c r="BE33">
+        <v>34</v>
+      </c>
+      <c r="BF33">
+        <v>7.8</v>
+      </c>
+      <c r="BG33">
+        <v>18</v>
+      </c>
+      <c r="BH33">
+        <v>5.7</v>
+      </c>
+      <c r="BI33">
+        <v>4.3</v>
+      </c>
+      <c r="BJ33">
+        <v>10</v>
+      </c>
+      <c r="BK33">
+        <v>4.1</v>
+      </c>
+      <c r="BL33">
+        <v>95</v>
+      </c>
+      <c r="BM33">
+        <v>6.2</v>
+      </c>
+      <c r="BN33">
+        <v>5.5</v>
+      </c>
+      <c r="BO33">
+        <v>4.2</v>
+      </c>
+      <c r="BP33">
+        <v>16</v>
+      </c>
+      <c r="BQ33">
+        <v>8</v>
+      </c>
+      <c r="BR33">
+        <v>20</v>
+      </c>
+      <c r="BS33">
+        <v>5.1</v>
+      </c>
+      <c r="BT33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU33">
+        <v>5.5</v>
+      </c>
+      <c r="BV33">
+        <v>23</v>
+      </c>
+      <c r="BW33">
+        <v>5.3</v>
+      </c>
+      <c r="BX33">
+        <v>27</v>
+      </c>
+      <c r="BY33">
+        <v>5.5</v>
+      </c>
+      <c r="BZ33">
+        <v>13</v>
+      </c>
+      <c r="CA33">
+        <v>4.5</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -517,7 +517,7 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-18 11:12:28</t>
+    <t>2026-08-18 13:20:51</t>
   </si>
 </sst>
 </file>
@@ -1111,19 +1111,19 @@
         <v>135</v>
       </c>
       <c r="F2">
+        <v>2.26</v>
+      </c>
+      <c r="G2">
         <v>2.3</v>
       </c>
-      <c r="G2">
-        <v>2.32</v>
-      </c>
       <c r="H2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
         <v>3.25</v>
@@ -1135,34 +1135,34 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P2">
         <v>1.68</v>
       </c>
       <c r="Q2">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T2">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U2">
         <v>1.93</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="X2">
         <v>11</v>
@@ -1186,7 +1186,7 @@
         <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF2">
         <v>13</v>
@@ -1201,37 +1201,37 @@
         <v>75</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AM2">
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AO2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP2">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR2">
         <v>23</v>
       </c>
       <c r="AS2">
-        <v>13.5</v>
+        <v>60</v>
       </c>
       <c r="AT2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1252,7 +1252,7 @@
         <v>18</v>
       </c>
       <c r="BA2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB2">
         <v>23</v>
@@ -1264,31 +1264,31 @@
         <v>42</v>
       </c>
       <c r="BE2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF2">
         <v>21</v>
       </c>
       <c r="BG2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI2">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BN2">
         <v>5.6</v>
@@ -1297,16 +1297,16 @@
         <v>4.4</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BQ2">
+        <v>11</v>
+      </c>
+      <c r="BR2">
+        <v>38</v>
+      </c>
+      <c r="BS2">
         <v>5.7</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>5.5</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
@@ -1315,22 +1315,22 @@
         <v>6</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BZ2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB2" t="s">
         <v>167</v>
@@ -1353,22 +1353,22 @@
         <v>136</v>
       </c>
       <c r="F3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G3">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I3">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="J3">
         <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
         <v>1.6</v>
@@ -1383,7 +1383,7 @@
         <v>1.56</v>
       </c>
       <c r="P3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q3">
         <v>2.72</v>
@@ -1401,13 +1401,13 @@
         <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y3">
         <v>8.4</v>
@@ -1419,7 +1419,7 @@
         <v>40</v>
       </c>
       <c r="AB3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC3">
         <v>7</v>
@@ -1452,10 +1452,10 @@
         <v>100</v>
       </c>
       <c r="AM3">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AO3">
         <v>42</v>
@@ -1470,7 +1470,7 @@
         <v>13</v>
       </c>
       <c r="AS3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT3">
         <v>8.800000000000001</v>
@@ -1506,52 +1506,52 @@
         <v>55</v>
       </c>
       <c r="BE3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF3">
         <v>55</v>
       </c>
       <c r="BG3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH3">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BI3">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3">
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BN3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BR3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BT3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU3">
         <v>4.6</v>
@@ -1560,19 +1560,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>2.28</v>
+        <v>14</v>
       </c>
       <c r="CB3" t="s">
         <v>167</v>
@@ -1598,13 +1598,13 @@
         <v>3.25</v>
       </c>
       <c r="G4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H4">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I4">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J4">
         <v>3.15</v>
@@ -1619,13 +1619,13 @@
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="O4">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q4">
         <v>2.58</v>
@@ -1634,25 +1634,25 @@
         <v>1.21</v>
       </c>
       <c r="S4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T4">
         <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W4">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z4">
         <v>15</v>
@@ -1661,7 +1661,7 @@
         <v>42</v>
       </c>
       <c r="AB4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -1688,7 +1688,7 @@
         <v>65</v>
       </c>
       <c r="AK4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL4">
         <v>70</v>
@@ -1709,7 +1709,7 @@
         <v>7.6</v>
       </c>
       <c r="AR4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS4">
         <v>34</v>
@@ -1727,13 +1727,13 @@
         <v>30</v>
       </c>
       <c r="AX4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY4">
         <v>13</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA4">
         <v>50</v>
@@ -1745,76 +1745,76 @@
         <v>40</v>
       </c>
       <c r="BD4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE4">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="BF4">
         <v>50</v>
       </c>
       <c r="BG4">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BH4">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BI4">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
+        <v>5.5</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>10</v>
+      </c>
+      <c r="BN4">
+        <v>6.6</v>
+      </c>
+      <c r="BO4">
+        <v>5.4</v>
+      </c>
+      <c r="BP4">
+        <v>32</v>
+      </c>
+      <c r="BQ4">
         <v>8.199999999999999</v>
       </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>13</v>
-      </c>
-      <c r="BN4">
-        <v>6.2</v>
-      </c>
-      <c r="BO4">
-        <v>5.2</v>
-      </c>
-      <c r="BP4">
-        <v>30</v>
-      </c>
-      <c r="BQ4">
-        <v>9.6</v>
-      </c>
       <c r="BR4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BT4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BU4">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV4">
         <v>23</v>
       </c>
       <c r="BW4">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="s">
         <v>167</v>
@@ -1840,10 +1840,10 @@
         <v>2.36</v>
       </c>
       <c r="G5">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>4.1</v>
@@ -1861,22 +1861,22 @@
         <v>1.15</v>
       </c>
       <c r="N5">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P5">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q5">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="R5">
         <v>1.17</v>
       </c>
       <c r="S5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T5">
         <v>2.28</v>
@@ -1888,7 +1888,7 @@
         <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X5">
         <v>7.4</v>
@@ -1900,7 +1900,7 @@
         <v>27</v>
       </c>
       <c r="AA5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB5">
         <v>6.8</v>
@@ -1924,25 +1924,25 @@
         <v>26</v>
       </c>
       <c r="AI5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK5">
         <v>42</v>
       </c>
       <c r="AL5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM5">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AN5">
         <v>40</v>
       </c>
       <c r="AO5">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AP5">
         <v>7</v>
@@ -1963,7 +1963,7 @@
         <v>6.4</v>
       </c>
       <c r="AV5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW5">
         <v>46</v>
@@ -1990,13 +1990,13 @@
         <v>48</v>
       </c>
       <c r="BE5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BF5">
         <v>34</v>
       </c>
       <c r="BG5">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH5">
         <v>2.82</v>
@@ -2011,13 +2011,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM5">
         <v>10.5</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO5">
         <v>4.3</v>
@@ -2026,25 +2026,25 @@
         <v>21</v>
       </c>
       <c r="BQ5">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BR5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS5">
         <v>9</v>
       </c>
       <c r="BT5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV5">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BW5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5">
         <v>70</v>
@@ -2053,10 +2053,10 @@
         <v>9.6</v>
       </c>
       <c r="BZ5">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="CA5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB5" t="s">
         <v>167</v>
@@ -2079,19 +2079,19 @@
         <v>139</v>
       </c>
       <c r="F6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G6">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="H6">
         <v>6.8</v>
       </c>
       <c r="I6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>5.3</v>
@@ -2112,13 +2112,13 @@
         <v>2.84</v>
       </c>
       <c r="Q6">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="R6">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T6">
         <v>1.67</v>
@@ -2130,13 +2130,13 @@
         <v>1.16</v>
       </c>
       <c r="W6">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="X6">
         <v>32</v>
       </c>
       <c r="Y6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z6">
         <v>70</v>
@@ -2166,7 +2166,7 @@
         <v>19</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="AJ6">
         <v>15</v>
@@ -2187,7 +2187,7 @@
         <v>65</v>
       </c>
       <c r="AP6">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AQ6">
         <v>30</v>
@@ -2208,7 +2208,7 @@
         <v>22</v>
       </c>
       <c r="AW6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX6">
         <v>10.5</v>
@@ -2262,25 +2262,25 @@
         <v>4.7</v>
       </c>
       <c r="BO6">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BP6">
         <v>9.199999999999999</v>
       </c>
       <c r="BQ6">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BR6">
         <v>19.5</v>
       </c>
       <c r="BS6">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
         <v>11.5</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2321,7 +2321,7 @@
         <v>140</v>
       </c>
       <c r="F7">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G7">
         <v>990</v>
@@ -2333,7 +2333,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2351,16 +2351,16 @@
         <v>1.52</v>
       </c>
       <c r="P7">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q7">
-        <v>1.52</v>
+        <v>2.12</v>
       </c>
       <c r="R7">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S7">
-        <v>1.05</v>
+        <v>3.6</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2369,10 +2369,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2429,52 +2429,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2486,61 +2486,61 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>167</v>
@@ -2590,19 +2590,19 @@
         <v>1.1</v>
       </c>
       <c r="O8">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
         <v>1.09</v>
       </c>
       <c r="Q8">
-        <v>1.92</v>
+        <v>1.02</v>
       </c>
       <c r="R8">
         <v>1.07</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>1.45</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2805,13 +2805,13 @@
         <v>142</v>
       </c>
       <c r="F9">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="G9">
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="I9">
         <v>990</v>
@@ -2820,31 +2820,31 @@
         <v>1.04</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N9">
         <v>1.1</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="P9">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q9">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="R9">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S9">
-        <v>1.43</v>
+        <v>3.85</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2856,7 +2856,7 @@
         <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3047,19 +3047,19 @@
         <v>143</v>
       </c>
       <c r="F10">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="G10">
-        <v>990</v>
+        <v>2.88</v>
       </c>
       <c r="H10">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>990</v>
       </c>
       <c r="J10">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3071,10 +3071,10 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P10">
         <v>1.09</v>
@@ -3086,7 +3086,7 @@
         <v>1.07</v>
       </c>
       <c r="S10">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3098,7 +3098,7 @@
         <v>1.02</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3289,19 +3289,19 @@
         <v>144</v>
       </c>
       <c r="F11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G11">
         <v>990</v>
       </c>
       <c r="H11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I11">
         <v>990</v>
       </c>
       <c r="J11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K11">
         <v>950</v>
@@ -3319,7 +3319,7 @@
         <v>1.01</v>
       </c>
       <c r="P11">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q11">
         <v>1.32</v>
@@ -3337,7 +3337,7 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11">
         <v>1.01</v>
@@ -3531,46 +3531,46 @@
         <v>145</v>
       </c>
       <c r="F12">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="G12">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="H12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J12">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M12">
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O12">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P12">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="Q12">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="R12">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="S12">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T12">
         <v>2.28</v>
@@ -3579,46 +3579,46 @@
         <v>1.63</v>
       </c>
       <c r="V12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W12">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="X12">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y12">
         <v>950</v>
       </c>
       <c r="Z12">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC12">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AD12">
         <v>950</v>
       </c>
       <c r="AE12">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="AF12">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH12">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AI12">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AJ12">
         <v>10.5</v>
@@ -3627,76 +3627,76 @@
         <v>18</v>
       </c>
       <c r="AL12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM12">
         <v>300</v>
       </c>
       <c r="AN12">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AO12">
         <v>1000</v>
       </c>
       <c r="AP12">
+        <v>19</v>
+      </c>
+      <c r="AQ12">
         <v>4.3</v>
       </c>
-      <c r="AQ12">
+      <c r="AR12">
         <v>4.6</v>
       </c>
-      <c r="AR12">
-        <v>4.9</v>
-      </c>
       <c r="AS12">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AT12">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU12">
-        <v>3.95</v>
+        <v>12.5</v>
       </c>
       <c r="AV12">
+        <v>4.4</v>
+      </c>
+      <c r="AW12">
+        <v>4.6</v>
+      </c>
+      <c r="AX12">
+        <v>3.05</v>
+      </c>
+      <c r="AY12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12">
+        <v>4.3</v>
+      </c>
+      <c r="BA12">
+        <v>4.6</v>
+      </c>
+      <c r="BB12">
+        <v>3.25</v>
+      </c>
+      <c r="BC12">
+        <v>12.5</v>
+      </c>
+      <c r="BD12">
+        <v>4.3</v>
+      </c>
+      <c r="BE12">
+        <v>4.6</v>
+      </c>
+      <c r="BF12">
+        <v>3.65</v>
+      </c>
+      <c r="BG12">
         <v>4.7</v>
       </c>
-      <c r="AW12">
-        <v>4.9</v>
-      </c>
-      <c r="AX12">
-        <v>6.4</v>
-      </c>
-      <c r="AY12">
-        <v>3.7</v>
-      </c>
-      <c r="AZ12">
-        <v>4.5</v>
-      </c>
-      <c r="BA12">
-        <v>4.9</v>
-      </c>
-      <c r="BB12">
-        <v>6.6</v>
-      </c>
-      <c r="BC12">
-        <v>3.9</v>
-      </c>
-      <c r="BD12">
-        <v>4.6</v>
-      </c>
-      <c r="BE12">
-        <v>4.9</v>
-      </c>
-      <c r="BF12">
-        <v>3.7</v>
-      </c>
-      <c r="BG12">
-        <v>5</v>
-      </c>
       <c r="BH12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI12">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12">
         <v>14.5</v>
@@ -3711,28 +3711,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BN12">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BO12">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BP12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BQ12">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BU12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV12">
         <v>1000</v>
@@ -3744,13 +3744,13 @@
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA12">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB12" t="s">
         <v>167</v>
@@ -3773,40 +3773,40 @@
         <v>146</v>
       </c>
       <c r="F13">
+        <v>1.03</v>
+      </c>
+      <c r="G13">
+        <v>990</v>
+      </c>
+      <c r="H13">
+        <v>1.03</v>
+      </c>
+      <c r="I13">
+        <v>990</v>
+      </c>
+      <c r="J13">
+        <v>1.04</v>
+      </c>
+      <c r="K13">
+        <v>950</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>1.1</v>
+      </c>
+      <c r="O13">
         <v>1.02</v>
       </c>
-      <c r="G13">
-        <v>110</v>
-      </c>
-      <c r="H13">
-        <v>1.02</v>
-      </c>
-      <c r="I13">
-        <v>110</v>
-      </c>
-      <c r="J13">
-        <v>1.02</v>
-      </c>
-      <c r="K13">
-        <v>110</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.01</v>
-      </c>
-      <c r="N13">
-        <v>1.06</v>
-      </c>
-      <c r="O13">
-        <v>1.01</v>
-      </c>
       <c r="P13">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Q13">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R13">
         <v>1.07</v>
@@ -3815,10 +3815,10 @@
         <v>1.38</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
         <v>1.01</v>
@@ -3938,61 +3938,61 @@
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
         <v>167</v>
@@ -4045,7 +4045,7 @@
         <v>1.01</v>
       </c>
       <c r="P14">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q14">
         <v>1.02</v>
@@ -4257,7 +4257,7 @@
         <v>148</v>
       </c>
       <c r="F15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G15">
         <v>990</v>
@@ -4269,7 +4269,7 @@
         <v>990</v>
       </c>
       <c r="J15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4281,22 +4281,22 @@
         <v>1.05</v>
       </c>
       <c r="N15">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="O15">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P15">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Q15">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R15">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S15">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4305,7 +4305,7 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15">
         <v>1.02</v>
@@ -4499,7 +4499,7 @@
         <v>149</v>
       </c>
       <c r="F16">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G16">
         <v>1.37</v>
@@ -4517,34 +4517,34 @@
         <v>5.7</v>
       </c>
       <c r="L16">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M16">
         <v>1.06</v>
       </c>
       <c r="N16">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P16">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q16">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="R16">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S16">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T16">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="U16">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V16">
         <v>1.09</v>
@@ -4553,10 +4553,10 @@
         <v>3.75</v>
       </c>
       <c r="X16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y16">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z16">
         <v>110</v>
@@ -4565,13 +4565,13 @@
         <v>570</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC16">
         <v>12.5</v>
       </c>
       <c r="AD16">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE16">
         <v>240</v>
@@ -4589,37 +4589,37 @@
         <v>190</v>
       </c>
       <c r="AJ16">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK16">
+        <v>16</v>
+      </c>
+      <c r="AL16">
+        <v>48</v>
+      </c>
+      <c r="AM16">
+        <v>260</v>
+      </c>
+      <c r="AN16">
+        <v>6.2</v>
+      </c>
+      <c r="AO16">
+        <v>470</v>
+      </c>
+      <c r="AP16">
         <v>15</v>
       </c>
-      <c r="AL16">
+      <c r="AQ16">
+        <v>26</v>
+      </c>
+      <c r="AR16">
         <v>46</v>
-      </c>
-      <c r="AM16">
-        <v>240</v>
-      </c>
-      <c r="AN16">
-        <v>5.8</v>
-      </c>
-      <c r="AO16">
-        <v>400</v>
-      </c>
-      <c r="AP16">
-        <v>16</v>
-      </c>
-      <c r="AQ16">
-        <v>27</v>
-      </c>
-      <c r="AR16">
-        <v>42</v>
       </c>
       <c r="AS16">
         <v>140</v>
       </c>
       <c r="AT16">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU16">
         <v>11.5</v>
@@ -4637,34 +4637,34 @@
         <v>10</v>
       </c>
       <c r="AZ16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA16">
         <v>46</v>
       </c>
       <c r="BB16">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC16">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD16">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE16">
         <v>50</v>
       </c>
       <c r="BF16">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG16">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BH16">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="BI16">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BJ16">
         <v>14</v>
@@ -4673,52 +4673,52 @@
         <v>8</v>
       </c>
       <c r="BL16">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="BM16">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="BN16">
         <v>3.55</v>
       </c>
       <c r="BO16">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BP16">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BQ16">
         <v>6.6</v>
       </c>
       <c r="BR16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT16">
         <v>15.5</v>
       </c>
       <c r="BU16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BV16">
         <v>130</v>
       </c>
       <c r="BW16">
+        <v>16</v>
+      </c>
+      <c r="BX16">
+        <v>120</v>
+      </c>
+      <c r="BY16">
         <v>15.5</v>
       </c>
-      <c r="BX16">
-        <v>110</v>
-      </c>
-      <c r="BY16">
+      <c r="BZ16">
         <v>15</v>
       </c>
-      <c r="BZ16">
-        <v>13.5</v>
-      </c>
       <c r="CA16">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB16" t="s">
         <v>167</v>
@@ -4750,13 +4750,13 @@
         <v>4.2</v>
       </c>
       <c r="I17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J17">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K17">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L17">
         <v>1.4</v>
@@ -4768,10 +4768,10 @@
         <v>3.15</v>
       </c>
       <c r="O17">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P17">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q17">
         <v>2.14</v>
@@ -4786,13 +4786,13 @@
         <v>1.92</v>
       </c>
       <c r="U17">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V17">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W17">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X17">
         <v>13.5</v>
@@ -4813,7 +4813,7 @@
         <v>8</v>
       </c>
       <c r="AD17">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AE17">
         <v>85</v>
@@ -4825,7 +4825,7 @@
         <v>11</v>
       </c>
       <c r="AH17">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI17">
         <v>95</v>
@@ -4849,16 +4849,16 @@
         <v>100</v>
       </c>
       <c r="AP17">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ17">
         <v>12</v>
       </c>
       <c r="AR17">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS17">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT17">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15.5</v>
       </c>
       <c r="AW17">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AX17">
         <v>10.5</v>
@@ -4882,7 +4882,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA17">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB17">
         <v>21</v>
@@ -4894,13 +4894,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE17">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF17">
         <v>16</v>
       </c>
       <c r="BG17">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH17">
         <v>3.5</v>
@@ -4986,7 +4986,7 @@
         <v>2.38</v>
       </c>
       <c r="G18">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H18">
         <v>3.5</v>
@@ -5001,16 +5001,16 @@
         <v>3.25</v>
       </c>
       <c r="L18">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
         <v>1.11</v>
       </c>
       <c r="N18">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O18">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P18">
         <v>1.53</v>
@@ -5025,22 +5025,22 @@
         <v>5.6</v>
       </c>
       <c r="T18">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U18">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V18">
         <v>1.37</v>
       </c>
       <c r="W18">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X18">
         <v>9.199999999999999</v>
       </c>
       <c r="Y18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z18">
         <v>25</v>
@@ -5049,7 +5049,7 @@
         <v>85</v>
       </c>
       <c r="AB18">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -5067,7 +5067,7 @@
         <v>12</v>
       </c>
       <c r="AH18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI18">
         <v>95</v>
@@ -5088,7 +5088,7 @@
         <v>38</v>
       </c>
       <c r="AO18">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP18">
         <v>8</v>
@@ -5103,7 +5103,7 @@
         <v>10.5</v>
       </c>
       <c r="AT18">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU18">
         <v>6.8</v>
@@ -5133,7 +5133,7 @@
         <v>29</v>
       </c>
       <c r="BD18">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="BE18">
         <v>11</v>
@@ -5142,67 +5142,67 @@
         <v>29</v>
       </c>
       <c r="BG18">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="BH18">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
         <v>167</v>
@@ -5225,40 +5225,40 @@
         <v>152</v>
       </c>
       <c r="F19">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G19">
         <v>5.9</v>
       </c>
       <c r="H19">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="I19">
         <v>1.89</v>
       </c>
       <c r="J19">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K19">
         <v>3.6</v>
       </c>
       <c r="L19">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M19">
         <v>1.11</v>
       </c>
       <c r="N19">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="O19">
         <v>1.48</v>
       </c>
       <c r="P19">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q19">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R19">
         <v>1.22</v>
@@ -5276,7 +5276,7 @@
         <v>2.12</v>
       </c>
       <c r="W19">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X19">
         <v>9.800000000000001</v>
@@ -5312,7 +5312,7 @@
         <v>28</v>
       </c>
       <c r="AI19">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ19">
         <v>210</v>
@@ -5330,7 +5330,7 @@
         <v>220</v>
       </c>
       <c r="AO19">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP19">
         <v>8.6</v>
@@ -5357,7 +5357,7 @@
         <v>21</v>
       </c>
       <c r="AX19">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="AY19">
         <v>20</v>
@@ -5366,7 +5366,7 @@
         <v>23</v>
       </c>
       <c r="BA19">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB19">
         <v>11</v>
@@ -5375,7 +5375,7 @@
         <v>10.5</v>
       </c>
       <c r="BD19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE19">
         <v>11</v>
@@ -5393,34 +5393,34 @@
         <v>2.38</v>
       </c>
       <c r="BJ19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK19">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BN19">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO19">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BP19">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BQ19">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BR19">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BS19">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BT19">
         <v>4.2</v>
@@ -5432,19 +5432,19 @@
         <v>14.5</v>
       </c>
       <c r="BW19">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BX19">
         <v>44</v>
       </c>
       <c r="BY19">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BZ19">
         <v>38</v>
       </c>
       <c r="CA19">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB19" t="s">
         <v>167</v>
@@ -5476,7 +5476,7 @@
         <v>6.2</v>
       </c>
       <c r="I20">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J20">
         <v>3.7</v>
@@ -5497,7 +5497,7 @@
         <v>1.34</v>
       </c>
       <c r="P20">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q20">
         <v>2.12</v>
@@ -5536,7 +5536,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD20">
         <v>28</v>
@@ -5581,10 +5581,10 @@
         <v>15.5</v>
       </c>
       <c r="AR20">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS20">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT20">
         <v>6</v>
@@ -5593,10 +5593,10 @@
         <v>7.6</v>
       </c>
       <c r="AV20">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AW20">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX20">
         <v>7.6</v>
@@ -5608,7 +5608,7 @@
         <v>21</v>
       </c>
       <c r="BA20">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB20">
         <v>14</v>
@@ -5617,16 +5617,16 @@
         <v>17.5</v>
       </c>
       <c r="BD20">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE20">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF20">
         <v>10.5</v>
       </c>
       <c r="BG20">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH20">
         <v>3.8</v>
@@ -5635,58 +5635,58 @@
         <v>2.64</v>
       </c>
       <c r="BJ20">
+        <v>14</v>
+      </c>
+      <c r="BK20">
+        <v>3.6</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>4.7</v>
+      </c>
+      <c r="BN20">
+        <v>4.6</v>
+      </c>
+      <c r="BO20">
+        <v>3.05</v>
+      </c>
+      <c r="BP20">
+        <v>13.5</v>
+      </c>
+      <c r="BQ20">
+        <v>3.55</v>
+      </c>
+      <c r="BR20">
+        <v>38</v>
+      </c>
+      <c r="BS20">
+        <v>4.3</v>
+      </c>
+      <c r="BT20">
         <v>12</v>
       </c>
-      <c r="BK20">
-        <v>8.4</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>7.4</v>
-      </c>
-      <c r="BN20">
-        <v>4</v>
-      </c>
-      <c r="BO20">
-        <v>3.4</v>
-      </c>
-      <c r="BP20">
-        <v>12</v>
-      </c>
-      <c r="BQ20">
-        <v>4.7</v>
-      </c>
-      <c r="BR20">
-        <v>36</v>
-      </c>
-      <c r="BS20">
-        <v>6.2</v>
-      </c>
-      <c r="BT20">
-        <v>10.5</v>
-      </c>
       <c r="BU20">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW20">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BX20">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="BY20">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ20">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="CA20">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="CB20" t="s">
         <v>167</v>
@@ -5709,16 +5709,16 @@
         <v>154</v>
       </c>
       <c r="F21">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G21">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H21">
         <v>2.82</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J21">
         <v>3.2</v>
@@ -5727,7 +5727,7 @@
         <v>3.3</v>
       </c>
       <c r="L21">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M21">
         <v>1.09</v>
@@ -5739,7 +5739,7 @@
         <v>1.41</v>
       </c>
       <c r="P21">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q21">
         <v>2.22</v>
@@ -5757,7 +5757,7 @@
         <v>1.98</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W21">
         <v>1.51</v>
@@ -5775,10 +5775,10 @@
         <v>60</v>
       </c>
       <c r="AB21">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21">
         <v>16</v>
@@ -5790,7 +5790,7 @@
         <v>23</v>
       </c>
       <c r="AG21">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH21">
         <v>23</v>
@@ -5823,10 +5823,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR21">
+        <v>3.9</v>
+      </c>
+      <c r="AS21">
         <v>4.3</v>
-      </c>
-      <c r="AS21">
-        <v>5.1</v>
       </c>
       <c r="AT21">
         <v>8.6</v>
@@ -5838,7 +5838,7 @@
         <v>11.5</v>
       </c>
       <c r="AW21">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX21">
         <v>16</v>
@@ -5850,31 +5850,31 @@
         <v>16.5</v>
       </c>
       <c r="BA21">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB21">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BC21">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BD21">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE21">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF21">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BG21">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BH21">
         <v>3.5</v>
       </c>
       <c r="BI21">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="BJ21">
         <v>12</v>
@@ -5963,13 +5963,13 @@
         <v>2.92</v>
       </c>
       <c r="J22">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K22">
         <v>4.4</v>
       </c>
       <c r="L22">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
         <v>1.01</v>
@@ -5981,13 +5981,13 @@
         <v>1.2</v>
       </c>
       <c r="P22">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q22">
         <v>1.59</v>
       </c>
       <c r="R22">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S22">
         <v>2.48</v>
@@ -6011,19 +6011,19 @@
         <v>19.5</v>
       </c>
       <c r="Z22">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA22">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB22">
         <v>16.5</v>
       </c>
       <c r="AC22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE22">
         <v>28</v>
@@ -6035,10 +6035,10 @@
         <v>15</v>
       </c>
       <c r="AH22">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI22">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ22">
         <v>44</v>
@@ -6050,10 +6050,10 @@
         <v>38</v>
       </c>
       <c r="AM22">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN22">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO22">
         <v>17.5</v>
@@ -6062,16 +6062,16 @@
         <v>17</v>
       </c>
       <c r="AQ22">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
         <v>7.2</v>
@@ -6083,7 +6083,7 @@
         <v>19</v>
       </c>
       <c r="AX22">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AY22">
         <v>9.199999999999999</v>
@@ -6092,85 +6092,85 @@
         <v>11</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
         <v>17.5</v>
       </c>
       <c r="BD22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE22">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
         <v>10.5</v>
       </c>
       <c r="BG22">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
         <v>167</v>
@@ -6193,22 +6193,22 @@
         <v>156</v>
       </c>
       <c r="F23">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G23">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H23">
         <v>4.7</v>
       </c>
       <c r="I23">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K23">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L23">
         <v>1.29</v>
@@ -6217,22 +6217,22 @@
         <v>1.05</v>
       </c>
       <c r="N23">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O23">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P23">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q23">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="R23">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S23">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="T23">
         <v>1.76</v>
@@ -6241,22 +6241,22 @@
         <v>2.08</v>
       </c>
       <c r="V23">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W23">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X23">
         <v>22</v>
       </c>
       <c r="Y23">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z23">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA23">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB23">
         <v>12</v>
@@ -6265,10 +6265,10 @@
         <v>11.5</v>
       </c>
       <c r="AD23">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE23">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF23">
         <v>14</v>
@@ -6280,52 +6280,52 @@
         <v>24</v>
       </c>
       <c r="AI23">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL23">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM23">
         <v>120</v>
       </c>
       <c r="AN23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO23">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP23">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
+        <v>1.03</v>
+      </c>
+      <c r="AR23">
+        <v>1.01</v>
+      </c>
+      <c r="AS23">
+        <v>1.01</v>
+      </c>
+      <c r="AT23">
+        <v>1.01</v>
+      </c>
+      <c r="AU23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV23">
         <v>14</v>
       </c>
-      <c r="AR23">
-        <v>1.01</v>
-      </c>
-      <c r="AS23">
-        <v>1.01</v>
-      </c>
-      <c r="AT23">
-        <v>7.2</v>
-      </c>
-      <c r="AU23">
-        <v>7</v>
-      </c>
-      <c r="AV23">
-        <v>14.5</v>
-      </c>
       <c r="AW23">
         <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AY23">
         <v>7.6</v>
@@ -6343,7 +6343,7 @@
         <v>13</v>
       </c>
       <c r="BD23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
         <v>1.01</v>
@@ -6355,16 +6355,16 @@
         <v>1.01</v>
       </c>
       <c r="BH23">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI23">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ23">
         <v>10</v>
       </c>
       <c r="BK23">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL23">
         <v>1000</v>
@@ -6385,7 +6385,7 @@
         <v>6</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS23">
         <v>8.6</v>
@@ -6412,7 +6412,7 @@
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB23" t="s">
         <v>167</v>
@@ -6435,22 +6435,22 @@
         <v>157</v>
       </c>
       <c r="F24">
-        <v>1.21</v>
+        <v>2.24</v>
       </c>
       <c r="G24">
-        <v>600</v>
+        <v>2.5</v>
       </c>
       <c r="H24">
-        <v>2.26</v>
+        <v>3.35</v>
       </c>
       <c r="I24">
-        <v>990</v>
+        <v>3.95</v>
       </c>
       <c r="J24">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="K24">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6459,22 +6459,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="O24">
         <v>1.42</v>
       </c>
       <c r="P24">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="Q24">
-        <v>1.42</v>
+        <v>2.16</v>
       </c>
       <c r="R24">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S24">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="T24">
         <v>1.11</v>
@@ -6483,10 +6483,10 @@
         <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="W24">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6689,13 +6689,13 @@
         <v>12.5</v>
       </c>
       <c r="J25">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K25">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L25">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
         <v>1.07</v>
@@ -6716,7 +6716,7 @@
         <v>1.35</v>
       </c>
       <c r="S25">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T25">
         <v>2.28</v>
@@ -6839,64 +6839,64 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BH25">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN25">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BP25">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR25">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT25">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="s">
         <v>167</v>
@@ -6919,19 +6919,19 @@
         <v>159</v>
       </c>
       <c r="F26">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G26">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="H26">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I26">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J26">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K26">
         <v>3.2</v>
@@ -6943,19 +6943,19 @@
         <v>1.13</v>
       </c>
       <c r="N26">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O26">
         <v>1.58</v>
       </c>
       <c r="P26">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Q26">
         <v>2.74</v>
       </c>
       <c r="R26">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S26">
         <v>5.8</v>
@@ -6967,16 +6967,16 @@
         <v>1.7</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W26">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X26">
         <v>8.6</v>
       </c>
       <c r="Y26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z26">
         <v>34</v>
@@ -6988,16 +6988,16 @@
         <v>6.8</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE26">
         <v>90</v>
       </c>
       <c r="AF26">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG26">
         <v>14</v>
@@ -7033,10 +7033,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR26">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS26">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT26">
         <v>5.9</v>
@@ -7048,7 +7048,7 @@
         <v>16</v>
       </c>
       <c r="AW26">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX26">
         <v>10</v>
@@ -7057,10 +7057,10 @@
         <v>10</v>
       </c>
       <c r="AZ26">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA26">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB26">
         <v>27</v>
@@ -7069,22 +7069,22 @@
         <v>27</v>
       </c>
       <c r="BD26">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE26">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF26">
         <v>29</v>
       </c>
       <c r="BG26">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH26">
         <v>2.68</v>
       </c>
       <c r="BI26">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BJ26">
         <v>12.5</v>
@@ -7096,10 +7096,10 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN26">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO26">
         <v>4.2</v>
@@ -7108,13 +7108,13 @@
         <v>22</v>
       </c>
       <c r="BQ26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR26">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT26">
         <v>7.4</v>
@@ -7126,19 +7126,19 @@
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ26">
+        <v>1000</v>
+      </c>
+      <c r="CA26">
         <v>9.4</v>
-      </c>
-      <c r="BZ26">
-        <v>1000</v>
-      </c>
-      <c r="CA26">
-        <v>9.199999999999999</v>
       </c>
       <c r="CB26" t="s">
         <v>167</v>
@@ -7188,25 +7188,25 @@
         <v>4.8</v>
       </c>
       <c r="O27">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P27">
         <v>2.28</v>
       </c>
       <c r="Q27">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R27">
         <v>1.51</v>
       </c>
       <c r="S27">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T27">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U27">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V27">
         <v>1.45</v>
@@ -7221,7 +7221,7 @@
         <v>15.5</v>
       </c>
       <c r="Z27">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA27">
         <v>70</v>
@@ -7239,10 +7239,10 @@
         <v>36</v>
       </c>
       <c r="AF27">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG27">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH27">
         <v>16</v>
@@ -7263,10 +7263,10 @@
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AO27">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AP27">
         <v>17</v>
@@ -7278,7 +7278,7 @@
         <v>20</v>
       </c>
       <c r="AS27">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AT27">
         <v>11.5</v>
@@ -7305,7 +7305,7 @@
         <v>23</v>
       </c>
       <c r="BB27">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC27">
         <v>20</v>
@@ -7323,16 +7323,16 @@
         <v>20</v>
       </c>
       <c r="BH27">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI27">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ27">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BK27">
-        <v>6.6</v>
+        <v>3.55</v>
       </c>
       <c r="BL27">
         <v>110</v>
@@ -7347,40 +7347,40 @@
         <v>4.9</v>
       </c>
       <c r="BP27">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BQ27">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BR27">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BS27">
+        <v>4.9</v>
+      </c>
+      <c r="BT27">
+        <v>6.6</v>
+      </c>
+      <c r="BU27">
+        <v>5.7</v>
+      </c>
+      <c r="BV27">
+        <v>27</v>
+      </c>
+      <c r="BW27">
+        <v>4.8</v>
+      </c>
+      <c r="BX27">
+        <v>38</v>
+      </c>
+      <c r="BY27">
+        <v>5</v>
+      </c>
+      <c r="BZ27">
+        <v>25</v>
+      </c>
+      <c r="CA27">
         <v>4.7</v>
-      </c>
-      <c r="BT27">
-        <v>7.8</v>
-      </c>
-      <c r="BU27">
-        <v>4.9</v>
-      </c>
-      <c r="BV27">
-        <v>22</v>
-      </c>
-      <c r="BW27">
-        <v>4.6</v>
-      </c>
-      <c r="BX27">
-        <v>30</v>
-      </c>
-      <c r="BY27">
-        <v>4.9</v>
-      </c>
-      <c r="BZ27">
-        <v>20</v>
-      </c>
-      <c r="CA27">
-        <v>4.5</v>
       </c>
       <c r="CB27" t="s">
         <v>167</v>
@@ -7403,13 +7403,13 @@
         <v>161</v>
       </c>
       <c r="F28">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G28">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H28">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I28">
         <v>2.38</v>
@@ -7427,25 +7427,25 @@
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O28">
         <v>1.19</v>
       </c>
       <c r="P28">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="Q28">
         <v>1.59</v>
       </c>
       <c r="R28">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S28">
         <v>2.48</v>
       </c>
       <c r="T28">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U28">
         <v>2.7</v>
@@ -7454,19 +7454,19 @@
         <v>1.72</v>
       </c>
       <c r="W28">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y28">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z28">
         <v>19</v>
       </c>
       <c r="AA28">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AB28">
         <v>19</v>
@@ -7475,40 +7475,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE28">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF28">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AG28">
         <v>14</v>
       </c>
       <c r="AH28">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI28">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AJ28">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AK28">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AL28">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM28">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="AN28">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AO28">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AP28">
         <v>18</v>
@@ -7517,7 +7517,7 @@
         <v>13.5</v>
       </c>
       <c r="AR28">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS28">
         <v>21</v>
@@ -7553,16 +7553,16 @@
         <v>19</v>
       </c>
       <c r="BD28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE28">
         <v>30</v>
       </c>
       <c r="BF28">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG28">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH28">
         <v>4.6</v>
@@ -7574,13 +7574,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK28">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN28">
         <v>7</v>
@@ -7592,16 +7592,16 @@
         <v>22</v>
       </c>
       <c r="BQ28">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR28">
         <v>28</v>
       </c>
       <c r="BS28">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT28">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU28">
         <v>4.9</v>
@@ -7610,7 +7610,7 @@
         <v>16</v>
       </c>
       <c r="BW28">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX28">
         <v>24</v>
@@ -7645,25 +7645,25 @@
         <v>162</v>
       </c>
       <c r="F29">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G29">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H29">
         <v>3.3</v>
       </c>
       <c r="I29">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J29">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K29">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L29">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M29">
         <v>1.06</v>
@@ -7672,13 +7672,13 @@
         <v>4.4</v>
       </c>
       <c r="O29">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P29">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q29">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R29">
         <v>1.46</v>
@@ -7687,16 +7687,16 @@
         <v>3.05</v>
       </c>
       <c r="T29">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U29">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V29">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X29">
         <v>20</v>
@@ -7708,16 +7708,16 @@
         <v>30</v>
       </c>
       <c r="AA29">
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="AB29">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC29">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD29">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE29">
         <v>44</v>
@@ -7726,7 +7726,7 @@
         <v>15.5</v>
       </c>
       <c r="AG29">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH29">
         <v>17</v>
@@ -7738,19 +7738,19 @@
         <v>38</v>
       </c>
       <c r="AK29">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL29">
         <v>40</v>
       </c>
       <c r="AM29">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN29">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO29">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP29">
         <v>15.5</v>
@@ -7762,7 +7762,7 @@
         <v>21</v>
       </c>
       <c r="AS29">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AT29">
         <v>10</v>
@@ -7780,22 +7780,22 @@
         <v>13.5</v>
       </c>
       <c r="AY29">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA29">
         <v>25</v>
       </c>
       <c r="BB29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC29">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BD29">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE29">
         <v>38</v>
@@ -7804,19 +7804,19 @@
         <v>14</v>
       </c>
       <c r="BG29">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BH29">
         <v>4.4</v>
       </c>
       <c r="BI29">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK29">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BL29">
         <v>1000</v>
@@ -7831,37 +7831,37 @@
         <v>4.7</v>
       </c>
       <c r="BP29">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BQ29">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BR29">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BS29">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BT29">
         <v>6.8</v>
       </c>
       <c r="BU29">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV29">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW29">
         <v>5.7</v>
       </c>
       <c r="BX29">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY29">
         <v>6</v>
       </c>
       <c r="BZ29">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CA29">
         <v>5.5</v>
@@ -7917,7 +7917,7 @@
         <v>1.13</v>
       </c>
       <c r="P30">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q30">
         <v>1.42</v>
@@ -7926,13 +7926,13 @@
         <v>1.9</v>
       </c>
       <c r="S30">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T30">
         <v>1.41</v>
       </c>
       <c r="U30">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V30">
         <v>1.71</v>
@@ -7995,7 +7995,7 @@
         <v>9.4</v>
       </c>
       <c r="AP30">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ30">
         <v>18.5</v>
@@ -8007,7 +8007,7 @@
         <v>32</v>
       </c>
       <c r="AT30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU30">
         <v>10</v>
@@ -8019,7 +8019,7 @@
         <v>18</v>
       </c>
       <c r="AX30">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY30">
         <v>12.5</v>
@@ -8046,67 +8046,67 @@
         <v>11.5</v>
       </c>
       <c r="BG30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH30">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL30">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN30">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BP30">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR30">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT30">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV30">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX30">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA30">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="s">
         <v>167</v>
@@ -8150,7 +8150,7 @@
         <v>1.29</v>
       </c>
       <c r="M31">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N31">
         <v>5.5</v>
@@ -8159,7 +8159,7 @@
         <v>1.2</v>
       </c>
       <c r="P31">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q31">
         <v>1.61</v>
@@ -8168,7 +8168,7 @@
         <v>1.62</v>
       </c>
       <c r="S31">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T31">
         <v>1.65</v>
@@ -8180,10 +8180,10 @@
         <v>1.24</v>
       </c>
       <c r="W31">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X31">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y31">
         <v>24</v>
@@ -8231,28 +8231,28 @@
         <v>1000</v>
       </c>
       <c r="AN31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO31">
         <v>48</v>
       </c>
       <c r="AP31">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ31">
         <v>20</v>
       </c>
       <c r="AR31">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS31">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT31">
         <v>10.5</v>
       </c>
       <c r="AU31">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV31">
         <v>16.5</v>
@@ -8318,7 +8318,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ31">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR31">
         <v>22</v>
@@ -8371,25 +8371,25 @@
         <v>165</v>
       </c>
       <c r="F32">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G32">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="H32">
+        <v>2.6</v>
+      </c>
+      <c r="I32">
         <v>2.66</v>
       </c>
-      <c r="I32">
-        <v>2.72</v>
-      </c>
       <c r="J32">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K32">
         <v>4.3</v>
       </c>
       <c r="L32">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M32">
         <v>1.02</v>
@@ -8407,7 +8407,7 @@
         <v>1.45</v>
       </c>
       <c r="R32">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S32">
         <v>2.1</v>
@@ -8419,19 +8419,19 @@
         <v>3.15</v>
       </c>
       <c r="V32">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W32">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X32">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y32">
         <v>21</v>
       </c>
       <c r="Z32">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA32">
         <v>44</v>
@@ -8443,67 +8443,67 @@
         <v>11.5</v>
       </c>
       <c r="AD32">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF32">
         <v>24</v>
       </c>
       <c r="AG32">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH32">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI32">
         <v>27</v>
       </c>
       <c r="AJ32">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL32">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM32">
         <v>42</v>
       </c>
       <c r="AN32">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO32">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP32">
+        <v>28</v>
+      </c>
+      <c r="AQ32">
+        <v>19</v>
+      </c>
+      <c r="AR32">
         <v>22</v>
       </c>
-      <c r="AQ32">
+      <c r="AS32">
+        <v>38</v>
+      </c>
+      <c r="AT32">
         <v>18.5</v>
-      </c>
-      <c r="AR32">
-        <v>21</v>
-      </c>
-      <c r="AS32">
-        <v>34</v>
-      </c>
-      <c r="AT32">
-        <v>18</v>
       </c>
       <c r="AU32">
         <v>10</v>
       </c>
       <c r="AV32">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW32">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX32">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY32">
         <v>11.5</v>
@@ -8512,25 +8512,25 @@
         <v>12.5</v>
       </c>
       <c r="BA32">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BB32">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC32">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD32">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE32">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BF32">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG32">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH32">
         <v>6.2</v>
@@ -8539,58 +8539,58 @@
         <v>4</v>
       </c>
       <c r="BJ32">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK32">
         <v>6</v>
       </c>
       <c r="BL32">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BM32">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BN32">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BO32">
         <v>4.8</v>
       </c>
       <c r="BP32">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BQ32">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="BR32">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BS32">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="BT32">
         <v>8</v>
       </c>
       <c r="BU32">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV32">
         <v>21</v>
       </c>
       <c r="BW32">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="BX32">
         <v>26</v>
       </c>
       <c r="BY32">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="BZ32">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA32">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="CB32" t="s">
         <v>167</v>
@@ -8613,7 +8613,7 @@
         <v>166</v>
       </c>
       <c r="F33">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G33">
         <v>2.08</v>
@@ -8622,13 +8622,13 @@
         <v>3.5</v>
       </c>
       <c r="I33">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J33">
         <v>4.2</v>
       </c>
       <c r="K33">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L33">
         <v>1.26</v>
@@ -8643,7 +8643,7 @@
         <v>1.16</v>
       </c>
       <c r="P33">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q33">
         <v>1.5</v>
@@ -8658,13 +8658,13 @@
         <v>1.5</v>
       </c>
       <c r="U33">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
         <v>1.37</v>
       </c>
       <c r="W33">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X33">
         <v>55</v>
@@ -8691,7 +8691,7 @@
         <v>34</v>
       </c>
       <c r="AF33">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG33">
         <v>11.5</v>
@@ -8715,13 +8715,13 @@
         <v>190</v>
       </c>
       <c r="AN33">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP33">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ33">
         <v>19.5</v>
@@ -8781,16 +8781,16 @@
         <v>4.3</v>
       </c>
       <c r="BJ33">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK33">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BL33">
         <v>95</v>
       </c>
       <c r="BM33">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BN33">
         <v>5.5</v>
@@ -8799,40 +8799,40 @@
         <v>4.2</v>
       </c>
       <c r="BP33">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ33">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="BR33">
         <v>20</v>
       </c>
       <c r="BS33">
+        <v>4.9</v>
+      </c>
+      <c r="BT33">
+        <v>9</v>
+      </c>
+      <c r="BU33">
+        <v>5.6</v>
+      </c>
+      <c r="BV33">
+        <v>24</v>
+      </c>
+      <c r="BW33">
         <v>5.1</v>
-      </c>
-      <c r="BT33">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU33">
-        <v>5.5</v>
-      </c>
-      <c r="BV33">
-        <v>23</v>
-      </c>
-      <c r="BW33">
-        <v>5.3</v>
       </c>
       <c r="BX33">
         <v>27</v>
       </c>
       <c r="BY33">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BZ33">
         <v>13</v>
       </c>
       <c r="CA33">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="CB33" t="s">
         <v>167</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -517,7 +517,7 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-18 13:20:51</t>
+    <t>2026-08-18 15:29:02</t>
   </si>
 </sst>
 </file>
@@ -1111,22 +1111,22 @@
         <v>135</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
         <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
         <v>1.51</v>
@@ -1138,7 +1138,7 @@
         <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P2">
         <v>1.68</v>
@@ -1159,10 +1159,10 @@
         <v>1.93</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X2">
         <v>11</v>
@@ -1183,10 +1183,10 @@
         <v>7</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF2">
         <v>13</v>
@@ -1198,28 +1198,28 @@
         <v>21</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK2">
         <v>28</v>
       </c>
       <c r="AL2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM2">
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AO2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
         <v>11</v>
@@ -1228,7 +1228,7 @@
         <v>23</v>
       </c>
       <c r="AS2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AT2">
         <v>7.2</v>
@@ -1237,16 +1237,16 @@
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
         <v>18</v>
@@ -1264,7 +1264,7 @@
         <v>42</v>
       </c>
       <c r="BE2">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BF2">
         <v>21</v>
@@ -1297,7 +1297,7 @@
         <v>4.4</v>
       </c>
       <c r="BP2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2">
         <v>11</v>
@@ -1318,7 +1318,7 @@
         <v>36</v>
       </c>
       <c r="BW2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BX2">
         <v>55</v>
@@ -1330,7 +1330,7 @@
         <v>40</v>
       </c>
       <c r="CA2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="CB2" t="s">
         <v>167</v>
@@ -1353,58 +1353,58 @@
         <v>136</v>
       </c>
       <c r="F3">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="G3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H3">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="I3">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="J3">
         <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
         <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="O3">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P3">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q3">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V3">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X3">
         <v>8.4</v>
@@ -1413,13 +1413,13 @@
         <v>8.4</v>
       </c>
       <c r="Z3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA3">
         <v>40</v>
       </c>
       <c r="AB3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3">
         <v>7</v>
@@ -1431,46 +1431,46 @@
         <v>38</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AL3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM3">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN3">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AO3">
         <v>42</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AR3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AT3">
         <v>8.800000000000001</v>
@@ -1485,31 +1485,31 @@
         <v>32</v>
       </c>
       <c r="AX3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA3">
         <v>46</v>
       </c>
       <c r="BB3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC3">
         <v>40</v>
       </c>
       <c r="BD3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE3">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="BF3">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="BG3">
         <v>36</v>
@@ -1518,7 +1518,7 @@
         <v>2.7</v>
       </c>
       <c r="BI3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3">
         <v>11</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>12</v>
+        <v>2.22</v>
       </c>
       <c r="BR3">
         <v>1000</v>
@@ -1557,7 +1557,7 @@
         <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW3">
         <v>10</v>
@@ -1566,13 +1566,13 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CB3" t="s">
         <v>167</v>
@@ -1598,7 +1598,7 @@
         <v>3.25</v>
       </c>
       <c r="G4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
         <v>2.58</v>
@@ -1613,34 +1613,34 @@
         <v>3.2</v>
       </c>
       <c r="L4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M4">
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O4">
         <v>1.52</v>
       </c>
       <c r="P4">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q4">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R4">
         <v>1.21</v>
       </c>
       <c r="S4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V4">
         <v>1.6</v>
@@ -1649,7 +1649,7 @@
         <v>1.42</v>
       </c>
       <c r="X4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y4">
         <v>8.199999999999999</v>
@@ -1664,10 +1664,10 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE4">
         <v>38</v>
@@ -1676,7 +1676,7 @@
         <v>21</v>
       </c>
       <c r="AG4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH4">
         <v>23</v>
@@ -1703,10 +1703,10 @@
         <v>40</v>
       </c>
       <c r="AP4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR4">
         <v>13.5</v>
@@ -1724,7 +1724,7 @@
         <v>11</v>
       </c>
       <c r="AW4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX4">
         <v>18.5</v>
@@ -1745,7 +1745,7 @@
         <v>40</v>
       </c>
       <c r="BD4">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BE4">
         <v>110</v>
@@ -1754,10 +1754,10 @@
         <v>50</v>
       </c>
       <c r="BG4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BH4">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BI4">
         <v>2.4</v>
@@ -1766,13 +1766,13 @@
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
         <v>6.6</v>
@@ -1784,13 +1784,13 @@
         <v>32</v>
       </c>
       <c r="BQ4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT4">
         <v>5.4</v>
@@ -1802,19 +1802,19 @@
         <v>23</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4">
         <v>48</v>
       </c>
       <c r="CA4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
         <v>167</v>
@@ -1837,16 +1837,16 @@
         <v>138</v>
       </c>
       <c r="F5">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G5">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J5">
         <v>2.98</v>
@@ -1864,13 +1864,13 @@
         <v>2.5</v>
       </c>
       <c r="O5">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P5">
         <v>1.48</v>
       </c>
       <c r="Q5">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R5">
         <v>1.17</v>
@@ -1882,13 +1882,13 @@
         <v>2.28</v>
       </c>
       <c r="U5">
+        <v>1.73</v>
+      </c>
+      <c r="V5">
+        <v>1.31</v>
+      </c>
+      <c r="W5">
         <v>1.72</v>
-      </c>
-      <c r="V5">
-        <v>1.32</v>
-      </c>
-      <c r="W5">
-        <v>1.71</v>
       </c>
       <c r="X5">
         <v>7.4</v>
@@ -1900,7 +1900,7 @@
         <v>27</v>
       </c>
       <c r="AA5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB5">
         <v>6.8</v>
@@ -1924,7 +1924,7 @@
         <v>26</v>
       </c>
       <c r="AI5">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="AJ5">
         <v>34</v>
@@ -1936,7 +1936,7 @@
         <v>75</v>
       </c>
       <c r="AM5">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN5">
         <v>40</v>
@@ -1957,7 +1957,7 @@
         <v>55</v>
       </c>
       <c r="AT5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
         <v>6.4</v>
@@ -1978,7 +1978,7 @@
         <v>24</v>
       </c>
       <c r="BA5">
-        <v>60</v>
+        <v>17.5</v>
       </c>
       <c r="BB5">
         <v>30</v>
@@ -1987,7 +1987,7 @@
         <v>32</v>
       </c>
       <c r="BD5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE5">
         <v>15.5</v>
@@ -1996,7 +1996,7 @@
         <v>34</v>
       </c>
       <c r="BG5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH5">
         <v>2.82</v>
@@ -2079,22 +2079,22 @@
         <v>139</v>
       </c>
       <c r="F6">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L6">
         <v>1.22</v>
@@ -2106,46 +2106,46 @@
         <v>6.4</v>
       </c>
       <c r="O6">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P6">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q6">
         <v>1.52</v>
       </c>
       <c r="R6">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="S6">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T6">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V6">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="X6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z6">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC6">
         <v>12</v>
@@ -2154,7 +2154,7 @@
         <v>27</v>
       </c>
       <c r="AE6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF6">
         <v>12</v>
@@ -2166,7 +2166,7 @@
         <v>19</v>
       </c>
       <c r="AI6">
-        <v>870</v>
+        <v>65</v>
       </c>
       <c r="AJ6">
         <v>15</v>
@@ -2175,13 +2175,13 @@
         <v>14.5</v>
       </c>
       <c r="AL6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM6">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AO6">
         <v>65</v>
@@ -2190,61 +2190,61 @@
         <v>25</v>
       </c>
       <c r="AQ6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR6">
+        <v>50</v>
+      </c>
+      <c r="AS6">
         <v>44</v>
-      </c>
-      <c r="AS6">
-        <v>46</v>
       </c>
       <c r="AT6">
         <v>11.5</v>
       </c>
       <c r="AU6">
+        <v>10.5</v>
+      </c>
+      <c r="AV6">
+        <v>23</v>
+      </c>
+      <c r="AW6">
+        <v>50</v>
+      </c>
+      <c r="AX6">
         <v>11</v>
-      </c>
-      <c r="AV6">
-        <v>22</v>
-      </c>
-      <c r="AW6">
-        <v>32</v>
-      </c>
-      <c r="AX6">
-        <v>10.5</v>
       </c>
       <c r="AY6">
         <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB6">
+        <v>13.5</v>
+      </c>
+      <c r="BC6">
         <v>13</v>
-      </c>
-      <c r="BC6">
-        <v>12.5</v>
       </c>
       <c r="BD6">
         <v>22</v>
       </c>
       <c r="BE6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF6">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG6">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BH6">
         <v>5.1</v>
       </c>
       <c r="BI6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BJ6">
         <v>10</v>
@@ -2262,7 +2262,7 @@
         <v>4.7</v>
       </c>
       <c r="BO6">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="BP6">
         <v>9.199999999999999</v>
@@ -2277,7 +2277,7 @@
         <v>10.5</v>
       </c>
       <c r="BT6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU6">
         <v>6.2</v>
@@ -2286,7 +2286,7 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX6">
         <v>1000</v>
@@ -2295,10 +2295,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA6">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="s">
         <v>167</v>
@@ -2321,7 +2321,7 @@
         <v>140</v>
       </c>
       <c r="F7">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="G7">
         <v>990</v>
@@ -2333,7 +2333,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2342,7 +2342,7 @@
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N7">
         <v>1.1</v>
@@ -2575,7 +2575,7 @@
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2590,13 +2590,13 @@
         <v>1.1</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8">
         <v>1.09</v>
       </c>
       <c r="Q8">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="R8">
         <v>1.07</v>
@@ -2811,13 +2811,13 @@
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="I9">
         <v>990</v>
       </c>
       <c r="J9">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K9">
         <v>3.45</v>
@@ -3050,7 +3050,7 @@
         <v>1.2</v>
       </c>
       <c r="G10">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -3077,13 +3077,13 @@
         <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q10">
         <v>1.35</v>
       </c>
       <c r="R10">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S10">
         <v>1.37</v>
@@ -3098,7 +3098,7 @@
         <v>1.02</v>
       </c>
       <c r="W10">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3289,13 +3289,13 @@
         <v>144</v>
       </c>
       <c r="F11">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
         <v>990</v>
       </c>
       <c r="H11">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="I11">
         <v>990</v>
@@ -3304,7 +3304,7 @@
         <v>1.04</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3319,7 +3319,7 @@
         <v>1.01</v>
       </c>
       <c r="P11">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q11">
         <v>1.32</v>
@@ -3328,7 +3328,7 @@
         <v>1.07</v>
       </c>
       <c r="S11">
-        <v>1.32</v>
+        <v>2.48</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3340,7 +3340,7 @@
         <v>1.02</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3531,10 +3531,10 @@
         <v>145</v>
       </c>
       <c r="F12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="G12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H12">
         <v>15</v>
@@ -3543,10 +3543,10 @@
         <v>22</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="K12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L12">
         <v>1.25</v>
@@ -3564,19 +3564,19 @@
         <v>2.28</v>
       </c>
       <c r="Q12">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R12">
         <v>1.49</v>
       </c>
       <c r="S12">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T12">
         <v>2.28</v>
       </c>
       <c r="U12">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V12">
         <v>1.05</v>
@@ -3600,7 +3600,7 @@
         <v>10.5</v>
       </c>
       <c r="AC12">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD12">
         <v>950</v>
@@ -3642,55 +3642,55 @@
         <v>19</v>
       </c>
       <c r="AQ12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS12">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT12">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU12">
         <v>12.5</v>
       </c>
       <c r="AV12">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AW12">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX12">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AY12">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA12">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB12">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="BC12">
         <v>12.5</v>
       </c>
       <c r="BD12">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE12">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF12">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BG12">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH12">
         <v>4.4</v>
@@ -3773,7 +3773,7 @@
         <v>146</v>
       </c>
       <c r="F13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="G13">
         <v>990</v>
@@ -3785,7 +3785,7 @@
         <v>990</v>
       </c>
       <c r="J13">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3794,25 +3794,25 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
         <v>1.1</v>
       </c>
       <c r="O13">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="P13">
         <v>1.1</v>
       </c>
       <c r="Q13">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="R13">
         <v>1.07</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
         <v>1.11</v>
@@ -3821,7 +3821,7 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
         <v>1.01</v>
@@ -4015,19 +4015,19 @@
         <v>147</v>
       </c>
       <c r="F14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="G14">
         <v>990</v>
       </c>
       <c r="H14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I14">
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4036,25 +4036,25 @@
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
         <v>1.1</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="P14">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q14">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="R14">
         <v>1.07</v>
       </c>
       <c r="S14">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -4257,19 +4257,19 @@
         <v>148</v>
       </c>
       <c r="F15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="G15">
         <v>990</v>
       </c>
       <c r="H15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I15">
         <v>990</v>
       </c>
       <c r="J15">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4287,7 +4287,7 @@
         <v>1.26</v>
       </c>
       <c r="P15">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Q15">
         <v>1.26</v>
@@ -4499,10 +4499,10 @@
         <v>149</v>
       </c>
       <c r="F16">
+        <v>1.35</v>
+      </c>
+      <c r="G16">
         <v>1.36</v>
-      </c>
-      <c r="G16">
-        <v>1.37</v>
       </c>
       <c r="H16">
         <v>11.5</v>
@@ -4511,34 +4511,34 @@
         <v>12</v>
       </c>
       <c r="J16">
+        <v>5.5</v>
+      </c>
+      <c r="K16">
         <v>5.6</v>
       </c>
-      <c r="K16">
-        <v>5.7</v>
-      </c>
       <c r="L16">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M16">
         <v>1.06</v>
       </c>
       <c r="N16">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O16">
         <v>1.29</v>
       </c>
       <c r="P16">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q16">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R16">
         <v>1.42</v>
       </c>
       <c r="S16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T16">
         <v>2.34</v>
@@ -4556,7 +4556,7 @@
         <v>16</v>
       </c>
       <c r="Y16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z16">
         <v>110</v>
@@ -4583,7 +4583,7 @@
         <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI16">
         <v>190</v>
@@ -4592,13 +4592,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AK16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL16">
         <v>48</v>
       </c>
       <c r="AM16">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AN16">
         <v>6.2</v>
@@ -4640,7 +4640,7 @@
         <v>32</v>
       </c>
       <c r="BA16">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="BB16">
         <v>9.4</v>
@@ -4652,10 +4652,10 @@
         <v>42</v>
       </c>
       <c r="BE16">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BF16">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG16">
         <v>75</v>
@@ -4676,7 +4676,7 @@
         <v>230</v>
       </c>
       <c r="BM16">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="BN16">
         <v>3.55</v>
@@ -4750,7 +4750,7 @@
         <v>4.2</v>
       </c>
       <c r="I17">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>3.3</v>
@@ -4765,7 +4765,7 @@
         <v>1.09</v>
       </c>
       <c r="N17">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O17">
         <v>1.4</v>
@@ -5019,7 +5019,7 @@
         <v>2.68</v>
       </c>
       <c r="R18">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S18">
         <v>5.6</v>
@@ -5064,7 +5064,7 @@
         <v>14</v>
       </c>
       <c r="AG18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH18">
         <v>26</v>
@@ -5091,7 +5091,7 @@
         <v>110</v>
       </c>
       <c r="AP18">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ18">
         <v>8.800000000000001</v>
@@ -5100,13 +5100,13 @@
         <v>20</v>
       </c>
       <c r="AS18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT18">
         <v>6.8</v>
       </c>
       <c r="AU18">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV18">
         <v>14.5</v>
@@ -5133,16 +5133,16 @@
         <v>29</v>
       </c>
       <c r="BD18">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="BE18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF18">
         <v>29</v>
       </c>
       <c r="BG18">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5225,7 +5225,7 @@
         <v>152</v>
       </c>
       <c r="F19">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="G19">
         <v>5.9</v>
@@ -5234,7 +5234,7 @@
         <v>1.81</v>
       </c>
       <c r="I19">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J19">
         <v>3.45</v>
@@ -5249,7 +5249,7 @@
         <v>1.11</v>
       </c>
       <c r="N19">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O19">
         <v>1.48</v>
@@ -5261,16 +5261,16 @@
         <v>2.46</v>
       </c>
       <c r="R19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S19">
         <v>5</v>
       </c>
       <c r="T19">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U19">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="V19">
         <v>2.12</v>
@@ -5303,7 +5303,7 @@
         <v>25</v>
       </c>
       <c r="AF19">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG19">
         <v>23</v>
@@ -5318,7 +5318,7 @@
         <v>210</v>
       </c>
       <c r="AK19">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL19">
         <v>140</v>
@@ -5327,7 +5327,7 @@
         <v>260</v>
       </c>
       <c r="AN19">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AO19">
         <v>19.5</v>
@@ -5369,19 +5369,19 @@
         <v>10</v>
       </c>
       <c r="BB19">
+        <v>11.5</v>
+      </c>
+      <c r="BC19">
         <v>11</v>
-      </c>
-      <c r="BC19">
-        <v>10.5</v>
       </c>
       <c r="BD19">
         <v>11</v>
       </c>
       <c r="BE19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG19">
         <v>17</v>
@@ -5402,22 +5402,22 @@
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN19">
         <v>9.199999999999999</v>
       </c>
       <c r="BO19">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP19">
         <v>75</v>
       </c>
       <c r="BQ19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR19">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BS19">
         <v>7.6</v>
@@ -5709,10 +5709,10 @@
         <v>154</v>
       </c>
       <c r="F21">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G21">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H21">
         <v>2.82</v>
@@ -5727,28 +5727,28 @@
         <v>3.3</v>
       </c>
       <c r="L21">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M21">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N21">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O21">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P21">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q21">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R21">
         <v>1.26</v>
       </c>
       <c r="S21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T21">
         <v>1.89</v>
@@ -5760,10 +5760,10 @@
         <v>1.51</v>
       </c>
       <c r="W21">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y21">
         <v>12</v>
@@ -5823,10 +5823,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR21">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT21">
         <v>8.6</v>
@@ -5838,7 +5838,7 @@
         <v>11.5</v>
       </c>
       <c r="AW21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX21">
         <v>16</v>
@@ -5853,31 +5853,31 @@
         <v>4.4</v>
       </c>
       <c r="BB21">
+        <v>4.4</v>
+      </c>
+      <c r="BC21">
         <v>4.3</v>
-      </c>
-      <c r="BC21">
-        <v>4.2</v>
       </c>
       <c r="BD21">
         <v>4.4</v>
       </c>
       <c r="BE21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF21">
         <v>4.3</v>
       </c>
       <c r="BG21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH21">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI21">
-        <v>2.78</v>
+        <v>2.42</v>
       </c>
       <c r="BJ21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK21">
         <v>3.5</v>
@@ -5886,7 +5886,7 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN21">
         <v>7</v>
@@ -5895,7 +5895,7 @@
         <v>4.4</v>
       </c>
       <c r="BP21">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BQ21">
         <v>4.2</v>
@@ -5904,7 +5904,7 @@
         <v>50</v>
       </c>
       <c r="BS21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT21">
         <v>6.8</v>
@@ -5916,16 +5916,16 @@
         <v>28</v>
       </c>
       <c r="BW21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BX21">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY21">
         <v>4.4</v>
       </c>
       <c r="BZ21">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="CA21">
         <v>4.4</v>
@@ -5966,7 +5966,7 @@
         <v>3.85</v>
       </c>
       <c r="K22">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -5987,7 +5987,7 @@
         <v>1.59</v>
       </c>
       <c r="R22">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S22">
         <v>2.48</v>
@@ -6062,16 +6062,16 @@
         <v>17</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU22">
         <v>7.2</v>
@@ -6092,10 +6092,10 @@
         <v>11</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC22">
         <v>17.5</v>
@@ -6104,13 +6104,13 @@
         <v>21</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF22">
         <v>10.5</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6196,43 +6196,43 @@
         <v>1.67</v>
       </c>
       <c r="G23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H23">
         <v>4.7</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J23">
         <v>4.2</v>
       </c>
       <c r="K23">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L23">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N23">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O23">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P23">
         <v>2.14</v>
       </c>
       <c r="Q23">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="R23">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S23">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="T23">
         <v>1.76</v>
@@ -6244,7 +6244,7 @@
         <v>1.2</v>
       </c>
       <c r="W23">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X23">
         <v>22</v>
@@ -6301,19 +6301,19 @@
         <v>70</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AQ23">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU23">
         <v>8.800000000000001</v>
@@ -6322,7 +6322,7 @@
         <v>14</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX23">
         <v>10</v>
@@ -6334,7 +6334,7 @@
         <v>14</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB23">
         <v>13</v>
@@ -6343,16 +6343,16 @@
         <v>13</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF23">
         <v>7.2</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH23">
         <v>3.9</v>
@@ -6447,7 +6447,7 @@
         <v>3.95</v>
       </c>
       <c r="J24">
-        <v>1.75</v>
+        <v>2.88</v>
       </c>
       <c r="K24">
         <v>3.9</v>
@@ -6713,7 +6713,7 @@
         <v>1.96</v>
       </c>
       <c r="R25">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S25">
         <v>3.5</v>
@@ -6919,22 +6919,22 @@
         <v>159</v>
       </c>
       <c r="F26">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="G26">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="H26">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I26">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J26">
         <v>3</v>
       </c>
       <c r="K26">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L26">
         <v>1.51</v>
@@ -6943,202 +6943,202 @@
         <v>1.13</v>
       </c>
       <c r="N26">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="O26">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P26">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q26">
         <v>2.74</v>
       </c>
       <c r="R26">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S26">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="T26">
         <v>2.2</v>
       </c>
       <c r="U26">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V26">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W26">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="X26">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y26">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z26">
         <v>34</v>
       </c>
       <c r="AA26">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB26">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>8.800000000000001</v>
       </c>
       <c r="AD26">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE26">
         <v>90</v>
       </c>
       <c r="AF26">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG26">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH26">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI26">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK26">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL26">
         <v>80</v>
       </c>
       <c r="AM26">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN26">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AO26">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP26">
         <v>7.2</v>
       </c>
       <c r="AQ26">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR26">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="AS26">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT26">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU26">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV26">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AW26">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY26">
         <v>10</v>
       </c>
       <c r="AZ26">
-        <v>5.5</v>
+        <v>21</v>
       </c>
       <c r="BA26">
+        <v>6.8</v>
+      </c>
+      <c r="BB26">
+        <v>6.2</v>
+      </c>
+      <c r="BC26">
+        <v>6.2</v>
+      </c>
+      <c r="BD26">
         <v>6.6</v>
       </c>
-      <c r="BB26">
-        <v>27</v>
-      </c>
-      <c r="BC26">
-        <v>27</v>
-      </c>
-      <c r="BD26">
-        <v>6.4</v>
-      </c>
       <c r="BE26">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF26">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="BG26">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH26">
         <v>2.68</v>
       </c>
       <c r="BI26">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="BJ26">
+        <v>12</v>
+      </c>
+      <c r="BK26">
+        <v>6.2</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
         <v>12.5</v>
-      </c>
-      <c r="BK26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>11</v>
       </c>
       <c r="BN26">
         <v>5</v>
       </c>
       <c r="BO26">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP26">
         <v>22</v>
       </c>
       <c r="BQ26">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT26">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU26">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB26" t="s">
         <v>167</v>
@@ -7167,7 +7167,7 @@
         <v>2.42</v>
       </c>
       <c r="H27">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I27">
         <v>3.2</v>
@@ -7176,124 +7176,124 @@
         <v>3.75</v>
       </c>
       <c r="K27">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L27">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M27">
         <v>1.05</v>
       </c>
       <c r="N27">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O27">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P27">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q27">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="R27">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="S27">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T27">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U27">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V27">
         <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X27">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="Y27">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z27">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA27">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="AB27">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC27">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD27">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE27">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF27">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH27">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI27">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ27">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK27">
         <v>24</v>
       </c>
       <c r="AL27">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM27">
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AO27">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AP27">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ27">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR27">
         <v>20</v>
       </c>
       <c r="AS27">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AT27">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU27">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV27">
         <v>12</v>
       </c>
       <c r="AW27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX27">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY27">
         <v>10</v>
@@ -7305,7 +7305,7 @@
         <v>23</v>
       </c>
       <c r="BB27">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC27">
         <v>20</v>
@@ -7314,16 +7314,16 @@
         <v>21</v>
       </c>
       <c r="BE27">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BF27">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG27">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BH27">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI27">
         <v>3.05</v>
@@ -7332,55 +7332,55 @@
         <v>9</v>
       </c>
       <c r="BK27">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="BL27">
         <v>110</v>
       </c>
       <c r="BM27">
+        <v>9.6</v>
+      </c>
+      <c r="BN27">
         <v>5.5</v>
-      </c>
-      <c r="BN27">
-        <v>6.6</v>
       </c>
       <c r="BO27">
         <v>4.9</v>
       </c>
       <c r="BP27">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BQ27">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="BR27">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BS27">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BT27">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU27">
         <v>5.7</v>
       </c>
       <c r="BV27">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BW27">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX27">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BY27">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BZ27">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CA27">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="CB27" t="s">
         <v>167</v>
@@ -7427,19 +7427,19 @@
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O28">
         <v>1.19</v>
       </c>
       <c r="P28">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q28">
         <v>1.59</v>
       </c>
       <c r="R28">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S28">
         <v>2.48</v>
@@ -7448,7 +7448,7 @@
         <v>1.55</v>
       </c>
       <c r="U28">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="V28">
         <v>1.72</v>
@@ -7505,7 +7505,7 @@
         <v>310</v>
       </c>
       <c r="AN28">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO28">
         <v>12</v>
@@ -7645,13 +7645,13 @@
         <v>162</v>
       </c>
       <c r="F29">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G29">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H29">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I29">
         <v>3.5</v>
@@ -7672,22 +7672,22 @@
         <v>4.4</v>
       </c>
       <c r="O29">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P29">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q29">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R29">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S29">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T29">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U29">
         <v>2.36</v>
@@ -7696,31 +7696,31 @@
         <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X29">
         <v>20</v>
       </c>
       <c r="Y29">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z29">
         <v>30</v>
       </c>
       <c r="AA29">
-        <v>700</v>
+        <v>570</v>
       </c>
       <c r="AB29">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC29">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD29">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE29">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AF29">
         <v>15.5</v>
@@ -7732,58 +7732,58 @@
         <v>17</v>
       </c>
       <c r="AI29">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AJ29">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AK29">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL29">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AM29">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO29">
         <v>55</v>
       </c>
       <c r="AP29">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ29">
         <v>13</v>
       </c>
       <c r="AR29">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AS29">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AT29">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU29">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV29">
         <v>12.5</v>
       </c>
       <c r="AW29">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX29">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AY29">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ29">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA29">
         <v>25</v>
@@ -7792,79 +7792,79 @@
         <v>20</v>
       </c>
       <c r="BC29">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BD29">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BE29">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BF29">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BG29">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BH29">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN29">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP29">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR29">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT29">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV29">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX29">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="s">
         <v>167</v>
@@ -7887,7 +7887,7 @@
         <v>163</v>
       </c>
       <c r="F30">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G30">
         <v>2.98</v>
@@ -7938,7 +7938,7 @@
         <v>1.71</v>
       </c>
       <c r="W30">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X30">
         <v>34</v>
@@ -8129,64 +8129,64 @@
         <v>164</v>
       </c>
       <c r="F31">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G31">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="H31">
         <v>4.9</v>
       </c>
       <c r="I31">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J31">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K31">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L31">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M31">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N31">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O31">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P31">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="Q31">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="R31">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="S31">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="T31">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U31">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V31">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W31">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X31">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y31">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z31">
         <v>44</v>
@@ -8195,64 +8195,64 @@
         <v>1000</v>
       </c>
       <c r="AB31">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC31">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD31">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE31">
         <v>60</v>
       </c>
       <c r="AF31">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG31">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH31">
         <v>17.5</v>
       </c>
       <c r="AI31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ31">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK31">
         <v>17</v>
       </c>
       <c r="AL31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM31">
         <v>1000</v>
       </c>
       <c r="AN31">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO31">
+        <v>55</v>
+      </c>
+      <c r="AP31">
+        <v>19.5</v>
+      </c>
+      <c r="AQ31">
+        <v>19</v>
+      </c>
+      <c r="AR31">
+        <v>24</v>
+      </c>
+      <c r="AS31">
         <v>48</v>
       </c>
-      <c r="AP31">
-        <v>20</v>
-      </c>
-      <c r="AQ31">
-        <v>20</v>
-      </c>
-      <c r="AR31">
-        <v>27</v>
-      </c>
-      <c r="AS31">
-        <v>46</v>
-      </c>
       <c r="AT31">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU31">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV31">
         <v>16.5</v>
@@ -8270,7 +8270,7 @@
         <v>15</v>
       </c>
       <c r="BA31">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB31">
         <v>16</v>
@@ -8279,22 +8279,22 @@
         <v>14.5</v>
       </c>
       <c r="BD31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF31">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG31">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BH31">
         <v>4.5</v>
       </c>
       <c r="BI31">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ31">
         <v>9.6</v>
@@ -8303,7 +8303,7 @@
         <v>4.9</v>
       </c>
       <c r="BL31">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM31">
         <v>9</v>
@@ -8315,10 +8315,10 @@
         <v>3.75</v>
       </c>
       <c r="BP31">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ31">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BR31">
         <v>22</v>
@@ -8339,13 +8339,13 @@
         <v>7.8</v>
       </c>
       <c r="BX31">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY31">
         <v>8</v>
       </c>
       <c r="BZ31">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA31">
         <v>6</v>
@@ -8371,25 +8371,25 @@
         <v>165</v>
       </c>
       <c r="F32">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G32">
         <v>2.6</v>
       </c>
       <c r="H32">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I32">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K32">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L32">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M32">
         <v>1.02</v>
@@ -8404,7 +8404,7 @@
         <v>3.1</v>
       </c>
       <c r="Q32">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R32">
         <v>1.87</v>
@@ -8419,7 +8419,7 @@
         <v>3.15</v>
       </c>
       <c r="V32">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W32">
         <v>1.62</v>
@@ -8434,7 +8434,7 @@
         <v>25</v>
       </c>
       <c r="AA32">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB32">
         <v>21</v>
@@ -8446,22 +8446,22 @@
         <v>13</v>
       </c>
       <c r="AE32">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF32">
         <v>24</v>
       </c>
       <c r="AG32">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH32">
         <v>14</v>
       </c>
       <c r="AI32">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ32">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK32">
         <v>22</v>
@@ -8473,13 +8473,13 @@
         <v>42</v>
       </c>
       <c r="AN32">
+        <v>11</v>
+      </c>
+      <c r="AO32">
         <v>11.5</v>
       </c>
-      <c r="AO32">
-        <v>12</v>
-      </c>
       <c r="AP32">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AQ32">
         <v>19</v>
@@ -8500,7 +8500,7 @@
         <v>12</v>
       </c>
       <c r="AW32">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX32">
         <v>21</v>
@@ -8515,7 +8515,7 @@
         <v>23</v>
       </c>
       <c r="BB32">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BC32">
         <v>20</v>
@@ -8545,31 +8545,31 @@
         <v>6</v>
       </c>
       <c r="BL32">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BM32">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BN32">
         <v>7.6</v>
       </c>
       <c r="BO32">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP32">
         <v>19</v>
       </c>
       <c r="BQ32">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BR32">
         <v>25</v>
       </c>
       <c r="BS32">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BT32">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU32">
         <v>5</v>
@@ -8578,19 +8578,19 @@
         <v>21</v>
       </c>
       <c r="BW32">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BX32">
         <v>26</v>
       </c>
       <c r="BY32">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BZ32">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA32">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="CB32" t="s">
         <v>167</v>
@@ -8613,19 +8613,19 @@
         <v>166</v>
       </c>
       <c r="F33">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="G33">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I33">
         <v>3.7</v>
       </c>
       <c r="J33">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K33">
         <v>4.5</v>
@@ -8643,13 +8643,13 @@
         <v>1.16</v>
       </c>
       <c r="P33">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q33">
         <v>1.5</v>
       </c>
       <c r="R33">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S33">
         <v>2.24</v>
@@ -8658,13 +8658,13 @@
         <v>1.5</v>
       </c>
       <c r="U33">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V33">
         <v>1.37</v>
       </c>
       <c r="W33">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="X33">
         <v>55</v>
@@ -8673,7 +8673,7 @@
         <v>23</v>
       </c>
       <c r="Z33">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA33">
         <v>1000</v>
@@ -8694,7 +8694,7 @@
         <v>17</v>
       </c>
       <c r="AG33">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH33">
         <v>15</v>
@@ -8715,7 +8715,7 @@
         <v>190</v>
       </c>
       <c r="AN33">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO33">
         <v>21</v>
@@ -8739,10 +8739,10 @@
         <v>9.6</v>
       </c>
       <c r="AV33">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW33">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX33">
         <v>15</v>
@@ -8754,7 +8754,7 @@
         <v>13</v>
       </c>
       <c r="BA33">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB33">
         <v>18.5</v>
@@ -8769,7 +8769,7 @@
         <v>34</v>
       </c>
       <c r="BF33">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG33">
         <v>18</v>
@@ -8781,58 +8781,58 @@
         <v>4.3</v>
       </c>
       <c r="BJ33">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BK33">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BL33">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="BM33">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BN33">
         <v>5.5</v>
       </c>
       <c r="BO33">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BP33">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ33">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="BR33">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BS33">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BT33">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BU33">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BW33">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BX33">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BY33">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BZ33">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CA33">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="CB33" t="s">
         <v>167</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -517,7 +517,7 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-18 15:29:02</t>
+    <t>2026-08-18 17:37:54</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1114,7 @@
         <v>2.24</v>
       </c>
       <c r="G2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -1135,16 +1135,16 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P2">
         <v>1.68</v>
       </c>
       <c r="Q2">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R2">
         <v>1.25</v>
@@ -1156,16 +1156,16 @@
         <v>1.98</v>
       </c>
       <c r="U2">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V2">
         <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y2">
         <v>12.5</v>
@@ -1180,19 +1180,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF2">
         <v>13</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
         <v>21</v>
@@ -1201,7 +1201,7 @@
         <v>80</v>
       </c>
       <c r="AJ2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK2">
         <v>28</v>
@@ -1213,13 +1213,13 @@
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
         <v>11</v>
@@ -1234,7 +1234,7 @@
         <v>7.2</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
         <v>15</v>
@@ -1255,16 +1255,16 @@
         <v>60</v>
       </c>
       <c r="BB2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BC2">
         <v>24</v>
       </c>
       <c r="BD2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE2">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF2">
         <v>21</v>
@@ -1279,7 +1279,7 @@
         <v>2.64</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
         <v>9.199999999999999</v>
@@ -1288,10 +1288,10 @@
         <v>190</v>
       </c>
       <c r="BM2">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO2">
         <v>4.4</v>
@@ -1306,10 +1306,10 @@
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BT2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BU2">
         <v>6</v>
@@ -1318,19 +1318,19 @@
         <v>36</v>
       </c>
       <c r="BW2">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BX2">
         <v>55</v>
       </c>
       <c r="BY2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2">
         <v>40</v>
       </c>
       <c r="CA2">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB2" t="s">
         <v>167</v>
@@ -1353,16 +1353,16 @@
         <v>136</v>
       </c>
       <c r="F3">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G3">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="H3">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="I3">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J3">
         <v>3.05</v>
@@ -1371,22 +1371,22 @@
         <v>3.1</v>
       </c>
       <c r="L3">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="M3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P3">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="R3">
         <v>1.19</v>
@@ -1395,46 +1395,46 @@
         <v>6</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V3">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W3">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="X3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y3">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="Z3">
         <v>14</v>
       </c>
       <c r="AA3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC3">
         <v>7</v>
       </c>
       <c r="AD3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH3">
         <v>25</v>
@@ -1443,28 +1443,28 @@
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AL3">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AN3">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AO3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AR3">
         <v>12.5</v>
@@ -1473,7 +1473,7 @@
         <v>32</v>
       </c>
       <c r="AT3">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
@@ -1494,31 +1494,31 @@
         <v>23</v>
       </c>
       <c r="BA3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB3">
+        <v>55</v>
+      </c>
+      <c r="BC3">
         <v>50</v>
-      </c>
-      <c r="BC3">
-        <v>40</v>
       </c>
       <c r="BD3">
         <v>60</v>
       </c>
       <c r="BE3">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BF3">
-        <v>12.5</v>
+        <v>75</v>
       </c>
       <c r="BG3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH3">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BI3">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BJ3">
         <v>11</v>
@@ -1530,28 +1530,28 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.34</v>
+        <v>20</v>
       </c>
       <c r="BN3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ3">
-        <v>2.22</v>
+        <v>13.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>2.28</v>
+        <v>6.6</v>
       </c>
       <c r="BT3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU3">
         <v>4.6</v>
@@ -1560,19 +1560,19 @@
         <v>23</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>2.26</v>
+        <v>15</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB3" t="s">
         <v>167</v>
@@ -1595,16 +1595,16 @@
         <v>137</v>
       </c>
       <c r="F4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H4">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I4">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J4">
         <v>3.15</v>
@@ -1613,43 +1613,43 @@
         <v>3.2</v>
       </c>
       <c r="L4">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="M4">
         <v>1.12</v>
       </c>
       <c r="N4">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="O4">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="P4">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q4">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U4">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="V4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W4">
         <v>1.42</v>
       </c>
       <c r="X4">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4">
         <v>8.199999999999999</v>
@@ -1661,10 +1661,10 @@
         <v>42</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD4">
         <v>12.5</v>
@@ -1682,37 +1682,37 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ4">
         <v>65</v>
       </c>
       <c r="AK4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL4">
+        <v>75</v>
+      </c>
+      <c r="AM4">
+        <v>190</v>
+      </c>
+      <c r="AN4">
         <v>70</v>
-      </c>
-      <c r="AM4">
-        <v>170</v>
-      </c>
-      <c r="AN4">
-        <v>65</v>
       </c>
       <c r="AO4">
         <v>40</v>
       </c>
       <c r="AP4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR4">
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT4">
         <v>9</v>
@@ -1727,7 +1727,7 @@
         <v>32</v>
       </c>
       <c r="AX4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY4">
         <v>13</v>
@@ -1736,43 +1736,43 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB4">
         <v>55</v>
       </c>
       <c r="BC4">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BD4">
+        <v>60</v>
+      </c>
+      <c r="BE4">
+        <v>120</v>
+      </c>
+      <c r="BF4">
         <v>55</v>
       </c>
-      <c r="BE4">
-        <v>110</v>
-      </c>
-      <c r="BF4">
-        <v>50</v>
-      </c>
       <c r="BG4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BH4">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BI4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN4">
         <v>6.6</v>
@@ -1784,13 +1784,13 @@
         <v>32</v>
       </c>
       <c r="BQ4">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
         <v>5.4</v>
@@ -1802,19 +1802,19 @@
         <v>23</v>
       </c>
       <c r="BW4">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX4">
         <v>44</v>
       </c>
       <c r="BY4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>48</v>
       </c>
       <c r="CA4">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>167</v>
@@ -1843,7 +1843,7 @@
         <v>2.38</v>
       </c>
       <c r="H5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>4.2</v>
@@ -1855,34 +1855,34 @@
         <v>3.05</v>
       </c>
       <c r="L5">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="M5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="P5">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q5">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="R5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U5">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V5">
         <v>1.31</v>
@@ -1891,10 +1891,10 @@
         <v>1.72</v>
       </c>
       <c r="X5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
         <v>27</v>
@@ -1903,13 +1903,13 @@
         <v>100</v>
       </c>
       <c r="AB5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE5">
         <v>75</v>
@@ -1921,7 +1921,7 @@
         <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI5">
         <v>190</v>
@@ -1930,34 +1930,34 @@
         <v>34</v>
       </c>
       <c r="AK5">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM5">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AN5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5">
         <v>9.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS5">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AT5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU5">
         <v>6.4</v>
@@ -1972,49 +1972,49 @@
         <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA5">
-        <v>17.5</v>
+        <v>60</v>
       </c>
       <c r="BB5">
         <v>30</v>
       </c>
       <c r="BC5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD5">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BE5">
         <v>15.5</v>
       </c>
       <c r="BF5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG5">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BH5">
         <v>2.82</v>
       </c>
       <c r="BI5">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
         <v>9.199999999999999</v>
       </c>
       <c r="BL5">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
         <v>4.8</v>
@@ -2023,16 +2023,16 @@
         <v>4.3</v>
       </c>
       <c r="BP5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ5">
         <v>15.5</v>
       </c>
       <c r="BR5">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BS5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT5">
         <v>7.2</v>
@@ -2044,19 +2044,19 @@
         <v>42</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="CA5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="s">
         <v>167</v>
@@ -2079,22 +2079,22 @@
         <v>139</v>
       </c>
       <c r="F6">
+        <v>1.5</v>
+      </c>
+      <c r="G6">
         <v>1.53</v>
       </c>
-      <c r="G6">
-        <v>1.55</v>
-      </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L6">
         <v>1.22</v>
@@ -2106,40 +2106,40 @@
         <v>6.4</v>
       </c>
       <c r="O6">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P6">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="Q6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R6">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S6">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T6">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U6">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V6">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W6">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z6">
-        <v>65</v>
+        <v>640</v>
       </c>
       <c r="AA6">
         <v>1000</v>
@@ -2151,10 +2151,10 @@
         <v>12</v>
       </c>
       <c r="AD6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>12</v>
@@ -2166,7 +2166,7 @@
         <v>19</v>
       </c>
       <c r="AI6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ6">
         <v>15</v>
@@ -2178,25 +2178,25 @@
         <v>26</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AO6">
         <v>65</v>
       </c>
       <c r="AP6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT6">
         <v>11.5</v>
@@ -2211,7 +2211,7 @@
         <v>50</v>
       </c>
       <c r="AX6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY6">
         <v>9.4</v>
@@ -2223,40 +2223,40 @@
         <v>55</v>
       </c>
       <c r="BB6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD6">
         <v>22</v>
       </c>
       <c r="BE6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF6">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BG6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BH6">
         <v>5.1</v>
       </c>
       <c r="BI6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ6">
         <v>10</v>
       </c>
       <c r="BK6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN6">
         <v>4.7</v>
@@ -2286,16 +2286,16 @@
         <v>1000</v>
       </c>
       <c r="BW6">
+        <v>8.6</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
         <v>8.4</v>
       </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BZ6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA6">
         <v>6.2</v>
@@ -2333,7 +2333,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2348,7 +2348,7 @@
         <v>1.1</v>
       </c>
       <c r="O7">
-        <v>1.52</v>
+        <v>1.12</v>
       </c>
       <c r="P7">
         <v>1.09</v>
@@ -2575,7 +2575,7 @@
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2811,22 +2811,22 @@
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="I9">
         <v>990</v>
       </c>
       <c r="J9">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="K9">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
         <v>1.1</v>
@@ -2844,7 +2844,7 @@
         <v>1.09</v>
       </c>
       <c r="S9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -3050,7 +3050,7 @@
         <v>1.2</v>
       </c>
       <c r="G10">
-        <v>2.86</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -3059,7 +3059,7 @@
         <v>990</v>
       </c>
       <c r="J10">
-        <v>3.15</v>
+        <v>1.6</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3074,19 +3074,19 @@
         <v>1.11</v>
       </c>
       <c r="O10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Q10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R10">
         <v>1.09</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>2.96</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3301,7 +3301,7 @@
         <v>990</v>
       </c>
       <c r="J11">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K11">
         <v>3.8</v>
@@ -3549,7 +3549,7 @@
         <v>7.2</v>
       </c>
       <c r="L12">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
         <v>1.01</v>
@@ -3558,13 +3558,13 @@
         <v>4.6</v>
       </c>
       <c r="O12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P12">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q12">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R12">
         <v>1.49</v>
@@ -3597,7 +3597,7 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>16</v>
@@ -3621,10 +3621,10 @@
         <v>270</v>
       </c>
       <c r="AJ12">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK12">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL12">
         <v>55</v>
@@ -3642,13 +3642,13 @@
         <v>19</v>
       </c>
       <c r="AQ12">
-        <v>4.4</v>
+        <v>32</v>
       </c>
       <c r="AR12">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AS12">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT12">
         <v>7.2</v>
@@ -3657,22 +3657,22 @@
         <v>12.5</v>
       </c>
       <c r="AV12">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AW12">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AX12">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AY12">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BA12">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB12">
         <v>7.8</v>
@@ -3681,16 +3681,16 @@
         <v>12.5</v>
       </c>
       <c r="BD12">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BE12">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF12">
         <v>4.1</v>
       </c>
       <c r="BG12">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BH12">
         <v>4.4</v>
@@ -3773,19 +3773,19 @@
         <v>146</v>
       </c>
       <c r="F13">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G13">
         <v>990</v>
       </c>
       <c r="H13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="I13">
         <v>990</v>
       </c>
       <c r="J13">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -4015,19 +4015,19 @@
         <v>147</v>
       </c>
       <c r="F14">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G14">
         <v>990</v>
       </c>
       <c r="H14">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I14">
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4048,13 +4048,13 @@
         <v>1.09</v>
       </c>
       <c r="Q14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="R14">
         <v>1.07</v>
       </c>
       <c r="S14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -4257,19 +4257,19 @@
         <v>148</v>
       </c>
       <c r="F15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G15">
         <v>990</v>
       </c>
       <c r="H15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I15">
         <v>990</v>
       </c>
       <c r="J15">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4281,13 +4281,13 @@
         <v>1.05</v>
       </c>
       <c r="N15">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O15">
         <v>1.26</v>
       </c>
       <c r="P15">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Q15">
         <v>1.26</v>
@@ -4296,7 +4296,7 @@
         <v>1.08</v>
       </c>
       <c r="S15">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4499,16 +4499,16 @@
         <v>149</v>
       </c>
       <c r="F16">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="G16">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H16">
+        <v>10.5</v>
+      </c>
+      <c r="I16">
         <v>11.5</v>
-      </c>
-      <c r="I16">
-        <v>12</v>
       </c>
       <c r="J16">
         <v>5.5</v>
@@ -4523,37 +4523,37 @@
         <v>1.06</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P16">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q16">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="R16">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S16">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T16">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U16">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V16">
         <v>1.09</v>
       </c>
       <c r="W16">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="X16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y16">
         <v>32</v>
@@ -4562,31 +4562,31 @@
         <v>110</v>
       </c>
       <c r="AA16">
-        <v>570</v>
+        <v>530</v>
       </c>
       <c r="AB16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>12.5</v>
       </c>
       <c r="AD16">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AE16">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AF16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AG16">
         <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI16">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AJ16">
         <v>9.800000000000001</v>
@@ -4595,19 +4595,19 @@
         <v>15.5</v>
       </c>
       <c r="AL16">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM16">
         <v>230</v>
       </c>
       <c r="AN16">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AO16">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="AP16">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16">
         <v>26</v>
@@ -4616,28 +4616,28 @@
         <v>46</v>
       </c>
       <c r="AS16">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="AT16">
         <v>7.4</v>
       </c>
       <c r="AU16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AW16">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AX16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY16">
         <v>10</v>
       </c>
       <c r="AZ16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BA16">
         <v>80</v>
@@ -4649,76 +4649,76 @@
         <v>14.5</v>
       </c>
       <c r="BD16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE16">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BF16">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG16">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="BH16">
         <v>3.6</v>
       </c>
       <c r="BI16">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK16">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BL16">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="BM16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BN16">
         <v>3.55</v>
       </c>
       <c r="BO16">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BP16">
         <v>7.8</v>
       </c>
       <c r="BQ16">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR16">
         <v>29</v>
       </c>
       <c r="BS16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT16">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU16">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BV16">
         <v>130</v>
       </c>
       <c r="BW16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BX16">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BY16">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BZ16">
         <v>15</v>
       </c>
       <c r="CA16">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB16" t="s">
         <v>167</v>
@@ -4768,13 +4768,13 @@
         <v>3.2</v>
       </c>
       <c r="O17">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P17">
         <v>1.75</v>
       </c>
       <c r="Q17">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R17">
         <v>1.28</v>
@@ -4983,13 +4983,13 @@
         <v>151</v>
       </c>
       <c r="F18">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G18">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H18">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I18">
         <v>3.7</v>
@@ -5013,7 +5013,7 @@
         <v>1.55</v>
       </c>
       <c r="P18">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q18">
         <v>2.68</v>
@@ -5231,10 +5231,10 @@
         <v>5.9</v>
       </c>
       <c r="H19">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="I19">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J19">
         <v>3.45</v>
@@ -5249,7 +5249,7 @@
         <v>1.11</v>
       </c>
       <c r="N19">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O19">
         <v>1.48</v>
@@ -5261,7 +5261,7 @@
         <v>2.46</v>
       </c>
       <c r="R19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S19">
         <v>5</v>
@@ -5497,7 +5497,7 @@
         <v>1.34</v>
       </c>
       <c r="P20">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q20">
         <v>2.12</v>
@@ -5635,58 +5635,58 @@
         <v>2.64</v>
       </c>
       <c r="BJ20">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BK20">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BN20">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BO20">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BP20">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BQ20">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BR20">
         <v>38</v>
       </c>
       <c r="BS20">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BT20">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BU20">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="BV20">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BX20">
         <v>95</v>
       </c>
       <c r="BY20">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ20">
         <v>32</v>
       </c>
       <c r="CA20">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="CB20" t="s">
         <v>167</v>
@@ -5727,7 +5727,7 @@
         <v>3.3</v>
       </c>
       <c r="L21">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M21">
         <v>1.1</v>
@@ -5739,10 +5739,10 @@
         <v>1.43</v>
       </c>
       <c r="P21">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q21">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R21">
         <v>1.26</v>
@@ -5769,7 +5769,7 @@
         <v>12</v>
       </c>
       <c r="Z21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA21">
         <v>60</v>
@@ -5850,7 +5850,7 @@
         <v>16.5</v>
       </c>
       <c r="BA21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB21">
         <v>4.4</v>
@@ -5859,10 +5859,10 @@
         <v>4.3</v>
       </c>
       <c r="BD21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE21">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF21">
         <v>4.3</v>
@@ -6196,7 +6196,7 @@
         <v>1.67</v>
       </c>
       <c r="G23">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H23">
         <v>4.7</v>
@@ -6214,25 +6214,25 @@
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N23">
         <v>4.2</v>
       </c>
       <c r="O23">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P23">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Q23">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="R23">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="S23">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="T23">
         <v>1.76</v>
@@ -6244,7 +6244,7 @@
         <v>1.2</v>
       </c>
       <c r="W23">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X23">
         <v>22</v>
@@ -6355,64 +6355,64 @@
         <v>4.5</v>
       </c>
       <c r="BH23">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
         <v>167</v>
@@ -6474,7 +6474,7 @@
         <v>1.14</v>
       </c>
       <c r="S24">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T24">
         <v>1.11</v>
@@ -6686,7 +6686,7 @@
         <v>11</v>
       </c>
       <c r="I25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J25">
         <v>4.8</v>
@@ -6725,7 +6725,7 @@
         <v>1.66</v>
       </c>
       <c r="V25">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W25">
         <v>3.35</v>
@@ -6919,46 +6919,46 @@
         <v>159</v>
       </c>
       <c r="F26">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G26">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="H26">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I26">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K26">
         <v>3.15</v>
       </c>
       <c r="L26">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M26">
         <v>1.13</v>
       </c>
       <c r="N26">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O26">
         <v>1.59</v>
       </c>
       <c r="P26">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q26">
         <v>2.74</v>
       </c>
       <c r="R26">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S26">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>2.2</v>
@@ -6967,10 +6967,10 @@
         <v>1.68</v>
       </c>
       <c r="V26">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="X26">
         <v>8.4</v>
@@ -6979,25 +6979,25 @@
         <v>12</v>
       </c>
       <c r="Z26">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA26">
         <v>110</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC26">
         <v>8.800000000000001</v>
       </c>
       <c r="AD26">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AE26">
         <v>90</v>
       </c>
       <c r="AF26">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG26">
         <v>12.5</v>
@@ -7009,10 +7009,10 @@
         <v>120</v>
       </c>
       <c r="AJ26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL26">
         <v>80</v>
@@ -7021,7 +7021,7 @@
         <v>270</v>
       </c>
       <c r="AN26">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AO26">
         <v>130</v>
@@ -7036,19 +7036,19 @@
         <v>21</v>
       </c>
       <c r="AS26">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT26">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV26">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW26">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX26">
         <v>11</v>
@@ -7060,28 +7060,28 @@
         <v>21</v>
       </c>
       <c r="BA26">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD26">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE26">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG26">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH26">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="BI26">
         <v>2.22</v>
@@ -7090,34 +7090,34 @@
         <v>12</v>
       </c>
       <c r="BK26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN26">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO26">
         <v>4.3</v>
       </c>
       <c r="BP26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ26">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT26">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BU26">
         <v>5.8</v>
@@ -7126,19 +7126,19 @@
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
+        <v>11.5</v>
+      </c>
+      <c r="BZ26">
+        <v>1000</v>
+      </c>
+      <c r="CA26">
         <v>11</v>
-      </c>
-      <c r="BZ26">
-        <v>1000</v>
-      </c>
-      <c r="CA26">
-        <v>10.5</v>
       </c>
       <c r="CB26" t="s">
         <v>167</v>
@@ -7161,13 +7161,13 @@
         <v>160</v>
       </c>
       <c r="F27">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G27">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H27">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I27">
         <v>3.2</v>
@@ -7179,7 +7179,7 @@
         <v>3.85</v>
       </c>
       <c r="L27">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M27">
         <v>1.05</v>
@@ -7194,7 +7194,7 @@
         <v>2.18</v>
       </c>
       <c r="Q27">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R27">
         <v>1.47</v>
@@ -7206,16 +7206,16 @@
         <v>1.65</v>
       </c>
       <c r="U27">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V27">
         <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X27">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y27">
         <v>15</v>
@@ -7236,7 +7236,7 @@
         <v>13.5</v>
       </c>
       <c r="AE27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF27">
         <v>17</v>
@@ -7278,7 +7278,7 @@
         <v>20</v>
       </c>
       <c r="AS27">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AT27">
         <v>11</v>
@@ -7314,7 +7314,7 @@
         <v>21</v>
       </c>
       <c r="BE27">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BF27">
         <v>14</v>
@@ -7415,7 +7415,7 @@
         <v>2.38</v>
       </c>
       <c r="J28">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K28">
         <v>4.2</v>
@@ -7430,7 +7430,7 @@
         <v>5.8</v>
       </c>
       <c r="O28">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P28">
         <v>2.6</v>
@@ -7439,7 +7439,7 @@
         <v>1.59</v>
       </c>
       <c r="R28">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S28">
         <v>2.48</v>
@@ -7451,61 +7451,61 @@
         <v>2.64</v>
       </c>
       <c r="V28">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W28">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y28">
         <v>16</v>
       </c>
       <c r="Z28">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA28">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AB28">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC28">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE28">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF28">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AG28">
         <v>14</v>
       </c>
       <c r="AH28">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI28">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AJ28">
         <v>170</v>
       </c>
       <c r="AK28">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AL28">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM28">
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="AN28">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO28">
         <v>12</v>
@@ -7514,52 +7514,52 @@
         <v>18</v>
       </c>
       <c r="AQ28">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR28">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS28">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AT28">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU28">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV28">
         <v>10.5</v>
       </c>
       <c r="AW28">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX28">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY28">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ28">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA28">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BB28">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BC28">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BD28">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE28">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BF28">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG28">
         <v>10.5</v>
@@ -7654,7 +7654,7 @@
         <v>3.35</v>
       </c>
       <c r="I29">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J29">
         <v>3.75</v>
@@ -7687,7 +7687,7 @@
         <v>3.1</v>
       </c>
       <c r="T29">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U29">
         <v>2.36</v>
@@ -7699,16 +7699,16 @@
         <v>1.78</v>
       </c>
       <c r="X29">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y29">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Z29">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA29">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="AB29">
         <v>11.5</v>
@@ -7717,7 +7717,7 @@
         <v>8.4</v>
       </c>
       <c r="AD29">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE29">
         <v>75</v>
@@ -7726,22 +7726,22 @@
         <v>15.5</v>
       </c>
       <c r="AG29">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH29">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI29">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ29">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AK29">
         <v>23</v>
       </c>
       <c r="AL29">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM29">
         <v>1000</v>
@@ -7759,16 +7759,16 @@
         <v>13</v>
       </c>
       <c r="AR29">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AS29">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT29">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU29">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV29">
         <v>12.5</v>
@@ -7777,31 +7777,31 @@
         <v>22</v>
       </c>
       <c r="AX29">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY29">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA29">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BB29">
         <v>20</v>
       </c>
       <c r="BC29">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD29">
         <v>21</v>
       </c>
       <c r="BE29">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BF29">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BG29">
         <v>20</v>
@@ -7923,10 +7923,10 @@
         <v>1.42</v>
       </c>
       <c r="R30">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S30">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T30">
         <v>1.41</v>
@@ -7953,7 +7953,7 @@
         <v>36</v>
       </c>
       <c r="AB30">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC30">
         <v>11</v>
@@ -7986,7 +7986,7 @@
         <v>29</v>
       </c>
       <c r="AM30">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN30">
         <v>13</v>
@@ -7995,19 +7995,19 @@
         <v>9.4</v>
       </c>
       <c r="AP30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ30">
         <v>18.5</v>
       </c>
       <c r="AR30">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS30">
         <v>32</v>
       </c>
       <c r="AT30">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU30">
         <v>10</v>
@@ -8019,7 +8019,7 @@
         <v>18</v>
       </c>
       <c r="AX30">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY30">
         <v>12.5</v>
@@ -8132,10 +8132,10 @@
         <v>1.73</v>
       </c>
       <c r="G31">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H31">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>5.3</v>
@@ -8144,7 +8144,7 @@
         <v>4.2</v>
       </c>
       <c r="K31">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L31">
         <v>1.31</v>
@@ -8171,7 +8171,7 @@
         <v>2.62</v>
       </c>
       <c r="T31">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U31">
         <v>2.36</v>
@@ -8180,19 +8180,19 @@
         <v>1.23</v>
       </c>
       <c r="W31">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X31">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y31">
         <v>23</v>
       </c>
       <c r="Z31">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB31">
         <v>11.5</v>
@@ -8201,7 +8201,7 @@
         <v>10</v>
       </c>
       <c r="AD31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE31">
         <v>60</v>
@@ -8216,70 +8216,70 @@
         <v>17.5</v>
       </c>
       <c r="AI31">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ31">
         <v>18.5</v>
       </c>
       <c r="AK31">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL31">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN31">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP31">
         <v>19.5</v>
       </c>
       <c r="AQ31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR31">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AS31">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AT31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU31">
         <v>9</v>
       </c>
       <c r="AV31">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW31">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AX31">
         <v>11</v>
       </c>
       <c r="AY31">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ31">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA31">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BB31">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC31">
         <v>14.5</v>
       </c>
       <c r="BD31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BE31">
         <v>34</v>
@@ -8374,16 +8374,16 @@
         <v>2.54</v>
       </c>
       <c r="G32">
+        <v>2.58</v>
+      </c>
+      <c r="H32">
         <v>2.6</v>
       </c>
-      <c r="H32">
-        <v>2.58</v>
-      </c>
       <c r="I32">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J32">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K32">
         <v>4.5</v>
@@ -8401,7 +8401,7 @@
         <v>1.14</v>
       </c>
       <c r="P32">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q32">
         <v>1.44</v>
@@ -8419,10 +8419,10 @@
         <v>3.15</v>
       </c>
       <c r="V32">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W32">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X32">
         <v>32</v>
@@ -8452,7 +8452,7 @@
         <v>24</v>
       </c>
       <c r="AG32">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH32">
         <v>14</v>
@@ -8461,7 +8461,7 @@
         <v>26</v>
       </c>
       <c r="AJ32">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK32">
         <v>22</v>
@@ -8479,7 +8479,7 @@
         <v>11.5</v>
       </c>
       <c r="AP32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ32">
         <v>19</v>
@@ -8500,7 +8500,7 @@
         <v>12</v>
       </c>
       <c r="AW32">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX32">
         <v>21</v>
@@ -8509,13 +8509,13 @@
         <v>11.5</v>
       </c>
       <c r="AZ32">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA32">
         <v>23</v>
       </c>
       <c r="BB32">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC32">
         <v>20</v>
@@ -8616,16 +8616,16 @@
         <v>1.99</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H33">
         <v>3.6</v>
       </c>
       <c r="I33">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J33">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K33">
         <v>4.5</v>
@@ -8658,16 +8658,16 @@
         <v>1.5</v>
       </c>
       <c r="U33">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
         <v>1.37</v>
       </c>
       <c r="W33">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X33">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="Y33">
         <v>23</v>
@@ -8676,19 +8676,19 @@
         <v>34</v>
       </c>
       <c r="AA33">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB33">
         <v>16</v>
       </c>
       <c r="AC33">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD33">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE33">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF33">
         <v>17</v>
@@ -8703,37 +8703,37 @@
         <v>34</v>
       </c>
       <c r="AJ33">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK33">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL33">
         <v>24</v>
       </c>
       <c r="AM33">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AN33">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO33">
         <v>21</v>
       </c>
       <c r="AP33">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AQ33">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR33">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AS33">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AT33">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU33">
         <v>9.6</v>
@@ -8742,7 +8742,7 @@
         <v>14.5</v>
       </c>
       <c r="AW33">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AX33">
         <v>15</v>
@@ -8751,13 +8751,13 @@
         <v>10</v>
       </c>
       <c r="AZ33">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA33">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BB33">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BC33">
         <v>16</v>
@@ -8766,13 +8766,13 @@
         <v>21</v>
       </c>
       <c r="BE33">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BF33">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG33">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH33">
         <v>5.7</v>
@@ -8790,7 +8790,7 @@
         <v>80</v>
       </c>
       <c r="BM33">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN33">
         <v>5.5</v>
@@ -8799,7 +8799,7 @@
         <v>4.9</v>
       </c>
       <c r="BP33">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BQ33">
         <v>10</v>
@@ -8808,7 +8808,7 @@
         <v>24</v>
       </c>
       <c r="BS33">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BT33">
         <v>7.6</v>
@@ -8817,16 +8817,16 @@
         <v>5.8</v>
       </c>
       <c r="BV33">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW33">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BX33">
         <v>34</v>
       </c>
       <c r="BY33">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BZ33">
         <v>16</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -547,7 +547,7 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-18 19:47:15</t>
+    <t>2026-08-18 21:56:48</t>
   </si>
 </sst>
 </file>
@@ -1141,226 +1141,226 @@
         <v>142</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.52</v>
+        <v>2.06</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="O2">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="P2">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q2">
-        <v>2.44</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S2">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="T2">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="U2">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="X2">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="Y2">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB2">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AC2">
+        <v>6.8</v>
+      </c>
+      <c r="AD2">
+        <v>17</v>
+      </c>
+      <c r="AE2">
+        <v>70</v>
+      </c>
+      <c r="AF2">
+        <v>14</v>
+      </c>
+      <c r="AG2">
+        <v>14</v>
+      </c>
+      <c r="AH2">
+        <v>28</v>
+      </c>
+      <c r="AI2">
+        <v>120</v>
+      </c>
+      <c r="AJ2">
+        <v>42</v>
+      </c>
+      <c r="AK2">
+        <v>42</v>
+      </c>
+      <c r="AL2">
+        <v>110</v>
+      </c>
+      <c r="AM2">
+        <v>300</v>
+      </c>
+      <c r="AN2">
+        <v>55</v>
+      </c>
+      <c r="AO2">
+        <v>110</v>
+      </c>
+      <c r="AP2">
         <v>7</v>
       </c>
-      <c r="AD2">
-        <v>16.5</v>
-      </c>
-      <c r="AE2">
+      <c r="AQ2">
+        <v>8.4</v>
+      </c>
+      <c r="AR2">
+        <v>19.5</v>
+      </c>
+      <c r="AS2">
         <v>60</v>
       </c>
-      <c r="AF2">
-        <v>13</v>
-      </c>
-      <c r="AG2">
-        <v>11</v>
-      </c>
-      <c r="AH2">
-        <v>21</v>
-      </c>
-      <c r="AI2">
-        <v>80</v>
-      </c>
-      <c r="AJ2">
-        <v>29</v>
-      </c>
-      <c r="AK2">
-        <v>28</v>
-      </c>
-      <c r="AL2">
-        <v>55</v>
-      </c>
-      <c r="AM2">
-        <v>150</v>
-      </c>
-      <c r="AN2">
-        <v>26</v>
-      </c>
-      <c r="AO2">
-        <v>75</v>
-      </c>
-      <c r="AP2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ2">
-        <v>11</v>
-      </c>
-      <c r="AR2">
-        <v>23</v>
-      </c>
-      <c r="AS2">
-        <v>75</v>
-      </c>
       <c r="AT2">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BA2">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BB2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BC2">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BD2">
+        <v>75</v>
+      </c>
+      <c r="BE2">
+        <v>230</v>
+      </c>
+      <c r="BF2">
         <v>44</v>
       </c>
-      <c r="BE2">
-        <v>16.5</v>
-      </c>
-      <c r="BF2">
-        <v>23</v>
-      </c>
       <c r="BG2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="BI2">
-        <v>2.66</v>
+        <v>1.87</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BK2">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="BL2">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7.4</v>
+        <v>17</v>
       </c>
       <c r="BN2">
         <v>5.5</v>
       </c>
       <c r="BO2">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP2">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="BQ2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="BR2">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="BS2">
-        <v>6.4</v>
+        <v>100</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU2">
         <v>6</v>
       </c>
       <c r="BV2">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BW2">
-        <v>7.2</v>
+        <v>46</v>
       </c>
       <c r="BX2">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="BY2">
-        <v>6.8</v>
+        <v>120</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="CA2">
-        <v>6.4</v>
+        <v>110</v>
       </c>
       <c r="CB2" t="s">
         <v>177</v>
@@ -1383,226 +1383,226 @@
         <v>143</v>
       </c>
       <c r="F3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H3">
+        <v>2.86</v>
+      </c>
+      <c r="I3">
+        <v>2.88</v>
+      </c>
+      <c r="J3">
+        <v>2.6</v>
+      </c>
+      <c r="K3">
+        <v>2.62</v>
+      </c>
+      <c r="L3">
         <v>2.48</v>
       </c>
-      <c r="I3">
-        <v>2.5</v>
-      </c>
-      <c r="J3">
-        <v>3.05</v>
-      </c>
-      <c r="K3">
-        <v>3.1</v>
-      </c>
-      <c r="L3">
-        <v>1.63</v>
-      </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="N3">
-        <v>2.62</v>
+        <v>1.92</v>
       </c>
       <c r="O3">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="P3">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="Q3">
-        <v>2.84</v>
+        <v>4.3</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="T3">
-        <v>2.22</v>
+        <v>1.15</v>
       </c>
       <c r="U3">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X3">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="Y3">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AA3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>7</v>
+        <v>990</v>
       </c>
       <c r="AD3">
+        <v>990</v>
+      </c>
+      <c r="AE3">
+        <v>480</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>990</v>
+      </c>
+      <c r="AH3">
+        <v>990</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>480</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>300</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>4</v>
+      </c>
+      <c r="AQ3">
+        <v>1.75</v>
+      </c>
+      <c r="AR3">
+        <v>12</v>
+      </c>
+      <c r="AS3">
+        <v>40</v>
+      </c>
+      <c r="AT3">
+        <v>1.92</v>
+      </c>
+      <c r="AU3">
+        <v>1.51</v>
+      </c>
+      <c r="AV3">
+        <v>15.5</v>
+      </c>
+      <c r="AW3">
+        <v>50</v>
+      </c>
+      <c r="AX3">
         <v>12.5</v>
       </c>
-      <c r="AE3">
-        <v>38</v>
-      </c>
-      <c r="AF3">
+      <c r="AY3">
+        <v>18</v>
+      </c>
+      <c r="AZ3">
+        <v>34</v>
+      </c>
+      <c r="BA3">
+        <v>85</v>
+      </c>
+      <c r="BB3">
+        <v>70</v>
+      </c>
+      <c r="BC3">
+        <v>75</v>
+      </c>
+      <c r="BD3">
+        <v>120</v>
+      </c>
+      <c r="BE3">
+        <v>150</v>
+      </c>
+      <c r="BF3">
+        <v>110</v>
+      </c>
+      <c r="BG3">
+        <v>65</v>
+      </c>
+      <c r="BH3">
+        <v>1.68</v>
+      </c>
+      <c r="BI3">
+        <v>1.64</v>
+      </c>
+      <c r="BJ3">
+        <v>29</v>
+      </c>
+      <c r="BK3">
         <v>24</v>
       </c>
-      <c r="AG3">
-        <v>17</v>
-      </c>
-      <c r="AH3">
-        <v>25</v>
-      </c>
-      <c r="AI3">
-        <v>70</v>
-      </c>
-      <c r="AJ3">
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>13</v>
+      </c>
+      <c r="BN3">
+        <v>7.6</v>
+      </c>
+      <c r="BO3">
+        <v>6.6</v>
+      </c>
+      <c r="BP3">
+        <v>140</v>
+      </c>
+      <c r="BQ3">
+        <v>21</v>
+      </c>
+      <c r="BR3">
+        <v>910</v>
+      </c>
+      <c r="BS3">
+        <v>12.5</v>
+      </c>
+      <c r="BT3">
+        <v>6.4</v>
+      </c>
+      <c r="BU3">
+        <v>5.4</v>
+      </c>
+      <c r="BV3">
         <v>85</v>
       </c>
-      <c r="AK3">
-        <v>60</v>
-      </c>
-      <c r="AL3">
-        <v>95</v>
-      </c>
-      <c r="AM3">
-        <v>250</v>
-      </c>
-      <c r="AN3">
-        <v>160</v>
-      </c>
-      <c r="AO3">
-        <v>42</v>
-      </c>
-      <c r="AP3">
-        <v>7.6</v>
-      </c>
-      <c r="AQ3">
-        <v>6.8</v>
-      </c>
-      <c r="AR3">
+      <c r="BW3">
+        <v>19</v>
+      </c>
+      <c r="BX3">
+        <v>230</v>
+      </c>
+      <c r="BY3">
         <v>12.5</v>
       </c>
-      <c r="AS3">
-        <v>32</v>
-      </c>
-      <c r="AT3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU3">
-        <v>6.6</v>
-      </c>
-      <c r="AV3">
-        <v>11.5</v>
-      </c>
-      <c r="AW3">
-        <v>32</v>
-      </c>
-      <c r="AX3">
-        <v>19.5</v>
-      </c>
-      <c r="AY3">
-        <v>14.5</v>
-      </c>
-      <c r="AZ3">
-        <v>23</v>
-      </c>
-      <c r="BA3">
-        <v>50</v>
-      </c>
-      <c r="BB3">
-        <v>60</v>
-      </c>
-      <c r="BC3">
-        <v>50</v>
-      </c>
-      <c r="BD3">
-        <v>60</v>
-      </c>
-      <c r="BE3">
-        <v>140</v>
-      </c>
-      <c r="BF3">
-        <v>75</v>
-      </c>
-      <c r="BG3">
-        <v>34</v>
-      </c>
-      <c r="BH3">
-        <v>2.62</v>
-      </c>
-      <c r="BI3">
-        <v>2.48</v>
-      </c>
-      <c r="BJ3">
-        <v>11</v>
-      </c>
-      <c r="BK3">
-        <v>7.6</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>21</v>
-      </c>
-      <c r="BN3">
-        <v>6.6</v>
-      </c>
-      <c r="BO3">
-        <v>5.2</v>
-      </c>
-      <c r="BP3">
-        <v>42</v>
-      </c>
-      <c r="BQ3">
-        <v>14</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>10.5</v>
-      </c>
-      <c r="BT3">
-        <v>5</v>
-      </c>
-      <c r="BU3">
-        <v>4.6</v>
-      </c>
-      <c r="BV3">
-        <v>23</v>
-      </c>
-      <c r="BW3">
-        <v>14</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>15.5</v>
-      </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA3">
-        <v>16.5</v>
+        <v>190</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1625,226 +1625,226 @@
         <v>144</v>
       </c>
       <c r="F4">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="G4">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="H4">
-        <v>2.56</v>
+        <v>1.57</v>
       </c>
       <c r="I4">
-        <v>2.58</v>
+        <v>1.58</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="K4">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N4">
+        <v>7.2</v>
+      </c>
+      <c r="O4">
+        <v>1.15</v>
+      </c>
+      <c r="P4">
+        <v>2.36</v>
+      </c>
+      <c r="Q4">
+        <v>1.71</v>
+      </c>
+      <c r="R4">
+        <v>1.43</v>
+      </c>
+      <c r="S4">
+        <v>3.25</v>
+      </c>
+      <c r="T4">
+        <v>1.52</v>
+      </c>
+      <c r="U4">
         <v>2.66</v>
       </c>
-      <c r="O4">
-        <v>1.57</v>
-      </c>
-      <c r="P4">
-        <v>1.55</v>
-      </c>
-      <c r="Q4">
-        <v>2.78</v>
-      </c>
-      <c r="R4">
-        <v>1.2</v>
-      </c>
-      <c r="S4">
-        <v>5.9</v>
-      </c>
-      <c r="T4">
-        <v>2.18</v>
-      </c>
-      <c r="U4">
-        <v>1.81</v>
-      </c>
       <c r="V4">
-        <v>1.63</v>
+        <v>2.74</v>
       </c>
       <c r="W4">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="X4">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z4">
+        <v>8</v>
+      </c>
+      <c r="AA4">
+        <v>17</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>7.2</v>
+      </c>
+      <c r="AD4">
+        <v>7.2</v>
+      </c>
+      <c r="AE4">
+        <v>16.5</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
         <v>15</v>
       </c>
-      <c r="AA4">
-        <v>42</v>
-      </c>
-      <c r="AB4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC4">
+      <c r="AH4">
+        <v>14.5</v>
+      </c>
+      <c r="AI4">
+        <v>32</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>60</v>
+      </c>
+      <c r="AL4">
+        <v>55</v>
+      </c>
+      <c r="AM4">
+        <v>120</v>
+      </c>
+      <c r="AN4">
+        <v>110</v>
+      </c>
+      <c r="AO4">
+        <v>16.5</v>
+      </c>
+      <c r="AP4">
+        <v>15</v>
+      </c>
+      <c r="AQ4">
         <v>7</v>
       </c>
-      <c r="AD4">
-        <v>12.5</v>
-      </c>
-      <c r="AE4">
-        <v>38</v>
-      </c>
-      <c r="AF4">
-        <v>21</v>
-      </c>
-      <c r="AG4">
-        <v>15.5</v>
-      </c>
-      <c r="AH4">
-        <v>25</v>
-      </c>
-      <c r="AI4">
-        <v>65</v>
-      </c>
-      <c r="AJ4">
-        <v>70</v>
-      </c>
-      <c r="AK4">
-        <v>55</v>
-      </c>
-      <c r="AL4">
-        <v>80</v>
-      </c>
-      <c r="AM4">
-        <v>190</v>
-      </c>
-      <c r="AN4">
-        <v>90</v>
-      </c>
-      <c r="AO4">
-        <v>42</v>
-      </c>
-      <c r="AP4">
-        <v>8</v>
-      </c>
-      <c r="AQ4">
+      <c r="AR4">
         <v>7.2</v>
       </c>
-      <c r="AR4">
-        <v>13.5</v>
-      </c>
       <c r="AS4">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="AT4">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="AU4">
         <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="AW4">
+        <v>15</v>
+      </c>
+      <c r="AX4">
+        <v>15</v>
+      </c>
+      <c r="AY4">
+        <v>13.5</v>
+      </c>
+      <c r="AZ4">
+        <v>13</v>
+      </c>
+      <c r="BA4">
+        <v>28</v>
+      </c>
+      <c r="BB4">
+        <v>15</v>
+      </c>
+      <c r="BC4">
+        <v>48</v>
+      </c>
+      <c r="BD4">
+        <v>42</v>
+      </c>
+      <c r="BE4">
+        <v>85</v>
+      </c>
+      <c r="BF4">
+        <v>75</v>
+      </c>
+      <c r="BG4">
+        <v>14.5</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>8.6</v>
+      </c>
+      <c r="BJ4">
+        <v>5.6</v>
+      </c>
+      <c r="BK4">
+        <v>5.1</v>
+      </c>
+      <c r="BL4">
+        <v>140</v>
+      </c>
+      <c r="BM4">
+        <v>100</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>8.6</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>8.6</v>
+      </c>
+      <c r="BR4">
+        <v>50</v>
+      </c>
+      <c r="BS4">
+        <v>36</v>
+      </c>
+      <c r="BT4">
+        <v>1.93</v>
+      </c>
+      <c r="BU4">
+        <v>1.89</v>
+      </c>
+      <c r="BV4">
+        <v>6.6</v>
+      </c>
+      <c r="BW4">
+        <v>5.8</v>
+      </c>
+      <c r="BX4">
+        <v>19.5</v>
+      </c>
+      <c r="BY4">
+        <v>18.5</v>
+      </c>
+      <c r="BZ4">
         <v>32</v>
       </c>
-      <c r="AX4">
-        <v>18.5</v>
-      </c>
-      <c r="AY4">
-        <v>14</v>
-      </c>
-      <c r="AZ4">
-        <v>21</v>
-      </c>
-      <c r="BA4">
-        <v>55</v>
-      </c>
-      <c r="BB4">
-        <v>55</v>
-      </c>
-      <c r="BC4">
-        <v>44</v>
-      </c>
-      <c r="BD4">
-        <v>65</v>
-      </c>
-      <c r="BE4">
-        <v>130</v>
-      </c>
-      <c r="BF4">
-        <v>60</v>
-      </c>
-      <c r="BG4">
-        <v>38</v>
-      </c>
-      <c r="BH4">
-        <v>2.78</v>
-      </c>
-      <c r="BI4">
-        <v>2.44</v>
-      </c>
-      <c r="BJ4">
-        <v>11</v>
-      </c>
-      <c r="BK4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BL4">
-        <v>210</v>
-      </c>
-      <c r="BM4">
-        <v>12</v>
-      </c>
-      <c r="BN4">
-        <v>6.6</v>
-      </c>
-      <c r="BO4">
-        <v>5.6</v>
-      </c>
-      <c r="BP4">
-        <v>32</v>
-      </c>
-      <c r="BQ4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR4">
-        <v>55</v>
-      </c>
-      <c r="BS4">
-        <v>10.5</v>
-      </c>
-      <c r="BT4">
-        <v>5.4</v>
-      </c>
-      <c r="BU4">
-        <v>4.7</v>
-      </c>
-      <c r="BV4">
-        <v>23</v>
-      </c>
-      <c r="BW4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX4">
-        <v>48</v>
-      </c>
-      <c r="BY4">
-        <v>10</v>
-      </c>
-      <c r="BZ4">
-        <v>55</v>
-      </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1867,226 +1867,226 @@
         <v>145</v>
       </c>
       <c r="F5">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="H5">
+        <v>4.1</v>
+      </c>
+      <c r="I5">
+        <v>4.3</v>
+      </c>
+      <c r="J5">
+        <v>2.78</v>
+      </c>
+      <c r="K5">
+        <v>2.84</v>
+      </c>
+      <c r="L5">
+        <v>2.24</v>
+      </c>
+      <c r="M5">
+        <v>1.23</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>1.96</v>
+      </c>
+      <c r="P5">
+        <v>1.31</v>
+      </c>
+      <c r="Q5">
         <v>4</v>
       </c>
-      <c r="I5">
-        <v>4.2</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>3.05</v>
-      </c>
-      <c r="L5">
-        <v>1.62</v>
-      </c>
-      <c r="M5">
-        <v>1.14</v>
-      </c>
-      <c r="N5">
-        <v>2.6</v>
-      </c>
-      <c r="O5">
-        <v>1.6</v>
-      </c>
-      <c r="P5">
-        <v>1.51</v>
-      </c>
-      <c r="Q5">
-        <v>2.86</v>
-      </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="S5">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="T5">
-        <v>2.24</v>
+        <v>2.84</v>
       </c>
       <c r="U5">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="X5">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="Y5">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AE5">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AF5">
         <v>13</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AH5">
+        <v>44</v>
+      </c>
+      <c r="AI5">
+        <v>220</v>
+      </c>
+      <c r="AJ5">
+        <v>48</v>
+      </c>
+      <c r="AK5">
+        <v>60</v>
+      </c>
+      <c r="AL5">
+        <v>150</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>85</v>
+      </c>
+      <c r="AO5">
+        <v>280</v>
+      </c>
+      <c r="AP5">
+        <v>5.3</v>
+      </c>
+      <c r="AQ5">
+        <v>7.8</v>
+      </c>
+      <c r="AR5">
         <v>25</v>
       </c>
-      <c r="AI5">
-        <v>190</v>
-      </c>
-      <c r="AJ5">
-        <v>34</v>
-      </c>
-      <c r="AK5">
-        <v>34</v>
-      </c>
-      <c r="AL5">
-        <v>80</v>
-      </c>
-      <c r="AM5">
-        <v>230</v>
-      </c>
-      <c r="AN5">
-        <v>38</v>
-      </c>
-      <c r="AO5">
-        <v>130</v>
-      </c>
-      <c r="AP5">
-        <v>7.2</v>
-      </c>
-      <c r="AQ5">
-        <v>9.6</v>
-      </c>
-      <c r="AR5">
-        <v>24</v>
-      </c>
       <c r="AS5">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AT5">
+        <v>5.2</v>
+      </c>
+      <c r="AU5">
         <v>6.6</v>
       </c>
-      <c r="AU5">
-        <v>6.4</v>
-      </c>
       <c r="AV5">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AW5">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AX5">
         <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AZ5">
+        <v>34</v>
+      </c>
+      <c r="BA5">
+        <v>170</v>
+      </c>
+      <c r="BB5">
+        <v>36</v>
+      </c>
+      <c r="BC5">
+        <v>44</v>
+      </c>
+      <c r="BD5">
+        <v>110</v>
+      </c>
+      <c r="BE5">
+        <v>260</v>
+      </c>
+      <c r="BF5">
+        <v>60</v>
+      </c>
+      <c r="BG5">
+        <v>150</v>
+      </c>
+      <c r="BH5">
+        <v>1.82</v>
+      </c>
+      <c r="BI5">
+        <v>1.77</v>
+      </c>
+      <c r="BJ5">
         <v>22</v>
       </c>
-      <c r="BA5">
+      <c r="BK5">
+        <v>19</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>23</v>
+      </c>
+      <c r="BN5">
+        <v>5.2</v>
+      </c>
+      <c r="BO5">
+        <v>4.8</v>
+      </c>
+      <c r="BP5">
+        <v>38</v>
+      </c>
+      <c r="BQ5">
+        <v>30</v>
+      </c>
+      <c r="BR5">
+        <v>160</v>
+      </c>
+      <c r="BS5">
+        <v>100</v>
+      </c>
+      <c r="BT5">
+        <v>8</v>
+      </c>
+      <c r="BU5">
+        <v>7</v>
+      </c>
+      <c r="BV5">
         <v>85</v>
       </c>
-      <c r="BB5">
-        <v>30</v>
-      </c>
-      <c r="BC5">
-        <v>30</v>
-      </c>
-      <c r="BD5">
-        <v>60</v>
-      </c>
-      <c r="BE5">
-        <v>16.5</v>
-      </c>
-      <c r="BF5">
-        <v>32</v>
-      </c>
-      <c r="BG5">
-        <v>75</v>
-      </c>
-      <c r="BH5">
-        <v>2.86</v>
-      </c>
-      <c r="BI5">
-        <v>2.44</v>
-      </c>
-      <c r="BJ5">
-        <v>11.5</v>
-      </c>
-      <c r="BK5">
-        <v>10</v>
-      </c>
-      <c r="BL5">
-        <v>260</v>
-      </c>
-      <c r="BM5">
-        <v>10.5</v>
-      </c>
-      <c r="BN5">
-        <v>4.8</v>
-      </c>
-      <c r="BO5">
-        <v>4.4</v>
-      </c>
-      <c r="BP5">
-        <v>20</v>
-      </c>
-      <c r="BQ5">
-        <v>15.5</v>
-      </c>
-      <c r="BR5">
-        <v>44</v>
-      </c>
-      <c r="BS5">
-        <v>9</v>
-      </c>
-      <c r="BT5">
-        <v>7.2</v>
-      </c>
-      <c r="BU5">
-        <v>6.2</v>
-      </c>
-      <c r="BV5">
-        <v>42</v>
-      </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BX5">
-        <v>65</v>
+        <v>240</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>120</v>
       </c>
       <c r="BZ5">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="CA5">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="CB5" t="s">
         <v>177</v>
@@ -2109,37 +2109,37 @@
         <v>146</v>
       </c>
       <c r="F6">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="G6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H6">
         <v>6.8</v>
       </c>
       <c r="I6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K6">
         <v>5.4</v>
       </c>
       <c r="L6">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M6">
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O6">
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q6">
         <v>1.5</v>
@@ -2148,7 +2148,7 @@
         <v>1.78</v>
       </c>
       <c r="S6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T6">
         <v>1.66</v>
@@ -2160,10 +2160,10 @@
         <v>1.16</v>
       </c>
       <c r="W6">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y6">
         <v>36</v>
@@ -2175,16 +2175,16 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC6">
         <v>12</v>
       </c>
       <c r="AD6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE6">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>12</v>
@@ -2196,19 +2196,19 @@
         <v>19</v>
       </c>
       <c r="AI6">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="AJ6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK6">
         <v>14</v>
       </c>
       <c r="AL6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM6">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
         <v>5</v>
@@ -2217,7 +2217,7 @@
         <v>65</v>
       </c>
       <c r="AP6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ6">
         <v>30</v>
@@ -2247,7 +2247,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA6">
         <v>55</v>
@@ -2268,7 +2268,7 @@
         <v>4.6</v>
       </c>
       <c r="BG6">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH6">
         <v>5.2</v>
@@ -2280,7 +2280,7 @@
         <v>10</v>
       </c>
       <c r="BK6">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2292,16 +2292,16 @@
         <v>4.7</v>
       </c>
       <c r="BO6">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BP6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ6">
         <v>5.4</v>
       </c>
       <c r="BR6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS6">
         <v>10.5</v>
@@ -2316,13 +2316,13 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6">
         <v>11</v>
@@ -2363,7 +2363,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2593,13 +2593,13 @@
         <v>148</v>
       </c>
       <c r="F8">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G8">
         <v>2.18</v>
       </c>
       <c r="H8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I8">
         <v>27</v>
@@ -2644,19 +2644,19 @@
         <v>1.13</v>
       </c>
       <c r="W8">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB8">
         <v>970</v>
@@ -2665,10 +2665,10 @@
         <v>950</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF8">
         <v>500</v>
@@ -2677,10 +2677,10 @@
         <v>950</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ8">
         <v>900</v>
@@ -2692,61 +2692,61 @@
         <v>500</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8">
         <v>500</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AQ8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AR8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AS8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AT8">
         <v>3.85</v>
       </c>
       <c r="AU8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AV8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AW8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AX8">
         <v>4.9</v>
       </c>
       <c r="AY8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AZ8">
+        <v>1.1</v>
+      </c>
+      <c r="BA8">
+        <v>1.1</v>
+      </c>
+      <c r="BB8">
+        <v>1.1</v>
+      </c>
+      <c r="BC8">
         <v>1.08</v>
       </c>
-      <c r="BA8">
-        <v>1.08</v>
-      </c>
-      <c r="BB8">
-        <v>1.08</v>
-      </c>
-      <c r="BC8">
-        <v>1.07</v>
-      </c>
       <c r="BD8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BE8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BF8">
         <v>4.3</v>
@@ -2835,7 +2835,7 @@
         <v>149</v>
       </c>
       <c r="F9">
-        <v>2.84</v>
+        <v>2.54</v>
       </c>
       <c r="G9">
         <v>17</v>
@@ -2889,106 +2889,106 @@
         <v>1.21</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA9">
         <v>900</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC9">
         <v>950</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH9">
         <v>950</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ9">
         <v>900</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM9">
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP9">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AR9">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AS9">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AT9">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AU9">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AV9">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AW9">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AX9">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AY9">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BA9">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="BB9">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="BC9">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="BD9">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="BE9">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="BF9">
         <v>1.55</v>
@@ -3080,7 +3080,7 @@
         <v>1.23</v>
       </c>
       <c r="G10">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="H10">
         <v>3.2</v>
@@ -3089,7 +3089,7 @@
         <v>990</v>
       </c>
       <c r="J10">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3104,13 +3104,13 @@
         <v>1.11</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P10">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Q10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R10">
         <v>1.07</v>
@@ -3128,7 +3128,7 @@
         <v>1.02</v>
       </c>
       <c r="W10">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3325,7 +3325,7 @@
         <v>20</v>
       </c>
       <c r="H11">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="I11">
         <v>2.48</v>
@@ -3340,19 +3340,19 @@
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
         <v>1.1</v>
       </c>
       <c r="O11">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="P11">
         <v>1.09</v>
       </c>
       <c r="Q11">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="R11">
         <v>1.07</v>
@@ -3439,7 +3439,7 @@
         <v>1.56</v>
       </c>
       <c r="AT11">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="AU11">
         <v>4.9</v>
@@ -3561,7 +3561,7 @@
         <v>152</v>
       </c>
       <c r="F12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G12">
         <v>1.29</v>
@@ -3594,7 +3594,7 @@
         <v>2.26</v>
       </c>
       <c r="Q12">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R12">
         <v>1.49</v>
@@ -3606,7 +3606,7 @@
         <v>2.28</v>
       </c>
       <c r="U12">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V12">
         <v>1.05</v>
@@ -3627,7 +3627,7 @@
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC12">
         <v>16</v>
@@ -3639,7 +3639,7 @@
         <v>380</v>
       </c>
       <c r="AF12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>14</v>
@@ -3654,7 +3654,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AK12">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AL12">
         <v>55</v>
@@ -3672,13 +3672,13 @@
         <v>19</v>
       </c>
       <c r="AQ12">
-        <v>32</v>
+        <v>4.6</v>
       </c>
       <c r="AR12">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AS12">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT12">
         <v>7.2</v>
@@ -3687,10 +3687,10 @@
         <v>12.5</v>
       </c>
       <c r="AV12">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="AW12">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AX12">
         <v>3.85</v>
@@ -3699,10 +3699,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ12">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BA12">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BB12">
         <v>7.8</v>
@@ -3711,16 +3711,16 @@
         <v>12.5</v>
       </c>
       <c r="BD12">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE12">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BF12">
         <v>4.1</v>
       </c>
       <c r="BG12">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH12">
         <v>4.4</v>
@@ -3803,10 +3803,10 @@
         <v>153</v>
       </c>
       <c r="F13">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G13">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H13">
         <v>2.8</v>
@@ -3854,7 +3854,7 @@
         <v>1.27</v>
       </c>
       <c r="W13">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4057,7 +4057,7 @@
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4081,7 +4081,7 @@
         <v>1.22</v>
       </c>
       <c r="R14">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="S14">
         <v>1.22</v>
@@ -4287,7 +4287,7 @@
         <v>155</v>
       </c>
       <c r="F15">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G15">
         <v>990</v>
@@ -4296,10 +4296,10 @@
         <v>1.6</v>
       </c>
       <c r="I15">
-        <v>21</v>
+        <v>2.82</v>
       </c>
       <c r="J15">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4335,118 +4335,118 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W15">
         <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
         <v>1.55</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4529,40 +4529,40 @@
         <v>156</v>
       </c>
       <c r="F16">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G16">
         <v>3.85</v>
       </c>
       <c r="H16">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="I16">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J16">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="K16">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O16">
         <v>1.56</v>
       </c>
       <c r="P16">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="Q16">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="R16">
         <v>1.15</v>
@@ -4574,13 +4574,13 @@
         <v>1.11</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V16">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W16">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4598,7 +4598,7 @@
         <v>1000</v>
       </c>
       <c r="AC16">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD16">
         <v>1000</v>
@@ -4637,58 +4637,58 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AY16">
-        <v>12</v>
+        <v>1.36</v>
       </c>
       <c r="AZ16">
         <v>16.5</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="BE16">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4771,7 +4771,7 @@
         <v>157</v>
       </c>
       <c r="F17">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G17">
         <v>2.06</v>
@@ -4780,7 +4780,7 @@
         <v>3.35</v>
       </c>
       <c r="I17">
-        <v>990</v>
+        <v>26</v>
       </c>
       <c r="J17">
         <v>3.15</v>
@@ -4795,7 +4795,7 @@
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>2.08</v>
+        <v>1.1</v>
       </c>
       <c r="O17">
         <v>1.26</v>
@@ -4822,7 +4822,7 @@
         <v>1.13</v>
       </c>
       <c r="W17">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4837,7 +4837,7 @@
         <v>1000</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC17">
         <v>950</v>
@@ -4849,7 +4849,7 @@
         <v>1000</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG17">
         <v>950</v>
@@ -4864,25 +4864,25 @@
         <v>900</v>
       </c>
       <c r="AK17">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM17">
         <v>1000</v>
       </c>
       <c r="AN17">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO17">
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AQ17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AR17">
         <v>1.1</v>
@@ -4891,13 +4891,13 @@
         <v>1.1</v>
       </c>
       <c r="AT17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AU17">
         <v>1.07</v>
       </c>
       <c r="AV17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AW17">
         <v>1.1</v>
@@ -4906,16 +4906,16 @@
         <v>1.1</v>
       </c>
       <c r="AY17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AZ17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BA17">
         <v>1.1</v>
       </c>
       <c r="BB17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BC17">
         <v>1.08</v>
@@ -4927,7 +4927,7 @@
         <v>1.1</v>
       </c>
       <c r="BF17">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG17">
         <v>1.55</v>
@@ -5013,16 +5013,16 @@
         <v>158</v>
       </c>
       <c r="F18">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G18">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H18">
         <v>11</v>
       </c>
       <c r="I18">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J18">
         <v>5.4</v>
@@ -5043,7 +5043,7 @@
         <v>1.27</v>
       </c>
       <c r="P18">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q18">
         <v>1.82</v>
@@ -5076,13 +5076,13 @@
         <v>110</v>
       </c>
       <c r="AA18">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="AB18">
         <v>8</v>
       </c>
       <c r="AC18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD18">
         <v>40</v>
@@ -5091,22 +5091,22 @@
         <v>200</v>
       </c>
       <c r="AF18">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG18">
         <v>10.5</v>
       </c>
       <c r="AH18">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI18">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ18">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AK18">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL18">
         <v>46</v>
@@ -5118,13 +5118,13 @@
         <v>5.9</v>
       </c>
       <c r="AO18">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AP18">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ18">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR18">
         <v>85</v>
@@ -5157,7 +5157,7 @@
         <v>80</v>
       </c>
       <c r="BB18">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC18">
         <v>14.5</v>
@@ -5178,7 +5178,7 @@
         <v>3.65</v>
       </c>
       <c r="BI18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BJ18">
         <v>13.5</v>
@@ -5205,7 +5205,7 @@
         <v>7.2</v>
       </c>
       <c r="BR18">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS18">
         <v>11</v>
@@ -5255,7 +5255,7 @@
         <v>159</v>
       </c>
       <c r="F19">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="G19">
         <v>3.25</v>
@@ -5264,13 +5264,13 @@
         <v>2.1</v>
       </c>
       <c r="I19">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="J19">
         <v>3.9</v>
       </c>
       <c r="K19">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5285,7 +5285,7 @@
         <v>1.06</v>
       </c>
       <c r="P19">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="Q19">
         <v>1.06</v>
@@ -5303,7 +5303,7 @@
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="W19">
         <v>1.44</v>
@@ -5497,7 +5497,7 @@
         <v>160</v>
       </c>
       <c r="F20">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G20">
         <v>2.12</v>
@@ -5506,7 +5506,7 @@
         <v>4.2</v>
       </c>
       <c r="I20">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J20">
         <v>3.35</v>
@@ -5533,7 +5533,7 @@
         <v>2.14</v>
       </c>
       <c r="R20">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S20">
         <v>4</v>
@@ -5545,7 +5545,7 @@
         <v>1.96</v>
       </c>
       <c r="V20">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W20">
         <v>1.89</v>
@@ -5635,7 +5635,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ20">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BA20">
         <v>9.800000000000001</v>
@@ -5739,19 +5739,19 @@
         <v>161</v>
       </c>
       <c r="F21">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G21">
         <v>2.46</v>
       </c>
       <c r="H21">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I21">
         <v>3.7</v>
       </c>
       <c r="J21">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K21">
         <v>3.25</v>
@@ -5760,31 +5760,31 @@
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N21">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O21">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="P21">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="Q21">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="R21">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S21">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="U21">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="V21">
         <v>1.37</v>
@@ -5796,7 +5796,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Z21">
         <v>25</v>
@@ -5805,7 +5805,7 @@
         <v>85</v>
       </c>
       <c r="AB21">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -5814,7 +5814,7 @@
         <v>17</v>
       </c>
       <c r="AE21">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF21">
         <v>14</v>
@@ -5823,31 +5823,31 @@
         <v>12.5</v>
       </c>
       <c r="AH21">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI21">
         <v>200</v>
       </c>
       <c r="AJ21">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK21">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AL21">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM21">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN21">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO21">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP21">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ21">
         <v>8.800000000000001</v>
@@ -5856,10 +5856,10 @@
         <v>20</v>
       </c>
       <c r="AS21">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="AT21">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU21">
         <v>6.8</v>
@@ -5877,7 +5877,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA21">
         <v>60</v>
@@ -5886,16 +5886,16 @@
         <v>29</v>
       </c>
       <c r="BC21">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BD21">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF21">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BG21">
         <v>65</v>
@@ -5981,25 +5981,25 @@
         <v>162</v>
       </c>
       <c r="F22">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G22">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H22">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="I22">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="J22">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K22">
         <v>3.55</v>
       </c>
       <c r="L22">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M22">
         <v>1.11</v>
@@ -6014,16 +6014,16 @@
         <v>1.6</v>
       </c>
       <c r="Q22">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="R22">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S22">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T22">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U22">
         <v>1.73</v>
@@ -6125,19 +6125,19 @@
         <v>28</v>
       </c>
       <c r="BB22">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG22">
         <v>17</v>
@@ -6146,37 +6146,37 @@
         <v>3.1</v>
       </c>
       <c r="BI22">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ22">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BK22">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN22">
+        <v>9</v>
+      </c>
+      <c r="BO22">
+        <v>7</v>
+      </c>
+      <c r="BP22">
+        <v>65</v>
+      </c>
+      <c r="BQ22">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BO22">
-        <v>4.5</v>
-      </c>
-      <c r="BP22">
-        <v>70</v>
-      </c>
-      <c r="BQ22">
-        <v>8</v>
       </c>
       <c r="BR22">
         <v>90</v>
       </c>
       <c r="BS22">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT22">
         <v>4.2</v>
@@ -6185,22 +6185,22 @@
         <v>3.7</v>
       </c>
       <c r="BV22">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW22">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX22">
         <v>44</v>
       </c>
       <c r="BY22">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ22">
         <v>38</v>
       </c>
       <c r="CA22">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="CB22" t="s">
         <v>177</v>
@@ -6223,25 +6223,25 @@
         <v>163</v>
       </c>
       <c r="F23">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="G23">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="H23">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I23">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K23">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L23">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M23">
         <v>1.09</v>
@@ -6250,13 +6250,13 @@
         <v>3.2</v>
       </c>
       <c r="O23">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P23">
         <v>1.76</v>
       </c>
       <c r="Q23">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R23">
         <v>1.27</v>
@@ -6265,16 +6265,16 @@
         <v>4.1</v>
       </c>
       <c r="T23">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U23">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V23">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W23">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="X23">
         <v>13</v>
@@ -6286,19 +6286,19 @@
         <v>65</v>
       </c>
       <c r="AA23">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB23">
         <v>7</v>
       </c>
       <c r="AC23">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD23">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE23">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF23">
         <v>9.4</v>
@@ -6310,7 +6310,7 @@
         <v>26</v>
       </c>
       <c r="AI23">
-        <v>450</v>
+        <v>130</v>
       </c>
       <c r="AJ23">
         <v>17.5</v>
@@ -6334,13 +6334,13 @@
         <v>10</v>
       </c>
       <c r="AQ23">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AR23">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AS23">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT23">
         <v>6</v>
@@ -6349,13 +6349,13 @@
         <v>7.6</v>
       </c>
       <c r="AV23">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AW23">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX23">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY23">
         <v>9</v>
@@ -6364,7 +6364,7 @@
         <v>21</v>
       </c>
       <c r="BA23">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB23">
         <v>14</v>
@@ -6373,76 +6373,76 @@
         <v>17.5</v>
       </c>
       <c r="BD23">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE23">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF23">
         <v>10.5</v>
       </c>
       <c r="BG23">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH23">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI23">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ23">
         <v>12</v>
       </c>
       <c r="BK23">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BN23">
         <v>4</v>
       </c>
       <c r="BO23">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP23">
         <v>12</v>
       </c>
       <c r="BQ23">
+        <v>5.1</v>
+      </c>
+      <c r="BR23">
+        <v>32</v>
+      </c>
+      <c r="BS23">
+        <v>7</v>
+      </c>
+      <c r="BT23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU23">
         <v>4.7</v>
       </c>
-      <c r="BR23">
-        <v>34</v>
-      </c>
-      <c r="BS23">
-        <v>6.4</v>
-      </c>
-      <c r="BT23">
-        <v>10.5</v>
-      </c>
-      <c r="BU23">
-        <v>4.5</v>
-      </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX23">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="BY23">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BZ23">
         <v>27</v>
       </c>
       <c r="CA23">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="CB23" t="s">
         <v>177</v>
@@ -6468,7 +6468,7 @@
         <v>2.82</v>
       </c>
       <c r="G24">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H24">
         <v>2.82</v>
@@ -6495,7 +6495,7 @@
         <v>1.43</v>
       </c>
       <c r="P24">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q24">
         <v>2.28</v>
@@ -6600,7 +6600,7 @@
         <v>9</v>
       </c>
       <c r="AY24">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ24">
         <v>10.5</v>
@@ -6710,7 +6710,7 @@
         <v>2.44</v>
       </c>
       <c r="G25">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H25">
         <v>2.58</v>
@@ -6755,10 +6755,10 @@
         <v>2.48</v>
       </c>
       <c r="V25">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X25">
         <v>29</v>
@@ -6830,7 +6830,7 @@
         <v>4</v>
       </c>
       <c r="AU25">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV25">
         <v>9.6</v>
@@ -6839,10 +6839,10 @@
         <v>19</v>
       </c>
       <c r="AX25">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AY25">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25">
         <v>11</v>
@@ -6860,7 +6860,7 @@
         <v>21</v>
       </c>
       <c r="BE25">
-        <v>4.9</v>
+        <v>40</v>
       </c>
       <c r="BF25">
         <v>10.5</v>
@@ -6958,7 +6958,7 @@
         <v>4.7</v>
       </c>
       <c r="I26">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J26">
         <v>4.2</v>
@@ -6997,7 +6997,7 @@
         <v>2.08</v>
       </c>
       <c r="V26">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W26">
         <v>2.28</v>
@@ -7069,7 +7069,7 @@
         <v>4.6</v>
       </c>
       <c r="AT26">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU26">
         <v>8.800000000000001</v>
@@ -7090,13 +7090,13 @@
         <v>14</v>
       </c>
       <c r="BA26">
-        <v>4.5</v>
+        <v>42</v>
       </c>
       <c r="BB26">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC26">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD26">
         <v>4.2</v>
@@ -7191,31 +7191,31 @@
         <v>167</v>
       </c>
       <c r="F27">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="G27">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H27">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I27">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="J27">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="K27">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N27">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O27">
         <v>1.42</v>
@@ -7224,25 +7224,25 @@
         <v>1.68</v>
       </c>
       <c r="Q27">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R27">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="S27">
-        <v>2.18</v>
+        <v>3.35</v>
       </c>
       <c r="T27">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U27">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V27">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W27">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7442,7 +7442,7 @@
         <v>5.1</v>
       </c>
       <c r="I28">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J28">
         <v>4.2</v>
@@ -7451,34 +7451,34 @@
         <v>4.4</v>
       </c>
       <c r="L28">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M28">
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O28">
         <v>1.22</v>
       </c>
       <c r="P28">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q28">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R28">
         <v>1.58</v>
       </c>
       <c r="S28">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T28">
         <v>1.69</v>
       </c>
       <c r="U28">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V28">
         <v>1.23</v>
@@ -7490,7 +7490,7 @@
         <v>22</v>
       </c>
       <c r="Y28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z28">
         <v>44</v>
@@ -7523,7 +7523,7 @@
         <v>55</v>
       </c>
       <c r="AJ28">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK28">
         <v>16.5</v>
@@ -7532,16 +7532,16 @@
         <v>28</v>
       </c>
       <c r="AM28">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN28">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO28">
         <v>50</v>
       </c>
       <c r="AP28">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ28">
         <v>20</v>
@@ -7556,7 +7556,7 @@
         <v>10.5</v>
       </c>
       <c r="AU28">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV28">
         <v>18</v>
@@ -7568,7 +7568,7 @@
         <v>11</v>
       </c>
       <c r="AY28">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28">
         <v>15.5</v>
@@ -7586,13 +7586,13 @@
         <v>24</v>
       </c>
       <c r="BE28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF28">
         <v>7.2</v>
       </c>
       <c r="BG28">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BH28">
         <v>4.5</v>
@@ -7601,7 +7601,7 @@
         <v>3.45</v>
       </c>
       <c r="BJ28">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK28">
         <v>4.9</v>
@@ -7610,7 +7610,7 @@
         <v>95</v>
       </c>
       <c r="BM28">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN28">
         <v>4.9</v>
@@ -7622,13 +7622,13 @@
         <v>11</v>
       </c>
       <c r="BQ28">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR28">
         <v>22</v>
       </c>
       <c r="BS28">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT28">
         <v>9.199999999999999</v>
@@ -7640,13 +7640,13 @@
         <v>38</v>
       </c>
       <c r="BW28">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX28">
         <v>42</v>
       </c>
       <c r="BY28">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ28">
         <v>15.5</v>
@@ -7693,7 +7693,7 @@
         <v>4.3</v>
       </c>
       <c r="L29">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M29">
         <v>1.02</v>
@@ -7714,7 +7714,7 @@
         <v>1.91</v>
       </c>
       <c r="S29">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T29">
         <v>1.41</v>
@@ -7783,13 +7783,13 @@
         <v>9.4</v>
       </c>
       <c r="AP29">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AQ29">
         <v>18.5</v>
       </c>
       <c r="AR29">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS29">
         <v>32</v>
@@ -7819,7 +7819,7 @@
         <v>21</v>
       </c>
       <c r="BB29">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC29">
         <v>23</v>
@@ -7837,64 +7837,64 @@
         <v>8.4</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI29">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BJ29">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK29">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO29">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ29">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS29">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU29">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW29">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA29">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB29" t="s">
         <v>177</v>
@@ -7917,13 +7917,13 @@
         <v>170</v>
       </c>
       <c r="F30">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G30">
         <v>2.28</v>
       </c>
       <c r="H30">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I30">
         <v>3.45</v>
@@ -7935,25 +7935,25 @@
         <v>3.85</v>
       </c>
       <c r="L30">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M30">
         <v>1.06</v>
       </c>
       <c r="N30">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O30">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P30">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q30">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R30">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S30">
         <v>3.1</v>
@@ -7965,13 +7965,13 @@
         <v>2.36</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W30">
         <v>1.78</v>
       </c>
       <c r="X30">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y30">
         <v>15</v>
@@ -7986,7 +7986,7 @@
         <v>11.5</v>
       </c>
       <c r="AC30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD30">
         <v>14</v>
@@ -8004,7 +8004,7 @@
         <v>16.5</v>
       </c>
       <c r="AI30">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AJ30">
         <v>32</v>
@@ -8019,7 +8019,7 @@
         <v>1000</v>
       </c>
       <c r="AN30">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO30">
         <v>55</v>
@@ -8040,7 +8040,7 @@
         <v>10</v>
       </c>
       <c r="AU30">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV30">
         <v>12.5</v>
@@ -8061,7 +8061,7 @@
         <v>34</v>
       </c>
       <c r="BB30">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC30">
         <v>19.5</v>
@@ -8070,7 +8070,7 @@
         <v>21</v>
       </c>
       <c r="BE30">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BF30">
         <v>14</v>
@@ -8159,22 +8159,22 @@
         <v>171</v>
       </c>
       <c r="F31">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G31">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H31">
         <v>11</v>
       </c>
       <c r="I31">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J31">
         <v>4.7</v>
       </c>
       <c r="K31">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8195,25 +8195,25 @@
         <v>1.96</v>
       </c>
       <c r="R31">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S31">
         <v>3.5</v>
       </c>
       <c r="T31">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U31">
         <v>1.66</v>
       </c>
       <c r="V31">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W31">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="X31">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y31">
         <v>32</v>
@@ -8261,7 +8261,7 @@
         <v>270</v>
       </c>
       <c r="AN31">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO31">
         <v>470</v>
@@ -8270,13 +8270,13 @@
         <v>13</v>
       </c>
       <c r="AQ31">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR31">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AS31">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT31">
         <v>6</v>
@@ -8285,10 +8285,10 @@
         <v>9.6</v>
       </c>
       <c r="AV31">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="AW31">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX31">
         <v>6.4</v>
@@ -8300,7 +8300,7 @@
         <v>27</v>
       </c>
       <c r="BA31">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB31">
         <v>9.6</v>
@@ -8312,13 +8312,13 @@
         <v>40</v>
       </c>
       <c r="BE31">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF31">
         <v>6.4</v>
       </c>
       <c r="BG31">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8401,7 +8401,7 @@
         <v>172</v>
       </c>
       <c r="F32">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G32">
         <v>2.44</v>
@@ -8431,7 +8431,7 @@
         <v>1.26</v>
       </c>
       <c r="P32">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q32">
         <v>1.79</v>
@@ -8443,19 +8443,19 @@
         <v>3</v>
       </c>
       <c r="T32">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U32">
         <v>2.4</v>
       </c>
       <c r="V32">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W32">
         <v>1.69</v>
       </c>
       <c r="X32">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y32">
         <v>15</v>
@@ -8464,7 +8464,7 @@
         <v>23</v>
       </c>
       <c r="AA32">
-        <v>220</v>
+        <v>50</v>
       </c>
       <c r="AB32">
         <v>12.5</v>
@@ -8497,7 +8497,7 @@
         <v>24</v>
       </c>
       <c r="AL32">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM32">
         <v>1000</v>
@@ -8542,7 +8542,7 @@
         <v>14</v>
       </c>
       <c r="BA32">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BB32">
         <v>20</v>
@@ -8554,19 +8554,19 @@
         <v>27</v>
       </c>
       <c r="BE32">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BF32">
         <v>14</v>
       </c>
       <c r="BG32">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BH32">
         <v>4.3</v>
       </c>
       <c r="BI32">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ32">
         <v>9</v>
@@ -8578,7 +8578,7 @@
         <v>110</v>
       </c>
       <c r="BM32">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN32">
         <v>5.5</v>
@@ -8587,7 +8587,7 @@
         <v>4.9</v>
       </c>
       <c r="BP32">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ32">
         <v>6.6</v>
@@ -8614,7 +8614,7 @@
         <v>32</v>
       </c>
       <c r="BY32">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ32">
         <v>21</v>
@@ -8667,25 +8667,25 @@
         <v>1.13</v>
       </c>
       <c r="N33">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O33">
         <v>1.59</v>
       </c>
       <c r="P33">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q33">
         <v>2.74</v>
       </c>
       <c r="R33">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S33">
         <v>6</v>
       </c>
       <c r="T33">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U33">
         <v>1.68</v>
@@ -8694,7 +8694,7 @@
         <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X33">
         <v>8.4</v>
@@ -8754,7 +8754,7 @@
         <v>7.2</v>
       </c>
       <c r="AQ33">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR33">
         <v>21</v>
@@ -8885,22 +8885,22 @@
         <v>174</v>
       </c>
       <c r="F34">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G34">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="H34">
+        <v>2.58</v>
+      </c>
+      <c r="I34">
         <v>2.62</v>
-      </c>
-      <c r="I34">
-        <v>2.68</v>
       </c>
       <c r="J34">
         <v>4.3</v>
       </c>
       <c r="K34">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L34">
         <v>1.23</v>
@@ -8909,52 +8909,52 @@
         <v>1.02</v>
       </c>
       <c r="N34">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="O34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P34">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q34">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="R34">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="S34">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T34">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="U34">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V34">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W34">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X34">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y34">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z34">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA34">
         <v>42</v>
       </c>
       <c r="AB34">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC34">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD34">
         <v>13</v>
@@ -8963,37 +8963,37 @@
         <v>23</v>
       </c>
       <c r="AF34">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG34">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH34">
         <v>14</v>
       </c>
       <c r="AI34">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AJ34">
+        <v>44</v>
+      </c>
+      <c r="AK34">
+        <v>23</v>
+      </c>
+      <c r="AL34">
+        <v>24</v>
+      </c>
+      <c r="AM34">
         <v>40</v>
-      </c>
-      <c r="AK34">
-        <v>22</v>
-      </c>
-      <c r="AL34">
-        <v>25</v>
-      </c>
-      <c r="AM34">
-        <v>42</v>
       </c>
       <c r="AN34">
         <v>11</v>
       </c>
       <c r="AO34">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP34">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AQ34">
         <v>19</v>
@@ -9005,10 +9005,10 @@
         <v>38</v>
       </c>
       <c r="AT34">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AU34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV34">
         <v>12</v>
@@ -9020,16 +9020,16 @@
         <v>21</v>
       </c>
       <c r="AY34">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ34">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA34">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB34">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BC34">
         <v>20</v>
@@ -9038,22 +9038,22 @@
         <v>22</v>
       </c>
       <c r="BE34">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BF34">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG34">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH34">
         <v>6.2</v>
       </c>
       <c r="BI34">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ34">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK34">
         <v>6</v>
@@ -9074,13 +9074,13 @@
         <v>19</v>
       </c>
       <c r="BQ34">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BR34">
         <v>25</v>
       </c>
       <c r="BS34">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BT34">
         <v>7.8</v>
@@ -9092,10 +9092,10 @@
         <v>21</v>
       </c>
       <c r="BW34">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BX34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY34">
         <v>4</v>
@@ -9127,7 +9127,7 @@
         <v>175</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G35">
         <v>3.1</v>
@@ -9136,7 +9136,7 @@
         <v>2.32</v>
       </c>
       <c r="I35">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J35">
         <v>3.95</v>
@@ -9151,13 +9151,13 @@
         <v>1.04</v>
       </c>
       <c r="N35">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O35">
         <v>1.2</v>
       </c>
       <c r="P35">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q35">
         <v>1.6</v>
@@ -9166,7 +9166,7 @@
         <v>1.63</v>
       </c>
       <c r="S35">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T35">
         <v>1.55</v>
@@ -9175,7 +9175,7 @@
         <v>2.64</v>
       </c>
       <c r="V35">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W35">
         <v>1.47</v>
@@ -9217,7 +9217,7 @@
         <v>28</v>
       </c>
       <c r="AJ35">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="AK35">
         <v>29</v>
@@ -9226,7 +9226,7 @@
         <v>34</v>
       </c>
       <c r="AM35">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AN35">
         <v>18.5</v>
@@ -9241,7 +9241,7 @@
         <v>14</v>
       </c>
       <c r="AR35">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS35">
         <v>28</v>
@@ -9259,7 +9259,7 @@
         <v>19</v>
       </c>
       <c r="AX35">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY35">
         <v>12</v>
@@ -9283,10 +9283,10 @@
         <v>46</v>
       </c>
       <c r="BF35">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG35">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH35">
         <v>4.6</v>
@@ -9393,7 +9393,7 @@
         <v>1.03</v>
       </c>
       <c r="N36">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O36">
         <v>1.16</v>
@@ -9414,7 +9414,7 @@
         <v>1.5</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V36">
         <v>1.36</v>
@@ -9447,7 +9447,7 @@
         <v>36</v>
       </c>
       <c r="AF36">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG36">
         <v>11</v>
@@ -9459,7 +9459,7 @@
         <v>34</v>
       </c>
       <c r="AJ36">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK36">
         <v>17.5</v>
@@ -9477,7 +9477,7 @@
         <v>22</v>
       </c>
       <c r="AP36">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ36">
         <v>20</v>
@@ -9513,7 +9513,7 @@
         <v>30</v>
       </c>
       <c r="BB36">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC36">
         <v>16</v>
@@ -9546,10 +9546,10 @@
         <v>80</v>
       </c>
       <c r="BM36">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BN36">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO36">
         <v>4.8</v>
@@ -9564,7 +9564,7 @@
         <v>24</v>
       </c>
       <c r="BS36">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BT36">
         <v>7.6</v>
@@ -9576,13 +9576,13 @@
         <v>29</v>
       </c>
       <c r="BW36">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX36">
         <v>34</v>
       </c>
       <c r="BY36">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ36">
         <v>13</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -529,7 +529,7 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-19 02:15:14</t>
+    <t>2026-08-19 04:24:07</t>
   </si>
 </sst>
 </file>
@@ -1129,16 +1129,16 @@
         <v>2.24</v>
       </c>
       <c r="H2">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I2">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L2">
         <v>1.55</v>
@@ -1147,7 +1147,7 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O2">
         <v>1.52</v>
@@ -1156,37 +1156,37 @@
         <v>1.52</v>
       </c>
       <c r="Q2">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
         <v>1.19</v>
       </c>
       <c r="S2">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X2">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z2">
         <v>38</v>
       </c>
       <c r="AA2">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB2">
         <v>7</v>
@@ -1195,94 +1195,94 @@
         <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE2">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ2">
+        <v>48</v>
+      </c>
+      <c r="AK2">
         <v>32</v>
       </c>
-      <c r="AK2">
-        <v>34</v>
-      </c>
       <c r="AL2">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM2">
         <v>230</v>
       </c>
       <c r="AN2">
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="AO2">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="AP2">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AR2">
+        <v>7.2</v>
+      </c>
+      <c r="AS2">
+        <v>8.4</v>
+      </c>
+      <c r="AT2">
+        <v>3.95</v>
+      </c>
+      <c r="AU2">
+        <v>4.1</v>
+      </c>
+      <c r="AV2">
+        <v>6.2</v>
+      </c>
+      <c r="AW2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX2">
         <v>5.2</v>
       </c>
-      <c r="AS2">
-        <v>5.7</v>
-      </c>
-      <c r="AT2">
-        <v>3.2</v>
-      </c>
-      <c r="AU2">
-        <v>3.4</v>
-      </c>
-      <c r="AV2">
-        <v>4.7</v>
-      </c>
-      <c r="AW2">
-        <v>5.6</v>
-      </c>
-      <c r="AX2">
-        <v>4.1</v>
-      </c>
       <c r="AY2">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AZ2">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BA2">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BB2">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BC2">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BD2">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BE2">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF2">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BG2">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
         <v>2.82</v>
@@ -1365,22 +1365,22 @@
         <v>140</v>
       </c>
       <c r="F3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H3">
         <v>6.6</v>
       </c>
       <c r="I3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L3">
         <v>1.26</v>
@@ -1395,28 +1395,28 @@
         <v>1.16</v>
       </c>
       <c r="P3">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R3">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
         <v>1.16</v>
       </c>
       <c r="W3">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X3">
         <v>30</v>
@@ -1425,52 +1425,52 @@
         <v>34</v>
       </c>
       <c r="Z3">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AA3">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC3">
         <v>12.5</v>
       </c>
       <c r="AD3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE3">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
         <v>14.5</v>
       </c>
       <c r="AK3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN3">
         <v>5.1</v>
       </c>
       <c r="AO3">
-        <v>980</v>
+        <v>70</v>
       </c>
       <c r="AP3">
         <v>27</v>
@@ -1482,7 +1482,7 @@
         <v>50</v>
       </c>
       <c r="AS3">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="AT3">
         <v>12</v>
@@ -1494,7 +1494,7 @@
         <v>23</v>
       </c>
       <c r="AW3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1515,7 +1515,7 @@
         <v>12.5</v>
       </c>
       <c r="BD3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE3">
         <v>65</v>
@@ -1524,10 +1524,10 @@
         <v>4.9</v>
       </c>
       <c r="BG3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI3">
         <v>4.3</v>
@@ -1536,13 +1536,13 @@
         <v>10</v>
       </c>
       <c r="BK3">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN3">
         <v>4.5</v>
@@ -1551,7 +1551,7 @@
         <v>4.1</v>
       </c>
       <c r="BP3">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BQ3">
         <v>5.4</v>
@@ -1560,28 +1560,28 @@
         <v>19</v>
       </c>
       <c r="BS3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU3">
         <v>6.2</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW3">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="BZ3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CA3">
         <v>6.2</v>
@@ -1607,226 +1607,226 @@
         <v>141</v>
       </c>
       <c r="F4">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="G4">
-        <v>990</v>
+        <v>2.34</v>
       </c>
       <c r="H4">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="I4">
-        <v>990</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
-        <v>1.18</v>
+        <v>2.98</v>
       </c>
       <c r="K4">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="O4">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="P4">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="Q4">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="S4">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V4">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="X4">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AA4">
         <v>500</v>
       </c>
       <c r="AB4">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="AE4">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AF4">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="AG4">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI4">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AJ4">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AK4">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AL4">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM4">
         <v>500</v>
       </c>
       <c r="AN4">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AO4">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BF4">
-        <v>1.55</v>
+        <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>1.55</v>
+        <v>36</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="CB4" t="s">
         <v>171</v>
@@ -1849,226 +1849,226 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="H5">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>3.3</v>
+      </c>
+      <c r="K5">
+        <v>3.85</v>
+      </c>
+      <c r="L5">
+        <v>1.5</v>
+      </c>
+      <c r="M5">
+        <v>1.1</v>
+      </c>
+      <c r="N5">
+        <v>2.74</v>
+      </c>
+      <c r="O5">
+        <v>1.45</v>
+      </c>
+      <c r="P5">
+        <v>1.58</v>
+      </c>
+      <c r="Q5">
+        <v>2.34</v>
+      </c>
+      <c r="R5">
+        <v>1.21</v>
+      </c>
+      <c r="S5">
+        <v>4.6</v>
+      </c>
+      <c r="T5">
+        <v>2.18</v>
+      </c>
+      <c r="U5">
+        <v>1.69</v>
+      </c>
+      <c r="V5">
+        <v>1.17</v>
+      </c>
+      <c r="W5">
+        <v>2.14</v>
+      </c>
+      <c r="X5">
+        <v>10.5</v>
+      </c>
+      <c r="Y5">
+        <v>16.5</v>
+      </c>
+      <c r="Z5">
+        <v>55</v>
+      </c>
+      <c r="AA5">
+        <v>900</v>
+      </c>
+      <c r="AB5">
+        <v>6.6</v>
+      </c>
+      <c r="AC5">
+        <v>8.6</v>
+      </c>
+      <c r="AD5">
         <v>27</v>
-      </c>
-      <c r="J5">
-        <v>3.25</v>
-      </c>
-      <c r="K5">
-        <v>4.4</v>
-      </c>
-      <c r="L5">
-        <v>1.01</v>
-      </c>
-      <c r="M5">
-        <v>1.01</v>
-      </c>
-      <c r="N5">
-        <v>1.1</v>
-      </c>
-      <c r="O5">
-        <v>1.42</v>
-      </c>
-      <c r="P5">
-        <v>1.09</v>
-      </c>
-      <c r="Q5">
-        <v>1.45</v>
-      </c>
-      <c r="R5">
-        <v>1.07</v>
-      </c>
-      <c r="S5">
-        <v>1.51</v>
-      </c>
-      <c r="T5">
-        <v>1.11</v>
-      </c>
-      <c r="U5">
-        <v>1.11</v>
-      </c>
-      <c r="V5">
-        <v>1.13</v>
-      </c>
-      <c r="W5">
-        <v>2</v>
-      </c>
-      <c r="X5">
-        <v>950</v>
-      </c>
-      <c r="Y5">
-        <v>950</v>
-      </c>
-      <c r="Z5">
-        <v>500</v>
-      </c>
-      <c r="AA5">
-        <v>500</v>
-      </c>
-      <c r="AB5">
-        <v>970</v>
-      </c>
-      <c r="AC5">
-        <v>950</v>
-      </c>
-      <c r="AD5">
-        <v>950</v>
       </c>
       <c r="AE5">
         <v>500</v>
       </c>
       <c r="AF5">
-        <v>500</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI5">
         <v>500</v>
       </c>
       <c r="AJ5">
-        <v>900</v>
+        <v>20</v>
       </c>
       <c r="AK5">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AL5">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM5">
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>600</v>
+        <v>18.5</v>
       </c>
       <c r="AO5">
         <v>500</v>
       </c>
       <c r="AP5">
-        <v>1.23</v>
+        <v>4.8</v>
       </c>
       <c r="AQ5">
-        <v>1.22</v>
+        <v>5.8</v>
       </c>
       <c r="AR5">
-        <v>1.23</v>
+        <v>7.8</v>
       </c>
       <c r="AS5">
-        <v>1.23</v>
+        <v>8.6</v>
       </c>
       <c r="AT5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AU5">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV5">
-        <v>1.23</v>
+        <v>6.8</v>
       </c>
       <c r="AW5">
-        <v>1.23</v>
+        <v>8.4</v>
       </c>
       <c r="AX5">
         <v>4.9</v>
       </c>
       <c r="AY5">
-        <v>1.19</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5">
-        <v>1.21</v>
+        <v>6.8</v>
       </c>
       <c r="BA5">
-        <v>1.23</v>
+        <v>8.4</v>
       </c>
       <c r="BB5">
-        <v>1.22</v>
+        <v>7.6</v>
       </c>
       <c r="BC5">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="BD5">
-        <v>1.23</v>
+        <v>7.8</v>
       </c>
       <c r="BE5">
-        <v>1.23</v>
+        <v>8.6</v>
       </c>
       <c r="BF5">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BG5">
-        <v>1.55</v>
+        <v>8.6</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="CB5" t="s">
         <v>171</v>
@@ -2091,16 +2091,16 @@
         <v>143</v>
       </c>
       <c r="F6">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="H6">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="I6">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -2115,7 +2115,7 @@
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O6">
         <v>1.41</v>
@@ -2124,13 +2124,13 @@
         <v>1.09</v>
       </c>
       <c r="Q6">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="R6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2139,10 +2139,10 @@
         <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W6">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X6">
         <v>970</v>
@@ -2190,10 +2190,10 @@
         <v>500</v>
       </c>
       <c r="AM6">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
         <v>600</v>
@@ -2223,16 +2223,16 @@
         <v>1.32</v>
       </c>
       <c r="AX6">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AY6">
         <v>1.32</v>
       </c>
       <c r="AZ6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BA6">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BB6">
         <v>1.33</v>
@@ -2333,226 +2333,226 @@
         <v>144</v>
       </c>
       <c r="F7">
+        <v>1.49</v>
+      </c>
+      <c r="G7">
+        <v>1.61</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J7">
+        <v>3.7</v>
+      </c>
+      <c r="K7">
+        <v>4.7</v>
+      </c>
+      <c r="L7">
+        <v>1.42</v>
+      </c>
+      <c r="M7">
+        <v>1.07</v>
+      </c>
+      <c r="N7">
+        <v>3.3</v>
+      </c>
+      <c r="O7">
+        <v>1.34</v>
+      </c>
+      <c r="P7">
+        <v>1.74</v>
+      </c>
+      <c r="Q7">
+        <v>2.04</v>
+      </c>
+      <c r="R7">
         <v>1.26</v>
       </c>
-      <c r="G7">
-        <v>2.54</v>
-      </c>
-      <c r="H7">
-        <v>3.3</v>
-      </c>
-      <c r="I7">
-        <v>990</v>
-      </c>
-      <c r="J7">
-        <v>3.35</v>
-      </c>
-      <c r="K7">
-        <v>100</v>
-      </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.01</v>
-      </c>
-      <c r="N7">
-        <v>1.11</v>
-      </c>
-      <c r="O7">
-        <v>1.02</v>
-      </c>
-      <c r="P7">
-        <v>1.07</v>
-      </c>
-      <c r="Q7">
-        <v>1.35</v>
-      </c>
-      <c r="R7">
-        <v>1.08</v>
-      </c>
       <c r="S7">
-        <v>1.34</v>
+        <v>3.4</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U7">
         <v>1.78</v>
       </c>
       <c r="V7">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W7">
-        <v>1.65</v>
+        <v>2.62</v>
       </c>
       <c r="X7">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="Y7">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="Z7">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AA7">
         <v>700</v>
       </c>
       <c r="AB7">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="AC7">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AE7">
         <v>700</v>
       </c>
       <c r="AF7">
-        <v>500</v>
+        <v>9.4</v>
       </c>
       <c r="AG7">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AH7">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI7">
         <v>700</v>
       </c>
       <c r="AJ7">
-        <v>900</v>
+        <v>16.5</v>
       </c>
       <c r="AK7">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AL7">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM7">
         <v>700</v>
       </c>
       <c r="AN7">
-        <v>600</v>
+        <v>11</v>
       </c>
       <c r="AO7">
         <v>700</v>
       </c>
       <c r="AP7">
-        <v>1.17</v>
+        <v>4.1</v>
       </c>
       <c r="AQ7">
-        <v>1.17</v>
+        <v>4.6</v>
       </c>
       <c r="AR7">
-        <v>1.17</v>
+        <v>5.3</v>
       </c>
       <c r="AS7">
-        <v>1.18</v>
+        <v>5.6</v>
       </c>
       <c r="AT7">
-        <v>1.14</v>
+        <v>3.25</v>
       </c>
       <c r="AU7">
-        <v>1.15</v>
+        <v>3.65</v>
       </c>
       <c r="AV7">
-        <v>1.17</v>
+        <v>4.9</v>
       </c>
       <c r="AW7">
-        <v>1.18</v>
+        <v>5.5</v>
       </c>
       <c r="AX7">
-        <v>1.15</v>
+        <v>3.5</v>
       </c>
       <c r="AY7">
-        <v>1.14</v>
+        <v>3.85</v>
       </c>
       <c r="AZ7">
-        <v>1.17</v>
+        <v>4.8</v>
       </c>
       <c r="BA7">
-        <v>1.18</v>
+        <v>5.5</v>
       </c>
       <c r="BB7">
-        <v>1.16</v>
+        <v>4.2</v>
       </c>
       <c r="BC7">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="BD7">
-        <v>1.17</v>
+        <v>5.1</v>
       </c>
       <c r="BE7">
-        <v>1.18</v>
+        <v>5.5</v>
       </c>
       <c r="BF7">
-        <v>1.17</v>
+        <v>3.75</v>
       </c>
       <c r="BG7">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB7" t="s">
         <v>171</v>
@@ -2575,226 +2575,226 @@
         <v>145</v>
       </c>
       <c r="F8">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="G8">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="H8">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="I8">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J8">
         <v>3.35</v>
       </c>
       <c r="K8">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P8">
-        <v>1.09</v>
+        <v>1.79</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R8">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>3.55</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V8">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W8">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="X8">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>950</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z8">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AA8">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB8">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AC8">
+        <v>8.4</v>
+      </c>
+      <c r="AD8">
+        <v>11.5</v>
+      </c>
+      <c r="AE8">
+        <v>25</v>
+      </c>
+      <c r="AF8">
         <v>42</v>
       </c>
-      <c r="AD8">
-        <v>950</v>
-      </c>
-      <c r="AE8">
-        <v>500</v>
-      </c>
-      <c r="AF8">
-        <v>500</v>
-      </c>
       <c r="AG8">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="AH8">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AI8">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AJ8">
         <v>900</v>
       </c>
       <c r="AK8">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AL8">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="AO8">
-        <v>600</v>
+        <v>18.5</v>
       </c>
       <c r="AP8">
-        <v>1.31</v>
+        <v>5.5</v>
       </c>
       <c r="AQ8">
-        <v>1.27</v>
+        <v>4.5</v>
       </c>
       <c r="AR8">
-        <v>1.28</v>
+        <v>5.3</v>
       </c>
       <c r="AS8">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="AT8">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU8">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV8">
-        <v>1.26</v>
+        <v>5</v>
       </c>
       <c r="AW8">
-        <v>1.28</v>
+        <v>6.4</v>
       </c>
       <c r="AX8">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="AY8">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="AZ8">
-        <v>1.28</v>
+        <v>6</v>
       </c>
       <c r="BA8">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="BB8">
-        <v>1.31</v>
+        <v>8</v>
       </c>
       <c r="BC8">
-        <v>1.31</v>
+        <v>7.6</v>
       </c>
       <c r="BD8">
-        <v>1.31</v>
+        <v>7.8</v>
       </c>
       <c r="BE8">
-        <v>1.31</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BG8">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="CB8" t="s">
         <v>171</v>
@@ -2832,7 +2832,7 @@
         <v>6</v>
       </c>
       <c r="K9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L9">
         <v>1.31</v>
@@ -2850,7 +2850,7 @@
         <v>2.4</v>
       </c>
       <c r="Q9">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R9">
         <v>1.54</v>
@@ -2862,7 +2862,7 @@
         <v>2.28</v>
       </c>
       <c r="U9">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V9">
         <v>1.06</v>
@@ -2928,7 +2928,7 @@
         <v>19</v>
       </c>
       <c r="AQ9">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR9">
         <v>6</v>
@@ -2946,7 +2946,7 @@
         <v>5.7</v>
       </c>
       <c r="AW9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX9">
         <v>6.4</v>
@@ -2955,7 +2955,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ9">
-        <v>5.4</v>
+        <v>32</v>
       </c>
       <c r="BA9">
         <v>6</v>
@@ -2970,7 +2970,7 @@
         <v>5.6</v>
       </c>
       <c r="BE9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF9">
         <v>4.2</v>
@@ -2994,7 +2994,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN9">
         <v>3.7</v>
@@ -3059,22 +3059,22 @@
         <v>147</v>
       </c>
       <c r="F10">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="G10">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="H10">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I10">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="J10">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L10">
         <v>1.13</v>
@@ -3083,142 +3083,142 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="O10">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q10">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="V10">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3301,22 +3301,22 @@
         <v>148</v>
       </c>
       <c r="F11">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="G11">
-        <v>990</v>
+        <v>2.6</v>
       </c>
       <c r="H11">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="I11">
         <v>990</v>
       </c>
       <c r="J11">
-        <v>1.17</v>
+        <v>3.3</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3325,22 +3325,22 @@
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="O11">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="P11">
         <v>1.1</v>
       </c>
       <c r="Q11">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="R11">
         <v>1.07</v>
       </c>
       <c r="S11">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3349,115 +3349,115 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BG11">
         <v>1.55</v>
@@ -3543,226 +3543,226 @@
         <v>149</v>
       </c>
       <c r="F12">
-        <v>2.1</v>
+        <v>2.84</v>
       </c>
       <c r="G12">
-        <v>990</v>
+        <v>3.45</v>
       </c>
       <c r="H12">
-        <v>1.6</v>
+        <v>2.52</v>
       </c>
       <c r="I12">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="O12">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="P12">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="Q12">
-        <v>1.07</v>
+        <v>2.32</v>
       </c>
       <c r="R12">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="S12">
-        <v>1.48</v>
+        <v>4.3</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="V12">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="X12">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="Y12">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="Z12">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AA12">
-        <v>900</v>
+        <v>50</v>
       </c>
       <c r="AB12">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AC12">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="AD12">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AE12">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AF12">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AG12">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AH12">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI12">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AJ12">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AK12">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AL12">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AM12">
         <v>500</v>
       </c>
       <c r="AN12">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AO12">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF12">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BG12">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="CB12" t="s">
         <v>171</v>
@@ -3785,58 +3785,58 @@
         <v>150</v>
       </c>
       <c r="F13">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H13">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I13">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J13">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="K13">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L13">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M13">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N13">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="O13">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P13">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q13">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="R13">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T13">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U13">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="V13">
         <v>1.58</v>
       </c>
       <c r="W13">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -3872,7 +3872,7 @@
         <v>30</v>
       </c>
       <c r="AI13">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AJ13">
         <v>95</v>
@@ -3911,7 +3911,7 @@
         <v>6</v>
       </c>
       <c r="AV13">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW13">
         <v>27</v>
@@ -3932,13 +3932,13 @@
         <v>7</v>
       </c>
       <c r="BC13">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD13">
         <v>7</v>
       </c>
       <c r="BE13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF13">
         <v>7</v>
@@ -3947,64 +3947,64 @@
         <v>36</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB13" t="s">
         <v>171</v>
@@ -4027,226 +4027,226 @@
         <v>151</v>
       </c>
       <c r="F14">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="G14">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="H14">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>26</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="K14">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M14">
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="O14">
         <v>1.26</v>
       </c>
       <c r="P14">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="Q14">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="R14">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="S14">
-        <v>1.35</v>
+        <v>2.82</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U14">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="V14">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W14">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB14">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="AC14">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF14">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AG14">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ14">
-        <v>900</v>
+        <v>17</v>
       </c>
       <c r="AK14">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AL14">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14">
-        <v>500</v>
+        <v>9.4</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP14">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="AQ14">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="AR14">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="AS14">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="AT14">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="AU14">
-        <v>1.07</v>
+        <v>3.8</v>
       </c>
       <c r="AV14">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="AW14">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX14">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="AY14">
-        <v>1.07</v>
+        <v>3.85</v>
       </c>
       <c r="AZ14">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="BA14">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB14">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC14">
-        <v>1.08</v>
+        <v>4.5</v>
       </c>
       <c r="BD14">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="BE14">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="BF14">
-        <v>1.08</v>
+        <v>3.65</v>
       </c>
       <c r="BG14">
-        <v>1.55</v>
+        <v>5.7</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="CB14" t="s">
         <v>171</v>
@@ -4269,10 +4269,10 @@
         <v>152</v>
       </c>
       <c r="F15">
+        <v>1.36</v>
+      </c>
+      <c r="G15">
         <v>1.37</v>
-      </c>
-      <c r="G15">
-        <v>1.38</v>
       </c>
       <c r="H15">
         <v>11</v>
@@ -4281,67 +4281,67 @@
         <v>11.5</v>
       </c>
       <c r="J15">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K15">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L15">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M15">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O15">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P15">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q15">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="R15">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S15">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="T15">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="U15">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="V15">
         <v>1.09</v>
       </c>
       <c r="W15">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X15">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y15">
         <v>34</v>
       </c>
       <c r="Z15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA15">
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="AB15">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC15">
         <v>13</v>
       </c>
       <c r="AD15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE15">
         <v>190</v>
@@ -4353,31 +4353,31 @@
         <v>10.5</v>
       </c>
       <c r="AH15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI15">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ15">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AK15">
         <v>15</v>
       </c>
       <c r="AL15">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM15">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN15">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AO15">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AP15">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ15">
         <v>30</v>
@@ -4386,28 +4386,28 @@
         <v>90</v>
       </c>
       <c r="AS15">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AT15">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AW15">
         <v>85</v>
       </c>
       <c r="AX15">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY15">
         <v>10</v>
       </c>
       <c r="AZ15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA15">
         <v>95</v>
@@ -4422,7 +4422,7 @@
         <v>38</v>
       </c>
       <c r="BE15">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="BF15">
         <v>5.2</v>
@@ -4431,37 +4431,37 @@
         <v>110</v>
       </c>
       <c r="BH15">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI15">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BJ15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BL15">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BM15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BN15">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BO15">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BP15">
         <v>8</v>
       </c>
       <c r="BQ15">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS15">
         <v>21</v>
@@ -4473,22 +4473,22 @@
         <v>12</v>
       </c>
       <c r="BV15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BW15">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="BX15">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BY15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BZ15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CA15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CB15" t="s">
         <v>171</v>
@@ -4517,16 +4517,16 @@
         <v>2.86</v>
       </c>
       <c r="H16">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="I16">
         <v>2.52</v>
       </c>
       <c r="J16">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="K16">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L16">
         <v>1.14</v>
@@ -4541,7 +4541,7 @@
         <v>1.07</v>
       </c>
       <c r="P16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q16">
         <v>1.24</v>
@@ -4565,19 +4565,19 @@
         <v>1.53</v>
       </c>
       <c r="X16">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="Y16">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z16">
+        <v>32</v>
+      </c>
+      <c r="AA16">
+        <v>42</v>
+      </c>
+      <c r="AB16">
         <v>36</v>
-      </c>
-      <c r="AA16">
-        <v>46</v>
-      </c>
-      <c r="AB16">
-        <v>40</v>
       </c>
       <c r="AC16">
         <v>16.5</v>
@@ -4586,10 +4586,10 @@
         <v>16</v>
       </c>
       <c r="AE16">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF16">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AG16">
         <v>18.5</v>
@@ -4598,7 +4598,7 @@
         <v>15</v>
       </c>
       <c r="AI16">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AJ16">
         <v>55</v>
@@ -4613,124 +4613,124 @@
         <v>36</v>
       </c>
       <c r="AN16">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO16">
+        <v>7.2</v>
+      </c>
+      <c r="AP16">
+        <v>7</v>
+      </c>
+      <c r="AQ16">
+        <v>6.4</v>
+      </c>
+      <c r="AR16">
+        <v>6.2</v>
+      </c>
+      <c r="AS16">
+        <v>6.6</v>
+      </c>
+      <c r="AT16">
+        <v>6.4</v>
+      </c>
+      <c r="AU16">
+        <v>5.3</v>
+      </c>
+      <c r="AV16">
+        <v>5.3</v>
+      </c>
+      <c r="AW16">
+        <v>5.9</v>
+      </c>
+      <c r="AX16">
+        <v>6.4</v>
+      </c>
+      <c r="AY16">
+        <v>5.5</v>
+      </c>
+      <c r="AZ16">
+        <v>5.1</v>
+      </c>
+      <c r="BA16">
+        <v>5.8</v>
+      </c>
+      <c r="BB16">
+        <v>6.8</v>
+      </c>
+      <c r="BC16">
+        <v>6</v>
+      </c>
+      <c r="BD16">
+        <v>6</v>
+      </c>
+      <c r="BE16">
+        <v>6.4</v>
+      </c>
+      <c r="BF16">
+        <v>4.1</v>
+      </c>
+      <c r="BG16">
+        <v>3.75</v>
+      </c>
+      <c r="BH16">
+        <v>7.2</v>
+      </c>
+      <c r="BI16">
+        <v>4.2</v>
+      </c>
+      <c r="BJ16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK16">
+        <v>4.5</v>
+      </c>
+      <c r="BL16">
+        <v>40</v>
+      </c>
+      <c r="BM16">
+        <v>8</v>
+      </c>
+      <c r="BN16">
         <v>7.8</v>
       </c>
-      <c r="AP16">
-        <v>5.4</v>
-      </c>
-      <c r="AQ16">
-        <v>5</v>
-      </c>
-      <c r="AR16">
-        <v>5</v>
-      </c>
-      <c r="AS16">
-        <v>5.2</v>
-      </c>
-      <c r="AT16">
-        <v>5.1</v>
-      </c>
-      <c r="AU16">
-        <v>4.3</v>
-      </c>
-      <c r="AV16">
+      <c r="BO16">
+        <v>4.4</v>
+      </c>
+      <c r="BP16">
+        <v>17.5</v>
+      </c>
+      <c r="BQ16">
+        <v>6.4</v>
+      </c>
+      <c r="BR16">
+        <v>18.5</v>
+      </c>
+      <c r="BS16">
+        <v>6.4</v>
+      </c>
+      <c r="BT16">
+        <v>7.4</v>
+      </c>
+      <c r="BU16">
         <v>4.2</v>
       </c>
-      <c r="AW16">
-        <v>4.7</v>
-      </c>
-      <c r="AX16">
-        <v>5.1</v>
-      </c>
-      <c r="AY16">
-        <v>4.4</v>
-      </c>
-      <c r="AZ16">
-        <v>4.2</v>
-      </c>
-      <c r="BA16">
-        <v>4.7</v>
-      </c>
-      <c r="BB16">
-        <v>5.3</v>
-      </c>
-      <c r="BC16">
-        <v>4.7</v>
-      </c>
-      <c r="BD16">
-        <v>4.7</v>
-      </c>
-      <c r="BE16">
-        <v>5</v>
-      </c>
-      <c r="BF16">
-        <v>3.6</v>
-      </c>
-      <c r="BG16">
-        <v>3.3</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.04</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.04</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.04</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.04</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.04</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.04</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>1.04</v>
-      </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB16" t="s">
         <v>171</v>
@@ -4756,19 +4756,19 @@
         <v>1.99</v>
       </c>
       <c r="G17">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H17">
         <v>4.4</v>
       </c>
       <c r="I17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J17">
         <v>3.35</v>
       </c>
       <c r="K17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L17">
         <v>1.46</v>
@@ -4804,7 +4804,7 @@
         <v>1.26</v>
       </c>
       <c r="W17">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="X17">
         <v>13.5</v>
@@ -4921,58 +4921,58 @@
         <v>2.6</v>
       </c>
       <c r="BJ17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK17">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BN17">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BO17">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP17">
         <v>17.5</v>
       </c>
       <c r="BQ17">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR17">
         <v>38</v>
       </c>
       <c r="BS17">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BT17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV17">
         <v>46</v>
       </c>
       <c r="BW17">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY17">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BZ17">
         <v>36</v>
       </c>
       <c r="CA17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CB17" t="s">
         <v>171</v>
@@ -5001,7 +5001,7 @@
         <v>2.48</v>
       </c>
       <c r="H18">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I18">
         <v>3.7</v>
@@ -5019,16 +5019,16 @@
         <v>1.14</v>
       </c>
       <c r="N18">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O18">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P18">
         <v>1.48</v>
       </c>
       <c r="Q18">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="R18">
         <v>1.16</v>
@@ -5037,7 +5037,7 @@
         <v>6.4</v>
       </c>
       <c r="T18">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U18">
         <v>1.66</v>
@@ -5112,7 +5112,7 @@
         <v>20</v>
       </c>
       <c r="AS18">
-        <v>11.5</v>
+        <v>70</v>
       </c>
       <c r="AT18">
         <v>6.4</v>
@@ -5145,7 +5145,7 @@
         <v>32</v>
       </c>
       <c r="BD18">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BE18">
         <v>13</v>
@@ -5240,13 +5240,13 @@
         <v>5.3</v>
       </c>
       <c r="G19">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H19">
         <v>1.86</v>
       </c>
       <c r="I19">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J19">
         <v>3.45</v>
@@ -5264,7 +5264,7 @@
         <v>2.82</v>
       </c>
       <c r="O19">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P19">
         <v>1.59</v>
@@ -5273,13 +5273,13 @@
         <v>2.6</v>
       </c>
       <c r="R19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S19">
         <v>5.3</v>
       </c>
       <c r="T19">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U19">
         <v>1.73</v>
@@ -5291,7 +5291,7 @@
         <v>1.21</v>
       </c>
       <c r="X19">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y19">
         <v>7.4</v>
@@ -5336,7 +5336,7 @@
         <v>130</v>
       </c>
       <c r="AM19">
-        <v>230</v>
+        <v>580</v>
       </c>
       <c r="AN19">
         <v>180</v>
@@ -5360,7 +5360,7 @@
         <v>12</v>
       </c>
       <c r="AU19">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV19">
         <v>9.6</v>
@@ -5429,7 +5429,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BR19">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BS19">
         <v>9.6</v>
@@ -5488,7 +5488,7 @@
         <v>6.2</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J20">
         <v>3.7</v>
@@ -5503,22 +5503,22 @@
         <v>1.09</v>
       </c>
       <c r="N20">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P20">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q20">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R20">
         <v>1.28</v>
       </c>
       <c r="S20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T20">
         <v>2.08</v>
@@ -5724,19 +5724,19 @@
         <v>2.86</v>
       </c>
       <c r="G21">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H21">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I21">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J21">
         <v>3.2</v>
       </c>
       <c r="K21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L21">
         <v>1.49</v>
@@ -5754,16 +5754,16 @@
         <v>1.73</v>
       </c>
       <c r="Q21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R21">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S21">
         <v>4.3</v>
       </c>
       <c r="T21">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U21">
         <v>2</v>
@@ -5787,7 +5787,7 @@
         <v>60</v>
       </c>
       <c r="AB21">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC21">
         <v>8.800000000000001</v>
@@ -5799,7 +5799,7 @@
         <v>44</v>
       </c>
       <c r="AF21">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AG21">
         <v>15.5</v>
@@ -5808,7 +5808,7 @@
         <v>23</v>
       </c>
       <c r="AI21">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ21">
         <v>60</v>
@@ -5838,7 +5838,7 @@
         <v>16</v>
       </c>
       <c r="AS21">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AT21">
         <v>8.6</v>
@@ -5862,19 +5862,19 @@
         <v>10.5</v>
       </c>
       <c r="BA21">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB21">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BC21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD21">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE21">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF21">
         <v>7.2</v>
@@ -5889,16 +5889,16 @@
         <v>2.48</v>
       </c>
       <c r="BJ21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK21">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BN21">
         <v>5.8</v>
@@ -5910,13 +5910,13 @@
         <v>29</v>
       </c>
       <c r="BQ21">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BR21">
         <v>48</v>
       </c>
       <c r="BS21">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BT21">
         <v>5.7</v>
@@ -5925,22 +5925,22 @@
         <v>5.1</v>
       </c>
       <c r="BV21">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BX21">
         <v>48</v>
       </c>
       <c r="BY21">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BZ21">
         <v>44</v>
       </c>
       <c r="CA21">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="CB21" t="s">
         <v>171</v>
@@ -5963,19 +5963,19 @@
         <v>159</v>
       </c>
       <c r="F22">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G22">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H22">
         <v>2.62</v>
       </c>
       <c r="I22">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K22">
         <v>4.3</v>
@@ -5996,7 +5996,7 @@
         <v>2.5</v>
       </c>
       <c r="Q22">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R22">
         <v>1.58</v>
@@ -6011,10 +6011,10 @@
         <v>2.52</v>
       </c>
       <c r="V22">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X22">
         <v>29</v>
@@ -6068,22 +6068,22 @@
         <v>18</v>
       </c>
       <c r="AO22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP22">
         <v>5.2</v>
       </c>
       <c r="AQ22">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AR22">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="AS22">
         <v>5.5</v>
       </c>
       <c r="AT22">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="AU22">
         <v>3.95</v>
@@ -6092,7 +6092,7 @@
         <v>4.3</v>
       </c>
       <c r="AW22">
-        <v>5.1</v>
+        <v>19</v>
       </c>
       <c r="AX22">
         <v>17</v>
@@ -6101,7 +6101,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ22">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="BA22">
         <v>5.3</v>
@@ -6110,79 +6110,79 @@
         <v>5.4</v>
       </c>
       <c r="BC22">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BD22">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="BE22">
         <v>5.7</v>
       </c>
       <c r="BF22">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG22">
         <v>4.6</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI22">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK22">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO22">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ22">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS22">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU22">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW22">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY22">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA22">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB22" t="s">
         <v>171</v>
@@ -6223,7 +6223,7 @@
         <v>4.5</v>
       </c>
       <c r="L23">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M23">
         <v>1.05</v>
@@ -6232,7 +6232,7 @@
         <v>4.5</v>
       </c>
       <c r="O23">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P23">
         <v>2.2</v>
@@ -6247,7 +6247,7 @@
         <v>2.94</v>
       </c>
       <c r="T23">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U23">
         <v>2.12</v>
@@ -6331,7 +6331,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV23">
-        <v>4.1</v>
+        <v>16.5</v>
       </c>
       <c r="AW23">
         <v>4.8</v>
@@ -6343,7 +6343,7 @@
         <v>3.6</v>
       </c>
       <c r="AZ23">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="BA23">
         <v>4.7</v>
@@ -6367,64 +6367,64 @@
         <v>4.8</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB23" t="s">
         <v>171</v>
@@ -6447,40 +6447,40 @@
         <v>161</v>
       </c>
       <c r="F24">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G24">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H24">
         <v>3.3</v>
       </c>
       <c r="I24">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J24">
         <v>3.2</v>
       </c>
       <c r="K24">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L24">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M24">
         <v>1.09</v>
       </c>
       <c r="N24">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O24">
         <v>1.42</v>
       </c>
       <c r="P24">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q24">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R24">
         <v>1.26</v>
@@ -6498,7 +6498,7 @@
         <v>1.39</v>
       </c>
       <c r="W24">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6716,7 +6716,7 @@
         <v>3.85</v>
       </c>
       <c r="O25">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P25">
         <v>1.94</v>
@@ -6800,7 +6800,7 @@
         <v>13</v>
       </c>
       <c r="AQ25">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="AR25">
         <v>9.800000000000001</v>
@@ -6866,7 +6866,7 @@
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN25">
         <v>3.7</v>
@@ -6875,7 +6875,7 @@
         <v>3.15</v>
       </c>
       <c r="BP25">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BQ25">
         <v>5</v>
@@ -6884,7 +6884,7 @@
         <v>30</v>
       </c>
       <c r="BS25">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT25">
         <v>14</v>
@@ -6896,19 +6896,19 @@
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ25">
         <v>17.5</v>
       </c>
       <c r="CA25">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB25" t="s">
         <v>171</v>
@@ -6934,13 +6934,13 @@
         <v>2.2</v>
       </c>
       <c r="G26">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H26">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J26">
         <v>3.1</v>
@@ -6952,10 +6952,10 @@
         <v>1.62</v>
       </c>
       <c r="M26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N26">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O26">
         <v>1.58</v>
@@ -6967,7 +6967,7 @@
         <v>2.78</v>
       </c>
       <c r="R26">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S26">
         <v>5.9</v>
@@ -6982,13 +6982,13 @@
         <v>1.29</v>
       </c>
       <c r="W26">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X26">
         <v>8.199999999999999</v>
       </c>
       <c r="Y26">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z26">
         <v>30</v>
@@ -7009,7 +7009,7 @@
         <v>80</v>
       </c>
       <c r="AF26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG26">
         <v>12</v>
@@ -7018,7 +7018,7 @@
         <v>27</v>
       </c>
       <c r="AI26">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ26">
         <v>30</v>
@@ -7033,13 +7033,13 @@
         <v>230</v>
       </c>
       <c r="AN26">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO26">
         <v>130</v>
       </c>
       <c r="AP26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ26">
         <v>9.800000000000001</v>
@@ -7048,7 +7048,7 @@
         <v>25</v>
       </c>
       <c r="AS26">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT26">
         <v>5.9</v>
@@ -7060,7 +7060,7 @@
         <v>17</v>
       </c>
       <c r="AW26">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX26">
         <v>10</v>
@@ -7072,25 +7072,25 @@
         <v>24</v>
       </c>
       <c r="BA26">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BB26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC26">
         <v>27</v>
       </c>
       <c r="BD26">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE26">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF26">
         <v>27</v>
       </c>
       <c r="BG26">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH26">
         <v>2.64</v>
@@ -7108,31 +7108,31 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN26">
         <v>4.9</v>
       </c>
       <c r="BO26">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BP26">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ26">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT26">
         <v>7.4</v>
       </c>
       <c r="BU26">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV26">
         <v>1000</v>
@@ -7144,7 +7144,7 @@
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
@@ -7197,22 +7197,22 @@
         <v>1.05</v>
       </c>
       <c r="N27">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O27">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P27">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q27">
         <v>1.73</v>
       </c>
       <c r="R27">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S27">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T27">
         <v>1.64</v>
@@ -7230,7 +7230,7 @@
         <v>21</v>
       </c>
       <c r="Y27">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z27">
         <v>24</v>
@@ -7251,7 +7251,7 @@
         <v>30</v>
       </c>
       <c r="AF27">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG27">
         <v>11</v>
@@ -7263,7 +7263,7 @@
         <v>38</v>
       </c>
       <c r="AJ27">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK27">
         <v>23</v>
@@ -7272,7 +7272,7 @@
         <v>32</v>
       </c>
       <c r="AM27">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
         <v>15</v>
@@ -7290,10 +7290,10 @@
         <v>20</v>
       </c>
       <c r="AS27">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AT27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU27">
         <v>8.199999999999999</v>
@@ -7302,7 +7302,7 @@
         <v>11.5</v>
       </c>
       <c r="AW27">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AX27">
         <v>15</v>
@@ -7326,10 +7326,10 @@
         <v>25</v>
       </c>
       <c r="BE27">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BF27">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG27">
         <v>21</v>
@@ -7338,7 +7338,7 @@
         <v>4.5</v>
       </c>
       <c r="BI27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ27">
         <v>8.800000000000001</v>
@@ -7350,7 +7350,7 @@
         <v>110</v>
       </c>
       <c r="BM27">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN27">
         <v>5.5</v>
@@ -7362,16 +7362,16 @@
         <v>16.5</v>
       </c>
       <c r="BQ27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR27">
         <v>26</v>
       </c>
       <c r="BS27">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT27">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU27">
         <v>5.7</v>
@@ -7380,19 +7380,19 @@
         <v>22</v>
       </c>
       <c r="BW27">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX27">
         <v>30</v>
       </c>
       <c r="BY27">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ27">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA27">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB27" t="s">
         <v>171</v>
@@ -7415,16 +7415,16 @@
         <v>165</v>
       </c>
       <c r="F28">
+        <v>2.96</v>
+      </c>
+      <c r="G28">
         <v>3.05</v>
       </c>
-      <c r="G28">
-        <v>3.15</v>
-      </c>
       <c r="H28">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="I28">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="J28">
         <v>3.95</v>
@@ -7439,19 +7439,19 @@
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O28">
         <v>1.2</v>
       </c>
       <c r="P28">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q28">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R28">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S28">
         <v>2.52</v>
@@ -7460,13 +7460,13 @@
         <v>1.54</v>
       </c>
       <c r="U28">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V28">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W28">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X28">
         <v>25</v>
@@ -7475,28 +7475,28 @@
         <v>15.5</v>
       </c>
       <c r="Z28">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AA28">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB28">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC28">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE28">
         <v>22</v>
       </c>
       <c r="AF28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG28">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH28">
         <v>15</v>
@@ -7505,22 +7505,22 @@
         <v>28</v>
       </c>
       <c r="AJ28">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK28">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL28">
         <v>34</v>
       </c>
       <c r="AM28">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AN28">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AO28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP28">
         <v>21</v>
@@ -7547,7 +7547,7 @@
         <v>19</v>
       </c>
       <c r="AX28">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY28">
         <v>12</v>
@@ -7556,7 +7556,7 @@
         <v>13.5</v>
       </c>
       <c r="BA28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB28">
         <v>42</v>
@@ -7571,13 +7571,13 @@
         <v>46</v>
       </c>
       <c r="BF28">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG28">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH28">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI28">
         <v>3.45</v>
@@ -7604,10 +7604,10 @@
         <v>21</v>
       </c>
       <c r="BQ28">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS28">
         <v>8.199999999999999</v>
@@ -7619,10 +7619,10 @@
         <v>4.9</v>
       </c>
       <c r="BV28">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BW28">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX28">
         <v>24</v>
@@ -7657,10 +7657,10 @@
         <v>166</v>
       </c>
       <c r="F29">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G29">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H29">
         <v>3.25</v>
@@ -7669,16 +7669,16 @@
         <v>3.35</v>
       </c>
       <c r="J29">
+        <v>3.7</v>
+      </c>
+      <c r="K29">
         <v>3.75</v>
       </c>
-      <c r="K29">
-        <v>3.85</v>
-      </c>
       <c r="L29">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N29">
         <v>4.5</v>
@@ -7693,7 +7693,7 @@
         <v>1.8</v>
       </c>
       <c r="R29">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S29">
         <v>3.05</v>
@@ -7702,19 +7702,19 @@
         <v>1.66</v>
       </c>
       <c r="U29">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
         <v>1.42</v>
       </c>
       <c r="W29">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X29">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y29">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z29">
         <v>25</v>
@@ -7726,13 +7726,13 @@
         <v>12</v>
       </c>
       <c r="AC29">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD29">
         <v>14</v>
       </c>
       <c r="AE29">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF29">
         <v>16.5</v>
@@ -7741,43 +7741,43 @@
         <v>11</v>
       </c>
       <c r="AH29">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI29">
         <v>42</v>
       </c>
       <c r="AJ29">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL29">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AM29">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN29">
         <v>15.5</v>
       </c>
       <c r="AO29">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP29">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ29">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS29">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AT29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU29">
         <v>7.8</v>
@@ -7786,37 +7786,37 @@
         <v>12.5</v>
       </c>
       <c r="AW29">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AX29">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY29">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ29">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA29">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB29">
         <v>27</v>
       </c>
       <c r="BC29">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD29">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BE29">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF29">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG29">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BH29">
         <v>4.4</v>
@@ -7828,13 +7828,13 @@
         <v>9</v>
       </c>
       <c r="BK29">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL29">
         <v>120</v>
       </c>
       <c r="BM29">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BN29">
         <v>5.3</v>
@@ -7852,22 +7852,22 @@
         <v>30</v>
       </c>
       <c r="BS29">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT29">
         <v>6.6</v>
       </c>
       <c r="BU29">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV29">
         <v>29</v>
       </c>
       <c r="BW29">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX29">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
         <v>6.8</v>
@@ -7899,16 +7899,16 @@
         <v>167</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G30">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H30">
+        <v>2.28</v>
+      </c>
+      <c r="I30">
         <v>2.32</v>
-      </c>
-      <c r="I30">
-        <v>2.36</v>
       </c>
       <c r="J30">
         <v>4.1</v>
@@ -7941,28 +7941,28 @@
         <v>2.04</v>
       </c>
       <c r="T30">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V30">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W30">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X30">
         <v>34</v>
       </c>
       <c r="Y30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z30">
         <v>22</v>
       </c>
       <c r="AA30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB30">
         <v>24</v>
@@ -7977,22 +7977,22 @@
         <v>20</v>
       </c>
       <c r="AF30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG30">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH30">
         <v>13.5</v>
       </c>
       <c r="AI30">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AJ30">
         <v>55</v>
       </c>
       <c r="AK30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL30">
         <v>27</v>
@@ -8001,22 +8001,22 @@
         <v>42</v>
       </c>
       <c r="AN30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO30">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP30">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AQ30">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR30">
         <v>20</v>
       </c>
       <c r="AS30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT30">
         <v>22</v>
@@ -8034,7 +8034,7 @@
         <v>26</v>
       </c>
       <c r="AY30">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ30">
         <v>12</v>
@@ -8043,7 +8043,7 @@
         <v>21</v>
       </c>
       <c r="BB30">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BC30">
         <v>24</v>
@@ -8070,13 +8070,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK30">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN30">
         <v>7</v>
@@ -8088,37 +8088,37 @@
         <v>18.5</v>
       </c>
       <c r="BQ30">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR30">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS30">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT30">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU30">
         <v>5.5</v>
       </c>
       <c r="BV30">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW30">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ30">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA30">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB30" t="s">
         <v>171</v>
@@ -8159,7 +8159,7 @@
         <v>4.4</v>
       </c>
       <c r="L31">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M31">
         <v>1.04</v>
@@ -8177,7 +8177,7 @@
         <v>1.64</v>
       </c>
       <c r="R31">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S31">
         <v>2.6</v>
@@ -8189,7 +8189,7 @@
         <v>2.38</v>
       </c>
       <c r="V31">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W31">
         <v>2.32</v>
@@ -8243,7 +8243,7 @@
         <v>75</v>
       </c>
       <c r="AN31">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AO31">
         <v>46</v>
@@ -8383,16 +8383,16 @@
         <v>169</v>
       </c>
       <c r="F32">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G32">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H32">
         <v>2.56</v>
       </c>
       <c r="I32">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J32">
         <v>4.3</v>
@@ -8401,70 +8401,70 @@
         <v>4.4</v>
       </c>
       <c r="L32">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M32">
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O32">
         <v>1.13</v>
       </c>
       <c r="P32">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q32">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R32">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="S32">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="T32">
         <v>1.39</v>
       </c>
       <c r="U32">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V32">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W32">
         <v>1.62</v>
       </c>
       <c r="X32">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y32">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z32">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA32">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB32">
         <v>23</v>
       </c>
       <c r="AC32">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD32">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE32">
         <v>23</v>
       </c>
       <c r="AF32">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG32">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH32">
         <v>13.5</v>
@@ -8479,13 +8479,13 @@
         <v>23</v>
       </c>
       <c r="AL32">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM32">
         <v>38</v>
       </c>
       <c r="AN32">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO32">
         <v>10.5</v>
@@ -8518,7 +8518,7 @@
         <v>23</v>
       </c>
       <c r="AY32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ32">
         <v>12.5</v>
@@ -8527,19 +8527,19 @@
         <v>21</v>
       </c>
       <c r="BB32">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC32">
         <v>20</v>
       </c>
       <c r="BD32">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE32">
         <v>32</v>
       </c>
       <c r="BF32">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG32">
         <v>9.6</v>
@@ -8548,7 +8548,7 @@
         <v>6.2</v>
       </c>
       <c r="BI32">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ32">
         <v>8.4</v>
@@ -8560,7 +8560,7 @@
         <v>55</v>
       </c>
       <c r="BM32">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BN32">
         <v>6.8</v>
@@ -8572,7 +8572,7 @@
         <v>16.5</v>
       </c>
       <c r="BQ32">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR32">
         <v>21</v>
@@ -8590,16 +8590,16 @@
         <v>17.5</v>
       </c>
       <c r="BW32">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX32">
         <v>22</v>
       </c>
       <c r="BY32">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ32">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA32">
         <v>4.9</v>
@@ -8625,16 +8625,16 @@
         <v>170</v>
       </c>
       <c r="F33">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="G33">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="H33">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I33">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="J33">
         <v>4.1</v>
@@ -8643,7 +8643,7 @@
         <v>4.3</v>
       </c>
       <c r="L33">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M33">
         <v>1.03</v>
@@ -8658,7 +8658,7 @@
         <v>2.94</v>
       </c>
       <c r="Q33">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R33">
         <v>1.78</v>
@@ -8667,19 +8667,19 @@
         <v>2.22</v>
       </c>
       <c r="T33">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U33">
         <v>2.98</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W33">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="X33">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y33">
         <v>23</v>
@@ -8691,19 +8691,19 @@
         <v>65</v>
       </c>
       <c r="AB33">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC33">
         <v>10.5</v>
       </c>
       <c r="AD33">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE33">
         <v>32</v>
       </c>
       <c r="AF33">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG33">
         <v>11.5</v>
@@ -8715,22 +8715,22 @@
         <v>32</v>
       </c>
       <c r="AJ33">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK33">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL33">
         <v>24</v>
       </c>
       <c r="AM33">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN33">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO33">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AP33">
         <v>26</v>
@@ -8751,13 +8751,13 @@
         <v>9.6</v>
       </c>
       <c r="AV33">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW33">
         <v>28</v>
       </c>
       <c r="AX33">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY33">
         <v>10.5</v>
@@ -8772,16 +8772,16 @@
         <v>26</v>
       </c>
       <c r="BC33">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE33">
         <v>40</v>
       </c>
       <c r="BF33">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG33">
         <v>17</v>
@@ -8796,13 +8796,13 @@
         <v>8.4</v>
       </c>
       <c r="BK33">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BL33">
         <v>75</v>
       </c>
       <c r="BM33">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN33">
         <v>5.5</v>
@@ -8811,16 +8811,16 @@
         <v>5</v>
       </c>
       <c r="BP33">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ33">
         <v>9.4</v>
       </c>
       <c r="BR33">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS33">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT33">
         <v>7.4</v>
@@ -8829,19 +8829,19 @@
         <v>5.5</v>
       </c>
       <c r="BV33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW33">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX33">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BZ33">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CA33">
         <v>6</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -559,7 +559,7 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-19 06:33:35</t>
+    <t>2026-08-19 08:43:11</t>
   </si>
 </sst>
 </file>
@@ -1153,226 +1153,226 @@
         <v>144</v>
       </c>
       <c r="F2">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="G2">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="H2">
         <v>4.2</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L2">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="M2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="O2">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="P2">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="Q2">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U2">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="X2">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA2">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE2">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI2">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL2">
+        <v>75</v>
+      </c>
+      <c r="AM2">
+        <v>280</v>
+      </c>
+      <c r="AN2">
+        <v>40</v>
+      </c>
+      <c r="AO2">
         <v>160</v>
       </c>
-      <c r="AM2">
-        <v>790</v>
-      </c>
-      <c r="AN2">
-        <v>36</v>
-      </c>
-      <c r="AO2">
-        <v>600</v>
-      </c>
       <c r="AP2">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AQ2">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AS2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AX2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY2">
         <v>9.6</v>
       </c>
       <c r="AZ2">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BD2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BE2">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="BF2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG2">
-        <v>55</v>
+        <v>6.8</v>
       </c>
       <c r="BH2">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="BI2">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="BM2">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>17.5</v>
+        <v>27</v>
       </c>
       <c r="BQ2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS2">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BT2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BU2">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW2">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY2">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="CB2" t="s">
         <v>181</v>
@@ -1395,226 +1395,226 @@
         <v>145</v>
       </c>
       <c r="F3">
-        <v>1.46</v>
+        <v>1.04</v>
       </c>
       <c r="G3">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="I3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K3">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="L3">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="O3">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P3">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="Q3">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="R3">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="S3">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="T3">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
         <v>13.5</v>
       </c>
-      <c r="AC3">
-        <v>12.5</v>
-      </c>
       <c r="AD3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH3">
         <v>21</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>4.8</v>
+        <v>42</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>29</v>
+        <v>2.5</v>
       </c>
       <c r="AQ3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AR3">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AS3">
-        <v>60</v>
+        <v>1.39</v>
       </c>
       <c r="AT3">
         <v>12</v>
       </c>
       <c r="AU3">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="AV3">
-        <v>24</v>
+        <v>1.2</v>
       </c>
       <c r="AW3">
-        <v>70</v>
+        <v>1.26</v>
       </c>
       <c r="AX3">
-        <v>10.5</v>
+        <v>1.26</v>
       </c>
       <c r="AY3">
-        <v>9.6</v>
+        <v>1.12</v>
       </c>
       <c r="AZ3">
-        <v>18</v>
+        <v>2.5</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>2.9</v>
       </c>
       <c r="BB3">
-        <v>13</v>
+        <v>1.26</v>
       </c>
       <c r="BC3">
-        <v>12.5</v>
+        <v>1.26</v>
       </c>
       <c r="BD3">
-        <v>23</v>
+        <v>2.9</v>
       </c>
       <c r="BE3">
-        <v>65</v>
+        <v>2.5</v>
       </c>
       <c r="BF3">
-        <v>4.6</v>
+        <v>1.22</v>
       </c>
       <c r="BG3">
-        <v>60</v>
+        <v>1.26</v>
       </c>
       <c r="BH3">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="BJ3">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="BM3">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
         <v>11</v>
       </c>
-      <c r="BU3">
-        <v>9.6</v>
-      </c>
       <c r="BV3">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>11</v>
+        <v>960</v>
       </c>
       <c r="CA3">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>181</v>
@@ -1637,88 +1637,88 @@
         <v>146</v>
       </c>
       <c r="F4">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="G4">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="H4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I4">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="J4">
+        <v>2.98</v>
+      </c>
+      <c r="K4">
         <v>3.1</v>
       </c>
-      <c r="K4">
-        <v>3.25</v>
-      </c>
       <c r="L4">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M4">
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="O4">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="P4">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="Q4">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S4">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="V4">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="X4">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA4">
         <v>170</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
         <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF4">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH4">
         <v>25</v>
@@ -1727,34 +1727,34 @@
         <v>380</v>
       </c>
       <c r="AJ4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AK4">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AL4">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AM4">
         <v>500</v>
       </c>
       <c r="AN4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO4">
         <v>600</v>
       </c>
       <c r="AP4">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AS4">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="AT4">
         <v>6.8</v>
@@ -1763,46 +1763,46 @@
         <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW4">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AX4">
         <v>12.5</v>
       </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>50</v>
+        <v>16.5</v>
       </c>
       <c r="BB4">
-        <v>32</v>
+        <v>9.6</v>
       </c>
       <c r="BC4">
         <v>30</v>
       </c>
       <c r="BD4">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BE4">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BF4">
         <v>32</v>
       </c>
       <c r="BG4">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="BH4">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BI4">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
@@ -1817,43 +1817,43 @@
         <v>13.5</v>
       </c>
       <c r="BN4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BO4">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BP4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
+        <v>11.5</v>
+      </c>
+      <c r="BT4">
+        <v>6.2</v>
+      </c>
+      <c r="BU4">
+        <v>5.3</v>
+      </c>
+      <c r="BV4">
+        <v>32</v>
+      </c>
+      <c r="BW4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
         <v>11</v>
       </c>
-      <c r="BT4">
-        <v>6.6</v>
-      </c>
-      <c r="BU4">
-        <v>4.9</v>
-      </c>
-      <c r="BV4">
-        <v>36</v>
-      </c>
-      <c r="BW4">
-        <v>10</v>
-      </c>
-      <c r="BX4">
-        <v>60</v>
-      </c>
-      <c r="BY4">
-        <v>11.5</v>
-      </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA4">
         <v>11</v>
@@ -1879,16 +1879,16 @@
         <v>147</v>
       </c>
       <c r="F5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G5">
         <v>1.87</v>
       </c>
       <c r="H5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>3.45</v>
@@ -1903,31 +1903,31 @@
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P5">
         <v>1.61</v>
       </c>
       <c r="Q5">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R5">
+        <v>1.23</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
+        <v>2.1</v>
+      </c>
+      <c r="U5">
+        <v>1.71</v>
+      </c>
+      <c r="V5">
         <v>1.21</v>
-      </c>
-      <c r="S5">
-        <v>4.8</v>
-      </c>
-      <c r="T5">
-        <v>2.12</v>
-      </c>
-      <c r="U5">
-        <v>1.72</v>
-      </c>
-      <c r="V5">
-        <v>1.2</v>
       </c>
       <c r="W5">
         <v>2.14</v>
@@ -1939,7 +1939,7 @@
         <v>16</v>
       </c>
       <c r="Z5">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AA5">
         <v>900</v>
@@ -1948,10 +1948,10 @@
         <v>6.8</v>
       </c>
       <c r="AC5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE5">
         <v>500</v>
@@ -1960,10 +1960,10 @@
         <v>10</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI5">
         <v>500</v>
@@ -1981,49 +1981,49 @@
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO5">
         <v>600</v>
       </c>
       <c r="AP5">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="AQ5">
         <v>13</v>
       </c>
       <c r="AR5">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS5">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AU5">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AV5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX5">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
         <v>21</v>
       </c>
       <c r="BA5">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB5">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="BC5">
         <v>20</v>
@@ -2032,13 +2032,13 @@
         <v>28</v>
       </c>
       <c r="BE5">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BG5">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5">
         <v>3</v>
@@ -2050,7 +2050,7 @@
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2068,7 +2068,7 @@
         <v>14</v>
       </c>
       <c r="BQ5">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BR5">
         <v>38</v>
@@ -2080,7 +2080,7 @@
         <v>9.4</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -2121,175 +2121,175 @@
         <v>148</v>
       </c>
       <c r="F6">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="G6">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="H6">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="I6">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J6">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="L6">
         <v>1.51</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P6">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q6">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S6">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="W6">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="X6">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y6">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="Z6">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="AA6">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB6">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AC6">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AE6">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AF6">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AG6">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AH6">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AI6">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AJ6">
-        <v>900</v>
+        <v>95</v>
       </c>
       <c r="AK6">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AL6">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AM6">
         <v>580</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO6">
-        <v>600</v>
+        <v>29</v>
       </c>
       <c r="AP6">
         <v>4.9</v>
       </c>
       <c r="AQ6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR6">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS6">
-        <v>1.36</v>
+        <v>9</v>
       </c>
       <c r="AT6">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="AU6">
         <v>4.9</v>
       </c>
       <c r="AV6">
-        <v>1.32</v>
+        <v>7.6</v>
       </c>
       <c r="AW6">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="AX6">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="AY6">
-        <v>1.36</v>
+        <v>7.6</v>
       </c>
       <c r="AZ6">
-        <v>1.34</v>
+        <v>5.8</v>
       </c>
       <c r="BA6">
-        <v>1.36</v>
+        <v>6.6</v>
       </c>
       <c r="BB6">
-        <v>1.37</v>
+        <v>6.8</v>
       </c>
       <c r="BC6">
-        <v>1.37</v>
+        <v>6.6</v>
       </c>
       <c r="BD6">
-        <v>1.37</v>
+        <v>6.8</v>
       </c>
       <c r="BE6">
-        <v>1.37</v>
+        <v>7</v>
       </c>
       <c r="BF6">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BG6">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK6">
         <v>1.04</v>
@@ -2301,43 +2301,43 @@
         <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO6">
         <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ6">
         <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS6">
         <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU6">
         <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW6">
         <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY6">
         <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA6">
         <v>1.04</v>
@@ -2363,58 +2363,58 @@
         <v>149</v>
       </c>
       <c r="F7">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="G7">
         <v>1.6</v>
       </c>
       <c r="H7">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J7">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R7">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T7">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="U7">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="V7">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W7">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X7">
         <v>15</v>
@@ -2429,7 +2429,7 @@
         <v>700</v>
       </c>
       <c r="AB7">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC7">
         <v>10.5</v>
@@ -2441,10 +2441,10 @@
         <v>700</v>
       </c>
       <c r="AF7">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH7">
         <v>32</v>
@@ -2471,61 +2471,61 @@
         <v>700</v>
       </c>
       <c r="AP7">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="AR7">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AS7">
+        <v>6.6</v>
+      </c>
+      <c r="AT7">
+        <v>5.4</v>
+      </c>
+      <c r="AU7">
+        <v>8.4</v>
+      </c>
+      <c r="AV7">
+        <v>5.7</v>
+      </c>
+      <c r="AW7">
+        <v>6.4</v>
+      </c>
+      <c r="AX7">
+        <v>7</v>
+      </c>
+      <c r="AY7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7">
         <v>5.6</v>
       </c>
-      <c r="AT7">
-        <v>3.25</v>
-      </c>
-      <c r="AU7">
-        <v>3.65</v>
-      </c>
-      <c r="AV7">
-        <v>4.9</v>
-      </c>
-      <c r="AW7">
-        <v>5.5</v>
-      </c>
-      <c r="AX7">
-        <v>3.5</v>
-      </c>
-      <c r="AY7">
-        <v>3.85</v>
-      </c>
-      <c r="AZ7">
-        <v>4.8</v>
-      </c>
       <c r="BA7">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB7">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BC7">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="BD7">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE7">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF7">
-        <v>3.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI7">
         <v>2.7</v>
@@ -2540,25 +2540,25 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN7">
         <v>4.3</v>
       </c>
       <c r="BO7">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BP7">
         <v>12</v>
       </c>
       <c r="BQ7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BR7">
         <v>36</v>
       </c>
       <c r="BS7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT7">
         <v>13</v>
@@ -2570,19 +2570,19 @@
         <v>95</v>
       </c>
       <c r="BW7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX7">
         <v>100</v>
       </c>
       <c r="BY7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ7">
         <v>26</v>
       </c>
       <c r="CA7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB7" t="s">
         <v>181</v>
@@ -2605,76 +2605,76 @@
         <v>150</v>
       </c>
       <c r="F8">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="G8">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="H8">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="I8">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J8">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M8">
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q8">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R8">
         <v>1.31</v>
       </c>
       <c r="S8">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T8">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="U8">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V8">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="W8">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="X8">
         <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA8">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AB8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8">
         <v>11.5</v>
@@ -2683,88 +2683,88 @@
         <v>25</v>
       </c>
       <c r="AF8">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AG8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI8">
         <v>65</v>
       </c>
       <c r="AJ8">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="AK8">
+        <v>65</v>
+      </c>
+      <c r="AL8">
         <v>85</v>
-      </c>
-      <c r="AL8">
-        <v>100</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AP8">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR8">
+        <v>10.5</v>
+      </c>
+      <c r="AS8">
+        <v>21</v>
+      </c>
+      <c r="AT8">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS8">
-        <v>17.5</v>
-      </c>
-      <c r="AT8">
-        <v>10</v>
-      </c>
       <c r="AU8">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW8">
+        <v>17</v>
+      </c>
+      <c r="AX8">
+        <v>18</v>
+      </c>
+      <c r="AY8">
+        <v>13</v>
+      </c>
+      <c r="AZ8">
         <v>15.5</v>
       </c>
-      <c r="AX8">
-        <v>14</v>
-      </c>
-      <c r="AY8">
+      <c r="BA8">
+        <v>27</v>
+      </c>
+      <c r="BB8">
+        <v>44</v>
+      </c>
+      <c r="BC8">
+        <v>29</v>
+      </c>
+      <c r="BD8">
+        <v>36</v>
+      </c>
+      <c r="BE8">
+        <v>28</v>
+      </c>
+      <c r="BF8">
+        <v>30</v>
+      </c>
+      <c r="BG8">
         <v>12.5</v>
-      </c>
-      <c r="AZ8">
-        <v>16</v>
-      </c>
-      <c r="BA8">
-        <v>18</v>
-      </c>
-      <c r="BB8">
-        <v>36</v>
-      </c>
-      <c r="BC8">
-        <v>21</v>
-      </c>
-      <c r="BD8">
-        <v>25</v>
-      </c>
-      <c r="BE8">
-        <v>55</v>
-      </c>
-      <c r="BF8">
-        <v>24</v>
-      </c>
-      <c r="BG8">
-        <v>11</v>
       </c>
       <c r="BH8">
         <v>3.35</v>
@@ -2776,55 +2776,55 @@
         <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>2.52</v>
+        <v>9.6</v>
       </c>
       <c r="BN8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO8">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>2.44</v>
+        <v>8.4</v>
       </c>
       <c r="BT8">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BU8">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BV8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW8">
         <v>6.4</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY8">
-        <v>2.38</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>2.36</v>
+        <v>7.6</v>
       </c>
       <c r="CB8" t="s">
         <v>181</v>
@@ -2853,70 +2853,70 @@
         <v>1.31</v>
       </c>
       <c r="H9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J9">
         <v>5.5</v>
       </c>
       <c r="K9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P9">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q9">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R9">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S9">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T9">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U9">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V9">
         <v>1.06</v>
       </c>
       <c r="W9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X9">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y9">
         <v>160</v>
       </c>
       <c r="Z9">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA9">
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC9">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD9">
         <v>340</v>
@@ -2928,10 +2928,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG9">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH9">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="AI9">
         <v>270</v>
@@ -2955,100 +2955,100 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9">
         <v>14.5</v>
       </c>
       <c r="AR9">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AS9">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU9">
         <v>11.5</v>
       </c>
       <c r="AV9">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AW9">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX9">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BA9">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BB9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC9">
+        <v>13</v>
+      </c>
+      <c r="BD9">
+        <v>23</v>
+      </c>
+      <c r="BE9">
         <v>7.8</v>
       </c>
-      <c r="BC9">
-        <v>12.5</v>
-      </c>
-      <c r="BD9">
-        <v>18.5</v>
-      </c>
-      <c r="BE9">
-        <v>6</v>
-      </c>
       <c r="BF9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG9">
+        <v>7.6</v>
+      </c>
+      <c r="BH9">
+        <v>4.2</v>
+      </c>
+      <c r="BI9">
+        <v>3.15</v>
+      </c>
+      <c r="BJ9">
+        <v>15</v>
+      </c>
+      <c r="BK9">
         <v>6.2</v>
       </c>
-      <c r="BH9">
-        <v>4.3</v>
-      </c>
-      <c r="BI9">
-        <v>3.25</v>
-      </c>
-      <c r="BJ9">
-        <v>14.5</v>
-      </c>
-      <c r="BK9">
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
         <v>10</v>
       </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>10.5</v>
-      </c>
       <c r="BN9">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BO9">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BP9">
         <v>7.2</v>
       </c>
       <c r="BQ9">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BR9">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT9">
         <v>18</v>
       </c>
       <c r="BU9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -3060,13 +3060,13 @@
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA9">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="CB9" t="s">
         <v>181</v>
@@ -3089,46 +3089,46 @@
         <v>152</v>
       </c>
       <c r="F10">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G10">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H10">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>70</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J10">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="K10">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O10">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P10">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q10">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R10">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S10">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3137,10 +3137,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="W10">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="X10">
         <v>950</v>
@@ -3197,16 +3197,16 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AQ10">
         <v>1.21</v>
       </c>
       <c r="AR10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AS10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT10">
         <v>1.17</v>
@@ -3215,37 +3215,37 @@
         <v>1.18</v>
       </c>
       <c r="AV10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AW10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AX10">
         <v>1.18</v>
       </c>
       <c r="AY10">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AZ10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BA10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BB10">
         <v>1.2</v>
       </c>
       <c r="BC10">
+        <v>1.2</v>
+      </c>
+      <c r="BD10">
+        <v>1.21</v>
+      </c>
+      <c r="BE10">
+        <v>1.22</v>
+      </c>
+      <c r="BF10">
         <v>1.19</v>
-      </c>
-      <c r="BD10">
-        <v>1.2</v>
-      </c>
-      <c r="BE10">
-        <v>1.21</v>
-      </c>
-      <c r="BF10">
-        <v>1.18</v>
       </c>
       <c r="BG10">
         <v>1.55</v>
@@ -3331,7 +3331,7 @@
         <v>153</v>
       </c>
       <c r="F11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G11">
         <v>1.85</v>
@@ -3340,13 +3340,13 @@
         <v>3.75</v>
       </c>
       <c r="I11">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J11">
         <v>4.7</v>
       </c>
       <c r="K11">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L11">
         <v>1.16</v>
@@ -3376,37 +3376,37 @@
         <v>1.37</v>
       </c>
       <c r="U11">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V11">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W11">
         <v>2.16</v>
       </c>
       <c r="X11">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Y11">
         <v>44</v>
       </c>
       <c r="Z11">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AA11">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB11">
         <v>28</v>
       </c>
       <c r="AC11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF11">
         <v>24</v>
@@ -3415,7 +3415,7 @@
         <v>14</v>
       </c>
       <c r="AH11">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI11">
         <v>32</v>
@@ -3427,22 +3427,22 @@
         <v>17.5</v>
       </c>
       <c r="AL11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AN11">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO11">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP11">
         <v>29</v>
       </c>
       <c r="AQ11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AR11">
         <v>40</v>
@@ -3451,10 +3451,10 @@
         <v>55</v>
       </c>
       <c r="AT11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV11">
         <v>17</v>
@@ -3463,94 +3463,94 @@
         <v>25</v>
       </c>
       <c r="AX11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ11">
         <v>12.5</v>
       </c>
       <c r="BA11">
+        <v>19</v>
+      </c>
+      <c r="BB11">
         <v>21</v>
       </c>
-      <c r="BB11">
-        <v>20</v>
-      </c>
       <c r="BC11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE11">
         <v>27</v>
       </c>
       <c r="BF11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG11">
         <v>12.5</v>
       </c>
       <c r="BH11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BI11">
         <v>5.1</v>
       </c>
       <c r="BJ11">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BK11">
         <v>6</v>
       </c>
       <c r="BL11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BM11">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ11">
+        <v>5.8</v>
+      </c>
+      <c r="BR11">
+        <v>15.5</v>
+      </c>
+      <c r="BS11">
+        <v>6.6</v>
+      </c>
+      <c r="BT11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU11">
+        <v>5.1</v>
+      </c>
+      <c r="BV11">
+        <v>25</v>
+      </c>
+      <c r="BW11">
+        <v>7.8</v>
+      </c>
+      <c r="BX11">
+        <v>23</v>
+      </c>
+      <c r="BY11">
+        <v>7.6</v>
+      </c>
+      <c r="BZ11">
         <v>8</v>
       </c>
-      <c r="BR11">
-        <v>16</v>
-      </c>
-      <c r="BS11">
-        <v>11</v>
-      </c>
-      <c r="BT11">
-        <v>9.6</v>
-      </c>
-      <c r="BU11">
-        <v>6.6</v>
-      </c>
-      <c r="BV11">
-        <v>26</v>
-      </c>
-      <c r="BW11">
-        <v>17.5</v>
-      </c>
-      <c r="BX11">
-        <v>24</v>
-      </c>
-      <c r="BY11">
-        <v>16.5</v>
-      </c>
-      <c r="BZ11">
-        <v>8.4</v>
-      </c>
       <c r="CA11">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="CB11" t="s">
         <v>181</v>
@@ -3573,7 +3573,7 @@
         <v>154</v>
       </c>
       <c r="F12">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="G12">
         <v>1.85</v>
@@ -3582,13 +3582,13 @@
         <v>3.8</v>
       </c>
       <c r="I12">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J12">
         <v>4.8</v>
       </c>
       <c r="K12">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L12">
         <v>1.17</v>
@@ -3603,13 +3603,13 @@
         <v>1.08</v>
       </c>
       <c r="P12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q12">
         <v>1.27</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
         <v>1.66</v>
@@ -3618,16 +3618,16 @@
         <v>1.35</v>
       </c>
       <c r="U12">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="V12">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W12">
         <v>2.18</v>
       </c>
       <c r="X12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Y12">
         <v>75</v>
@@ -3639,49 +3639,49 @@
         <v>110</v>
       </c>
       <c r="AB12">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AC12">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AD12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE12">
         <v>60</v>
       </c>
       <c r="AF12">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AG12">
         <v>13.5</v>
       </c>
       <c r="AH12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ12">
         <v>26</v>
       </c>
       <c r="AK12">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AL12">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AM12">
         <v>50</v>
       </c>
       <c r="AN12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP12">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="AQ12">
         <v>32</v>
@@ -3714,7 +3714,7 @@
         <v>13</v>
       </c>
       <c r="BA12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB12">
         <v>20</v>
@@ -3723,76 +3723,76 @@
         <v>13.5</v>
       </c>
       <c r="BD12">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BE12">
         <v>29</v>
       </c>
       <c r="BF12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG12">
         <v>13.5</v>
       </c>
       <c r="BH12">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BI12">
         <v>5.3</v>
       </c>
       <c r="BJ12">
+        <v>8.4</v>
+      </c>
+      <c r="BK12">
+        <v>5.2</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>10.5</v>
+      </c>
+      <c r="BN12">
+        <v>6</v>
+      </c>
+      <c r="BO12">
+        <v>4.7</v>
+      </c>
+      <c r="BP12">
+        <v>11</v>
+      </c>
+      <c r="BQ12">
+        <v>6</v>
+      </c>
+      <c r="BR12">
+        <v>15.5</v>
+      </c>
+      <c r="BS12">
+        <v>7.2</v>
+      </c>
+      <c r="BT12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU12">
+        <v>5.5</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
         <v>8.6</v>
       </c>
-      <c r="BK12">
-        <v>6.4</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>32</v>
-      </c>
-      <c r="BN12">
-        <v>6.2</v>
-      </c>
-      <c r="BO12">
-        <v>4.6</v>
-      </c>
-      <c r="BP12">
-        <v>11.5</v>
-      </c>
-      <c r="BQ12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR12">
-        <v>16</v>
-      </c>
-      <c r="BS12">
-        <v>11.5</v>
-      </c>
-      <c r="BT12">
-        <v>9.4</v>
-      </c>
-      <c r="BU12">
-        <v>7</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>19</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>17.5</v>
-      </c>
       <c r="BZ12">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CA12">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="CB12" t="s">
         <v>181</v>
@@ -3818,91 +3818,91 @@
         <v>4.3</v>
       </c>
       <c r="G13">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="I13">
         <v>1.78</v>
       </c>
       <c r="J13">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K13">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L13">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="O13">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P13">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="R13">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="S13">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="T13">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="U13">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X13">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Y13">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Z13">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AA13">
         <v>23</v>
       </c>
       <c r="AB13">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AC13">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI13">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AJ13">
         <v>110</v>
@@ -3911,130 +3911,130 @@
         <v>55</v>
       </c>
       <c r="AL13">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM13">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AN13">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AO13">
+        <v>7</v>
+      </c>
+      <c r="AP13">
+        <v>4.6</v>
+      </c>
+      <c r="AQ13">
+        <v>11</v>
+      </c>
+      <c r="AR13">
+        <v>11</v>
+      </c>
+      <c r="AS13">
+        <v>14.5</v>
+      </c>
+      <c r="AT13">
+        <v>20</v>
+      </c>
+      <c r="AU13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV13">
+        <v>8.4</v>
+      </c>
+      <c r="AW13">
+        <v>12</v>
+      </c>
+      <c r="AX13">
+        <v>4.7</v>
+      </c>
+      <c r="AY13">
+        <v>14.5</v>
+      </c>
+      <c r="AZ13">
+        <v>12.5</v>
+      </c>
+      <c r="BA13">
+        <v>18.5</v>
+      </c>
+      <c r="BB13">
+        <v>5</v>
+      </c>
+      <c r="BC13">
+        <v>4.8</v>
+      </c>
+      <c r="BD13">
+        <v>4.7</v>
+      </c>
+      <c r="BE13">
+        <v>4.8</v>
+      </c>
+      <c r="BF13">
+        <v>4.6</v>
+      </c>
+      <c r="BG13">
+        <v>5.1</v>
+      </c>
+      <c r="BH13">
+        <v>5.2</v>
+      </c>
+      <c r="BI13">
+        <v>4.1</v>
+      </c>
+      <c r="BJ13">
+        <v>9</v>
+      </c>
+      <c r="BK13">
+        <v>5.2</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>10.5</v>
+      </c>
+      <c r="BN13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO13">
+        <v>5.2</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>9</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>9</v>
+      </c>
+      <c r="BT13">
+        <v>5.1</v>
+      </c>
+      <c r="BU13">
+        <v>4</v>
+      </c>
+      <c r="BV13">
+        <v>11</v>
+      </c>
+      <c r="BW13">
         <v>5.9</v>
       </c>
-      <c r="AP13">
-        <v>1.03</v>
-      </c>
-      <c r="AQ13">
-        <v>14</v>
-      </c>
-      <c r="AR13">
-        <v>12.5</v>
-      </c>
-      <c r="AS13">
-        <v>15</v>
-      </c>
-      <c r="AT13">
-        <v>1.03</v>
-      </c>
-      <c r="AU13">
-        <v>10</v>
-      </c>
-      <c r="AV13">
-        <v>9</v>
-      </c>
-      <c r="AW13">
+      <c r="BX13">
+        <v>18.5</v>
+      </c>
+      <c r="BY13">
+        <v>7.4</v>
+      </c>
+      <c r="BZ13">
         <v>11.5</v>
       </c>
-      <c r="AX13">
-        <v>1.03</v>
-      </c>
-      <c r="AY13">
-        <v>15.5</v>
-      </c>
-      <c r="AZ13">
-        <v>12</v>
-      </c>
-      <c r="BA13">
-        <v>16.5</v>
-      </c>
-      <c r="BB13">
-        <v>1.03</v>
-      </c>
-      <c r="BC13">
-        <v>1.03</v>
-      </c>
-      <c r="BD13">
-        <v>1.03</v>
-      </c>
-      <c r="BE13">
-        <v>1.03</v>
-      </c>
-      <c r="BF13">
-        <v>21</v>
-      </c>
-      <c r="BG13">
-        <v>4.1</v>
-      </c>
-      <c r="BH13">
-        <v>5.8</v>
-      </c>
-      <c r="BI13">
-        <v>4.5</v>
-      </c>
-      <c r="BJ13">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK13">
-        <v>6.6</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>42</v>
-      </c>
-      <c r="BN13">
-        <v>9.4</v>
-      </c>
-      <c r="BO13">
-        <v>7</v>
-      </c>
-      <c r="BP13">
-        <v>32</v>
-      </c>
-      <c r="BQ13">
-        <v>22</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>21</v>
-      </c>
-      <c r="BT13">
-        <v>5.4</v>
-      </c>
-      <c r="BU13">
-        <v>4.2</v>
-      </c>
-      <c r="BV13">
-        <v>10.5</v>
-      </c>
-      <c r="BW13">
-        <v>7.8</v>
-      </c>
-      <c r="BX13">
-        <v>17.5</v>
-      </c>
-      <c r="BY13">
-        <v>12.5</v>
-      </c>
-      <c r="BZ13">
-        <v>10</v>
-      </c>
       <c r="CA13">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="CB13" t="s">
         <v>181</v>
@@ -4057,22 +4057,22 @@
         <v>156</v>
       </c>
       <c r="F14">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G14">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="H14">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I14">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J14">
         <v>4.7</v>
       </c>
       <c r="K14">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L14">
         <v>1.14</v>
@@ -4081,34 +4081,34 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O14">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P14">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q14">
         <v>1.25</v>
       </c>
       <c r="R14">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="S14">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T14">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U14">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="V14">
         <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="X14">
         <v>85</v>
@@ -4126,10 +4126,10 @@
         <v>34</v>
       </c>
       <c r="AC14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AD14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE14">
         <v>34</v>
@@ -4141,10 +4141,10 @@
         <v>15.5</v>
       </c>
       <c r="AH14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ14">
         <v>32</v>
@@ -4153,16 +4153,16 @@
         <v>19</v>
       </c>
       <c r="AL14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM14">
         <v>32</v>
       </c>
       <c r="AN14">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AO14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP14">
         <v>46</v>
@@ -4171,7 +4171,7 @@
         <v>34</v>
       </c>
       <c r="AR14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AS14">
         <v>50</v>
@@ -4180,13 +4180,13 @@
         <v>25</v>
       </c>
       <c r="AU14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AV14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX14">
         <v>21</v>
@@ -4201,82 +4201,82 @@
         <v>21</v>
       </c>
       <c r="BB14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD14">
+        <v>16</v>
+      </c>
+      <c r="BE14">
+        <v>26</v>
+      </c>
+      <c r="BF14">
+        <v>4</v>
+      </c>
+      <c r="BG14">
+        <v>10</v>
+      </c>
+      <c r="BH14">
+        <v>8</v>
+      </c>
+      <c r="BI14">
+        <v>4.3</v>
+      </c>
+      <c r="BJ14">
+        <v>8.4</v>
+      </c>
+      <c r="BK14">
+        <v>4.4</v>
+      </c>
+      <c r="BL14">
+        <v>38</v>
+      </c>
+      <c r="BM14">
+        <v>7.4</v>
+      </c>
+      <c r="BN14">
+        <v>6.8</v>
+      </c>
+      <c r="BO14">
+        <v>5.2</v>
+      </c>
+      <c r="BP14">
+        <v>12.5</v>
+      </c>
+      <c r="BQ14">
+        <v>5.3</v>
+      </c>
+      <c r="BR14">
         <v>15.5</v>
       </c>
-      <c r="BE14">
+      <c r="BS14">
+        <v>5.8</v>
+      </c>
+      <c r="BT14">
+        <v>9.4</v>
+      </c>
+      <c r="BU14">
+        <v>4.7</v>
+      </c>
+      <c r="BV14">
         <v>23</v>
       </c>
-      <c r="BF14">
-        <v>4.1</v>
-      </c>
-      <c r="BG14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.04</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.04</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.04</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>1.04</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>1.04</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.04</v>
-      </c>
-      <c r="BT14">
-        <v>1000</v>
-      </c>
-      <c r="BU14">
-        <v>1.04</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB14" t="s">
         <v>181</v>
@@ -4299,22 +4299,22 @@
         <v>157</v>
       </c>
       <c r="F15">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G15">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H15">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K15">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L15">
         <v>1.21</v>
@@ -4323,7 +4323,7 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="O15">
         <v>1.12</v>
@@ -4335,88 +4335,88 @@
         <v>1.43</v>
       </c>
       <c r="R15">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="S15">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="V15">
         <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ15">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT15">
         <v>13.5</v>
@@ -4428,10 +4428,10 @@
         <v>12.5</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY15">
         <v>8.800000000000001</v>
@@ -4440,10 +4440,10 @@
         <v>11</v>
       </c>
       <c r="BA15">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="BB15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC15">
         <v>12.5</v>
@@ -4452,73 +4452,73 @@
         <v>16</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF15">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG15">
         <v>13.5</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="CB15" t="s">
         <v>181</v>
@@ -4544,19 +4544,19 @@
         <v>2.9</v>
       </c>
       <c r="G16">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="H16">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I16">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="J16">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K16">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L16">
         <v>1.52</v>
@@ -4565,76 +4565,76 @@
         <v>1.1</v>
       </c>
       <c r="N16">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="O16">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P16">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q16">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R16">
         <v>1.21</v>
       </c>
       <c r="S16">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T16">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U16">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V16">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W16">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z16">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA16">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE16">
         <v>40</v>
       </c>
       <c r="AF16">
+        <v>21</v>
+      </c>
+      <c r="AG16">
+        <v>15</v>
+      </c>
+      <c r="AH16">
         <v>22</v>
       </c>
-      <c r="AG16">
-        <v>15.5</v>
-      </c>
-      <c r="AH16">
-        <v>23</v>
-      </c>
       <c r="AI16">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AJ16">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AK16">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL16">
         <v>70</v>
@@ -4643,37 +4643,37 @@
         <v>580</v>
       </c>
       <c r="AN16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO16">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP16">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AQ16">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AR16">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AS16">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AT16">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AU16">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AV16">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AW16">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AX16">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AY16">
         <v>6.2</v>
@@ -4682,25 +4682,25 @@
         <v>9</v>
       </c>
       <c r="BA16">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB16">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC16">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD16">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE16">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BF16">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG16">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BH16">
         <v>3</v>
@@ -4736,7 +4736,7 @@
         <v>50</v>
       </c>
       <c r="BS16">
-        <v>2.14</v>
+        <v>7.4</v>
       </c>
       <c r="BT16">
         <v>5.9</v>
@@ -4783,64 +4783,64 @@
         <v>159</v>
       </c>
       <c r="F17">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G17">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I17">
         <v>5</v>
       </c>
       <c r="J17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K17">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L17">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P17">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q17">
         <v>1.4</v>
       </c>
       <c r="R17">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S17">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T17">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="U17">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="V17">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W17">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="X17">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Y17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z17">
         <v>50</v>
@@ -4849,10 +4849,10 @@
         <v>100</v>
       </c>
       <c r="AB17">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AC17">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD17">
         <v>23</v>
@@ -4861,19 +4861,19 @@
         <v>50</v>
       </c>
       <c r="AF17">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG17">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH17">
         <v>19</v>
       </c>
       <c r="AI17">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ17">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK17">
         <v>19.5</v>
@@ -4888,34 +4888,34 @@
         <v>7.2</v>
       </c>
       <c r="AO17">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AQ17">
         <v>20</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT17">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU17">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AV17">
         <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX17">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY17">
         <v>8.4</v>
@@ -4924,7 +4924,7 @@
         <v>11.5</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB17">
         <v>15</v>
@@ -4936,73 +4936,73 @@
         <v>16.5</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF17">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG17">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BH17">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BI17">
         <v>4</v>
       </c>
       <c r="BJ17">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK17">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>42</v>
+        <v>9.4</v>
       </c>
       <c r="BN17">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO17">
         <v>4</v>
       </c>
       <c r="BP17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ17">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BR17">
         <v>19</v>
       </c>
       <c r="BS17">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BT17">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU17">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV17">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BX17">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BZ17">
         <v>11.5</v>
       </c>
       <c r="CA17">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="CB17" t="s">
         <v>181</v>
@@ -5025,58 +5025,58 @@
         <v>160</v>
       </c>
       <c r="F18">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G18">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I18">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L18">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M18">
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O18">
         <v>1.26</v>
       </c>
       <c r="P18">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q18">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R18">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S18">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T18">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U18">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V18">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W18">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X18">
         <v>22</v>
@@ -5085,28 +5085,28 @@
         <v>27</v>
       </c>
       <c r="Z18">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AA18">
         <v>700</v>
       </c>
       <c r="AB18">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AC18">
         <v>10.5</v>
       </c>
       <c r="AD18">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE18">
         <v>240</v>
       </c>
       <c r="AF18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH18">
         <v>26</v>
@@ -5115,76 +5115,76 @@
         <v>230</v>
       </c>
       <c r="AJ18">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK18">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL18">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM18">
         <v>580</v>
       </c>
       <c r="AN18">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO18">
         <v>130</v>
       </c>
       <c r="AP18">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ18">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AR18">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS18">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AT18">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AU18">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AV18">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AW18">
+        <v>6.6</v>
+      </c>
+      <c r="AX18">
+        <v>4.2</v>
+      </c>
+      <c r="AY18">
+        <v>4.2</v>
+      </c>
+      <c r="AZ18">
         <v>5.6</v>
       </c>
-      <c r="AX18">
-        <v>3.85</v>
-      </c>
-      <c r="AY18">
-        <v>3.85</v>
-      </c>
-      <c r="AZ18">
-        <v>4.8</v>
-      </c>
       <c r="BA18">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB18">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BC18">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD18">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE18">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF18">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BG18">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH18">
         <v>3.95</v>
@@ -5267,16 +5267,16 @@
         <v>161</v>
       </c>
       <c r="F19">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G19">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H19">
         <v>10</v>
       </c>
       <c r="I19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J19">
         <v>5.5</v>
@@ -5291,13 +5291,13 @@
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P19">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q19">
         <v>1.73</v>
@@ -5309,7 +5309,7 @@
         <v>2.84</v>
       </c>
       <c r="T19">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U19">
         <v>1.84</v>
@@ -5318,19 +5318,19 @@
         <v>1.1</v>
       </c>
       <c r="W19">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X19">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AA19">
-        <v>440</v>
+        <v>370</v>
       </c>
       <c r="AB19">
         <v>8.800000000000001</v>
@@ -5339,10 +5339,10 @@
         <v>12.5</v>
       </c>
       <c r="AD19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE19">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF19">
         <v>8</v>
@@ -5351,10 +5351,10 @@
         <v>10.5</v>
       </c>
       <c r="AH19">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI19">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ19">
         <v>10.5</v>
@@ -5366,52 +5366,52 @@
         <v>40</v>
       </c>
       <c r="AM19">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN19">
         <v>5.4</v>
       </c>
       <c r="AO19">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AP19">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AR19">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AS19">
         <v>70</v>
       </c>
       <c r="AT19">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV19">
         <v>34</v>
       </c>
       <c r="AW19">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AX19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY19">
         <v>10</v>
       </c>
       <c r="AZ19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA19">
         <v>110</v>
       </c>
       <c r="BB19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC19">
         <v>14</v>
@@ -5429,7 +5429,7 @@
         <v>150</v>
       </c>
       <c r="BH19">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI19">
         <v>3.7</v>
@@ -5441,46 +5441,46 @@
         <v>10.5</v>
       </c>
       <c r="BL19">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="BM19">
         <v>22</v>
       </c>
       <c r="BN19">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BO19">
         <v>3.55</v>
       </c>
       <c r="BP19">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BQ19">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS19">
         <v>21</v>
       </c>
       <c r="BT19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BU19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BV19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BW19">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="BX19">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BY19">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BZ19">
         <v>13</v>
@@ -5509,16 +5509,16 @@
         <v>162</v>
       </c>
       <c r="F20">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G20">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H20">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I20">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J20">
         <v>2.9</v>
@@ -5533,43 +5533,43 @@
         <v>1.14</v>
       </c>
       <c r="N20">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O20">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P20">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q20">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R20">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S20">
         <v>5.3</v>
       </c>
       <c r="T20">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U20">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="V20">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W20">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Z20">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA20">
         <v>55</v>
@@ -5581,34 +5581,34 @@
         <v>7.4</v>
       </c>
       <c r="AD20">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE20">
         <v>38</v>
       </c>
       <c r="AF20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG20">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH20">
         <v>23</v>
       </c>
       <c r="AI20">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AJ20">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AK20">
         <v>65</v>
       </c>
       <c r="AL20">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="AM20">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN20">
         <v>75</v>
@@ -5617,10 +5617,10 @@
         <v>40</v>
       </c>
       <c r="AP20">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ20">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR20">
         <v>12.5</v>
@@ -5629,106 +5629,106 @@
         <v>29</v>
       </c>
       <c r="AT20">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU20">
         <v>6</v>
       </c>
       <c r="AV20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW20">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AX20">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY20">
         <v>13</v>
       </c>
       <c r="AZ20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA20">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="BB20">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="BC20">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BD20">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BE20">
-        <v>9.4</v>
+        <v>65</v>
       </c>
       <c r="BF20">
-        <v>8.6</v>
+        <v>46</v>
       </c>
       <c r="BG20">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="BH20">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BI20">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ20">
         <v>11.5</v>
       </c>
       <c r="BK20">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BN20">
         <v>6.6</v>
       </c>
       <c r="BO20">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BP20">
         <v>34</v>
       </c>
       <c r="BQ20">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BT20">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU20">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BV20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW20">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB20" t="s">
         <v>181</v>
@@ -5751,97 +5751,97 @@
         <v>163</v>
       </c>
       <c r="F21">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G21">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H21">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="I21">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J21">
         <v>4.5</v>
       </c>
       <c r="K21">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L21">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M21">
         <v>1.01</v>
       </c>
       <c r="N21">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>1.08</v>
       </c>
       <c r="P21">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q21">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="R21">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="S21">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="T21">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="U21">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="V21">
         <v>1.65</v>
       </c>
       <c r="W21">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X21">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="Y21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z21">
         <v>32</v>
       </c>
       <c r="AA21">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AC21">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AD21">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE21">
         <v>23</v>
       </c>
       <c r="AF21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG21">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ21">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK21">
         <v>25</v>
@@ -5850,127 +5850,127 @@
         <v>26</v>
       </c>
       <c r="AM21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AN21">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AO21">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AP21">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="AQ21">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="AR21">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="AS21">
         <v>7</v>
       </c>
       <c r="AT21">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="AU21">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="AV21">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW21">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="AX21">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="AY21">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="AZ21">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA21">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BB21">
+        <v>4</v>
+      </c>
+      <c r="BC21">
+        <v>19.5</v>
+      </c>
+      <c r="BD21">
+        <v>19</v>
+      </c>
+      <c r="BE21">
+        <v>13.5</v>
+      </c>
+      <c r="BF21">
+        <v>7</v>
+      </c>
+      <c r="BG21">
+        <v>6.4</v>
+      </c>
+      <c r="BH21">
+        <v>7</v>
+      </c>
+      <c r="BI21">
+        <v>5.2</v>
+      </c>
+      <c r="BJ21">
+        <v>8.4</v>
+      </c>
+      <c r="BK21">
+        <v>2.98</v>
+      </c>
+      <c r="BL21">
+        <v>42</v>
+      </c>
+      <c r="BM21">
+        <v>4.1</v>
+      </c>
+      <c r="BN21">
+        <v>7.6</v>
+      </c>
+      <c r="BO21">
+        <v>5.7</v>
+      </c>
+      <c r="BP21">
+        <v>17</v>
+      </c>
+      <c r="BQ21">
+        <v>3.65</v>
+      </c>
+      <c r="BR21">
+        <v>19</v>
+      </c>
+      <c r="BS21">
+        <v>3.7</v>
+      </c>
+      <c r="BT21">
         <v>7.2</v>
       </c>
-      <c r="BC21">
-        <v>6.4</v>
-      </c>
-      <c r="BD21">
-        <v>6.4</v>
-      </c>
-      <c r="BE21">
-        <v>6.8</v>
-      </c>
-      <c r="BF21">
-        <v>4.2</v>
-      </c>
-      <c r="BG21">
-        <v>5.9</v>
-      </c>
-      <c r="BH21">
-        <v>7.2</v>
-      </c>
-      <c r="BI21">
-        <v>5.4</v>
-      </c>
-      <c r="BJ21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BK21">
-        <v>6</v>
-      </c>
-      <c r="BL21">
-        <v>40</v>
-      </c>
-      <c r="BM21">
-        <v>8</v>
-      </c>
-      <c r="BN21">
-        <v>7.8</v>
-      </c>
-      <c r="BO21">
-        <v>4.4</v>
-      </c>
-      <c r="BP21">
-        <v>17.5</v>
-      </c>
-      <c r="BQ21">
-        <v>6.4</v>
-      </c>
-      <c r="BR21">
+      <c r="BU21">
+        <v>5.5</v>
+      </c>
+      <c r="BV21">
+        <v>16</v>
+      </c>
+      <c r="BW21">
+        <v>3.6</v>
+      </c>
+      <c r="BX21">
         <v>18.5</v>
       </c>
-      <c r="BS21">
-        <v>6.4</v>
-      </c>
-      <c r="BT21">
-        <v>7.4</v>
-      </c>
-      <c r="BU21">
-        <v>4.2</v>
-      </c>
-      <c r="BV21">
-        <v>15.5</v>
-      </c>
-      <c r="BW21">
-        <v>6</v>
-      </c>
-      <c r="BX21">
-        <v>17.5</v>
-      </c>
       <c r="BY21">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="BZ21">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB21" t="s">
         <v>181</v>
@@ -5993,25 +5993,25 @@
         <v>164</v>
       </c>
       <c r="F22">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G22">
         <v>2.08</v>
       </c>
       <c r="H22">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I22">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J22">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K22">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L22">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M22">
         <v>1.09</v>
@@ -6020,34 +6020,34 @@
         <v>3.3</v>
       </c>
       <c r="O22">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P22">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q22">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R22">
         <v>1.29</v>
       </c>
       <c r="S22">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T22">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U22">
         <v>1.96</v>
       </c>
       <c r="V22">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W22">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X22">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y22">
         <v>14</v>
@@ -6059,28 +6059,28 @@
         <v>500</v>
       </c>
       <c r="AB22">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC22">
         <v>7.8</v>
       </c>
       <c r="AD22">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE22">
         <v>85</v>
       </c>
       <c r="AF22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH22">
         <v>24</v>
       </c>
       <c r="AI22">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="AJ22">
         <v>29</v>
@@ -6089,10 +6089,10 @@
         <v>32</v>
       </c>
       <c r="AL22">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM22">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN22">
         <v>23</v>
@@ -6101,13 +6101,13 @@
         <v>180</v>
       </c>
       <c r="AP22">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ22">
         <v>12</v>
       </c>
       <c r="AR22">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS22">
         <v>70</v>
@@ -6116,7 +6116,7 @@
         <v>7</v>
       </c>
       <c r="AU22">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV22">
         <v>15.5</v>
@@ -6128,7 +6128,7 @@
         <v>10.5</v>
       </c>
       <c r="AY22">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22">
         <v>17</v>
@@ -6137,16 +6137,16 @@
         <v>46</v>
       </c>
       <c r="BB22">
+        <v>18</v>
+      </c>
+      <c r="BC22">
         <v>21</v>
-      </c>
-      <c r="BC22">
-        <v>20</v>
       </c>
       <c r="BD22">
         <v>30</v>
       </c>
       <c r="BE22">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="BF22">
         <v>16</v>
@@ -6158,10 +6158,10 @@
         <v>3.45</v>
       </c>
       <c r="BI22">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="BJ22">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK22">
         <v>8.199999999999999</v>
@@ -6170,7 +6170,7 @@
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BN22">
         <v>4.6</v>
@@ -6182,37 +6182,37 @@
         <v>17.5</v>
       </c>
       <c r="BQ22">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BR22">
+        <v>36</v>
+      </c>
+      <c r="BS22">
+        <v>7.4</v>
+      </c>
+      <c r="BT22">
+        <v>7.6</v>
+      </c>
+      <c r="BU22">
+        <v>5.9</v>
+      </c>
+      <c r="BV22">
+        <v>46</v>
+      </c>
+      <c r="BW22">
+        <v>7.8</v>
+      </c>
+      <c r="BX22">
+        <v>60</v>
+      </c>
+      <c r="BY22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ22">
         <v>38</v>
       </c>
-      <c r="BS22">
-        <v>6.6</v>
-      </c>
-      <c r="BT22">
-        <v>7.8</v>
-      </c>
-      <c r="BU22">
-        <v>6.2</v>
-      </c>
-      <c r="BV22">
-        <v>48</v>
-      </c>
-      <c r="BW22">
-        <v>6.8</v>
-      </c>
-      <c r="BX22">
-        <v>1000</v>
-      </c>
-      <c r="BY22">
-        <v>7</v>
-      </c>
-      <c r="BZ22">
-        <v>36</v>
-      </c>
       <c r="CA22">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB22" t="s">
         <v>181</v>
@@ -6235,13 +6235,13 @@
         <v>165</v>
       </c>
       <c r="F23">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G23">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H23">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I23">
         <v>3.7</v>
@@ -6253,7 +6253,7 @@
         <v>3.25</v>
       </c>
       <c r="L23">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M23">
         <v>1.14</v>
@@ -6268,7 +6268,7 @@
         <v>1.48</v>
       </c>
       <c r="Q23">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="R23">
         <v>1.16</v>
@@ -6277,7 +6277,7 @@
         <v>6.4</v>
       </c>
       <c r="T23">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="U23">
         <v>1.66</v>
@@ -6286,7 +6286,7 @@
         <v>1.37</v>
       </c>
       <c r="W23">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X23">
         <v>7.8</v>
@@ -6295,19 +6295,19 @@
         <v>9.4</v>
       </c>
       <c r="Z23">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA23">
         <v>85</v>
       </c>
       <c r="AB23">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC23">
         <v>7.6</v>
       </c>
       <c r="AD23">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE23">
         <v>85</v>
@@ -6319,7 +6319,7 @@
         <v>13</v>
       </c>
       <c r="AH23">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI23">
         <v>100</v>
@@ -6328,10 +6328,10 @@
         <v>38</v>
       </c>
       <c r="AK23">
+        <v>40</v>
+      </c>
+      <c r="AL23">
         <v>80</v>
-      </c>
-      <c r="AL23">
-        <v>160</v>
       </c>
       <c r="AM23">
         <v>500</v>
@@ -6346,7 +6346,7 @@
         <v>7</v>
       </c>
       <c r="AQ23">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR23">
         <v>20</v>
@@ -6358,13 +6358,13 @@
         <v>6.4</v>
       </c>
       <c r="AU23">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV23">
         <v>15.5</v>
       </c>
       <c r="AW23">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX23">
         <v>11.5</v>
@@ -6373,7 +6373,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ23">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA23">
         <v>60</v>
@@ -6385,76 +6385,76 @@
         <v>32</v>
       </c>
       <c r="BD23">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE23">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="BF23">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BG23">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BH23">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BI23">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BJ23">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BK23">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BN23">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BO23">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BP23">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BQ23">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR23">
         <v>60</v>
       </c>
       <c r="BS23">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BT23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BU23">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV23">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW23">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY23">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BZ23">
         <v>70</v>
       </c>
       <c r="CA23">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="CB23" t="s">
         <v>181</v>
@@ -6477,22 +6477,22 @@
         <v>166</v>
       </c>
       <c r="F24">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G24">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H24">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I24">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="J24">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K24">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L24">
         <v>1.55</v>
@@ -6501,13 +6501,13 @@
         <v>1.12</v>
       </c>
       <c r="N24">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O24">
         <v>1.52</v>
       </c>
       <c r="P24">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q24">
         <v>2.6</v>
@@ -6519,25 +6519,25 @@
         <v>5.3</v>
       </c>
       <c r="T24">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U24">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V24">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="W24">
         <v>1.2</v>
       </c>
       <c r="X24">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y24">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="Z24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA24">
         <v>21</v>
@@ -6555,7 +6555,7 @@
         <v>25</v>
       </c>
       <c r="AF24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG24">
         <v>23</v>
@@ -6567,22 +6567,22 @@
         <v>70</v>
       </c>
       <c r="AJ24">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AK24">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AL24">
         <v>140</v>
       </c>
       <c r="AM24">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN24">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AO24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP24">
         <v>8.4</v>
@@ -6591,7 +6591,7 @@
         <v>6</v>
       </c>
       <c r="AR24">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS24">
         <v>18</v>
@@ -6600,19 +6600,19 @@
         <v>12</v>
       </c>
       <c r="AU24">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV24">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW24">
         <v>22</v>
       </c>
       <c r="AX24">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AY24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ24">
         <v>24</v>
@@ -6621,82 +6621,82 @@
         <v>50</v>
       </c>
       <c r="BB24">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC24">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BD24">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="BE24">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="BF24">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="BG24">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BH24">
         <v>3.1</v>
       </c>
       <c r="BI24">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BJ24">
         <v>12</v>
       </c>
       <c r="BK24">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BN24">
         <v>9</v>
       </c>
       <c r="BO24">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BQ24">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BR24">
         <v>90</v>
       </c>
       <c r="BS24">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT24">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BU24">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV24">
         <v>14.5</v>
       </c>
       <c r="BW24">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY24">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ24">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="CA24">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB24" t="s">
         <v>181</v>
@@ -6719,10 +6719,10 @@
         <v>167</v>
       </c>
       <c r="F25">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G25">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H25">
         <v>6.2</v>
@@ -6731,25 +6731,25 @@
         <v>6.8</v>
       </c>
       <c r="J25">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K25">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L25">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M25">
         <v>1.09</v>
       </c>
       <c r="N25">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O25">
         <v>1.41</v>
       </c>
       <c r="P25">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q25">
         <v>2.24</v>
@@ -6761,7 +6761,7 @@
         <v>4.3</v>
       </c>
       <c r="T25">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U25">
         <v>1.79</v>
@@ -6770,10 +6770,10 @@
         <v>1.17</v>
       </c>
       <c r="W25">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y25">
         <v>18</v>
@@ -6806,7 +6806,7 @@
         <v>25</v>
       </c>
       <c r="AI25">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ25">
         <v>17.5</v>
@@ -6848,10 +6848,10 @@
         <v>20</v>
       </c>
       <c r="AW25">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX25">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY25">
         <v>9.199999999999999</v>
@@ -6860,7 +6860,7 @@
         <v>21</v>
       </c>
       <c r="BA25">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB25">
         <v>14</v>
@@ -6869,76 +6869,76 @@
         <v>17.5</v>
       </c>
       <c r="BD25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE25">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF25">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG25">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH25">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="BI25">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ25">
         <v>12</v>
       </c>
       <c r="BK25">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BN25">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO25">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP25">
         <v>12</v>
       </c>
       <c r="BQ25">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BR25">
         <v>32</v>
       </c>
       <c r="BS25">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BT25">
         <v>9.6</v>
       </c>
       <c r="BU25">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BV25">
         <v>65</v>
       </c>
       <c r="BW25">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BX25">
         <v>75</v>
       </c>
       <c r="BY25">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BZ25">
         <v>27</v>
       </c>
       <c r="CA25">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="CB25" t="s">
         <v>181</v>
@@ -6961,22 +6961,22 @@
         <v>168</v>
       </c>
       <c r="F26">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="G26">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H26">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="J26">
         <v>3.2</v>
       </c>
       <c r="K26">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L26">
         <v>1.49</v>
@@ -6991,196 +6991,196 @@
         <v>1.42</v>
       </c>
       <c r="P26">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q26">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R26">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S26">
         <v>4.4</v>
       </c>
       <c r="T26">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U26">
         <v>2</v>
       </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W26">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X26">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Y26">
+        <v>10.5</v>
+      </c>
+      <c r="Z26">
+        <v>19.5</v>
+      </c>
+      <c r="AA26">
+        <v>55</v>
+      </c>
+      <c r="AB26">
+        <v>9.6</v>
+      </c>
+      <c r="AC26">
+        <v>7.4</v>
+      </c>
+      <c r="AD26">
+        <v>14</v>
+      </c>
+      <c r="AE26">
+        <v>40</v>
+      </c>
+      <c r="AF26">
+        <v>17.5</v>
+      </c>
+      <c r="AG26">
         <v>12.5</v>
       </c>
-      <c r="Z26">
-        <v>24</v>
-      </c>
-      <c r="AA26">
-        <v>60</v>
-      </c>
-      <c r="AB26">
-        <v>11.5</v>
-      </c>
-      <c r="AC26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD26">
-        <v>16.5</v>
-      </c>
-      <c r="AE26">
-        <v>44</v>
-      </c>
-      <c r="AF26">
-        <v>22</v>
-      </c>
-      <c r="AG26">
-        <v>15.5</v>
-      </c>
       <c r="AH26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI26">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="AJ26">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AK26">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL26">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM26">
         <v>580</v>
       </c>
       <c r="AN26">
+        <v>34</v>
+      </c>
+      <c r="AO26">
         <v>42</v>
-      </c>
-      <c r="AO26">
-        <v>46</v>
       </c>
       <c r="AP26">
         <v>9.6</v>
       </c>
       <c r="AQ26">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR26">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS26">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="AT26">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU26">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV26">
+        <v>12</v>
+      </c>
+      <c r="AW26">
+        <v>34</v>
+      </c>
+      <c r="AX26">
+        <v>15</v>
+      </c>
+      <c r="AY26">
         <v>11.5</v>
       </c>
-      <c r="AW26">
-        <v>16.5</v>
-      </c>
-      <c r="AX26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY26">
-        <v>11</v>
-      </c>
       <c r="AZ26">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BA26">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BB26">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="BC26">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BD26">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BE26">
-        <v>4.8</v>
+        <v>14</v>
       </c>
       <c r="BF26">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="BG26">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="BH26">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BI26">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="BJ26">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK26">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BN26">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO26">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP26">
         <v>29</v>
       </c>
       <c r="BQ26">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BR26">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS26">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BU26">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV26">
         <v>29</v>
       </c>
       <c r="BW26">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX26">
         <v>50</v>
       </c>
       <c r="BY26">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ26">
         <v>44</v>
       </c>
       <c r="CA26">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="CB26" t="s">
         <v>181</v>
@@ -7203,25 +7203,25 @@
         <v>169</v>
       </c>
       <c r="F27">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G27">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H27">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I27">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J27">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K27">
         <v>3.45</v>
       </c>
       <c r="L27">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M27">
         <v>1.09</v>
@@ -7230,31 +7230,31 @@
         <v>3.15</v>
       </c>
       <c r="O27">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P27">
         <v>1.7</v>
       </c>
       <c r="Q27">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R27">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S27">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T27">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U27">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="V27">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7448,13 +7448,13 @@
         <v>2.44</v>
       </c>
       <c r="G28">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="H28">
         <v>2.62</v>
       </c>
       <c r="I28">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J28">
         <v>3.85</v>
@@ -7496,7 +7496,7 @@
         <v>1.54</v>
       </c>
       <c r="W28">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X28">
         <v>29</v>
@@ -7505,13 +7505,13 @@
         <v>19.5</v>
       </c>
       <c r="Z28">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA28">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AB28">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC28">
         <v>10.5</v>
@@ -7529,7 +7529,7 @@
         <v>15</v>
       </c>
       <c r="AH28">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AI28">
         <v>34</v>
@@ -7550,28 +7550,28 @@
         <v>18</v>
       </c>
       <c r="AO28">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP28">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="AQ28">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="AR28">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AS28">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT28">
         <v>13</v>
       </c>
       <c r="AU28">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV28">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AW28">
         <v>19</v>
@@ -7583,28 +7583,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ28">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA28">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB28">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC28">
         <v>20</v>
       </c>
       <c r="BD28">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE28">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BF28">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="BG28">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="BH28">
         <v>4.5</v>
@@ -7690,7 +7690,7 @@
         <v>1.69</v>
       </c>
       <c r="G29">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H29">
         <v>4.9</v>
@@ -7702,7 +7702,7 @@
         <v>4.2</v>
       </c>
       <c r="K29">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L29">
         <v>1.34</v>
@@ -7714,10 +7714,10 @@
         <v>4.5</v>
       </c>
       <c r="O29">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P29">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q29">
         <v>1.75</v>
@@ -7738,7 +7738,7 @@
         <v>1.22</v>
       </c>
       <c r="W29">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X29">
         <v>22</v>
@@ -7750,10 +7750,10 @@
         <v>44</v>
       </c>
       <c r="AA29">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB29">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC29">
         <v>11.5</v>
@@ -7765,16 +7765,16 @@
         <v>70</v>
       </c>
       <c r="AF29">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG29">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH29">
         <v>24</v>
       </c>
       <c r="AI29">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AJ29">
         <v>21</v>
@@ -7783,31 +7783,31 @@
         <v>21</v>
       </c>
       <c r="AL29">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AM29">
         <v>110</v>
       </c>
       <c r="AN29">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO29">
         <v>75</v>
       </c>
       <c r="AP29">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AQ29">
         <v>16.5</v>
       </c>
       <c r="AR29">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AS29">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AT29">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU29">
         <v>8.800000000000001</v>
@@ -7816,19 +7816,19 @@
         <v>16.5</v>
       </c>
       <c r="AW29">
-        <v>4.6</v>
+        <v>26</v>
       </c>
       <c r="AX29">
         <v>9.800000000000001</v>
       </c>
       <c r="AY29">
-        <v>3.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ29">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA29">
-        <v>4.6</v>
+        <v>38</v>
       </c>
       <c r="BB29">
         <v>15</v>
@@ -7837,16 +7837,16 @@
         <v>15</v>
       </c>
       <c r="BD29">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="BE29">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF29">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG29">
-        <v>4.6</v>
+        <v>22</v>
       </c>
       <c r="BH29">
         <v>3.9</v>
@@ -7929,19 +7929,19 @@
         <v>172</v>
       </c>
       <c r="F30">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G30">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="H30">
+        <v>4.7</v>
+      </c>
+      <c r="I30">
         <v>4.9</v>
       </c>
-      <c r="I30">
-        <v>5</v>
-      </c>
       <c r="J30">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K30">
         <v>4.4</v>
@@ -7962,34 +7962,34 @@
         <v>2.52</v>
       </c>
       <c r="Q30">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R30">
         <v>1.6</v>
       </c>
       <c r="S30">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T30">
         <v>1.66</v>
       </c>
       <c r="U30">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V30">
         <v>1.25</v>
       </c>
       <c r="W30">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X30">
         <v>23</v>
       </c>
       <c r="Y30">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z30">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA30">
         <v>1000</v>
@@ -7998,43 +7998,43 @@
         <v>12</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD30">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE30">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF30">
         <v>13</v>
       </c>
       <c r="AG30">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH30">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI30">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ30">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK30">
         <v>16.5</v>
       </c>
       <c r="AL30">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM30">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO30">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP30">
         <v>20</v>
@@ -8046,19 +8046,19 @@
         <v>36</v>
       </c>
       <c r="AS30">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AT30">
         <v>10.5</v>
       </c>
       <c r="AU30">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV30">
         <v>17</v>
       </c>
       <c r="AW30">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX30">
         <v>11.5</v>
@@ -8067,25 +8067,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ30">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA30">
         <v>44</v>
       </c>
       <c r="BB30">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC30">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD30">
         <v>24</v>
       </c>
       <c r="BE30">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BF30">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG30">
         <v>36</v>
@@ -8097,7 +8097,7 @@
         <v>3.5</v>
       </c>
       <c r="BJ30">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK30">
         <v>4.9</v>
@@ -8106,19 +8106,19 @@
         <v>90</v>
       </c>
       <c r="BM30">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN30">
         <v>4.9</v>
       </c>
       <c r="BO30">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BP30">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ30">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR30">
         <v>22</v>
@@ -8127,28 +8127,28 @@
         <v>7</v>
       </c>
       <c r="BT30">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU30">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV30">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW30">
         <v>8</v>
       </c>
       <c r="BX30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY30">
         <v>8.199999999999999</v>
       </c>
       <c r="BZ30">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA30">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB30" t="s">
         <v>181</v>
@@ -8171,16 +8171,16 @@
         <v>173</v>
       </c>
       <c r="F31">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="G31">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="H31">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="I31">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="J31">
         <v>4.1</v>
@@ -8189,7 +8189,7 @@
         <v>4.3</v>
       </c>
       <c r="L31">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M31">
         <v>1.02</v>
@@ -8216,25 +8216,25 @@
         <v>1.41</v>
       </c>
       <c r="U31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V31">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="W31">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X31">
         <v>34</v>
       </c>
       <c r="Y31">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z31">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB31">
         <v>24</v>
@@ -8246,13 +8246,13 @@
         <v>12.5</v>
       </c>
       <c r="AE31">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AF31">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG31">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH31">
         <v>13</v>
@@ -8261,22 +8261,22 @@
         <v>23</v>
       </c>
       <c r="AJ31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK31">
         <v>26</v>
       </c>
       <c r="AL31">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM31">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AN31">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO31">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AP31">
         <v>30</v>
@@ -8288,25 +8288,25 @@
         <v>20</v>
       </c>
       <c r="AS31">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT31">
         <v>22</v>
       </c>
       <c r="AU31">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW31">
         <v>18</v>
       </c>
       <c r="AX31">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY31">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ31">
         <v>12</v>
@@ -8315,25 +8315,25 @@
         <v>21</v>
       </c>
       <c r="BB31">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BC31">
+        <v>23</v>
+      </c>
+      <c r="BD31">
         <v>24</v>
-      </c>
-      <c r="BD31">
-        <v>25</v>
       </c>
       <c r="BE31">
         <v>36</v>
       </c>
       <c r="BF31">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG31">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH31">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI31">
         <v>4.1</v>
@@ -8342,55 +8342,55 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK31">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN31">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO31">
         <v>6</v>
       </c>
       <c r="BP31">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ31">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BR31">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS31">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BT31">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BU31">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW31">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BY31">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA31">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB31" t="s">
         <v>181</v>
@@ -8413,22 +8413,22 @@
         <v>174</v>
       </c>
       <c r="F32">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="G32">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="H32">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="I32">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="J32">
         <v>3.7</v>
       </c>
       <c r="K32">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L32">
         <v>1.36</v>
@@ -8440,19 +8440,19 @@
         <v>4.6</v>
       </c>
       <c r="O32">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P32">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q32">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R32">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S32">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T32">
         <v>1.65</v>
@@ -8461,37 +8461,37 @@
         <v>2.44</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W32">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="X32">
         <v>17.5</v>
       </c>
       <c r="Y32">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z32">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA32">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB32">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC32">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD32">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE32">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF32">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG32">
         <v>11.5</v>
@@ -8503,22 +8503,22 @@
         <v>40</v>
       </c>
       <c r="AJ32">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK32">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL32">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM32">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN32">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO32">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP32">
         <v>16</v>
@@ -8527,25 +8527,25 @@
         <v>13.5</v>
       </c>
       <c r="AR32">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS32">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AT32">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU32">
         <v>7.8</v>
       </c>
       <c r="AV32">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW32">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AX32">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AY32">
         <v>10</v>
@@ -8554,85 +8554,85 @@
         <v>14.5</v>
       </c>
       <c r="BA32">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB32">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC32">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE32">
         <v>55</v>
       </c>
       <c r="BF32">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BG32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH32">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI32">
         <v>3.05</v>
       </c>
       <c r="BJ32">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK32">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BL32">
         <v>110</v>
       </c>
       <c r="BM32">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BN32">
+        <v>5.6</v>
+      </c>
+      <c r="BO32">
+        <v>5</v>
+      </c>
+      <c r="BP32">
+        <v>17</v>
+      </c>
+      <c r="BQ32">
+        <v>4.8</v>
+      </c>
+      <c r="BR32">
+        <v>34</v>
+      </c>
+      <c r="BS32">
+        <v>5.6</v>
+      </c>
+      <c r="BT32">
+        <v>7.6</v>
+      </c>
+      <c r="BU32">
+        <v>4.8</v>
+      </c>
+      <c r="BV32">
+        <v>26</v>
+      </c>
+      <c r="BW32">
         <v>5.3</v>
       </c>
-      <c r="BO32">
-        <v>4.7</v>
-      </c>
-      <c r="BP32">
-        <v>19</v>
-      </c>
-      <c r="BQ32">
-        <v>10</v>
-      </c>
-      <c r="BR32">
-        <v>30</v>
-      </c>
-      <c r="BS32">
-        <v>6.8</v>
-      </c>
-      <c r="BT32">
-        <v>6.6</v>
-      </c>
-      <c r="BU32">
+      <c r="BX32">
+        <v>36</v>
+      </c>
+      <c r="BY32">
+        <v>5.6</v>
+      </c>
+      <c r="BZ32">
+        <v>24</v>
+      </c>
+      <c r="CA32">
         <v>5.2</v>
-      </c>
-      <c r="BV32">
-        <v>29</v>
-      </c>
-      <c r="BW32">
-        <v>6.6</v>
-      </c>
-      <c r="BX32">
-        <v>1000</v>
-      </c>
-      <c r="BY32">
-        <v>6.8</v>
-      </c>
-      <c r="BZ32">
-        <v>21</v>
-      </c>
-      <c r="CA32">
-        <v>6.2</v>
       </c>
       <c r="CB32" t="s">
         <v>181</v>
@@ -8679,28 +8679,28 @@
         <v>1.02</v>
       </c>
       <c r="N33">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="O33">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P33">
+        <v>3.45</v>
+      </c>
+      <c r="Q33">
+        <v>1.39</v>
+      </c>
+      <c r="R33">
+        <v>2</v>
+      </c>
+      <c r="S33">
+        <v>1.95</v>
+      </c>
+      <c r="T33">
+        <v>1.39</v>
+      </c>
+      <c r="U33">
         <v>3.4</v>
-      </c>
-      <c r="Q33">
-        <v>1.4</v>
-      </c>
-      <c r="R33">
-        <v>1.98</v>
-      </c>
-      <c r="S33">
-        <v>1.97</v>
-      </c>
-      <c r="T33">
-        <v>1.4</v>
-      </c>
-      <c r="U33">
-        <v>3.35</v>
       </c>
       <c r="V33">
         <v>1.62</v>
@@ -8709,7 +8709,7 @@
         <v>1.61</v>
       </c>
       <c r="X33">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y33">
         <v>24</v>
@@ -8718,16 +8718,16 @@
         <v>26</v>
       </c>
       <c r="AA33">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB33">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC33">
         <v>12</v>
       </c>
       <c r="AD33">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE33">
         <v>22</v>
@@ -8742,10 +8742,10 @@
         <v>13.5</v>
       </c>
       <c r="AI33">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ33">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK33">
         <v>22</v>
@@ -8757,13 +8757,13 @@
         <v>38</v>
       </c>
       <c r="AN33">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO33">
         <v>10.5</v>
       </c>
       <c r="AP33">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ33">
         <v>20</v>
@@ -8775,10 +8775,10 @@
         <v>38</v>
       </c>
       <c r="AT33">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU33">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV33">
         <v>12</v>
@@ -8790,7 +8790,7 @@
         <v>23</v>
       </c>
       <c r="AY33">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ33">
         <v>12.5</v>
@@ -8811,13 +8811,13 @@
         <v>32</v>
       </c>
       <c r="BF33">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG33">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH33">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BI33">
         <v>4.3</v>
@@ -8826,55 +8826,55 @@
         <v>8.4</v>
       </c>
       <c r="BK33">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="BL33">
         <v>55</v>
       </c>
       <c r="BM33">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BN33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO33">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BP33">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ33">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR33">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BS33">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BT33">
         <v>7</v>
       </c>
       <c r="BU33">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV33">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BW33">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BX33">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BY33">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BZ33">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="CA33">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="CB33" t="s">
         <v>181</v>
@@ -8903,7 +8903,7 @@
         <v>2.42</v>
       </c>
       <c r="H34">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I34">
         <v>3.15</v>
@@ -8921,40 +8921,40 @@
         <v>1.05</v>
       </c>
       <c r="N34">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O34">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P34">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q34">
         <v>1.7</v>
       </c>
       <c r="R34">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S34">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T34">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U34">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
         <v>1.7</v>
       </c>
       <c r="X34">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y34">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z34">
         <v>24</v>
@@ -8963,10 +8963,10 @@
         <v>46</v>
       </c>
       <c r="AB34">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC34">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD34">
         <v>13</v>
@@ -8978,16 +8978,16 @@
         <v>18</v>
       </c>
       <c r="AG34">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH34">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI34">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ34">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK34">
         <v>23</v>
@@ -8996,16 +8996,16 @@
         <v>32</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN34">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP34">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ34">
         <v>14</v>
@@ -9014,34 +9014,34 @@
         <v>20</v>
       </c>
       <c r="AS34">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AT34">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU34">
         <v>8.199999999999999</v>
       </c>
       <c r="AV34">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW34">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX34">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY34">
         <v>10</v>
       </c>
       <c r="AZ34">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA34">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB34">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BC34">
         <v>20</v>
@@ -9050,52 +9050,52 @@
         <v>25</v>
       </c>
       <c r="BE34">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BF34">
         <v>13</v>
       </c>
       <c r="BG34">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH34">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BI34">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BJ34">
         <v>8.800000000000001</v>
       </c>
       <c r="BK34">
+        <v>6.4</v>
+      </c>
+      <c r="BL34">
+        <v>100</v>
+      </c>
+      <c r="BM34">
+        <v>8.4</v>
+      </c>
+      <c r="BN34">
+        <v>5.6</v>
+      </c>
+      <c r="BO34">
         <v>5</v>
-      </c>
-      <c r="BL34">
-        <v>110</v>
-      </c>
-      <c r="BM34">
-        <v>10.5</v>
-      </c>
-      <c r="BN34">
-        <v>5.5</v>
-      </c>
-      <c r="BO34">
-        <v>4.9</v>
       </c>
       <c r="BP34">
         <v>16.5</v>
       </c>
       <c r="BQ34">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR34">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BS34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BT34">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU34">
         <v>5.7</v>
@@ -9104,19 +9104,19 @@
         <v>22</v>
       </c>
       <c r="BW34">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX34">
         <v>29</v>
       </c>
       <c r="BY34">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BZ34">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA34">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="CB34" t="s">
         <v>181</v>
@@ -9139,10 +9139,10 @@
         <v>177</v>
       </c>
       <c r="F35">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G35">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H35">
         <v>4.2</v>
@@ -9154,13 +9154,13 @@
         <v>3.1</v>
       </c>
       <c r="K35">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L35">
         <v>1.61</v>
       </c>
       <c r="M35">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N35">
         <v>2.62</v>
@@ -9172,7 +9172,7 @@
         <v>1.52</v>
       </c>
       <c r="Q35">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
         <v>1.18</v>
@@ -9190,13 +9190,13 @@
         <v>1.29</v>
       </c>
       <c r="W35">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X35">
         <v>8.199999999999999</v>
       </c>
       <c r="Y35">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z35">
         <v>30</v>
@@ -9211,13 +9211,13 @@
         <v>7.6</v>
       </c>
       <c r="AD35">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE35">
         <v>80</v>
       </c>
       <c r="AF35">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG35">
         <v>12</v>
@@ -9226,7 +9226,7 @@
         <v>27</v>
       </c>
       <c r="AI35">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ35">
         <v>30</v>
@@ -9235,7 +9235,7 @@
         <v>32</v>
       </c>
       <c r="AL35">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM35">
         <v>230</v>
@@ -9244,19 +9244,19 @@
         <v>32</v>
       </c>
       <c r="AO35">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP35">
         <v>7.4</v>
       </c>
       <c r="AQ35">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR35">
         <v>25</v>
       </c>
       <c r="AS35">
-        <v>14.5</v>
+        <v>75</v>
       </c>
       <c r="AT35">
         <v>6.2</v>
@@ -9268,7 +9268,7 @@
         <v>17</v>
       </c>
       <c r="AW35">
-        <v>13.5</v>
+        <v>46</v>
       </c>
       <c r="AX35">
         <v>10.5</v>
@@ -9283,7 +9283,7 @@
         <v>12.5</v>
       </c>
       <c r="BB35">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BC35">
         <v>27</v>
@@ -9292,31 +9292,31 @@
         <v>55</v>
       </c>
       <c r="BE35">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF35">
         <v>26</v>
       </c>
       <c r="BG35">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="BH35">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="BI35">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="BJ35">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK35">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BN35">
         <v>4.9</v>
@@ -9325,19 +9325,19 @@
         <v>4.1</v>
       </c>
       <c r="BP35">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ35">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT35">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU35">
         <v>5.2</v>
@@ -9346,19 +9346,19 @@
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="CB35" t="s">
         <v>181</v>
@@ -9381,22 +9381,22 @@
         <v>178</v>
       </c>
       <c r="F36">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G36">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="H36">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I36">
         <v>11.5</v>
       </c>
       <c r="J36">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K36">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L36">
         <v>1.41</v>
@@ -9405,16 +9405,16 @@
         <v>1.07</v>
       </c>
       <c r="N36">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O36">
         <v>1.33</v>
       </c>
       <c r="P36">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q36">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R36">
         <v>1.35</v>
@@ -9423,52 +9423,52 @@
         <v>3.6</v>
       </c>
       <c r="T36">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U36">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V36">
         <v>1.09</v>
       </c>
       <c r="W36">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="X36">
         <v>15.5</v>
       </c>
       <c r="Y36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Z36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AA36">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AB36">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC36">
         <v>11.5</v>
       </c>
       <c r="AD36">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AE36">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="AF36">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AG36">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH36">
         <v>34</v>
       </c>
       <c r="AI36">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AJ36">
         <v>11.5</v>
@@ -9477,130 +9477,130 @@
         <v>17.5</v>
       </c>
       <c r="AL36">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM36">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AN36">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO36">
-        <v>460</v>
+        <v>360</v>
       </c>
       <c r="AP36">
         <v>13</v>
       </c>
       <c r="AQ36">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="AR36">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AS36">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT36">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU36">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV36">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AW36">
+        <v>11.5</v>
+      </c>
+      <c r="AX36">
+        <v>6.6</v>
+      </c>
+      <c r="AY36">
+        <v>9.6</v>
+      </c>
+      <c r="AZ36">
+        <v>30</v>
+      </c>
+      <c r="BA36">
+        <v>12.5</v>
+      </c>
+      <c r="BB36">
         <v>10</v>
       </c>
-      <c r="AX36">
-        <v>6.4</v>
-      </c>
-      <c r="AY36">
-        <v>9</v>
-      </c>
-      <c r="AZ36">
-        <v>27</v>
-      </c>
-      <c r="BA36">
-        <v>10</v>
-      </c>
-      <c r="BB36">
-        <v>9.6</v>
-      </c>
       <c r="BC36">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD36">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE36">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF36">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG36">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH36">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BI36">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="BJ36">
         <v>13.5</v>
       </c>
       <c r="BK36">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN36">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BO36">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BP36">
         <v>8.6</v>
       </c>
       <c r="BQ36">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BR36">
         <v>30</v>
       </c>
       <c r="BS36">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BT36">
         <v>14</v>
       </c>
       <c r="BU36">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BZ36">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA36">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="CB36" t="s">
         <v>181</v>
@@ -9623,22 +9623,22 @@
         <v>179</v>
       </c>
       <c r="F37">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="G37">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="H37">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="I37">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="J37">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K37">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L37">
         <v>1.3</v>
@@ -9647,49 +9647,49 @@
         <v>1.04</v>
       </c>
       <c r="N37">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O37">
         <v>1.2</v>
       </c>
       <c r="P37">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q37">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R37">
         <v>1.64</v>
       </c>
       <c r="S37">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T37">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U37">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="V37">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W37">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X37">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y37">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z37">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA37">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB37">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC37">
         <v>9.4</v>
@@ -9698,13 +9698,13 @@
         <v>12</v>
       </c>
       <c r="AE37">
+        <v>24</v>
+      </c>
+      <c r="AF37">
         <v>23</v>
       </c>
-      <c r="AF37">
-        <v>25</v>
-      </c>
       <c r="AG37">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH37">
         <v>15</v>
@@ -9713,34 +9713,34 @@
         <v>28</v>
       </c>
       <c r="AJ37">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="AK37">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL37">
         <v>32</v>
       </c>
       <c r="AM37">
-        <v>290</v>
+        <v>65</v>
       </c>
       <c r="AN37">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO37">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP37">
         <v>21</v>
       </c>
       <c r="AQ37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR37">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS37">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT37">
         <v>16</v>
@@ -9749,19 +9749,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV37">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW37">
         <v>19</v>
       </c>
       <c r="AX37">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY37">
         <v>12</v>
       </c>
       <c r="AZ37">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA37">
         <v>25</v>
@@ -9770,7 +9770,7 @@
         <v>42</v>
       </c>
       <c r="BC37">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD37">
         <v>28</v>
@@ -9779,70 +9779,70 @@
         <v>46</v>
       </c>
       <c r="BF37">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG37">
         <v>11.5</v>
       </c>
       <c r="BH37">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BI37">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ37">
         <v>8.800000000000001</v>
       </c>
       <c r="BK37">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BL37">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM37">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN37">
         <v>6.8</v>
       </c>
       <c r="BO37">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BP37">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ37">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR37">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS37">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BT37">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BU37">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV37">
         <v>17</v>
       </c>
       <c r="BW37">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BX37">
         <v>24</v>
       </c>
       <c r="BY37">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ37">
         <v>16</v>
       </c>
       <c r="CA37">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB37" t="s">
         <v>181</v>
@@ -9871,7 +9871,7 @@
         <v>2.02</v>
       </c>
       <c r="H38">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I38">
         <v>3.75</v>
@@ -9880,7 +9880,7 @@
         <v>4.2</v>
       </c>
       <c r="K38">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L38">
         <v>1.26</v>
@@ -9895,7 +9895,7 @@
         <v>1.15</v>
       </c>
       <c r="P38">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q38">
         <v>1.48</v>
@@ -9904,13 +9904,13 @@
         <v>1.81</v>
       </c>
       <c r="S38">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T38">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U38">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="V38">
         <v>1.36</v>
@@ -9925,28 +9925,28 @@
         <v>24</v>
       </c>
       <c r="Z38">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA38">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB38">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC38">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD38">
         <v>15.5</v>
       </c>
       <c r="AE38">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF38">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG38">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH38">
         <v>14</v>
@@ -9958,19 +9958,19 @@
         <v>27</v>
       </c>
       <c r="AK38">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL38">
         <v>23</v>
       </c>
       <c r="AM38">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN38">
         <v>8</v>
       </c>
       <c r="AO38">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AP38">
         <v>27</v>
@@ -9979,16 +9979,16 @@
         <v>21</v>
       </c>
       <c r="AR38">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS38">
         <v>55</v>
       </c>
       <c r="AT38">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU38">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV38">
         <v>14.5</v>
@@ -9997,10 +9997,10 @@
         <v>28</v>
       </c>
       <c r="AX38">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY38">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ38">
         <v>13</v>
@@ -10012,10 +10012,10 @@
         <v>24</v>
       </c>
       <c r="BC38">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD38">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE38">
         <v>40</v>
@@ -10024,67 +10024,67 @@
         <v>7.2</v>
       </c>
       <c r="BG38">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH38">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BI38">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BJ38">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK38">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BL38">
         <v>75</v>
       </c>
       <c r="BM38">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BN38">
         <v>5.4</v>
       </c>
       <c r="BO38">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BP38">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BQ38">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BR38">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BS38">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BT38">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU38">
         <v>5.5</v>
       </c>
       <c r="BV38">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BW38">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX38">
         <v>27</v>
       </c>
       <c r="BY38">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BZ38">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CA38">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB38" t="s">
         <v>181</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-19.xlsx
@@ -535,7 +535,7 @@
     <t>New York City</t>
   </si>
   <si>
-    <t>2026-08-19 10:51:58</t>
+    <t>2026-08-19 13:01:38</t>
   </si>
 </sst>
 </file>
@@ -1129,226 +1129,226 @@
         <v>138</v>
       </c>
       <c r="F2">
-        <v>2.3</v>
+        <v>9.6</v>
       </c>
       <c r="G2">
-        <v>2.44</v>
+        <v>11</v>
       </c>
       <c r="H2">
-        <v>3.7</v>
+        <v>1.51</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>1.56</v>
       </c>
       <c r="J2">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.58</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="P2">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="Q2">
+        <v>2.4</v>
+      </c>
+      <c r="R2">
+        <v>1.18</v>
+      </c>
+      <c r="S2">
+        <v>6</v>
+      </c>
+      <c r="T2">
+        <v>1.79</v>
+      </c>
+      <c r="U2">
+        <v>2.08</v>
+      </c>
+      <c r="V2">
         <v>2.78</v>
       </c>
-      <c r="R2">
-        <v>1.17</v>
-      </c>
-      <c r="S2">
-        <v>5.7</v>
-      </c>
-      <c r="T2">
-        <v>2.12</v>
-      </c>
-      <c r="U2">
-        <v>1.72</v>
-      </c>
-      <c r="V2">
-        <v>1.32</v>
-      </c>
       <c r="W2">
-        <v>1.69</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>4.3</v>
+      </c>
+      <c r="Z2">
+        <v>6.8</v>
+      </c>
+      <c r="AA2">
+        <v>25</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>5.3</v>
+      </c>
+      <c r="AD2">
+        <v>10</v>
+      </c>
+      <c r="AE2">
+        <v>36</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>18.5</v>
+      </c>
+      <c r="AH2">
+        <v>28</v>
+      </c>
+      <c r="AI2">
+        <v>95</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>90</v>
+      </c>
+      <c r="AL2">
+        <v>140</v>
+      </c>
+      <c r="AM2">
+        <v>380</v>
+      </c>
+      <c r="AN2">
+        <v>310</v>
+      </c>
+      <c r="AO2">
+        <v>50</v>
+      </c>
+      <c r="AP2">
         <v>8.4</v>
       </c>
-      <c r="Y2">
-        <v>11</v>
-      </c>
-      <c r="Z2">
-        <v>28</v>
-      </c>
-      <c r="AA2">
-        <v>170</v>
-      </c>
-      <c r="AB2">
+      <c r="AQ2">
+        <v>4</v>
+      </c>
+      <c r="AR2">
+        <v>5.8</v>
+      </c>
+      <c r="AS2">
+        <v>17.5</v>
+      </c>
+      <c r="AT2">
+        <v>8.4</v>
+      </c>
+      <c r="AU2">
+        <v>4.6</v>
+      </c>
+      <c r="AV2">
         <v>7.4</v>
       </c>
-      <c r="AC2">
-        <v>7.4</v>
-      </c>
-      <c r="AD2">
-        <v>18.5</v>
-      </c>
-      <c r="AE2">
-        <v>90</v>
-      </c>
-      <c r="AF2">
-        <v>13</v>
-      </c>
-      <c r="AG2">
+      <c r="AW2">
+        <v>24</v>
+      </c>
+      <c r="AX2">
+        <v>8.4</v>
+      </c>
+      <c r="AY2">
         <v>12</v>
       </c>
-      <c r="AH2">
-        <v>27</v>
-      </c>
-      <c r="AI2">
-        <v>230</v>
-      </c>
-      <c r="AJ2">
-        <v>36</v>
-      </c>
-      <c r="AK2">
-        <v>34</v>
-      </c>
-      <c r="AL2">
-        <v>150</v>
-      </c>
-      <c r="AM2">
-        <v>500</v>
-      </c>
-      <c r="AN2">
-        <v>36</v>
-      </c>
-      <c r="AO2">
-        <v>600</v>
-      </c>
-      <c r="AP2">
-        <v>7.2</v>
-      </c>
-      <c r="AQ2">
-        <v>9</v>
-      </c>
-      <c r="AR2">
+      <c r="AZ2">
         <v>19.5</v>
       </c>
-      <c r="AS2">
-        <v>10</v>
-      </c>
-      <c r="AT2">
-        <v>6.2</v>
-      </c>
-      <c r="AU2">
-        <v>6.2</v>
-      </c>
-      <c r="AV2">
-        <v>15</v>
-      </c>
-      <c r="AW2">
-        <v>12</v>
-      </c>
-      <c r="AX2">
-        <v>10.5</v>
-      </c>
-      <c r="AY2">
-        <v>10</v>
-      </c>
-      <c r="AZ2">
-        <v>22</v>
-      </c>
       <c r="BA2">
-        <v>16.5</v>
+        <v>55</v>
       </c>
       <c r="BB2">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="BC2">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="BD2">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BE2">
-        <v>11</v>
+        <v>190</v>
       </c>
       <c r="BF2">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="BG2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BH2">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>173</v>
@@ -1371,226 +1371,226 @@
         <v>139</v>
       </c>
       <c r="F3">
-        <v>1.81</v>
+        <v>6.4</v>
       </c>
       <c r="G3">
-        <v>1.91</v>
+        <v>6.8</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>1.84</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2.68</v>
+        <v>3.65</v>
       </c>
       <c r="O3">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="P3">
         <v>1.56</v>
       </c>
       <c r="Q3">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="U3">
-        <v>1.69</v>
+        <v>2.26</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>2.18</v>
       </c>
       <c r="W3">
-        <v>2.08</v>
+        <v>1.17</v>
       </c>
       <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>4</v>
+      </c>
+      <c r="Z3">
+        <v>9</v>
+      </c>
+      <c r="AA3">
+        <v>48</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>4.4</v>
+      </c>
+      <c r="AD3">
         <v>10.5</v>
       </c>
-      <c r="Y3">
-        <v>15</v>
-      </c>
-      <c r="Z3">
-        <v>44</v>
-      </c>
-      <c r="AA3">
-        <v>900</v>
-      </c>
-      <c r="AB3">
-        <v>7</v>
-      </c>
-      <c r="AC3">
-        <v>8.4</v>
-      </c>
-      <c r="AD3">
-        <v>24</v>
-      </c>
       <c r="AE3">
-        <v>260</v>
+        <v>60</v>
       </c>
       <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
         <v>11</v>
       </c>
-      <c r="AG3">
-        <v>12</v>
-      </c>
       <c r="AH3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI3">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AJ3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AL3">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AM3">
-        <v>580</v>
+        <v>490</v>
       </c>
       <c r="AN3">
-        <v>22</v>
+        <v>170</v>
       </c>
       <c r="AO3">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="AR3">
-        <v>26</v>
+        <v>7.6</v>
       </c>
       <c r="AS3">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="AT3">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="AV3">
+        <v>8.6</v>
+      </c>
+      <c r="AW3">
+        <v>40</v>
+      </c>
+      <c r="AX3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY3">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3">
         <v>19</v>
       </c>
-      <c r="AW3">
-        <v>7.6</v>
-      </c>
-      <c r="AX3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY3">
-        <v>9</v>
-      </c>
-      <c r="AZ3">
-        <v>21</v>
-      </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BB3">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BD3">
-        <v>38</v>
+        <v>10.5</v>
       </c>
       <c r="BE3">
-        <v>7.6</v>
+        <v>140</v>
       </c>
       <c r="BF3">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>7.6</v>
+        <v>80</v>
       </c>
       <c r="BH3">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>173</v>
@@ -1613,13 +1613,13 @@
         <v>140</v>
       </c>
       <c r="F4">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G4">
         <v>4</v>
       </c>
       <c r="H4">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I4">
         <v>2.24</v>
@@ -1628,25 +1628,25 @@
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L4">
         <v>1.51</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
         <v>1.23</v>
@@ -1655,58 +1655,58 @@
         <v>4.7</v>
       </c>
       <c r="T4">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V4">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W4">
         <v>1.33</v>
       </c>
       <c r="X4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB4">
         <v>12</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD4">
         <v>12</v>
       </c>
       <c r="AE4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF4">
         <v>29</v>
       </c>
       <c r="AG4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
         <v>95</v>
       </c>
       <c r="AK4">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AL4">
         <v>90</v>
@@ -1718,31 +1718,31 @@
         <v>85</v>
       </c>
       <c r="AO4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR4">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS4">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX4">
         <v>21</v>
@@ -1751,34 +1751,34 @@
         <v>14</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA4">
+        <v>36</v>
+      </c>
+      <c r="BB4">
         <v>15</v>
       </c>
-      <c r="BB4">
-        <v>7.2</v>
-      </c>
       <c r="BC4">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BD4">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BE4">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BF4">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BG4">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BH4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI4">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4">
         <v>13</v>
@@ -1790,16 +1790,16 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BO4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BQ4">
         <v>4.5</v>
@@ -1811,22 +1811,22 @@
         <v>4.6</v>
       </c>
       <c r="BT4">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BU4">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BV4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BX4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ4">
         <v>46</v>
@@ -1870,7 +1870,7 @@
         <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.44</v>
@@ -1882,13 +1882,13 @@
         <v>3.55</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R5">
         <v>1.31</v>
@@ -1897,7 +1897,7 @@
         <v>3.85</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U5">
         <v>1.72</v>
@@ -1915,7 +1915,7 @@
         <v>23</v>
       </c>
       <c r="Z5">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AA5">
         <v>700</v>
@@ -1936,7 +1936,7 @@
         <v>8.6</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
         <v>29</v>
@@ -1948,7 +1948,7 @@
         <v>15</v>
       </c>
       <c r="AK5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL5">
         <v>50</v>
@@ -1969,58 +1969,58 @@
         <v>18.5</v>
       </c>
       <c r="AR5">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS5">
+        <v>9</v>
+      </c>
+      <c r="AT5">
+        <v>6</v>
+      </c>
+      <c r="AU5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5">
+        <v>7.6</v>
+      </c>
+      <c r="AW5">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT5">
-        <v>5.8</v>
-      </c>
-      <c r="AU5">
-        <v>8.4</v>
-      </c>
-      <c r="AV5">
-        <v>15</v>
-      </c>
-      <c r="AW5">
-        <v>8.6</v>
-      </c>
       <c r="AX5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY5">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BA5">
-        <v>26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5">
         <v>11.5</v>
       </c>
       <c r="BC5">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="BE5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH5">
         <v>3.65</v>
       </c>
       <c r="BI5">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
@@ -2032,7 +2032,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BN5">
         <v>3.95</v>
@@ -2050,10 +2050,10 @@
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BU5">
         <v>8.800000000000001</v>
@@ -2062,19 +2062,19 @@
         <v>95</v>
       </c>
       <c r="BW5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX5">
         <v>100</v>
       </c>
       <c r="BY5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CA5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
         <v>173</v>
@@ -2097,103 +2097,103 @@
         <v>142</v>
       </c>
       <c r="F6">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G6">
         <v>3.9</v>
       </c>
       <c r="H6">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="I6">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="P6">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="Q6">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="R6">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S6">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="T6">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="U6">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="V6">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="W6">
         <v>1.35</v>
       </c>
       <c r="X6">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB6">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6">
         <v>11.5</v>
       </c>
       <c r="AE6">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AF6">
         <v>28</v>
       </c>
       <c r="AG6">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI6">
         <v>55</v>
       </c>
       <c r="AJ6">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AK6">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AL6">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AM6">
         <v>580</v>
@@ -2202,121 +2202,121 @@
         <v>250</v>
       </c>
       <c r="AO6">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AP6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS6">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AT6">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU6">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
         <v>9.4</v>
       </c>
       <c r="AW6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX6">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY6">
         <v>13</v>
       </c>
       <c r="AZ6">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BA6">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB6">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BC6">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="BD6">
-        <v>44</v>
+        <v>7.8</v>
       </c>
       <c r="BE6">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="BF6">
-        <v>40</v>
+        <v>7.8</v>
       </c>
       <c r="BG6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH6">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BI6">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN6">
         <v>7.4</v>
       </c>
       <c r="BO6">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BU6">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BV6">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BW6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA6">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="CB6" t="s">
         <v>173</v>
@@ -2339,178 +2339,178 @@
         <v>143</v>
       </c>
       <c r="F7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G7">
+        <v>1.3</v>
+      </c>
+      <c r="H7">
+        <v>13.5</v>
+      </c>
+      <c r="I7">
+        <v>16.5</v>
+      </c>
+      <c r="J7">
+        <v>5.8</v>
+      </c>
+      <c r="K7">
+        <v>6.6</v>
+      </c>
+      <c r="L7">
         <v>1.31</v>
       </c>
-      <c r="H7">
-        <v>15</v>
-      </c>
-      <c r="I7">
-        <v>18</v>
-      </c>
-      <c r="J7">
-        <v>5.6</v>
-      </c>
-      <c r="K7">
-        <v>6.8</v>
-      </c>
-      <c r="L7">
-        <v>1.33</v>
-      </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O7">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P7">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="Q7">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="R7">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S7">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="T7">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="U7">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="V7">
         <v>1.06</v>
       </c>
       <c r="W7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y7">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="Z7">
-        <v>170</v>
+        <v>560</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="AB7">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>14.5</v>
       </c>
       <c r="AD7">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AE7">
-        <v>410</v>
+        <v>360</v>
       </c>
       <c r="AF7">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AI7">
         <v>270</v>
       </c>
       <c r="AJ7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AK7">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL7">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM7">
-        <v>330</v>
+        <v>240</v>
       </c>
       <c r="AN7">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AP7">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ7">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AR7">
+        <v>11.5</v>
+      </c>
+      <c r="AS7">
+        <v>10.5</v>
+      </c>
+      <c r="AT7">
         <v>7.8</v>
       </c>
-      <c r="AS7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT7">
+      <c r="AU7">
+        <v>12.5</v>
+      </c>
+      <c r="AV7">
+        <v>42</v>
+      </c>
+      <c r="AW7">
+        <v>10.5</v>
+      </c>
+      <c r="AX7">
         <v>6.8</v>
-      </c>
-      <c r="AU7">
-        <v>11.5</v>
-      </c>
-      <c r="AV7">
-        <v>20</v>
-      </c>
-      <c r="AW7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX7">
-        <v>6.2</v>
       </c>
       <c r="AY7">
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BA7">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BB7">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7">
+        <v>12.5</v>
+      </c>
+      <c r="BD7">
+        <v>24</v>
+      </c>
+      <c r="BE7">
+        <v>11.5</v>
+      </c>
+      <c r="BF7">
+        <v>4.3</v>
+      </c>
+      <c r="BG7">
+        <v>12</v>
+      </c>
+      <c r="BH7">
+        <v>4.4</v>
+      </c>
+      <c r="BI7">
+        <v>3.85</v>
+      </c>
+      <c r="BJ7">
         <v>14</v>
       </c>
-      <c r="BD7">
-        <v>23</v>
-      </c>
-      <c r="BE7">
-        <v>8.4</v>
-      </c>
-      <c r="BF7">
-        <v>4.5</v>
-      </c>
-      <c r="BG7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH7">
-        <v>4.1</v>
-      </c>
-      <c r="BI7">
-        <v>3.15</v>
-      </c>
-      <c r="BJ7">
-        <v>15</v>
-      </c>
       <c r="BK7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2519,34 +2519,34 @@
         <v>11</v>
       </c>
       <c r="BN7">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BO7">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="BP7">
         <v>7.2</v>
       </c>
       <c r="BQ7">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BU7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
@@ -2555,10 +2555,10 @@
         <v>10.5</v>
       </c>
       <c r="BZ7">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="CA7">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="s">
         <v>173</v>
@@ -2581,22 +2581,22 @@
         <v>144</v>
       </c>
       <c r="F8">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="G8">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="I8">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="J8">
         <v>3</v>
       </c>
       <c r="K8">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L8">
         <v>1.55</v>
@@ -2605,16 +2605,16 @@
         <v>1.11</v>
       </c>
       <c r="N8">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
         <v>1.5</v>
       </c>
       <c r="P8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q8">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R8">
         <v>1.2</v>
@@ -2623,43 +2623,43 @@
         <v>5.1</v>
       </c>
       <c r="T8">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V8">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W8">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y8">
         <v>8.4</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC8">
         <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF8">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AG8">
         <v>17</v>
@@ -2683,10 +2683,10 @@
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AO8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP8">
         <v>8</v>
@@ -2698,7 +2698,7 @@
         <v>11.5</v>
       </c>
       <c r="AS8">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="AT8">
         <v>9</v>
@@ -2710,13 +2710,13 @@
         <v>10</v>
       </c>
       <c r="AW8">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AX8">
+        <v>21</v>
+      </c>
+      <c r="AY8">
         <v>13.5</v>
-      </c>
-      <c r="AY8">
-        <v>13</v>
       </c>
       <c r="AZ8">
         <v>17.5</v>
@@ -2725,28 +2725,28 @@
         <v>38</v>
       </c>
       <c r="BB8">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="BD8">
-        <v>7.6</v>
+        <v>46</v>
       </c>
       <c r="BE8">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF8">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BG8">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BH8">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BI8">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
@@ -2758,16 +2758,16 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO8">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ8">
         <v>7.4</v>
@@ -2779,16 +2779,16 @@
         <v>8</v>
       </c>
       <c r="BT8">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU8">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX8">
         <v>44</v>
@@ -2800,7 +2800,7 @@
         <v>46</v>
       </c>
       <c r="CA8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB8" t="s">
         <v>173</v>
@@ -2823,226 +2823,226 @@
         <v>145</v>
       </c>
       <c r="F9">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="G9">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
         <v>3.85</v>
       </c>
       <c r="K9">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O9">
         <v>1.36</v>
       </c>
       <c r="P9">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q9">
         <v>2.08</v>
       </c>
       <c r="R9">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S9">
         <v>3.85</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="V9">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W9">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X9">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="Y9">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="Z9">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AA9">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB9">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="AC9">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="AD9">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AE9">
         <v>700</v>
       </c>
       <c r="AF9">
-        <v>500</v>
+        <v>9.4</v>
       </c>
       <c r="AG9">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI9">
         <v>700</v>
       </c>
       <c r="AJ9">
-        <v>900</v>
+        <v>16</v>
       </c>
       <c r="AK9">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AL9">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AM9">
         <v>700</v>
       </c>
       <c r="AN9">
-        <v>600</v>
+        <v>11</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP9">
-        <v>1.24</v>
+        <v>5.9</v>
       </c>
       <c r="AQ9">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR9">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="AS9">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT9">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU9">
-        <v>1.21</v>
+        <v>4.8</v>
       </c>
       <c r="AV9">
-        <v>2.5</v>
+        <v>7.2</v>
       </c>
       <c r="AW9">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX9">
-        <v>1.21</v>
+        <v>4.8</v>
       </c>
       <c r="AY9">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="AZ9">
-        <v>1.23</v>
+        <v>7</v>
       </c>
       <c r="BA9">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="BB9">
-        <v>1.23</v>
+        <v>12.5</v>
       </c>
       <c r="BC9">
-        <v>1.22</v>
+        <v>6.6</v>
       </c>
       <c r="BD9">
-        <v>1.23</v>
+        <v>8</v>
       </c>
       <c r="BE9">
-        <v>1.24</v>
+        <v>9.4</v>
       </c>
       <c r="BF9">
-        <v>1.21</v>
+        <v>8.6</v>
       </c>
       <c r="BG9">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB9" t="s">
         <v>173</v>
@@ -3065,10 +3065,10 @@
         <v>146</v>
       </c>
       <c r="F10">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G10">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H10">
         <v>3.75</v>
@@ -3080,7 +3080,7 @@
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L10">
         <v>1.16</v>
@@ -3095,28 +3095,28 @@
         <v>1.08</v>
       </c>
       <c r="P10">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="R10">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="S10">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="T10">
         <v>1.37</v>
       </c>
       <c r="U10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V10">
         <v>1.31</v>
       </c>
       <c r="W10">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X10">
         <v>70</v>
@@ -3125,7 +3125,7 @@
         <v>44</v>
       </c>
       <c r="Z10">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AA10">
         <v>170</v>
@@ -3134,7 +3134,7 @@
         <v>28</v>
       </c>
       <c r="AC10">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD10">
         <v>21</v>
@@ -3185,7 +3185,7 @@
         <v>55</v>
       </c>
       <c r="AT10">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AU10">
         <v>13.5</v>
@@ -3194,7 +3194,7 @@
         <v>17</v>
       </c>
       <c r="AW10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX10">
         <v>19</v>
@@ -3206,7 +3206,7 @@
         <v>12.5</v>
       </c>
       <c r="BA10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB10">
         <v>21</v>
@@ -3221,16 +3221,16 @@
         <v>27</v>
       </c>
       <c r="BF10">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BG10">
         <v>12.5</v>
       </c>
       <c r="BH10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BI10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BJ10">
         <v>8.800000000000001</v>
@@ -3242,7 +3242,7 @@
         <v>46</v>
       </c>
       <c r="BM10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BN10">
         <v>6.4</v>
@@ -3254,25 +3254,25 @@
         <v>12</v>
       </c>
       <c r="BQ10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR10">
         <v>16</v>
       </c>
       <c r="BS10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT10">
         <v>9.6</v>
       </c>
       <c r="BU10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV10">
         <v>26</v>
       </c>
       <c r="BW10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX10">
         <v>24</v>
@@ -3284,7 +3284,7 @@
         <v>8.4</v>
       </c>
       <c r="CA10">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="CB10" t="s">
         <v>173</v>
@@ -3313,10 +3313,10 @@
         <v>1.8</v>
       </c>
       <c r="H11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J11">
         <v>4.8</v>
@@ -3349,7 +3349,7 @@
         <v>1.68</v>
       </c>
       <c r="T11">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="U11">
         <v>3.3</v>
@@ -3358,10 +3358,10 @@
         <v>1.29</v>
       </c>
       <c r="W11">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X11">
-        <v>130</v>
+        <v>950</v>
       </c>
       <c r="Y11">
         <v>65</v>
@@ -3376,7 +3376,7 @@
         <v>36</v>
       </c>
       <c r="AC11">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AD11">
         <v>21</v>
@@ -3385,13 +3385,13 @@
         <v>55</v>
       </c>
       <c r="AF11">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AG11">
         <v>13.5</v>
       </c>
       <c r="AH11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI11">
         <v>40</v>
@@ -3400,19 +3400,19 @@
         <v>26</v>
       </c>
       <c r="AK11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL11">
         <v>32</v>
       </c>
       <c r="AM11">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN11">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AO11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP11">
         <v>29</v>
@@ -3424,7 +3424,7 @@
         <v>40</v>
       </c>
       <c r="AS11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT11">
         <v>21</v>
@@ -3436,10 +3436,10 @@
         <v>17.5</v>
       </c>
       <c r="AW11">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AX11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY11">
         <v>11</v>
@@ -3457,7 +3457,7 @@
         <v>13.5</v>
       </c>
       <c r="BD11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE11">
         <v>29</v>
@@ -3549,22 +3549,22 @@
         <v>148</v>
       </c>
       <c r="F12">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G12">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H12">
         <v>3.5</v>
       </c>
       <c r="I12">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K12">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L12">
         <v>1.14</v>
@@ -3573,37 +3573,37 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="O12">
         <v>1.06</v>
       </c>
       <c r="P12">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Q12">
         <v>1.23</v>
       </c>
       <c r="R12">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="S12">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="T12">
         <v>1.3</v>
       </c>
       <c r="U12">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W12">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X12">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="Y12">
         <v>50</v>
@@ -3612,10 +3612,10 @@
         <v>55</v>
       </c>
       <c r="AA12">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC12">
         <v>18.5</v>
@@ -3627,7 +3627,7 @@
         <v>34</v>
       </c>
       <c r="AF12">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG12">
         <v>15.5</v>
@@ -3645,31 +3645,31 @@
         <v>18.5</v>
       </c>
       <c r="AL12">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AM12">
         <v>32</v>
       </c>
       <c r="AN12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP12">
         <v>46</v>
       </c>
       <c r="AQ12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AR12">
         <v>40</v>
       </c>
       <c r="AS12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU12">
         <v>15</v>
@@ -3693,16 +3693,16 @@
         <v>21</v>
       </c>
       <c r="BB12">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC12">
         <v>15</v>
       </c>
       <c r="BD12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BF12">
         <v>3.95</v>
@@ -3711,43 +3711,43 @@
         <v>10</v>
       </c>
       <c r="BH12">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BI12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BJ12">
         <v>8.6</v>
       </c>
       <c r="BK12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BL12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BM12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO12">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP12">
         <v>12.5</v>
       </c>
       <c r="BQ12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR12">
         <v>15.5</v>
       </c>
       <c r="BS12">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT12">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU12">
         <v>4.4</v>
@@ -3762,13 +3762,13 @@
         <v>21</v>
       </c>
       <c r="BY12">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BZ12">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CA12">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="CB12" t="s">
         <v>173</v>
@@ -3791,19 +3791,19 @@
         <v>149</v>
       </c>
       <c r="F13">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G13">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H13">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I13">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="J13">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <v>4.9</v>
@@ -3812,145 +3812,145 @@
         <v>1.24</v>
       </c>
       <c r="M13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
         <v>6.4</v>
       </c>
       <c r="O13">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P13">
         <v>2.84</v>
       </c>
       <c r="Q13">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R13">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S13">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T13">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="U13">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="V13">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X13">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="Y13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z13">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA13">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AB13">
+        <v>19</v>
+      </c>
+      <c r="AC13">
+        <v>12.5</v>
+      </c>
+      <c r="AD13">
+        <v>16.5</v>
+      </c>
+      <c r="AE13">
+        <v>44</v>
+      </c>
+      <c r="AF13">
         <v>21</v>
       </c>
-      <c r="AC13">
-        <v>12</v>
-      </c>
-      <c r="AD13">
+      <c r="AG13">
+        <v>13</v>
+      </c>
+      <c r="AH13">
         <v>16</v>
       </c>
-      <c r="AE13">
-        <v>30</v>
-      </c>
-      <c r="AF13">
-        <v>22</v>
-      </c>
-      <c r="AG13">
-        <v>13.5</v>
-      </c>
-      <c r="AH13">
-        <v>15</v>
-      </c>
       <c r="AI13">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AJ13">
         <v>32</v>
       </c>
       <c r="AK13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL13">
         <v>26</v>
       </c>
       <c r="AM13">
-        <v>580</v>
+        <v>65</v>
       </c>
       <c r="AN13">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO13">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP13">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AQ13">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR13">
+        <v>23</v>
+      </c>
+      <c r="AS13">
+        <v>38</v>
+      </c>
+      <c r="AT13">
+        <v>14.5</v>
+      </c>
+      <c r="AU13">
+        <v>9.6</v>
+      </c>
+      <c r="AV13">
         <v>12.5</v>
       </c>
-      <c r="AS13">
-        <v>6.4</v>
-      </c>
-      <c r="AT13">
-        <v>15</v>
-      </c>
-      <c r="AU13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV13">
+      <c r="AW13">
+        <v>23</v>
+      </c>
+      <c r="AX13">
+        <v>16</v>
+      </c>
+      <c r="AY13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ13">
         <v>12</v>
       </c>
-      <c r="AW13">
-        <v>20</v>
-      </c>
-      <c r="AX13">
-        <v>17</v>
-      </c>
-      <c r="AY13">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13">
-        <v>11.5</v>
-      </c>
       <c r="BA13">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BB13">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BC13">
         <v>16</v>
       </c>
       <c r="BD13">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BE13">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="BF13">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH13">
         <v>5.3</v>
@@ -4039,16 +4039,16 @@
         <v>5.1</v>
       </c>
       <c r="H14">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I14">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="J14">
         <v>4.4</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L14">
         <v>1.24</v>
@@ -4060,28 +4060,28 @@
         <v>6.8</v>
       </c>
       <c r="O14">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P14">
         <v>2.98</v>
       </c>
       <c r="Q14">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="R14">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S14">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="T14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U14">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V14">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="W14">
         <v>1.25</v>
@@ -4093,7 +4093,7 @@
         <v>17.5</v>
       </c>
       <c r="Z14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA14">
         <v>23</v>
@@ -4102,16 +4102,16 @@
         <v>32</v>
       </c>
       <c r="AC14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE14">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF14">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AG14">
         <v>21</v>
@@ -4120,10 +4120,10 @@
         <v>17</v>
       </c>
       <c r="AI14">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AJ14">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AK14">
         <v>55</v>
@@ -4132,43 +4132,43 @@
         <v>100</v>
       </c>
       <c r="AM14">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO14">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AP14">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AQ14">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AR14">
         <v>12.5</v>
       </c>
       <c r="AS14">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT14">
-        <v>5.9</v>
+        <v>21</v>
       </c>
       <c r="AU14">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV14">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW14">
         <v>12</v>
       </c>
       <c r="AX14">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="AY14">
-        <v>5.3</v>
+        <v>15.5</v>
       </c>
       <c r="AZ14">
         <v>12.5</v>
@@ -4177,25 +4177,25 @@
         <v>18.5</v>
       </c>
       <c r="BB14">
-        <v>6.8</v>
+        <v>55</v>
       </c>
       <c r="BC14">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="BD14">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="BE14">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="BF14">
-        <v>5.9</v>
+        <v>17</v>
       </c>
       <c r="BG14">
         <v>5.1</v>
       </c>
       <c r="BH14">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BI14">
         <v>4.1</v>
@@ -4204,34 +4204,34 @@
         <v>9</v>
       </c>
       <c r="BK14">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN14">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO14">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU14">
         <v>4</v>
@@ -4240,19 +4240,19 @@
         <v>11</v>
       </c>
       <c r="BW14">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BX14">
         <v>18.5</v>
       </c>
       <c r="BY14">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ14">
         <v>11.5</v>
       </c>
       <c r="CA14">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="CB14" t="s">
         <v>173</v>
@@ -4275,10 +4275,10 @@
         <v>151</v>
       </c>
       <c r="F15">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G15">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>3.7</v>
@@ -4287,64 +4287,64 @@
         <v>4.2</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L15">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M15">
         <v>1.02</v>
       </c>
       <c r="N15">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="Q15">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="R15">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="S15">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="T15">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="U15">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="V15">
         <v>1.32</v>
       </c>
       <c r="W15">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X15">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y15">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="Z15">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA15">
         <v>160</v>
       </c>
       <c r="AB15">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
         <v>18</v>
@@ -4353,7 +4353,7 @@
         <v>55</v>
       </c>
       <c r="AF15">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG15">
         <v>12</v>
@@ -4362,7 +4362,7 @@
         <v>16</v>
       </c>
       <c r="AI15">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AJ15">
         <v>24</v>
@@ -4371,40 +4371,40 @@
         <v>18.5</v>
       </c>
       <c r="AL15">
+        <v>27</v>
+      </c>
+      <c r="AM15">
+        <v>580</v>
+      </c>
+      <c r="AN15">
+        <v>8.4</v>
+      </c>
+      <c r="AO15">
+        <v>29</v>
+      </c>
+      <c r="AP15">
+        <v>23</v>
+      </c>
+      <c r="AQ15">
+        <v>19</v>
+      </c>
+      <c r="AR15">
         <v>25</v>
       </c>
-      <c r="AM15">
-        <v>200</v>
-      </c>
-      <c r="AN15">
+      <c r="AS15">
         <v>7.8</v>
       </c>
-      <c r="AO15">
-        <v>26</v>
-      </c>
-      <c r="AP15">
-        <v>18.5</v>
-      </c>
-      <c r="AQ15">
-        <v>21</v>
-      </c>
-      <c r="AR15">
-        <v>27</v>
-      </c>
-      <c r="AS15">
-        <v>50</v>
-      </c>
       <c r="AT15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU15">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AV15">
         <v>14.5</v>
       </c>
       <c r="AW15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX15">
         <v>13</v>
@@ -4419,82 +4419,82 @@
         <v>27</v>
       </c>
       <c r="BB15">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD15">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE15">
-        <v>38</v>
+        <v>7.6</v>
       </c>
       <c r="BF15">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG15">
-        <v>19.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH15">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BI15">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BJ15">
         <v>9.199999999999999</v>
       </c>
       <c r="BK15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BN15">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP15">
         <v>13</v>
       </c>
       <c r="BQ15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BT15">
         <v>8.4</v>
       </c>
       <c r="BU15">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW15">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BX15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ15">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA15">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="CB15" t="s">
         <v>173</v>
@@ -4532,7 +4532,7 @@
         <v>4.1</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L16">
         <v>1.36</v>
@@ -4541,7 +4541,7 @@
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O16">
         <v>1.27</v>
@@ -4604,7 +4604,7 @@
         <v>23</v>
       </c>
       <c r="AI16">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="AJ16">
         <v>16.5</v>
@@ -4673,7 +4673,7 @@
         <v>6.6</v>
       </c>
       <c r="BF16">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BG16">
         <v>6.6</v>
@@ -4759,7 +4759,7 @@
         <v>153</v>
       </c>
       <c r="F17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G17">
         <v>3.7</v>
@@ -4768,10 +4768,10 @@
         <v>2.52</v>
       </c>
       <c r="I17">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J17">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K17">
         <v>3.2</v>
@@ -4789,31 +4789,31 @@
         <v>1.52</v>
       </c>
       <c r="P17">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R17">
         <v>1.2</v>
       </c>
       <c r="S17">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T17">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U17">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W17">
         <v>1.38</v>
       </c>
       <c r="X17">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>8.4</v>
@@ -4846,25 +4846,25 @@
         <v>23</v>
       </c>
       <c r="AI17">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AJ17">
         <v>85</v>
       </c>
       <c r="AK17">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL17">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AM17">
         <v>500</v>
       </c>
       <c r="AN17">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AO17">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AP17">
         <v>7.6</v>
@@ -4888,7 +4888,7 @@
         <v>10.5</v>
       </c>
       <c r="AW17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX17">
         <v>19</v>
@@ -4900,7 +4900,7 @@
         <v>18.5</v>
       </c>
       <c r="BA17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB17">
         <v>46</v>
@@ -4912,19 +4912,19 @@
         <v>46</v>
       </c>
       <c r="BE17">
-        <v>65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17">
         <v>50</v>
       </c>
       <c r="BG17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH17">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI17">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BJ17">
         <v>11.5</v>
@@ -4951,10 +4951,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS17">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT17">
         <v>5.5</v>
@@ -4975,10 +4975,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA17">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB17" t="s">
         <v>173</v>
@@ -5001,10 +5001,10 @@
         <v>154</v>
       </c>
       <c r="F18">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="G18">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="H18">
         <v>10</v>
@@ -5013,10 +5013,10 @@
         <v>10.5</v>
       </c>
       <c r="J18">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K18">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L18">
         <v>1.35</v>
@@ -5025,46 +5025,46 @@
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O18">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P18">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R18">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S18">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T18">
         <v>2.14</v>
       </c>
       <c r="U18">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V18">
         <v>1.1</v>
       </c>
       <c r="W18">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="X18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y18">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA18">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="AB18">
         <v>9.199999999999999</v>
@@ -5076,7 +5076,7 @@
         <v>36</v>
       </c>
       <c r="AE18">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF18">
         <v>8</v>
@@ -5091,49 +5091,49 @@
         <v>130</v>
       </c>
       <c r="AJ18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK18">
         <v>14.5</v>
       </c>
       <c r="AL18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM18">
         <v>150</v>
       </c>
       <c r="AN18">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AO18">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AP18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ18">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR18">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AS18">
         <v>70</v>
       </c>
       <c r="AT18">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU18">
         <v>11.5</v>
       </c>
       <c r="AV18">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AW18">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AX18">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY18">
         <v>10</v>
@@ -5145,7 +5145,7 @@
         <v>110</v>
       </c>
       <c r="BB18">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC18">
         <v>13.5</v>
@@ -5157,13 +5157,13 @@
         <v>120</v>
       </c>
       <c r="BF18">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG18">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="BH18">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI18">
         <v>3.7</v>
@@ -5184,13 +5184,13 @@
         <v>3.75</v>
       </c>
       <c r="BO18">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP18">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ18">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR18">
         <v>23</v>
@@ -5199,25 +5199,25 @@
         <v>21</v>
       </c>
       <c r="BT18">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BU18">
         <v>11.5</v>
       </c>
       <c r="BV18">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BW18">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="BX18">
         <v>80</v>
       </c>
       <c r="BY18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BZ18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA18">
         <v>11</v>
@@ -5243,25 +5243,25 @@
         <v>155</v>
       </c>
       <c r="F19">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G19">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H19">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I19">
         <v>2.52</v>
       </c>
       <c r="J19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K19">
         <v>5.1</v>
       </c>
       <c r="L19">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M19">
         <v>1.01</v>
@@ -5276,25 +5276,25 @@
         <v>4</v>
       </c>
       <c r="Q19">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S19">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="T19">
         <v>1.33</v>
       </c>
       <c r="U19">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="V19">
         <v>1.66</v>
       </c>
       <c r="W19">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X19">
         <v>60</v>
@@ -5318,13 +5318,13 @@
         <v>15.5</v>
       </c>
       <c r="AE19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF19">
         <v>34</v>
       </c>
       <c r="AG19">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH19">
         <v>14.5</v>
@@ -5339,19 +5339,19 @@
         <v>25</v>
       </c>
       <c r="AL19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM19">
         <v>34</v>
       </c>
       <c r="AN19">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO19">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ19">
         <v>14.5</v>
@@ -5360,16 +5360,16 @@
         <v>14</v>
       </c>
       <c r="AS19">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT19">
         <v>14</v>
       </c>
       <c r="AU19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AV19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW19">
         <v>18</v>
@@ -5387,46 +5387,46 @@
         <v>18</v>
       </c>
       <c r="BB19">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC19">
+        <v>20</v>
+      </c>
+      <c r="BD19">
         <v>19.5</v>
-      </c>
-      <c r="BD19">
-        <v>19</v>
       </c>
       <c r="BE19">
         <v>13.5</v>
       </c>
       <c r="BF19">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG19">
         <v>6.4</v>
       </c>
       <c r="BH19">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BI19">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BJ19">
         <v>8.4</v>
       </c>
       <c r="BK19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BL19">
         <v>44</v>
       </c>
       <c r="BM19">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BN19">
         <v>7.6</v>
       </c>
       <c r="BO19">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP19">
         <v>17.5</v>
@@ -5450,13 +5450,13 @@
         <v>15.5</v>
       </c>
       <c r="BW19">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BX19">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BY19">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ19">
         <v>9.199999999999999</v>
@@ -5485,85 +5485,85 @@
         <v>156</v>
       </c>
       <c r="F20">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G20">
         <v>2.12</v>
       </c>
       <c r="H20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I20">
         <v>4.8</v>
       </c>
       <c r="J20">
+        <v>3.15</v>
+      </c>
+      <c r="K20">
         <v>3.25</v>
-      </c>
-      <c r="K20">
-        <v>3.35</v>
       </c>
       <c r="L20">
         <v>1.56</v>
       </c>
       <c r="M20">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N20">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O20">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P20">
         <v>1.58</v>
       </c>
       <c r="Q20">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R20">
         <v>1.21</v>
       </c>
       <c r="S20">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T20">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U20">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="V20">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W20">
         <v>1.89</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y20">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z20">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA20">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC20">
         <v>7.4</v>
       </c>
       <c r="AD20">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE20">
         <v>95</v>
       </c>
       <c r="AF20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG20">
         <v>11.5</v>
@@ -5575,76 +5575,76 @@
         <v>120</v>
       </c>
       <c r="AJ20">
+        <v>27</v>
+      </c>
+      <c r="AK20">
         <v>32</v>
-      </c>
-      <c r="AK20">
-        <v>34</v>
       </c>
       <c r="AL20">
         <v>60</v>
       </c>
       <c r="AM20">
-        <v>580</v>
+        <v>220</v>
       </c>
       <c r="AN20">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO20">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="AP20">
         <v>8</v>
       </c>
       <c r="AQ20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR20">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS20">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AT20">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU20">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV20">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW20">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX20">
         <v>10</v>
       </c>
       <c r="AY20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20">
+        <v>22</v>
+      </c>
+      <c r="BA20">
+        <v>60</v>
+      </c>
+      <c r="BB20">
+        <v>23</v>
+      </c>
+      <c r="BC20">
+        <v>24</v>
+      </c>
+      <c r="BD20">
+        <v>44</v>
+      </c>
+      <c r="BE20">
+        <v>85</v>
+      </c>
+      <c r="BF20">
         <v>21</v>
       </c>
-      <c r="BA20">
-        <v>55</v>
-      </c>
-      <c r="BB20">
-        <v>20</v>
-      </c>
-      <c r="BC20">
-        <v>21</v>
-      </c>
-      <c r="BD20">
-        <v>36</v>
-      </c>
-      <c r="BE20">
-        <v>65</v>
-      </c>
-      <c r="BF20">
-        <v>19</v>
-      </c>
       <c r="BG20">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BH20">
         <v>3.1</v>
@@ -5662,25 +5662,25 @@
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO20">
         <v>4.1</v>
       </c>
       <c r="BP20">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BQ20">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR20">
         <v>42</v>
       </c>
       <c r="BS20">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT20">
         <v>7.6</v>
@@ -5689,22 +5689,22 @@
         <v>5.9</v>
       </c>
       <c r="BV20">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX20">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY20">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ20">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="CA20">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB20" t="s">
         <v>173</v>
@@ -5727,10 +5727,10 @@
         <v>157</v>
       </c>
       <c r="F21">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G21">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H21">
         <v>3.6</v>
@@ -5739,52 +5739,52 @@
         <v>3.7</v>
       </c>
       <c r="J21">
+        <v>3.1</v>
+      </c>
+      <c r="K21">
         <v>3.15</v>
       </c>
-      <c r="K21">
+      <c r="L21">
+        <v>1.71</v>
+      </c>
+      <c r="M21">
+        <v>1.16</v>
+      </c>
+      <c r="N21">
+        <v>2.32</v>
+      </c>
+      <c r="O21">
+        <v>1.72</v>
+      </c>
+      <c r="P21">
+        <v>1.44</v>
+      </c>
+      <c r="Q21">
         <v>3.2</v>
       </c>
-      <c r="L21">
-        <v>1.67</v>
-      </c>
-      <c r="M21">
+      <c r="R21">
         <v>1.14</v>
       </c>
-      <c r="N21">
-        <v>2.42</v>
-      </c>
-      <c r="O21">
-        <v>1.67</v>
-      </c>
-      <c r="P21">
-        <v>1.46</v>
-      </c>
-      <c r="Q21">
-        <v>3.05</v>
-      </c>
-      <c r="R21">
-        <v>1.16</v>
-      </c>
       <c r="S21">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="T21">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U21">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V21">
         <v>1.37</v>
       </c>
       <c r="W21">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="X21">
         <v>7.4</v>
       </c>
       <c r="Y21">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z21">
         <v>23</v>
@@ -5799,46 +5799,46 @@
         <v>7.6</v>
       </c>
       <c r="AD21">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE21">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH21">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AI21">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ21">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AK21">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AL21">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AM21">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AN21">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AO21">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP21">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ21">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR21">
         <v>20</v>
@@ -5847,16 +5847,16 @@
         <v>70</v>
       </c>
       <c r="AT21">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU21">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV21">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW21">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX21">
         <v>11.5</v>
@@ -5868,7 +5868,7 @@
         <v>25</v>
       </c>
       <c r="BA21">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB21">
         <v>32</v>
@@ -5877,7 +5877,7 @@
         <v>32</v>
       </c>
       <c r="BD21">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE21">
         <v>160</v>
@@ -5886,19 +5886,19 @@
         <v>38</v>
       </c>
       <c r="BG21">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="BH21">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="BI21">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BJ21">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BK21">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL21">
         <v>1000</v>
@@ -5907,46 +5907,46 @@
         <v>200</v>
       </c>
       <c r="BN21">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP21">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BQ21">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR21">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BS21">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT21">
         <v>7</v>
       </c>
       <c r="BU21">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW21">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY21">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="CA21">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB21" t="s">
         <v>173</v>
@@ -5969,22 +5969,22 @@
         <v>158</v>
       </c>
       <c r="F22">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G22">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H22">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I22">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="J22">
         <v>3.35</v>
       </c>
       <c r="K22">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L22">
         <v>1.56</v>
@@ -5996,40 +5996,40 @@
         <v>2.8</v>
       </c>
       <c r="O22">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P22">
         <v>1.58</v>
       </c>
       <c r="Q22">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R22">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S22">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T22">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U22">
         <v>1.72</v>
       </c>
       <c r="V22">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X22">
         <v>8.800000000000001</v>
       </c>
       <c r="Y22">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA22">
         <v>21</v>
@@ -6047,7 +6047,7 @@
         <v>26</v>
       </c>
       <c r="AF22">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG22">
         <v>23</v>
@@ -6062,7 +6062,7 @@
         <v>170</v>
       </c>
       <c r="AK22">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AL22">
         <v>130</v>
@@ -6071,16 +6071,16 @@
         <v>230</v>
       </c>
       <c r="AN22">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="AO22">
         <v>22</v>
       </c>
       <c r="AP22">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ22">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR22">
         <v>8.800000000000001</v>
@@ -6089,7 +6089,7 @@
         <v>19</v>
       </c>
       <c r="AT22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU22">
         <v>7.2</v>
@@ -6098,13 +6098,13 @@
         <v>10</v>
       </c>
       <c r="AW22">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX22">
         <v>34</v>
       </c>
       <c r="AY22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ22">
         <v>24</v>
@@ -6113,7 +6113,7 @@
         <v>50</v>
       </c>
       <c r="BB22">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BC22">
         <v>65</v>
@@ -6128,46 +6128,46 @@
         <v>140</v>
       </c>
       <c r="BG22">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH22">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI22">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BJ22">
         <v>12</v>
       </c>
       <c r="BK22">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN22">
         <v>8.800000000000001</v>
       </c>
       <c r="BO22">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BP22">
         <v>60</v>
       </c>
       <c r="BQ22">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR22">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BS22">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT22">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BU22">
         <v>3.8</v>
@@ -6176,19 +6176,19 @@
         <v>14.5</v>
       </c>
       <c r="BW22">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX22">
         <v>40</v>
       </c>
       <c r="BY22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BZ22">
         <v>40</v>
       </c>
       <c r="CA22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CB22" t="s">
         <v>173</v>
@@ -6211,10 +6211,10 @@
         <v>159</v>
       </c>
       <c r="F23">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G23">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H23">
         <v>6.2</v>
@@ -6256,22 +6256,22 @@
         <v>2.16</v>
       </c>
       <c r="U23">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V23">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W23">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X23">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y23">
         <v>18</v>
       </c>
       <c r="Z23">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA23">
         <v>900</v>
@@ -6283,13 +6283,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AE23">
         <v>130</v>
       </c>
       <c r="AF23">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG23">
         <v>11</v>
@@ -6298,7 +6298,7 @@
         <v>25</v>
       </c>
       <c r="AI23">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ23">
         <v>17.5</v>
@@ -6307,7 +6307,7 @@
         <v>21</v>
       </c>
       <c r="AL23">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM23">
         <v>580</v>
@@ -6319,40 +6319,40 @@
         <v>700</v>
       </c>
       <c r="AP23">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ23">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR23">
         <v>22</v>
       </c>
       <c r="AS23">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT23">
         <v>6</v>
       </c>
       <c r="AU23">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV23">
         <v>20</v>
       </c>
       <c r="AW23">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX23">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY23">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA23">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB23">
         <v>14</v>
@@ -6361,7 +6361,7 @@
         <v>17.5</v>
       </c>
       <c r="BD23">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BE23">
         <v>120</v>
@@ -6370,7 +6370,7 @@
         <v>12</v>
       </c>
       <c r="BG23">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH23">
         <v>3.05</v>
@@ -6453,13 +6453,13 @@
         <v>160</v>
       </c>
       <c r="F24">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G24">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H24">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I24">
         <v>3.3</v>
@@ -6468,34 +6468,34 @@
         <v>3.35</v>
       </c>
       <c r="K24">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L24">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M24">
         <v>1.1</v>
       </c>
       <c r="N24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O24">
         <v>1.42</v>
       </c>
       <c r="P24">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q24">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R24">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S24">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T24">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U24">
         <v>2</v>
@@ -6504,7 +6504,7 @@
         <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X24">
         <v>11</v>
@@ -6516,25 +6516,25 @@
         <v>22</v>
       </c>
       <c r="AA24">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB24">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC24">
         <v>7.6</v>
       </c>
       <c r="AD24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE24">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF24">
         <v>15.5</v>
       </c>
       <c r="AG24">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH24">
         <v>19.5</v>
@@ -6549,28 +6549,28 @@
         <v>38</v>
       </c>
       <c r="AL24">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM24">
         <v>130</v>
       </c>
       <c r="AN24">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AO24">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ24">
         <v>9.800000000000001</v>
       </c>
       <c r="AR24">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS24">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT24">
         <v>8.4</v>
@@ -6579,7 +6579,7 @@
         <v>6.8</v>
       </c>
       <c r="AV24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW24">
         <v>38</v>
@@ -6618,13 +6618,13 @@
         <v>3.05</v>
       </c>
       <c r="BI24">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ24">
         <v>10</v>
       </c>
       <c r="BK24">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL24">
         <v>1000</v>
@@ -6639,16 +6639,16 @@
         <v>4.7</v>
       </c>
       <c r="BP24">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BQ24">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR24">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BS24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT24">
         <v>6.4</v>
@@ -6657,22 +6657,22 @@
         <v>5.7</v>
       </c>
       <c r="BV24">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BW24">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX24">
         <v>55</v>
       </c>
       <c r="BY24">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ24">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA24">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="CB24" t="s">
         <v>173</v>
@@ -6701,10 +6701,10 @@
         <v>2.56</v>
       </c>
       <c r="H25">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I25">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J25">
         <v>4</v>
@@ -6731,19 +6731,19 @@
         <v>1.6</v>
       </c>
       <c r="R25">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S25">
         <v>2.52</v>
       </c>
       <c r="T25">
+        <v>1.53</v>
+      </c>
+      <c r="U25">
+        <v>2.56</v>
+      </c>
+      <c r="V25">
         <v>1.54</v>
-      </c>
-      <c r="U25">
-        <v>2.52</v>
-      </c>
-      <c r="V25">
-        <v>1.55</v>
       </c>
       <c r="W25">
         <v>1.64</v>
@@ -6770,13 +6770,13 @@
         <v>14</v>
       </c>
       <c r="AE25">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF25">
         <v>24</v>
       </c>
       <c r="AG25">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH25">
         <v>17.5</v>
@@ -6785,7 +6785,7 @@
         <v>34</v>
       </c>
       <c r="AJ25">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK25">
         <v>26</v>
@@ -6794,10 +6794,10 @@
         <v>38</v>
       </c>
       <c r="AM25">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AN25">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO25">
         <v>20</v>
@@ -6806,13 +6806,13 @@
         <v>20</v>
       </c>
       <c r="AQ25">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR25">
         <v>18.5</v>
       </c>
       <c r="AS25">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AT25">
         <v>13</v>
@@ -6824,7 +6824,7 @@
         <v>11</v>
       </c>
       <c r="AW25">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="AX25">
         <v>17</v>
@@ -6833,10 +6833,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ25">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BA25">
-        <v>4.5</v>
+        <v>22</v>
       </c>
       <c r="BB25">
         <v>4.6</v>
@@ -6845,16 +6845,16 @@
         <v>20</v>
       </c>
       <c r="BD25">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="BE25">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF25">
+        <v>10.5</v>
+      </c>
+      <c r="BG25">
         <v>12</v>
-      </c>
-      <c r="BG25">
-        <v>13.5</v>
       </c>
       <c r="BH25">
         <v>4.5</v>
@@ -6940,7 +6940,7 @@
         <v>1.69</v>
       </c>
       <c r="G26">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H26">
         <v>4.9</v>
@@ -6961,7 +6961,7 @@
         <v>1.05</v>
       </c>
       <c r="N26">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O26">
         <v>1.24</v>
@@ -6988,7 +6988,7 @@
         <v>1.22</v>
       </c>
       <c r="W26">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X26">
         <v>22</v>
@@ -7018,7 +7018,7 @@
         <v>13</v>
       </c>
       <c r="AG26">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH26">
         <v>24</v>
@@ -7033,16 +7033,16 @@
         <v>21</v>
       </c>
       <c r="AL26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM26">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AN26">
         <v>10.5</v>
       </c>
       <c r="AO26">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP26">
         <v>14.5</v>
@@ -7081,22 +7081,22 @@
         <v>38</v>
       </c>
       <c r="BB26">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC26">
         <v>14.5</v>
       </c>
       <c r="BD26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE26">
         <v>22</v>
       </c>
       <c r="BF26">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG26">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH26">
         <v>3.9</v>
@@ -7179,7 +7179,7 @@
         <v>163</v>
       </c>
       <c r="F27">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G27">
         <v>2.44</v>
@@ -7233,7 +7233,7 @@
         <v>1.69</v>
       </c>
       <c r="X27">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y27">
         <v>13</v>
@@ -7257,7 +7257,7 @@
         <v>60</v>
       </c>
       <c r="AF27">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG27">
         <v>13</v>
@@ -7266,7 +7266,7 @@
         <v>23</v>
       </c>
       <c r="AI27">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ27">
         <v>34</v>
@@ -7284,7 +7284,7 @@
         <v>32</v>
       </c>
       <c r="AO27">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP27">
         <v>9.4</v>
@@ -7296,7 +7296,7 @@
         <v>21</v>
       </c>
       <c r="AS27">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT27">
         <v>7.4</v>
@@ -7320,25 +7320,25 @@
         <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB27">
-        <v>29</v>
+        <v>5.8</v>
       </c>
       <c r="BC27">
         <v>21</v>
       </c>
       <c r="BD27">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE27">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF27">
         <v>20</v>
       </c>
       <c r="BG27">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH27">
         <v>3.3</v>
@@ -7350,13 +7350,13 @@
         <v>12</v>
       </c>
       <c r="BK27">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BL27">
         <v>190</v>
       </c>
       <c r="BM27">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BN27">
         <v>5.7</v>
@@ -7368,13 +7368,13 @@
         <v>22</v>
       </c>
       <c r="BQ27">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR27">
         <v>44</v>
       </c>
       <c r="BS27">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BT27">
         <v>7.6</v>
@@ -7386,10 +7386,10 @@
         <v>38</v>
       </c>
       <c r="BW27">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BX27">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY27">
         <v>5.4</v>
@@ -7398,7 +7398,7 @@
         <v>44</v>
       </c>
       <c r="CA27">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB27" t="s">
         <v>173</v>
@@ -7421,7 +7421,7 @@
         <v>164</v>
       </c>
       <c r="F28">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G28">
         <v>1.81</v>
@@ -7436,37 +7436,37 @@
         <v>4.2</v>
       </c>
       <c r="K28">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L28">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M28">
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O28">
         <v>1.21</v>
       </c>
       <c r="P28">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q28">
         <v>1.64</v>
       </c>
       <c r="R28">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S28">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T28">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U28">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V28">
         <v>1.26</v>
@@ -7475,7 +7475,7 @@
         <v>2.22</v>
       </c>
       <c r="X28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y28">
         <v>22</v>
@@ -7484,7 +7484,7 @@
         <v>40</v>
       </c>
       <c r="AA28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB28">
         <v>12</v>
@@ -7499,7 +7499,7 @@
         <v>55</v>
       </c>
       <c r="AF28">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -7508,7 +7508,7 @@
         <v>16.5</v>
       </c>
       <c r="AI28">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ28">
         <v>19</v>
@@ -7523,13 +7523,13 @@
         <v>75</v>
       </c>
       <c r="AN28">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO28">
         <v>42</v>
       </c>
       <c r="AP28">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ28">
         <v>20</v>
@@ -7538,25 +7538,25 @@
         <v>36</v>
       </c>
       <c r="AS28">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT28">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU28">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV28">
         <v>17</v>
       </c>
       <c r="AW28">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY28">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ28">
         <v>15</v>
@@ -7577,13 +7577,13 @@
         <v>55</v>
       </c>
       <c r="BF28">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG28">
         <v>36</v>
       </c>
       <c r="BH28">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BI28">
         <v>3.5</v>
@@ -7592,55 +7592,55 @@
         <v>9.4</v>
       </c>
       <c r="BK28">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BL28">
         <v>90</v>
       </c>
       <c r="BM28">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN28">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO28">
         <v>4.1</v>
       </c>
       <c r="BP28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ28">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BR28">
         <v>22</v>
       </c>
       <c r="BS28">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BT28">
         <v>8.800000000000001</v>
       </c>
       <c r="BU28">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV28">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW28">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BX28">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY28">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ28">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA28">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="CB28" t="s">
         <v>173</v>
@@ -7663,16 +7663,16 @@
         <v>165</v>
       </c>
       <c r="F29">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="G29">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H29">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I29">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="J29">
         <v>4.1</v>
@@ -7687,55 +7687,55 @@
         <v>1.02</v>
       </c>
       <c r="N29">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>1.13</v>
       </c>
       <c r="P29">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q29">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R29">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S29">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T29">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="U29">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="V29">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W29">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X29">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y29">
         <v>22</v>
       </c>
       <c r="Z29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA29">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC29">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE29">
         <v>21</v>
@@ -7753,25 +7753,25 @@
         <v>23</v>
       </c>
       <c r="AJ29">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK29">
+        <v>24</v>
+      </c>
+      <c r="AL29">
         <v>25</v>
       </c>
-      <c r="AL29">
-        <v>26</v>
-      </c>
       <c r="AM29">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AN29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO29">
         <v>9.6</v>
       </c>
       <c r="AP29">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ29">
         <v>19</v>
@@ -7780,7 +7780,7 @@
         <v>20</v>
       </c>
       <c r="AS29">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT29">
         <v>22</v>
@@ -7810,16 +7810,16 @@
         <v>42</v>
       </c>
       <c r="BC29">
+        <v>22</v>
+      </c>
+      <c r="BD29">
         <v>23</v>
       </c>
-      <c r="BD29">
-        <v>24</v>
-      </c>
       <c r="BE29">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BF29">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG29">
         <v>8.800000000000001</v>
@@ -7828,7 +7828,7 @@
         <v>5.4</v>
       </c>
       <c r="BI29">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BJ29">
         <v>8.199999999999999</v>
@@ -7840,7 +7840,7 @@
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN29">
         <v>6.8</v>
@@ -7849,16 +7849,16 @@
         <v>6</v>
       </c>
       <c r="BP29">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ29">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR29">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS29">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT29">
         <v>6.4</v>
@@ -7870,19 +7870,19 @@
         <v>15</v>
       </c>
       <c r="BW29">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX29">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BY29">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ29">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA29">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="CB29" t="s">
         <v>173</v>
@@ -7905,61 +7905,61 @@
         <v>166</v>
       </c>
       <c r="F30">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G30">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H30">
+        <v>2.78</v>
+      </c>
+      <c r="I30">
         <v>2.84</v>
       </c>
-      <c r="I30">
-        <v>2.9</v>
-      </c>
       <c r="J30">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K30">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L30">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N30">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O30">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P30">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q30">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R30">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S30">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T30">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U30">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W30">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X30">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Y30">
         <v>14</v>
@@ -7968,7 +7968,7 @@
         <v>21</v>
       </c>
       <c r="AA30">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB30">
         <v>13.5</v>
@@ -7986,34 +7986,34 @@
         <v>19</v>
       </c>
       <c r="AG30">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH30">
         <v>15.5</v>
       </c>
       <c r="AI30">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ30">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AK30">
         <v>26</v>
       </c>
       <c r="AL30">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM30">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN30">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO30">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP30">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ30">
         <v>12.5</v>
@@ -8022,7 +8022,7 @@
         <v>19</v>
       </c>
       <c r="AS30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT30">
         <v>12.5</v>
@@ -8037,10 +8037,10 @@
         <v>26</v>
       </c>
       <c r="AX30">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ30">
         <v>14</v>
@@ -8052,10 +8052,10 @@
         <v>34</v>
       </c>
       <c r="BC30">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE30">
         <v>55</v>
@@ -8064,25 +8064,25 @@
         <v>16.5</v>
       </c>
       <c r="BG30">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH30">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI30">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ30">
         <v>8.800000000000001</v>
       </c>
       <c r="BK30">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="BL30">
         <v>110</v>
       </c>
       <c r="BM30">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BN30">
         <v>5.9</v>
@@ -8091,40 +8091,40 @@
         <v>5</v>
       </c>
       <c r="BP30">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ30">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BR30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT30">
         <v>6</v>
       </c>
-      <c r="BT30">
+      <c r="BU30">
+        <v>5.4</v>
+      </c>
+      <c r="BV30">
+        <v>19.5</v>
+      </c>
+      <c r="BW30">
+        <v>7</v>
+      </c>
+      <c r="BX30">
+        <v>30</v>
+      </c>
+      <c r="BY30">
+        <v>8</v>
+      </c>
+      <c r="BZ30">
+        <v>20</v>
+      </c>
+      <c r="CA30">
         <v>7.2</v>
-      </c>
-      <c r="BU30">
-        <v>4.8</v>
-      </c>
-      <c r="BV30">
-        <v>21</v>
-      </c>
-      <c r="BW30">
-        <v>5.4</v>
-      </c>
-      <c r="BX30">
-        <v>36</v>
-      </c>
-      <c r="BY30">
-        <v>6</v>
-      </c>
-      <c r="BZ30">
-        <v>21</v>
-      </c>
-      <c r="CA30">
-        <v>5.4</v>
       </c>
       <c r="CB30" t="s">
         <v>173</v>
@@ -8147,31 +8147,31 @@
         <v>167</v>
       </c>
       <c r="F31">
+        <v>1.39</v>
+      </c>
+      <c r="G31">
         <v>1.4</v>
       </c>
-      <c r="G31">
-        <v>1.42</v>
-      </c>
       <c r="H31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I31">
         <v>12</v>
       </c>
       <c r="J31">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L31">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M31">
         <v>1.07</v>
       </c>
       <c r="N31">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O31">
         <v>1.33</v>
@@ -8180,16 +8180,16 @@
         <v>1.96</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R31">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S31">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T31">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U31">
         <v>1.68</v>
@@ -8198,16 +8198,16 @@
         <v>1.09</v>
       </c>
       <c r="W31">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="X31">
         <v>15.5</v>
       </c>
       <c r="Y31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z31">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA31">
         <v>490</v>
@@ -8216,40 +8216,40 @@
         <v>7</v>
       </c>
       <c r="AC31">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD31">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE31">
         <v>220</v>
       </c>
       <c r="AF31">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG31">
         <v>10.5</v>
       </c>
       <c r="AH31">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI31">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AJ31">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK31">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM31">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="AN31">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AO31">
         <v>360</v>
@@ -8261,10 +8261,10 @@
         <v>26</v>
       </c>
       <c r="AR31">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AS31">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AT31">
         <v>6.4</v>
@@ -8276,7 +8276,7 @@
         <v>36</v>
       </c>
       <c r="AW31">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AX31">
         <v>6.6</v>
@@ -8288,25 +8288,25 @@
         <v>30</v>
       </c>
       <c r="BA31">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BB31">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BC31">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD31">
         <v>42</v>
       </c>
       <c r="BE31">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF31">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG31">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH31">
         <v>3.5</v>
@@ -8324,7 +8324,7 @@
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN31">
         <v>3.6</v>
@@ -8342,7 +8342,7 @@
         <v>30</v>
       </c>
       <c r="BS31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT31">
         <v>14</v>
@@ -8354,16 +8354,16 @@
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ31">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA31">
         <v>8.4</v>
@@ -8413,25 +8413,25 @@
         <v>1.05</v>
       </c>
       <c r="N32">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O32">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P32">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q32">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R32">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S32">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T32">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U32">
         <v>2.58</v>
@@ -8440,7 +8440,7 @@
         <v>1.47</v>
       </c>
       <c r="W32">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X32">
         <v>21</v>
@@ -8449,16 +8449,16 @@
         <v>16.5</v>
       </c>
       <c r="Z32">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA32">
         <v>46</v>
       </c>
       <c r="AB32">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC32">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD32">
         <v>13</v>
@@ -8467,7 +8467,7 @@
         <v>30</v>
       </c>
       <c r="AF32">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG32">
         <v>11.5</v>
@@ -8485,22 +8485,22 @@
         <v>23</v>
       </c>
       <c r="AL32">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM32">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN32">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP32">
         <v>18</v>
       </c>
       <c r="AQ32">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR32">
         <v>20</v>
@@ -8539,19 +8539,19 @@
         <v>20</v>
       </c>
       <c r="BD32">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE32">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF32">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG32">
         <v>19.5</v>
       </c>
       <c r="BH32">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI32">
         <v>3.3</v>
@@ -8566,10 +8566,10 @@
         <v>100</v>
       </c>
       <c r="BM32">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN32">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO32">
         <v>5</v>
@@ -8578,37 +8578,37 @@
         <v>16</v>
       </c>
       <c r="BQ32">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BR32">
         <v>25</v>
       </c>
       <c r="BS32">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT32">
         <v>6.6</v>
       </c>
       <c r="BU32">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV32">
         <v>21</v>
       </c>
       <c r="BW32">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX32">
         <v>28</v>
       </c>
       <c r="BY32">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ32">
         <v>18</v>
       </c>
       <c r="CA32">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="CB32" t="s">
         <v>173</v>
@@ -8631,52 +8631,52 @@
         <v>169</v>
       </c>
       <c r="F33">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G33">
         <v>2.16</v>
       </c>
       <c r="H33">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I33">
         <v>4.7</v>
       </c>
       <c r="J33">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K33">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L33">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M33">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N33">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O33">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P33">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q33">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="R33">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S33">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="T33">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U33">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V33">
         <v>1.27</v>
@@ -8685,7 +8685,7 @@
         <v>1.86</v>
       </c>
       <c r="X33">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y33">
         <v>11.5</v>
@@ -8697,7 +8697,7 @@
         <v>120</v>
       </c>
       <c r="AB33">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC33">
         <v>7.4</v>
@@ -8718,28 +8718,28 @@
         <v>27</v>
       </c>
       <c r="AI33">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AJ33">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK33">
         <v>32</v>
       </c>
       <c r="AL33">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AM33">
         <v>230</v>
       </c>
       <c r="AN33">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AO33">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="AP33">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ33">
         <v>10</v>
@@ -8763,7 +8763,7 @@
         <v>50</v>
       </c>
       <c r="AX33">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY33">
         <v>10.5</v>
@@ -8775,31 +8775,31 @@
         <v>14</v>
       </c>
       <c r="BB33">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC33">
         <v>27</v>
       </c>
       <c r="BD33">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE33">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BF33">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BG33">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH33">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="BI33">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ33">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK33">
         <v>8.6</v>
@@ -8808,37 +8808,37 @@
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN33">
         <v>4.8</v>
       </c>
       <c r="BO33">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP33">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ33">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT33">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU33">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX33">
         <v>1000</v>
@@ -8850,7 +8850,7 @@
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CB33" t="s">
         <v>173</v>
@@ -8873,22 +8873,22 @@
         <v>170</v>
       </c>
       <c r="F34">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="G34">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="H34">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="I34">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="J34">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K34">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L34">
         <v>1.22</v>
@@ -8897,7 +8897,7 @@
         <v>1.02</v>
       </c>
       <c r="N34">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O34">
         <v>1.12</v>
@@ -8906,55 +8906,55 @@
         <v>3.5</v>
       </c>
       <c r="Q34">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R34">
         <v>2.02</v>
       </c>
       <c r="S34">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="T34">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U34">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V34">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="X34">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Y34">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z34">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA34">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB34">
         <v>24</v>
       </c>
       <c r="AC34">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD34">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE34">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG34">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH34">
         <v>13.5</v>
@@ -8966,109 +8966,109 @@
         <v>40</v>
       </c>
       <c r="AK34">
+        <v>21</v>
+      </c>
+      <c r="AL34">
         <v>22</v>
-      </c>
-      <c r="AL34">
-        <v>23</v>
       </c>
       <c r="AM34">
         <v>38</v>
       </c>
       <c r="AN34">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO34">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP34">
         <v>34</v>
       </c>
       <c r="AQ34">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR34">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS34">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT34">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU34">
         <v>11</v>
       </c>
       <c r="AV34">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW34">
         <v>21</v>
       </c>
       <c r="AX34">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY34">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ34">
         <v>12.5</v>
       </c>
       <c r="BA34">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB34">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BC34">
+        <v>19</v>
+      </c>
+      <c r="BD34">
         <v>20</v>
       </c>
-      <c r="BD34">
-        <v>21</v>
-      </c>
       <c r="BE34">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BF34">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG34">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH34">
         <v>6.6</v>
       </c>
       <c r="BI34">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BJ34">
         <v>8.4</v>
       </c>
       <c r="BK34">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BL34">
         <v>55</v>
       </c>
       <c r="BM34">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BN34">
         <v>7</v>
       </c>
       <c r="BO34">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BP34">
         <v>16.5</v>
       </c>
       <c r="BQ34">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS34">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BT34">
         <v>7</v>
@@ -9077,19 +9077,19 @@
         <v>5.8</v>
       </c>
       <c r="BV34">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW34">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BX34">
         <v>24</v>
       </c>
       <c r="BY34">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BZ34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA34">
         <v>4.3</v>
@@ -9130,40 +9130,40 @@
         <v>3.9</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L35">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M35">
         <v>1.04</v>
       </c>
       <c r="N35">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O35">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P35">
         <v>2.6</v>
       </c>
       <c r="Q35">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R35">
         <v>1.65</v>
       </c>
       <c r="S35">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T35">
         <v>1.54</v>
       </c>
       <c r="U35">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="V35">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W35">
         <v>1.53</v>
@@ -9181,7 +9181,7 @@
         <v>36</v>
       </c>
       <c r="AB35">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC35">
         <v>9.199999999999999</v>
@@ -9190,13 +9190,13 @@
         <v>12</v>
       </c>
       <c r="AE35">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF35">
         <v>23</v>
       </c>
       <c r="AG35">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH35">
         <v>13.5</v>
@@ -9217,7 +9217,7 @@
         <v>60</v>
       </c>
       <c r="AN35">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO35">
         <v>13.5</v>
@@ -9229,13 +9229,13 @@
         <v>14.5</v>
       </c>
       <c r="AR35">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS35">
         <v>30</v>
       </c>
       <c r="AT35">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU35">
         <v>8.800000000000001</v>
@@ -9274,10 +9274,10 @@
         <v>15</v>
       </c>
       <c r="BG35">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH35">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI35">
         <v>3.5</v>
@@ -9286,13 +9286,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK35">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL35">
         <v>75</v>
       </c>
       <c r="BM35">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN35">
         <v>6.6</v>
@@ -9304,13 +9304,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ35">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR35">
         <v>26</v>
       </c>
       <c r="BS35">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT35">
         <v>6</v>
@@ -9328,13 +9328,13 @@
         <v>24</v>
       </c>
       <c r="BY35">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ35">
         <v>16</v>
       </c>
       <c r="CA35">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB35" t="s">
         <v>173</v>
@@ -9372,37 +9372,37 @@
         <v>4.3</v>
       </c>
       <c r="K36">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L36">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M36">
         <v>1.03</v>
       </c>
       <c r="N36">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="O36">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P36">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q36">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="R36">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="S36">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="T36">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U36">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="V36">
         <v>1.34</v>
@@ -9411,19 +9411,19 @@
         <v>2.04</v>
       </c>
       <c r="X36">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y36">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z36">
         <v>36</v>
       </c>
       <c r="AA36">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB36">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC36">
         <v>11</v>
@@ -9432,10 +9432,10 @@
         <v>16.5</v>
       </c>
       <c r="AE36">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF36">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG36">
         <v>11</v>
@@ -9444,52 +9444,52 @@
         <v>14</v>
       </c>
       <c r="AI36">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ36">
         <v>26</v>
       </c>
       <c r="AK36">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL36">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM36">
+        <v>46</v>
+      </c>
+      <c r="AN36">
+        <v>7</v>
+      </c>
+      <c r="AO36">
+        <v>21</v>
+      </c>
+      <c r="AP36">
+        <v>30</v>
+      </c>
+      <c r="AQ36">
+        <v>24</v>
+      </c>
+      <c r="AR36">
+        <v>34</v>
+      </c>
+      <c r="AS36">
         <v>50</v>
       </c>
-      <c r="AN36">
-        <v>7.4</v>
-      </c>
-      <c r="AO36">
-        <v>24</v>
-      </c>
-      <c r="AP36">
-        <v>28</v>
-      </c>
-      <c r="AQ36">
-        <v>21</v>
-      </c>
-      <c r="AR36">
+      <c r="AT36">
+        <v>16</v>
+      </c>
+      <c r="AU36">
+        <v>10.5</v>
+      </c>
+      <c r="AV36">
+        <v>15</v>
+      </c>
+      <c r="AW36">
         <v>32</v>
       </c>
-      <c r="AS36">
-        <v>60</v>
-      </c>
-      <c r="AT36">
-        <v>15</v>
-      </c>
-      <c r="AU36">
-        <v>10</v>
-      </c>
-      <c r="AV36">
-        <v>14.5</v>
-      </c>
-      <c r="AW36">
-        <v>30</v>
-      </c>
       <c r="AX36">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY36">
         <v>10</v>
@@ -9498,46 +9498,46 @@
         <v>13</v>
       </c>
       <c r="BA36">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB36">
         <v>23</v>
       </c>
       <c r="BC36">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD36">
         <v>20</v>
       </c>
       <c r="BE36">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF36">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG36">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH36">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BI36">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BJ36">
         <v>8.6</v>
       </c>
       <c r="BK36">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BL36">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BM36">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN36">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BO36">
         <v>4.8</v>
@@ -9546,13 +9546,13 @@
         <v>12</v>
       </c>
       <c r="BQ36">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BR36">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BS36">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT36">
         <v>7.8</v>
@@ -9564,16 +9564,16 @@
         <v>29</v>
       </c>
       <c r="BW36">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX36">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY36">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ36">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="CA36">
         <v>5.5</v>
